--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/rjuan_mgcontecnica_com_br/Documents/Área de Trabalho/Python/Chamados/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{75ABA41F-6853-49EB-94D9-045052CC97E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{75ABA41F-6853-49EB-94D9-045052CC97E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EF1F885-3587-41C9-8283-38A4DFB25A80}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{45AA7DE4-8F9A-4240-A45C-A0DC1A65219E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{45AA7DE4-8F9A-4240-A45C-A0DC1A65219E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="137">
   <si>
     <t>Id</t>
   </si>
@@ -101,142 +101,46 @@
     <t>GC - ADMINISTRATIVO</t>
   </si>
   <si>
-    <t>Prezados, boa tarde!Segue pendência na Ata de Reunião IMPOSTOS EM DEDUÇÃO DE VENDAS	Avaliar contabilização de Impostos s/vendas, pois cliente indica que o valor esta a menor em R$ 100 mil, o que prejudica a apuração de IRPJ/CSLL do primeiro trimestre de 2026.</t>
-  </si>
-  <si>
-    <t>BANDEIRANTES REFRIGERAÇÃO COMERCIAL LTDA</t>
-  </si>
-  <si>
-    <t>Erika Santana</t>
-  </si>
-  <si>
-    <t>CTB - CONTÁBIL INDUSTRIA</t>
-  </si>
-  <si>
-    <t>Atendido</t>
-  </si>
-  <si>
     <t>Victoria Virgens</t>
   </si>
   <si>
-    <t xml:space="preserve">Foi revisado antes da apuração do IRPJ/CSLL </t>
-  </si>
-  <si>
     <t>Reunião externa</t>
   </si>
   <si>
-    <t>Enviar guia para pagamentoEnviar guia para pagamento</t>
-  </si>
-  <si>
     <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
   </si>
   <si>
-    <t>Renata Cavalheiro</t>
-  </si>
-  <si>
     <t>CTB - CONTÁBIL VAREJO</t>
   </si>
   <si>
     <t>Bruno Contieri</t>
   </si>
   <si>
-    <t>De qual imposto se refere?</t>
-  </si>
-  <si>
-    <t>Verificar valores ref. 11/2025 em aberto qual a origem dos débitos e enviar ao cliente para pagamentoverificar SITUAÇÃO FISCAL</t>
-  </si>
-  <si>
-    <t>SUPERMERCADO YAMATO LTDA</t>
-  </si>
-  <si>
-    <t>ok</t>
-  </si>
-  <si>
-    <t>Bom dia.SUPER PREÇO.1ASSUNTO: Pro LaborePENDÊNCIA: Os sócios Herick, Emerson e Fabiana irão retirar Prolabore pela H.E.F - Teto maximo de contribuição2ASSUNTO: SCI REPORT - DRIVE - RHNETPENDÊNCIA: Cliente quer trenamento para utilizar o sistema 100%. Disse que o Leandro explicou para ele, porém não ficou claro. Favor agendar treinamento</t>
-  </si>
-  <si>
     <t>H E F COMERCIO DE OPORTUNIDADES LTDA</t>
   </si>
   <si>
-    <t>Tania Luz</t>
-  </si>
-  <si>
     <t>DP - DEPTO. PESSOAL</t>
   </si>
   <si>
     <t>Daniel Oliveira</t>
   </si>
   <si>
-    <t>solicitações atendidas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estoque:Informado sobre a importância do envio das informações, cliente informou que foram disponibilizados pelo DriveDistribuição de lucros:Foi feita distribuição de 200.000 ao sócio em 27/02, verificar se foi feita a apuração do IRPF, além de fazer 20.000 de retirada todos os meses	</t>
-  </si>
-  <si>
     <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
   </si>
   <si>
     <t>Tatiana Linardi</t>
   </si>
   <si>
-    <t>Bom dia.JAPÃOASSUNTO: e-CACPENDÊNCIA: "Apresentados consultas com pendências.Guias referentes os valores residuais previdenciários disponibilizados ao cliente para pagamento.Pendências de entrega DCTFWeb, por gentileza proceder conforme e-mail enviado."</t>
-  </si>
-  <si>
     <t xml:space="preserve">DISTRIBUIDORA DE ALIMENTOS JAPÃO LTDA </t>
   </si>
   <si>
-    <t xml:space="preserve">Resolvido por email </t>
-  </si>
-  <si>
-    <t>Bom dia.ÁGUA LIMPA - KURODAASSUNTO: e-CACPENDÊNCIA: Apresentado pendências referentes IRPJ e CSLL 1° Trim./2025. Por gentileza, verificar se não se trata de divergência em declarações. Caso, sim, por gentileza regularizar (conforme e-mail enviado).</t>
-  </si>
-  <si>
     <t>ÁGUA LIMPA DISTRIBUIDORA DE HORTIFRUTI, ALIMENTOS E SERVIÇOS DE TRANSPORTES LTDA.</t>
   </si>
   <si>
-    <t>Bom dia.Quitandão  CordeirópolisASSUNTO: Correção EstoquesPENDÊNCIA: "Por gentileza proceder com a correção dos estoques, sendo:01/2026: 4.370.565,0802/2026: 4.583.908,15Ajustes a serem realizados na matriz (4821)"</t>
-  </si>
-  <si>
     <t>RODRIGUES &amp; PEREIRA CORDEIROPOLIS LTDA</t>
   </si>
   <si>
-    <t>Bom dia.Quitandão  CordeirópolisASSUNTO: VerificaçãoPENDÊNCIA: Por gentileza verificar a conta "outros tributos a compensar" (ativo circulante) e correções necessárias, com saldo negativo em R$ 124.375,71.</t>
-  </si>
-  <si>
-    <t>Bom dia.Quitandão  CordeirópolisASSUNTO: Créditos tributáriosPENDÊNCIA: "Como é de conhecimento, cliente está realizando compensação de créditos tributários. Por gentileza providenciar as contabilizações e correção dos balancetes.Verificar e-mail enviado com as observações e apontamentos detalhados para correção."</t>
-  </si>
-  <si>
-    <t>Bom dia.Quitandão  CordeirópolisASSUNTO: e-CACPENDÊNCIA: Pendências PIS e COFINS 09/2020 e demais pendências 2020 precisam ser analisadas, pois não existiam as pendências.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Respondido por email </t>
-  </si>
-  <si>
-    <t>Bom dia.VIT FRUT - AR4ASSUNTO: Recebimento LucrosPENDÊNCIA: Verificar porque os valores mensais que a empresa está recebendo de lucros da empresa POMAR (GRUPO VARANDA) está sendo contabilizado como adiantamento á Socios.</t>
-  </si>
-  <si>
     <t>AR4 TAVARES PARTICIPAÇÕES LTDA</t>
-  </si>
-  <si>
-    <t>Vai distribuir esse valor ???</t>
-  </si>
-  <si>
-    <t>Bom dia.Quitandão  CordeirópolisASSUNTO: Empréstimos sóciosPENDÊNCIA: "26/02/2026: Os sócios realizaram empréstimos no total de R$ 1.200.000,00, os quais serão devolvidos à eles nos próximos meses.Por gentileza contabilizar as entradas via banco corretamente, para viabilizar as devoluções na contabilidade corretamente."</t>
-  </si>
-  <si>
-    <t>não identificamos essa operação de entrada, as unicas informações que recebemos mensalmente são os valores de distribuição de lucros feito via caixa</t>
-  </si>
-  <si>
-    <t>Bom dia.VIT FRUT - AR4ASSUNTO: Distr LucrosPENDÊNCIA: Fazer a distribuição de 2025 conforme saídas em 2025 para Alice.</t>
-  </si>
-  <si>
-    <t>No aguardo do GM posicionar o que vamos fazer, pois não temos lucro.</t>
-  </si>
-  <si>
-    <t>Verificar conta 928791 - Empréstimo Stone - Cliente não possui empréstimo. Verificar/Conciliar a conta 491 - INSS -  valor a pagar muito alto em aberto.Verificar/Conciliar a conta 574 e 215 - Adiantamento - cliente não possui.Verificar/Conciliar a Grupo 110 - Cartões - Saldo em 30/06/2025 no valor de $ 46.510,60! Cliente manda relatório mensalmente!Verificar/Conciliar a Conta 912 - Valor lançado de 122mil, em janeiro de 2026.Distribuição de Lucros em 2025, para Sr. Wilson Pereira R$ 85.700,00 e Wellington Pereira R$ 64.000,00, conforme relatório. Por favor alterar e enviar novo informe de rendimento para o cliente!</t>
-  </si>
-  <si>
-    <t>WW JOTAW LTDA</t>
   </si>
   <si>
     <t>Ricardo Ferreira</t>
@@ -592,10 +496,10 @@
   </cellStyles>
   <dxfs count="3">
     <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="27" formatCode="dd/mm/yyyy\ hh:mm"/>
@@ -614,8 +518,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}" name="Tabela2" displayName="Tabela2" ref="A1:Q60" totalsRowShown="0">
-  <autoFilter ref="A1:Q60" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}" name="Tabela2" displayName="Tabela2" ref="A1:Q45" totalsRowShown="0">
+  <autoFilter ref="A1:Q45" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{5F184F27-3CF1-414F-86B8-9CC4716D84CF}" name="Id"/>
     <tableColumn id="2" xr3:uid="{1D77350B-469D-463F-A5E2-FCE238DF5E95}" name="Categoria"/>
@@ -626,12 +530,12 @@
     <tableColumn id="7" xr3:uid="{5DA79EC8-A301-43B3-898A-C688606648AB}" name="Cliente"/>
     <tableColumn id="8" xr3:uid="{EA87443E-4E8D-4EDE-A773-CD0BE90ACA01}" name="Responsável"/>
     <tableColumn id="9" xr3:uid="{515AA978-E26B-4441-8971-C0088B305A3F}" name="Departamento Responsavel"/>
-    <tableColumn id="10" xr3:uid="{4DC0FC52-9891-4537-AACE-43134F942CD2}" name="Data Cadastro" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{7C7F3F0B-65B8-4752-ADB4-28F5268C7430}" name="Prazo Vencimento" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{4DC0FC52-9891-4537-AACE-43134F942CD2}" name="Data Cadastro" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{7C7F3F0B-65B8-4752-ADB4-28F5268C7430}" name="Prazo Vencimento" dataDxfId="1"/>
     <tableColumn id="12" xr3:uid="{E555C0D4-65E8-4628-8EC8-B39211F6DA49}" name="Status"/>
     <tableColumn id="13" xr3:uid="{46B84291-95B5-4E76-B08D-BFE3B6D965C2}" name="Solicitante"/>
     <tableColumn id="14" xr3:uid="{BE56CE2A-3639-465F-9D35-E5FA5EED5FFC}" name="Inicio Atend."/>
-    <tableColumn id="15" xr3:uid="{36EAF47C-C1C5-478A-B2BD-B9F9B7B73864}" name="Data Entrega" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{36EAF47C-C1C5-478A-B2BD-B9F9B7B73864}" name="Data Entrega" dataDxfId="0"/>
     <tableColumn id="16" xr3:uid="{80FBDD9B-AE41-4426-890E-D1F5E628A549}" name="Responsável pela conclusão"/>
     <tableColumn id="17" xr3:uid="{5BEA926D-7D70-41A0-9356-00B391210CA1}" name="Ultimo Comentário"/>
   </tableColumns>
@@ -956,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211084A7-C91A-468E-BA90-602A3F34D72B}">
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
@@ -1031,213 +935,189 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>79113</v>
+        <v>79467</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
         <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F2">
-        <v>1119</v>
+        <v>1931</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="J2" s="1">
-        <v>46153.574119907411</v>
+        <v>46168.598741817128</v>
       </c>
       <c r="K2" s="2">
-        <v>46160</v>
+        <v>46170</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O2" s="1">
-        <v>46154.706851967596</v>
-      </c>
-      <c r="P2" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="Q2" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>78446</v>
+        <v>79470</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="F3">
-        <v>5100</v>
+        <v>4218</v>
       </c>
       <c r="G3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J3" s="1">
-        <v>46114.576648113427</v>
+        <v>46168.607073761574</v>
       </c>
       <c r="K3" s="2">
-        <v>46121</v>
+        <v>46170</v>
       </c>
       <c r="L3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O3" s="1">
-        <v>46114.619850034724</v>
-      </c>
-      <c r="P3" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>78425</v>
+        <v>79464</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D4" t="s">
         <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F4">
-        <v>1180</v>
+        <v>4327</v>
       </c>
       <c r="G4" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J4" s="1">
-        <v>46113.689436840279</v>
+        <v>46168.513686921295</v>
       </c>
       <c r="K4" s="2">
-        <v>46120</v>
+        <v>46170</v>
       </c>
       <c r="L4" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M4" t="s">
-        <v>32</v>
-      </c>
-      <c r="O4" s="1">
-        <v>46114.620315891203</v>
-      </c>
-      <c r="P4" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="Q4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>78500</v>
+        <v>79469</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
         <v>19</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F5">
-        <v>6293</v>
+        <v>2209</v>
       </c>
       <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
         <v>38</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>39</v>
       </c>
-      <c r="I5" t="s">
-        <v>40</v>
-      </c>
       <c r="J5" s="1">
-        <v>46119.459494328701</v>
+        <v>46168.605940706017</v>
       </c>
       <c r="K5" s="2">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M5" t="s">
         <v>41</v>
       </c>
-      <c r="O5" s="1">
-        <v>46160.743096990744</v>
-      </c>
-      <c r="P5" t="s">
-        <v>39</v>
-      </c>
       <c r="Q5" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>78612</v>
+        <v>79471</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>19</v>
@@ -1246,92 +1126,74 @@
         <v>43</v>
       </c>
       <c r="F6">
-        <v>6621</v>
+        <v>5026</v>
       </c>
       <c r="G6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J6" s="1">
-        <v>46125.593314467595</v>
+        <v>46168.608738460651</v>
       </c>
       <c r="K6" s="2">
-        <v>46132</v>
+        <v>46170</v>
       </c>
       <c r="L6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>32</v>
-      </c>
-      <c r="O6" s="1">
-        <v>46125.72338599537</v>
-      </c>
-      <c r="P6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>78493</v>
+        <v>79502</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
         <v>19</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7">
-        <v>2046</v>
+        <v>5165</v>
       </c>
       <c r="G7" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J7" s="1">
-        <v>46119.437933912035</v>
+        <v>46169.514836111113</v>
       </c>
       <c r="K7" s="2">
-        <v>46140</v>
+        <v>46181</v>
       </c>
       <c r="L7" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="1">
-        <v>46119.66213271991</v>
-      </c>
-      <c r="P7" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>78496</v>
+        <v>78854</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
@@ -1343,45 +1205,39 @@
         <v>19</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8">
-        <v>3627</v>
+        <v>4811</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H8" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J8" s="1">
-        <v>46119.439394791669</v>
+        <v>46134.747386261573</v>
       </c>
       <c r="K8" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="L8" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" t="s">
         <v>24</v>
       </c>
-      <c r="M8" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="1">
-        <v>46119.663940509257</v>
-      </c>
-      <c r="P8" t="s">
-        <v>45</v>
-      </c>
       <c r="Q8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>78502</v>
+        <v>78445</v>
       </c>
       <c r="B9" t="s">
         <v>17</v>
@@ -1393,45 +1249,39 @@
         <v>19</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F9">
-        <v>4821</v>
+        <v>5100</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="H9" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="I9" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J9" s="1">
-        <v>46119.490702083334</v>
+        <v>46114.575707291668</v>
       </c>
       <c r="K9" s="2">
-        <v>46140</v>
+        <v>46121</v>
       </c>
       <c r="L9" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="1">
-        <v>46119.66440671296</v>
-      </c>
-      <c r="P9" t="s">
-        <v>45</v>
-      </c>
       <c r="Q9" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>78503</v>
+        <v>78447</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
@@ -1443,45 +1293,39 @@
         <v>19</v>
       </c>
       <c r="E10" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F10">
-        <v>4821</v>
+        <v>5740</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I10" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J10" s="1">
-        <v>46119.491110451389</v>
+        <v>46114.582553275461</v>
       </c>
       <c r="K10" s="2">
-        <v>46140</v>
+        <v>46121</v>
       </c>
       <c r="L10" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="1">
-        <v>46119.664769988427</v>
-      </c>
-      <c r="P10" t="s">
-        <v>45</v>
-      </c>
       <c r="Q10" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>78504</v>
+        <v>78614</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
@@ -1493,45 +1337,39 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F11">
-        <v>4821</v>
+        <v>6621</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I11" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J11" s="1">
-        <v>46119.491527858794</v>
+        <v>46125.594015162038</v>
       </c>
       <c r="K11" s="2">
-        <v>46140</v>
+        <v>46132</v>
       </c>
       <c r="L11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M11" t="s">
         <v>24</v>
       </c>
-      <c r="M11" t="s">
-        <v>41</v>
-      </c>
-      <c r="O11" s="1">
-        <v>46119.665339583335</v>
-      </c>
-      <c r="P11" t="s">
-        <v>45</v>
-      </c>
       <c r="Q11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>78506</v>
+        <v>78615</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1543,45 +1381,39 @@
         <v>19</v>
       </c>
       <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>6622</v>
+      </c>
+      <c r="G12" t="s">
+        <v>62</v>
+      </c>
+      <c r="H12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I12" t="s">
         <v>55</v>
       </c>
-      <c r="F12">
-        <v>4821</v>
-      </c>
-      <c r="G12" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" t="s">
-        <v>31</v>
-      </c>
       <c r="J12" s="1">
-        <v>46119.492292326388</v>
+        <v>46125.594442326386</v>
       </c>
       <c r="K12" s="2">
-        <v>46140</v>
+        <v>46132</v>
       </c>
       <c r="L12" t="s">
+        <v>40</v>
+      </c>
+      <c r="M12" t="s">
         <v>24</v>
       </c>
-      <c r="M12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="1">
-        <v>46119.668346064813</v>
-      </c>
-      <c r="P12" t="s">
-        <v>45</v>
-      </c>
       <c r="Q12" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>78512</v>
+        <v>79022</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
@@ -1593,48 +1425,42 @@
         <v>19</v>
       </c>
       <c r="E13" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F13">
-        <v>4115</v>
+        <v>5843</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J13" s="1">
-        <v>46119.496058020835</v>
+        <v>46148.468115243057</v>
       </c>
       <c r="K13" s="2">
-        <v>46140</v>
+        <v>46157</v>
       </c>
       <c r="L13" t="s">
+        <v>40</v>
+      </c>
+      <c r="M13" t="s">
         <v>24</v>
       </c>
-      <c r="M13" t="s">
-        <v>41</v>
-      </c>
-      <c r="O13" s="1">
-        <v>46119.671099537038</v>
-      </c>
-      <c r="P13" t="s">
-        <v>45</v>
-      </c>
       <c r="Q13" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>78505</v>
+        <v>78847</v>
       </c>
       <c r="B14" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
@@ -1643,45 +1469,33 @@
         <v>19</v>
       </c>
       <c r="E14" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="F14">
-        <v>4821</v>
+        <v>5350</v>
       </c>
       <c r="G14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="I14" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J14" s="1">
-        <v>46119.491888159719</v>
+        <v>46134.669651932869</v>
       </c>
       <c r="K14" s="2">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="L14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M14" t="s">
         <v>24</v>
-      </c>
-      <c r="M14" t="s">
-        <v>41</v>
-      </c>
-      <c r="O14" s="1">
-        <v>46119.675743518521</v>
-      </c>
-      <c r="P14" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>78513</v>
+        <v>78613</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
@@ -1693,45 +1507,33 @@
         <v>19</v>
       </c>
       <c r="E15" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F15">
-        <v>4115</v>
+        <v>6621</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
-      </c>
-      <c r="H15" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J15" s="1">
-        <v>46119.496526041665</v>
+        <v>46125.593685185187</v>
       </c>
       <c r="K15" s="2">
-        <v>46140</v>
+        <v>46132</v>
       </c>
       <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" t="s">
         <v>24</v>
-      </c>
-      <c r="M15" t="s">
-        <v>41</v>
-      </c>
-      <c r="O15" s="1">
-        <v>46125.752609340278</v>
-      </c>
-      <c r="P15" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>78410</v>
+        <v>78497</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
@@ -1743,303 +1545,303 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16">
-        <v>5001</v>
+        <v>2992</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H16" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J16" s="1">
-        <v>46113.58232306713</v>
+        <v>46119.440335613428</v>
       </c>
       <c r="K16" s="2">
-        <v>46127</v>
+        <v>46140</v>
       </c>
       <c r="L16" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="M16" t="s">
-        <v>66</v>
-      </c>
-      <c r="O16" s="1">
-        <v>46113.684197719907</v>
-      </c>
-      <c r="P16" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="Q16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>79467</v>
+        <v>79370</v>
       </c>
       <c r="B17" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
         <v>19</v>
       </c>
       <c r="E17" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F17">
-        <v>1931</v>
+        <v>6179</v>
       </c>
       <c r="G17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H17" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I17" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J17" s="1">
-        <v>46168.598741817128</v>
+        <v>46161.656835995367</v>
       </c>
       <c r="K17" s="2">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="L17" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M17" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q17" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>79470</v>
+        <v>79371</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C18" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D18" t="s">
         <v>19</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F18">
-        <v>4218</v>
+        <v>6159</v>
       </c>
       <c r="G18" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H18" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="I18" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J18" s="1">
-        <v>46168.607073761574</v>
+        <v>46161.657618368059</v>
       </c>
       <c r="K18" s="2">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M18" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q18" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>79464</v>
+        <v>78495</v>
       </c>
       <c r="B19" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
       </c>
       <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19">
+        <v>1778</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
         <v>77</v>
       </c>
-      <c r="F19">
-        <v>4327</v>
-      </c>
-      <c r="G19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s">
-        <v>70</v>
-      </c>
       <c r="I19" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J19" s="1">
-        <v>46168.513686921295</v>
+        <v>46119.438558912036</v>
       </c>
       <c r="K19" s="2">
-        <v>46170</v>
+        <v>46140</v>
       </c>
       <c r="L19" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q19" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>79469</v>
+        <v>79376</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
         <v>19</v>
       </c>
       <c r="E20" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F20">
-        <v>2209</v>
+        <v>1778</v>
       </c>
       <c r="G20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H20" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J20" s="1">
-        <v>46168.605940706017</v>
+        <v>46161.662515509262</v>
       </c>
       <c r="K20" s="2">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="L20" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M20" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q20" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>79471</v>
+        <v>79377</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D21" t="s">
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F21">
-        <v>5026</v>
+        <v>1778</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J21" s="1">
-        <v>46168.608738460651</v>
+        <v>46161.663288229167</v>
       </c>
       <c r="K21" s="2">
-        <v>46170</v>
+        <v>46175</v>
       </c>
       <c r="L21" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M21" t="s">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="Q21" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>79502</v>
+        <v>79369</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="D22" t="s">
         <v>19</v>
       </c>
       <c r="E22" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22">
+        <v>3627</v>
+      </c>
+      <c r="G22" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" t="s">
         <v>81</v>
       </c>
-      <c r="F22">
-        <v>5165</v>
-      </c>
-      <c r="G22" t="s">
-        <v>82</v>
-      </c>
       <c r="I22" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="J22" s="1">
-        <v>46169.514836111113</v>
+        <v>46161.65612349537</v>
       </c>
       <c r="K22" s="2">
-        <v>46181</v>
+        <v>46175</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="M22" t="s">
-        <v>73</v>
+        <v>27</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>78854</v>
+        <v>79378</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -2051,39 +1853,39 @@
         <v>19</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F23">
-        <v>4811</v>
+        <v>2857</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="I23" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J23" s="1">
-        <v>46134.747386261573</v>
+        <v>46161.664008368054</v>
       </c>
       <c r="K23" s="2">
-        <v>46142</v>
+        <v>46175</v>
       </c>
       <c r="L23" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M23" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>78445</v>
+        <v>79372</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
@@ -2095,39 +1897,39 @@
         <v>19</v>
       </c>
       <c r="E24" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F24">
-        <v>5100</v>
+        <v>3970</v>
       </c>
       <c r="G24" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="H24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="I24" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J24" s="1">
-        <v>46114.575707291668</v>
+        <v>46161.659104513892</v>
       </c>
       <c r="K24" s="2">
-        <v>46121</v>
+        <v>46175</v>
       </c>
       <c r="L24" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M24" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q24" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>78447</v>
+        <v>79375</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
@@ -2139,39 +1941,39 @@
         <v>19</v>
       </c>
       <c r="E25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F25">
-        <v>5740</v>
+        <v>2564</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="I25" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J25" s="1">
-        <v>46114.582553275461</v>
+        <v>46161.661440011572</v>
       </c>
       <c r="K25" s="2">
-        <v>46121</v>
+        <v>46175</v>
       </c>
       <c r="L25" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M25" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>78614</v>
+        <v>78507</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
@@ -2183,39 +1985,39 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F26">
-        <v>6621</v>
+        <v>6293</v>
       </c>
       <c r="G26" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="J26" s="1">
-        <v>46125.594015162038</v>
+        <v>46119.492916006944</v>
       </c>
       <c r="K26" s="2">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="L26" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M26" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q26" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>78615</v>
+        <v>78508</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
@@ -2227,39 +2029,39 @@
         <v>19</v>
       </c>
       <c r="E27" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27">
+        <v>1767</v>
+      </c>
+      <c r="G27" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" t="s">
         <v>93</v>
       </c>
-      <c r="F27">
-        <v>6622</v>
-      </c>
-      <c r="G27" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" t="s">
-        <v>92</v>
-      </c>
       <c r="I27" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J27" s="1">
-        <v>46125.594442326386</v>
+        <v>46119.493672222219</v>
       </c>
       <c r="K27" s="2">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="L27" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M27" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>79022</v>
+        <v>78509</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
@@ -2271,77 +2073,83 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F28">
-        <v>5843</v>
+        <v>1767</v>
       </c>
       <c r="G28" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H28" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I28" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J28" s="1">
-        <v>46148.468115243057</v>
+        <v>46119.49403483796</v>
       </c>
       <c r="K28" s="2">
-        <v>46157</v>
+        <v>46140</v>
       </c>
       <c r="L28" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M28" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="Q28" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>78847</v>
+        <v>78510</v>
       </c>
       <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29">
+        <v>1767</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
+      </c>
+      <c r="H29" t="s">
+        <v>93</v>
+      </c>
+      <c r="I29" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="1">
+        <v>46119.494437384259</v>
+      </c>
+      <c r="K29" s="2">
+        <v>46140</v>
+      </c>
+      <c r="L29" t="s">
+        <v>40</v>
+      </c>
+      <c r="M29" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" t="s">
-        <v>19</v>
-      </c>
-      <c r="E29" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29">
-        <v>5350</v>
-      </c>
-      <c r="G29" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" t="s">
-        <v>40</v>
-      </c>
-      <c r="J29" s="1">
-        <v>46134.669651932869</v>
-      </c>
-      <c r="K29" s="2">
-        <v>46142</v>
-      </c>
-      <c r="L29" t="s">
-        <v>83</v>
-      </c>
-      <c r="M29" t="s">
-        <v>32</v>
+      <c r="Q29" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>78613</v>
+        <v>78511</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -2353,33 +2161,39 @@
         <v>19</v>
       </c>
       <c r="E30" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F30">
-        <v>6621</v>
+        <v>1767</v>
       </c>
       <c r="G30" t="s">
-        <v>44</v>
+        <v>92</v>
+      </c>
+      <c r="H30" t="s">
+        <v>93</v>
       </c>
       <c r="I30" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="J30" s="1">
-        <v>46125.593685185187</v>
+        <v>46119.494797303239</v>
       </c>
       <c r="K30" s="2">
-        <v>46132</v>
+        <v>46140</v>
       </c>
       <c r="L30" t="s">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="M30" t="s">
-        <v>32</v>
+        <v>27</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>78497</v>
+        <v>78514</v>
       </c>
       <c r="B31" t="s">
         <v>17</v>
@@ -2391,39 +2205,39 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F31">
-        <v>2992</v>
+        <v>4115</v>
       </c>
       <c r="G31" t="s">
-        <v>102</v>
+        <v>33</v>
       </c>
       <c r="H31" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="I31" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J31" s="1">
-        <v>46119.440335613428</v>
+        <v>46119.4968878125</v>
       </c>
       <c r="K31" s="2">
         <v>46140</v>
       </c>
       <c r="L31" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M31" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q31" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>79370</v>
+        <v>78492</v>
       </c>
       <c r="B32" t="s">
         <v>17</v>
@@ -2435,39 +2249,42 @@
         <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F32">
-        <v>6179</v>
+        <v>2046</v>
       </c>
       <c r="G32" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>97</v>
+        <v>29</v>
       </c>
       <c r="I32" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J32" s="1">
-        <v>46161.656835995367</v>
+        <v>46119.436787928244</v>
       </c>
       <c r="K32" s="2">
-        <v>46175</v>
+        <v>46140</v>
       </c>
       <c r="L32" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="M32" t="s">
-        <v>41</v>
+        <v>27</v>
+      </c>
+      <c r="N32">
+        <v>46119.673519525466</v>
       </c>
       <c r="Q32" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>79371</v>
+        <v>79373</v>
       </c>
       <c r="B33" t="s">
         <v>17</v>
@@ -2479,39 +2296,39 @@
         <v>19</v>
       </c>
       <c r="E33" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F33">
-        <v>6159</v>
+        <v>4821</v>
       </c>
       <c r="G33" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="I33" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J33" s="1">
-        <v>46161.657618368059</v>
+        <v>46161.659884918983</v>
       </c>
       <c r="K33" s="2">
         <v>46175</v>
       </c>
       <c r="L33" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M33" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q33" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>78495</v>
+        <v>79374</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -2523,215 +2340,197 @@
         <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F34">
-        <v>1778</v>
+        <v>4821</v>
       </c>
       <c r="G34" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="I34" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J34" s="1">
-        <v>46119.438558912036</v>
+        <v>46161.660798726851</v>
       </c>
       <c r="K34" s="2">
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="L34" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M34" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="Q34" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>79376</v>
+        <v>79499</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="F35">
-        <v>1778</v>
+        <v>4585</v>
       </c>
       <c r="G35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H35" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="I35" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J35" s="1">
-        <v>46161.662515509262</v>
+        <v>46169.502877511572</v>
       </c>
       <c r="K35" s="2">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="L35" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M35" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="Q35" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>79377</v>
+        <v>79500</v>
       </c>
       <c r="B36" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D36" t="s">
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F36">
-        <v>1778</v>
+        <v>3916</v>
       </c>
       <c r="G36" t="s">
-        <v>108</v>
-      </c>
-      <c r="H36" t="s">
         <v>109</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J36" s="1">
-        <v>46161.663288229167</v>
+        <v>46169.507391319443</v>
       </c>
       <c r="K36" s="2">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="L36" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M36" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>79369</v>
+        <v>79506</v>
       </c>
       <c r="B37" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D37" t="s">
         <v>19</v>
       </c>
       <c r="E37" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37">
+        <v>2744</v>
+      </c>
+      <c r="G37" t="s">
+        <v>111</v>
+      </c>
+      <c r="I37" t="s">
+        <v>23</v>
+      </c>
+      <c r="J37" s="1">
+        <v>46169.623843090281</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46181</v>
+      </c>
+      <c r="L37" t="s">
+        <v>51</v>
+      </c>
+      <c r="M37" t="s">
         <v>112</v>
-      </c>
-      <c r="F37">
-        <v>3627</v>
-      </c>
-      <c r="G37" t="s">
-        <v>50</v>
-      </c>
-      <c r="H37" t="s">
-        <v>113</v>
-      </c>
-      <c r="I37" t="s">
-        <v>31</v>
-      </c>
-      <c r="J37" s="1">
-        <v>46161.65612349537</v>
-      </c>
-      <c r="K37" s="2">
-        <v>46175</v>
-      </c>
-      <c r="L37" t="s">
-        <v>72</v>
-      </c>
-      <c r="M37" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>79378</v>
+        <v>79515</v>
       </c>
       <c r="B38" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C38" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
       </c>
       <c r="E38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F38">
+        <v>1948</v>
+      </c>
+      <c r="G38" t="s">
         <v>114</v>
       </c>
-      <c r="F38">
-        <v>2857</v>
-      </c>
-      <c r="G38" t="s">
-        <v>115</v>
-      </c>
-      <c r="H38" t="s">
-        <v>113</v>
-      </c>
       <c r="I38" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J38" s="1">
-        <v>46161.664008368054</v>
+        <v>46169.730614618056</v>
       </c>
       <c r="K38" s="2">
-        <v>46175</v>
+        <v>46181</v>
       </c>
       <c r="L38" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M38" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>79372</v>
+        <v>78607</v>
       </c>
       <c r="B39" t="s">
         <v>17</v>
@@ -2743,39 +2542,39 @@
         <v>19</v>
       </c>
       <c r="E39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39">
+        <v>5142</v>
+      </c>
+      <c r="G39" t="s">
         <v>116</v>
       </c>
-      <c r="F39">
-        <v>3970</v>
-      </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>117</v>
       </c>
-      <c r="H39" t="s">
-        <v>118</v>
-      </c>
       <c r="I39" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J39" s="1">
-        <v>46161.659104513892</v>
+        <v>46125.491774884256</v>
       </c>
       <c r="K39" s="2">
-        <v>46175</v>
+        <v>46129</v>
       </c>
       <c r="L39" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M39" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q39" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>79375</v>
+        <v>78422</v>
       </c>
       <c r="B40" t="s">
         <v>17</v>
@@ -2787,39 +2586,39 @@
         <v>19</v>
       </c>
       <c r="E40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40">
+        <v>5886</v>
+      </c>
+      <c r="G40" t="s">
         <v>119</v>
       </c>
-      <c r="F40">
-        <v>2564</v>
-      </c>
-      <c r="G40" t="s">
+      <c r="H40" t="s">
         <v>120</v>
       </c>
-      <c r="H40" t="s">
-        <v>118</v>
-      </c>
       <c r="I40" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J40" s="1">
-        <v>46161.661440011572</v>
+        <v>46113.659672372683</v>
       </c>
       <c r="K40" s="2">
-        <v>46175</v>
+        <v>46126</v>
       </c>
       <c r="L40" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M40" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="Q40" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>78507</v>
+        <v>79116</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
@@ -2834,80 +2633,83 @@
         <v>121</v>
       </c>
       <c r="F41">
-        <v>6293</v>
+        <v>3578</v>
       </c>
       <c r="G41" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="H41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="J41" s="1">
-        <v>46119.492916006944</v>
+        <v>46153.589470682869</v>
       </c>
       <c r="K41" s="2">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="L41" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="M41" t="s">
-        <v>41</v>
+        <v>20</v>
+      </c>
+      <c r="N41">
+        <v>46154.572128553242</v>
       </c>
       <c r="Q41" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>78508</v>
+        <v>79510</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
         <v>19</v>
       </c>
       <c r="E42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F42">
-        <v>1767</v>
+        <v>6278</v>
       </c>
       <c r="G42" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H42" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I42" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="J42" s="1">
-        <v>46119.493672222219</v>
+        <v>46169.656332673614</v>
       </c>
       <c r="K42" s="2">
-        <v>46140</v>
+        <v>46171</v>
       </c>
       <c r="L42" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="M42" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="Q42" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>78509</v>
+        <v>79115</v>
       </c>
       <c r="B43" t="s">
         <v>17</v>
@@ -2919,752 +2721,104 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F43">
-        <v>1767</v>
+        <v>9578</v>
       </c>
       <c r="G43" t="s">
-        <v>124</v>
-      </c>
-      <c r="H43" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="I43" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J43" s="1">
-        <v>46119.49403483796</v>
+        <v>46153.588272222223</v>
       </c>
       <c r="K43" s="2">
-        <v>46140</v>
+        <v>46160</v>
       </c>
       <c r="L43" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M43" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>74</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>78510</v>
+        <v>79511</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F44">
-        <v>1767</v>
+        <v>3995</v>
       </c>
       <c r="G44" t="s">
-        <v>124</v>
-      </c>
-      <c r="H44" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I44" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J44" s="1">
-        <v>46119.494437384259</v>
+        <v>46169.659685960651</v>
       </c>
       <c r="K44" s="2">
-        <v>46140</v>
+        <v>46192</v>
       </c>
       <c r="L44" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M44" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>78511</v>
+        <v>79505</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="C45" t="s">
-        <v>18</v>
+        <v>131</v>
       </c>
       <c r="D45" t="s">
         <v>19</v>
       </c>
       <c r="E45" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F45">
-        <v>1767</v>
+        <v>3464</v>
       </c>
       <c r="G45" t="s">
-        <v>124</v>
-      </c>
-      <c r="H45" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="I45" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="J45" s="1">
-        <v>46119.494797303239</v>
+        <v>46169.6113428588</v>
       </c>
       <c r="K45" s="2">
-        <v>46140</v>
+        <v>46192</v>
       </c>
       <c r="L45" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="M45" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>78514</v>
-      </c>
-      <c r="B46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C46" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" t="s">
-        <v>19</v>
-      </c>
-      <c r="E46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F46">
-        <v>4115</v>
-      </c>
-      <c r="G46" t="s">
-        <v>58</v>
-      </c>
-      <c r="H46" t="s">
-        <v>130</v>
-      </c>
-      <c r="I46" t="s">
-        <v>31</v>
-      </c>
-      <c r="J46" s="1">
-        <v>46119.4968878125</v>
-      </c>
-      <c r="K46" s="2">
-        <v>46140</v>
-      </c>
-      <c r="L46" t="s">
-        <v>72</v>
-      </c>
-      <c r="M46" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>78492</v>
-      </c>
-      <c r="B47" t="s">
-        <v>17</v>
-      </c>
-      <c r="C47" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" t="s">
-        <v>19</v>
-      </c>
-      <c r="E47" t="s">
-        <v>131</v>
-      </c>
-      <c r="F47">
-        <v>2046</v>
-      </c>
-      <c r="G47" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" t="s">
-        <v>45</v>
-      </c>
-      <c r="I47" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="1">
-        <v>46119.436787928244</v>
-      </c>
-      <c r="K47" s="2">
-        <v>46140</v>
-      </c>
-      <c r="L47" t="s">
-        <v>132</v>
-      </c>
-      <c r="M47" t="s">
-        <v>41</v>
-      </c>
-      <c r="N47">
-        <v>46119.673519525466</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>79373</v>
-      </c>
-      <c r="B48" t="s">
-        <v>17</v>
-      </c>
-      <c r="C48" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" t="s">
         <v>134</v>
-      </c>
-      <c r="F48">
-        <v>4821</v>
-      </c>
-      <c r="G48" t="s">
-        <v>52</v>
-      </c>
-      <c r="H48" t="s">
-        <v>135</v>
-      </c>
-      <c r="I48" t="s">
-        <v>31</v>
-      </c>
-      <c r="J48" s="1">
-        <v>46161.659884918983</v>
-      </c>
-      <c r="K48" s="2">
-        <v>46175</v>
-      </c>
-      <c r="L48" t="s">
-        <v>72</v>
-      </c>
-      <c r="M48" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>79374</v>
-      </c>
-      <c r="B49" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" t="s">
-        <v>136</v>
-      </c>
-      <c r="F49">
-        <v>4821</v>
-      </c>
-      <c r="G49" t="s">
-        <v>52</v>
-      </c>
-      <c r="H49" t="s">
-        <v>135</v>
-      </c>
-      <c r="I49" t="s">
-        <v>31</v>
-      </c>
-      <c r="J49" s="1">
-        <v>46161.660798726851</v>
-      </c>
-      <c r="K49" s="2">
-        <v>46175</v>
-      </c>
-      <c r="L49" t="s">
-        <v>72</v>
-      </c>
-      <c r="M49" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>79499</v>
-      </c>
-      <c r="B50" t="s">
-        <v>67</v>
-      </c>
-      <c r="C50" t="s">
-        <v>67</v>
-      </c>
-      <c r="D50" t="s">
-        <v>19</v>
-      </c>
-      <c r="E50" t="s">
-        <v>137</v>
-      </c>
-      <c r="F50">
-        <v>4585</v>
-      </c>
-      <c r="G50" t="s">
-        <v>138</v>
-      </c>
-      <c r="H50" t="s">
-        <v>70</v>
-      </c>
-      <c r="I50" t="s">
-        <v>71</v>
-      </c>
-      <c r="J50" s="1">
-        <v>46169.502877511572</v>
-      </c>
-      <c r="K50" s="2">
-        <v>46181</v>
-      </c>
-      <c r="L50" t="s">
-        <v>72</v>
-      </c>
-      <c r="M50" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>79500</v>
-      </c>
-      <c r="B51" t="s">
-        <v>67</v>
-      </c>
-      <c r="C51" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" t="s">
-        <v>140</v>
-      </c>
-      <c r="F51">
-        <v>3916</v>
-      </c>
-      <c r="G51" t="s">
-        <v>141</v>
-      </c>
-      <c r="I51" t="s">
-        <v>71</v>
-      </c>
-      <c r="J51" s="1">
-        <v>46169.507391319443</v>
-      </c>
-      <c r="K51" s="2">
-        <v>46181</v>
-      </c>
-      <c r="L51" t="s">
-        <v>83</v>
-      </c>
-      <c r="M51" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>79506</v>
-      </c>
-      <c r="B52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C52" t="s">
-        <v>67</v>
-      </c>
-      <c r="D52" t="s">
-        <v>19</v>
-      </c>
-      <c r="E52" t="s">
-        <v>142</v>
-      </c>
-      <c r="F52">
-        <v>2744</v>
-      </c>
-      <c r="G52" t="s">
-        <v>143</v>
-      </c>
-      <c r="I52" t="s">
-        <v>31</v>
-      </c>
-      <c r="J52" s="1">
-        <v>46169.623843090281</v>
-      </c>
-      <c r="K52" s="2">
-        <v>46181</v>
-      </c>
-      <c r="L52" t="s">
-        <v>83</v>
-      </c>
-      <c r="M52" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>79515</v>
-      </c>
-      <c r="B53" t="s">
-        <v>67</v>
-      </c>
-      <c r="C53" t="s">
-        <v>67</v>
-      </c>
-      <c r="D53" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" t="s">
-        <v>145</v>
-      </c>
-      <c r="F53">
-        <v>1948</v>
-      </c>
-      <c r="G53" t="s">
-        <v>146</v>
-      </c>
-      <c r="I53" t="s">
-        <v>87</v>
-      </c>
-      <c r="J53" s="1">
-        <v>46169.730614618056</v>
-      </c>
-      <c r="K53" s="2">
-        <v>46181</v>
-      </c>
-      <c r="L53" t="s">
-        <v>83</v>
-      </c>
-      <c r="M53" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>78607</v>
-      </c>
-      <c r="B54" t="s">
-        <v>17</v>
-      </c>
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" t="s">
-        <v>147</v>
-      </c>
-      <c r="F54">
-        <v>5142</v>
-      </c>
-      <c r="G54" t="s">
-        <v>148</v>
-      </c>
-      <c r="H54" t="s">
-        <v>149</v>
-      </c>
-      <c r="I54" t="s">
-        <v>87</v>
-      </c>
-      <c r="J54" s="1">
-        <v>46125.491774884256</v>
-      </c>
-      <c r="K54" s="2">
-        <v>46129</v>
-      </c>
-      <c r="L54" t="s">
-        <v>72</v>
-      </c>
-      <c r="M54" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>78422</v>
-      </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" t="s">
-        <v>19</v>
-      </c>
-      <c r="E55" t="s">
-        <v>150</v>
-      </c>
-      <c r="F55">
-        <v>5886</v>
-      </c>
-      <c r="G55" t="s">
-        <v>151</v>
-      </c>
-      <c r="H55" t="s">
-        <v>152</v>
-      </c>
-      <c r="I55" t="s">
-        <v>40</v>
-      </c>
-      <c r="J55" s="1">
-        <v>46113.659672372683</v>
-      </c>
-      <c r="K55" s="2">
-        <v>46126</v>
-      </c>
-      <c r="L55" t="s">
-        <v>72</v>
-      </c>
-      <c r="M55" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>79116</v>
-      </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>18</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" t="s">
-        <v>153</v>
-      </c>
-      <c r="F56">
-        <v>3578</v>
-      </c>
-      <c r="G56" t="s">
-        <v>154</v>
-      </c>
-      <c r="H56" t="s">
-        <v>155</v>
-      </c>
-      <c r="I56" t="s">
-        <v>31</v>
-      </c>
-      <c r="J56" s="1">
-        <v>46153.589470682869</v>
-      </c>
-      <c r="K56" s="2">
-        <v>46160</v>
-      </c>
-      <c r="L56" t="s">
-        <v>132</v>
-      </c>
-      <c r="M56" t="s">
-        <v>25</v>
-      </c>
-      <c r="N56">
-        <v>46154.572128553242</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>79510</v>
-      </c>
-      <c r="B57" t="s">
-        <v>157</v>
-      </c>
-      <c r="C57" t="s">
-        <v>157</v>
-      </c>
-      <c r="D57" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" t="s">
-        <v>158</v>
-      </c>
-      <c r="F57">
-        <v>6278</v>
-      </c>
-      <c r="G57" t="s">
-        <v>159</v>
-      </c>
-      <c r="H57" t="s">
-        <v>160</v>
-      </c>
-      <c r="I57" t="s">
-        <v>31</v>
-      </c>
-      <c r="J57" s="1">
-        <v>46169.656332673614</v>
-      </c>
-      <c r="K57" s="2">
-        <v>46171</v>
-      </c>
-      <c r="L57" t="s">
-        <v>72</v>
-      </c>
-      <c r="M57" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>79115</v>
-      </c>
-      <c r="B58" t="s">
-        <v>17</v>
-      </c>
-      <c r="C58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" t="s">
-        <v>161</v>
-      </c>
-      <c r="F58">
-        <v>9578</v>
-      </c>
-      <c r="G58" t="s">
-        <v>162</v>
-      </c>
-      <c r="I58" t="s">
-        <v>40</v>
-      </c>
-      <c r="J58" s="1">
-        <v>46153.588272222223</v>
-      </c>
-      <c r="K58" s="2">
-        <v>46160</v>
-      </c>
-      <c r="L58" t="s">
-        <v>83</v>
-      </c>
-      <c r="M58" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>79511</v>
-      </c>
-      <c r="B59" t="s">
-        <v>163</v>
-      </c>
-      <c r="C59" t="s">
-        <v>163</v>
-      </c>
-      <c r="D59" t="s">
-        <v>19</v>
-      </c>
-      <c r="E59" t="s">
-        <v>164</v>
-      </c>
-      <c r="F59">
-        <v>3995</v>
-      </c>
-      <c r="G59" t="s">
-        <v>165</v>
-      </c>
-      <c r="I59" t="s">
-        <v>87</v>
-      </c>
-      <c r="J59" s="1">
-        <v>46169.659685960651</v>
-      </c>
-      <c r="K59" s="2">
-        <v>46192</v>
-      </c>
-      <c r="L59" t="s">
-        <v>83</v>
-      </c>
-      <c r="M59" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>79505</v>
-      </c>
-      <c r="B60" t="s">
-        <v>163</v>
-      </c>
-      <c r="C60" t="s">
-        <v>163</v>
-      </c>
-      <c r="D60" t="s">
-        <v>19</v>
-      </c>
-      <c r="E60" t="s">
-        <v>167</v>
-      </c>
-      <c r="F60">
-        <v>3464</v>
-      </c>
-      <c r="G60" t="s">
-        <v>168</v>
-      </c>
-      <c r="I60" t="s">
-        <v>87</v>
-      </c>
-      <c r="J60" s="1">
-        <v>46169.6113428588</v>
-      </c>
-      <c r="K60" s="2">
-        <v>46192</v>
-      </c>
-      <c r="L60" t="s">
-        <v>83</v>
-      </c>
-      <c r="M60" t="s">
-        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgcontecnica1-my.sharepoint.com/personal/rjuan_mgcontecnica_com_br/Documents/Área de Trabalho/Python/Chamados/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gamaral\Desktop\Python\Chamados\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{75ABA41F-6853-49EB-94D9-045052CC97E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EF1F885-3587-41C9-8283-38A4DFB25A80}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16BA40BC-C912-4CC9-B320-F410FCA06EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{45AA7DE4-8F9A-4240-A45C-A0DC1A65219E}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{45AA7DE4-8F9A-4240-A45C-A0DC1A65219E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="139">
   <si>
     <t>Id</t>
   </si>
@@ -451,6 +451,12 @@
   </si>
   <si>
     <t>SUPERMERCADO VICALI PARATY LTDA</t>
+  </si>
+  <si>
+    <t>Boa tarde! Segue malha fiscal.A Secretaria Especial da Receita Federal do Brasil vem por meio deste aviso informar inconsistências em relação à base de cálculo do IRPF e da CSLL dos rendimentos e ganhos líquidos auferidos em aplicações financeiras de renda fixa e/ou do JCP – Juros sobre Capital Próprio, identificadas ao comparar as informações prestadas na ECF – ESCRITURAÇÃO CONTÁBIL FISCAL com a DIRF – DECLARAÇÃO DO IMPOSTO DE RENDA RETIDO NA FONTE, nas quais esse contribuinte consta como beneficiário, em que valores não foram oferecidos à tributação.</t>
+  </si>
+  <si>
+    <t>COXA PARTICIPACOES S A</t>
   </si>
 </sst>
 </file>
@@ -474,7 +480,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -482,14 +488,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -518,8 +560,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}" name="Tabela2" displayName="Tabela2" ref="A1:Q45" totalsRowShown="0">
-  <autoFilter ref="A1:Q45" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}" name="Tabela2" displayName="Tabela2" ref="A1:Q46" totalsRowShown="0">
+  <autoFilter ref="A1:Q46" xr:uid="{5CEA8883-799A-4907-9BF0-BF994E33E689}"/>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{5F184F27-3CF1-414F-86B8-9CC4716D84CF}" name="Id"/>
     <tableColumn id="2" xr3:uid="{1D77350B-469D-463F-A5E2-FCE238DF5E95}" name="Categoria"/>
@@ -860,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{211084A7-C91A-468E-BA90-602A3F34D72B}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.85546875" customWidth="1"/>
@@ -2821,6 +2863,49 @@
         <v>134</v>
       </c>
     </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>79551</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="F46" s="3">
+        <v>5178</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J46" s="7">
+        <v>46171.608240740738</v>
+      </c>
+      <c r="K46" s="8">
+        <v>46181</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N46" s="6"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <tableParts count="1">

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q46" headerRowCount="1">
-  <autoFilter ref="A1:Q46"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q43" headerRowCount="1">
+  <autoFilter ref="A1:Q43"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:Q43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1962,7 +1962,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>79373</v>
+        <v>79375</v>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
@@ -1981,20 +1981,20 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeQUITANDÃO CORDEIRÓPOLISASSUNTO: Créditos tributáriosPENDÊNCIA: "Como é de conhecimento, cliente está realizando compensação de créditos tributários. Por gentileza providenciar as contabilizações e correção dos balancetes.Verificar e-mail enviado com as observações e apontamentos detalhados para correção."</t>
+          <t>Boa tardeJAPÃOASSUNTO: e-CACPENDÊNCIA: "Apresentados consultas com pendências.Guias referentes os valores residuais previdenciários disponibilizados ao cliente para pagamento.Pendências de entrega DCTFWeb, por gentileza prceder conforme e-mail enviado."</t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>4821</v>
+        <v>2564</v>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>RODRIGUES &amp; PEREIRA CORDEIROPOLIS LTDA</t>
+          <t>COMÉRCIO DE HORTI FRUTTI JAPÃO LTDA</t>
         </is>
       </c>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Patricia Borges</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46161.65988491898</v>
+        <v>46161.66144001157</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>46175</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>79374</v>
+        <v>79376</v>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
@@ -2044,20 +2044,20 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeQUITANDÃO CORDEIRÓPOLISASSUNTO: Empréstimos sóciosPENDÊNCIA: "26/02/2026: Os sócios realizaram empréstimos no total de R$ 1.200.000,00, os quais serão devolvidos à eles nos próximos meses.Por gentileza contabilizar as entradas via banco corretamente, para viabilizar as devoluções na contabilidade corretamente."</t>
+          <t xml:space="preserve">Boa tardeDOCES MARINGÁASSUNTO: Clientes x FornecedoresPENDÊNCIA:  Verificar saldo de fornecedor x clientes da Maringá Manutenção. </t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>4821</v>
+        <v>1778</v>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>RODRIGUES &amp; PEREIRA CORDEIROPOLIS LTDA</t>
+          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>Vitor Domingues</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46161.66079872685</v>
+        <v>46161.66251550926</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>46175</v>
@@ -2088,7 +2088,7 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>79375</v>
+        <v>79377</v>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
@@ -2107,20 +2107,20 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeJAPÃOASSUNTO: e-CACPENDÊNCIA: "Apresentados consultas com pendências.Guias referentes os valores residuais previdenciários disponibilizados ao cliente para pagamento.Pendências de entrega DCTFWeb, por gentileza prceder conforme e-mail enviado."</t>
+          <t>Boa tardeDOCES MARINGÁASSUNTO: Distribuição de lucrosPENDÊNCIA: " Não contabilizar em adiantamentos as retiradas em 2026,Fazer as distribuições mensais.1778 - Doces maringa para Sr. Edemir2789 - Manutenção Para Srta Mara "</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>2564</v>
+        <v>1778</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>COMÉRCIO DE HORTI FRUTTI JAPÃO LTDA</t>
+          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46161.66144001157</v>
+        <v>46161.66328822917</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>46175</v>
@@ -2151,7 +2151,7 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>79376</v>
+        <v>79378</v>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
@@ -2170,20 +2170,20 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tardeDOCES MARINGÁASSUNTO: Clientes x FornecedoresPENDÊNCIA:  Verificar saldo de fornecedor x clientes da Maringá Manutenção. </t>
+          <t>Boa tardeSUP. ZARELLIASSUNTO: Taxa de CartãoPENDÊNCIA: Cliente solicitou de onde retiramos o valor da taxa de cartão lançada mensalmente.</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>1778</v>
+        <v>2857</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
+          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Naiara Dutra</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
@@ -2192,7 +2192,7 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46161.66251550926</v>
+        <v>46161.66400836805</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>46175</v>
@@ -2214,16 +2214,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>79377</v>
+        <v>79467</v>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeDOCES MARINGÁASSUNTO: Distribuição de lucrosPENDÊNCIA: " Não contabilizar em adiantamentos as retiradas em 2026,Fazer as distribuições mensais.1778 - Doces maringa para Sr. Edemir2789 - Manutenção Para Srta Mara "</t>
+          <t>Boa tarde! Segue malha. Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>1778</v>
+        <v>1931</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
+          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46161.66328822917</v>
+        <v>46168.59874181713</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N28" s="1" t="n"/>
@@ -2277,16 +2277,16 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>79378</v>
+        <v>79470</v>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -2296,32 +2296,32 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeSUP. ZARELLIASSUNTO: Taxa de CartãoPENDÊNCIA: Cliente solicitou de onde retiramos o valor da taxa de cartão lançada mensalmente.</t>
+          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>2857</v>
+        <v>4218</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
+          <t>ARABAIANA EMPREENDIMENTOS E PARTICIPACOES LTDA</t>
         </is>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46161.66400836805</v>
+        <v>46168.60707376157</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N29" s="1" t="n"/>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>79467</v>
+        <v>79464</v>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
@@ -2359,15 +2359,15 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha. Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>Boa tarde! Segue malha fiscal.  Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>1931</v>
+        <v>4327</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
+          <t>ACCESS EVENTOS E VIAGENS LTDA</t>
         </is>
       </c>
       <c r="H30" s="1" t="inlineStr">
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46168.59874181713</v>
+        <v>46168.51368692129</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>46170</v>
@@ -2403,7 +2403,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>79470</v>
+        <v>79469</v>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
@@ -2426,11 +2426,11 @@
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>4218</v>
+        <v>2209</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t>ARABAIANA EMPREENDIMENTOS E PARTICIPACOES LTDA</t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H31" s="1" t="inlineStr">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46168.60707376157</v>
+        <v>46168.60594070602</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>46170</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>79510</v>
+        <v>79471</v>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, solicito o envio da DRE e do Balanço da empresa 6278, referentes aos períodos de 2025 e 2026.</t>
+          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F32" s="1" t="n">
-        <v>6278</v>
+        <v>5026</v>
       </c>
       <c r="G32" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
         </is>
       </c>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>Isabela Lemos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46169.65633267361</v>
+        <v>46168.60873846065</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="L32" s="1" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
       </c>
       <c r="M32" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N32" s="1" t="n"/>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>79464</v>
+        <v>79499</v>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
@@ -2548,17 +2548,13 @@
       </c>
       <c r="E33" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha fiscal.  Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t xml:space="preserve"> 4585 - V. J. ALMEIDA ADMINISTRACAO DE BENS LTDAA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
         </is>
       </c>
       <c r="F33" s="1" t="n">
-        <v>4327</v>
-      </c>
-      <c r="G33" s="1" t="inlineStr">
-        <is>
-          <t>ACCESS EVENTOS E VIAGENS LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="inlineStr">
         <is>
           <t>Andrea Medeiros</t>
@@ -2570,10 +2566,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46168.51368692129</v>
+        <v>46169.50287751157</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>46170</v>
+        <v>46181</v>
       </c>
       <c r="L33" s="1" t="inlineStr">
         <is>
@@ -2582,7 +2578,7 @@
       </c>
       <c r="M33" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="N33" s="1" t="n"/>
@@ -2592,16 +2588,16 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>79469</v>
+        <v>78613</v>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
@@ -2611,32 +2607,32 @@
       </c>
       <c r="E34" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>Pró-Labore:Providenciar ao sócio com 1 salário mínimo</t>
         </is>
       </c>
       <c r="F34" s="1" t="n">
-        <v>2209</v>
+        <v>6621</v>
       </c>
       <c r="G34" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
         </is>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46168.60594070602</v>
+        <v>46125.59368518519</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>46170</v>
+        <v>46132</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2645,7 +2641,7 @@
       </c>
       <c r="M34" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N34" s="1" t="n"/>
@@ -2655,16 +2651,16 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>79471</v>
+        <v>79115</v>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -2674,32 +2670,32 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>Prezados, boa tarde!Segue pendências da Ata de reuniãoINSS	Enviado em duplicidade ref. 01/2026, verificar o que houve Pendencia Recorrente</t>
         </is>
       </c>
       <c r="F35" s="1" t="n">
-        <v>5026</v>
+        <v>9578</v>
       </c>
       <c r="G35" s="1" t="inlineStr">
         <is>
-          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
+          <t>PAULO CESAR RIZARDI</t>
         </is>
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>46168.60873846065</v>
+        <v>46153.58827222222</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>46170</v>
+        <v>46160</v>
       </c>
       <c r="L35" s="1" t="inlineStr">
         <is>
@@ -2708,7 +2704,7 @@
       </c>
       <c r="M35" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="N35" s="1" t="n"/>
@@ -2718,16 +2714,16 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>79499</v>
+        <v>78847</v>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Reunião externa</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
@@ -2737,7 +2733,7 @@
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4585 - V. J. ALMEIDA ADMINISTRACAO DE BENS LTDAA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
+          <t>Verificar o sindicato Patronal, lembrando que o cliente não abre mais aos domingosCliente tem dificuldade sobre os recebimentos dos atestados demissionaisApresentar ao cliente sobre as obrigações da empresa5350 - AKAFER</t>
         </is>
       </c>
       <c r="F36" s="1" t="n">
@@ -2746,47 +2742,54 @@
       <c r="G36" s="1" t="n"/>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>46169.50287751157</v>
+        <v>46134.66965193287</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>46181</v>
+        <v>46142</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M36" s="1" t="inlineStr">
         <is>
-          <t>Isabelli Afonso</t>
-        </is>
-      </c>
-      <c r="N36" s="1" t="n"/>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>46171.59439259259</v>
+      </c>
       <c r="O36" s="1" t="n"/>
       <c r="P36" s="1" t="inlineStr"/>
-      <c r="Q36" s="1" t="inlineStr"/>
+      <c r="Q36" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM ATENDIMENTO
+</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>78613</v>
+        <v>79511</v>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>PER/DCOMP - Intimação/Comunicado</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>PER/DCOMP - Intimação/Comunicado</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -2796,60 +2799,52 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>Pró-Labore:Providenciar ao sócio com 1 salário mínimo</t>
+          <t>3995 - SUPER MERCADO SOROCABA LTDA (62.133.459/0001-10)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Qualquer duvida estou a disposição.</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>6621</v>
-      </c>
-      <c r="G37" s="1" t="inlineStr">
-        <is>
-          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="n"/>
+      <c r="H37" s="1" t="n"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46125.59368518519</v>
+        <v>46169.65968596065</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>46132</v>
+        <v>46192</v>
       </c>
       <c r="L37" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M37" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N37" s="1" t="n"/>
       <c r="O37" s="1" t="n"/>
       <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>79115</v>
+        <v>79502</v>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
@@ -2859,60 +2854,52 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Segue pendências da Ata de reuniãoINSS	Enviado em duplicidade ref. 01/2026, verificar o que houve Pendencia Recorrente</t>
+          <t>Boa tarde! Segue malha fiscal do cliente 5165 - Legume S/AA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>9578</v>
-      </c>
-      <c r="G38" s="1" t="inlineStr">
-        <is>
-          <t>PAULO CESAR RIZARDI</t>
-        </is>
-      </c>
-      <c r="H38" s="1" t="inlineStr">
-        <is>
-          <t>David Bragança</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G38" s="1" t="n"/>
+      <c r="H38" s="1" t="n"/>
       <c r="I38" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46153.58827222222</v>
+        <v>46169.51483611111</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>46160</v>
+        <v>46181</v>
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M38" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N38" s="1" t="n"/>
       <c r="O38" s="1" t="n"/>
       <c r="P38" s="1" t="inlineStr"/>
-      <c r="Q38" s="1" t="inlineStr"/>
+      <c r="Q38" s="1" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>78847</v>
+        <v>79551</v>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>Reunião externa</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -2922,54 +2909,47 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>Verificar o sindicato Patronal, lembrando que o cliente não abre mais aos domingosCliente tem dificuldade sobre os recebimentos dos atestados demissionaisApresentar ao cliente sobre as obrigações da empresa5350 - AKAFER</t>
+          <t>Boa tarde! Segue malha fiscal.A Secretaria Especial da Receita Federal do Brasil vem por meio deste aviso informar inconsistências em relação à base de cálculo do IRPF e da CSLL dos rendimentos e ganhos líquidos auferidos em aplicações financeiras de renda fixa e/ou do JCP – Juros sobre Capital Próprio, identificadas ao comparar as informações prestadas na ECF – ESCRITURAÇÃO CONTÁBIL FISCAL com a DIRF – DECLARAÇÃO DO IMPOSTO DE RENDA RETIDO NA FONTE, nas quais esse contribuinte consta como beneficiário, em que valores não foram oferecidos à tributação.</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="1" t="n"/>
-      <c r="H39" s="1" t="inlineStr">
-        <is>
-          <t>Mauricio Lermen</t>
-        </is>
-      </c>
+        <v>5178</v>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>COXA PARTICIPACOES S A</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="n"/>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46134.66965193287</v>
+        <v>46171.6082369213</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>46142</v>
+        <v>46181</v>
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M39" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="n">
-        <v>46171.59439259259</v>
-      </c>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N39" s="1" t="n"/>
       <c r="O39" s="1" t="n"/>
       <c r="P39" s="1" t="inlineStr"/>
-      <c r="Q39" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EM ATENDIMENTO
-</t>
-        </is>
-      </c>
+      <c r="Q39" s="1" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>79511</v>
+        <v>79505</v>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
@@ -2988,7 +2968,7 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>3995 - SUPER MERCADO SOROCABA LTDA (62.133.459/0001-10)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Qualquer duvida estou a disposição.</t>
+          <t xml:space="preserve">3464 - SUPERMERCADO VICALI PARATY LTDA  (28.466.073/0001-92)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Qualquer duvida estou a disposição. </t>
         </is>
       </c>
       <c r="F40" s="1" t="n">
@@ -3002,7 +2982,7 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>46169.65968596065</v>
+        <v>46169.6113428588</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>46192</v>
@@ -3024,7 +3004,7 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>79502</v>
+        <v>79500</v>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
@@ -3043,7 +3023,7 @@
       </c>
       <c r="E41" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha fiscal do cliente 5165 - Legume S/AA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
+          <t>3916 - ALETA PARTICIPACOES LTDAA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
         </is>
       </c>
       <c r="F41" s="1" t="n">
@@ -3057,7 +3037,7 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>46169.51483611111</v>
+        <v>46169.50739131944</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>46181</v>
@@ -3069,7 +3049,7 @@
       </c>
       <c r="M41" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Isabelli Afonso</t>
         </is>
       </c>
       <c r="N41" s="1" t="n"/>
@@ -3079,7 +3059,7 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>79551</v>
+        <v>79506</v>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
@@ -3098,25 +3078,21 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha fiscal.A Secretaria Especial da Receita Federal do Brasil vem por meio deste aviso informar inconsistências em relação à base de cálculo do IRPF e da CSLL dos rendimentos e ganhos líquidos auferidos em aplicações financeiras de renda fixa e/ou do JCP – Juros sobre Capital Próprio, identificadas ao comparar as informações prestadas na ECF – ESCRITURAÇÃO CONTÁBIL FISCAL com a DIRF – DECLARAÇÃO DO IMPOSTO DE RENDA RETIDO NA FONTE, nas quais esse contribuinte consta como beneficiário, em que valores não foram oferecidos à tributação.</t>
+          <t>2744 CUCINARE PRO ALIMENTAÇÃOsegue malha fiscal: Exercício 2024 - Ano-calendário 2023Enviamos uma primeira comunicação no dia09 de março sobre esta infração e não identifi camos nenhumaprovidência sua de regularização. Esta é a última oportunidade sem autuação.Até 15/05/2026, você tem a oportunidade para fazer a regularização sem a multa de ofício, permitindo que recolhaou parcele os valores devidos apenas com os devidos acréscimos legais.Caso não corrija as irregularidades, fi ca sujeito a procedimento de fi scalização e lavratura de Auto de Infração, paracobrança dos valores devidos acrescidos de multa de ofício, em percentual de 75%, além de juros de mora.Aproveite esta última oportunidade para proceder à retifi cação da(s) DCTF(s) transmitida(s) com inconsistências efazer o recolhimento em DARF.</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>5178</v>
-      </c>
-      <c r="G42" s="1" t="inlineStr">
-        <is>
-          <t>COXA PARTICIPACOES S A</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G42" s="1" t="n"/>
       <c r="H42" s="1" t="n"/>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46171.6082369213</v>
+        <v>46169.62384309028</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>46181</v>
@@ -3128,7 +3104,7 @@
       </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N42" s="1" t="n"/>
@@ -3138,16 +3114,16 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>79505</v>
+        <v>79515</v>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>PER/DCOMP - Intimação/Comunicado</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>PER/DCOMP - Intimação/Comunicado</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -3157,7 +3133,7 @@
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464 - SUPERMERCADO VICALI PARATY LTDA  (28.466.073/0001-92)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Qualquer duvida estou a disposição. </t>
+          <t>1948 - comercio de horti frutti catroque ltda segue malha fiscal: Esta mensagem é um complemento da mensagem principal, enviada para sua caixa postal no e-CAC com o assuntoAVISO MALHA FISCAL PJ - IRPJ/CSLL - LUCRO PRESUMIDO - DEMONSTRATIVO DE DIVERGÊNCIAS.O objetivo desta mensagem, portanto, é inserir outras informações que não constaram na mensagem principal,incluindo, aqui, o demonstrativo de apuração do IRPJ com base nos dados das respectivas ECF.</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
@@ -3171,10 +3147,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46169.6113428588</v>
+        <v>46169.73061461806</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>46192</v>
+        <v>46181</v>
       </c>
       <c r="L43" s="1" t="inlineStr">
         <is>
@@ -3183,178 +3159,13 @@
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N43" s="1" t="n"/>
       <c r="O43" s="1" t="n"/>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>79500</v>
-      </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>3916 - ALETA PARTICIPACOES LTDAA Secretaria da Receita Federal do Brasil (RFB) identificou divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF). Essas divergências evidenciam insuficiência de declaração e recolhimento de IRPJ e CSLL devidos pelo Lucro Presumido.</t>
-        </is>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="1" t="n"/>
-      <c r="H44" s="1" t="n"/>
-      <c r="I44" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n">
-        <v>46169.50739131944</v>
-      </c>
-      <c r="K44" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="L44" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M44" s="1" t="inlineStr">
-        <is>
-          <t>Isabelli Afonso</t>
-        </is>
-      </c>
-      <c r="N44" s="1" t="n"/>
-      <c r="O44" s="1" t="n"/>
-      <c r="P44" s="1" t="inlineStr"/>
-      <c r="Q44" s="1" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>79506</v>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>2744 CUCINARE PRO ALIMENTAÇÃOsegue malha fiscal: Exercício 2024 - Ano-calendário 2023Enviamos uma primeira comunicação no dia09 de março sobre esta infração e não identifi camos nenhumaprovidência sua de regularização. Esta é a última oportunidade sem autuação.Até 15/05/2026, você tem a oportunidade para fazer a regularização sem a multa de ofício, permitindo que recolhaou parcele os valores devidos apenas com os devidos acréscimos legais.Caso não corrija as irregularidades, fi ca sujeito a procedimento de fi scalização e lavratura de Auto de Infração, paracobrança dos valores devidos acrescidos de multa de ofício, em percentual de 75%, além de juros de mora.Aproveite esta última oportunidade para proceder à retifi cação da(s) DCTF(s) transmitida(s) com inconsistências efazer o recolhimento em DARF.</t>
-        </is>
-      </c>
-      <c r="F45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="1" t="n"/>
-      <c r="H45" s="1" t="n"/>
-      <c r="I45" s="1" t="inlineStr">
-        <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n">
-        <v>46169.62384309028</v>
-      </c>
-      <c r="K45" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M45" s="1" t="inlineStr">
-        <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N45" s="1" t="n"/>
-      <c r="O45" s="1" t="n"/>
-      <c r="P45" s="1" t="inlineStr"/>
-      <c r="Q45" s="1" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>79515</v>
-      </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>Malha Fiscal</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>1948 - comercio de horti frutti catroque ltda segue malha fiscal: Esta mensagem é um complemento da mensagem principal, enviada para sua caixa postal no e-CAC com o assuntoAVISO MALHA FISCAL PJ - IRPJ/CSLL - LUCRO PRESUMIDO - DEMONSTRATIVO DE DIVERGÊNCIAS.O objetivo desta mensagem, portanto, é inserir outras informações que não constaram na mensagem principal,incluindo, aqui, o demonstrativo de apuração do IRPJ com base nos dados das respectivas ECF.</t>
-        </is>
-      </c>
-      <c r="F46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n">
-        <v>46169.73061461806</v>
-      </c>
-      <c r="K46" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="L46" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M46" s="1" t="inlineStr">
-        <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N46" s="1" t="n"/>
-      <c r="O46" s="1" t="n"/>
-      <c r="P46" s="1" t="inlineStr"/>
-      <c r="Q46" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q121" headerRowCount="1">
-  <autoFilter ref="A1:Q121"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q133" headerRowCount="1">
+  <autoFilter ref="A1:Q133"/>
   <tableColumns count="17">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:Q133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>78511</v>
+        <v>79376</v>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
@@ -1506,20 +1506,20 @@
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.ALVORADAASSUNTO: NF PENDÊNCIA: Conta 9396 - Serviços Administrativos, por favor, verificar este valor, pois não teve faturamento da Gran Manjerona!</t>
+          <t xml:space="preserve">Boa tardeDOCES MARINGÁASSUNTO: Clientes x FornecedoresPENDÊNCIA:  Verificar saldo de fornecedor x clientes da Maringá Manutenção. </t>
         </is>
       </c>
       <c r="F18" s="1" t="n">
-        <v>1767</v>
+        <v>1778</v>
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO ALVORADA IRMÃOS SILVEIRA LTDA</t>
+          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H18" s="1" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Monica Medeiros</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>46119.49479730324</v>
+        <v>46161.66251550926</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>46140</v>
+        <v>46175</v>
       </c>
       <c r="L18" s="1" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>79376</v>
+        <v>76812</v>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
@@ -1569,32 +1569,32 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tardeDOCES MARINGÁASSUNTO: Clientes x FornecedoresPENDÊNCIA:  Verificar saldo de fornecedor x clientes da Maringá Manutenção. </t>
+          <t>EFD:	Verificar Transporte de Saldo Credor Incorreto ref.: 09/2024, 12/2024, 11/2025 e 12/2025 RESSALTO QUE COBRANÇA É REFERENTE 2024</t>
         </is>
       </c>
       <c r="F19" s="1" t="n">
-        <v>1778</v>
+        <v>1874</v>
       </c>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>SUPER DOCES MARINGÁ LTDA (MATRIZ)</t>
+          <t>Distribuidora de Alimentos SM Carvalho Ltda.</t>
         </is>
       </c>
       <c r="H19" s="1" t="inlineStr">
         <is>
-          <t>Monica Medeiros</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46161.66251550926</v>
+        <v>46048.48471686342</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>46175</v>
+        <v>46059</v>
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="M19" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N19" s="1" t="n"/>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>76812</v>
+        <v>76551</v>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
@@ -1632,20 +1632,20 @@
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>EFD:	Verificar Transporte de Saldo Credor Incorreto ref.: 09/2024, 12/2024, 11/2025 e 12/2025 RESSALTO QUE COBRANÇA É REFERENTE 2024</t>
+          <t>1890	N. S. LAR SUPERMERCADO LTDA	Gerencia	Darlan Rodrigues	ICMS	Verificar valor ref. 07/2025 que está em aberto1261	N. S. LAR SUPERMERCADO LTDA	Gerencia	Darlan Rodrigues	ICMS	Verificar valor ref. 07/2025 que está em aberto</t>
         </is>
       </c>
       <c r="F20" s="1" t="n">
-        <v>1874</v>
+        <v>1890</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
-          <t>Distribuidora de Alimentos SM Carvalho Ltda.</t>
+          <t>N. S. LAR SUPERMERCADO LTDA (FILIAL 01)</t>
         </is>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Deleia Oliveira</t>
         </is>
       </c>
       <c r="I20" s="1" t="inlineStr">
@@ -1654,10 +1654,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46048.48471686342</v>
+        <v>46034.36140964121</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>46059</v>
+        <v>46041</v>
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="M20" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N20" s="1" t="n"/>
@@ -1676,16 +1676,16 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>76551</v>
+        <v>79467</v>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
@@ -1695,32 +1695,32 @@
       </c>
       <c r="E21" s="1" t="inlineStr">
         <is>
-          <t>1890	N. S. LAR SUPERMERCADO LTDA	Gerencia	Darlan Rodrigues	ICMS	Verificar valor ref. 07/2025 que está em aberto1261	N. S. LAR SUPERMERCADO LTDA	Gerencia	Darlan Rodrigues	ICMS	Verificar valor ref. 07/2025 que está em aberto</t>
+          <t>Boa tarde! Segue malha. Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F21" s="1" t="n">
-        <v>1890</v>
+        <v>1931</v>
       </c>
       <c r="G21" s="1" t="inlineStr">
         <is>
-          <t>N. S. LAR SUPERMERCADO LTDA (FILIAL 01)</t>
+          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H21" s="1" t="inlineStr">
         <is>
-          <t>Deleia Oliveira</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I21" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>46034.36140964121</v>
+        <v>46168.59874181713</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>46041</v>
+        <v>46170</v>
       </c>
       <c r="L21" s="1" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="M21" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N21" s="1" t="n"/>
@@ -1739,16 +1739,16 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>79467</v>
+        <v>76547</v>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -1758,32 +1758,32 @@
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha. Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>1948	COMERCIO DE HORTI FRUTI CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento1646	EMPORIO CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento1147	SUPERMERCADO CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 06/2025 para pagamento1948	COMERCIO DE HORTI FRUTI CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento</t>
         </is>
       </c>
       <c r="F22" s="1" t="n">
-        <v>1931</v>
+        <v>1948</v>
       </c>
       <c r="G22" s="1" t="inlineStr">
         <is>
-          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
+          <t>Comércio de Horti Frutti Catroque Ltda.</t>
         </is>
       </c>
       <c r="H22" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>yasming</t>
         </is>
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46168.59874181713</v>
+        <v>46034.35984803241</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>46170</v>
+        <v>46041</v>
       </c>
       <c r="L22" s="1" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="M22" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N22" s="1" t="n"/>
@@ -1802,16 +1802,16 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>76547</v>
+        <v>79627</v>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -1821,60 +1821,56 @@
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>1948	COMERCIO DE HORTI FRUTI CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento1646	EMPORIO CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento1147	SUPERMERCADO CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 06/2025 para pagamento1948	COMERCIO DE HORTI FRUTI CATROQUE LTDA	ICMS	Enviar guia Mês de Referência: 07/2025 para pagamento</t>
+          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2024 e 2025.</t>
         </is>
       </c>
       <c r="F23" s="1" t="n">
-        <v>1948</v>
+        <v>2023</v>
       </c>
       <c r="G23" s="1" t="inlineStr">
         <is>
-          <t>Comércio de Horti Frutti Catroque Ltda.</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>yasming</t>
-        </is>
-      </c>
+          <t>Stantuer Participações Ltda</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="n"/>
       <c r="I23" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46034.35984803241</v>
+        <v>46175.61315721065</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>46041</v>
+        <v>46176</v>
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M23" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N23" s="1" t="n"/>
       <c r="O23" s="1" t="n"/>
       <c r="P23" s="1" t="inlineStr"/>
-      <c r="Q23" s="1" t="inlineStr"/>
+      <c r="Q23" s="1" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>79627</v>
+        <v>78149</v>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
@@ -1884,56 +1880,60 @@
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2024 e 2025.</t>
+          <t xml:space="preserve">ATITUDE / PENDENCIA	DEPTO.	TIPO	AÇÃOCobrança efetivada junto a Elenilva, ao que informou que até 10/3/2026, estaria sendo encaminhada para contabilidade, por isso acompanhar o recebimento dos mesmos.	FISCAL	INFORMATIVO	COBRAR EM CASO DE DEMORA.Opção tributária a ser adotada pela empresa será a do LUCFRO PRESUMIDO, portanto cliente ciente de que se operar alguma venda por esta empresa necessário volume de compras no mês da venda para arrefecer o ICMS e IPI se houver.	FISCAL	INFORMATIVO	 </t>
         </is>
       </c>
       <c r="F24" s="1" t="n">
-        <v>2023</v>
+        <v>2060</v>
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>Stantuer Participações Ltda</t>
-        </is>
-      </c>
-      <c r="H24" s="1" t="n"/>
+          <t>L.A.D. METALURGICA LTDA</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>Gustavo Tonan</t>
+        </is>
+      </c>
       <c r="I24" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>46175.61315721065</v>
+        <v>46105.36634513889</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>46176</v>
+        <v>46112</v>
       </c>
       <c r="L24" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M24" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N24" s="1" t="n"/>
       <c r="O24" s="1" t="n"/>
       <c r="P24" s="1" t="inlineStr"/>
-      <c r="Q24" s="1" t="n"/>
+      <c r="Q24" s="1" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>78492</v>
+        <v>79469</v>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1943,57 +1943,51 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.JAPÃOASSUNTO: Compensações tributáriasPENDÊNCIA: "Cliente está praticando compensações no INSS, IRPJ, CSLL, PIS e COFINS.Atentar para as contabilizações das compensações, inclusive para integrar as bases de cálculo do IRPJ e CSLL.Solicitado novamente ao cliente que em todas as oportunidades de realização de compensações, enviar cópia dos processos para que possamos contabilizar."</t>
+          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F25" s="1" t="n">
-        <v>2046</v>
+        <v>2209</v>
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DISTRIBUIDORA DE ALIMENTOS JAPÃO LTDA </t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>46119.43678792824</v>
+        <v>46168.60594070602</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>46140</v>
+        <v>46170</v>
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="n">
-        <v>46119.67351952547</v>
-      </c>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N25" s="1" t="n"/>
       <c r="O25" s="1" t="n"/>
       <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">em atendimento </t>
-        </is>
-      </c>
+      <c r="Q25" s="1" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>78149</v>
+        <v>77414</v>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
@@ -2012,32 +2006,32 @@
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ATITUDE / PENDENCIA	DEPTO.	TIPO	AÇÃOCobrança efetivada junto a Elenilva, ao que informou que até 10/3/2026, estaria sendo encaminhada para contabilidade, por isso acompanhar o recebimento dos mesmos.	FISCAL	INFORMATIVO	COBRAR EM CASO DE DEMORA.Opção tributária a ser adotada pela empresa será a do LUCFRO PRESUMIDO, portanto cliente ciente de que se operar alguma venda por esta empresa necessário volume de compras no mês da venda para arrefecer o ICMS e IPI se houver.	FISCAL	INFORMATIVO	 </t>
+          <t>2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Enviar guias para pagamentos ref. 08/2025 Cobrança Recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA										2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Verificar EFD ref. 04/2025, 07/2025 e 10/2025 GIA INDEVIDA Cobrança recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2427	Valentina	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2930	Patriot	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	Débitos RFB	Enviar guias para pagamento que estão em aberto	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2930	Patriot	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2947	Jam Enterprise	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA5746	Padaria Vila Nova Conceição	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Verificar EFD ref. 03/2025 INDEVIDA Cobrança recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA3697	Brooklin Bakery	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA5746	Padaria Vila Nova Conceição	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA</t>
         </is>
       </c>
       <c r="F26" s="1" t="n">
-        <v>2060</v>
+        <v>2382</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
-          <t>L.A.D. METALURGICA LTDA</t>
+          <t>NOVA CANADÁ PÃES E DOCES EIRELI</t>
         </is>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
-          <t>Gustavo Tonan</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>46105.36634513889</v>
+        <v>46077.63287079861</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>46112</v>
+        <v>46084</v>
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
@@ -2056,16 +2050,16 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>79469</v>
+        <v>76487</v>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -2075,20 +2069,20 @@
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>EFD 01/2025 E 03/2025 SEM MOVIMENTO	Avaliar e regularizar o mais breve possível as pendências de entrega de EFDF sem movimento nos meses de jan e Março de 2025, sendo que a conta fiscal apresenta crédito sem débito, o que pode chamar a atenção da fiscalização.</t>
         </is>
       </c>
       <c r="F27" s="1" t="n">
-        <v>2209</v>
+        <v>2495</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t>ESQUADRIAS SIDNEY LTDA</t>
         </is>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>tatianag</t>
         </is>
       </c>
       <c r="I27" s="1" t="inlineStr">
@@ -2097,10 +2091,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>46168.60594070602</v>
+        <v>46030.48230420139</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>46170</v>
+        <v>46037</v>
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
@@ -2119,79 +2113,75 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>77414</v>
+        <v>79661</v>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
         <is>
-          <t>2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Enviar guias para pagamentos ref. 08/2025 Cobrança Recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA										2382	Nova Canadá	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Verificar EFD ref. 04/2025, 07/2025 e 10/2025 GIA INDEVIDA Cobrança recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2427	Valentina	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2930	Patriot	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	Débitos RFB	Enviar guias para pagamento que estão em aberto	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2930	Patriot	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA2947	Jam Enterprise	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA5746	Padaria Vila Nova Conceição	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	EFD	Verificar EFD ref. 03/2025 INDEVIDA Cobrança recorrente	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA3697	Brooklin Bakery	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA5746	Padaria Vila Nova Conceição	Gerencia de Contas	Ricardo Silva	Darlan Rodrigues	DUC	Enviar guias para pagamento	20/02/2026	28/02/2026	28/02/2026	PENDÊNCIA</t>
+          <t>Os sócios Pedro Pereira da Costa Ribeiro Neto e Roberto André Pereira da Costa Ribeiro apresentaram pendências na malha fiscal referentes aos valores constantes nos informes de rendimentos. Por gentileza, confirme se a EFD-Reinf foi retificada, pois, na Receita Federal, está constando o valor de R$ 125.325,19 para você, para o Pedro e para o Roberto. O master José Carlos solicita um retorno urgente. Ele pediu que fossem encaminhados, por e-mail, o informe de rendimentos corrigido e a análise da EFD-Reinf para que possa comunicar o cliente</t>
         </is>
       </c>
       <c r="F28" s="1" t="n">
-        <v>2382</v>
+        <v>2495</v>
       </c>
       <c r="G28" s="1" t="inlineStr">
         <is>
-          <t>NOVA CANADÁ PÃES E DOCES EIRELI</t>
-        </is>
-      </c>
-      <c r="H28" s="1" t="inlineStr">
-        <is>
-          <t>Eduardo Lopes</t>
-        </is>
-      </c>
+          <t>ESQUADRIAS SIDNEY LTDA</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="n"/>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>46077.63287079861</v>
+        <v>46176.45757542824</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>46084</v>
+        <v>46188</v>
       </c>
       <c r="L28" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M28" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N28" s="1" t="n"/>
       <c r="O28" s="1" t="n"/>
       <c r="P28" s="1" t="inlineStr"/>
-      <c r="Q28" s="1" t="inlineStr"/>
+      <c r="Q28" s="1" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>76487</v>
+        <v>79642</v>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -2201,60 +2191,56 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>EFD 01/2025 E 03/2025 SEM MOVIMENTO	Avaliar e regularizar o mais breve possível as pendências de entrega de EFDF sem movimento nos meses de jan e Março de 2025, sendo que a conta fiscal apresenta crédito sem débito, o que pode chamar a atenção da fiscalização.</t>
+          <t>Segue autorregularização do cliente em anexo. Ex cliente, nosso periodo</t>
         </is>
       </c>
       <c r="F29" s="1" t="n">
-        <v>2495</v>
+        <v>2602</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
-          <t>ESQUADRIAS SIDNEY LTDA</t>
-        </is>
-      </c>
-      <c r="H29" s="1" t="inlineStr">
-        <is>
-          <t>tatianag</t>
-        </is>
-      </c>
+          <t>JANAE PAES E DOCES LTDA</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="n"/>
       <c r="I29" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>46030.48230420139</v>
+        <v>46175.70763541666</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>46037</v>
+        <v>46182</v>
       </c>
       <c r="L29" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M29" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N29" s="1" t="n"/>
       <c r="O29" s="1" t="n"/>
       <c r="P29" s="1" t="inlineStr"/>
-      <c r="Q29" s="1" t="inlineStr"/>
+      <c r="Q29" s="1" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>79642</v>
+        <v>79648</v>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Multas Diversas</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Multas Diversas</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
@@ -2264,15 +2250,15 @@
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
-          <t>Segue autorregularização do cliente em anexo. Ex cliente, nosso periodo</t>
+          <t>Segue em anexo pendencia do cliente 2751 - Ricardo Santos Costa</t>
         </is>
       </c>
       <c r="F30" s="1" t="n">
-        <v>2602</v>
+        <v>2751</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
-          <t>JANAE PAES E DOCES LTDA</t>
+          <t xml:space="preserve">RICARDO SANTOS COSTA </t>
         </is>
       </c>
       <c r="H30" s="1" t="n"/>
@@ -2282,7 +2268,7 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>46175.70763541666</v>
+        <v>46175.72595871528</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>46182</v>
@@ -2304,16 +2290,16 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>79648</v>
+        <v>76748</v>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>Multas Diversas</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Multas Diversas</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
@@ -2323,43 +2309,51 @@
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>Segue em anexo pendencia do cliente 2751 - Ricardo Santos Costa</t>
+          <t>Bom dia,SUP. ZARELLIASSUNTO: ReclassificaçõesPENDÊNCIA: Fazer as reclassificações para construções em andamento conforme e-mail,</t>
         </is>
       </c>
       <c r="F31" s="1" t="n">
-        <v>2751</v>
+        <v>2857</v>
       </c>
       <c r="G31" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RICARDO SANTOS COSTA </t>
-        </is>
-      </c>
-      <c r="H31" s="1" t="n"/>
+          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46175.72595871528</v>
+        <v>46044.39091392361</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>46182</v>
+        <v>46058</v>
       </c>
       <c r="L31" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M31" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N31" s="1" t="n"/>
       <c r="O31" s="1" t="n"/>
       <c r="P31" s="1" t="inlineStr"/>
-      <c r="Q31" s="1" t="n"/>
+      <c r="Q31" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2684,70 +2678,66 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>76490</v>
+        <v>79658</v>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Material de Reunião - Solicitação Interna</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Material de Reunião - Solicitação Interna</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>DIFAL 07/2025	Verificar imediatamente a péndência constante na consulta a contribuinte de DIFAL 07/2025 em aberto. Procede? Foi enviado ao cliente? Reenviar para pagamento imediata.</t>
+          <t>Teremos reunião com o Cliente Varanda. Solicitado pelo Master Felipe os relatórios de estoque do cliente.Necessário período de 2024, 2025 e 2026.Favor salvar em uma pasta da rede para eu incluir no material de reunião.</t>
         </is>
       </c>
       <c r="F37" s="1" t="n">
-        <v>3488</v>
+        <v>3411</v>
       </c>
       <c r="G37" s="1" t="inlineStr">
         <is>
-          <t>D.P.R. ESQUADRIAS LTDA</t>
-        </is>
-      </c>
-      <c r="H37" s="1" t="inlineStr">
-        <is>
-          <t>tatianag</t>
-        </is>
-      </c>
+          <t xml:space="preserve">VARANDA FRUTAS E MERCEARIA LTDA </t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="n"/>
       <c r="I37" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>46030.48510459491</v>
+        <v>46176.41855825231</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>46037</v>
+        <v>46178</v>
       </c>
       <c r="L37" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M37" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N37" s="1" t="n"/>
       <c r="O37" s="1" t="n"/>
       <c r="P37" s="1" t="inlineStr"/>
-      <c r="Q37" s="1" t="inlineStr"/>
+      <c r="Q37" s="1" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>76997</v>
+        <v>76490</v>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
@@ -2766,20 +2756,20 @@
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>IRPJ/CSLL	Providenciar procedimentos para apuração mensal de IRPJ/CSLL a partir dos valores de vendas apurados no mês, disponibilizando a equipe contábil junto com as apurações dos impostos mensais.</t>
+          <t>DIFAL 07/2025	Verificar imediatamente a péndência constante na consulta a contribuinte de DIFAL 07/2025 em aberto. Procede? Foi enviado ao cliente? Reenviar para pagamento imediata.</t>
         </is>
       </c>
       <c r="F38" s="1" t="n">
-        <v>3499</v>
+        <v>3488</v>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
+          <t>D.P.R. ESQUADRIAS LTDA</t>
         </is>
       </c>
       <c r="H38" s="1" t="inlineStr">
         <is>
-          <t>Romario Silva</t>
+          <t>tatianag</t>
         </is>
       </c>
       <c r="I38" s="1" t="inlineStr">
@@ -2788,10 +2778,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>46057.50608815972</v>
+        <v>46030.48510459491</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>46064</v>
+        <v>46037</v>
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
@@ -2810,7 +2800,7 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>79369</v>
+        <v>76997</v>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
@@ -2829,32 +2819,32 @@
       </c>
       <c r="E39" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeAGUÁ LIMPA - KURODAASSUNTO e-CACPENDÊNCIA: Apresentado pendências referentes IRPJ e CSLL 1° Trim./2025. Por gentileza, verificar se não se trata de divergência em declarações. Caso, sim, por gentileza regularizar (conforme e-mail enviado).</t>
+          <t>IRPJ/CSLL	Providenciar procedimentos para apuração mensal de IRPJ/CSLL a partir dos valores de vendas apurados no mês, disponibilizando a equipe contábil junto com as apurações dos impostos mensais.</t>
         </is>
       </c>
       <c r="F39" s="1" t="n">
-        <v>3627</v>
+        <v>3499</v>
       </c>
       <c r="G39" s="1" t="inlineStr">
         <is>
-          <t>ÁGUA LIMPA DISTRIBUIDORA DE HORTIFRUTI, ALIMENTOS E SERVIÇOS DE TRANSPORTES LTDA.</t>
+          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
         </is>
       </c>
       <c r="H39" s="1" t="inlineStr">
         <is>
-          <t>Naiara Dutra</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="I39" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>46161.65612349537</v>
+        <v>46057.50608815972</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>46175</v>
+        <v>46064</v>
       </c>
       <c r="L39" s="1" t="inlineStr">
         <is>
@@ -2863,7 +2853,7 @@
       </c>
       <c r="M39" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N39" s="1" t="n"/>
@@ -2999,16 +2989,16 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>79372</v>
+        <v>79470</v>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
@@ -3018,32 +3008,32 @@
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeRio das PedrasASSUNTO: N.I.L. x Frutaria Rio das PedrasPENDÊNCIA: Por gentileza, providenciar a conciliação do saldo de contas a pagar na empresa Frutaria Rios das Pedras em relação ao fornecedor N.I.L. e também, o contar a receber na empresa N.I.L em relação a empresa Frutaria Rios das Pedras.</t>
+          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F42" s="1" t="n">
-        <v>3970</v>
+        <v>4218</v>
       </c>
       <c r="G42" s="1" t="inlineStr">
         <is>
-          <t>RIO DAS PEDRAS COMERCIO DE HORTIFRUTIGRANJEIROS E MERCEARIA LIMITADA</t>
+          <t>ARABAIANA EMPREENDIMENTOS E PARTICIPACOES LTDA</t>
         </is>
       </c>
       <c r="H42" s="1" t="inlineStr">
         <is>
-          <t>Patricia Borges</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I42" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46161.65910451389</v>
+        <v>46168.60707376157</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="L42" s="1" t="inlineStr">
         <is>
@@ -3052,7 +3042,7 @@
       </c>
       <c r="M42" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N42" s="1" t="n"/>
@@ -3062,66 +3052,62 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>79470</v>
+        <v>79684</v>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>Cliente possui débitos em aberto com saldo devedor menor do que o valor original. O saldo devedor remanescente é devido a retificações? Por gentileza realizar o levantamento</t>
         </is>
       </c>
       <c r="F43" s="1" t="n">
-        <v>4218</v>
+        <v>4282</v>
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>ARABAIANA EMPREENDIMENTOS E PARTICIPACOES LTDA</t>
-        </is>
-      </c>
-      <c r="H43" s="1" t="inlineStr">
-        <is>
-          <t>Andrea Medeiros</t>
-        </is>
-      </c>
+          <t>ROGUSTEC INDUSTRIA E COMERCIO EIRELI</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="n"/>
       <c r="I43" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>46168.60707376157</v>
+        <v>46176.69647399306</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="L43" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M43" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N43" s="1" t="n"/>
       <c r="O43" s="1" t="n"/>
       <c r="P43" s="1" t="inlineStr"/>
-      <c r="Q43" s="1" t="inlineStr"/>
+      <c r="Q43" s="1" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3438,133 +3424,125 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>77661</v>
+        <v>79660</v>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>Bom dia4922 - SUP. DUARTEASSUNTO: Pro LaborePENDÊNICIA: "A partir de 02/2026, o pro labore dos 3 sócios de R$ 2.000,00 para cada um.Por gentileza, promover a alteração na folha dos sócios para efetivação."</t>
+          <t>Favor retificar declarações na Sefaz, consta transporte de saldo credor incorreto GIA 01/2024 - 12/2024 E 01/2025</t>
         </is>
       </c>
       <c r="F49" s="1" t="n">
-        <v>4922</v>
+        <v>4808</v>
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADOS CAPPI DUARTE LTDA</t>
-        </is>
-      </c>
-      <c r="H49" s="1" t="inlineStr">
-        <is>
-          <t>Micaele Cordeiro</t>
-        </is>
-      </c>
+          <t>DAN AGRO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="n"/>
       <c r="I49" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>46084.41093417824</v>
+        <v>46176.45003255787</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>46098</v>
+        <v>46183</v>
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N49" s="1" t="n"/>
       <c r="O49" s="1" t="n"/>
       <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="inlineStr"/>
+      <c r="Q49" s="1" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>79471</v>
+        <v>79659</v>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t>Cliente solicita que seja analisado se há recolhimento de imposto do fornecedor Banatec, conforme NF anexa. Informou que nunca foi recolhido.</t>
         </is>
       </c>
       <c r="F50" s="1" t="n">
-        <v>5026</v>
+        <v>4811</v>
       </c>
       <c r="G50" s="1" t="inlineStr">
         <is>
-          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
-        </is>
-      </c>
-      <c r="H50" s="1" t="inlineStr">
-        <is>
-          <t>Andrea Medeiros</t>
-        </is>
-      </c>
+          <t>ORIVALDO DAN</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="n"/>
       <c r="I50" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>46168.60873846065</v>
+        <v>46176.42599556713</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>46170</v>
+        <v>46178</v>
       </c>
       <c r="L50" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M50" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N50" s="1" t="n"/>
       <c r="O50" s="1" t="n"/>
       <c r="P50" s="1" t="inlineStr"/>
-      <c r="Q50" s="1" t="inlineStr"/>
+      <c r="Q50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>77872</v>
+        <v>77661</v>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
@@ -3583,32 +3561,32 @@
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>ICMS:10/2025 EFD Transporte de Saldo Credor Incorreto12/2025 GIA/EFD Não apresentou GIA/EFD - Cobrança Recorrente</t>
+          <t>Bom dia4922 - SUP. DUARTEASSUNTO: Pro LaborePENDÊNICIA: "A partir de 02/2026, o pro labore dos 3 sócios de R$ 2.000,00 para cada um.Por gentileza, promover a alteração na folha dos sócios para efetivação."</t>
         </is>
       </c>
       <c r="F51" s="1" t="n">
-        <v>5101</v>
+        <v>4922</v>
       </c>
       <c r="G51" s="1" t="inlineStr">
         <is>
-          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
+          <t>SUPERMERCADOS CAPPI DUARTE LTDA</t>
         </is>
       </c>
       <c r="H51" s="1" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Micaele Cordeiro</t>
         </is>
       </c>
       <c r="I51" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46091.44676890046</v>
+        <v>46084.41093417824</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="L51" s="1" t="inlineStr">
         <is>
@@ -3617,7 +3595,7 @@
       </c>
       <c r="M51" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N51" s="1" t="n"/>
@@ -3627,16 +3605,16 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>76916</v>
+        <v>79471</v>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
@@ -3646,32 +3624,32 @@
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>ICMS:10/2025 EFD Transporte de Saldo Credor Incorreto12/2025 GIA/EFD Não apresentou GIA/EFD</t>
+          <t>Boa tarde! Segue mensagem recebida no e-cac referente a divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F52" s="1" t="n">
-        <v>5101</v>
+        <v>5026</v>
       </c>
       <c r="G52" s="1" t="inlineStr">
         <is>
-          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
+          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
         </is>
       </c>
       <c r="H52" s="1" t="inlineStr">
         <is>
-          <t>Gustavo Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I52" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>46052.61991234954</v>
+        <v>46168.60873846065</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>46065</v>
+        <v>46170</v>
       </c>
       <c r="L52" s="1" t="inlineStr">
         <is>
@@ -3680,7 +3658,7 @@
       </c>
       <c r="M52" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N52" s="1" t="n"/>
@@ -3690,70 +3668,66 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>78344</v>
+        <v>79665</v>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>SALDO CREDOR INCORRETO	"Reguilarizar imediatamente a EFD 11 e 12/2025, cuja consulta perante SEFAZ SP, apresenta transporte de saldo credor incorreto."</t>
+          <t>Autoregularização - Simples Nacional - Janeiro a Dezembro 2024Cliente recebeu notificação de autoregularização do Simples Nacional referente período 2024. Por gentileza, providenciar retificação dentro do prazo estipulado pela Receita.</t>
         </is>
       </c>
       <c r="F53" s="1" t="n">
-        <v>5132</v>
+        <v>5100</v>
       </c>
       <c r="G53" s="1" t="inlineStr">
         <is>
-          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
-        </is>
-      </c>
-      <c r="H53" s="1" t="inlineStr">
-        <is>
-          <t>Rosilene Santos</t>
-        </is>
-      </c>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="n"/>
       <c r="I53" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>46112.41756226852</v>
+        <v>46176.49184155092</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>46119</v>
+        <v>46199</v>
       </c>
       <c r="L53" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M53" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N53" s="1" t="n"/>
       <c r="O53" s="1" t="n"/>
       <c r="P53" s="1" t="inlineStr"/>
-      <c r="Q53" s="1" t="inlineStr"/>
+      <c r="Q53" s="1" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>78607</v>
+        <v>77872</v>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
@@ -3772,20 +3746,20 @@
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>Situação do Contribuinte:	Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. E-Cac:	Por favor verificar - Pis e Cofins 02 e 08/2024 e DCTFWeb 05/2025 em aberto. Cliente esta verificando se pagou.E-Cac:	Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
+          <t>ICMS:10/2025 EFD Transporte de Saldo Credor Incorreto12/2025 GIA/EFD Não apresentou GIA/EFD - Cobrança Recorrente</t>
         </is>
       </c>
       <c r="F54" s="1" t="n">
-        <v>5142</v>
+        <v>5101</v>
       </c>
       <c r="G54" s="1" t="inlineStr">
         <is>
-          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
+          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
         </is>
       </c>
       <c r="H54" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="I54" s="1" t="inlineStr">
@@ -3794,10 +3768,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>46125.49177488426</v>
+        <v>46091.44676890046</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>46129</v>
+        <v>46101</v>
       </c>
       <c r="L54" s="1" t="inlineStr">
         <is>
@@ -3806,7 +3780,7 @@
       </c>
       <c r="M54" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N54" s="1" t="n"/>
@@ -3816,7 +3790,7 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>77862</v>
+        <v>76916</v>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
@@ -3835,20 +3809,20 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>E-Cac: Por favor verificar - Pis e Cofins 02 e 08/2024 em aberto. Cliente esta verificando se pagou.E-Cac: Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
+          <t>ICMS:10/2025 EFD Transporte de Saldo Credor Incorreto12/2025 GIA/EFD Não apresentou GIA/EFD</t>
         </is>
       </c>
       <c r="F55" s="1" t="n">
-        <v>5142</v>
+        <v>5101</v>
       </c>
       <c r="G55" s="1" t="inlineStr">
         <is>
-          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
+          <t>CEREALISTA IDEAL DE SÃO CAETANO LTDA</t>
         </is>
       </c>
       <c r="H55" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Gustavo Santos</t>
         </is>
       </c>
       <c r="I55" s="1" t="inlineStr">
@@ -3857,10 +3831,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>46091.42641597222</v>
+        <v>46052.61991234954</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>46101</v>
+        <v>46065</v>
       </c>
       <c r="L55" s="1" t="inlineStr">
         <is>
@@ -3869,7 +3843,7 @@
       </c>
       <c r="M55" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N55" s="1" t="n"/>
@@ -3879,7 +3853,7 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>77865</v>
+        <v>78344</v>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
@@ -3898,32 +3872,32 @@
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Situação do Contribuinte:Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. </t>
+          <t>SALDO CREDOR INCORRETO	"Reguilarizar imediatamente a EFD 11 e 12/2025, cuja consulta perante SEFAZ SP, apresenta transporte de saldo credor incorreto."</t>
         </is>
       </c>
       <c r="F56" s="1" t="n">
-        <v>5142</v>
+        <v>5132</v>
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
+          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
         </is>
       </c>
       <c r="H56" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Rosilene Santos</t>
         </is>
       </c>
       <c r="I56" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>46091.42728761574</v>
+        <v>46112.41756226852</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
@@ -3932,7 +3906,7 @@
       </c>
       <c r="M56" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N56" s="1" t="n"/>
@@ -3942,7 +3916,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>76771</v>
+        <v>77862</v>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
@@ -3961,7 +3935,7 @@
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. Por favor verificar - Pis e Cofins 02 e 08/2024 Cliente esta verificando se pagou.Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
+          <t>E-Cac: Por favor verificar - Pis e Cofins 02 e 08/2024 em aberto. Cliente esta verificando se pagou.E-Cac: Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
         </is>
       </c>
       <c r="F57" s="1" t="n">
@@ -3983,10 +3957,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>46044.64042673611</v>
+        <v>46091.42641597222</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>46051</v>
+        <v>46101</v>
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
@@ -3995,7 +3969,7 @@
       </c>
       <c r="M57" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N57" s="1" t="n"/>
@@ -4005,16 +3979,16 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>79551</v>
+        <v>77865</v>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
@@ -4024,47 +3998,51 @@
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha fiscal.A Secretaria Especial da Receita Federal do Brasil vem por meio deste aviso informar inconsistências em relação à base de cálculo do IRPF e da CSLL dos rendimentos e ganhos líquidos auferidos em aplicações financeiras de renda fixa e/ou do JCP – Juros sobre Capital Próprio, identificadas ao comparar as informações prestadas na ECF – ESCRITURAÇÃO CONTÁBIL FISCAL com a DIRF – DECLARAÇÃO DO IMPOSTO DE RENDA RETIDO NA FONTE, nas quais esse contribuinte consta como beneficiário, em que valores não foram oferecidos à tributação.</t>
+          <t xml:space="preserve">Situação do Contribuinte:Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. </t>
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>5178</v>
+        <v>5142</v>
       </c>
       <c r="G58" s="1" t="inlineStr">
         <is>
-          <t>COXA PARTICIPACOES S A</t>
-        </is>
-      </c>
-      <c r="H58" s="1" t="n"/>
+          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Henrique</t>
+        </is>
+      </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46171.6082369213</v>
+        <v>46091.42728761574</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>46181</v>
+        <v>46101</v>
       </c>
       <c r="L58" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M58" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N58" s="1" t="n"/>
       <c r="O58" s="1" t="n"/>
       <c r="P58" s="1" t="inlineStr"/>
-      <c r="Q58" s="1" t="n"/>
+      <c r="Q58" s="1" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>76919</v>
+        <v>76771</v>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
@@ -4083,20 +4061,20 @@
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>DUC: Enviar guia de pagamento ref. TFE 12/2023 (Cobrança Recorrente)DASN: Verificar Omissão de DASN SIMEI (Ano-Calendário) 2023 (Cobrança Recorrente)Débito RFB: Enviar guias para pagamento (Cobrança Recorrente)</t>
+          <t>Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. Por favor verificar - Pis e Cofins 02 e 08/2024 Cliente esta verificando se pagou.Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
         </is>
       </c>
       <c r="F59" s="1" t="n">
-        <v>5254</v>
+        <v>5142</v>
       </c>
       <c r="G59" s="1" t="inlineStr">
         <is>
-          <t>RCL COMERCIO VAREJISTA E ROTISSERIE LTDA</t>
+          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
         </is>
       </c>
       <c r="H59" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
@@ -4105,10 +4083,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>46052.62820482639</v>
+        <v>46044.64042673611</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>46065</v>
+        <v>46051</v>
       </c>
       <c r="L59" s="1" t="inlineStr">
         <is>
@@ -4127,7 +4105,7 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>78279</v>
+        <v>78607</v>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
@@ -4146,66 +4124,60 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente aguardará regularização das pendências fiscais e parcelamentos perante RFB, para então proceder com pedido de ressarcimento de saldo credor de IPI	FISLCAL	INFORMATIVO	 </t>
+          <t>Situação do Contribuinte:	Por favor verificar - Transporte de saldo credor incorreto EFD 05, 09, 10, 11 e 12/2024. E-Cac:	Por favor verificar - Pis e Cofins 02 e 08/2024 e DCTFWeb 05/2025 em aberto. Cliente esta verificando se pagou.E-Cac:	Por favor verificar - Cofins  08/2024 em aberto (Verificar Codigo).</t>
         </is>
       </c>
       <c r="F60" s="1" t="n">
-        <v>5256</v>
+        <v>5142</v>
       </c>
       <c r="G60" s="1" t="inlineStr">
         <is>
-          <t>PERFIL REFRIGERAÇÃO INDUSTRIA ,COMÉRCIO E SERVIÇO LTDA</t>
+          <t>MERCADO, PADARIA ACOUGUE E RESTAURANTE OLIMPIA LTDA</t>
         </is>
       </c>
       <c r="H60" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Bruno Henrique</t>
         </is>
       </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>46111.4000221875</v>
+        <v>46125.49177488426</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>46118</v>
+        <v>46129</v>
       </c>
       <c r="L60" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M60" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>46122.70309189815</v>
-      </c>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N60" s="1" t="n"/>
       <c r="O60" s="1" t="n"/>
       <c r="P60" s="1" t="inlineStr"/>
-      <c r="Q60" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resolvido </t>
-        </is>
-      </c>
+      <c r="Q60" s="1" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>76497</v>
+        <v>79551</v>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
@@ -4215,36 +4187,32 @@
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>NFs de Serviços	estamos tomando credito de Pis e Cofins nas NFs  emitidas para o Colegio das empresas do grupo ( 5286 - Lemos e 5285 - Colegio Leão)?</t>
+          <t>Boa tarde! Segue malha fiscal.A Secretaria Especial da Receita Federal do Brasil vem por meio deste aviso informar inconsistências em relação à base de cálculo do IRPF e da CSLL dos rendimentos e ganhos líquidos auferidos em aplicações financeiras de renda fixa e/ou do JCP – Juros sobre Capital Próprio, identificadas ao comparar as informações prestadas na ECF – ESCRITURAÇÃO CONTÁBIL FISCAL com a DIRF – DECLARAÇÃO DO IMPOSTO DE RENDA RETIDO NA FONTE, nas quais esse contribuinte consta como beneficiário, em que valores não foram oferecidos à tributação.</t>
         </is>
       </c>
       <c r="F61" s="1" t="n">
-        <v>5284</v>
+        <v>5178</v>
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t>COLÉGIO COGNOS EDUCACIONAL LTDA</t>
-        </is>
-      </c>
-      <c r="H61" s="1" t="inlineStr">
-        <is>
-          <t>Luan Batista</t>
-        </is>
-      </c>
+          <t>COXA PARTICIPACOES S A</t>
+        </is>
+      </c>
+      <c r="H61" s="1" t="n"/>
       <c r="I61" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>46030.5029665162</v>
+        <v>46171.6082369213</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>46037</v>
+        <v>46181</v>
       </c>
       <c r="L61" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M61" s="1" t="inlineStr">
@@ -4255,11 +4223,11 @@
       <c r="N61" s="1" t="n"/>
       <c r="O61" s="1" t="n"/>
       <c r="P61" s="1" t="inlineStr"/>
-      <c r="Q61" s="1" t="inlineStr"/>
+      <c r="Q61" s="1" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>76815</v>
+        <v>76919</v>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
@@ -4278,32 +4246,32 @@
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>RESSARCIMENTO IPI	Apresentar posição de saldo de créditos de IPI, ressarcidos anteriormente cujo saldo não foi abatido pela RFB em dívidas tributárias de forma que apresentemos ao cliente sua posição de saldo disponível para compensação de impostos a vencer.</t>
+          <t>DUC: Enviar guia de pagamento ref. TFE 12/2023 (Cobrança Recorrente)DASN: Verificar Omissão de DASN SIMEI (Ano-Calendário) 2023 (Cobrança Recorrente)Débito RFB: Enviar guias para pagamento (Cobrança Recorrente)</t>
         </is>
       </c>
       <c r="F62" s="1" t="n">
-        <v>5370</v>
+        <v>5254</v>
       </c>
       <c r="G62" s="1" t="inlineStr">
         <is>
-          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
+          <t>RCL COMERCIO VAREJISTA E ROTISSERIE LTDA</t>
         </is>
       </c>
       <c r="H62" s="1" t="inlineStr">
         <is>
-          <t>tatianag</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>46048.48993850694</v>
+        <v>46052.62820482639</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>46055</v>
+        <v>46065</v>
       </c>
       <c r="L62" s="1" t="inlineStr">
         <is>
@@ -4312,7 +4280,7 @@
       </c>
       <c r="M62" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N62" s="1" t="n"/>
@@ -4322,7 +4290,7 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>77395</v>
+        <v>78279</v>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
@@ -4341,51 +4309,57 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>DUC SP:Apresentado consulta COM PENDENCIAS. Encaminhar para cliente guia atualizada.</t>
+          <t xml:space="preserve">Cliente aguardará regularização das pendências fiscais e parcelamentos perante RFB, para então proceder com pedido de ressarcimento de saldo credor de IPI	FISLCAL	INFORMATIVO	 </t>
         </is>
       </c>
       <c r="F63" s="1" t="n">
-        <v>5392</v>
+        <v>5256</v>
       </c>
       <c r="G63" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">E E F SERVICOS ADMINISTRATIVOS LTDA </t>
+          <t>PERFIL REFRIGERAÇÃO INDUSTRIA ,COMÉRCIO E SERVIÇO LTDA</t>
         </is>
       </c>
       <c r="H63" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>46077.38946674769</v>
+        <v>46111.4000221875</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>46084</v>
+        <v>46118</v>
       </c>
       <c r="L63" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M63" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
-        </is>
-      </c>
-      <c r="N63" s="1" t="n"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>46122.70309189815</v>
+      </c>
       <c r="O63" s="1" t="n"/>
       <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="inlineStr"/>
+      <c r="Q63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>77606</v>
+        <v>76497</v>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
@@ -4404,32 +4378,32 @@
       </c>
       <c r="E64" s="1" t="inlineStr">
         <is>
-          <t>5416	"	GALDINO SERVICOS ADMINISTRATIVOS LTDA"	GC	Ricardo Silva	Darlan Rodrigues	DAS	Verificar pendencia de MAED - PGDAS-D em aberto	27/02/2026	13/03/2026	13/03/2026	PENDENCIA</t>
+          <t>NFs de Serviços	estamos tomando credito de Pis e Cofins nas NFs  emitidas para o Colegio das empresas do grupo ( 5286 - Lemos e 5285 - Colegio Leão)?</t>
         </is>
       </c>
       <c r="F64" s="1" t="n">
-        <v>5416</v>
+        <v>5284</v>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
-          <t>GALDINO SERVICOS ADMINISTRATIVOS LTDA</t>
+          <t>COLÉGIO COGNOS EDUCACIONAL LTDA</t>
         </is>
       </c>
       <c r="H64" s="1" t="inlineStr">
         <is>
-          <t>Igor Valezi</t>
+          <t>Luan Batista</t>
         </is>
       </c>
       <c r="I64" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>46083.37643741899</v>
+        <v>46030.5029665162</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>46090</v>
+        <v>46037</v>
       </c>
       <c r="L64" s="1" t="inlineStr">
         <is>
@@ -4438,7 +4412,7 @@
       </c>
       <c r="M64" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N64" s="1" t="n"/>
@@ -4448,70 +4422,66 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>76808</v>
+        <v>79674</v>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E65" s="1" t="inlineStr">
         <is>
-          <t>ICMS	Ref. 11/2025 EFD-ST Transporte de Saldo Credor Incorreto</t>
+          <t>Favor retificar DCTF do período de MAIO/2025. Os valores de PIS e COFINS estão divergentes da apuração que consta no sistema de análise.</t>
         </is>
       </c>
       <c r="F65" s="1" t="n">
-        <v>5466</v>
+        <v>5331</v>
       </c>
       <c r="G65" s="1" t="inlineStr">
         <is>
-          <t>ALSEV COMERCIO DE ALUMINIO LTDA</t>
-        </is>
-      </c>
-      <c r="H65" s="1" t="inlineStr">
-        <is>
-          <t>Eliane Moreira</t>
-        </is>
-      </c>
+          <t>PIRANA - AUTO SERVIÇO LTDA</t>
+        </is>
+      </c>
+      <c r="H65" s="1" t="n"/>
       <c r="I65" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>46048.47000836806</v>
+        <v>46176.62133761574</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>46055</v>
+        <v>46191</v>
       </c>
       <c r="L65" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M65" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N65" s="1" t="n"/>
       <c r="O65" s="1" t="n"/>
       <c r="P65" s="1" t="inlineStr"/>
-      <c r="Q65" s="1" t="inlineStr"/>
+      <c r="Q65" s="1" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>76399</v>
+        <v>76815</v>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
@@ -4530,20 +4500,20 @@
       </c>
       <c r="E66" s="1" t="inlineStr">
         <is>
-          <t>Sucata	Informar fiscalmente como deve-se proceder para o envio e retorno dos produtos danificados que voltam para revenda</t>
+          <t>RESSARCIMENTO IPI	Apresentar posição de saldo de créditos de IPI, ressarcidos anteriormente cujo saldo não foi abatido pela RFB em dívidas tributárias de forma que apresentemos ao cliente sua posição de saldo disponível para compensação de impostos a vencer.</t>
         </is>
       </c>
       <c r="F66" s="1" t="n">
-        <v>5466</v>
+        <v>5370</v>
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t>ALSEV COMERCIO DE ALUMINIO LTDA</t>
+          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>tatianag</t>
         </is>
       </c>
       <c r="I66" s="1" t="inlineStr">
@@ -4552,14 +4522,14 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>46024.69328252315</v>
+        <v>46048.48993850694</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>46031</v>
+        <v>46055</v>
       </c>
       <c r="L66" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M66" s="1" t="inlineStr">
@@ -4567,20 +4537,14 @@
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
-        <v>46122.57509690972</v>
-      </c>
+      <c r="N66" s="1" t="n"/>
       <c r="O66" s="1" t="n"/>
       <c r="P66" s="1" t="inlineStr"/>
-      <c r="Q66" s="1" t="inlineStr">
-        <is>
-          <t>resolvido</t>
-        </is>
-      </c>
+      <c r="Q66" s="1" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>76463</v>
+        <v>77395</v>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
@@ -4599,125 +4563,123 @@
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>Elaborar planilha do fator R, considerando sempre o mês anterior. Para todas as empresas do Grupo.Por favor, referente aos dois topicos acima, precisamos revisar todo o ano de 2024, cliente alega que mesmo quando a MG assumiu em 02/2024, ficou acordado de revisar e corrigir eventual erros de janeiro de 2024. foi feito?Por favor, precisamos melhor as repostas para o cliente, apuração pelo regime de caixa.</t>
+          <t>DUC SP:Apresentado consulta COM PENDENCIAS. Encaminhar para cliente guia atualizada.</t>
         </is>
       </c>
       <c r="F67" s="1" t="n">
-        <v>5472</v>
+        <v>5392</v>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t>T C DE CASTRO EMPREENDIMENTOS LTDA</t>
+          <t xml:space="preserve">E E F SERVICOS ADMINISTRATIVOS LTDA </t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="I67" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>46029.71428680555</v>
+        <v>46077.38946674769</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>46036</v>
+        <v>46084</v>
       </c>
       <c r="L67" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M67" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="n">
-        <v>46122.57568209491</v>
-      </c>
+          <t>mtoledo</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="n"/>
       <c r="O67" s="1" t="n"/>
       <c r="P67" s="1" t="inlineStr"/>
-      <c r="Q67" s="1" t="inlineStr">
-        <is>
-          <t>resolvido</t>
-        </is>
-      </c>
+      <c r="Q67" s="1" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>79590</v>
+        <v>77606</v>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>Omissão na Declaração DCTF referente 12/2024, conforme consulta fiscal anexa. Contador atual entregou DCTF conforme recibo, apenas para liberação da pendencia. Precisamos retficar com as informações corretas.</t>
+          <t>5416	"	GALDINO SERVICOS ADMINISTRATIVOS LTDA"	GC	Ricardo Silva	Darlan Rodrigues	DAS	Verificar pendencia de MAED - PGDAS-D em aberto	27/02/2026	13/03/2026	13/03/2026	PENDENCIA</t>
         </is>
       </c>
       <c r="F68" s="1" t="n">
-        <v>5530</v>
+        <v>5416</v>
       </c>
       <c r="G68" s="1" t="inlineStr">
         <is>
-          <t>GONJES EDIFICACOES E COMERCIO LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H68" s="1" t="n"/>
+          <t>GALDINO SERVICOS ADMINISTRATIVOS LTDA</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>Igor Valezi</t>
+        </is>
+      </c>
       <c r="I68" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>46174.64053989583</v>
+        <v>46083.37643741899</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>46176</v>
+        <v>46090</v>
       </c>
       <c r="L68" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M68" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N68" s="1" t="n"/>
       <c r="O68" s="1" t="n"/>
       <c r="P68" s="1" t="inlineStr"/>
-      <c r="Q68" s="1" t="n"/>
+      <c r="Q68" s="1" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>79625</v>
+        <v>76808</v>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
@@ -4727,47 +4689,51 @@
       </c>
       <c r="E69" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!!Retificar PGDAS 01/2024 á 12/2024.</t>
+          <t>ICMS	Ref. 11/2025 EFD-ST Transporte de Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="F69" s="1" t="n">
-        <v>5650</v>
+        <v>5466</v>
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>RICHETTI COMERCIO DE BEBIDAS E ALIMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H69" s="1" t="n"/>
+          <t>ALSEV COMERCIO DE ALUMINIO LTDA</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>Eliane Moreira</t>
+        </is>
+      </c>
       <c r="I69" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>46175.61280998842</v>
+        <v>46048.47000836806</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>46177</v>
+        <v>46055</v>
       </c>
       <c r="L69" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M69" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N69" s="1" t="n"/>
       <c r="O69" s="1" t="n"/>
       <c r="P69" s="1" t="inlineStr"/>
-      <c r="Q69" s="1" t="n"/>
+      <c r="Q69" s="1" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>78422</v>
+        <v>76399</v>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
@@ -4786,51 +4752,57 @@
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>Por favor, verificar junto ao cliente a situação sindical. Foi feito?</t>
+          <t>Sucata	Informar fiscalmente como deve-se proceder para o envio e retorno dos produtos danificados que voltam para revenda</t>
         </is>
       </c>
       <c r="F70" s="1" t="n">
-        <v>5886</v>
+        <v>5466</v>
       </c>
       <c r="G70" s="1" t="inlineStr">
         <is>
-          <t>ITA - TECNOLOGIA ASSISTIVA LTDA</t>
+          <t>ALSEV COMERCIO DE ALUMINIO LTDA</t>
         </is>
       </c>
       <c r="H70" s="1" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>46113.65967237268</v>
+        <v>46024.69328252315</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>46126</v>
+        <v>46031</v>
       </c>
       <c r="L70" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M70" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N70" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>46122.57509690972</v>
+      </c>
       <c r="O70" s="1" t="n"/>
       <c r="P70" s="1" t="inlineStr"/>
-      <c r="Q70" s="1" t="inlineStr"/>
+      <c r="Q70" s="1" t="inlineStr">
+        <is>
+          <t>resolvido</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>76458</v>
+        <v>76463</v>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
@@ -4849,15 +4821,15 @@
       </c>
       <c r="E71" s="1" t="inlineStr">
         <is>
-          <t>Divergência fechamento fiscal 04/2025	"Por gentileza, verificar definição do e-mail enviado em , sobre a divergência no fechamento fiscal de 04/2025, apontada para correção.08/09: Concluído.26/11/2025: Necessário verificar o aproveitamento do valor pago a maior em 04/2025 no DAS de 10/2025."</t>
+          <t>Elaborar planilha do fator R, considerando sempre o mês anterior. Para todas as empresas do Grupo.Por favor, referente aos dois topicos acima, precisamos revisar todo o ano de 2024, cliente alega que mesmo quando a MG assumiu em 02/2024, ficou acordado de revisar e corrigir eventual erros de janeiro de 2024. foi feito?Por favor, precisamos melhor as repostas para o cliente, apuração pelo regime de caixa.</t>
         </is>
       </c>
       <c r="F71" s="1" t="n">
-        <v>5891</v>
+        <v>5472</v>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>PRO-CAM COMERCIAL LTDA</t>
+          <t>T C DE CASTRO EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H71" s="1" t="inlineStr">
@@ -4871,7 +4843,7 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>46029.68589652778</v>
+        <v>46029.71428680555</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>46036</v>
@@ -4887,7 +4859,7 @@
         </is>
       </c>
       <c r="N71" s="2" t="n">
-        <v>46122.57529575231</v>
+        <v>46122.57568209491</v>
       </c>
       <c r="O71" s="1" t="n"/>
       <c r="P71" s="1" t="inlineStr"/>
@@ -4899,34 +4871,34 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,por gentileza, providenciar balanço e DRE 2025 da empresa: 5912 - L G Coelho Representações  e também 1 trimestre 2026</t>
+          <t>Omissão na Declaração DCTF referente 12/2024, conforme consulta fiscal anexa. Contador atual entregou DCTF conforme recibo, apenas para liberação da pendencia. Precisamos retficar com as informações corretas.</t>
         </is>
       </c>
       <c r="F72" s="1" t="n">
-        <v>5912</v>
+        <v>5530</v>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">L G Coelho Representacoes </t>
+          <t>GONJES EDIFICACOES E COMERCIO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H72" s="1" t="n"/>
@@ -4936,10 +4908,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>46174.63016921296</v>
+        <v>46174.64053989583</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="L72" s="1" t="inlineStr">
         <is>
@@ -4948,7 +4920,7 @@
       </c>
       <c r="M72" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N72" s="1" t="n"/>
@@ -4958,47 +4930,47 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>79585</v>
+        <v>79664</v>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue mensagem recebida no DEC, por gentileza, verificar e corrigir. -  Existência de omissão/inconsistência/incorreção no(s) período(s): 02/2026.</t>
+          <t>Autoregularização  Simples Nacional - Janeiro a Dezembro 2024.Cliente recebeu notificação de auto regularização referente período mencionado acima. Por gentileza, providenciar dentro do prazo estipulado pela Receita.</t>
         </is>
       </c>
       <c r="F73" s="1" t="n">
-        <v>5920</v>
+        <v>5595</v>
       </c>
       <c r="G73" s="1" t="inlineStr">
         <is>
-          <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
+          <t>SUPERMERCADO QUEIROZ LTDA</t>
         </is>
       </c>
       <c r="H73" s="1" t="n"/>
       <c r="I73" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>46174.62819915509</v>
+        <v>46176.46938182871</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>46176</v>
+        <v>46199</v>
       </c>
       <c r="L73" s="1" t="inlineStr">
         <is>
@@ -5007,7 +4979,7 @@
       </c>
       <c r="M73" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N73" s="1" t="n"/>
@@ -5017,34 +4989,34 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>79638</v>
+        <v>79683</v>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>Pesquisa IBGE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>Pesquisa IBGE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza verificar o e-mail referente a pesquisa IBGE da Anderson Julio Fernandes. </t>
+          <t>Por gentileza, verificar omissão de DCTFWeb 12/2025.</t>
         </is>
       </c>
       <c r="F74" s="1" t="n">
-        <v>6012</v>
+        <v>5628</v>
       </c>
       <c r="G74" s="1" t="inlineStr">
         <is>
-          <t>ANDERSON JULIO FERNANDES</t>
+          <t>VINILOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="H74" s="1" t="n"/>
@@ -5054,10 +5026,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>46175.68464371528</v>
+        <v>46176.6925068287</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="L74" s="1" t="inlineStr">
         <is>
@@ -5076,47 +5048,47 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>79618</v>
+        <v>79625</v>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Balanço, Balancete e DRE  após a implantação de saldo com a posição de 31.12.2025 para enviar ao atual contador, e com a posição de 01.01.2026 a 28.02.2026- A solicitação foi feita por e-mail  desde 06/05/2026 11:23  </t>
+          <t>Boa tarde!!Retificar PGDAS 01/2024 á 12/2024.</t>
         </is>
       </c>
       <c r="F75" s="1" t="n">
-        <v>6016</v>
+        <v>5650</v>
       </c>
       <c r="G75" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
+          <t>RICHETTI COMERCIO DE BEBIDAS E ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H75" s="1" t="n"/>
       <c r="I75" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>46175.58080038195</v>
+        <v>46175.61280998842</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="L75" s="1" t="inlineStr">
         <is>
@@ -5125,7 +5097,7 @@
       </c>
       <c r="M75" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N75" s="1" t="n"/>
@@ -5135,34 +5107,34 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>79617</v>
+        <v>79678</v>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>Balanço, Balancete e Dre para colher assinatura com posição de 31.12.2025 e  Balanço, Balancete e Dre com posição de 28.02.2026 -Assunto iniciou em 06.05.2026 -ENC: ALUMÍNIO IMPERIAL  -Encerramento de 31.12.2025 -  reforçado no e-mail de 27 de maio de 2026 13:05  -RES: Balanço Patrimonial e DRE - Ano Calendário 2025 - Click Comércio Digital Ltda</t>
+          <t>Por gentileza, verificar omissão de DCTFWeb 12/2025</t>
         </is>
       </c>
       <c r="F76" s="1" t="n">
-        <v>6017</v>
+        <v>5779</v>
       </c>
       <c r="G76" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLICK COMERCIO DIGITAL LTDA </t>
+          <t>A ESTANCIA MORRO GRANDE - CENTRO DE REABILITACAO SOCIAL LTDA</t>
         </is>
       </c>
       <c r="H76" s="1" t="n"/>
@@ -5172,10 +5144,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>46175.57705008102</v>
+        <v>46176.64156195602</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>46176</v>
+        <v>46181</v>
       </c>
       <c r="L76" s="1" t="inlineStr">
         <is>
@@ -5184,7 +5156,7 @@
       </c>
       <c r="M76" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N76" s="1" t="n"/>
@@ -5194,134 +5166,148 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>79620</v>
+        <v>78422</v>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
+          <t>Por favor, verificar junto ao cliente a situação sindical. Foi feito?</t>
         </is>
       </c>
       <c r="F77" s="1" t="n">
-        <v>6018</v>
+        <v>5886</v>
       </c>
       <c r="G77" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENOR PRECO BRASIL DIGITAL LTDA </t>
-        </is>
-      </c>
-      <c r="H77" s="1" t="n"/>
+          <t>ITA - TECNOLOGIA ASSISTIVA LTDA</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>Oliene Mariano</t>
+        </is>
+      </c>
       <c r="I77" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>46175.58723063657</v>
+        <v>46113.65967237268</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>46176</v>
+        <v>46126</v>
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M77" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N77" s="1" t="n"/>
       <c r="O77" s="1" t="n"/>
       <c r="P77" s="1" t="inlineStr"/>
-      <c r="Q77" s="1" t="n"/>
+      <c r="Q77" s="1" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>79621</v>
+        <v>76458</v>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
+          <t>Divergência fechamento fiscal 04/2025	"Por gentileza, verificar definição do e-mail enviado em , sobre a divergência no fechamento fiscal de 04/2025, apontada para correção.08/09: Concluído.26/11/2025: Necessário verificar o aproveitamento do valor pago a maior em 04/2025 no DAS de 10/2025."</t>
         </is>
       </c>
       <c r="F78" s="1" t="n">
-        <v>6019</v>
+        <v>5891</v>
       </c>
       <c r="G78" s="1" t="inlineStr">
         <is>
-          <t>FELIPE CIUFFA LIMA LTDA</t>
-        </is>
-      </c>
-      <c r="H78" s="1" t="n"/>
+          <t>PRO-CAM COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I78" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46175.58796859954</v>
+        <v>46029.68589652778</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>46176</v>
+        <v>46036</v>
       </c>
       <c r="L78" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M78" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N78" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>46122.57529575231</v>
+      </c>
       <c r="O78" s="1" t="n"/>
       <c r="P78" s="1" t="inlineStr"/>
-      <c r="Q78" s="1" t="n"/>
+      <c r="Q78" s="1" t="inlineStr">
+        <is>
+          <t>resolvido</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>79619</v>
+        <v>79651</v>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
@@ -5331,28 +5317,28 @@
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
+          <t>Caros, cliente solicita a antecipação da ECF 2025. "Eu estou tentando uma linha de crédito de pronamp mas preciso que já tenham entregue a ECF de 2025"</t>
         </is>
       </c>
       <c r="F79" s="1" t="n">
-        <v>6019</v>
+        <v>5909</v>
       </c>
       <c r="G79" s="1" t="inlineStr">
         <is>
-          <t>FELIPE CIUFFA LIMA LTDA</t>
+          <t xml:space="preserve">Odonto Store Equipamentos Odotologicos LTDA </t>
         </is>
       </c>
       <c r="H79" s="1" t="n"/>
       <c r="I79" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>46175.5866752662</v>
+        <v>46175.76486354167</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>46176</v>
+        <v>46182</v>
       </c>
       <c r="L79" s="1" t="inlineStr">
         <is>
@@ -5361,7 +5347,7 @@
       </c>
       <c r="M79" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N79" s="1" t="n"/>
@@ -5371,7 +5357,7 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>79622</v>
+        <v>79586</v>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
@@ -5385,33 +5371,33 @@
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
+          <t>Boa tarde,por gentileza, providenciar balanço e DRE 2025 da empresa: 5912 - L G Coelho Representações  e também 1 trimestre 2026</t>
         </is>
       </c>
       <c r="F80" s="1" t="n">
-        <v>6024</v>
+        <v>5912</v>
       </c>
       <c r="G80" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">F C COMERCIO DIGITAL LTDA </t>
+          <t xml:space="preserve">L G Coelho Representacoes </t>
         </is>
       </c>
       <c r="H80" s="1" t="n"/>
       <c r="I80" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>46175.58973290509</v>
+        <v>46174.63016921296</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="L80" s="1" t="inlineStr">
         <is>
@@ -5420,7 +5406,7 @@
       </c>
       <c r="M80" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N80" s="1" t="n"/>
@@ -5430,16 +5416,16 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>76562</v>
+        <v>79585</v>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
@@ -5449,498 +5435,460 @@
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>ICMS :Por favor, verificar se temos ICMS em aberto e enviar para o cliente (inclusive divida ativa).</t>
+          <t>Boa tarde! Segue mensagem recebida no DEC, por gentileza, verificar e corrigir. -  Existência de omissão/inconsistência/incorreção no(s) período(s): 02/2026.</t>
         </is>
       </c>
       <c r="F81" s="1" t="n">
-        <v>6070</v>
+        <v>5920</v>
       </c>
       <c r="G81" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
-        </is>
-      </c>
-      <c r="H81" s="1" t="inlineStr">
-        <is>
-          <t>Gustavo Tonan</t>
-        </is>
-      </c>
+          <t>G13 IMPORTAÇÃO E EXPORTAÇÃO LTDA (FILIAL 3)</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n"/>
       <c r="I81" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>46034.51344255787</v>
+        <v>46174.62819915509</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>46042</v>
+        <v>46176</v>
       </c>
       <c r="L81" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M81" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N81" s="1" t="n"/>
       <c r="O81" s="1" t="n"/>
       <c r="P81" s="1" t="inlineStr"/>
-      <c r="Q81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>78058</v>
+        <v>79638</v>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Pesquisa IBGE</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pesquisa IBGE</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>ICMS: Cliente não recebeu a guia de ICMS, foi enviado para protesto, reembolsar multa e juros! 09/2025 - R$ 567,00</t>
+          <t xml:space="preserve">Por gentileza verificar o e-mail referente a pesquisa IBGE da Anderson Julio Fernandes. </t>
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>6070</v>
+        <v>6012</v>
       </c>
       <c r="G82" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
-        </is>
-      </c>
-      <c r="H82" s="1" t="inlineStr">
-        <is>
-          <t>Gustavo Tonan</t>
-        </is>
-      </c>
+          <t>ANDERSON JULIO FERNANDES</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n"/>
       <c r="I82" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>46098.66110049769</v>
+        <v>46175.68464371528</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>46106</v>
+        <v>46178</v>
       </c>
       <c r="L82" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M82" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N82" s="1" t="n"/>
       <c r="O82" s="1" t="n"/>
       <c r="P82" s="1" t="inlineStr"/>
-      <c r="Q82" s="1" t="inlineStr"/>
+      <c r="Q82" s="1" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>78059</v>
+        <v>79618</v>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
         <is>
-          <t>INSS: Cliente solicitou a inclusão e geração do Pro-Labore do inicio de 2025, por favor, gerar e enviar uma guia por mês do período em atraso!</t>
+          <t xml:space="preserve">Balanço, Balancete e DRE  após a implantação de saldo com a posição de 31.12.2025 para enviar ao atual contador, e com a posição de 01.01.2026 a 28.02.2026- A solicitação foi feita por e-mail  desde 06/05/2026 11:23  </t>
         </is>
       </c>
       <c r="F83" s="1" t="n">
-        <v>6070</v>
+        <v>6016</v>
       </c>
       <c r="G83" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
-        </is>
-      </c>
-      <c r="H83" s="1" t="inlineStr">
-        <is>
-          <t>Janaina Rocha</t>
-        </is>
-      </c>
+          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="n"/>
       <c r="I83" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>46098.66206072917</v>
+        <v>46175.58080038195</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>46107</v>
+        <v>46176</v>
       </c>
       <c r="L83" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M83" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N83" s="1" t="n"/>
       <c r="O83" s="1" t="n"/>
       <c r="P83" s="1" t="inlineStr"/>
-      <c r="Q83" s="1" t="inlineStr"/>
+      <c r="Q83" s="1" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>76372</v>
+        <v>79617</v>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D84" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E84" s="1" t="inlineStr">
         <is>
-          <t>EFD SALDO TRANSPORTE SALDO CREDOR INCORRETO	Avaliar imediatamentos motivos que levaram a SEFAZ apresentar transporte de saldo credor incorreto para EFD 10/2025.</t>
+          <t>Balanço, Balancete e Dre para colher assinatura com posição de 31.12.2025 e  Balanço, Balancete e Dre com posição de 28.02.2026 -Assunto iniciou em 06.05.2026 -ENC: ALUMÍNIO IMPERIAL  -Encerramento de 31.12.2025 -  reforçado no e-mail de 27 de maio de 2026 13:05  -RES: Balanço Patrimonial e DRE - Ano Calendário 2025 - Click Comércio Digital Ltda</t>
         </is>
       </c>
       <c r="F84" s="1" t="n">
-        <v>6088</v>
+        <v>6017</v>
       </c>
       <c r="G84" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
-        </is>
-      </c>
-      <c r="H84" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+          <t xml:space="preserve">CLICK COMERCIO DIGITAL LTDA </t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="n"/>
       <c r="I84" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>46024.66418596065</v>
+        <v>46175.57705008102</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>46031</v>
+        <v>46176</v>
       </c>
       <c r="L84" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M84" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N84" s="2" t="n">
-        <v>46122.57290100694</v>
-      </c>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N84" s="1" t="n"/>
       <c r="O84" s="1" t="n"/>
       <c r="P84" s="1" t="inlineStr"/>
-      <c r="Q84" s="1" t="inlineStr">
-        <is>
-          <t>resolvido</t>
-        </is>
-      </c>
+      <c r="Q84" s="1" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>77015</v>
+        <v>79620</v>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
         <is>
-          <t>Fiscal	EFD 10, 11 e 12/2025 - Transporte de Saldo Credor Incorreto, corrigir por favor!</t>
+          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
         </is>
       </c>
       <c r="F85" s="1" t="n">
-        <v>6106</v>
+        <v>6018</v>
       </c>
       <c r="G85" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
-        </is>
-      </c>
-      <c r="H85" s="1" t="inlineStr">
-        <is>
-          <t>ilarao</t>
-        </is>
-      </c>
+          <t xml:space="preserve">MENOR PRECO BRASIL DIGITAL LTDA </t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="n"/>
       <c r="I85" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>46057.59395454861</v>
+        <v>46175.58723063657</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>46064</v>
+        <v>46176</v>
       </c>
       <c r="L85" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M85" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N85" s="1" t="n"/>
       <c r="O85" s="1" t="n"/>
       <c r="P85" s="1" t="inlineStr"/>
-      <c r="Q85" s="1" t="inlineStr"/>
+      <c r="Q85" s="1" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>77019</v>
+        <v>79621</v>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D86" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E86" s="1" t="inlineStr">
         <is>
-          <t>EFD	EFD 06 e 08/2025 - saldo Incorreto - por favor, verificar!ISS retido	Por favor, precisamos com urgência gerar e enviar para o cliente as guias de ISS retido de outros municipios. Cliente cobrando em aberto desde 04/2025. cliente pedindo reembolso de multa e juros.</t>
+          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
         </is>
       </c>
       <c r="F86" s="1" t="n">
-        <v>6148</v>
+        <v>6019</v>
       </c>
       <c r="G86" s="1" t="inlineStr">
         <is>
-          <t>VALE CONCRETO LTDA</t>
-        </is>
-      </c>
-      <c r="H86" s="1" t="inlineStr">
-        <is>
-          <t>Romario Silva</t>
-        </is>
-      </c>
+          <t>FELIPE CIUFFA LIMA LTDA</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="n"/>
       <c r="I86" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>46057.64800393519</v>
+        <v>46175.58796859954</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>46064</v>
+        <v>46176</v>
       </c>
       <c r="L86" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M86" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N86" s="1" t="n"/>
       <c r="O86" s="1" t="n"/>
       <c r="P86" s="1" t="inlineStr"/>
-      <c r="Q86" s="1" t="inlineStr"/>
+      <c r="Q86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>79371</v>
+        <v>79619</v>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeHOTEIS - ITALO BRASILEIRAASSUNTO: Classificação fiscal / apuração de PIS e COFINSPENDÊNCIA: "Rodeio Hospedagem - Gabriela afirma que Airton faz mensalmente depósitos para cobrir as despesas, porem, não localizei isso na contabilidade. Solicitei envio das informações pela GabrielaTODOS OS HOTÉIS TEM VALORES A CLASSIFICAR, PRECISAMOS VERIFICAR.Loft - Tem uma conta de empréstimo entre empresas de 76.000,00 - precisamos verificar a origemO.L.R - Não recebemos o baçlanço de abertura?MOTEL CAMPO GRANDE - Não tem aporte do AirtonRENOVAÇÃO - Verificar balanço de abertura"</t>
+          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
         </is>
       </c>
       <c r="F87" s="1" t="n">
-        <v>6159</v>
+        <v>6019</v>
       </c>
       <c r="G87" s="1" t="inlineStr">
         <is>
-          <t>LOFT EMPREENDIMENTOS HOTELEIROS LTDA</t>
-        </is>
-      </c>
-      <c r="H87" s="1" t="inlineStr">
-        <is>
-          <t>Danielle Silva</t>
-        </is>
-      </c>
+          <t>FELIPE CIUFFA LIMA LTDA</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="n"/>
       <c r="I87" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>46161.65761836806</v>
+        <v>46175.5866752662</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="L87" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M87" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N87" s="1" t="n"/>
       <c r="O87" s="1" t="n"/>
       <c r="P87" s="1" t="inlineStr"/>
-      <c r="Q87" s="1" t="inlineStr"/>
+      <c r="Q87" s="1" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>79370</v>
+        <v>79622</v>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D88" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
         <is>
-          <t>Boa tardeITALO BRASILEIRAASSUNTO: Emprestimos entre empresasPENDÊNCIA: Esses valores são referentes a aportes que Ratinho faz para cobrir as despesas, como estamos contabilizando?</t>
+          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
         </is>
       </c>
       <c r="F88" s="1" t="n">
-        <v>6179</v>
+        <v>6024</v>
       </c>
       <c r="G88" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
-        </is>
-      </c>
-      <c r="H88" s="1" t="inlineStr">
-        <is>
-          <t>Danielle Silva</t>
-        </is>
-      </c>
+          <t xml:space="preserve">F C COMERCIO DIGITAL LTDA </t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="n"/>
       <c r="I88" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>46161.65683599537</v>
+        <v>46175.58973290509</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="L88" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M88" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N88" s="1" t="n"/>
       <c r="O88" s="1" t="n"/>
       <c r="P88" s="1" t="inlineStr"/>
-      <c r="Q88" s="1" t="inlineStr"/>
+      <c r="Q88" s="1" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>77930</v>
+        <v>76562</v>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
@@ -5959,20 +5907,20 @@
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.ITALO BRASILEIRA.ASSUNTO: Impostos recebidos na data do vencimentoPENDÊNCIA: Cliente reclama que ultimamente tem recebido no dia do vencimento e pior, no FINAL DO DIA. Favor verificar o que está ocorrendo pois Gabriela afirma cumprir todos os prazos e salvar todos os docuementos em tempo hábil</t>
+          <t>ICMS :Por favor, verificar se temos ICMS em aberto e enviar para o cliente (inclusive divida ativa).</t>
         </is>
       </c>
       <c r="F89" s="1" t="n">
-        <v>6179</v>
+        <v>6070</v>
       </c>
       <c r="G89" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
         </is>
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>rubial</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="I89" s="1" t="inlineStr">
@@ -5981,10 +5929,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46093.45040390046</v>
+        <v>46034.51344255787</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>46107</v>
+        <v>46042</v>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
@@ -5993,7 +5941,7 @@
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N89" s="1" t="n"/>
@@ -6003,7 +5951,7 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>77931</v>
+        <v>78058</v>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
@@ -6022,20 +5970,20 @@
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.ITALO BRASILEIRA.ASSUNTO: Classificação fiscal / apuração de PIS e COFINSPENDÊNCIA: Precisamos classificar corretamente as compras do cliente, o que for para revenda deve fazer parte da base de calculo pois o PIS e COFINS está muito alto. Favor revisar todos os fechamentos e buscar possíveis créditos de PIS e COFINS - PENDENTE</t>
+          <t>ICMS: Cliente não recebeu a guia de ICMS, foi enviado para protesto, reembolsar multa e juros! 09/2025 - R$ 567,00</t>
         </is>
       </c>
       <c r="F90" s="1" t="n">
-        <v>6179</v>
+        <v>6070</v>
       </c>
       <c r="G90" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
         </is>
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>rubial</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="I90" s="1" t="inlineStr">
@@ -6044,10 +5992,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46093.45111496528</v>
+        <v>46098.66110049769</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>46107</v>
+        <v>46106</v>
       </c>
       <c r="L90" s="1" t="inlineStr">
         <is>
@@ -6056,7 +6004,7 @@
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N90" s="1" t="n"/>
@@ -6066,7 +6014,7 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>76465</v>
+        <v>78059</v>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
@@ -6085,66 +6033,60 @@
       </c>
       <c r="E91" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Termo de Intimação Receia federalpor favor, verificar termo de intimação, cliente pagou IRPJ e CSLL 2° e 3°  trimestre/2025 -  em 3 Parcelas </t>
+          <t>INSS: Cliente solicitou a inclusão e geração do Pro-Labore do inicio de 2025, por favor, gerar e enviar uma guia por mês do período em atraso!</t>
         </is>
       </c>
       <c r="F91" s="1" t="n">
-        <v>6217</v>
+        <v>6070</v>
       </c>
       <c r="G91" s="1" t="inlineStr">
         <is>
-          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
+          <t xml:space="preserve">MEGACAR DISTRIBUIDORA AUTOMOTIVA LTDA </t>
         </is>
       </c>
       <c r="H91" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Janaina Rocha</t>
         </is>
       </c>
       <c r="I91" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>46029.71832045139</v>
+        <v>46098.66206072917</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>46036</v>
+        <v>46107</v>
       </c>
       <c r="L91" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M91" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="n">
-        <v>46122.57589409722</v>
-      </c>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N91" s="1" t="n"/>
       <c r="O91" s="1" t="n"/>
       <c r="P91" s="1" t="inlineStr"/>
-      <c r="Q91" s="1" t="inlineStr">
-        <is>
-          <t>resolvido</t>
-        </is>
-      </c>
+      <c r="Q91" s="1" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>79626</v>
+        <v>76372</v>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D92" s="1" t="inlineStr">
@@ -6154,32 +6096,36 @@
       </c>
       <c r="E92" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2025.</t>
+          <t>EFD SALDO TRANSPORTE SALDO CREDOR INCORRETO	Avaliar imediatamentos motivos que levaram a SEFAZ apresentar transporte de saldo credor incorreto para EFD 10/2025.</t>
         </is>
       </c>
       <c r="F92" s="1" t="n">
-        <v>6263</v>
+        <v>6088</v>
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DRAKKAR 1 INTERMEDIACAO DE NEGOCIOS LTDA (MATRIZ) </t>
-        </is>
-      </c>
-      <c r="H92" s="1" t="n"/>
+          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I92" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>46175.61281142361</v>
+        <v>46024.66418596065</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>46176</v>
+        <v>46031</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M92" s="1" t="inlineStr">
@@ -6187,23 +6133,29 @@
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N92" s="1" t="n"/>
+      <c r="N92" s="2" t="n">
+        <v>46122.57290100694</v>
+      </c>
       <c r="O92" s="1" t="n"/>
       <c r="P92" s="1" t="inlineStr"/>
-      <c r="Q92" s="1" t="n"/>
+      <c r="Q92" s="1" t="inlineStr">
+        <is>
+          <t>resolvido</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>79624</v>
+        <v>77015</v>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -6213,32 +6165,36 @@
       </c>
       <c r="E93" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2025.</t>
+          <t>Fiscal	EFD 10, 11 e 12/2025 - Transporte de Saldo Credor Incorreto, corrigir por favor!</t>
         </is>
       </c>
       <c r="F93" s="1" t="n">
-        <v>6265</v>
+        <v>6106</v>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H93" s="1" t="n"/>
+          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>ilarao</t>
+        </is>
+      </c>
       <c r="I93" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>46175.61261015046</v>
+        <v>46057.59395454861</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>46176</v>
+        <v>46064</v>
       </c>
       <c r="L93" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M93" s="1" t="inlineStr">
@@ -6249,11 +6205,11 @@
       <c r="N93" s="1" t="n"/>
       <c r="O93" s="1" t="n"/>
       <c r="P93" s="1" t="inlineStr"/>
-      <c r="Q93" s="1" t="n"/>
+      <c r="Q93" s="1" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>76473</v>
+        <v>77019</v>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
@@ -6272,32 +6228,32 @@
       </c>
       <c r="E94" s="1" t="inlineStr">
         <is>
-          <t>Difal:Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados</t>
+          <t>EFD	EFD 06 e 08/2025 - saldo Incorreto - por favor, verificar!ISS retido	Por favor, precisamos com urgência gerar e enviar para o cliente as guias de ISS retido de outros municipios. Cliente cobrando em aberto desde 04/2025. cliente pedindo reembolso de multa e juros.</t>
         </is>
       </c>
       <c r="F94" s="1" t="n">
-        <v>6272</v>
+        <v>6148</v>
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>VALE CONCRETO LTDA</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Romario Silva</t>
         </is>
       </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>46030.36961565972</v>
+        <v>46057.64800393519</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>46043</v>
+        <v>46064</v>
       </c>
       <c r="L94" s="1" t="inlineStr">
         <is>
@@ -6306,7 +6262,7 @@
       </c>
       <c r="M94" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N94" s="1" t="n"/>
@@ -6316,7 +6272,7 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>76475</v>
+        <v>79371</v>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
@@ -6335,32 +6291,32 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t>Certidões:	Fazer levantamento de todas as certidões sobre débitos trabalhistas</t>
+          <t>Boa tardeHOTEIS - ITALO BRASILEIRAASSUNTO: Classificação fiscal / apuração de PIS e COFINSPENDÊNCIA: "Rodeio Hospedagem - Gabriela afirma que Airton faz mensalmente depósitos para cobrir as despesas, porem, não localizei isso na contabilidade. Solicitei envio das informações pela GabrielaTODOS OS HOTÉIS TEM VALORES A CLASSIFICAR, PRECISAMOS VERIFICAR.Loft - Tem uma conta de empréstimo entre empresas de 76.000,00 - precisamos verificar a origemO.L.R - Não recebemos o baçlanço de abertura?MOTEL CAMPO GRANDE - Não tem aporte do AirtonRENOVAÇÃO - Verificar balanço de abertura"</t>
         </is>
       </c>
       <c r="F95" s="1" t="n">
-        <v>6272</v>
+        <v>6159</v>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>LOFT EMPREENDIMENTOS HOTELEIROS LTDA</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>46030.37061041666</v>
+        <v>46161.65761836806</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>46043</v>
+        <v>46175</v>
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
@@ -6369,7 +6325,7 @@
       </c>
       <c r="M95" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N95" s="1" t="n"/>
@@ -6379,7 +6335,7 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>76476</v>
+        <v>79370</v>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
@@ -6398,32 +6354,32 @@
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t>Sistema:	Alinhar reunião com o cliente para ajustar o sistema para a emissão do SPED corretamente</t>
+          <t>Boa tardeITALO BRASILEIRAASSUNTO: Emprestimos entre empresasPENDÊNCIA: Esses valores são referentes a aportes que Ratinho faz para cobrir as despesas, como estamos contabilizando?</t>
         </is>
       </c>
       <c r="F96" s="1" t="n">
-        <v>6272</v>
+        <v>6179</v>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Danielle Silva</t>
         </is>
       </c>
       <c r="I96" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>46030.37112800926</v>
+        <v>46161.65683599537</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>46043</v>
+        <v>46175</v>
       </c>
       <c r="L96" s="1" t="inlineStr">
         <is>
@@ -6432,7 +6388,7 @@
       </c>
       <c r="M96" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N96" s="1" t="n"/>
@@ -6442,7 +6398,7 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>78160</v>
+        <v>77930</v>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
@@ -6461,20 +6417,20 @@
       </c>
       <c r="E97" s="1" t="inlineStr">
         <is>
-          <t>COFINS: Verificar 11/2025 Em aberto se é devido.DIFAL: Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados - Cobrança RecorrenteICMS: Verificar 12/2025 EFD Transporte de Saldo Credor Incorreto - Cobrança Recorrente</t>
+          <t>Bom dia.ITALO BRASILEIRA.ASSUNTO: Impostos recebidos na data do vencimentoPENDÊNCIA: Cliente reclama que ultimamente tem recebido no dia do vencimento e pior, no FINAL DO DIA. Favor verificar o que está ocorrendo pois Gabriela afirma cumprir todos os prazos e salvar todos os docuementos em tempo hábil</t>
         </is>
       </c>
       <c r="F97" s="1" t="n">
-        <v>6272</v>
+        <v>6179</v>
       </c>
       <c r="G97" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H97" s="1" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>rubial</t>
         </is>
       </c>
       <c r="I97" s="1" t="inlineStr">
@@ -6483,10 +6439,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>46105.43280350694</v>
+        <v>46093.45040390046</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="L97" s="1" t="inlineStr">
         <is>
@@ -6495,7 +6451,7 @@
       </c>
       <c r="M97" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N97" s="1" t="n"/>
@@ -6505,7 +6461,7 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>78161</v>
+        <v>77931</v>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
@@ -6524,32 +6480,32 @@
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Motorista: Contratou um motorista, verificar se está classificado no sindicato correto</t>
+          <t>Bom dia.ITALO BRASILEIRA.ASSUNTO: Classificação fiscal / apuração de PIS e COFINSPENDÊNCIA: Precisamos classificar corretamente as compras do cliente, o que for para revenda deve fazer parte da base de calculo pois o PIS e COFINS está muito alto. Favor revisar todos os fechamentos e buscar possíveis créditos de PIS e COFINS - PENDENTE</t>
         </is>
       </c>
       <c r="F98" s="1" t="n">
-        <v>6272</v>
+        <v>6179</v>
       </c>
       <c r="G98" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H98" s="1" t="inlineStr">
         <is>
-          <t>Jhenifer Tenorio</t>
+          <t>rubial</t>
         </is>
       </c>
       <c r="I98" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>46105.43378148148</v>
+        <v>46093.45111496528</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="L98" s="1" t="inlineStr">
         <is>
@@ -6558,7 +6514,7 @@
       </c>
       <c r="M98" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N98" s="1" t="n"/>
@@ -6568,7 +6524,7 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>77539</v>
+        <v>76465</v>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
@@ -6587,123 +6543,125 @@
       </c>
       <c r="E99" s="1" t="inlineStr">
         <is>
-          <t>Difal:Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados - Cobrança Recorrente</t>
+          <t xml:space="preserve">Termo de Intimação Receia federalpor favor, verificar termo de intimação, cliente pagou IRPJ e CSLL 2° e 3°  trimestre/2025 -  em 3 Parcelas </t>
         </is>
       </c>
       <c r="F99" s="1" t="n">
-        <v>6272</v>
+        <v>6217</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
         <is>
-          <t>Bruna Souza</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I99" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>46079.62766767361</v>
+        <v>46029.71832045139</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>46092</v>
+        <v>46036</v>
       </c>
       <c r="L99" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M99" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
-        </is>
-      </c>
-      <c r="N99" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>46122.57589409722</v>
+      </c>
       <c r="O99" s="1" t="n"/>
       <c r="P99" s="1" t="inlineStr"/>
-      <c r="Q99" s="1" t="inlineStr"/>
+      <c r="Q99" s="1" t="inlineStr">
+        <is>
+          <t>resolvido</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>77541</v>
+        <v>79680</v>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t>ICMS: Verificar 12/2025 EFD Transporte de Saldo Credor Incorreto</t>
+          <t xml:space="preserve">Cliente possui débitos em aberto com saldo devedor menor do que o valor original.  O saldo devedor remanescente é devido a retificações? Por gentileza realizar o levantamento, cliente esta precisando de uma CND e recebeu Painel de Conformidade. </t>
         </is>
       </c>
       <c r="F100" s="1" t="n">
-        <v>6272</v>
+        <v>6217</v>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
-        </is>
-      </c>
-      <c r="H100" s="1" t="inlineStr">
-        <is>
-          <t>Bruna Souza</t>
-        </is>
-      </c>
+          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="n"/>
       <c r="I100" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>46079.62931998842</v>
+        <v>46176.65661782408</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>46093</v>
+        <v>46181</v>
       </c>
       <c r="L100" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M100" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N100" s="1" t="n"/>
       <c r="O100" s="1" t="n"/>
       <c r="P100" s="1" t="inlineStr"/>
-      <c r="Q100" s="1" t="inlineStr"/>
+      <c r="Q100" s="1" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>78507</v>
+        <v>79673</v>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -6713,60 +6671,56 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.SUPER PREÇO.ASSUNTO: Planilha de conferenciaPENDÊNCIA: Mensalmente baixar a planilha do FTP e conforontar com o que estamos lançando na contabilidade</t>
+          <t>Por gentileza, verificar omissão de DCTFWeb 12/2025 e 03/2026.</t>
         </is>
       </c>
       <c r="F101" s="1" t="n">
-        <v>6293</v>
+        <v>6217</v>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t>H E F COMERCIO DE OPORTUNIDADES LTDA</t>
-        </is>
-      </c>
-      <c r="H101" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Moreira</t>
-        </is>
-      </c>
+          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="n"/>
       <c r="I101" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>46119.49291600694</v>
+        <v>46176.61147271991</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>46140</v>
+        <v>46181</v>
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M101" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N101" s="1" t="n"/>
       <c r="O101" s="1" t="n"/>
       <c r="P101" s="1" t="inlineStr"/>
-      <c r="Q101" s="1" t="inlineStr"/>
+      <c r="Q101" s="1" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>78148</v>
+        <v>79626</v>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
@@ -6776,66 +6730,56 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>PENDENCIA	DEPTO2	TIPO	AÇÃOCliente na pessoa do Izaque, está verificando junto a contabilidade anterior qual seria o valor real de depreciação a sder utilizado desde 09/2025, pois o mapa de depreciação apresenta determinado valor em discordância com o valor existente na EFD - Contribuições de 08/2025. 	CONTABILIDADE E FISCAL	INFORMATIVO	ANOTAR E COBRAR INFORMAÇÃO EM CASO DE DEMORA.Manter o faturamento declarado desta empresa em torno de R$ 200 mil  mensais, um cpouco mais um pouco menos em fevereiro de 2026 e nos meses subsequentes.	FISCAL	INFORMATIVO	 Necessária antecipação de fechamento contábil de fevereiro de 2026 e meses subsequentes no dia 20 do mês seguinte, de forma que possa-se discutir com o cliente na pessoa do Izaque os resultados apresentados e se necessária eftuar correções para que a apresentação perante a diretoria possa ser mais efetiva.	CONTABILIDADE E FISCAL	SOLICITAÇÃO	ANTECIPAR O FECHAMENTO FISCAL E CONTABIL, CONCLUSÃO TOTAL ATÉ 19/03.@Caroline Nascimento - EFI, qual a data prevista para conclusão do fiscal?</t>
+          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2025.</t>
         </is>
       </c>
       <c r="F102" s="1" t="n">
-        <v>6427</v>
+        <v>6263</v>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H102" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+          <t xml:space="preserve">DRAKKAR 1 INTERMEDIACAO DE NEGOCIOS LTDA (MATRIZ) </t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="n"/>
       <c r="I102" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>46105.36571898148</v>
+        <v>46175.61281142361</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>46112</v>
+        <v>46176</v>
       </c>
       <c r="L102" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M102" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N102" s="2" t="n">
-        <v>46122.70353086806</v>
-      </c>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N102" s="1" t="n"/>
       <c r="O102" s="1" t="n"/>
       <c r="P102" s="1" t="inlineStr"/>
-      <c r="Q102" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resolvido </t>
-        </is>
-      </c>
+      <c r="Q102" s="1" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>78054</v>
+        <v>79624</v>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -6845,51 +6789,47 @@
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t>Contrato de Trabalho:Ajustar o horário de entrada nos contratos de trabalhoBanco de Horas:Informar sobre o controle de banco de horas, e as obrigações.Controle de ponto:Informar ao cliente sobre a obrigatoriedade do controle de ponto, principalmente sobre o horário de almoço</t>
+          <t>Boa tarde! Por gentileza, encaminhar balanço e DRE 2025.</t>
         </is>
       </c>
       <c r="F103" s="1" t="n">
-        <v>6440</v>
+        <v>6265</v>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t>INFINITY UTILIDADES LTDA</t>
-        </is>
-      </c>
-      <c r="H103" s="1" t="inlineStr">
-        <is>
-          <t>Luana Marques</t>
-        </is>
-      </c>
+          <t>B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="n"/>
       <c r="I103" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>46098.64556820602</v>
+        <v>46175.61261015046</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>46111</v>
+        <v>46176</v>
       </c>
       <c r="L103" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M103" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N103" s="1" t="n"/>
       <c r="O103" s="1" t="n"/>
       <c r="P103" s="1" t="inlineStr"/>
-      <c r="Q103" s="1" t="inlineStr"/>
+      <c r="Q103" s="1" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>78055</v>
+        <v>76473</v>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
@@ -6908,20 +6848,20 @@
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t>DUC: Enviar as guias para pagamento</t>
+          <t>Difal:Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados</t>
         </is>
       </c>
       <c r="F104" s="1" t="n">
-        <v>6440</v>
+        <v>6272</v>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t>INFINITY UTILIDADES LTDA</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
         <is>
-          <t>Anna Ramalho</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="I104" s="1" t="inlineStr">
@@ -6930,10 +6870,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>46098.6472283912</v>
+        <v>46030.36961565972</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>46111</v>
+        <v>46043</v>
       </c>
       <c r="L104" s="1" t="inlineStr">
         <is>
@@ -6942,7 +6882,7 @@
       </c>
       <c r="M104" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N104" s="1" t="n"/>
@@ -6952,66 +6892,70 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>79588</v>
+        <v>76475</v>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularizar pendência de Omissão de EFD 02.2026 Saldo de transporte incorreto </t>
+          <t>Certidões:	Fazer levantamento de todas as certidões sobre débitos trabalhistas</t>
         </is>
       </c>
       <c r="F105" s="1" t="n">
-        <v>6460</v>
+        <v>6272</v>
       </c>
       <c r="G105" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H105" s="1" t="n"/>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>Jhenifer Tenorio</t>
+        </is>
+      </c>
       <c r="I105" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>46174.63777623843</v>
+        <v>46030.37061041666</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>46176</v>
+        <v>46043</v>
       </c>
       <c r="L105" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M105" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N105" s="1" t="n"/>
       <c r="O105" s="1" t="n"/>
       <c r="P105" s="1" t="inlineStr"/>
-      <c r="Q105" s="1" t="n"/>
+      <c r="Q105" s="1" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>77301</v>
+        <v>76476</v>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
@@ -7030,57 +6974,51 @@
       </c>
       <c r="E106" s="1" t="inlineStr">
         <is>
-          <t>COD.	EMPRESA	ATITUDE / PENDENCIA	 	 	  	 	 	DPTO	TIPO	AÇÃO6477	HPLAST EMBALAGENS FLEXIVEIS LTDA	CLIENTE RECLAMOU QUE RECEBEU A GUIA DO DAS 12/2025 NO DIA 20/01 NA DATA DO VENCIMENTO	FISCAL	SOLICITAÇÃO	ANTECIAPAÇÃO DO ENVIO6477	HPLAST EMBALAGENS FLEXIVEIS LTDA	REGIME TRIBUTÁRIO SERÁ SIMPLES NACIONAL ATÉ FINAL DO 1 TRIM, SERÁ AVALIADO POSSIBILIDADE DE MIGRAR PARA LUCRO REAL TRIMESTAL	FISCAL	INFORMATIVO	-</t>
+          <t>Sistema:	Alinhar reunião com o cliente para ajustar o sistema para a emissão do SPED corretamente</t>
         </is>
       </c>
       <c r="F106" s="1" t="n">
-        <v>6477</v>
+        <v>6272</v>
       </c>
       <c r="G106" s="1" t="inlineStr">
         <is>
-          <t>HPLAST EMBALAGENS FLEXIVEIS LTDA</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H106" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="I106" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>46071.60250181713</v>
+        <v>46030.37112800926</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>46078</v>
+        <v>46043</v>
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M106" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N106" s="2" t="n">
-        <v>46122.7037792824</v>
-      </c>
+          <t>mtoledo</t>
+        </is>
+      </c>
+      <c r="N106" s="1" t="n"/>
       <c r="O106" s="1" t="n"/>
       <c r="P106" s="1" t="inlineStr"/>
-      <c r="Q106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">resolvido </t>
-        </is>
-      </c>
+      <c r="Q106" s="1" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>77018</v>
+        <v>78160</v>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
@@ -7099,32 +7037,32 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t>Consulta Fiscal	Apresentada para o cliente com pendência (Sefaz). Por favor, verificar EFD 10 e 11/2025.</t>
+          <t>COFINS: Verificar 11/2025 Em aberto se é devido.DIFAL: Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados - Cobrança RecorrenteICMS: Verificar 12/2025 EFD Transporte de Saldo Credor Incorreto - Cobrança Recorrente</t>
         </is>
       </c>
       <c r="F107" s="1" t="n">
-        <v>6520</v>
+        <v>6272</v>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t>BONNARO COMERCIO E REPRESENTAÇÃO LTDA</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
         <is>
-          <t>ilarao</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="I107" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>46057.634546875</v>
+        <v>46105.43280350694</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>46064</v>
+        <v>46113</v>
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
@@ -7133,7 +7071,7 @@
       </c>
       <c r="M107" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N107" s="1" t="n"/>
@@ -7143,7 +7081,7 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>79645</v>
+        <v>78161</v>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
@@ -7157,52 +7095,56 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
         <is>
-          <t>Cliente pediu para fazer uma simulação da rescisão dos funcionários para análise do valor a pagar, tendo em vista a possibilidade de terceirização da mão de obra!</t>
+          <t>Motorista: Contratou um motorista, verificar se está classificado no sindicato correto</t>
         </is>
       </c>
       <c r="F108" s="1" t="n">
-        <v>6537</v>
+        <v>6272</v>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAKABOX - COMERCIO DE PECAS E ACESSORIOS PARA VEICULOS E MOTOCICLETAS LTDA  </t>
-        </is>
-      </c>
-      <c r="H108" s="1" t="n"/>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>Jhenifer Tenorio</t>
+        </is>
+      </c>
       <c r="I108" s="1" t="inlineStr">
         <is>
           <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>46175.7141352662</v>
+        <v>46105.43378148148</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>46178</v>
+        <v>46113</v>
       </c>
       <c r="L108" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M108" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N108" s="1" t="n"/>
       <c r="O108" s="1" t="n"/>
       <c r="P108" s="1" t="inlineStr"/>
-      <c r="Q108" s="1" t="n"/>
+      <c r="Q108" s="1" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>78614</v>
+        <v>77539</v>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
@@ -7221,20 +7163,20 @@
       </c>
       <c r="E109" s="1" t="inlineStr">
         <is>
-          <t>DUC:Enviar guias para pagamento</t>
+          <t>Difal:Fazer levantamento de possíveis valores em aberto sobre as vendas em outros estados - Cobrança Recorrente</t>
         </is>
       </c>
       <c r="F109" s="1" t="n">
-        <v>6621</v>
+        <v>6272</v>
       </c>
       <c r="G109" s="1" t="inlineStr">
         <is>
-          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H109" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="I109" s="1" t="inlineStr">
@@ -7243,10 +7185,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>46125.59401516204</v>
+        <v>46079.62766767361</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>46132</v>
+        <v>46092</v>
       </c>
       <c r="L109" s="1" t="inlineStr">
         <is>
@@ -7255,7 +7197,7 @@
       </c>
       <c r="M109" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N109" s="1" t="n"/>
@@ -7265,7 +7207,7 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>78615</v>
+        <v>77541</v>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
@@ -7284,20 +7226,20 @@
       </c>
       <c r="E110" s="1" t="inlineStr">
         <is>
-          <t>DUC:Enviar guias para pagamento</t>
+          <t>ICMS: Verificar 12/2025 EFD Transporte de Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="F110" s="1" t="n">
-        <v>6622</v>
+        <v>6272</v>
       </c>
       <c r="G110" s="1" t="inlineStr">
         <is>
-          <t>COMBATEAINCENDIOS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANCA LTDA</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H110" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Bruna Souza</t>
         </is>
       </c>
       <c r="I110" s="1" t="inlineStr">
@@ -7306,10 +7248,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>46125.59444232639</v>
+        <v>46079.62931998842</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>46132</v>
+        <v>46093</v>
       </c>
       <c r="L110" s="1" t="inlineStr">
         <is>
@@ -7318,7 +7260,7 @@
       </c>
       <c r="M110" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N110" s="1" t="n"/>
@@ -7328,7 +7270,7 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>76937</v>
+        <v>78507</v>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
@@ -7347,20 +7289,20 @@
       </c>
       <c r="E111" s="1" t="inlineStr">
         <is>
-          <t>ENVIAR MODELO DE EXTRAÇÃO DE XML (TAG): Enviar modelo e auxiliar cliente na inserção dos dados da MG conforme combinado em reunião.</t>
+          <t>Bom dia.SUPER PREÇO.ASSUNTO: Planilha de conferenciaPENDÊNCIA: Mensalmente baixar a planilha do FTP e conforontar com o que estamos lançando na contabilidade</t>
         </is>
       </c>
       <c r="F111" s="1" t="n">
-        <v>6638</v>
+        <v>6293</v>
       </c>
       <c r="G111" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
+          <t>H E F COMERCIO DE OPORTUNIDADES LTDA</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
         <is>
-          <t>rubial</t>
+          <t>Priscila Moreira</t>
         </is>
       </c>
       <c r="I111" s="1" t="inlineStr">
@@ -7369,10 +7311,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>46055.45643252315</v>
+        <v>46119.49291600694</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>46062</v>
+        <v>46140</v>
       </c>
       <c r="L111" s="1" t="inlineStr">
         <is>
@@ -7381,7 +7323,7 @@
       </c>
       <c r="M111" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N111" s="1" t="n"/>
@@ -7391,7 +7333,7 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>77639</v>
+        <v>78148</v>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
@@ -7410,55 +7352,61 @@
       </c>
       <c r="E112" s="1" t="inlineStr">
         <is>
-          <t>Possui Filial: Excluir da BC do PIS e COFINS o ICMS - Cliente passou a base legal</t>
+          <t>PENDENCIA	DEPTO2	TIPO	AÇÃOCliente na pessoa do Izaque, está verificando junto a contabilidade anterior qual seria o valor real de depreciação a sder utilizado desde 09/2025, pois o mapa de depreciação apresenta determinado valor em discordância com o valor existente na EFD - Contribuições de 08/2025. 	CONTABILIDADE E FISCAL	INFORMATIVO	ANOTAR E COBRAR INFORMAÇÃO EM CASO DE DEMORA.Manter o faturamento declarado desta empresa em torno de R$ 200 mil  mensais, um cpouco mais um pouco menos em fevereiro de 2026 e nos meses subsequentes.	FISCAL	INFORMATIVO	 Necessária antecipação de fechamento contábil de fevereiro de 2026 e meses subsequentes no dia 20 do mês seguinte, de forma que possa-se discutir com o cliente na pessoa do Izaque os resultados apresentados e se necessária eftuar correções para que a apresentação perante a diretoria possa ser mais efetiva.	CONTABILIDADE E FISCAL	SOLICITAÇÃO	ANTECIPAR O FECHAMENTO FISCAL E CONTABIL, CONCLUSÃO TOTAL ATÉ 19/03.@Caroline Nascimento - EFI, qual a data prevista para conclusão do fiscal?</t>
         </is>
       </c>
       <c r="F112" s="1" t="n">
-        <v>6640</v>
+        <v>6427</v>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t>rubial</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I112" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>46083.60260243055</v>
+        <v>46105.36571898148</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="L112" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M112" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
-        </is>
-      </c>
-      <c r="N112" s="1" t="n"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>46122.70353086806</v>
+      </c>
       <c r="O112" s="1" t="n"/>
       <c r="P112" s="1" t="inlineStr"/>
-      <c r="Q112" s="1" t="inlineStr"/>
+      <c r="Q112" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>78847</v>
+        <v>78054</v>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>Reunião externa</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
@@ -7473,16 +7421,20 @@
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t>Verificar o sindicato Patronal, lembrando que o cliente não abre mais aos domingosCliente tem dificuldade sobre os recebimentos dos atestados demissionaisApresentar ao cliente sobre as obrigações da empresa5350 - AKAFER</t>
+          <t>Contrato de Trabalho:Ajustar o horário de entrada nos contratos de trabalhoBanco de Horas:Informar sobre o controle de banco de horas, e as obrigações.Controle de ponto:Informar ao cliente sobre a obrigatoriedade do controle de ponto, principalmente sobre o horário de almoço</t>
         </is>
       </c>
       <c r="F113" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G113" s="1" t="n"/>
+        <v>6440</v>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>INFINITY UTILIDADES LTDA</t>
+        </is>
+      </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Luana Marques</t>
         </is>
       </c>
       <c r="I113" s="1" t="inlineStr">
@@ -7491,14 +7443,14 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>46134.66965193287</v>
+        <v>46098.64556820602</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>46142</v>
+        <v>46111</v>
       </c>
       <c r="L113" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M113" s="1" t="inlineStr">
@@ -7506,21 +7458,14 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N113" s="2" t="n">
-        <v>46171.59439259259</v>
-      </c>
+      <c r="N113" s="1" t="n"/>
       <c r="O113" s="1" t="n"/>
       <c r="P113" s="1" t="inlineStr"/>
-      <c r="Q113" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EM ATENDIMENTO
-</t>
-        </is>
-      </c>
+      <c r="Q113" s="1" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>78854</v>
+        <v>78055</v>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
@@ -7539,15 +7484,15 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t>IMPORTANTEPor gentileza, necessário realizar a captura de 100% dos arquivos XML referentes a compras realizadas pela empresa de janeiro a novembro/2025, para a contabilização correta de todas as compras realizadas pela empresa no período citado.</t>
+          <t>DUC: Enviar as guias para pagamento</t>
         </is>
       </c>
       <c r="F114" s="1" t="n">
-        <v>4811</v>
+        <v>6440</v>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t>ORIVALDO DAN</t>
+          <t>INFINITY UTILIDADES LTDA</t>
         </is>
       </c>
       <c r="H114" s="1" t="inlineStr">
@@ -7561,10 +7506,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>46134.74738626157</v>
+        <v>46098.6472283912</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>46142</v>
+        <v>46111</v>
       </c>
       <c r="L114" s="1" t="inlineStr">
         <is>
@@ -7583,16 +7528,16 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>78445</v>
+        <v>79681</v>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -7602,91 +7547,87 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025, 11/2025 e 12/2025Verificar se o cliente responde o e-mail com as críticas das NFs de entrada</t>
+          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2025/2026 até abril</t>
         </is>
       </c>
       <c r="F115" s="1" t="n">
-        <v>5100</v>
+        <v>6440</v>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
-        </is>
-      </c>
-      <c r="H115" s="1" t="inlineStr">
-        <is>
-          <t>Bruna Souza</t>
-        </is>
-      </c>
+          <t>INFINITY UTILIDADES LTDA</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="n"/>
       <c r="I115" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>46114.57570729167</v>
+        <v>46176.66350790509</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>46121</v>
+        <v>46178</v>
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M115" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N115" s="1" t="n"/>
       <c r="O115" s="1" t="n"/>
       <c r="P115" s="1" t="inlineStr"/>
-      <c r="Q115" s="1" t="inlineStr"/>
+      <c r="Q115" s="1" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>79640</v>
+        <v>79588</v>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração </t>
+          <t xml:space="preserve">Regularizar pendência de Omissão de EFD 02.2026 Saldo de transporte incorreto </t>
         </is>
       </c>
       <c r="F116" s="1" t="n">
-        <v>5726</v>
+        <v>6460</v>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t>VIANA &amp; CIA LTDA</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H116" s="1" t="n"/>
       <c r="I116" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>46175.7045628125</v>
+        <v>46174.63777623843</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>46178</v>
+        <v>46176</v>
       </c>
       <c r="L116" s="1" t="inlineStr">
         <is>
@@ -7695,7 +7636,7 @@
       </c>
       <c r="M116" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N116" s="1" t="n"/>
@@ -7705,16 +7646,16 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>79641</v>
+        <v>77301</v>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
@@ -7724,47 +7665,57 @@
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração</t>
+          <t>COD.	EMPRESA	ATITUDE / PENDENCIA	 	 	  	 	 	DPTO	TIPO	AÇÃO6477	HPLAST EMBALAGENS FLEXIVEIS LTDA	CLIENTE RECLAMOU QUE RECEBEU A GUIA DO DAS 12/2025 NO DIA 20/01 NA DATA DO VENCIMENTO	FISCAL	SOLICITAÇÃO	ANTECIAPAÇÃO DO ENVIO6477	HPLAST EMBALAGENS FLEXIVEIS LTDA	REGIME TRIBUTÁRIO SERÁ SIMPLES NACIONAL ATÉ FINAL DO 1 TRIM, SERÁ AVALIADO POSSIBILIDADE DE MIGRAR PARA LUCRO REAL TRIMESTAL	FISCAL	INFORMATIVO	-</t>
         </is>
       </c>
       <c r="F117" s="1" t="n">
-        <v>5726</v>
+        <v>6477</v>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t>VIANA &amp; CIA LTDA</t>
-        </is>
-      </c>
-      <c r="H117" s="1" t="n"/>
+          <t>HPLAST EMBALAGENS FLEXIVEIS LTDA</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>46175.70509568287</v>
+        <v>46071.60250181713</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>46178</v>
+        <v>46078</v>
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M117" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
-      <c r="N117" s="1" t="n"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>46122.7037792824</v>
+      </c>
       <c r="O117" s="1" t="n"/>
       <c r="P117" s="1" t="inlineStr"/>
-      <c r="Q117" s="1" t="n"/>
+      <c r="Q117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>78447</v>
+        <v>77018</v>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
@@ -7783,32 +7734,32 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>Ref. 01/2026 GIA/EFD Não apresentou GIA/EFD Cobrança RecorrenteVerificar MAED - PGDAS-D em aberto Cobrança Recorrente</t>
+          <t>Consulta Fiscal	Apresentada para o cliente com pendência (Sefaz). Por favor, verificar EFD 10 e 11/2025.</t>
         </is>
       </c>
       <c r="F118" s="1" t="n">
-        <v>5740</v>
+        <v>6520</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>MARIA VALDENE FERREIRA RIBEIRO</t>
+          <t>BONNARO COMERCIO E REPRESENTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>ilarao</t>
         </is>
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46114.58255327546</v>
+        <v>46057.634546875</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>46121</v>
+        <v>46064</v>
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
@@ -7817,7 +7768,7 @@
       </c>
       <c r="M118" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N118" s="1" t="n"/>
@@ -7827,47 +7778,47 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>79569</v>
+        <v>79645</v>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E119" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom dia!Solicito por gentileza o balanço e DRE da empresa ODONTO STORE do periodo mais recente.Obrigada!</t>
+          <t>Cliente pediu para fazer uma simulação da rescisão dos funcionários para análise do valor a pagar, tendo em vista a possibilidade de terceirização da mão de obra!</t>
         </is>
       </c>
       <c r="F119" s="1" t="n">
-        <v>5909</v>
+        <v>6537</v>
       </c>
       <c r="G119" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odonto Store Equipamentos Odotologicos LTDA </t>
+          <t xml:space="preserve">NAKABOX - COMERCIO DE PECAS E ACESSORIOS PARA VEICULOS E MOTOCICLETAS LTDA  </t>
         </is>
       </c>
       <c r="H119" s="1" t="n"/>
       <c r="I119" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>46174.45886207176</v>
+        <v>46175.7141352662</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="L119" s="1" t="inlineStr">
         <is>
@@ -7876,7 +7827,7 @@
       </c>
       <c r="M119" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N119" s="1" t="n"/>
@@ -7886,66 +7837,70 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>77046</v>
+        <v>78614</v>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
         <is>
-          <t>Fiscalização Municipal</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E120" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, Solicito, por gentileza, a baixa das tarefas pendentes referente a FOPAG das empresas da MAC LEIXO (6422, 6423 e 6424). A empresa está inativa e saiu da MG no inicio de Janeiro, onde os documentos referente ao departamento já foram enviados para a nova contabilidade. Caso seja possível, solicito também a exclusão das futuras tarefas. Obrigado! </t>
+          <t>DUC:Enviar guias para pagamento</t>
         </is>
       </c>
       <c r="F120" s="1" t="n">
-        <v>6422</v>
+        <v>6621</v>
       </c>
       <c r="G120" s="1" t="inlineStr">
         <is>
-          <t>M.A.C LEIXO OFFSHORE MONTAGEM E REPAROS NAVAIS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="n"/>
+          <t>BOMBEIROS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANÇA LTDA</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>Beatriz Ferreira</t>
+        </is>
+      </c>
       <c r="I120" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>46059.64559829861</v>
+        <v>46125.59401516204</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>46064</v>
+        <v>46132</v>
       </c>
       <c r="L120" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M120" s="1" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N120" s="1" t="n"/>
       <c r="O120" s="1" t="n"/>
       <c r="P120" s="1" t="inlineStr"/>
-      <c r="Q120" s="1" t="n"/>
+      <c r="Q120" s="1" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>79115</v>
+        <v>78615</v>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
@@ -7964,32 +7919,32 @@
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Segue pendências da Ata de reuniãoINSS	Enviado em duplicidade ref. 01/2026, verificar o que houve Pendencia Recorrente</t>
+          <t>DUC:Enviar guias para pagamento</t>
         </is>
       </c>
       <c r="F121" s="1" t="n">
-        <v>9578</v>
+        <v>6622</v>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>PAULO CESAR RIZARDI</t>
+          <t>COMBATEAINCENDIOS.COM.BR COMERCIO DE EQUIPAMENTOS DE SEGURANCA LTDA</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46153.58827222222</v>
+        <v>46125.59444232639</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>46160</v>
+        <v>46132</v>
       </c>
       <c r="L121" s="1" t="inlineStr">
         <is>
@@ -7998,13 +7953,752 @@
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N121" s="1" t="n"/>
       <c r="O121" s="1" t="n"/>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>76937</v>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>ENVIAR MODELO DE EXTRAÇÃO DE XML (TAG): Enviar modelo e auxiliar cliente na inserção dos dados da MG conforme combinado em reunião.</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>6638</v>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>rubial</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>46055.45643252315</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>46062</v>
+      </c>
+      <c r="L122" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M122" s="1" t="inlineStr">
+        <is>
+          <t>mtoledo</t>
+        </is>
+      </c>
+      <c r="N122" s="1" t="n"/>
+      <c r="O122" s="1" t="n"/>
+      <c r="P122" s="1" t="inlineStr"/>
+      <c r="Q122" s="1" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>77639</v>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>Possui Filial: Excluir da BC do PIS e COFINS o ICMS - Cliente passou a base legal</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>6640</v>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>FORT FRUIT LTDA</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>rubial</t>
+        </is>
+      </c>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>46083.60260243055</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="L123" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M123" s="1" t="inlineStr">
+        <is>
+          <t>mtoledo</t>
+        </is>
+      </c>
+      <c r="N123" s="1" t="n"/>
+      <c r="O123" s="1" t="n"/>
+      <c r="P123" s="1" t="inlineStr"/>
+      <c r="Q123" s="1" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>79669</v>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>Cliente recebeu uma notificação referente ao Pré - Cancelamento da Inscrição Estadual devido omissões, por gentileza verificar pois o mesmo possui pendência de EFD Omissa ref. 03/2026 e 04/2026.</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>6880</v>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS (FILIAL)</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="n"/>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>46176.50974965277</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="L124" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M124" s="1" t="inlineStr">
+        <is>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N124" s="1" t="n"/>
+      <c r="O124" s="1" t="n"/>
+      <c r="P124" s="1" t="inlineStr"/>
+      <c r="Q124" s="1" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>78847</v>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>Reunião externa</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>Verificar o sindicato Patronal, lembrando que o cliente não abre mais aos domingosCliente tem dificuldade sobre os recebimentos dos atestados demissionaisApresentar ao cliente sobre as obrigações da empresa5350 - AKAFER</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G125" s="1" t="n"/>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>Mauricio Lermen</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>46134.66965193287</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="L125" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M125" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>46171.59439259259</v>
+      </c>
+      <c r="O125" s="1" t="n"/>
+      <c r="P125" s="1" t="inlineStr"/>
+      <c r="Q125" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM ATENDIMENTO
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>78854</v>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANTEPor gentileza, necessário realizar a captura de 100% dos arquivos XML referentes a compras realizadas pela empresa de janeiro a novembro/2025, para a contabilização correta de todas as compras realizadas pela empresa no período citado.</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>4811</v>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>ORIVALDO DAN</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>Anna Ramalho</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>46134.74738626157</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="L126" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M126" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N126" s="1" t="n"/>
+      <c r="O126" s="1" t="n"/>
+      <c r="P126" s="1" t="inlineStr"/>
+      <c r="Q126" s="1" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>78445</v>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025, 11/2025 e 12/2025Verificar se o cliente responde o e-mail com as críticas das NFs de entrada</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>Bruna Souza</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>46114.57570729167</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="L127" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M127" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N127" s="1" t="n"/>
+      <c r="O127" s="1" t="n"/>
+      <c r="P127" s="1" t="inlineStr"/>
+      <c r="Q127" s="1" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>79640</v>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>Alteração de Regime Tributário</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>Alteração de Regime Tributário</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração </t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>5726</v>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>VIANA &amp; CIA LTDA</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="n"/>
+      <c r="I128" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>46175.7045628125</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="L128" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M128" s="1" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
+      <c r="N128" s="1" t="n"/>
+      <c r="O128" s="1" t="n"/>
+      <c r="P128" s="1" t="inlineStr"/>
+      <c r="Q128" s="1" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>79641</v>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>Alteração de Regime Tributário</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Alteração de Regime Tributário</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>5726</v>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>VIANA &amp; CIA LTDA</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="n"/>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>46175.70509568287</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>46178</v>
+      </c>
+      <c r="L129" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M129" s="1" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
+      <c r="N129" s="1" t="n"/>
+      <c r="O129" s="1" t="n"/>
+      <c r="P129" s="1" t="inlineStr"/>
+      <c r="Q129" s="1" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>78447</v>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>Ref. 01/2026 GIA/EFD Não apresentou GIA/EFD Cobrança RecorrenteVerificar MAED - PGDAS-D em aberto Cobrança Recorrente</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>5740</v>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>MARIA VALDENE FERREIRA RIBEIRO</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>Beatriz Ferreira</t>
+        </is>
+      </c>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>46114.58255327546</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="L130" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M130" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N130" s="1" t="n"/>
+      <c r="O130" s="1" t="n"/>
+      <c r="P130" s="1" t="inlineStr"/>
+      <c r="Q130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>79569</v>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>Balanço e DRE</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Balanço e DRE</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, bom dia!Solicito por gentileza o balanço e DRE da empresa ODONTO STORE do periodo mais recente.Obrigada!</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>5909</v>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Odonto Store Equipamentos Odotologicos LTDA </t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="n"/>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL VAREJO</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>46174.45886207176</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>46176</v>
+      </c>
+      <c r="L131" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M131" s="1" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
+      <c r="N131" s="1" t="n"/>
+      <c r="O131" s="1" t="n"/>
+      <c r="P131" s="1" t="inlineStr"/>
+      <c r="Q131" s="1" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>77046</v>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Fiscalização Municipal</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>RJ - DP</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados, Solicito, por gentileza, a baixa das tarefas pendentes referente a FOPAG das empresas da MAC LEIXO (6422, 6423 e 6424). A empresa está inativa e saiu da MG no inicio de Janeiro, onde os documentos referente ao departamento já foram enviados para a nova contabilidade. Caso seja possível, solicito também a exclusão das futuras tarefas. Obrigado! </t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>6422</v>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>M.A.C LEIXO OFFSHORE MONTAGEM E REPAROS NAVAIS LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="n"/>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>46059.64559829861</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>46064</v>
+      </c>
+      <c r="L132" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M132" s="1" t="inlineStr">
+        <is>
+          <t>Jefferson Barros</t>
+        </is>
+      </c>
+      <c r="N132" s="1" t="n"/>
+      <c r="O132" s="1" t="n"/>
+      <c r="P132" s="1" t="inlineStr"/>
+      <c r="Q132" s="1" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>79115</v>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, boa tarde!Segue pendências da Ata de reuniãoINSS	Enviado em duplicidade ref. 01/2026, verificar o que houve Pendencia Recorrente</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>9578</v>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>PAULO CESAR RIZARDI</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>David Bragança</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>46153.58827222222</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="L133" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M133" s="1" t="inlineStr">
+        <is>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
+      <c r="N133" s="1" t="n"/>
+      <c r="O133" s="1" t="n"/>
+      <c r="P133" s="1" t="inlineStr"/>
+      <c r="Q133" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,9 +138,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:Q229" headerRowCount="1">
-  <autoFilter ref="A1:Q229"/>
-  <tableColumns count="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:R231" headerRowCount="1">
+  <autoFilter ref="A1:R231"/>
+  <tableColumns count="18">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
     <tableColumn id="3" name="Assunto"/>
@@ -158,6 +158,7 @@
     <tableColumn id="15" name="Data Entrega"/>
     <tableColumn id="16" name="Responsável pela conclusão"/>
     <tableColumn id="17" name="Ultimo Comentário"/>
+    <tableColumn id="18" name="Retornado"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -452,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q229"/>
+  <dimension ref="A1:R231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -472,6 +473,7 @@
     <col width="15.57" customWidth="1" min="15" max="15"/>
     <col width="28.57" customWidth="1" min="16" max="16"/>
     <col width="20.29" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -560,6 +562,11 @@
           <t>Ultimo Comentário</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Retornado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -619,6 +626,11 @@
       <c r="O2" s="1" t="n"/>
       <c r="P2" s="1" t="inlineStr"/>
       <c r="Q2" s="1" t="inlineStr"/>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -678,6 +690,11 @@
       <c r="O3" s="1" t="n"/>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr"/>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -737,6 +754,11 @@
       <c r="O4" s="1" t="n"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
+      <c r="R4" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -792,6 +814,11 @@
       <c r="O5" s="1" t="n"/>
       <c r="P5" s="1" t="inlineStr"/>
       <c r="Q5" s="1" t="n"/>
+      <c r="R5" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -847,6 +874,11 @@
       <c r="O6" s="1" t="n"/>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="n"/>
+      <c r="R6" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -902,6 +934,11 @@
       <c r="O7" s="1" t="n"/>
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="n"/>
+      <c r="R7" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -961,6 +998,11 @@
       <c r="O8" s="1" t="n"/>
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr"/>
+      <c r="R8" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -1020,6 +1062,11 @@
       <c r="O9" s="1" t="n"/>
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr"/>
+      <c r="R9" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -1079,6 +1126,11 @@
       <c r="O10" s="1" t="n"/>
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr"/>
+      <c r="R10" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1138,6 +1190,11 @@
       <c r="O11" s="1" t="n"/>
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr"/>
+      <c r="R11" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1193,6 +1250,11 @@
       <c r="O12" s="1" t="n"/>
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="n"/>
+      <c r="R12" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -1256,6 +1318,11 @@
       <c r="O13" s="1" t="n"/>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr"/>
+      <c r="R13" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -1319,6 +1386,11 @@
       <c r="O14" s="1" t="n"/>
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr"/>
+      <c r="R14" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1382,6 +1454,11 @@
       <c r="O15" s="1" t="n"/>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr"/>
+      <c r="R15" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -1445,6 +1522,11 @@
       <c r="O16" s="1" t="n"/>
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr"/>
+      <c r="R16" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -1508,6 +1590,11 @@
       <c r="O17" s="1" t="n"/>
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr"/>
+      <c r="R17" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -1571,6 +1658,11 @@
       <c r="O18" s="1" t="n"/>
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr"/>
+      <c r="R18" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1634,6 +1726,11 @@
       <c r="O19" s="1" t="n"/>
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr"/>
+      <c r="R19" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1697,6 +1794,11 @@
       <c r="O20" s="1" t="n"/>
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr"/>
+      <c r="R20" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1760,6 +1862,11 @@
       <c r="O21" s="1" t="n"/>
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr"/>
+      <c r="R21" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1823,6 +1930,11 @@
       <c r="O22" s="1" t="n"/>
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr"/>
+      <c r="R22" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1886,6 +1998,11 @@
       <c r="O23" s="1" t="n"/>
       <c r="P23" s="1" t="inlineStr"/>
       <c r="Q23" s="1" t="inlineStr"/>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1949,6 +2066,11 @@
       <c r="O24" s="1" t="n"/>
       <c r="P24" s="1" t="inlineStr"/>
       <c r="Q24" s="1" t="inlineStr"/>
+      <c r="R24" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -2008,6 +2130,11 @@
       <c r="O25" s="1" t="n"/>
       <c r="P25" s="1" t="inlineStr"/>
       <c r="Q25" s="1" t="n"/>
+      <c r="R25" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -2071,6 +2198,11 @@
       <c r="O26" s="1" t="n"/>
       <c r="P26" s="1" t="inlineStr"/>
       <c r="Q26" s="1" t="inlineStr"/>
+      <c r="R26" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2134,6 +2266,11 @@
       <c r="O27" s="1" t="n"/>
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr"/>
+      <c r="R27" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2193,6 +2330,11 @@
       <c r="O28" s="1" t="n"/>
       <c r="P28" s="1" t="inlineStr"/>
       <c r="Q28" s="1" t="n"/>
+      <c r="R28" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2252,6 +2394,11 @@
       <c r="O29" s="1" t="n"/>
       <c r="P29" s="1" t="inlineStr"/>
       <c r="Q29" s="1" t="n"/>
+      <c r="R29" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2319,6 +2466,11 @@
           <t>ok</t>
         </is>
       </c>
+      <c r="R30" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2386,6 +2538,11 @@
       <c r="Q31" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R31" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -2451,6 +2608,11 @@
       <c r="O32" s="1" t="n"/>
       <c r="P32" s="1" t="inlineStr"/>
       <c r="Q32" s="1" t="inlineStr"/>
+      <c r="R32" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -2514,6 +2676,11 @@
       <c r="O33" s="1" t="n"/>
       <c r="P33" s="1" t="inlineStr"/>
       <c r="Q33" s="1" t="inlineStr"/>
+      <c r="R33" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -2577,6 +2744,11 @@
       <c r="O34" s="1" t="n"/>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -2640,6 +2812,11 @@
       <c r="O35" s="1" t="n"/>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
+      <c r="R35" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -2703,6 +2880,11 @@
       <c r="O36" s="1" t="n"/>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
+      <c r="R36" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -2766,6 +2948,11 @@
       <c r="O37" s="1" t="n"/>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
+      <c r="R37" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -2829,6 +3016,11 @@
       <c r="O38" s="1" t="n"/>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
+      <c r="R38" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -2892,6 +3084,11 @@
       <c r="O39" s="1" t="n"/>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
+      <c r="R39" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -2955,6 +3152,11 @@
       <c r="O40" s="1" t="n"/>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
+      <c r="R40" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -3018,6 +3220,11 @@
       <c r="O41" s="1" t="n"/>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
+      <c r="R41" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -3081,6 +3288,11 @@
       <c r="O42" s="1" t="n"/>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
+      <c r="R42" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -3144,6 +3356,11 @@
       <c r="O43" s="1" t="n"/>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
+      <c r="R43" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -3207,6 +3424,11 @@
       <c r="O44" s="1" t="n"/>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
+      <c r="R44" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3270,6 +3492,11 @@
       <c r="O45" s="1" t="n"/>
       <c r="P45" s="1" t="inlineStr"/>
       <c r="Q45" s="1" t="inlineStr"/>
+      <c r="R45" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3329,6 +3556,11 @@
       <c r="O46" s="1" t="n"/>
       <c r="P46" s="1" t="inlineStr"/>
       <c r="Q46" s="1" t="n"/>
+      <c r="R46" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -3396,6 +3628,11 @@
       <c r="Q47" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R47" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -3461,6 +3698,11 @@
       <c r="O48" s="1" t="n"/>
       <c r="P48" s="1" t="inlineStr"/>
       <c r="Q48" s="1" t="inlineStr"/>
+      <c r="R48" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3520,6 +3762,11 @@
       <c r="O49" s="1" t="n"/>
       <c r="P49" s="1" t="inlineStr"/>
       <c r="Q49" s="1" t="n"/>
+      <c r="R49" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3579,6 +3826,11 @@
       <c r="O50" s="1" t="n"/>
       <c r="P50" s="1" t="inlineStr"/>
       <c r="Q50" s="1" t="n"/>
+      <c r="R50" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -3642,6 +3894,11 @@
       <c r="O51" s="1" t="n"/>
       <c r="P51" s="1" t="inlineStr"/>
       <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -3701,6 +3958,11 @@
       <c r="O52" s="1" t="n"/>
       <c r="P52" s="1" t="inlineStr"/>
       <c r="Q52" s="1" t="n"/>
+      <c r="R52" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -3764,6 +4026,11 @@
       <c r="O53" s="1" t="n"/>
       <c r="P53" s="1" t="inlineStr"/>
       <c r="Q53" s="1" t="inlineStr"/>
+      <c r="R53" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3827,6 +4094,11 @@
       <c r="O54" s="1" t="n"/>
       <c r="P54" s="1" t="inlineStr"/>
       <c r="Q54" s="1" t="inlineStr"/>
+      <c r="R54" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3890,6 +4162,11 @@
       <c r="O55" s="1" t="n"/>
       <c r="P55" s="1" t="inlineStr"/>
       <c r="Q55" s="1" t="inlineStr"/>
+      <c r="R55" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -3953,6 +4230,11 @@
       <c r="O56" s="1" t="n"/>
       <c r="P56" s="1" t="inlineStr"/>
       <c r="Q56" s="1" t="inlineStr"/>
+      <c r="R56" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4016,6 +4298,11 @@
       <c r="O57" s="1" t="n"/>
       <c r="P57" s="1" t="inlineStr"/>
       <c r="Q57" s="1" t="inlineStr"/>
+      <c r="R57" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4079,6 +4366,11 @@
       <c r="O58" s="1" t="n"/>
       <c r="P58" s="1" t="inlineStr"/>
       <c r="Q58" s="1" t="inlineStr"/>
+      <c r="R58" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -4142,6 +4434,11 @@
       <c r="O59" s="1" t="n"/>
       <c r="P59" s="1" t="inlineStr"/>
       <c r="Q59" s="1" t="inlineStr"/>
+      <c r="R59" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4201,6 +4498,11 @@
       <c r="O60" s="1" t="n"/>
       <c r="P60" s="1" t="inlineStr"/>
       <c r="Q60" s="1" t="n"/>
+      <c r="R60" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4264,6 +4566,11 @@
       <c r="O61" s="1" t="n"/>
       <c r="P61" s="1" t="inlineStr"/>
       <c r="Q61" s="1" t="inlineStr"/>
+      <c r="R61" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -4331,6 +4638,11 @@
       <c r="Q62" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
+      <c r="R62" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -4396,6 +4708,11 @@
       <c r="O63" s="1" t="n"/>
       <c r="P63" s="1" t="inlineStr"/>
       <c r="Q63" s="1" t="inlineStr"/>
+      <c r="R63" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -4459,6 +4776,11 @@
       <c r="O64" s="1" t="n"/>
       <c r="P64" s="1" t="inlineStr"/>
       <c r="Q64" s="1" t="inlineStr"/>
+      <c r="R64" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4522,6 +4844,11 @@
       <c r="O65" s="1" t="n"/>
       <c r="P65" s="1" t="inlineStr"/>
       <c r="Q65" s="1" t="inlineStr"/>
+      <c r="R65" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4585,6 +4912,11 @@
       <c r="O66" s="1" t="n"/>
       <c r="P66" s="1" t="inlineStr"/>
       <c r="Q66" s="1" t="inlineStr"/>
+      <c r="R66" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4648,6 +4980,11 @@
       <c r="O67" s="1" t="n"/>
       <c r="P67" s="1" t="inlineStr"/>
       <c r="Q67" s="1" t="inlineStr"/>
+      <c r="R67" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4707,6 +5044,11 @@
       <c r="O68" s="1" t="n"/>
       <c r="P68" s="1" t="inlineStr"/>
       <c r="Q68" s="1" t="n"/>
+      <c r="R68" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4766,6 +5108,11 @@
       <c r="O69" s="1" t="n"/>
       <c r="P69" s="1" t="inlineStr"/>
       <c r="Q69" s="1" t="n"/>
+      <c r="R69" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -4829,6 +5176,11 @@
       <c r="O70" s="1" t="n"/>
       <c r="P70" s="1" t="inlineStr"/>
       <c r="Q70" s="1" t="inlineStr"/>
+      <c r="R70" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -4898,6 +5250,11 @@
           <t>resolvido</t>
         </is>
       </c>
+      <c r="R71" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -4965,6 +5322,11 @@
       <c r="Q72" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R72" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -5030,6 +5392,11 @@
       <c r="O73" s="1" t="n"/>
       <c r="P73" s="1" t="inlineStr"/>
       <c r="Q73" s="1" t="inlineStr"/>
+      <c r="R73" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -5089,6 +5456,11 @@
       <c r="O74" s="1" t="n"/>
       <c r="P74" s="1" t="inlineStr"/>
       <c r="Q74" s="1" t="n"/>
+      <c r="R74" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -5148,6 +5520,11 @@
       <c r="O75" s="1" t="n"/>
       <c r="P75" s="1" t="inlineStr"/>
       <c r="Q75" s="1" t="n"/>
+      <c r="R75" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -5211,6 +5588,11 @@
       <c r="O76" s="1" t="n"/>
       <c r="P76" s="1" t="inlineStr"/>
       <c r="Q76" s="1" t="inlineStr"/>
+      <c r="R76" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -5270,6 +5652,11 @@
       <c r="O77" s="1" t="n"/>
       <c r="P77" s="1" t="inlineStr"/>
       <c r="Q77" s="1" t="n"/>
+      <c r="R77" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -5333,6 +5720,11 @@
       <c r="O78" s="1" t="n"/>
       <c r="P78" s="1" t="inlineStr"/>
       <c r="Q78" s="1" t="inlineStr"/>
+      <c r="R78" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -5396,6 +5788,11 @@
       <c r="O79" s="1" t="n"/>
       <c r="P79" s="1" t="inlineStr"/>
       <c r="Q79" s="1" t="inlineStr"/>
+      <c r="R79" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -5463,6 +5860,11 @@
       <c r="Q80" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R80" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -5528,6 +5930,11 @@
       <c r="O81" s="1" t="n"/>
       <c r="P81" s="1" t="inlineStr"/>
       <c r="Q81" s="1" t="inlineStr"/>
+      <c r="R81" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5587,6 +5994,11 @@
       <c r="O82" s="1" t="n"/>
       <c r="P82" s="1" t="inlineStr"/>
       <c r="Q82" s="1" t="n"/>
+      <c r="R82" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -5650,6 +6062,11 @@
       <c r="O83" s="1" t="n"/>
       <c r="P83" s="1" t="inlineStr"/>
       <c r="Q83" s="1" t="inlineStr"/>
+      <c r="R83" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -5713,6 +6130,11 @@
       <c r="O84" s="1" t="n"/>
       <c r="P84" s="1" t="inlineStr"/>
       <c r="Q84" s="1" t="inlineStr"/>
+      <c r="R84" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -5776,6 +6198,11 @@
       <c r="O85" s="1" t="n"/>
       <c r="P85" s="1" t="inlineStr"/>
       <c r="Q85" s="1" t="inlineStr"/>
+      <c r="R85" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -5839,6 +6266,11 @@
       <c r="O86" s="1" t="n"/>
       <c r="P86" s="1" t="inlineStr"/>
       <c r="Q86" s="1" t="inlineStr"/>
+      <c r="R86" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -5902,6 +6334,11 @@
       <c r="O87" s="1" t="n"/>
       <c r="P87" s="1" t="inlineStr"/>
       <c r="Q87" s="1" t="inlineStr"/>
+      <c r="R87" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5965,6 +6402,11 @@
       <c r="O88" s="1" t="n"/>
       <c r="P88" s="1" t="inlineStr"/>
       <c r="Q88" s="1" t="inlineStr"/>
+      <c r="R88" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -6028,6 +6470,11 @@
       <c r="O89" s="1" t="n"/>
       <c r="P89" s="1" t="inlineStr"/>
       <c r="Q89" s="1" t="inlineStr"/>
+      <c r="R89" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -6091,6 +6538,11 @@
       <c r="O90" s="1" t="n"/>
       <c r="P90" s="1" t="inlineStr"/>
       <c r="Q90" s="1" t="inlineStr"/>
+      <c r="R90" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -6158,6 +6610,11 @@
       <c r="Q91" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R91" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -6223,6 +6680,11 @@
       <c r="O92" s="1" t="n"/>
       <c r="P92" s="1" t="inlineStr"/>
       <c r="Q92" s="1" t="inlineStr"/>
+      <c r="R92" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -6286,6 +6748,11 @@
       <c r="O93" s="1" t="n"/>
       <c r="P93" s="1" t="inlineStr"/>
       <c r="Q93" s="1" t="inlineStr"/>
+      <c r="R93" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -6349,6 +6816,11 @@
       <c r="O94" s="1" t="n"/>
       <c r="P94" s="1" t="inlineStr"/>
       <c r="Q94" s="1" t="inlineStr"/>
+      <c r="R94" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -6412,6 +6884,11 @@
       <c r="O95" s="1" t="n"/>
       <c r="P95" s="1" t="inlineStr"/>
       <c r="Q95" s="1" t="inlineStr"/>
+      <c r="R95" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -6475,6 +6952,11 @@
       <c r="O96" s="1" t="n"/>
       <c r="P96" s="1" t="inlineStr"/>
       <c r="Q96" s="1" t="inlineStr"/>
+      <c r="R96" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -6538,6 +7020,11 @@
       <c r="O97" s="1" t="n"/>
       <c r="P97" s="1" t="inlineStr"/>
       <c r="Q97" s="1" t="inlineStr"/>
+      <c r="R97" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -6605,6 +7092,11 @@
       <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>resolvido</t>
+        </is>
+      </c>
+      <c r="R98" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -6670,6 +7162,11 @@
       <c r="O99" s="1" t="n"/>
       <c r="P99" s="1" t="inlineStr"/>
       <c r="Q99" s="1" t="inlineStr"/>
+      <c r="R99" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -6729,6 +7226,11 @@
       <c r="O100" s="1" t="n"/>
       <c r="P100" s="1" t="inlineStr"/>
       <c r="Q100" s="1" t="n"/>
+      <c r="R100" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -6792,6 +7294,11 @@
       <c r="O101" s="1" t="n"/>
       <c r="P101" s="1" t="inlineStr"/>
       <c r="Q101" s="1" t="inlineStr"/>
+      <c r="R101" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6855,6 +7362,11 @@
       <c r="O102" s="1" t="n"/>
       <c r="P102" s="1" t="inlineStr"/>
       <c r="Q102" s="1" t="inlineStr"/>
+      <c r="R102" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6918,6 +7430,11 @@
       <c r="O103" s="1" t="n"/>
       <c r="P103" s="1" t="inlineStr"/>
       <c r="Q103" s="1" t="inlineStr"/>
+      <c r="R103" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -6981,6 +7498,11 @@
       <c r="O104" s="1" t="n"/>
       <c r="P104" s="1" t="inlineStr"/>
       <c r="Q104" s="1" t="inlineStr"/>
+      <c r="R104" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -7044,6 +7566,11 @@
       <c r="O105" s="1" t="n"/>
       <c r="P105" s="1" t="inlineStr"/>
       <c r="Q105" s="1" t="inlineStr"/>
+      <c r="R105" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -7107,6 +7634,11 @@
       <c r="O106" s="1" t="n"/>
       <c r="P106" s="1" t="inlineStr"/>
       <c r="Q106" s="1" t="inlineStr"/>
+      <c r="R106" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -7170,6 +7702,11 @@
       <c r="O107" s="1" t="n"/>
       <c r="P107" s="1" t="inlineStr"/>
       <c r="Q107" s="1" t="inlineStr"/>
+      <c r="R107" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -7233,6 +7770,11 @@
       <c r="O108" s="1" t="n"/>
       <c r="P108" s="1" t="inlineStr"/>
       <c r="Q108" s="1" t="inlineStr"/>
+      <c r="R108" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -7296,6 +7838,11 @@
       <c r="O109" s="1" t="n"/>
       <c r="P109" s="1" t="inlineStr"/>
       <c r="Q109" s="1" t="inlineStr"/>
+      <c r="R109" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -7363,6 +7910,11 @@
       <c r="Q110" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
+      <c r="R110" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -7428,6 +7980,11 @@
       <c r="O111" s="1" t="n"/>
       <c r="P111" s="1" t="inlineStr"/>
       <c r="Q111" s="1" t="inlineStr"/>
+      <c r="R111" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -7491,6 +8048,11 @@
       <c r="O112" s="1" t="n"/>
       <c r="P112" s="1" t="inlineStr"/>
       <c r="Q112" s="1" t="inlineStr"/>
+      <c r="R112" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -7550,6 +8112,11 @@
       <c r="O113" s="1" t="n"/>
       <c r="P113" s="1" t="inlineStr"/>
       <c r="Q113" s="1" t="n"/>
+      <c r="R113" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -7617,6 +8184,11 @@
       <c r="Q114" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">resolvido </t>
+        </is>
+      </c>
+      <c r="R114" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
@@ -7682,6 +8254,11 @@
       <c r="O115" s="1" t="n"/>
       <c r="P115" s="1" t="inlineStr"/>
       <c r="Q115" s="1" t="inlineStr"/>
+      <c r="R115" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -7741,6 +8318,11 @@
       <c r="O116" s="1" t="n"/>
       <c r="P116" s="1" t="inlineStr"/>
       <c r="Q116" s="1" t="n"/>
+      <c r="R116" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7800,6 +8382,11 @@
       <c r="O117" s="1" t="n"/>
       <c r="P117" s="1" t="inlineStr"/>
       <c r="Q117" s="1" t="n"/>
+      <c r="R117" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7863,6 +8450,11 @@
       <c r="O118" s="1" t="n"/>
       <c r="P118" s="1" t="inlineStr"/>
       <c r="Q118" s="1" t="inlineStr"/>
+      <c r="R118" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7926,6 +8518,11 @@
       <c r="O119" s="1" t="n"/>
       <c r="P119" s="1" t="inlineStr"/>
       <c r="Q119" s="1" t="inlineStr"/>
+      <c r="R119" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -7989,6 +8586,11 @@
       <c r="O120" s="1" t="n"/>
       <c r="P120" s="1" t="inlineStr"/>
       <c r="Q120" s="1" t="inlineStr"/>
+      <c r="R120" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -8052,6 +8654,11 @@
       <c r="O121" s="1" t="n"/>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr"/>
+      <c r="R121" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -8111,6 +8718,11 @@
       <c r="O122" s="1" t="n"/>
       <c r="P122" s="1" t="inlineStr"/>
       <c r="Q122" s="1" t="n"/>
+      <c r="R122" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -8174,6 +8786,11 @@
       <c r="O123" s="1" t="n"/>
       <c r="P123" s="1" t="inlineStr"/>
       <c r="Q123" s="1" t="inlineStr"/>
+      <c r="R123" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -8237,6 +8854,11 @@
       <c r="O124" s="1" t="n"/>
       <c r="P124" s="1" t="inlineStr"/>
       <c r="Q124" s="1" t="inlineStr"/>
+      <c r="R124" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -8296,6 +8918,11 @@
       <c r="O125" s="1" t="n"/>
       <c r="P125" s="1" t="inlineStr"/>
       <c r="Q125" s="1" t="n"/>
+      <c r="R125" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -8359,6 +8986,11 @@
       <c r="O126" s="1" t="n"/>
       <c r="P126" s="1" t="inlineStr"/>
       <c r="Q126" s="1" t="inlineStr"/>
+      <c r="R126" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -8418,6 +9050,11 @@
       <c r="O127" s="1" t="n"/>
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="n"/>
+      <c r="R127" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -8481,6 +9118,11 @@
       <c r="O128" s="1" t="n"/>
       <c r="P128" s="1" t="inlineStr"/>
       <c r="Q128" s="1" t="inlineStr"/>
+      <c r="R128" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -8544,6 +9186,11 @@
       <c r="O129" s="1" t="n"/>
       <c r="P129" s="1" t="inlineStr"/>
       <c r="Q129" s="1" t="inlineStr"/>
+      <c r="R129" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -8607,6 +9254,11 @@
       <c r="O130" s="1" t="n"/>
       <c r="P130" s="1" t="inlineStr"/>
       <c r="Q130" s="1" t="inlineStr"/>
+      <c r="R130" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -8670,6 +9322,11 @@
       <c r="O131" s="1" t="n"/>
       <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr"/>
+      <c r="R131" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -8733,10 +9390,15 @@
       <c r="O132" s="1" t="n"/>
       <c r="P132" s="1" t="inlineStr"/>
       <c r="Q132" s="1" t="inlineStr"/>
+      <c r="R132" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>77683</v>
+        <v>77096</v>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
@@ -8750,25 +9412,25 @@
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">solicitar ao cliente que nos enviei a documentação via FTP, os e-mail enviados pelo cliente tem uma alto consumo de memoria em nossos e-mail. </t>
+          <t>2.01.003.0001.00001 - Salários a Pagar</t>
         </is>
       </c>
       <c r="F133" s="1" t="n">
-        <v>1119</v>
+        <v>861</v>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>BANDEIRANTES REFRIGERAÇÃO COMERCIAL LTDA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H133" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="I133" s="1" t="inlineStr">
@@ -8777,29 +9439,44 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46085.38586099537</v>
+        <v>46063.39483510417</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>46087</v>
+        <v>46070</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="N133" s="1" t="n"/>
-      <c r="O133" s="1" t="n"/>
-      <c r="P133" s="1" t="inlineStr"/>
-      <c r="Q133" s="1" t="inlineStr"/>
+      <c r="O133" s="2" t="n">
+        <v>46175.47102299768</v>
+      </c>
+      <c r="P133" s="1" t="inlineStr">
+        <is>
+          <t>diegol</t>
+        </is>
+      </c>
+      <c r="Q133" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resolvido. </t>
+        </is>
+      </c>
+      <c r="R133" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>77609</v>
+        <v>77683</v>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
@@ -8813,25 +9490,25 @@
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Grupo Catroque	GC	Ricardo Silva	Darlan Rodrigues	Cadastro de Produtos	Como está a análise?	27/02/2026	13/03/2026	13/03/2026	PENDÊNCIA	Grupo Catroque	GC	Ricardo Silva	Darlan Rodrigues	ICMS	Enviar apuração para demonstrar os créditos recuperados	27/02/2026	13/03/2026	13/03/2026	PENDÊNCIA</t>
+          <t xml:space="preserve">solicitar ao cliente que nos enviei a documentação via FTP, os e-mail enviados pelo cliente tem uma alto consumo de memoria em nossos e-mail. </t>
         </is>
       </c>
       <c r="F134" s="1" t="n">
-        <v>1147</v>
+        <v>1119</v>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CATROQUE LTDA</t>
+          <t>BANDEIRANTES REFRIGERAÇÃO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I134" s="1" t="inlineStr">
@@ -8840,10 +9517,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46083.37776230324</v>
+        <v>46085.38586099537</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>46090</v>
+        <v>46087</v>
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
@@ -8852,26 +9529,31 @@
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N134" s="1" t="n"/>
       <c r="O134" s="1" t="n"/>
       <c r="P134" s="1" t="inlineStr"/>
       <c r="Q134" s="1" t="inlineStr"/>
+      <c r="R134" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>76708</v>
+        <v>77609</v>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
@@ -8881,20 +9563,20 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>IBS / CBS X XML	Sistema ajustado para contemplar no XML das emissões de NF os campos de IBS e XML.LUCRO PRESUMIDO	Adiantamos ao cliente as informações contidas no DL de 26/12/2025, que onera os percentuais da base de cálculo do IRPJ/CSLL a partir de sua vigência IR Jan/2026 e CSLL a partir de Abr/2026</t>
+          <t xml:space="preserve">	Grupo Catroque	GC	Ricardo Silva	Darlan Rodrigues	Cadastro de Produtos	Como está a análise?	27/02/2026	13/03/2026	13/03/2026	PENDÊNCIA	Grupo Catroque	GC	Ricardo Silva	Darlan Rodrigues	ICMS	Enviar apuração para demonstrar os créditos recuperados	27/02/2026	13/03/2026	13/03/2026	PENDÊNCIA</t>
         </is>
       </c>
       <c r="F135" s="1" t="n">
-        <v>1286</v>
+        <v>1147</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
+          <t>SUPERMERCADO CATROQUE LTDA</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
@@ -8903,10 +9585,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46041.6894391551</v>
+        <v>46083.37776230324</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>46048</v>
+        <v>46090</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -8915,36 +9597,41 @@
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N135" s="1" t="n"/>
       <c r="O135" s="1" t="n"/>
       <c r="P135" s="1" t="inlineStr"/>
       <c r="Q135" s="1" t="inlineStr"/>
+      <c r="R135" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>78306</v>
+        <v>76708</v>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>IBS / CBS X XML	Sistema ajustado para contemplar no XML das emissões de NF os campos de IBS e XML.LUCRO PRESUMIDO	Adiantamos ao cliente as informações contidas no DL de 26/12/2025, que onera os percentuais da base de cálculo do IRPJ/CSLL a partir de sua vigência IR Jan/2026 e CSLL a partir de Abr/2026</t>
         </is>
       </c>
       <c r="F136" s="1" t="n">
@@ -8966,10 +9653,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46111.42803700231</v>
+        <v>46041.6894391551</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
@@ -8978,44 +9665,49 @@
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N136" s="1" t="n"/>
       <c r="O136" s="1" t="n"/>
       <c r="P136" s="1" t="inlineStr"/>
       <c r="Q136" s="1" t="inlineStr"/>
+      <c r="R136" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>76698</v>
+        <v>78306</v>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>REGIME DE CAIXA	Confirmar se houve resposta a questionamento anterior de que a empresa poderia se enquadrar no Regime de Caixa.EXCLUSÃO ICMS ST SETOR DE PRODUTOS ALIMENTÍCIOS	Levantar junto ao depto técnico, INFORMATIVO da exclusão de ICMS ST na comercialização de produtos alimentícios e encaminhar ao cliente na pessoa da Sueli com cópia para Fábio.REDUÇÃO BASE CÁLCULO PRODUTOS ALIMENTÍCIOS	Sabe-se que a indústria venda para o comércio, produtos alimentícios cuja base de ICMS é reduzida de forma que o ICMS fique em 12%. Confirmar tal procedimento e quais possíveis produtos manteriam a redução da base de cálculo até o cosumidor final (ex. Café em grão tem reduçção de forma que o ICMS seja 7% até o consumidor final).CÁLCULO ICMS ST NOS ESTOQUES	Levantar junto ao dpto técnico legislação e especificamente fórmula para o cálculo do ICMS nos estoques de produtos que sairam da substituição tributária. Encmainhar para o cliente na pessoa das Sras. Sueli e Meire.INTGEGRAÇÃO HIPCOM	Sabe-se que clientes do varejo mantém integração financeiro/Único de dados registrados no sistema HIPCOM e que também poderiam ser intgegrados das MQ para SCI. Por isso, levantar junto a diretoria o que poderia ser feito para que isto se torne realidade no menor espaço de tempo possível.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F137" s="1" t="n">
-        <v>1443</v>
+        <v>1286</v>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t>MQ PRODUSERV COMÉRCIO E EMPREENDIMENTOS LTDA</t>
+          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
@@ -9029,10 +9721,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46041.67581362269</v>
+        <v>46111.42803700231</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>46042</v>
+        <v>46122</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
@@ -9041,49 +9733,54 @@
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N137" s="1" t="n"/>
       <c r="O137" s="1" t="n"/>
       <c r="P137" s="1" t="inlineStr"/>
       <c r="Q137" s="1" t="inlineStr"/>
+      <c r="R137" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>78322</v>
+        <v>76698</v>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>REGIME DE CAIXA	Confirmar se houve resposta a questionamento anterior de que a empresa poderia se enquadrar no Regime de Caixa.EXCLUSÃO ICMS ST SETOR DE PRODUTOS ALIMENTÍCIOS	Levantar junto ao depto técnico, INFORMATIVO da exclusão de ICMS ST na comercialização de produtos alimentícios e encaminhar ao cliente na pessoa da Sueli com cópia para Fábio.REDUÇÃO BASE CÁLCULO PRODUTOS ALIMENTÍCIOS	Sabe-se que a indústria venda para o comércio, produtos alimentícios cuja base de ICMS é reduzida de forma que o ICMS fique em 12%. Confirmar tal procedimento e quais possíveis produtos manteriam a redução da base de cálculo até o cosumidor final (ex. Café em grão tem reduçção de forma que o ICMS seja 7% até o consumidor final).CÁLCULO ICMS ST NOS ESTOQUES	Levantar junto ao dpto técnico legislação e especificamente fórmula para o cálculo do ICMS nos estoques de produtos que sairam da substituição tributária. Encmainhar para o cliente na pessoa das Sras. Sueli e Meire.INTGEGRAÇÃO HIPCOM	Sabe-se que clientes do varejo mantém integração financeiro/Único de dados registrados no sistema HIPCOM e que também poderiam ser intgegrados das MQ para SCI. Por isso, levantar junto a diretoria o que poderia ser feito para que isto se torne realidade no menor espaço de tempo possível.</t>
         </is>
       </c>
       <c r="F138" s="1" t="n">
-        <v>2209</v>
+        <v>1443</v>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t>MQ PRODUSERV COMÉRCIO E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I138" s="1" t="inlineStr">
@@ -9092,10 +9789,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46111.44774475694</v>
+        <v>46041.67581362269</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>46122</v>
+        <v>46042</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
@@ -9104,17 +9801,22 @@
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N138" s="1" t="n"/>
       <c r="O138" s="1" t="n"/>
       <c r="P138" s="1" t="inlineStr"/>
       <c r="Q138" s="1" t="inlineStr"/>
+      <c r="R138" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>76820</v>
+        <v>76705</v>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
@@ -9133,20 +9835,20 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>IOF S/ EMPRÉSTIMOS	Confirmar junto ao depto técnico se empréstimos concedidos de Pessoa Jurídica para Pessoa Física teria IOF e quais as condições, informar Sr. Luiz</t>
+          <t>2192 -ORVALHOSUB-LIMITE	Acompanhar a recuperação do sub-limite, cujo processo precisa ser realizado pelo paralegal, paa que a empresa esteja 100% no Simples Nacional em 20262209 -TENDAS SIMPLES NACIONAL	Acompanhar enquadramento no simples nacional desta empresa que sairá do lucro presumido para o Simples Nacional em 2026</t>
         </is>
       </c>
       <c r="F139" s="1" t="n">
-        <v>2481</v>
+        <v>2192</v>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t>DON MARCHÊ SERVIÇOS DE ALIMENTAÇÃO LTDA (MATRIZ)</t>
+          <t xml:space="preserve">ORVALHO DO SOL INDÚSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
@@ -9155,14 +9857,14 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46048.50494429398</v>
+        <v>46041.68550995371</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>46055</v>
+        <v>46048</v>
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M139" s="1" t="inlineStr">
@@ -9171,45 +9873,60 @@
         </is>
       </c>
       <c r="N139" s="1" t="n"/>
-      <c r="O139" s="1" t="n"/>
-      <c r="P139" s="1" t="inlineStr"/>
-      <c r="Q139" s="1" t="inlineStr"/>
+      <c r="O139" s="2" t="n">
+        <v>46058.48028619213</v>
+      </c>
+      <c r="P139" s="1" t="inlineStr">
+        <is>
+          <t>beatrizr</t>
+        </is>
+      </c>
+      <c r="Q139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2209 - Não foi possível enquadrar no SN, receita bruta excede o limite estabelecido. Será aberta uma nova empresa conforme informado pelo GM </t>
+        </is>
+      </c>
+      <c r="R139" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>78340</v>
+        <v>78322</v>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>ESSÊNCIA PORTUGUESA X IPI	"Cliente cobra resposta da tributação ou não de IPI na venda para o cliente Essência Portuguesa."</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F140" s="1" t="n">
-        <v>2576</v>
+        <v>2209</v>
       </c>
       <c r="G140" s="1" t="inlineStr">
         <is>
-          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H140" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I140" s="1" t="inlineStr">
@@ -9218,10 +9935,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46112.40695462963</v>
+        <v>46111.44774475694</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>46119</v>
+        <v>46122</v>
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
@@ -9230,49 +9947,54 @@
       </c>
       <c r="M140" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N140" s="1" t="n"/>
       <c r="O140" s="1" t="n"/>
       <c r="P140" s="1" t="inlineStr"/>
       <c r="Q140" s="1" t="inlineStr"/>
+      <c r="R140" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>78304</v>
+        <v>76820</v>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>IOF S/ EMPRÉSTIMOS	Confirmar junto ao depto técnico se empréstimos concedidos de Pessoa Jurídica para Pessoa Física teria IOF e quais as condições, informar Sr. Luiz</t>
         </is>
       </c>
       <c r="F141" s="1" t="n">
-        <v>2620</v>
+        <v>2481</v>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>ANTOCON GALVANOPLASTIA LTDA</t>
+          <t>DON MARCHÊ SERVIÇOS DE ALIMENTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H141" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I141" s="1" t="inlineStr">
@@ -9281,10 +10003,10 @@
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46111.42458850695</v>
+        <v>46048.50494429398</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>46122</v>
+        <v>46055</v>
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
@@ -9293,17 +10015,22 @@
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N141" s="1" t="n"/>
       <c r="O141" s="1" t="n"/>
       <c r="P141" s="1" t="inlineStr"/>
       <c r="Q141" s="1" t="inlineStr"/>
+      <c r="R141" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>76753</v>
+        <v>78340</v>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
@@ -9312,7 +10039,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -9322,20 +10049,20 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,SUP. ZARELLIASSUNTO: TransferenciaPENDÊNCIA: "Informado ao cliente que os valores de transferencias entre lojas não batem.GC levantar as tranferencias entre lojas SAÌDAS x Entradas. Apresentar diferenças das notas "</t>
+          <t>ESSÊNCIA PORTUGUESA X IPI	"Cliente cobra resposta da tributação ou não de IPI na venda para o cliente Essência Portuguesa."</t>
         </is>
       </c>
       <c r="F142" s="1" t="n">
-        <v>2857</v>
+        <v>2576</v>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
+          <t>P.E Latina Maquinas para Rotulagem Ltda.</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I142" s="1" t="inlineStr">
@@ -9344,10 +10071,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46044.40140454861</v>
+        <v>46112.40695462963</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>46058</v>
+        <v>46119</v>
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
@@ -9356,49 +10083,54 @@
       </c>
       <c r="M142" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N142" s="1" t="n"/>
       <c r="O142" s="1" t="n"/>
       <c r="P142" s="1" t="inlineStr"/>
       <c r="Q142" s="1" t="inlineStr"/>
+      <c r="R142" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>76754</v>
+        <v>78304</v>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,SUP. ZARELLIASSUNTO: AluguelPENDÊNCIA: "Verificar os valores lançados como Despesas, o valor do aluguel é de 3% do Faturamento. Pagto é feito no começo do mês seguinte.Daniel, conforme conversamos, solciitar o controle de aluguel para Camila e revisar os alugueis."</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F143" s="1" t="n">
-        <v>2857</v>
+        <v>2620</v>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
+          <t>ANTOCON GALVANOPLASTIA LTDA</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I143" s="1" t="inlineStr">
@@ -9407,10 +10139,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46044.40214846065</v>
+        <v>46111.42458850695</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>46058</v>
+        <v>46122</v>
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
@@ -9419,17 +10151,22 @@
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N143" s="1" t="n"/>
       <c r="O143" s="1" t="n"/>
       <c r="P143" s="1" t="inlineStr"/>
       <c r="Q143" s="1" t="inlineStr"/>
+      <c r="R143" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>76755</v>
+        <v>76753</v>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
@@ -9448,7 +10185,7 @@
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,SUP. ZARELLIASSUNTO: HortfruitPENDÊNCIA: analisar e lançar os descontos obtidos sobre fornecedores. As compras feitas é pago 82% do valor de cada NF e o valor de 18% é desconto.</t>
+          <t>Bom dia,SUP. ZARELLIASSUNTO: TransferenciaPENDÊNCIA: "Informado ao cliente que os valores de transferencias entre lojas não batem.GC levantar as tranferencias entre lojas SAÌDAS x Entradas. Apresentar diferenças das notas "</t>
         </is>
       </c>
       <c r="F144" s="1" t="n">
@@ -9470,7 +10207,7 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46044.40260181713</v>
+        <v>46044.40140454861</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>46058</v>
@@ -9489,10 +10226,15 @@
       <c r="O144" s="1" t="n"/>
       <c r="P144" s="1" t="inlineStr"/>
       <c r="Q144" s="1" t="inlineStr"/>
+      <c r="R144" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>76756</v>
+        <v>76754</v>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
@@ -9511,7 +10253,7 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,SUP. ZARELLIASSUNTO: DescontosPENDÊNCIA: analisar e lançar os descontos obtidos sobre fornecedores. As compras feitas é pago 82% do valor de cada NF e o valor de 18% é desconto.</t>
+          <t>Bom dia,SUP. ZARELLIASSUNTO: AluguelPENDÊNCIA: "Verificar os valores lançados como Despesas, o valor do aluguel é de 3% do Faturamento. Pagto é feito no começo do mês seguinte.Daniel, conforme conversamos, solciitar o controle de aluguel para Camila e revisar os alugueis."</t>
         </is>
       </c>
       <c r="F145" s="1" t="n">
@@ -9533,7 +10275,7 @@
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46044.4030815625</v>
+        <v>46044.40214846065</v>
       </c>
       <c r="K145" s="2" t="n">
         <v>46058</v>
@@ -9552,10 +10294,15 @@
       <c r="O145" s="1" t="n"/>
       <c r="P145" s="1" t="inlineStr"/>
       <c r="Q145" s="1" t="inlineStr"/>
+      <c r="R145" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>76387</v>
+        <v>76755</v>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
@@ -9574,20 +10321,20 @@
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE LUCROSSerão após equivaçência apurados os resultados e definida as reservas para emissão de ATA de reunião dos Sócios para cumprir com a determinação legal de se manter isenta em distribuição de lucros nos anos 2026 a 2028, ATA esta a ser preparada e registrada pelo Jurídico e paralegal da própria Treecorp.</t>
+          <t>Bom dia,SUP. ZARELLIASSUNTO: HortfruitPENDÊNCIA: analisar e lançar os descontos obtidos sobre fornecedores. As compras feitas é pago 82% do valor de cada NF e o valor de 18% é desconto.</t>
         </is>
       </c>
       <c r="F146" s="1" t="n">
-        <v>2891</v>
+        <v>2857</v>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t>TREE CORP PARTNERS CONSULTORIA EMPRESARIAL LTDA</t>
+          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H146" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="I146" s="1" t="inlineStr">
@@ -9596,10 +10343,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46024.67288244213</v>
+        <v>46044.40260181713</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>46031</v>
+        <v>46058</v>
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
@@ -9608,17 +10355,22 @@
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N146" s="1" t="n"/>
       <c r="O146" s="1" t="n"/>
       <c r="P146" s="1" t="inlineStr"/>
       <c r="Q146" s="1" t="inlineStr"/>
+      <c r="R146" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>76999</v>
+        <v>76756</v>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
@@ -9627,7 +10379,7 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
@@ -9637,20 +10389,20 @@
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t>RESULTADOS 2025	Resultados de 2025 serão alterado com receita de descontos obtidos de empréstimos a pagar em 2025 desde o 1º trimestre, em quais trimestres anteriores ao 4º trimestre haja prejuízo que será compensado com o lucro do 4º trimestre trazendo resultado positivo de algo em torno de R$ 30 mil e pagamento de IRPJ/CSLL no valor de R$ 7 mil.</t>
+          <t>Bom dia,SUP. ZARELLIASSUNTO: DescontosPENDÊNCIA: analisar e lançar os descontos obtidos sobre fornecedores. As compras feitas é pago 82% do valor de cada NF e o valor de 18% é desconto.</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
-        <v>3262</v>
+        <v>2857</v>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
+          <t>ZARELLI SUPERMERCADOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H147" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="I147" s="1" t="inlineStr">
@@ -9659,10 +10411,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46057.50747534722</v>
+        <v>46044.4030815625</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>46064</v>
+        <v>46058</v>
       </c>
       <c r="L147" s="1" t="inlineStr">
         <is>
@@ -9671,44 +10423,49 @@
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N147" s="1" t="n"/>
       <c r="O147" s="1" t="n"/>
       <c r="P147" s="1" t="inlineStr"/>
       <c r="Q147" s="1" t="inlineStr"/>
+      <c r="R147" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>78313</v>
+        <v>76387</v>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>DISTRIBUIÇÃO DE LUCROSSerão após equivaçência apurados os resultados e definida as reservas para emissão de ATA de reunião dos Sócios para cumprir com a determinação legal de se manter isenta em distribuição de lucros nos anos 2026 a 2028, ATA esta a ser preparada e registrada pelo Jurídico e paralegal da própria Treecorp.</t>
         </is>
       </c>
       <c r="F148" s="1" t="n">
-        <v>3262</v>
+        <v>2891</v>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
+          <t>TREE CORP PARTNERS CONSULTORIA EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="H148" s="1" t="inlineStr">
@@ -9722,10 +10479,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46111.43707260417</v>
+        <v>46024.67288244213</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>46122</v>
+        <v>46031</v>
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
@@ -9734,17 +10491,22 @@
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N148" s="1" t="n"/>
       <c r="O148" s="1" t="n"/>
       <c r="P148" s="1" t="inlineStr"/>
       <c r="Q148" s="1" t="inlineStr"/>
+      <c r="R148" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>76995</v>
+        <v>76999</v>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
@@ -9763,15 +10525,15 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>ISS JAN/2026	Cliente emitiu várias notas fiscais em princípio de janeiro diretamente no site das PMTS cujo valor de ISS foi destacado, como o cliente esta no simples nacional acompanhar apuração dos impostos de Jan/206, e confirmar junto ao processo se não haverá interferência na apuração e no pagamento dos impostos, deixando possível pendência perante a PMTS.</t>
+          <t>RESULTADOS 2025	Resultados de 2025 serão alterado com receita de descontos obtidos de empréstimos a pagar em 2025 desde o 1º trimestre, em quais trimestres anteriores ao 4º trimestre haja prejuízo que será compensado com o lucro do 4º trimestre trazendo resultado positivo de algo em torno de R$ 30 mil e pagamento de IRPJ/CSLL no valor de R$ 7 mil.</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
-        <v>3498</v>
+        <v>3262</v>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPLACA SERVIÇOS LTDA </t>
+          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
         </is>
       </c>
       <c r="H149" s="1" t="inlineStr">
@@ -9785,7 +10547,7 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46057.50510605324</v>
+        <v>46057.50747534722</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>46064</v>
@@ -9804,37 +10566,42 @@
       <c r="O149" s="1" t="n"/>
       <c r="P149" s="1" t="inlineStr"/>
       <c r="Q149" s="1" t="inlineStr"/>
+      <c r="R149" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>76393</v>
+        <v>78313</v>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>GRUPO EMPLACADISTRIBUIÇÃO DE LUCROS	Segundo informações do cliente em até 12/2025, as reservas serão esvasiadas, por isso não haverá Ata de reunião dos sócios para distribuição de lucros, a menos que em 12/2025 seja obtido resultados que apresentem reservas e neste caso será tratado ao final da contabilização de 12/2025,s e farão ou não ATA para registro de suposta reserva.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>3499</v>
+        <v>3262</v>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
+          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
         </is>
       </c>
       <c r="H150" s="1" t="inlineStr">
@@ -9848,10 +10615,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46024.67690671296</v>
+        <v>46111.43707260417</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>46031</v>
+        <v>46122</v>
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
@@ -9860,17 +10627,22 @@
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N150" s="1" t="n"/>
       <c r="O150" s="1" t="n"/>
       <c r="P150" s="1" t="inlineStr"/>
       <c r="Q150" s="1" t="inlineStr"/>
+      <c r="R150" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>76703</v>
+        <v>76995</v>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
@@ -9889,15 +10661,15 @@
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>3499 - EMPLACA AUTOMAÇÃONF SERVIÇOS	Cliente demonstrou exarcebado descontentamento quanto a possível falta de informação contábil quanto a necessidade de adaptar os CNAEs da empresa aos códigos de serviço para emissão de nota fiscal, que ficou prejudicada pela não atualização e que segundo consulta perante a PMTS as contabilidades parceiras teriam sabido da exigência desde 07/2025. Por isso, acompanhar junto ao Para-legal processo de regularização em andamento.3498 - EMPLACA SERVIÇOSNF SERVIÇOS	Cliente demonstrou exarcebado descontentamento quanto a possível falta de informação contábil quanto a necessidade de adaptar os CNAEs da empresa aos códigos de serviço para emissão de nota fiscal, que ficou prejudicada pela não atualização e que segundo consulta perante a PMTS as contabilidades parceiras teriam sabido da exigência desde 07/2025. Por isso, acompanhar junto ao Para-legal processo de regularização em andamento.NF SERVIÇOS	Cliente emitiu nota fiscal de prestação de serviços diretamente no site da PMTS, e as mesmas sdairam com destaque de ISS, informar se na apuração do Simples Nacional este destaque não representaria qualquer obrigatoriedade em recolhimento.</t>
+          <t>ISS JAN/2026	Cliente emitiu várias notas fiscais em princípio de janeiro diretamente no site das PMTS cujo valor de ISS foi destacado, como o cliente esta no simples nacional acompanhar apuração dos impostos de Jan/206, e confirmar junto ao processo se não haverá interferência na apuração e no pagamento dos impostos, deixando possível pendência perante a PMTS.</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>3499</v>
+        <v>3498</v>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
+          <t xml:space="preserve">EMPLACA SERVIÇOS LTDA </t>
         </is>
       </c>
       <c r="H151" s="1" t="inlineStr">
@@ -9911,10 +10683,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46041.68250575232</v>
+        <v>46057.50510605324</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>46048</v>
+        <v>46064</v>
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
@@ -9930,29 +10702,34 @@
       <c r="O151" s="1" t="n"/>
       <c r="P151" s="1" t="inlineStr"/>
       <c r="Q151" s="1" t="inlineStr"/>
+      <c r="R151" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>78309</v>
+        <v>76393</v>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>GRUPO EMPLACADISTRIBUIÇÃO DE LUCROS	Segundo informações do cliente em até 12/2025, as reservas serão esvasiadas, por isso não haverá Ata de reunião dos sócios para distribuição de lucros, a menos que em 12/2025 seja obtido resultados que apresentem reservas e neste caso será tratado ao final da contabilização de 12/2025,s e farão ou não ATA para registro de suposta reserva.</t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
@@ -9974,10 +10751,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46111.43159019676</v>
+        <v>46024.67690671296</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>46122</v>
+        <v>46031</v>
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
@@ -9986,44 +10763,49 @@
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N152" s="1" t="n"/>
       <c r="O152" s="1" t="n"/>
       <c r="P152" s="1" t="inlineStr"/>
       <c r="Q152" s="1" t="inlineStr"/>
+      <c r="R152" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>78326</v>
+        <v>76703</v>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>3499 - EMPLACA AUTOMAÇÃONF SERVIÇOS	Cliente demonstrou exarcebado descontentamento quanto a possível falta de informação contábil quanto a necessidade de adaptar os CNAEs da empresa aos códigos de serviço para emissão de nota fiscal, que ficou prejudicada pela não atualização e que segundo consulta perante a PMTS as contabilidades parceiras teriam sabido da exigência desde 07/2025. Por isso, acompanhar junto ao Para-legal processo de regularização em andamento.3498 - EMPLACA SERVIÇOSNF SERVIÇOS	Cliente demonstrou exarcebado descontentamento quanto a possível falta de informação contábil quanto a necessidade de adaptar os CNAEs da empresa aos códigos de serviço para emissão de nota fiscal, que ficou prejudicada pela não atualização e que segundo consulta perante a PMTS as contabilidades parceiras teriam sabido da exigência desde 07/2025. Por isso, acompanhar junto ao Para-legal processo de regularização em andamento.NF SERVIÇOS	Cliente emitiu nota fiscal de prestação de serviços diretamente no site da PMTS, e as mesmas sdairam com destaque de ISS, informar se na apuração do Simples Nacional este destaque não representaria qualquer obrigatoriedade em recolhimento.</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>3598</v>
+        <v>3499</v>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
+          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
         </is>
       </c>
       <c r="H153" s="1" t="inlineStr">
@@ -10037,10 +10819,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46111.45085925926</v>
+        <v>46041.68250575232</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
@@ -10049,44 +10831,49 @@
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N153" s="1" t="n"/>
       <c r="O153" s="1" t="n"/>
       <c r="P153" s="1" t="inlineStr"/>
       <c r="Q153" s="1" t="inlineStr"/>
+      <c r="R153" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>76706</v>
+        <v>78309</v>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>PIS/COFINS - TOMADA DE CRÉDITOS	Levantar junto ao nosso dpto técnico listagem de itens e/ou aquisição de materiais ou serviços que poderiam se tomar crédito de PIS E COFINS no regime não cumulativo, tendo em vista que a empresa passou ao lucro real, tais como: Material de consumo/manutenção e informar para Adriana.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F154" s="1" t="n">
-        <v>3693</v>
+        <v>3499</v>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>AF DATALINK CABOS, CONEXOES E SISTEMAS LTDA</t>
+          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
@@ -10100,10 +10887,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46041.68631774306</v>
+        <v>46111.43159019676</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>46048</v>
+        <v>46122</v>
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
@@ -10112,17 +10899,22 @@
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N154" s="1" t="n"/>
       <c r="O154" s="1" t="n"/>
       <c r="P154" s="1" t="inlineStr"/>
       <c r="Q154" s="1" t="inlineStr"/>
+      <c r="R154" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>78319</v>
+        <v>78326</v>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
@@ -10145,16 +10937,16 @@
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>3723</v>
+        <v>3598</v>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>PLASTIJAPA INDUSTRIA E COMÉRCIO LTDA</t>
+          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I155" s="1" t="inlineStr">
@@ -10163,7 +10955,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46111.44368935185</v>
+        <v>46111.45085925926</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>46122</v>
@@ -10182,42 +10974,47 @@
       <c r="O155" s="1" t="n"/>
       <c r="P155" s="1" t="inlineStr"/>
       <c r="Q155" s="1" t="inlineStr"/>
+      <c r="R155" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>78291</v>
+        <v>76706</v>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>PIS/COFINS - TOMADA DE CRÉDITOS	Levantar junto ao nosso dpto técnico listagem de itens e/ou aquisição de materiais ou serviços que poderiam se tomar crédito de PIS E COFINS no regime não cumulativo, tendo em vista que a empresa passou ao lucro real, tais como: Material de consumo/manutenção e informar para Adriana.</t>
         </is>
       </c>
       <c r="F156" s="1" t="n">
-        <v>3724</v>
+        <v>3693</v>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>ACCESSORY HOUSE COMÉRCIO E INDÚSTRIA LTDA</t>
+          <t>AF DATALINK CABOS, CONEXOES E SISTEMAS LTDA</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I156" s="1" t="inlineStr">
@@ -10226,10 +11023,10 @@
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46111.41570663195</v>
+        <v>46041.68631774306</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>46122</v>
+        <v>46048</v>
       </c>
       <c r="L156" s="1" t="inlineStr">
         <is>
@@ -10238,17 +11035,22 @@
       </c>
       <c r="M156" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N156" s="1" t="n"/>
       <c r="O156" s="1" t="n"/>
       <c r="P156" s="1" t="inlineStr"/>
       <c r="Q156" s="1" t="inlineStr"/>
+      <c r="R156" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>78310</v>
+        <v>78319</v>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
@@ -10271,16 +11073,16 @@
         </is>
       </c>
       <c r="F157" s="1" t="n">
-        <v>3744</v>
+        <v>3723</v>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t>HAITTER INDUSTRIA DE MAQUINAS LTDA.</t>
+          <t>PLASTIJAPA INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I157" s="1" t="inlineStr">
@@ -10289,7 +11091,7 @@
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46111.43257133102</v>
+        <v>46111.44368935185</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>46122</v>
@@ -10308,10 +11110,15 @@
       <c r="O157" s="1" t="n"/>
       <c r="P157" s="1" t="inlineStr"/>
       <c r="Q157" s="1" t="inlineStr"/>
+      <c r="R157" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>78308</v>
+        <v>78291</v>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
@@ -10334,16 +11141,16 @@
         </is>
       </c>
       <c r="F158" s="1" t="n">
-        <v>3954</v>
+        <v>3724</v>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>Cristaleria Bruxelas Indústria e Comércio Eireli</t>
+          <t>ACCESSORY HOUSE COMÉRCIO E INDÚSTRIA LTDA</t>
         </is>
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I158" s="1" t="inlineStr">
@@ -10352,7 +11159,7 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46111.43023637732</v>
+        <v>46111.41570663195</v>
       </c>
       <c r="K158" s="2" t="n">
         <v>46122</v>
@@ -10371,42 +11178,47 @@
       <c r="O158" s="1" t="n"/>
       <c r="P158" s="1" t="inlineStr"/>
       <c r="Q158" s="1" t="inlineStr"/>
+      <c r="R158" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>77000</v>
+        <v>78310</v>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>DESTDA	Houve e-mail de nossa colaboradora sobre DESTDA informada equivocadamente e que gerou cobrança desnecessária, por isso cliente neste mesmo e-mail (09/12), cobra o valor da diferença de juros e a restituição do valor pago a maior.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>4003</v>
+        <v>3744</v>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>NUTRI- QUEEN COMÉRCIO VAREJISTA DE ALIMENTOS LTDA</t>
+          <t>HAITTER INDUSTRIA DE MAQUINAS LTDA.</t>
         </is>
       </c>
       <c r="H159" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I159" s="1" t="inlineStr">
@@ -10415,10 +11227,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46057.50836859953</v>
+        <v>46111.43257133102</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>46064</v>
+        <v>46122</v>
       </c>
       <c r="L159" s="1" t="inlineStr">
         <is>
@@ -10427,44 +11239,49 @@
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N159" s="1" t="n"/>
       <c r="O159" s="1" t="n"/>
       <c r="P159" s="1" t="inlineStr"/>
       <c r="Q159" s="1" t="inlineStr"/>
+      <c r="R159" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>76701</v>
+        <v>78308</v>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>BLOCO "G" - CIAP	Cliente deu por encerrado o atendimento a notificação, porém não satisfeita com a informação de que a MG não teria como atender as informações necessárias para correta geração do arquivo. Cliente não irá contratar suporte, pois encontra-se em regime de economia de guerra e não irá dispender para regularização do referido arquivo.VENDA DE SERVIÇO	Considerando o incentivo fiscal de vendas obtido em Minas Gerais, onde pagam algo em torno de 3,5% de ICMS, comparado com ISS que seria 5%, cliente prefere a opção de venda à dividir 70% vendas 30% serviços. Porém, para a linha de postes irá estudar junto ao comercial se conseguiriam adotar tal políticaRESULTADO A PARTIR DE 2026	Considerar abrir nova conta em grupo de lucros suspensos, conta de "Resultado após 2026" para que fique identificado que quando forem sacar destas reservas elas serão tributadas dentro das regras estabelecidas.CADASTRO PRODUTOS	Cliente solicita confirmação se os novos impostos IBS/CBS foram devidamente informados no cadastro de produtos, pois eles não receberam retorno depois que a MG solicitou o referido cadastro.D&amp;TFECHAMENTO 12/2025	Apresentar fechamento 12/2025 para arquivos do cliente.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>4219</v>
+        <v>3954</v>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>REPUME REPUXAÇÃO E METALÚRGICA LTDA</t>
+          <t>Cristaleria Bruxelas Indústria e Comércio Eireli</t>
         </is>
       </c>
       <c r="H160" s="1" t="inlineStr">
@@ -10478,10 +11295,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46041.67975239583</v>
+        <v>46111.43023637732</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>46042</v>
+        <v>46122</v>
       </c>
       <c r="L160" s="1" t="inlineStr">
         <is>
@@ -10490,17 +11307,22 @@
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N160" s="1" t="n"/>
       <c r="O160" s="1" t="n"/>
       <c r="P160" s="1" t="inlineStr"/>
       <c r="Q160" s="1" t="inlineStr"/>
+      <c r="R160" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>76488</v>
+        <v>77000</v>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
@@ -10509,7 +11331,7 @@
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
@@ -10519,15 +11341,15 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>LUCRO PRESUMIDO 2025/2026	Considerando evolução do faturamento da empresa, para o ano de 2026 esta será enquadrada no lucro presumido, cuja avaliação foi analisada junto ao cliente nesta data (aumento de carga tributária)</t>
+          <t>DESTDA	Houve e-mail de nossa colaboradora sobre DESTDA informada equivocadamente e que gerou cobrança desnecessária, por isso cliente neste mesmo e-mail (09/12), cobra o valor da diferença de juros e a restituição do valor pago a maior.</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>4521</v>
+        <v>4003</v>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>GODOI ESQUADRIAS LTDA</t>
+          <t>NUTRI- QUEEN COMÉRCIO VAREJISTA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
@@ -10541,10 +11363,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46030.48313483796</v>
+        <v>46057.50836859953</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>46037</v>
+        <v>46064</v>
       </c>
       <c r="L161" s="1" t="inlineStr">
         <is>
@@ -10560,42 +11382,47 @@
       <c r="O161" s="1" t="n"/>
       <c r="P161" s="1" t="inlineStr"/>
       <c r="Q161" s="1" t="inlineStr"/>
+      <c r="R161" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>78283</v>
+        <v>76701</v>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido; Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais. ? Observações importantes:A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização).Em anexo a planilha modelo que deverá ser preenchida. </t>
+          <t>BLOCO "G" - CIAP	Cliente deu por encerrado o atendimento a notificação, porém não satisfeita com a informação de que a MG não teria como atender as informações necessárias para correta geração do arquivo. Cliente não irá contratar suporte, pois encontra-se em regime de economia de guerra e não irá dispender para regularização do referido arquivo.VENDA DE SERVIÇO	Considerando o incentivo fiscal de vendas obtido em Minas Gerais, onde pagam algo em torno de 3,5% de ICMS, comparado com ISS que seria 5%, cliente prefere a opção de venda à dividir 70% vendas 30% serviços. Porém, para a linha de postes irá estudar junto ao comercial se conseguiriam adotar tal políticaRESULTADO A PARTIR DE 2026	Considerar abrir nova conta em grupo de lucros suspensos, conta de "Resultado após 2026" para que fique identificado que quando forem sacar destas reservas elas serão tributadas dentro das regras estabelecidas.CADASTRO PRODUTOS	Cliente solicita confirmação se os novos impostos IBS/CBS foram devidamente informados no cadastro de produtos, pois eles não receberam retorno depois que a MG solicitou o referido cadastro.D&amp;TFECHAMENTO 12/2025	Apresentar fechamento 12/2025 para arquivos do cliente.</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>4599</v>
+        <v>4219</v>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>AERODUTO EQUIPAMENTOS INDUSTRIAIS LTDA</t>
+          <t>REPUME REPUXAÇÃO E METALÚRGICA LTDA</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I162" s="1" t="inlineStr">
@@ -10604,10 +11431,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46111.40819378472</v>
+        <v>46041.67975239583</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>46122</v>
+        <v>46042</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
@@ -10616,49 +11443,54 @@
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N162" s="1" t="n"/>
       <c r="O162" s="1" t="n"/>
       <c r="P162" s="1" t="inlineStr"/>
       <c r="Q162" s="1" t="inlineStr"/>
+      <c r="R162" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>78323</v>
+        <v>76488</v>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>LUCRO PRESUMIDO 2025/2026	Considerando evolução do faturamento da empresa, para o ano de 2026 esta será enquadrada no lucro presumido, cuja avaliação foi analisada junto ao cliente nesta data (aumento de carga tributária)</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>4962</v>
+        <v>4521</v>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>TRONICS DO BRASIL INDUSTRIA DE EQUIPAMENTOS LTDA</t>
+          <t>GODOI ESQUADRIAS LTDA</t>
         </is>
       </c>
       <c r="H163" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I163" s="1" t="inlineStr">
@@ -10667,10 +11499,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46111.44858903936</v>
+        <v>46030.48313483796</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>46122</v>
+        <v>46037</v>
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
@@ -10679,49 +11511,54 @@
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N163" s="1" t="n"/>
       <c r="O163" s="1" t="n"/>
       <c r="P163" s="1" t="inlineStr"/>
       <c r="Q163" s="1" t="inlineStr"/>
+      <c r="R163" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>76817</v>
+        <v>78283</v>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>NF descarte	O cliente não conseguiu emitir nota fiscal de descarte e informou haver problema na inscrição estadual para emissão dessas notas. Solicito verificação e orientação.</t>
+          <t xml:space="preserve">O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido; Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais. ? Observações importantes:A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização).Em anexo a planilha modelo que deverá ser preenchida. </t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>5026</v>
+        <v>4599</v>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
+          <t>AERODUTO EQUIPAMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
       <c r="H164" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I164" s="1" t="inlineStr">
@@ -10730,10 +11567,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46048.50034903935</v>
+        <v>46111.40819378472</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>46055</v>
+        <v>46122</v>
       </c>
       <c r="L164" s="1" t="inlineStr">
         <is>
@@ -10742,17 +11579,22 @@
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N164" s="1" t="n"/>
       <c r="O164" s="1" t="n"/>
       <c r="P164" s="1" t="inlineStr"/>
       <c r="Q164" s="1" t="inlineStr"/>
+      <c r="R164" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>78320</v>
+        <v>78323</v>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
@@ -10775,16 +11617,16 @@
         </is>
       </c>
       <c r="F165" s="1" t="n">
-        <v>5053</v>
+        <v>4962</v>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
+          <t>TRONICS DO BRASIL INDUSTRIA DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H165" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I165" s="1" t="inlineStr">
@@ -10793,7 +11635,7 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46111.4448534375</v>
+        <v>46111.44858903936</v>
       </c>
       <c r="K165" s="2" t="n">
         <v>46122</v>
@@ -10812,10 +11654,15 @@
       <c r="O165" s="1" t="n"/>
       <c r="P165" s="1" t="inlineStr"/>
       <c r="Q165" s="1" t="inlineStr"/>
+      <c r="R165" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>77005</v>
+        <v>76817</v>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
@@ -10834,15 +11681,15 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>CRÉDITOS ICMS ST	Considerando equívoco por parte do cliente a CABEXPRESS em nbão destacar em nota fiscal os valores do ICMS ST recolhidos e que na devolução de mercadoria deveriam ser considerados, apurar junto ao fiscal e apresentar ao cliente a tomada de crédito mesmo que extemporânea confirmando assim junto ao cliente os créditos correspondente. Clientes: COMDUSCAMP e PJ, não só a ST mas o da operação própria, nos parec e que não esta devidamente creditado.APURAÇÃO FISCAL	Cliente na pessoa do consultor Reginaldo, não encontra na contabilidade os valores correspondentes a débitos e créditos de impostos e por isso solicita-se revisão da contabilização do ano de 2025, pois o mesmo avaliou desde janeiro e já neste primeiro mês há divergências.LUCRATIVIDADE	Para que se obtenha lucratividade no 4º trimestre de forma que no ano tenha-se um pequeno lucro, definido a partir de um lucro anual de algo em torno de R$ 30 mil, considerar talves reclassificar despesas como Manutenção e conservação, Manutencção de máquinas e equipamentos em imobilizado, opção esta a ser avaliada após apresentação dos saldos de estoque que reflitam os saldos com a devolução ocorrida nos meses de Jul, Ago, e Set, principalmente.ESTOQUES	Cliente reavaliando apuração de estoques a custo de absorção, opção adotada em 2026, que após volume expressivo de devolução pode estar apresentando diferença não ocorrida.RECLASSIFICAÇÕES	"ESTAS CONFIRMAÇÕES E/OU RECLASSIFICAÇÕES DE 30/12/2025 NÃO NÃO FORAM ATENDIDAS NESTE FECHAMENTO: Confirmar classificações contábeis, cuja reclassificação se torna necessária, a saber:1) VALE TRANSPORTE, em grupo de MOD e GGF, este deve permanecer em grupo de MOD.2) ASSISTÊNCIA MÉDICA, em grupo de MOD, avaliar mês 11/2025, contabilização indica duplicidade.3) ALUGUEL em grupo de GGF, apresenta valor elevado, segundo cliente não houve reajuste, porque o valor aumentou quase 50%.4) VALE TRANSPORTE 11/25, em grupo de despesas trabalhistas, não havia lançamentos anteriores, estaria correta a classificação?5) ASSISTÊNCIA MÉDICA , em grupo despesas trabalhistas no mês 10/2025, valor elevado. Confirme.6) JUROS E MULTAS SOBRE IMPOSTOS, ausência de registro, pagamentos de impostos atrasados são pagos mensalmente. Onde estariam os juros e multas?7) JUROS SOBRE EMPRÉSTIMOS, ausência de registro, pagamentos são realizados mensalmente.8) JUROS RISCO SACADO FORNECEDORES 10/2025, ausência é isso mesmo?"</t>
+          <t>NF descarte	O cliente não conseguiu emitir nota fiscal de descarte e informou haver problema na inscrição estadual para emissão dessas notas. Solicito verificação e orientação.</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
-        <v>5132</v>
+        <v>5026</v>
       </c>
       <c r="G166" s="1" t="inlineStr">
         <is>
-          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
+          <t>DUO CENOGRAFIA E ESTANDES LTDA</t>
         </is>
       </c>
       <c r="H166" s="1" t="inlineStr">
@@ -10856,10 +11703,10 @@
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46057.51525987269</v>
+        <v>46048.50034903935</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>46064</v>
+        <v>46055</v>
       </c>
       <c r="L166" s="1" t="inlineStr">
         <is>
@@ -10875,10 +11722,15 @@
       <c r="O166" s="1" t="n"/>
       <c r="P166" s="1" t="inlineStr"/>
       <c r="Q166" s="1" t="inlineStr"/>
+      <c r="R166" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>78294</v>
+        <v>78320</v>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
@@ -10901,16 +11753,16 @@
         </is>
       </c>
       <c r="F167" s="1" t="n">
-        <v>5370</v>
+        <v>5053</v>
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
+          <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H167" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I167" s="1" t="inlineStr">
@@ -10919,7 +11771,7 @@
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46111.41717407407</v>
+        <v>46111.4448534375</v>
       </c>
       <c r="K167" s="2" t="n">
         <v>46122</v>
@@ -10938,37 +11790,42 @@
       <c r="O167" s="1" t="n"/>
       <c r="P167" s="1" t="inlineStr"/>
       <c r="Q167" s="1" t="inlineStr"/>
+      <c r="R167" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>78316</v>
+        <v>77005</v>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>CRÉDITOS ICMS ST	Considerando equívoco por parte do cliente a CABEXPRESS em nbão destacar em nota fiscal os valores do ICMS ST recolhidos e que na devolução de mercadoria deveriam ser considerados, apurar junto ao fiscal e apresentar ao cliente a tomada de crédito mesmo que extemporânea confirmando assim junto ao cliente os créditos correspondente. Clientes: COMDUSCAMP e PJ, não só a ST mas o da operação própria, nos parec e que não esta devidamente creditado.APURAÇÃO FISCAL	Cliente na pessoa do consultor Reginaldo, não encontra na contabilidade os valores correspondentes a débitos e créditos de impostos e por isso solicita-se revisão da contabilização do ano de 2025, pois o mesmo avaliou desde janeiro e já neste primeiro mês há divergências.LUCRATIVIDADE	Para que se obtenha lucratividade no 4º trimestre de forma que no ano tenha-se um pequeno lucro, definido a partir de um lucro anual de algo em torno de R$ 30 mil, considerar talves reclassificar despesas como Manutenção e conservação, Manutencção de máquinas e equipamentos em imobilizado, opção esta a ser avaliada após apresentação dos saldos de estoque que reflitam os saldos com a devolução ocorrida nos meses de Jul, Ago, e Set, principalmente.ESTOQUES	Cliente reavaliando apuração de estoques a custo de absorção, opção adotada em 2026, que após volume expressivo de devolução pode estar apresentando diferença não ocorrida.RECLASSIFICAÇÕES	"ESTAS CONFIRMAÇÕES E/OU RECLASSIFICAÇÕES DE 30/12/2025 NÃO NÃO FORAM ATENDIDAS NESTE FECHAMENTO: Confirmar classificações contábeis, cuja reclassificação se torna necessária, a saber:1) VALE TRANSPORTE, em grupo de MOD e GGF, este deve permanecer em grupo de MOD.2) ASSISTÊNCIA MÉDICA, em grupo de MOD, avaliar mês 11/2025, contabilização indica duplicidade.3) ALUGUEL em grupo de GGF, apresenta valor elevado, segundo cliente não houve reajuste, porque o valor aumentou quase 50%.4) VALE TRANSPORTE 11/25, em grupo de despesas trabalhistas, não havia lançamentos anteriores, estaria correta a classificação?5) ASSISTÊNCIA MÉDICA , em grupo despesas trabalhistas no mês 10/2025, valor elevado. Confirme.6) JUROS E MULTAS SOBRE IMPOSTOS, ausência de registro, pagamentos de impostos atrasados são pagos mensalmente. Onde estariam os juros e multas?7) JUROS SOBRE EMPRÉSTIMOS, ausência de registro, pagamentos são realizados mensalmente.8) JUROS RISCO SACADO FORNECEDORES 10/2025, ausência é isso mesmo?"</t>
         </is>
       </c>
       <c r="F168" s="1" t="n">
-        <v>5371</v>
+        <v>5132</v>
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t>METALBRAS INDUSTRIA E COMERCIO DE METAIS LTDA</t>
+          <t>CABEXPRESS INDUSTRIA E COMÉRCIO DE CABOS ELÉTRICOS LTDA</t>
         </is>
       </c>
       <c r="H168" s="1" t="inlineStr">
@@ -10982,10 +11839,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46111.44022480324</v>
+        <v>46057.51525987269</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>46122</v>
+        <v>46064</v>
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
@@ -10994,17 +11851,22 @@
       </c>
       <c r="M168" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N168" s="1" t="n"/>
       <c r="O168" s="1" t="n"/>
       <c r="P168" s="1" t="inlineStr"/>
       <c r="Q168" s="1" t="inlineStr"/>
+      <c r="R168" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>78314</v>
+        <v>78294</v>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
@@ -11027,16 +11889,16 @@
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>5427</v>
+        <v>5370</v>
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t>LEANDRO SEBASTIAO SIQUEIRA LTDA</t>
+          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="H169" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I169" s="1" t="inlineStr">
@@ -11045,7 +11907,7 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46111.43827118055</v>
+        <v>46111.41717407407</v>
       </c>
       <c r="K169" s="2" t="n">
         <v>46122</v>
@@ -11064,10 +11926,15 @@
       <c r="O169" s="1" t="n"/>
       <c r="P169" s="1" t="inlineStr"/>
       <c r="Q169" s="1" t="inlineStr"/>
+      <c r="R169" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>78312</v>
+        <v>78316</v>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
@@ -11090,16 +11957,16 @@
         </is>
       </c>
       <c r="F170" s="1" t="n">
-        <v>5600</v>
+        <v>5371</v>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t>INTERMETRIC INSTRUMENTOS LTDA</t>
+          <t>METALBRAS INDUSTRIA E COMERCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="H170" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I170" s="1" t="inlineStr">
@@ -11108,7 +11975,7 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46111.43577152778</v>
+        <v>46111.44022480324</v>
       </c>
       <c r="K170" s="2" t="n">
         <v>46122</v>
@@ -11127,10 +11994,15 @@
       <c r="O170" s="1" t="n"/>
       <c r="P170" s="1" t="inlineStr"/>
       <c r="Q170" s="1" t="inlineStr"/>
+      <c r="R170" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>78305</v>
+        <v>78314</v>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
@@ -11153,11 +12025,11 @@
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>5744</v>
+        <v>5427</v>
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
+          <t>LEANDRO SEBASTIAO SIQUEIRA LTDA</t>
         </is>
       </c>
       <c r="H171" s="1" t="inlineStr">
@@ -11171,7 +12043,7 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46111.42608159722</v>
+        <v>46111.43827118055</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>46122</v>
@@ -11190,10 +12062,15 @@
       <c r="O171" s="1" t="n"/>
       <c r="P171" s="1" t="inlineStr"/>
       <c r="Q171" s="1" t="inlineStr"/>
+      <c r="R171" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>78318</v>
+        <v>78312</v>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
@@ -11216,11 +12093,11 @@
         </is>
       </c>
       <c r="F172" s="1" t="n">
-        <v>5801</v>
+        <v>5600</v>
       </c>
       <c r="G172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
+          <t>INTERMETRIC INSTRUMENTOS LTDA</t>
         </is>
       </c>
       <c r="H172" s="1" t="inlineStr">
@@ -11234,7 +12111,7 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46111.44276319444</v>
+        <v>46111.43577152778</v>
       </c>
       <c r="K172" s="2" t="n">
         <v>46122</v>
@@ -11253,10 +12130,15 @@
       <c r="O172" s="1" t="n"/>
       <c r="P172" s="1" t="inlineStr"/>
       <c r="Q172" s="1" t="inlineStr"/>
+      <c r="R172" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>78311</v>
+        <v>78305</v>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
@@ -11279,11 +12161,11 @@
         </is>
       </c>
       <c r="F173" s="1" t="n">
-        <v>5803</v>
+        <v>5744</v>
       </c>
       <c r="G173" s="1" t="inlineStr">
         <is>
-          <t>Ink Flex Industria Grafica LTDA</t>
+          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H173" s="1" t="inlineStr">
@@ -11297,7 +12179,7 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46111.43436825232</v>
+        <v>46111.42608159722</v>
       </c>
       <c r="K173" s="2" t="n">
         <v>46122</v>
@@ -11316,10 +12198,15 @@
       <c r="O173" s="1" t="n"/>
       <c r="P173" s="1" t="inlineStr"/>
       <c r="Q173" s="1" t="inlineStr"/>
+      <c r="R173" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>78307</v>
+        <v>78318</v>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
@@ -11342,16 +12229,16 @@
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>5834</v>
+        <v>5801</v>
       </c>
       <c r="G174" s="1" t="inlineStr">
         <is>
-          <t>Caete Comunicacao Visual LTDA</t>
+          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
         </is>
       </c>
       <c r="H174" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I174" s="1" t="inlineStr">
@@ -11360,7 +12247,7 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46111.42888533565</v>
+        <v>46111.44276319444</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>46122</v>
@@ -11379,10 +12266,15 @@
       <c r="O174" s="1" t="n"/>
       <c r="P174" s="1" t="inlineStr"/>
       <c r="Q174" s="1" t="inlineStr"/>
+      <c r="R174" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>78315</v>
+        <v>78311</v>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
@@ -11405,16 +12297,16 @@
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>5995</v>
+        <v>5803</v>
       </c>
       <c r="G175" s="1" t="inlineStr">
         <is>
-          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
+          <t>Ink Flex Industria Grafica LTDA</t>
         </is>
       </c>
       <c r="H175" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I175" s="1" t="inlineStr">
@@ -11423,7 +12315,7 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46111.4391908912</v>
+        <v>46111.43436825232</v>
       </c>
       <c r="K175" s="2" t="n">
         <v>46122</v>
@@ -11442,10 +12334,15 @@
       <c r="O175" s="1" t="n"/>
       <c r="P175" s="1" t="inlineStr"/>
       <c r="Q175" s="1" t="inlineStr"/>
+      <c r="R175" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>76800</v>
+        <v>78307</v>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
@@ -11459,25 +12356,25 @@
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Gostaria de relatar uma situação que vem ocorrendo há algum tempo e que merece atenção.A Sra. Noemia tem entrado em contato telefônico com a colaboradora Natalia de forma inadequada, utilizando tom exaltado e, por vezes, gritando, além de afirmar que a MG “nunca faz nada certo”. Esse comportamento tem sido recorrente e não ocorria anteriormente, quando a Claudilene era responsável pelo DP da empresa.Na data mais recente, em razão de um erro interno da Litocomp relacionado ao convênio médico (conforme e-mail anexo), a Sra. Noemia novamente se dirigiu à Natalia de maneira extremamente grosseira e desrespeitosa por telefone, apesar de a falha não ter sido ocasionada pela MG.Diante disso, solicito apoio para que essa situação seja tratada, pois a Natalia não está sendo tratada de forma adequada em seus atendimentos telefônicos, o que tem causado desconforto e prejuízo ao ambiente de trabalho.Gostaria de relatar outra situação que também vem impactando o andamento dos processos.Refere-se à planilha de importação das informações utilizada para o cálculo da folha de pagamento. A Sra. Noemia tem se negado a utilizar essa planilha, sendo importante ressaltar que essa recusa ocorre exclusivamente com ela. Quando a Claudilene atuava na Litocomp, a mesma planilha era utilizada normalmente, sem qualquer impedimento ou questionamento.Essa postura tem gerado dificuldades operacionais e retrabalho, considerando que a planilha foi desenvolvida justamente para padronizar e otimizar o processo de cálculo da folha.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>5995</v>
+        <v>5834</v>
       </c>
       <c r="G176" s="1" t="inlineStr">
         <is>
-          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
+          <t>Caete Comunicacao Visual LTDA</t>
         </is>
       </c>
       <c r="H176" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I176" s="1" t="inlineStr">
@@ -11486,10 +12383,10 @@
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46048.38019675926</v>
+        <v>46111.42888533565</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>46049</v>
+        <v>46122</v>
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
@@ -11498,17 +12395,22 @@
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N176" s="1" t="n"/>
       <c r="O176" s="1" t="n"/>
       <c r="P176" s="1" t="inlineStr"/>
       <c r="Q176" s="1" t="inlineStr"/>
+      <c r="R176" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>78301</v>
+        <v>78315</v>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
@@ -11531,16 +12433,16 @@
         </is>
       </c>
       <c r="F177" s="1" t="n">
-        <v>6016</v>
+        <v>5995</v>
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
+          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="H177" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I177" s="1" t="inlineStr">
@@ -11549,7 +12451,7 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>46111.42218321759</v>
+        <v>46111.4391908912</v>
       </c>
       <c r="K177" s="2" t="n">
         <v>46122</v>
@@ -11568,10 +12470,15 @@
       <c r="O177" s="1" t="n"/>
       <c r="P177" s="1" t="inlineStr"/>
       <c r="Q177" s="1" t="inlineStr"/>
+      <c r="R177" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>78321</v>
+        <v>76800</v>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
@@ -11585,25 +12492,25 @@
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Bom dia!Gostaria de relatar uma situação que vem ocorrendo há algum tempo e que merece atenção.A Sra. Noemia tem entrado em contato telefônico com a colaboradora Natalia de forma inadequada, utilizando tom exaltado e, por vezes, gritando, além de afirmar que a MG “nunca faz nada certo”. Esse comportamento tem sido recorrente e não ocorria anteriormente, quando a Claudilene era responsável pelo DP da empresa.Na data mais recente, em razão de um erro interno da Litocomp relacionado ao convênio médico (conforme e-mail anexo), a Sra. Noemia novamente se dirigiu à Natalia de maneira extremamente grosseira e desrespeitosa por telefone, apesar de a falha não ter sido ocasionada pela MG.Diante disso, solicito apoio para que essa situação seja tratada, pois a Natalia não está sendo tratada de forma adequada em seus atendimentos telefônicos, o que tem causado desconforto e prejuízo ao ambiente de trabalho.Gostaria de relatar outra situação que também vem impactando o andamento dos processos.Refere-se à planilha de importação das informações utilizada para o cálculo da folha de pagamento. A Sra. Noemia tem se negado a utilizar essa planilha, sendo importante ressaltar que essa recusa ocorre exclusivamente com ela. Quando a Claudilene atuava na Litocomp, a mesma planilha era utilizada normalmente, sem qualquer impedimento ou questionamento.Essa postura tem gerado dificuldades operacionais e retrabalho, considerando que a planilha foi desenvolvida justamente para padronizar e otimizar o processo de cálculo da folha.</t>
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>6088</v>
+        <v>5995</v>
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
+          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="H178" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I178" s="1" t="inlineStr">
@@ -11612,52 +12519,61 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>46111.44696084491</v>
+        <v>46048.38019675926</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>46122</v>
+        <v>46049</v>
       </c>
       <c r="L178" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M178" s="1" t="inlineStr"/>
+      <c r="M178" s="1" t="inlineStr">
+        <is>
+          <t>Edivaldo Veiga</t>
+        </is>
+      </c>
       <c r="N178" s="1" t="n"/>
       <c r="O178" s="1" t="n"/>
       <c r="P178" s="1" t="inlineStr"/>
       <c r="Q178" s="1" t="inlineStr"/>
+      <c r="R178" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>76992</v>
+        <v>78301</v>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t>ESTQOUE / CLIENTES / FORNECEDORES	Cliente na pessoa do Michel apresentará para fechamento do ano relatório de CLIENTES, FORNECEDORES E ESTOQUE para contabilização. Por isso, acompanhar.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F179" s="1" t="n">
-        <v>6088</v>
+        <v>6016</v>
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
+          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
         </is>
       </c>
       <c r="H179" s="1" t="inlineStr">
@@ -11671,10 +12587,10 @@
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>46057.5020125</v>
+        <v>46111.42218321759</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>46064</v>
+        <v>46122</v>
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
@@ -11683,17 +12599,22 @@
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N179" s="1" t="n"/>
       <c r="O179" s="1" t="n"/>
       <c r="P179" s="1" t="inlineStr"/>
       <c r="Q179" s="1" t="inlineStr"/>
+      <c r="R179" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>78798</v>
+        <v>78321</v>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
@@ -11712,20 +12633,20 @@
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F180" s="1" t="n">
-        <v>6106</v>
+        <v>6088</v>
       </c>
       <c r="G180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
+          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
         </is>
       </c>
       <c r="H180" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I180" s="1" t="inlineStr">
@@ -11734,61 +12655,62 @@
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>46128.70572581018</v>
+        <v>46111.44696084491</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="L180" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M180" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+      <c r="M180" s="1" t="inlineStr"/>
       <c r="N180" s="1" t="n"/>
       <c r="O180" s="1" t="n"/>
       <c r="P180" s="1" t="inlineStr"/>
       <c r="Q180" s="1" t="inlineStr"/>
+      <c r="R180" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>78325</v>
+        <v>76992</v>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>ESTQOUE / CLIENTES / FORNECEDORES	Cliente na pessoa do Michel apresentará para fechamento do ano relatório de CLIENTES, FORNECEDORES E ESTOQUE para contabilização. Por isso, acompanhar.</t>
         </is>
       </c>
       <c r="F181" s="1" t="n">
-        <v>6148</v>
+        <v>6088</v>
       </c>
       <c r="G181" s="1" t="inlineStr">
         <is>
-          <t>VALE CONCRETO LTDA</t>
+          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
         </is>
       </c>
       <c r="H181" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I181" s="1" t="inlineStr">
@@ -11797,10 +12719,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>46111.45013549768</v>
+        <v>46057.5020125</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>46122</v>
+        <v>46064</v>
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
@@ -11809,49 +12731,54 @@
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N181" s="1" t="n"/>
       <c r="O181" s="1" t="n"/>
       <c r="P181" s="1" t="inlineStr"/>
       <c r="Q181" s="1" t="inlineStr"/>
+      <c r="R181" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>76461</v>
+        <v>78798</v>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUIÇÃO DE LUCROS	Providenciar distribuição de lucros da empresa para a investidora DANESES, efetivando págamento com saldo da conta de empréstimos a receber.DISTRIBUIÇÃO DE LUCROS	Avaliar saldo de reservas e possível emissão de ata de distribuição de lucros.EQUIVALÊNCIA PATRIMONIAL	Conforme quadro societário providenciar equivalência patrimonial em 30/9/2025.ADTO FORNECEDORES / ADTO CLIENTES	Avaliar saldo das contas de adiantamentos, pois a Daneses é uma Holding Operacional, investidora.RECEBIMENTO DISTRIBUIÇÃO LUCROS INVESTIDA	Considerar contabilizar distribuição de lucros recebida da DRAKKAR, contra a conta de empréstimos a receber (valor que esta pendente a pagar na B HOVE)</t>
+          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
         </is>
       </c>
       <c r="F182" s="1" t="n">
-        <v>6254</v>
+        <v>6106</v>
       </c>
       <c r="G182" s="1" t="inlineStr">
         <is>
-          <t>DANESES HOLDING DE PARTICIPACOES LTDA</t>
+          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
       <c r="H182" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I182" s="1" t="inlineStr">
@@ -11860,10 +12787,10 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>46029.70892152778</v>
+        <v>46128.70572581018</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>46036</v>
+        <v>46132</v>
       </c>
       <c r="L182" s="1" t="inlineStr">
         <is>
@@ -11872,17 +12799,22 @@
       </c>
       <c r="M182" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N182" s="1" t="n"/>
       <c r="O182" s="1" t="n"/>
       <c r="P182" s="1" t="inlineStr"/>
       <c r="Q182" s="1" t="inlineStr"/>
+      <c r="R182" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>78324</v>
+        <v>78325</v>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
@@ -11905,16 +12837,16 @@
         </is>
       </c>
       <c r="F183" s="1" t="n">
-        <v>6261</v>
+        <v>6148</v>
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
+          <t>VALE CONCRETO LTDA</t>
         </is>
       </c>
       <c r="H183" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I183" s="1" t="inlineStr">
@@ -11923,7 +12855,7 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>46111.44946597222</v>
+        <v>46111.45013549768</v>
       </c>
       <c r="K183" s="2" t="n">
         <v>46122</v>
@@ -11942,10 +12874,15 @@
       <c r="O183" s="1" t="n"/>
       <c r="P183" s="1" t="inlineStr"/>
       <c r="Q183" s="1" t="inlineStr"/>
+      <c r="R183" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>76816</v>
+        <v>76461</v>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
@@ -11954,7 +12891,7 @@
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -11964,15 +12901,15 @@
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t>CRÉDITOS PERDCOMP	Tendo em vista aviso de créditos de PERDCOMP cliente solicita possível esclarecimento ou seja levantamento junto a RFB do que se refere os PERDCOMPs informados no aviso de crédito. A relação com contador anterior está extremecida justamente por pagamentos que eram realizados e que não deveriam e que supostamente teriam sido solicitados e reembolso.</t>
+          <t>DISTRIBUIÇÃO DE LUCROS	Providenciar distribuição de lucros da empresa para a investidora DANESES, efetivando págamento com saldo da conta de empréstimos a receber.DISTRIBUIÇÃO DE LUCROS	Avaliar saldo de reservas e possível emissão de ata de distribuição de lucros.EQUIVALÊNCIA PATRIMONIAL	Conforme quadro societário providenciar equivalência patrimonial em 30/9/2025.ADTO FORNECEDORES / ADTO CLIENTES	Avaliar saldo das contas de adiantamentos, pois a Daneses é uma Holding Operacional, investidora.RECEBIMENTO DISTRIBUIÇÃO LUCROS INVESTIDA	Considerar contabilizar distribuição de lucros recebida da DRAKKAR, contra a conta de empréstimos a receber (valor que esta pendente a pagar na B HOVE)</t>
         </is>
       </c>
       <c r="F184" s="1" t="n">
-        <v>6265</v>
+        <v>6254</v>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t>B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (MATRIZ)</t>
+          <t>DANESES HOLDING DE PARTICIPACOES LTDA</t>
         </is>
       </c>
       <c r="H184" s="1" t="inlineStr">
@@ -11986,10 +12923,10 @@
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46048.49620679399</v>
+        <v>46029.70892152778</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>46055</v>
+        <v>46036</v>
       </c>
       <c r="L184" s="1" t="inlineStr">
         <is>
@@ -12005,42 +12942,47 @@
       <c r="O184" s="1" t="n"/>
       <c r="P184" s="1" t="inlineStr"/>
       <c r="Q184" s="1" t="inlineStr"/>
+      <c r="R184" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>77538</v>
+        <v>78324</v>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t>CAT 42:Favor fazer simulação na apuração mensal, cliente tem interesse - Cobrança recorrente</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>6272</v>
+        <v>6261</v>
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
+          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
         </is>
       </c>
       <c r="H185" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I185" s="1" t="inlineStr">
@@ -12049,10 +12991,10 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>46079.62666554398</v>
+        <v>46111.44946597222</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>46086</v>
+        <v>46122</v>
       </c>
       <c r="L185" s="1" t="inlineStr">
         <is>
@@ -12061,49 +13003,54 @@
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N185" s="1" t="n"/>
       <c r="O185" s="1" t="n"/>
       <c r="P185" s="1" t="inlineStr"/>
       <c r="Q185" s="1" t="inlineStr"/>
+      <c r="R185" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>78317</v>
+        <v>76816</v>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>CRÉDITOS PERDCOMP	Tendo em vista aviso de créditos de PERDCOMP cliente solicita possível esclarecimento ou seja levantamento junto a RFB do que se refere os PERDCOMPs informados no aviso de crédito. A relação com contador anterior está extremecida justamente por pagamentos que eram realizados e que não deveriam e que supostamente teriam sido solicitados e reembolso.</t>
         </is>
       </c>
       <c r="F186" s="1" t="n">
-        <v>6288</v>
+        <v>6265</v>
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
+          <t>B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H186" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I186" s="1" t="inlineStr">
@@ -12112,10 +13059,10 @@
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>46111.44151450232</v>
+        <v>46048.49620679399</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>46122</v>
+        <v>46055</v>
       </c>
       <c r="L186" s="1" t="inlineStr">
         <is>
@@ -12124,49 +13071,54 @@
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N186" s="1" t="n"/>
       <c r="O186" s="1" t="n"/>
       <c r="P186" s="1" t="inlineStr"/>
       <c r="Q186" s="1" t="inlineStr"/>
+      <c r="R186" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>78289</v>
+        <v>77538</v>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>CAT 42:Favor fazer simulação na apuração mensal, cliente tem interesse - Cobrança recorrente</t>
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>6289</v>
+        <v>6272</v>
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
+          <t>REDFLEX 90 DO BRASIL COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H187" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I187" s="1" t="inlineStr">
@@ -12175,10 +13127,10 @@
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>46111.41423260417</v>
+        <v>46079.62666554398</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>46122</v>
+        <v>46086</v>
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
@@ -12187,49 +13139,54 @@
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N187" s="1" t="n"/>
       <c r="O187" s="1" t="n"/>
       <c r="P187" s="1" t="inlineStr"/>
       <c r="Q187" s="1" t="inlineStr"/>
+      <c r="R187" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>76370</v>
+        <v>78317</v>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t>DIRF 2022	Consulta perante RFB apresenta pendência de entrega de DIRF 2022, por isso levantar junto a diretoria se há possibilidade de entregar em branco.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F188" s="1" t="n">
-        <v>6416</v>
+        <v>6288</v>
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO ENTERTAINMENT LTDA </t>
+          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H188" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I188" s="1" t="inlineStr">
@@ -12238,10 +13195,10 @@
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>46024.66316292824</v>
+        <v>46111.44151450232</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>46031</v>
+        <v>46122</v>
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
@@ -12250,49 +13207,54 @@
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N188" s="1" t="n"/>
       <c r="O188" s="1" t="n"/>
       <c r="P188" s="1" t="inlineStr"/>
       <c r="Q188" s="1" t="inlineStr"/>
+      <c r="R188" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>76469</v>
+        <v>78289</v>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t>Pendência ATA</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t>JCP	Considerar avaliar pagamento de JCP nos resultados do 3º e 4º trimestres de 2025.TAXA FUNCIONAMENTO	Apresentar ao cliente andamento do processo de obtenção da lincença de funcionamento da filial perante prefeitura de Belo Horizonte.CMV IMPORTAÇÃO	Analisar contabilização dos valores em conta de custos de importação mediante avaliação de processos de importação, poius importação do mês é de R$ 1.784 mil e os custos de importação em torno de R$ 800 mil.DRE	Em DRE considerar trazer para o grupo de custos as contas de comissão sobvre vendas, pois a análise de custo do importador tem impacto muito forte com estas despesas.CLIENTES PERDIDOS	Avaliar junto ao cliente saldo de contas de clientes, pois poderá haver valores passivos de baixa por perda e/ou RJ, economizando assim IRPJ/CSLL.ADTO FORNECEDORES	Verificar junto ao contábil classificação nesta conta, pois cliente informar que não adianta valores aos seus fornecedores.DOAÇÕES	Em conjunto com Cliente na pessoa do Erinaldo, avalição das despesas contabilizados em período de responsabilidade de contador anterior, pois no fechamento do ano tal despesas impacta na apuração do IRPJ/CSLL como indedutível.RAZÃO	Apresentar ao cliente razão das contas de despesas com: REEMBOLSO, PROPAGANDA E PUBLICIDADE, SERV ADMINISTRATIVOSATA DISTRIBUIÇÃO DE LUCROS	Avaliar contabilizxação de reservas com a finalidade de emitir ata de reunião dos sócios aprovando distribuição de lucros próximos 3 anos sem IR.CND	Manter cliente informado quando as CNDs, âmbitos: FEDERAL, ESTADUAL, MUNICIPAL e FGTS, pois clientes do mesmo solicitam constantemente tais referências.CONSULTAS NCM	Esclarecido ao cliente quanto a cobrança de consultas de ncms fora do estado onde a empresa esta constituída a saber: SP, MG e SC. Ficando possível consulta exporádica de um ou outro NCM.ICMS ST SOBRE VENDAS CONSIGNADAS	Avaliar junto ao dpto técnico, como seria a cobrança de ICMS ST em venda consignada.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F189" s="1" t="n">
-        <v>6460</v>
+        <v>6289</v>
       </c>
       <c r="G189" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
+          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
         </is>
       </c>
       <c r="H189" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I189" s="1" t="inlineStr">
@@ -12301,10 +13263,10 @@
         </is>
       </c>
       <c r="J189" s="2" t="n">
-        <v>46029.7300304051</v>
+        <v>46111.41423260417</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>46036</v>
+        <v>46122</v>
       </c>
       <c r="L189" s="1" t="inlineStr">
         <is>
@@ -12313,17 +13275,22 @@
       </c>
       <c r="M189" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N189" s="1" t="n"/>
       <c r="O189" s="1" t="n"/>
       <c r="P189" s="1" t="inlineStr"/>
       <c r="Q189" s="1" t="inlineStr"/>
+      <c r="R189" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>77001</v>
+        <v>76370</v>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
@@ -12342,15 +13309,15 @@
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t>SENHA CONTADOR MINAS GERAIS	Verificar junto a operação porque não se consegue entregar a obrigação de Minas Gerais com a senha do contador responsável, pois o contador anterior assim entregava, A Sócia Sra. Mônica esta com documentos vencidos e não conseguiria adquirir certificado digital para filial, algo nunca pedido anteriormente.ATA DISTRIBUIÇÃO LUCROS 12/2025	Preparar apuração de disponibilidade para confecção de nova ata.APURAÇÃO IMPOSTOS	Cliente reclama do envio dos impostos em cima da hora do pagamento, por exemplo, porque o PIS e COFINS não foi disponibilizado ainda?TRIBUTAÇÃO	Esclarecido ao cliente cobrança de impostos, tanto na Base de cálculo do lucro presumido, majorado em 10% cujo impacto na carga tributária trás aumento de 0,32% para comercialização e 0,60% nos serviços, bem como na Distribuição de lucros a partir de 2026, com tributação para valores acima de R$ 50.000,00</t>
+          <t>DIRF 2022	Consulta perante RFB apresenta pendência de entrega de DIRF 2022, por isso levantar junto a diretoria se há possibilidade de entregar em branco.</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>6460</v>
+        <v>6416</v>
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">SINZATO ENTERTAINMENT LTDA </t>
         </is>
       </c>
       <c r="H190" s="1" t="inlineStr">
@@ -12364,10 +13331,10 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>46057.51196813658</v>
+        <v>46024.66316292824</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>46064</v>
+        <v>46031</v>
       </c>
       <c r="L190" s="1" t="inlineStr">
         <is>
@@ -12383,10 +13350,15 @@
       <c r="O190" s="1" t="n"/>
       <c r="P190" s="1" t="inlineStr"/>
       <c r="Q190" s="1" t="inlineStr"/>
+      <c r="R190" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>76809</v>
+        <v>76469</v>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
@@ -12395,7 +13367,7 @@
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Pendência ATA</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -12405,15 +13377,15 @@
       </c>
       <c r="E191" s="1" t="inlineStr">
         <is>
-          <t>TRIBUTAÇÃO DOS CADASTRO PRODUTOS	CLIENTE SOLICITOU RETORNO SOBRE ANALISE DA TRIBUTAÇÃO DOS CADASTRO DOS PRODUTOS</t>
+          <t>JCP	Considerar avaliar pagamento de JCP nos resultados do 3º e 4º trimestres de 2025.TAXA FUNCIONAMENTO	Apresentar ao cliente andamento do processo de obtenção da lincença de funcionamento da filial perante prefeitura de Belo Horizonte.CMV IMPORTAÇÃO	Analisar contabilização dos valores em conta de custos de importação mediante avaliação de processos de importação, poius importação do mês é de R$ 1.784 mil e os custos de importação em torno de R$ 800 mil.DRE	Em DRE considerar trazer para o grupo de custos as contas de comissão sobvre vendas, pois a análise de custo do importador tem impacto muito forte com estas despesas.CLIENTES PERDIDOS	Avaliar junto ao cliente saldo de contas de clientes, pois poderá haver valores passivos de baixa por perda e/ou RJ, economizando assim IRPJ/CSLL.ADTO FORNECEDORES	Verificar junto ao contábil classificação nesta conta, pois cliente informar que não adianta valores aos seus fornecedores.DOAÇÕES	Em conjunto com Cliente na pessoa do Erinaldo, avalição das despesas contabilizados em período de responsabilidade de contador anterior, pois no fechamento do ano tal despesas impacta na apuração do IRPJ/CSLL como indedutível.RAZÃO	Apresentar ao cliente razão das contas de despesas com: REEMBOLSO, PROPAGANDA E PUBLICIDADE, SERV ADMINISTRATIVOSATA DISTRIBUIÇÃO DE LUCROS	Avaliar contabilizxação de reservas com a finalidade de emitir ata de reunião dos sócios aprovando distribuição de lucros próximos 3 anos sem IR.CND	Manter cliente informado quando as CNDs, âmbitos: FEDERAL, ESTADUAL, MUNICIPAL e FGTS, pois clientes do mesmo solicitam constantemente tais referências.CONSULTAS NCM	Esclarecido ao cliente quanto a cobrança de consultas de ncms fora do estado onde a empresa esta constituída a saber: SP, MG e SC. Ficando possível consulta exporádica de um ou outro NCM.ICMS ST SOBRE VENDAS CONSIGNADAS	Avaliar junto ao dpto técnico, como seria a cobrança de ICMS ST em venda consignada.</t>
         </is>
       </c>
       <c r="F191" s="1" t="n">
-        <v>6507</v>
+        <v>6460</v>
       </c>
       <c r="G191" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H191" s="1" t="inlineStr">
@@ -12427,10 +13399,10 @@
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>46048.47468460648</v>
+        <v>46029.7300304051</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>46055</v>
+        <v>46036</v>
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
@@ -12446,42 +13418,47 @@
       <c r="O191" s="1" t="n"/>
       <c r="P191" s="1" t="inlineStr"/>
       <c r="Q191" s="1" t="inlineStr"/>
+      <c r="R191" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>77985</v>
+        <v>77001</v>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E192" s="1" t="inlineStr">
         <is>
-          <t>Cliente não está respondendo aos e-mails de classificação das entradas, solictar ao Gm que instrua o cliente como fazer a classificação e a importãncia da mesma. At.te</t>
+          <t>SENHA CONTADOR MINAS GERAIS	Verificar junto a operação porque não se consegue entregar a obrigação de Minas Gerais com a senha do contador responsável, pois o contador anterior assim entregava, A Sócia Sra. Mônica esta com documentos vencidos e não conseguiria adquirir certificado digital para filial, algo nunca pedido anteriormente.ATA DISTRIBUIÇÃO LUCROS 12/2025	Preparar apuração de disponibilidade para confecção de nova ata.APURAÇÃO IMPOSTOS	Cliente reclama do envio dos impostos em cima da hora do pagamento, por exemplo, porque o PIS e COFINS não foi disponibilizado ainda?TRIBUTAÇÃO	Esclarecido ao cliente cobrança de impostos, tanto na Base de cálculo do lucro presumido, majorado em 10% cujo impacto na carga tributária trás aumento de 0,32% para comercialização e 0,60% nos serviços, bem como na Distribuição de lucros a partir de 2026, com tributação para valores acima de R$ 50.000,00</t>
         </is>
       </c>
       <c r="F192" s="1" t="n">
-        <v>6544</v>
+        <v>6460</v>
       </c>
       <c r="G192" s="1" t="inlineStr">
         <is>
-          <t>CENTRO COMERCIAL DE FERRAMENTAS LTDA</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H192" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I192" s="1" t="inlineStr">
@@ -12490,10 +13467,10 @@
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>46097.34584575232</v>
+        <v>46057.51196813658</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>46112</v>
+        <v>46064</v>
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
@@ -12502,17 +13479,22 @@
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N192" s="1" t="n"/>
       <c r="O192" s="1" t="n"/>
       <c r="P192" s="1" t="inlineStr"/>
       <c r="Q192" s="1" t="inlineStr"/>
+      <c r="R192" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>77640</v>
+        <v>76809</v>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
@@ -12531,20 +13513,20 @@
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>70% valor de entradas: Cliente possui cerca de 70% das notas de entrada. Restante deve ser feito compensação com nota de transporteImpostos enviados em atraso ou na data do vencimento:Cliente precisa receber os impostos com no mínimo 07 dias da data do vencimento. Passei para o mesmo o cronograma de envio de documentação. Ppor gentileza, este é um ponto chave para a satisfação do cliente.</t>
+          <t>TRIBUTAÇÃO DOS CADASTRO PRODUTOS	CLIENTE SOLICITOU RETORNO SOBRE ANALISE DA TRIBUTAÇÃO DOS CADASTRO DOS PRODUTOS</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>6638</v>
+        <v>6507</v>
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
+          <t xml:space="preserve">ERS PRINT SOLUÇÕES GRAFICAS E VISUAIS LTDA </t>
         </is>
       </c>
       <c r="H193" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I193" s="1" t="inlineStr">
@@ -12553,10 +13535,10 @@
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>46083.6041244213</v>
+        <v>46048.47468460648</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>46086</v>
+        <v>46055</v>
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
@@ -12565,49 +13547,54 @@
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N193" s="1" t="n"/>
       <c r="O193" s="1" t="n"/>
       <c r="P193" s="1" t="inlineStr"/>
       <c r="Q193" s="1" t="inlineStr"/>
+      <c r="R193" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>77643</v>
+        <v>77985</v>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t>Acesso remoto: Cliente disse que já passou acesso remoto para a MG mas não vê quando acessamos. A dúvida é, estamos acessando?</t>
+          <t>Cliente não está respondendo aos e-mails de classificação das entradas, solictar ao Gm que instrua o cliente como fazer a classificação e a importãncia da mesma. At.te</t>
         </is>
       </c>
       <c r="F194" s="1" t="n">
-        <v>6638</v>
+        <v>6544</v>
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
+          <t>CENTRO COMERCIAL DE FERRAMENTAS LTDA</t>
         </is>
       </c>
       <c r="H194" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I194" s="1" t="inlineStr">
@@ -12616,10 +13603,10 @@
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>46083.60717986111</v>
+        <v>46097.34584575232</v>
       </c>
       <c r="K194" s="2" t="n">
-        <v>46086</v>
+        <v>46112</v>
       </c>
       <c r="L194" s="1" t="inlineStr">
         <is>
@@ -12628,44 +13615,49 @@
       </c>
       <c r="M194" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N194" s="1" t="n"/>
       <c r="O194" s="1" t="n"/>
       <c r="P194" s="1" t="inlineStr"/>
       <c r="Q194" s="1" t="inlineStr"/>
+      <c r="R194" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>77557</v>
+        <v>77640</v>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
+          <t>70% valor de entradas: Cliente possui cerca de 70% das notas de entrada. Restante deve ser feito compensação com nota de transporteImpostos enviados em atraso ou na data do vencimento:Cliente precisa receber os impostos com no mínimo 07 dias da data do vencimento. Passei para o mesmo o cronograma de envio de documentação. Ppor gentileza, este é um ponto chave para a satisfação do cliente.</t>
         </is>
       </c>
       <c r="F195" s="1" t="n">
-        <v>6640</v>
+        <v>6638</v>
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
         </is>
       </c>
       <c r="H195" s="1" t="inlineStr">
@@ -12679,10 +13671,10 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>46079.72002283565</v>
+        <v>46083.6041244213</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>46079</v>
+        <v>46086</v>
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
@@ -12691,57 +13683,66 @@
       </c>
       <c r="M195" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N195" s="1" t="n"/>
       <c r="O195" s="1" t="n"/>
       <c r="P195" s="1" t="inlineStr"/>
       <c r="Q195" s="1" t="inlineStr"/>
+      <c r="R195" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>77048</v>
+        <v>77643</v>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Adição de layout para baixa</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Tivemos ocorrencia de duas falhas, ocasionando multas significativas para MG, por este motivo solicito analise e aplicação do ajuste de leiaute de baixa abaixo:Tarefa relacionada: 5867 - GFD - FGTS Digital MensalCompetencia relacionada: 12 Aplica-se as demais competenicas: NãoValidação necessária:Exclusivamente no mês 12 (dezembro) de cada ano, deverá o sistema MGC analisar o arquivo carregado (GFD guia de FGTS), para baixa da tarefa 5867 - GFD - FGTS Digital Mensal, para esta competencia a guia deverá conter as seguintes linhas:13º/202512/2025 Exclusivamente para este mês devemos enviar guia de FGTS contendo os valores de FGTS mensal (12) e da folha de 13º salário, observamos que em falhas recentes o colaborador deixou de gerar a guia consolidada, ocasionando na falta de recolhimento de FGTS no prazo e consequentemente multas de juros no recalculo;Dúvias entrar em contato anexo, modelo de guia.</t>
+          <t>Acesso remoto: Cliente disse que já passou acesso remoto para a MG mas não vê quando acessamos. A dúvida é, estamos acessando?</t>
         </is>
       </c>
       <c r="F196" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" s="1" t="n"/>
+        <v>6638</v>
+      </c>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ETANA COMERCIO E REPRESENTAÇÕES DE CEREAIS LTDA </t>
+        </is>
+      </c>
       <c r="H196" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>46059.66311450231</v>
+        <v>46083.60717986111</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>46063</v>
+        <v>46086</v>
       </c>
       <c r="L196" s="1" t="inlineStr">
         <is>
@@ -12750,80 +13751,90 @@
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
-          <t>Mauricio Lermen</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N196" s="1" t="n"/>
       <c r="O196" s="1" t="n"/>
       <c r="P196" s="1" t="inlineStr"/>
       <c r="Q196" s="1" t="inlineStr"/>
+      <c r="R196" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>77267</v>
+        <v>77557</v>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>5254 - RAFAELTAREFA: DCTFWEB ENVIO DE IMPOSTOS.Esta com erro para baixar.</t>
+          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" s="1" t="n"/>
+        <v>6640</v>
+      </c>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t>FORT FRUIT LTDA</t>
+        </is>
+      </c>
       <c r="H197" s="1" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>46070.67445335648</v>
+        <v>46079.72002283565</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>46071</v>
+        <v>46079</v>
       </c>
       <c r="L197" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M197" s="1" t="inlineStr">
         <is>
-          <t>Diogo Calazans</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="N197" s="1" t="n"/>
       <c r="O197" s="1" t="n"/>
       <c r="P197" s="1" t="inlineStr"/>
-      <c r="Q197" s="1" t="inlineStr">
-        <is>
-          <t>Baixada</t>
+      <c r="Q197" s="1" t="inlineStr"/>
+      <c r="R197" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>77282</v>
+        <v>77048</v>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
@@ -12832,17 +13843,17 @@
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Vencimento de Tarefas</t>
+          <t>Adição de layout para baixa</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>Bom dia.Por gentileza, baixar as tarefas de consultas DEC (1ª quinzena - 01/2026), pois ao consultar consta "acesso negado":35455019504361186619</t>
+          <t>Boa tarde!Tivemos ocorrencia de duas falhas, ocasionando multas significativas para MG, por este motivo solicito analise e aplicação do ajuste de leiaute de baixa abaixo:Tarefa relacionada: 5867 - GFD - FGTS Digital MensalCompetencia relacionada: 12 Aplica-se as demais competenicas: NãoValidação necessária:Exclusivamente no mês 12 (dezembro) de cada ano, deverá o sistema MGC analisar o arquivo carregado (GFD guia de FGTS), para baixa da tarefa 5867 - GFD - FGTS Digital Mensal, para esta competencia a guia deverá conter as seguintes linhas:13º/202512/2025 Exclusivamente para este mês devemos enviar guia de FGTS contendo os valores de FGTS mensal (12) e da folha de 13º salário, observamos que em falhas recentes o colaborador deixou de gerar a guia consolidada, ocasionando na falta de recolhimento de FGTS no prazo e consequentemente multas de juros no recalculo;Dúvias entrar em contato anexo, modelo de guia.</t>
         </is>
       </c>
       <c r="F198" s="1" t="n">
@@ -12851,7 +13862,7 @@
       <c r="G198" s="1" t="n"/>
       <c r="H198" s="1" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I198" s="1" t="inlineStr">
@@ -12860,33 +13871,34 @@
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>46071.4031716088</v>
+        <v>46059.66311450231</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>46072</v>
+        <v>46063</v>
       </c>
       <c r="L198" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="N198" s="1" t="n"/>
       <c r="O198" s="1" t="n"/>
       <c r="P198" s="1" t="inlineStr"/>
-      <c r="Q198" s="1" t="inlineStr">
-        <is>
-          <t>Feito</t>
+      <c r="Q198" s="1" t="inlineStr"/>
+      <c r="R198" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>77071</v>
+        <v>77267</v>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
@@ -12900,12 +13912,12 @@
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>Não estamos conseguindo baixar a tarefa DAS para empresas sem movimento. Segue anexo.</t>
+          <t>5254 - RAFAELTAREFA: DCTFWEB ENVIO DE IMPOSTOS.Esta com erro para baixar.</t>
         </is>
       </c>
       <c r="F199" s="1" t="n">
@@ -12914,7 +13926,7 @@
       <c r="G199" s="1" t="n"/>
       <c r="H199" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="I199" s="1" t="inlineStr">
@@ -12923,35 +13935,38 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>46062.49334166667</v>
+        <v>46070.67445335648</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>46063</v>
+        <v>46071</v>
       </c>
       <c r="L199" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="n">
-        <v>46066.50029050926</v>
-      </c>
+          <t>Diogo Calazans</t>
+        </is>
+      </c>
+      <c r="N199" s="1" t="n"/>
       <c r="O199" s="1" t="n"/>
       <c r="P199" s="1" t="inlineStr"/>
       <c r="Q199" s="1" t="inlineStr">
         <is>
-          <t>Verificando.</t>
+          <t>Baixada</t>
+        </is>
+      </c>
+      <c r="R199" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>77073</v>
+        <v>77282</v>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
@@ -12960,17 +13975,17 @@
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Vencimento de Tarefas</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>Não estamos conseguindo fazer a baixa da tarefa DAS para empresas com movimento, segue documentos em anexo.</t>
+          <t>Bom dia.Por gentileza, baixar as tarefas de consultas DEC (1ª quinzena - 01/2026), pois ao consultar consta "acesso negado":35455019504361186619</t>
         </is>
       </c>
       <c r="F200" s="1" t="n">
@@ -12979,7 +13994,7 @@
       <c r="G200" s="1" t="n"/>
       <c r="H200" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="I200" s="1" t="inlineStr">
@@ -12988,54 +14003,57 @@
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>46062.49889204861</v>
+        <v>46071.4031716088</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>46063</v>
+        <v>46072</v>
       </c>
       <c r="L200" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="n">
-        <v>46066.49782600695</v>
-      </c>
+          <t>Bianca Castro</t>
+        </is>
+      </c>
+      <c r="N200" s="1" t="n"/>
       <c r="O200" s="1" t="n"/>
       <c r="P200" s="1" t="inlineStr"/>
       <c r="Q200" s="1" t="inlineStr">
         <is>
-          <t>Verificando.</t>
+          <t>Feito</t>
+        </is>
+      </c>
+      <c r="R200" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>77520</v>
+        <v>77071</v>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Radar de Obrigações</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Adição de Tarefas ao Radar</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t>oi boa tarde por gentileza, colocar o e-mail da colaboradora Juliane (jvaz@mgcontecnica.com.br) .para receber as obrigações do dia que recebemos as 08: 15 por e-mails. pois a mesma não recebe das lojas dela</t>
+          <t>Não estamos conseguindo baixar a tarefa DAS para empresas sem movimento. Segue anexo.</t>
         </is>
       </c>
       <c r="F201" s="1" t="n">
@@ -13053,33 +14071,40 @@
         </is>
       </c>
       <c r="J201" s="2" t="n">
-        <v>46079.52839001158</v>
+        <v>46062.49334166667</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>46083</v>
+        <v>46063</v>
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
-          <t>Vanessa Tavares</t>
-        </is>
-      </c>
-      <c r="N201" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="n">
+        <v>46066.50029050926</v>
+      </c>
       <c r="O201" s="1" t="n"/>
       <c r="P201" s="1" t="inlineStr"/>
       <c r="Q201" s="1" t="inlineStr">
         <is>
-          <t>Caso ainda não esteja aparecendo, por favor responda esse chamado.</t>
+          <t>Verificando.</t>
+        </is>
+      </c>
+      <c r="R201" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>77545</v>
+        <v>77073</v>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
@@ -13088,17 +14113,17 @@
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Forçar baixa de tarefas via banco de dados</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>Caros, boa tarde!Gentileza realizar baixa da tarefa "Informe Rendimento PDF (DIRF)" da empresa 9776. Segue em anexo o arquivo retirado do eSocial. Devido funcionária ser domestica, foi necessário emitir o informe através do eSocial e por esse motivo não é possível dar baixa. Desde já agradeço.</t>
+          <t>Não estamos conseguindo fazer a baixa da tarefa DAS para empresas com movimento, segue documentos em anexo.</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
@@ -13107,7 +14132,7 @@
       <c r="G202" s="1" t="n"/>
       <c r="H202" s="1" t="inlineStr">
         <is>
-          <t>Juan Rodrigues</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I202" s="1" t="inlineStr">
@@ -13116,52 +14141,59 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>46079.65684244213</v>
+        <v>46062.49889204861</v>
       </c>
       <c r="K202" s="2" t="n">
-        <v>46080</v>
+        <v>46063</v>
       </c>
       <c r="L202" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
-          <t>nathaliap</t>
-        </is>
-      </c>
-      <c r="N202" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="n">
+        <v>46066.49782600695</v>
+      </c>
       <c r="O202" s="1" t="n"/>
       <c r="P202" s="1" t="inlineStr"/>
       <c r="Q202" s="1" t="inlineStr">
         <is>
-          <t>Feito</t>
+          <t>Verificando.</t>
+        </is>
+      </c>
+      <c r="R202" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>77950</v>
+        <v>77520</v>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Radar de Obrigações</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
         <is>
-          <t>Criação de Tarefas</t>
+          <t>Adição de Tarefas ao Radar</t>
         </is>
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA OPERACIONAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>Acrescentar no checklist da Escrita Fiscal a cobrança de relatório de distribuição de lucros aos sócios.</t>
+          <t>oi boa tarde por gentileza, colocar o e-mail da colaboradora Juliane (jvaz@mgcontecnica.com.br) .para receber as obrigações do dia que recebemos as 08: 15 por e-mails. pois a mesma não recebe das lojas dela</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
@@ -13179,35 +14211,38 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>46093.61446322917</v>
+        <v>46079.52839001158</v>
       </c>
       <c r="K203" s="2" t="n">
-        <v>46097</v>
+        <v>46083</v>
       </c>
       <c r="L203" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M203" s="1" t="inlineStr">
         <is>
-          <t>Vitor Ferreira</t>
-        </is>
-      </c>
-      <c r="N203" s="2" t="n">
-        <v>46104.49035262731</v>
-      </c>
+          <t>Vanessa Tavares</t>
+        </is>
+      </c>
+      <c r="N203" s="1" t="n"/>
       <c r="O203" s="1" t="n"/>
       <c r="P203" s="1" t="inlineStr"/>
       <c r="Q203" s="1" t="inlineStr">
         <is>
-          <t>Aguardando retorno do desenvolvimento: 2 026 031 126.</t>
+          <t>Caso ainda não esteja aparecendo, por favor responda esse chamado.</t>
+        </is>
+      </c>
+      <c r="R203" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>78001</v>
+        <v>77545</v>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
@@ -13216,17 +14251,17 @@
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>Criação de Tarefas</t>
+          <t>Forçar baixa de tarefas via banco de dados</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>Preciso que criem uma tarefa de obrigação acessoria de Santa Catarina para empresa 4884. Esta tarefa se cham DIME e vence todo dia 10 do mês subsequente. Segue em anexo arquivos para validação e baixa da tatrefa</t>
+          <t>Caros, boa tarde!Gentileza realizar baixa da tarefa "Informe Rendimento PDF (DIRF)" da empresa 9776. Segue em anexo o arquivo retirado do eSocial. Devido funcionária ser domestica, foi necessário emitir o informe através do eSocial e por esse motivo não é possível dar baixa. Desde já agradeço.</t>
         </is>
       </c>
       <c r="F204" s="1" t="n">
@@ -13235,7 +14270,7 @@
       <c r="G204" s="1" t="n"/>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Juan Rodrigues</t>
         </is>
       </c>
       <c r="I204" s="1" t="inlineStr">
@@ -13244,35 +14279,38 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>46097.46794487268</v>
+        <v>46079.65684244213</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>46099</v>
+        <v>46080</v>
       </c>
       <c r="L204" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
-          <t>Julio Santos</t>
-        </is>
-      </c>
-      <c r="N204" s="2" t="n">
-        <v>46098.36950836806</v>
-      </c>
+          <t>nathaliap</t>
+        </is>
+      </c>
+      <c r="N204" s="1" t="n"/>
       <c r="O204" s="1" t="n"/>
       <c r="P204" s="1" t="inlineStr"/>
       <c r="Q204" s="1" t="inlineStr">
         <is>
-          <t>Tarefa criada, layout em validação.</t>
+          <t>Feito</t>
+        </is>
+      </c>
+      <c r="R204" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>78491</v>
+        <v>77950</v>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
@@ -13281,17 +14319,17 @@
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Criação de Tarefas</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA OPERACIONAL</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom diaPor favor alterar a tarefa abaixo para o mes 02.2026 da empresa 6590 - VPSEst- ICMS SN - Diferencial Alíquota (EF - INDUSTRIA)</t>
+          <t>Acrescentar no checklist da Escrita Fiscal a cobrança de relatório de distribuição de lucros aos sócios.</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
@@ -13309,48 +14347,59 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>46119.42360952546</v>
+        <v>46093.61446322917</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>46120</v>
+        <v>46097</v>
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
-          <t>ruths</t>
-        </is>
-      </c>
-      <c r="N205" s="1" t="n"/>
+          <t>Vitor Ferreira</t>
+        </is>
+      </c>
+      <c r="N205" s="2" t="n">
+        <v>46104.49035262731</v>
+      </c>
       <c r="O205" s="1" t="n"/>
       <c r="P205" s="1" t="inlineStr"/>
-      <c r="Q205" s="1" t="inlineStr"/>
+      <c r="Q205" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando retorno do desenvolvimento: 2 026 031 126.</t>
+        </is>
+      </c>
+      <c r="R205" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>78555</v>
+        <v>78001</v>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>Fechamento Fiscal</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
         <is>
-          <t>Ajuste</t>
+          <t>Criação de Tarefas</t>
         </is>
       </c>
       <c r="D206" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>Prezados, bom diaPor favor alterar a data de vencimento do ISS da AERODUTO e AEROINDUSTRIAL , pois o vencimento da guia de prestados é dia 15 e tomados dia 20 de cada mês.</t>
+          <t>Preciso que criem uma tarefa de obrigação acessoria de Santa Catarina para empresa 4884. Esta tarefa se cham DIME e vence todo dia 10 do mês subsequente. Segue em anexo arquivos para validação e baixa da tatrefa</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
@@ -13368,10 +14417,10 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>46121.39910072917</v>
+        <v>46097.46794487268</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>46122</v>
+        <v>46099</v>
       </c>
       <c r="L206" s="1" t="inlineStr">
         <is>
@@ -13380,23 +14429,28 @@
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Julio Santos</t>
         </is>
       </c>
       <c r="N206" s="2" t="n">
-        <v>46121.6632869213</v>
+        <v>46098.36950836806</v>
       </c>
       <c r="O206" s="1" t="n"/>
       <c r="P206" s="1" t="inlineStr"/>
       <c r="Q206" s="1" t="inlineStr">
         <is>
-          <t>Aguardando retorno do desenvolvimento: 2 026 040 436</t>
+          <t>Tarefa criada, layout em validação.</t>
+        </is>
+      </c>
+      <c r="R206" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>78887</v>
+        <v>78491</v>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
@@ -13410,12 +14464,12 @@
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Favor baixar a tarefa IRPJ/CSLL - FISCAL LUCRO PRESUMIDOPois a empresa é de Lucro Real a partir de 2026</t>
+          <t>Prezados, bom diaPor favor alterar a tarefa abaixo para o mes 02.2026 da empresa 6590 - VPSEst- ICMS SN - Diferencial Alíquota (EF - INDUSTRIA)</t>
         </is>
       </c>
       <c r="F207" s="1" t="n">
@@ -13433,52 +14487,53 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>46139.42510072917</v>
+        <v>46119.42360952546</v>
       </c>
       <c r="K207" s="2" t="n">
-        <v>46140</v>
+        <v>46120</v>
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>ruths</t>
         </is>
       </c>
       <c r="N207" s="1" t="n"/>
       <c r="O207" s="1" t="n"/>
       <c r="P207" s="1" t="inlineStr"/>
-      <c r="Q207" s="1" t="inlineStr">
-        <is>
-          <t>Informar qual é a empresa.</t>
+      <c r="Q207" s="1" t="inlineStr"/>
+      <c r="R207" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>78929</v>
+        <v>78555</v>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Fechamento Fiscal</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Ajuste</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>EMPRESA: 5287 - ATIV COMERCIODivergências de honorários 03/2026. Na planilha e na contabilidade tem 2 notas da MG, porém com valores diferentes e no portal nacional tem apenas 1 Nota da MG.</t>
+          <t>Prezados, bom diaPor favor alterar a data de vencimento do ISS da AERODUTO e AEROINDUSTRIAL , pois o vencimento da guia de prestados é dia 15 e tomados dia 20 de cada mês.</t>
         </is>
       </c>
       <c r="F208" s="1" t="n">
@@ -13496,29 +14551,40 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>46139.70211655093</v>
+        <v>46121.39910072917</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>46140</v>
+        <v>46122</v>
       </c>
       <c r="L208" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
-          <t>Leticia Barbosa</t>
-        </is>
-      </c>
-      <c r="N208" s="1" t="n"/>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
+      <c r="N208" s="2" t="n">
+        <v>46121.6632869213</v>
+      </c>
       <c r="O208" s="1" t="n"/>
       <c r="P208" s="1" t="inlineStr"/>
-      <c r="Q208" s="1" t="inlineStr"/>
+      <c r="Q208" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando retorno do desenvolvimento: 2 026 040 436</t>
+        </is>
+      </c>
+      <c r="R208" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>79090</v>
+        <v>78887</v>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
@@ -13527,17 +14593,17 @@
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>Vencimento de Tarefas</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>Alterar vencimento de tarefa de ISS sob Serviços Tomados e Prestados da empresa 6375 - I9 SOLUÇÕES. Pois o vencimento da guia da prefeitura é apenas no dia 25 de cada mês.</t>
+          <t>Bom dia!Favor baixar a tarefa IRPJ/CSLL - FISCAL LUCRO PRESUMIDOPois a empresa é de Lucro Real a partir de 2026</t>
         </is>
       </c>
       <c r="F209" s="1" t="n">
@@ -13555,29 +14621,38 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>46150.60774603009</v>
+        <v>46139.42510072917</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>46153</v>
+        <v>46140</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
-          <t>Eliane Moreira</t>
+          <t>Beatriz Oliveira</t>
         </is>
       </c>
       <c r="N209" s="1" t="n"/>
       <c r="O209" s="1" t="n"/>
       <c r="P209" s="1" t="inlineStr"/>
-      <c r="Q209" s="1" t="inlineStr"/>
+      <c r="Q209" s="1" t="inlineStr">
+        <is>
+          <t>Informar qual é a empresa.</t>
+        </is>
+      </c>
+      <c r="R209" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>79119</v>
+        <v>78929</v>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
@@ -13591,12 +14666,12 @@
       </c>
       <c r="D210" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>BOA TARDEPOR FAVOR, BAIXAR A TAREFA GIA ST PR / SCEMPRESA: 6460 - Nor Import</t>
+          <t>EMPRESA: 5287 - ATIV COMERCIODivergências de honorários 03/2026. Na planilha e na contabilidade tem 2 notas da MG, porém com valores diferentes e no portal nacional tem apenas 1 Nota da MG.</t>
         </is>
       </c>
       <c r="F210" s="1" t="n">
@@ -13614,10 +14689,10 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46153.65490871527</v>
+        <v>46139.70211655093</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>46154</v>
+        <v>46140</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
@@ -13626,17 +14701,22 @@
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Leticia Barbosa</t>
         </is>
       </c>
       <c r="N210" s="1" t="n"/>
       <c r="O210" s="1" t="n"/>
       <c r="P210" s="1" t="inlineStr"/>
       <c r="Q210" s="1" t="inlineStr"/>
+      <c r="R210" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>79122</v>
+        <v>79090</v>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
@@ -13645,17 +14725,17 @@
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Vencimento de Tarefas</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>GRUPO CARLÃONo análise de balanço, a tarefa reapareceu para os meses 2 e 3.aparece o seguinte erro ANEXO quando tento baixar:Estou tentando baixar 4625 no mês 4 também e aparece o mesmo erro</t>
+          <t>Alterar vencimento de tarefa de ISS sob Serviços Tomados e Prestados da empresa 6375 - I9 SOLUÇÕES. Pois o vencimento da guia da prefeitura é apenas no dia 25 de cada mês.</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
@@ -13673,10 +14753,10 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>46153.68092109953</v>
+        <v>46150.60774603009</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
@@ -13685,17 +14765,22 @@
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Cruz</t>
+          <t>Eliane Moreira</t>
         </is>
       </c>
       <c r="N211" s="1" t="n"/>
       <c r="O211" s="1" t="n"/>
       <c r="P211" s="1" t="inlineStr"/>
       <c r="Q211" s="1" t="inlineStr"/>
+      <c r="R211" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>79123</v>
+        <v>79119</v>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
@@ -13704,17 +14789,17 @@
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>Forçar baixa de tarefas via banco de dados</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Prezados,Solicito da baixa na tarefa de GFD - FGTS DIGITAL MENSAL ref. 04/2026 da empresa 5916 - IMPERIO DO BANHO..., pois a mesma não haverá guia no mês em questão.Obrigada!</t>
+          <t>BOA TARDEPOR FAVOR, BAIXAR A TAREFA GIA ST PR / SCEMPRESA: 6460 - Nor Import</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
@@ -13732,7 +14817,7 @@
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>46153.71334178241</v>
+        <v>46153.65490871527</v>
       </c>
       <c r="K212" s="2" t="n">
         <v>46154</v>
@@ -13744,17 +14829,22 @@
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
-          <t>Oliene Mariano</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N212" s="1" t="n"/>
       <c r="O212" s="1" t="n"/>
       <c r="P212" s="1" t="inlineStr"/>
       <c r="Q212" s="1" t="inlineStr"/>
+      <c r="R212" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>79132</v>
+        <v>79122</v>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
@@ -13763,17 +14853,17 @@
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>Abertura de protocolo</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia ,O Walter Ramos nosso Diretor Geral solicitou em reunião a alteração da Empresas que estão no MG Controle com a Unidade como MG Contabifacil para MG Express pois quando ele puxa os relatórios e indicativos da Express algumas empresas não aparecem pois estão como ContabiFacil , sendo que essa empresa foi descontinuada.</t>
+          <t>GRUPO CARLÃONo análise de balanço, a tarefa reapareceu para os meses 2 e 3.aparece o seguinte erro ANEXO quando tento baixar:Estou tentando baixar 4625 no mês 4 também e aparece o mesmo erro</t>
         </is>
       </c>
       <c r="F213" s="1" t="n">
@@ -13791,10 +14881,10 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>46154.44455590278</v>
+        <v>46153.68092109953</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>46155</v>
+        <v>46154</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
@@ -13803,17 +14893,22 @@
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
-          <t>Helmer Dantas</t>
+          <t>Eduardo Cruz</t>
         </is>
       </c>
       <c r="N213" s="1" t="n"/>
       <c r="O213" s="1" t="n"/>
       <c r="P213" s="1" t="inlineStr"/>
       <c r="Q213" s="1" t="inlineStr"/>
+      <c r="R213" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>79163</v>
+        <v>79123</v>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
@@ -13822,17 +14917,17 @@
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>Reabertura de tarefa</t>
+          <t>Forçar baixa de tarefas via banco de dados</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - DP</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia,Ao retirar o relatório na data de Hoje no MG Controle, notei que há tarefas referente a Contribuição Assistencial Empresa 2ª Parcela, com descritivos de Sindicatos que não pertencem as empresas Listadas. Exemplo: Sindicato 115 não pertence a nenhuma das empresas descritas. Sindicato 82 a mesma situação. O mais estranho de fato são os vencimentos das tarefas, sendo 10/02/2026 e uma com vencimento 10/02/2025? Enfim, solicito a Revisão dessas tarefas e a exclusão dasmesmas uma vez que não compete as empresas, deixarei em anexo, o relatório sindical da competência 02/2026 de uma das empresas como exemplo e a tela com as tarefas que de fato estão erradas no MG Controle. </t>
+          <t>Boa tarde!Prezados,Solicito da baixa na tarefa de GFD - FGTS DIGITAL MENSAL ref. 04/2026 da empresa 5916 - IMPERIO DO BANHO..., pois a mesma não haverá guia no mês em questão.Obrigada!</t>
         </is>
       </c>
       <c r="F214" s="1" t="n">
@@ -13841,7 +14936,7 @@
       <c r="G214" s="1" t="n"/>
       <c r="H214" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I214" s="1" t="inlineStr">
@@ -13850,35 +14945,34 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>46155.38992508102</v>
+        <v>46153.71334178241</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
-          <t>Cintia Andrade</t>
-        </is>
-      </c>
-      <c r="N214" s="2" t="n">
-        <v>46155.41136643518</v>
-      </c>
+          <t>Oliene Mariano</t>
+        </is>
+      </c>
+      <c r="N214" s="1" t="n"/>
       <c r="O214" s="1" t="n"/>
       <c r="P214" s="1" t="inlineStr"/>
-      <c r="Q214" s="1" t="inlineStr">
-        <is>
-          <t>Em processo de conferencia</t>
+      <c r="Q214" s="1" t="inlineStr"/>
+      <c r="R214" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>78180</v>
+        <v>79132</v>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
@@ -13897,7 +14991,7 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>Precisamos que a tarefa "Folha Pro-Labore/Autonomo - Impressão PDF" e "Folha Mensal/Pro-Labore" sejam retiradas dos modelos: MG EXPRESS DP - COMERCIO EM GERAL; MG EXPRESS DP - INDUSTRIAS EM GERAL/SERVIÇO. Para estes modelos deve constar apenas a tarefa "FOPAG Impressão PDF"</t>
+          <t>Bom Dia ,O Walter Ramos nosso Diretor Geral solicitou em reunião a alteração da Empresas que estão no MG Controle com a Unidade como MG Contabifacil para MG Express pois quando ele puxa os relatórios e indicativos da Express algumas empresas não aparecem pois estão como ContabiFacil , sendo que essa empresa foi descontinuada.</t>
         </is>
       </c>
       <c r="F215" s="1" t="n">
@@ -13915,35 +15009,34 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>46106.4896372338</v>
+        <v>46154.44455590278</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>46107</v>
+        <v>46155</v>
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
-        </is>
-      </c>
-      <c r="N215" s="2" t="n">
-        <v>46108.39641195602</v>
-      </c>
+          <t>Helmer Dantas</t>
+        </is>
+      </c>
+      <c r="N215" s="1" t="n"/>
       <c r="O215" s="1" t="n"/>
       <c r="P215" s="1" t="inlineStr"/>
-      <c r="Q215" s="1" t="inlineStr">
-        <is>
-          <t>Em andamento.</t>
+      <c r="Q215" s="1" t="inlineStr"/>
+      <c r="R215" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>79033</v>
+        <v>79163</v>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
@@ -13952,17 +15045,17 @@
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Reabertura de tarefa</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde Baixar tarefa impressão PDF empresa 3969, empresa sem funcionario</t>
+          <t xml:space="preserve">Bom dia,Ao retirar o relatório na data de Hoje no MG Controle, notei que há tarefas referente a Contribuição Assistencial Empresa 2ª Parcela, com descritivos de Sindicatos que não pertencem as empresas Listadas. Exemplo: Sindicato 115 não pertence a nenhuma das empresas descritas. Sindicato 82 a mesma situação. O mais estranho de fato são os vencimentos das tarefas, sendo 10/02/2026 e uma com vencimento 10/02/2025? Enfim, solicito a Revisão dessas tarefas e a exclusão dasmesmas uma vez que não compete as empresas, deixarei em anexo, o relatório sindical da competência 02/2026 de uma das empresas como exemplo e a tela com as tarefas que de fato estão erradas no MG Controle. </t>
         </is>
       </c>
       <c r="F216" s="1" t="n">
@@ -13971,7 +15064,7 @@
       <c r="G216" s="1" t="n"/>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I216" s="1" t="inlineStr">
@@ -13980,29 +15073,40 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>46148.72114085648</v>
+        <v>46155.38992508102</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
-        </is>
-      </c>
-      <c r="N216" s="1" t="n"/>
+          <t>Cintia Andrade</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="n">
+        <v>46155.41136643518</v>
+      </c>
       <c r="O216" s="1" t="n"/>
       <c r="P216" s="1" t="inlineStr"/>
-      <c r="Q216" s="1" t="inlineStr"/>
+      <c r="Q216" s="1" t="inlineStr">
+        <is>
+          <t>Em processo de conferencia</t>
+        </is>
+      </c>
+      <c r="R216" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>79034</v>
+        <v>78180</v>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
@@ -14011,17 +15115,17 @@
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Abertura de protocolo</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde Favor baixar tarefa impressão PDF empresa 3965, empresa mudou de sistema </t>
+          <t>Precisamos que a tarefa "Folha Pro-Labore/Autonomo - Impressão PDF" e "Folha Mensal/Pro-Labore" sejam retiradas dos modelos: MG EXPRESS DP - COMERCIO EM GERAL; MG EXPRESS DP - INDUSTRIAS EM GERAL/SERVIÇO. Para estes modelos deve constar apenas a tarefa "FOPAG Impressão PDF"</t>
         </is>
       </c>
       <c r="F217" s="1" t="n">
@@ -14039,29 +15143,40 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>46148.74504545139</v>
+        <v>46106.4896372338</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>46149</v>
+        <v>46107</v>
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
-          <t>Graziele Almeida</t>
-        </is>
-      </c>
-      <c r="N217" s="1" t="n"/>
+          <t>Romero Borges</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>46108.39641195602</v>
+      </c>
       <c r="O217" s="1" t="n"/>
       <c r="P217" s="1" t="inlineStr"/>
-      <c r="Q217" s="1" t="inlineStr"/>
+      <c r="Q217" s="1" t="inlineStr">
+        <is>
+          <t>Em andamento.</t>
+        </is>
+      </c>
+      <c r="R217" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>79040</v>
+        <v>79033</v>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
@@ -14070,17 +15185,17 @@
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por gentileza baixa a tarefa de Confirmação de IRJP E CSLL das empresas:286528664809</t>
+          <t>Boa tarde Baixar tarefa impressão PDF empresa 3969, empresa sem funcionario</t>
         </is>
       </c>
       <c r="F218" s="1" t="n">
@@ -14098,10 +15213,10 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>46149.43554383102</v>
+        <v>46148.72114085648</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
@@ -14110,17 +15225,22 @@
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="N218" s="1" t="n"/>
       <c r="O218" s="1" t="n"/>
       <c r="P218" s="1" t="inlineStr"/>
       <c r="Q218" s="1" t="inlineStr"/>
+      <c r="R218" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>79449</v>
+        <v>79034</v>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
@@ -14129,17 +15249,17 @@
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde !!Favor baixar a tarefa PIS E COFINS competência 04/2026, referente a empresa 6248. Pois foi feita por planilha e deu credora.Att. </t>
+          <t xml:space="preserve">Boa tarde Favor baixar tarefa impressão PDF empresa 3965, empresa mudou de sistema </t>
         </is>
       </c>
       <c r="F219" s="1" t="n">
@@ -14157,10 +15277,10 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>46167.74551987268</v>
+        <v>46148.74504545139</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>46168</v>
+        <v>46149</v>
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
@@ -14169,17 +15289,22 @@
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Oliveira</t>
+          <t>Graziele Almeida</t>
         </is>
       </c>
       <c r="N219" s="1" t="n"/>
       <c r="O219" s="1" t="n"/>
       <c r="P219" s="1" t="inlineStr"/>
       <c r="Q219" s="1" t="inlineStr"/>
+      <c r="R219" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>79450</v>
+        <v>79040</v>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
@@ -14193,12 +15318,12 @@
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>favor baixar as empresas: 4120; 4124; 4183; 4503; 4504; 4506; estão sem certificadotarefa de dec 1 quinzena de maio</t>
+          <t>Bom dia!Por gentileza baixa a tarefa de Confirmação de IRJP E CSLL das empresas:286528664809</t>
         </is>
       </c>
       <c r="F220" s="1" t="n">
@@ -14216,10 +15341,10 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>46167.75093834491</v>
+        <v>46149.43554383102</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>46168</v>
+        <v>46150</v>
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
@@ -14228,17 +15353,22 @@
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Bruna Costa</t>
         </is>
       </c>
       <c r="N220" s="1" t="n"/>
       <c r="O220" s="1" t="n"/>
       <c r="P220" s="1" t="inlineStr"/>
       <c r="Q220" s="1" t="inlineStr"/>
+      <c r="R220" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>79490</v>
+        <v>79449</v>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
@@ -14247,17 +15377,17 @@
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>Correção de Relatórios</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t>A EMPRESA 4195- TERRA BRASIL HORTI FRUTI LTDA - 02.823.571/0001-51, ESTÁ COM O RELATORIO DIVERGENTE NO PIS E CONFIS A SOMA DO MES FEVEREIRO PARA MARÇO NÃO ESTA SENDO CALCULADO POR ESSE MOTIVO O SALDO CREDOR NAÕ ESTÁ CORRETO.POR FAVOR VERIFICAR</t>
+          <t xml:space="preserve">Boa tarde !!Favor baixar a tarefa PIS E COFINS competência 04/2026, referente a empresa 6248. Pois foi feita por planilha e deu credora.Att. </t>
         </is>
       </c>
       <c r="F221" s="1" t="n">
@@ -14266,7 +15396,7 @@
       <c r="G221" s="1" t="n"/>
       <c r="H221" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I221" s="1" t="inlineStr">
@@ -14275,35 +15405,34 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>46169.41753695602</v>
+        <v>46167.74551987268</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
-          <t>Paulo Silva</t>
-        </is>
-      </c>
-      <c r="N221" s="2" t="n">
-        <v>46176.75945694444</v>
-      </c>
+          <t>Beatriz Oliveira</t>
+        </is>
+      </c>
+      <c r="N221" s="1" t="n"/>
       <c r="O221" s="1" t="n"/>
       <c r="P221" s="1" t="inlineStr"/>
-      <c r="Q221" s="1" t="inlineStr">
-        <is>
-          <t>Em atendimento em conjunto com a Nicole</t>
+      <c r="Q221" s="1" t="inlineStr"/>
+      <c r="R221" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>79693</v>
+        <v>79450</v>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
@@ -14317,12 +15446,12 @@
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>RJ - GC ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>Erro ao baixar sped contribuições sem movimento.</t>
+          <t>favor baixar as empresas: 4120; 4124; 4183; 4503; 4504; 4506; estão sem certificadotarefa de dec 1 quinzena de maio</t>
         </is>
       </c>
       <c r="F222" s="1" t="n">
@@ -14331,7 +15460,7 @@
       <c r="G222" s="1" t="n"/>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I222" s="1" t="inlineStr">
@@ -14340,35 +15469,34 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>46176.76007549769</v>
+        <v>46167.75093834491</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>46178</v>
+        <v>46168</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
-          <t>Renata Paixão</t>
-        </is>
-      </c>
-      <c r="N222" s="2" t="n">
-        <v>46178.42107121528</v>
-      </c>
+          <t>Amanda Mesquita</t>
+        </is>
+      </c>
+      <c r="N222" s="1" t="n"/>
       <c r="O222" s="1" t="n"/>
       <c r="P222" s="1" t="inlineStr"/>
-      <c r="Q222" s="1" t="inlineStr">
-        <is>
-          <t>Enviado layout para o desenvolvimento</t>
+      <c r="Q222" s="1" t="inlineStr"/>
+      <c r="R222" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>79704</v>
+        <v>79490</v>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
@@ -14377,53 +15505,68 @@
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Correção de Relatórios</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">por gentileza, baixar as tarefas de SPED CONTRIBUIÇÕES referente a 04/2026 das empresas: 5455, 5587 e 6443.Motivo: esta com erro na baixa. </t>
+          <t>A EMPRESA 4195- TERRA BRASIL HORTI FRUTI LTDA - 02.823.571/0001-51, ESTÁ COM O RELATORIO DIVERGENTE NO PIS E CONFIS A SOMA DO MES FEVEREIRO PARA MARÇO NÃO ESTA SENDO CALCULADO POR ESSE MOTIVO O SALDO CREDOR NAÕ ESTÁ CORRETO.POR FAVOR VERIFICAR</t>
         </is>
       </c>
       <c r="F223" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G223" s="1" t="n"/>
-      <c r="H223" s="1" t="n"/>
+      <c r="H223" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I223" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>46178.42227739583</v>
+        <v>46169.41753695602</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>46181</v>
+        <v>46171</v>
       </c>
       <c r="L223" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
-          <t>Thayna Melo</t>
-        </is>
-      </c>
-      <c r="N223" s="1" t="n"/>
+          <t>Paulo Silva</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>46176.75945694444</v>
+      </c>
       <c r="O223" s="1" t="n"/>
       <c r="P223" s="1" t="inlineStr"/>
-      <c r="Q223" s="1" t="n"/>
+      <c r="Q223" s="1" t="inlineStr">
+        <is>
+          <t>Em atendimento em conjunto com a Nicole</t>
+        </is>
+      </c>
+      <c r="R223" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>79706</v>
+        <v>79693</v>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
@@ -14432,53 +15575,68 @@
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>Abertura de protocolo</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - EF</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por favor poderiam me auxiliar com a baixa da tarefa [ Controle de baixa recebimento de XML entrada ( Mensal ) - 05/2026 ] e [Cobrança de XML entrada (Mensal ) - 05/2026 ] das seguintes empresas:552562006474647565316626</t>
+          <t>Erro ao baixar sped contribuições sem movimento.</t>
         </is>
       </c>
       <c r="F224" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G224" s="1" t="n"/>
-      <c r="H224" s="1" t="n"/>
+      <c r="H224" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I224" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>46178.46903596065</v>
+        <v>46176.76007549769</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="L224" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
-          <t>Jose Eudes</t>
-        </is>
-      </c>
-      <c r="N224" s="1" t="n"/>
+          <t>Renata Paixão</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="n">
+        <v>46178.42107121528</v>
+      </c>
       <c r="O224" s="1" t="n"/>
       <c r="P224" s="1" t="inlineStr"/>
-      <c r="Q224" s="1" t="n"/>
+      <c r="Q224" s="1" t="inlineStr">
+        <is>
+          <t>Enviado layout para o desenvolvimento</t>
+        </is>
+      </c>
+      <c r="R224" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>79709</v>
+        <v>79704</v>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
@@ -14487,17 +15645,17 @@
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia. Por gentileza, baixar a tarefa  "FOPAG Impressão PDF" da empresa 5508 - competência 05/2026. Ao tentar baixar aparece os erros: "Estte CNPJ NÃO esta e nossos registros de Clientes"; "Verifique se o arquivo é do cliente, mês e ano escolhido". </t>
+          <t xml:space="preserve">por gentileza, baixar as tarefas de SPED CONTRIBUIÇÕES referente a 04/2026 das empresas: 5455, 5587 e 6443.Motivo: esta com erro na baixa. </t>
         </is>
       </c>
       <c r="F225" s="1" t="n">
@@ -14511,7 +15669,7 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>46178.48589880787</v>
+        <v>46178.42227739583</v>
       </c>
       <c r="K225" s="2" t="n">
         <v>46181</v>
@@ -14523,17 +15681,22 @@
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
-          <t>Jayne Tavares</t>
+          <t>Thayna Melo</t>
         </is>
       </c>
       <c r="N225" s="1" t="n"/>
       <c r="O225" s="1" t="n"/>
       <c r="P225" s="1" t="inlineStr"/>
       <c r="Q225" s="1" t="n"/>
+      <c r="R225" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>79023</v>
+        <v>79706</v>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
@@ -14542,61 +15705,58 @@
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Abertura de protocolo</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>ROSSI - CTB</t>
+          <t>MG EXPRESS - EF</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
         <is>
-          <t>MGC não está aceitando o Balancete gerado pelo sistema Consinco WEB, segue anexo arquivo.</t>
+          <t>Bom dia, por favor poderiam me auxiliar com a baixa da tarefa [ Controle de baixa recebimento de XML entrada ( Mensal ) - 05/2026 ] e [Cobrança de XML entrada (Mensal ) - 05/2026 ] das seguintes empresas:552562006474647565316626</t>
         </is>
       </c>
       <c r="F226" s="1" t="n">
-        <v>2371</v>
-      </c>
-      <c r="G226" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO ROSSI NEW LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H226" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G226" s="1" t="n"/>
+      <c r="H226" s="1" t="n"/>
       <c r="I226" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J226" s="2" t="n">
-        <v>46148.49059690972</v>
+        <v>46178.46903596065</v>
       </c>
       <c r="K226" s="2" t="n">
-        <v>46149</v>
+        <v>46181</v>
       </c>
       <c r="L226" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
-          <t>Thiago Santos</t>
+          <t>Jose Eudes</t>
         </is>
       </c>
       <c r="N226" s="1" t="n"/>
       <c r="O226" s="1" t="n"/>
       <c r="P226" s="1" t="inlineStr"/>
-      <c r="Q226" s="1" t="inlineStr"/>
+      <c r="Q226" s="1" t="n"/>
+      <c r="R226" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>79037</v>
+        <v>79709</v>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
@@ -14610,56 +15770,53 @@
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>DALBEN - CTB</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, Na tarefa ECAC não está aceitando 2 relatórios, no total são 4 relatórios para baixa mas o relatório "principal" e "intimação" não está aceitando.Por gentileza, poderia baixar a tarefa da 2ª quinzena 04/2026.Relatórios salvos na pasta publica/Dalben ECAC/Obrigada</t>
+          <t xml:space="preserve">Bom dia. Por gentileza, baixar a tarefa  "FOPAG Impressão PDF" da empresa 5508 - competência 05/2026. Ao tentar baixar aparece os erros: "Estte CNPJ NÃO esta e nossos registros de Clientes"; "Verifique se o arquivo é do cliente, mês e ano escolhido". </t>
         </is>
       </c>
       <c r="F227" s="1" t="n">
-        <v>3212</v>
-      </c>
-      <c r="G227" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADOS DALBEN LTDA. (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H227" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G227" s="1" t="n"/>
+      <c r="H227" s="1" t="n"/>
       <c r="I227" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>46149.39857369213</v>
+        <v>46178.48589880787</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>46150</v>
+        <v>46181</v>
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
-          <t>Karen Corazza</t>
+          <t>Jayne Tavares</t>
         </is>
       </c>
       <c r="N227" s="1" t="n"/>
       <c r="O227" s="1" t="n"/>
       <c r="P227" s="1" t="inlineStr"/>
-      <c r="Q227" s="1" t="inlineStr"/>
+      <c r="Q227" s="1" t="n"/>
+      <c r="R227" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>79703</v>
+        <v>79023</v>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
@@ -14668,30 +15825,30 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>Baixa automática - Arquivos</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t>RJ - DP</t>
+          <t>ROSSI - CTB</t>
         </is>
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Por gentileza, solicito baixa nas tarefas de ARQUIVO CONSIGNADO (Importação e Envio), cujo vencimento é na data de hoje 05/06/26, da empresa 5547 - ACF SERVIÇOS DE APOIO. Motivo: Empresa não possui arquivo referente a competência 06/2026.Obrigado!</t>
+          <t>MGC não está aceitando o Balancete gerado pelo sistema Consinco WEB, segue anexo arquivo.</t>
         </is>
       </c>
       <c r="F228" s="1" t="n">
-        <v>5547</v>
+        <v>2371</v>
       </c>
       <c r="G228" s="1" t="inlineStr">
         <is>
-          <t>ACF SERVICOS DE APOIO LTDA</t>
+          <t>SUPERMERCADO ROSSI NEW LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H228" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I228" s="1" t="inlineStr">
@@ -14700,10 +15857,10 @@
         </is>
       </c>
       <c r="J228" s="2" t="n">
-        <v>46178.41989267361</v>
+        <v>46148.49059690972</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>46181</v>
+        <v>46149</v>
       </c>
       <c r="L228" s="1" t="inlineStr">
         <is>
@@ -14712,17 +15869,22 @@
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
-          <t>Jefferson Barros</t>
+          <t>Thiago Santos</t>
         </is>
       </c>
       <c r="N228" s="1" t="n"/>
       <c r="O228" s="1" t="n"/>
       <c r="P228" s="1" t="inlineStr"/>
       <c r="Q228" s="1" t="inlineStr"/>
+      <c r="R228" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>79451</v>
+        <v>79037</v>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
@@ -14736,20 +15898,20 @@
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>DALBEN - CTB</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Solicito a baixa da tarefa do "MIT", pois se trata de filial.</t>
+          <t>Bom dia, Na tarefa ECAC não está aceitando 2 relatórios, no total são 4 relatórios para baixa mas o relatório "principal" e "intimação" não está aceitando.Por gentileza, poderia baixar a tarefa da 2ª quinzena 04/2026.Relatórios salvos na pasta publica/Dalben ECAC/Obrigada</t>
         </is>
       </c>
       <c r="F229" s="1" t="n">
-        <v>6863</v>
+        <v>3212</v>
       </c>
       <c r="G229" s="1" t="inlineStr">
         <is>
-          <t>TECMAR SERVICOS NAVAIS OFFSHORE LTDA (FILIAL 1)</t>
+          <t>SUPERMERCADOS DALBEN LTDA. (MATRIZ)</t>
         </is>
       </c>
       <c r="H229" s="1" t="inlineStr">
@@ -14763,10 +15925,10 @@
         </is>
       </c>
       <c r="J229" s="2" t="n">
-        <v>46167.75658214121</v>
+        <v>46149.39857369213</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>46168</v>
+        <v>46150</v>
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
@@ -14775,13 +15937,154 @@
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Lopes</t>
+          <t>Karen Corazza</t>
         </is>
       </c>
       <c r="N229" s="1" t="n"/>
       <c r="O229" s="1" t="n"/>
       <c r="P229" s="1" t="inlineStr"/>
       <c r="Q229" s="1" t="inlineStr"/>
+      <c r="R229" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>79703</v>
+      </c>
+      <c r="B230" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="inlineStr">
+        <is>
+          <t>Baixa automática - Arquivos</t>
+        </is>
+      </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>RJ - DP</t>
+        </is>
+      </c>
+      <c r="E230" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia!Por gentileza, solicito baixa nas tarefas de ARQUIVO CONSIGNADO (Importação e Envio), cujo vencimento é na data de hoje 05/06/26, da empresa 5547 - ACF SERVIÇOS DE APOIO. Motivo: Empresa não possui arquivo referente a competência 06/2026.Obrigado!</t>
+        </is>
+      </c>
+      <c r="F230" s="1" t="n">
+        <v>5547</v>
+      </c>
+      <c r="G230" s="1" t="inlineStr">
+        <is>
+          <t>ACF SERVICOS DE APOIO LTDA</t>
+        </is>
+      </c>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="I230" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="n">
+        <v>46178.41989267361</v>
+      </c>
+      <c r="K230" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="L230" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M230" s="1" t="inlineStr">
+        <is>
+          <t>Jefferson Barros</t>
+        </is>
+      </c>
+      <c r="N230" s="1" t="n"/>
+      <c r="O230" s="1" t="n"/>
+      <c r="P230" s="1" t="inlineStr"/>
+      <c r="Q230" s="1" t="inlineStr"/>
+      <c r="R230" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>79451</v>
+      </c>
+      <c r="B231" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="inlineStr">
+        <is>
+          <t>Erro de Baixa</t>
+        </is>
+      </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>RJ - CTB</t>
+        </is>
+      </c>
+      <c r="E231" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!Solicito a baixa da tarefa do "MIT", pois se trata de filial.</t>
+        </is>
+      </c>
+      <c r="F231" s="1" t="n">
+        <v>6863</v>
+      </c>
+      <c r="G231" s="1" t="inlineStr">
+        <is>
+          <t>TECMAR SERVICOS NAVAIS OFFSHORE LTDA (FILIAL 1)</t>
+        </is>
+      </c>
+      <c r="H231" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="I231" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="n">
+        <v>46167.75658214121</v>
+      </c>
+      <c r="K231" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="L231" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M231" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Lopes</t>
+        </is>
+      </c>
+      <c r="N231" s="1" t="n"/>
+      <c r="O231" s="1" t="n"/>
+      <c r="P231" s="1" t="inlineStr"/>
+      <c r="Q231" s="1" t="inlineStr"/>
+      <c r="R231" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S574" headerRowCount="1">
-  <autoFilter ref="A1:S574"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S573" headerRowCount="1">
+  <autoFilter ref="A1:S573"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S574"/>
+  <dimension ref="A1:S573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
@@ -2388,12 +2388,22 @@
         </is>
       </c>
       <c r="N25" s="1" t="n"/>
-      <c r="O25" s="1" t="n"/>
-      <c r="P25" s="1" t="inlineStr"/>
-      <c r="Q25" s="1" t="inlineStr"/>
+      <c r="O25" s="2" t="n">
+        <v>46192.346565625</v>
+      </c>
+      <c r="P25" s="1" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="Q25" s="1" t="inlineStr">
+        <is>
+          <t>Segue conforme solicitado.</t>
+        </is>
+      </c>
       <c r="R25" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S25" s="1" t="n"/>
@@ -2527,7 +2537,7 @@
       </c>
       <c r="L27" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M27" s="1" t="inlineStr">
@@ -2536,12 +2546,22 @@
         </is>
       </c>
       <c r="N27" s="1" t="n"/>
-      <c r="O27" s="1" t="n"/>
-      <c r="P27" s="1" t="inlineStr"/>
-      <c r="Q27" s="1" t="inlineStr"/>
+      <c r="O27" s="2" t="n">
+        <v>46191.75819690972</v>
+      </c>
+      <c r="P27" s="1" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="Q27" s="1" t="inlineStr">
+        <is>
+          <t>Segue conforme solicitado.</t>
+        </is>
+      </c>
       <c r="R27" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S27" s="1" t="n"/>
@@ -3145,7 +3165,7 @@
       </c>
       <c r="L35" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M35" s="1" t="inlineStr">
@@ -3154,12 +3174,22 @@
         </is>
       </c>
       <c r="N35" s="1" t="n"/>
-      <c r="O35" s="1" t="n"/>
-      <c r="P35" s="1" t="inlineStr"/>
-      <c r="Q35" s="1" t="inlineStr"/>
+      <c r="O35" s="2" t="n">
+        <v>46191.75739950231</v>
+      </c>
+      <c r="P35" s="1" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="Q35" s="1" t="inlineStr">
+        <is>
+          <t>Segue conforme solicitado.</t>
+        </is>
+      </c>
       <c r="R35" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S35" s="1" t="n"/>
@@ -4770,7 +4800,7 @@
       </c>
       <c r="L56" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M56" s="1" t="inlineStr">
@@ -4779,12 +4809,22 @@
         </is>
       </c>
       <c r="N56" s="1" t="n"/>
-      <c r="O56" s="1" t="n"/>
-      <c r="P56" s="1" t="inlineStr"/>
-      <c r="Q56" s="1" t="inlineStr"/>
+      <c r="O56" s="2" t="n">
+        <v>46191.75782056713</v>
+      </c>
+      <c r="P56" s="1" t="inlineStr">
+        <is>
+          <t>jackson</t>
+        </is>
+      </c>
+      <c r="Q56" s="1" t="inlineStr">
+        <is>
+          <t>Segue conforme solicitado.</t>
+        </is>
+      </c>
       <c r="R56" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S56" s="1" t="n"/>
@@ -7738,7 +7778,7 @@
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M95" s="1" t="inlineStr">
@@ -7746,10 +7786,16 @@
           <t>Ricardo Ferreira</t>
         </is>
       </c>
-      <c r="N95" s="1" t="n"/>
+      <c r="N95" s="2" t="n">
+        <v>46191.7695471875</v>
+      </c>
       <c r="O95" s="1" t="n"/>
       <c r="P95" s="1" t="inlineStr"/>
-      <c r="Q95" s="1" t="inlineStr"/>
+      <c r="Q95" s="1" t="inlineStr">
+        <is>
+          <t>Cliente não enviou o SPED do mês 09/2025, por isso foi entregue em branco e gerou diferença de transporte de saldo. O processo de montagem para retificação está sendo realizado conforme autorização da Claudineia.</t>
+        </is>
+      </c>
       <c r="R95" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -7807,7 +7853,7 @@
       </c>
       <c r="L96" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M96" s="1" t="inlineStr">
@@ -7816,12 +7862,22 @@
         </is>
       </c>
       <c r="N96" s="1" t="n"/>
-      <c r="O96" s="1" t="n"/>
-      <c r="P96" s="1" t="inlineStr"/>
-      <c r="Q96" s="1" t="inlineStr"/>
+      <c r="O96" s="2" t="n">
+        <v>46191.76695482639</v>
+      </c>
+      <c r="P96" s="1" t="inlineStr">
+        <is>
+          <t>ricardof</t>
+        </is>
+      </c>
+      <c r="Q96" s="1" t="inlineStr">
+        <is>
+          <t>Guias recalculadas.</t>
+        </is>
+      </c>
       <c r="R96" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S96" s="1" t="n"/>
@@ -25598,7 +25654,7 @@
       </c>
       <c r="L329" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M329" s="1" t="inlineStr">
@@ -25607,12 +25663,22 @@
         </is>
       </c>
       <c r="N329" s="1" t="n"/>
-      <c r="O329" s="1" t="n"/>
-      <c r="P329" s="1" t="inlineStr"/>
-      <c r="Q329" s="1" t="inlineStr"/>
+      <c r="O329" s="2" t="n">
+        <v>46191.76178888889</v>
+      </c>
+      <c r="P329" s="1" t="inlineStr">
+        <is>
+          <t>mateusm</t>
+        </is>
+      </c>
+      <c r="Q329" s="1" t="inlineStr">
+        <is>
+          <t>Segue documentos solicitados</t>
+        </is>
+      </c>
       <c r="R329" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S329" s="1" t="n"/>
@@ -43018,7 +43084,7 @@
     </row>
     <row r="569">
       <c r="A569" s="1" t="n">
-        <v>80217</v>
+        <v>80225</v>
       </c>
       <c r="B569" s="1" t="inlineStr">
         <is>
@@ -43027,53 +43093,49 @@
       </c>
       <c r="C569" s="1" t="inlineStr">
         <is>
-          <t>Baixa Automática - SPED</t>
+          <t>Chamados</t>
         </is>
       </c>
       <c r="D569" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>B.P.O. - GUARANI CTB</t>
         </is>
       </c>
       <c r="E569" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solicito a baixa do sped fiscal da empresa 5165 - LEGUME S/A na qual o IE dela foi cadastrado no Período 02/10/2025, sendo assim não tem o porque ter tarefas do período de 2023 a 09/2025. segue situação do posto fiscal </t>
+          <t>por gentileza poderia baixar os Das as empresas - 4917 e 4064 em anexo - e observação a guia ICMS da empresa 4059 encontrasse com o responsável e não foi liberado para contabilidade ainda</t>
         </is>
       </c>
       <c r="F569" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="1" t="n"/>
-      <c r="H569" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
+      <c r="H569" s="1" t="n"/>
       <c r="I569" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J569" s="2" t="n">
-        <v>46191.66336269676</v>
+        <v>46191.74847341435</v>
       </c>
       <c r="K569" s="2" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="L569" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M569" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Flavia Dariolli</t>
         </is>
       </c>
       <c r="N569" s="1" t="n"/>
       <c r="O569" s="1" t="n"/>
       <c r="P569" s="1" t="inlineStr"/>
-      <c r="Q569" s="1" t="inlineStr"/>
+      <c r="Q569" s="1" t="n"/>
       <c r="R569" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -43083,7 +43145,7 @@
     </row>
     <row r="570">
       <c r="A570" s="1" t="n">
-        <v>80225</v>
+        <v>76508</v>
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
@@ -43092,59 +43154,77 @@
       </c>
       <c r="C570" s="1" t="inlineStr">
         <is>
-          <t>Chamados</t>
+          <t>Verificar Validação Obrigação</t>
         </is>
       </c>
       <c r="D570" s="1" t="inlineStr">
         <is>
-          <t>B.P.O. - GUARANI CTB</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E570" s="1" t="inlineStr">
         <is>
-          <t>por gentileza poderia baixar os Das as empresas - 4917 e 4064 em anexo - e observação a guia ICMS da empresa 4059 encontrasse com o responsável e não foi liberado para contabilidade ainda</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F570" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G570" s="1" t="n"/>
-      <c r="H570" s="1" t="n"/>
+        <v>6605</v>
+      </c>
+      <c r="G570" s="1" t="inlineStr">
+        <is>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
+        </is>
+      </c>
+      <c r="H570" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
       <c r="I570" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J570" s="2" t="n">
-        <v>46191.74847341435</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K570" s="2" t="n">
-        <v>46195</v>
+        <v>46034</v>
       </c>
       <c r="L570" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
-          <t>Flavia Dariolli</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="N570" s="1" t="n"/>
-      <c r="O570" s="1" t="n"/>
-      <c r="P570" s="1" t="inlineStr"/>
-      <c r="Q570" s="1" t="n"/>
+      <c r="O570" s="2" t="n">
+        <v>46030.75027241898</v>
+      </c>
+      <c r="P570" s="1" t="inlineStr">
+        <is>
+          <t>nicoleo</t>
+        </is>
+      </c>
+      <c r="Q570" s="1" t="inlineStr">
+        <is>
+          <t>Baixadas.</t>
+        </is>
+      </c>
       <c r="R570" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S570" s="1" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
-        <v>76508</v>
+        <v>76505</v>
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
@@ -43163,15 +43243,15 @@
       </c>
       <c r="E571" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F571" s="1" t="n">
-        <v>6605</v>
+        <v>6640</v>
       </c>
       <c r="G571" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H571" s="1" t="inlineStr">
@@ -43185,7 +43265,7 @@
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K571" s="2" t="n">
         <v>46034</v>
@@ -43202,7 +43282,7 @@
       </c>
       <c r="N571" s="1" t="n"/>
       <c r="O571" s="2" t="n">
-        <v>46030.75027241898</v>
+        <v>46030.63182743055</v>
       </c>
       <c r="P571" s="1" t="inlineStr">
         <is>
@@ -43223,7 +43303,7 @@
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
-        <v>76505</v>
+        <v>76515</v>
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
@@ -43242,15 +43322,15 @@
       </c>
       <c r="E572" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
         </is>
       </c>
       <c r="F572" s="1" t="n">
-        <v>6640</v>
+        <v>6641</v>
       </c>
       <c r="G572" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
         </is>
       </c>
       <c r="H572" s="1" t="inlineStr">
@@ -43264,7 +43344,7 @@
         </is>
       </c>
       <c r="J572" s="2" t="n">
-        <v>46030.60213634259</v>
+        <v>46030.73046079861</v>
       </c>
       <c r="K572" s="2" t="n">
         <v>46034</v>
@@ -43281,7 +43361,7 @@
       </c>
       <c r="N572" s="1" t="n"/>
       <c r="O572" s="2" t="n">
-        <v>46030.63182743055</v>
+        <v>46030.74734336806</v>
       </c>
       <c r="P572" s="1" t="inlineStr">
         <is>
@@ -43290,7 +43370,7 @@
       </c>
       <c r="Q572" s="1" t="inlineStr">
         <is>
-          <t>Baixadas.</t>
+          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
         </is>
       </c>
       <c r="R572" s="1" t="inlineStr">
@@ -43302,7 +43382,7 @@
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
-        <v>76515</v>
+        <v>76501</v>
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
@@ -43321,7 +43401,7 @@
       </c>
       <c r="E573" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
         </is>
       </c>
       <c r="F573" s="1" t="n">
@@ -43343,7 +43423,7 @@
         </is>
       </c>
       <c r="J573" s="2" t="n">
-        <v>46030.73046079861</v>
+        <v>46030.51327708333</v>
       </c>
       <c r="K573" s="2" t="n">
         <v>46034</v>
@@ -43360,7 +43440,7 @@
       </c>
       <c r="N573" s="1" t="n"/>
       <c r="O573" s="2" t="n">
-        <v>46030.74734336806</v>
+        <v>46030.64333047454</v>
       </c>
       <c r="P573" s="1" t="inlineStr">
         <is>
@@ -43369,7 +43449,7 @@
       </c>
       <c r="Q573" s="1" t="inlineStr">
         <is>
-          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
+          <t>Baixadas.</t>
         </is>
       </c>
       <c r="R573" s="1" t="inlineStr">
@@ -43378,85 +43458,6 @@
         </is>
       </c>
       <c r="S573" s="1" t="n"/>
-    </row>
-    <row r="574">
-      <c r="A574" s="1" t="n">
-        <v>76501</v>
-      </c>
-      <c r="B574" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C574" s="1" t="inlineStr">
-        <is>
-          <t>Verificar Validação Obrigação</t>
-        </is>
-      </c>
-      <c r="D574" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E574" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
-        </is>
-      </c>
-      <c r="F574" s="1" t="n">
-        <v>6641</v>
-      </c>
-      <c r="G574" s="1" t="inlineStr">
-        <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
-        </is>
-      </c>
-      <c r="H574" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
-      <c r="I574" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J574" s="2" t="n">
-        <v>46030.51327708333</v>
-      </c>
-      <c r="K574" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="L574" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M574" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N574" s="1" t="n"/>
-      <c r="O574" s="2" t="n">
-        <v>46030.64333047454</v>
-      </c>
-      <c r="P574" s="1" t="inlineStr">
-        <is>
-          <t>nicoleo</t>
-        </is>
-      </c>
-      <c r="Q574" s="1" t="inlineStr">
-        <is>
-          <t>Baixadas.</t>
-        </is>
-      </c>
-      <c r="R574" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S574" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -3163,7 +3163,7 @@
       </c>
       <c r="H35" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
-          <t>Bruno Henrique</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I36" s="1" t="inlineStr">
@@ -5346,7 +5346,11 @@
           <t>Distribuidora J Jotas Ltda.</t>
         </is>
       </c>
-      <c r="H63" s="1" t="n"/>
+      <c r="H63" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I63" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -5360,7 +5364,7 @@
       </c>
       <c r="L63" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M63" s="1" t="inlineStr">
@@ -5371,7 +5375,7 @@
       <c r="N63" s="1" t="n"/>
       <c r="O63" s="1" t="n"/>
       <c r="P63" s="1" t="inlineStr"/>
-      <c r="Q63" s="1" t="n"/>
+      <c r="Q63" s="1" t="inlineStr"/>
       <c r="R63" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -7697,7 +7701,11 @@
           <t>COMERCIO DE ALIMENTOS VICALI LTDA</t>
         </is>
       </c>
-      <c r="H94" s="1" t="n"/>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I94" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -7711,7 +7719,7 @@
       </c>
       <c r="L94" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M94" s="1" t="inlineStr">
@@ -7722,7 +7730,7 @@
       <c r="N94" s="1" t="n"/>
       <c r="O94" s="1" t="n"/>
       <c r="P94" s="1" t="inlineStr"/>
-      <c r="Q94" s="1" t="n"/>
+      <c r="Q94" s="1" t="inlineStr"/>
       <c r="R94" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -9496,7 +9504,11 @@
           <t>TERRA BRASIL HORTI FRUTI LTDA</t>
         </is>
       </c>
-      <c r="H117" s="1" t="n"/>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I117" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -9510,7 +9522,7 @@
       </c>
       <c r="L117" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M117" s="1" t="inlineStr">
@@ -9521,7 +9533,7 @@
       <c r="N117" s="1" t="n"/>
       <c r="O117" s="1" t="n"/>
       <c r="P117" s="1" t="inlineStr"/>
-      <c r="Q117" s="1" t="n"/>
+      <c r="Q117" s="1" t="inlineStr"/>
       <c r="R117" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -10549,7 +10561,11 @@
           <t>SAMPA ATACADO DE GENEROS ALIMENTICIOS E BEBIDAS LTDA</t>
         </is>
       </c>
-      <c r="H131" s="1" t="n"/>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -10563,7 +10579,7 @@
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M131" s="1" t="inlineStr">
@@ -10574,7 +10590,7 @@
       <c r="N131" s="1" t="n"/>
       <c r="O131" s="1" t="n"/>
       <c r="P131" s="1" t="inlineStr"/>
-      <c r="Q131" s="1" t="n"/>
+      <c r="Q131" s="1" t="inlineStr"/>
       <c r="R131" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -11604,7 +11620,11 @@
           <t>SAMPATACADO DE GÊNEROS ALIMENTÍCIOS E BEBIDAS LTDA (FILIAL 02)</t>
         </is>
       </c>
-      <c r="H145" s="1" t="n"/>
+      <c r="H145" s="1" t="inlineStr">
+        <is>
+          <t>Karina Santos</t>
+        </is>
+      </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -11618,7 +11638,7 @@
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M145" s="1" t="inlineStr">
@@ -11629,7 +11649,7 @@
       <c r="N145" s="1" t="n"/>
       <c r="O145" s="1" t="n"/>
       <c r="P145" s="1" t="inlineStr"/>
-      <c r="Q145" s="1" t="n"/>
+      <c r="Q145" s="1" t="inlineStr"/>
       <c r="R145" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -16214,7 +16234,11 @@
           <t>DISTRIBUIDOR DE MORANGOS LTDA</t>
         </is>
       </c>
-      <c r="H205" s="1" t="n"/>
+      <c r="H205" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I205" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -16228,7 +16252,7 @@
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M205" s="1" t="inlineStr">
@@ -16239,7 +16263,7 @@
       <c r="N205" s="1" t="n"/>
       <c r="O205" s="1" t="n"/>
       <c r="P205" s="1" t="inlineStr"/>
-      <c r="Q205" s="1" t="n"/>
+      <c r="Q205" s="1" t="inlineStr"/>
       <c r="R205" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -16348,7 +16372,11 @@
           <t>DISTRIBUIDOR DE MORANGOS LTDA</t>
         </is>
       </c>
-      <c r="H207" s="1" t="n"/>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -16362,7 +16390,7 @@
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M207" s="1" t="inlineStr">
@@ -16373,7 +16401,7 @@
       <c r="N207" s="1" t="n"/>
       <c r="O207" s="1" t="n"/>
       <c r="P207" s="1" t="inlineStr"/>
-      <c r="Q207" s="1" t="n"/>
+      <c r="Q207" s="1" t="inlineStr"/>
       <c r="R207" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -16803,7 +16831,7 @@
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M213" s="1" t="inlineStr">
@@ -16811,10 +16839,16 @@
           <t>Beatriz Rangel</t>
         </is>
       </c>
-      <c r="N213" s="1" t="n"/>
+      <c r="N213" s="2" t="n">
+        <v>46192.55170297454</v>
+      </c>
       <c r="O213" s="1" t="n"/>
       <c r="P213" s="1" t="inlineStr"/>
-      <c r="Q213" s="1" t="inlineStr"/>
+      <c r="Q213" s="1" t="inlineStr">
+        <is>
+          <t>Ajustes vão ser reallizados junto ao fechamento</t>
+        </is>
+      </c>
       <c r="R213" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -18090,7 +18124,11 @@
           <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
-      <c r="H230" s="1" t="n"/>
+      <c r="H230" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I230" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -18104,7 +18142,7 @@
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M230" s="1" t="inlineStr">
@@ -18115,7 +18153,7 @@
       <c r="N230" s="1" t="n"/>
       <c r="O230" s="1" t="n"/>
       <c r="P230" s="1" t="inlineStr"/>
-      <c r="Q230" s="1" t="n"/>
+      <c r="Q230" s="1" t="inlineStr"/>
       <c r="R230" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -19004,7 +19042,11 @@
           <t xml:space="preserve">LINHARES E FONTOURA CONSTRUCAO CIVIL LTDA </t>
         </is>
       </c>
-      <c r="H242" s="1" t="n"/>
+      <c r="H242" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I242" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -19018,7 +19060,7 @@
       </c>
       <c r="L242" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M242" s="1" t="inlineStr">
@@ -19029,7 +19071,7 @@
       <c r="N242" s="1" t="n"/>
       <c r="O242" s="1" t="n"/>
       <c r="P242" s="1" t="inlineStr"/>
-      <c r="Q242" s="1" t="n"/>
+      <c r="Q242" s="1" t="inlineStr"/>
       <c r="R242" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -19486,7 +19528,7 @@
       </c>
       <c r="L248" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M248" s="1" t="inlineStr">
@@ -19494,10 +19536,16 @@
           <t>Rogerio Egidio</t>
         </is>
       </c>
-      <c r="N248" s="1" t="n"/>
+      <c r="N248" s="2" t="n">
+        <v>46192.55194065972</v>
+      </c>
       <c r="O248" s="1" t="n"/>
       <c r="P248" s="1" t="inlineStr"/>
-      <c r="Q248" s="1" t="inlineStr"/>
+      <c r="Q248" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando dpto fiscal retificar a reinf</t>
+        </is>
+      </c>
       <c r="R248" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -19606,7 +19654,11 @@
           <t xml:space="preserve">GM RECICLA SERVICOS LTDA </t>
         </is>
       </c>
-      <c r="H250" s="1" t="n"/>
+      <c r="H250" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I250" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -19620,7 +19672,7 @@
       </c>
       <c r="L250" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M250" s="1" t="inlineStr">
@@ -19631,7 +19683,7 @@
       <c r="N250" s="1" t="n"/>
       <c r="O250" s="1" t="n"/>
       <c r="P250" s="1" t="inlineStr"/>
-      <c r="Q250" s="1" t="n"/>
+      <c r="Q250" s="1" t="inlineStr"/>
       <c r="R250" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23869,7 +23921,11 @@
           <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H306" s="1" t="n"/>
+      <c r="H306" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I306" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -23883,7 +23939,7 @@
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M306" s="1" t="inlineStr">
@@ -23894,7 +23950,7 @@
       <c r="N306" s="1" t="n"/>
       <c r="O306" s="1" t="n"/>
       <c r="P306" s="1" t="inlineStr"/>
-      <c r="Q306" s="1" t="n"/>
+      <c r="Q306" s="1" t="inlineStr"/>
       <c r="R306" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -25852,7 +25908,11 @@
           <t>L.S.V COMERCIO , LOCACAO ,MONTAGENS E REPRESENTACAO COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="H332" s="1" t="n"/>
+      <c r="H332" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I332" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -25866,7 +25926,7 @@
       </c>
       <c r="L332" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M332" s="1" t="inlineStr">
@@ -25877,7 +25937,7 @@
       <c r="N332" s="1" t="n"/>
       <c r="O332" s="1" t="n"/>
       <c r="P332" s="1" t="inlineStr"/>
-      <c r="Q332" s="1" t="n"/>
+      <c r="Q332" s="1" t="inlineStr"/>
       <c r="R332" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -25917,7 +25977,11 @@
           <t>ARAO PEREIRA DE SA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H333" s="1" t="n"/>
+      <c r="H333" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I333" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -25931,7 +25995,7 @@
       </c>
       <c r="L333" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M333" s="1" t="inlineStr">
@@ -25942,7 +26006,7 @@
       <c r="N333" s="1" t="n"/>
       <c r="O333" s="1" t="n"/>
       <c r="P333" s="1" t="inlineStr"/>
-      <c r="Q333" s="1" t="n"/>
+      <c r="Q333" s="1" t="inlineStr"/>
       <c r="R333" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S578" headerRowCount="1">
-  <autoFilter ref="A1:S578"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S575" headerRowCount="1">
+  <autoFilter ref="A1:S575"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S578"/>
+  <dimension ref="A1:S575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43369,7 +43369,7 @@
     </row>
     <row r="570">
       <c r="A570" s="1" t="n">
-        <v>80255</v>
+        <v>80173</v>
       </c>
       <c r="B570" s="1" t="inlineStr">
         <is>
@@ -43383,12 +43383,12 @@
       </c>
       <c r="D570" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E570" s="1" t="inlineStr">
         <is>
-          <t>Boa Tarde Amigos,Podem nos auxiliar na Baixa da Tarefa " Fed - DAS " Colocamos 2 vezes na Baixa Automática mas não está Baixando as tarefas.</t>
+          <t>Bom dia! Por gentileza, poderia realizar a baixa da tarefa DEC 2 quinzena dos clientes abaixo. ISENTO3498	EMPLACA SERVIÇOS LTDA4327	ACCESS EVENTOS E VIAGENS LTDA5780	A Estancia Morro Grande Centro de Reabilitacao Social (Filial 1)5873	FRRD ADMINISTRADORA DE IMOVEIS LTDA5906	A Estancia Morro Grande - Centro de Reabilitacao Social LTDA (Filial 2)5978	HLL LOCADORA DE GUINDASTES LTDA5979	AMATRUDA LOCADORA DE GUINDASTES E ARTICULADOS LTDA6172	MEDICAL DISCOVERY TREINAMENTOS &amp; DESENVOLVIMENTO LTDA.6173	CLINICA TONON DE DERMATOLOGISTA LTDA6266	B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (FILIAL 1)6267	CEO7 - SERVICOS DE MARKETING E APOIO ADMINISTRATIVO LTDA6415	FABIO PEREIRA DA COSTA6416	SINZATO ENTERTAINMENT LTDA6450	RDF VEICULOS LTDA6501	MD TREINAMENTOS E DESENVOLVIMENTO LTDA6652	RAZEC EMPRESA DE APOIO ADMINISTRATIVO LTDA6766	MASTER IN THREADS CURSOS E EVENTOS SPE LTDA6794	C.M.A EDUCACIONAL LTDA6796	COLÉGIO JOAQUIM MARIA MACHADO DE ASSIS LTDA (FILIAL)6798	LFJ TRANSPORTE LTDA6930	DOMENICO BIEMMI FRANCISCO LEITEERRO ( SEM CERTIFICADO)5084	REPUME REPUXAÇÃO E METALURGICA LTDA (FILIAL 01)5292	EZEKY LTDA</t>
         </is>
       </c>
       <c r="F570" s="1" t="n">
@@ -43406,35 +43406,45 @@
         </is>
       </c>
       <c r="J570" s="2" t="n">
-        <v>46192.67904146991</v>
+        <v>46191.36702172454</v>
       </c>
       <c r="K570" s="2" t="n">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="L570" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M570" s="1" t="inlineStr">
         <is>
-          <t>Helmer Dantas</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N570" s="1" t="n"/>
-      <c r="O570" s="1" t="n"/>
-      <c r="P570" s="1" t="inlineStr"/>
-      <c r="Q570" s="1" t="inlineStr"/>
+      <c r="O570" s="2" t="n">
+        <v>46191.38533472222</v>
+      </c>
+      <c r="P570" s="1" t="inlineStr">
+        <is>
+          <t>gamaral</t>
+        </is>
+      </c>
+      <c r="Q570" s="1" t="inlineStr">
+        <is>
+          <t>Tarefas baixadas</t>
+        </is>
+      </c>
       <c r="R570" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S570" s="1" t="n"/>
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
-        <v>80173</v>
+        <v>80174</v>
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
@@ -43443,7 +43453,7 @@
       </c>
       <c r="C571" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Vencimento de Tarefas</t>
         </is>
       </c>
       <c r="D571" s="1" t="inlineStr">
@@ -43453,7 +43463,7 @@
       </c>
       <c r="E571" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderia realizar a baixa da tarefa DEC 2 quinzena dos clientes abaixo. ISENTO3498	EMPLACA SERVIÇOS LTDA4327	ACCESS EVENTOS E VIAGENS LTDA5780	A Estancia Morro Grande Centro de Reabilitacao Social (Filial 1)5873	FRRD ADMINISTRADORA DE IMOVEIS LTDA5906	A Estancia Morro Grande - Centro de Reabilitacao Social LTDA (Filial 2)5978	HLL LOCADORA DE GUINDASTES LTDA5979	AMATRUDA LOCADORA DE GUINDASTES E ARTICULADOS LTDA6172	MEDICAL DISCOVERY TREINAMENTOS &amp; DESENVOLVIMENTO LTDA.6173	CLINICA TONON DE DERMATOLOGISTA LTDA6266	B. HOVE COMERCIO E INDUSTRIA DE PRODUTOS ABRASIVOS LTDA (FILIAL 1)6267	CEO7 - SERVICOS DE MARKETING E APOIO ADMINISTRATIVO LTDA6415	FABIO PEREIRA DA COSTA6416	SINZATO ENTERTAINMENT LTDA6450	RDF VEICULOS LTDA6501	MD TREINAMENTOS E DESENVOLVIMENTO LTDA6652	RAZEC EMPRESA DE APOIO ADMINISTRATIVO LTDA6766	MASTER IN THREADS CURSOS E EVENTOS SPE LTDA6794	C.M.A EDUCACIONAL LTDA6796	COLÉGIO JOAQUIM MARIA MACHADO DE ASSIS LTDA (FILIAL)6798	LFJ TRANSPORTE LTDA6930	DOMENICO BIEMMI FRANCISCO LEITEERRO ( SEM CERTIFICADO)5084	REPUME REPUXAÇÃO E METALURGICA LTDA (FILIAL 01)5292	EZEKY LTDA</t>
+          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
         </is>
       </c>
       <c r="F571" s="1" t="n">
@@ -43471,7 +43481,7 @@
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>46191.36702172454</v>
+        <v>46191.36721832176</v>
       </c>
       <c r="K571" s="2" t="n">
         <v>46192</v>
@@ -43483,12 +43493,12 @@
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N571" s="1" t="n"/>
       <c r="O571" s="2" t="n">
-        <v>46191.38533472222</v>
+        <v>46191.49335512731</v>
       </c>
       <c r="P571" s="1" t="inlineStr">
         <is>
@@ -43509,7 +43519,7 @@
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
-        <v>80174</v>
+        <v>76508</v>
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
@@ -43518,7 +43528,7 @@
       </c>
       <c r="C572" s="1" t="inlineStr">
         <is>
-          <t>Vencimento de Tarefas</t>
+          <t>Verificar Validação Obrigação</t>
         </is>
       </c>
       <c r="D572" s="1" t="inlineStr">
@@ -43528,16 +43538,20 @@
       </c>
       <c r="E572" s="1" t="inlineStr">
         <is>
-          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F572" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G572" s="1" t="n"/>
+        <v>6605</v>
+      </c>
+      <c r="G572" s="1" t="inlineStr">
+        <is>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
+        </is>
+      </c>
       <c r="H572" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I572" s="1" t="inlineStr">
@@ -43546,10 +43560,10 @@
         </is>
       </c>
       <c r="J572" s="2" t="n">
-        <v>46191.36721832176</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K572" s="2" t="n">
-        <v>46192</v>
+        <v>46034</v>
       </c>
       <c r="L572" s="1" t="inlineStr">
         <is>
@@ -43558,21 +43572,21 @@
       </c>
       <c r="M572" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="N572" s="1" t="n"/>
       <c r="O572" s="2" t="n">
-        <v>46191.49335512731</v>
+        <v>46030.75027241898</v>
       </c>
       <c r="P572" s="1" t="inlineStr">
         <is>
-          <t>gamaral</t>
+          <t>nicoleo</t>
         </is>
       </c>
       <c r="Q572" s="1" t="inlineStr">
         <is>
-          <t>Tarefas baixadas</t>
+          <t>Baixadas.</t>
         </is>
       </c>
       <c r="R572" s="1" t="inlineStr">
@@ -43584,7 +43598,7 @@
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
-        <v>80260</v>
+        <v>76505</v>
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
@@ -43593,30 +43607,30 @@
       </c>
       <c r="C573" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Verificar Validação Obrigação</t>
         </is>
       </c>
       <c r="D573" s="1" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E573" s="1" t="inlineStr">
         <is>
-          <t>Esta com erro honorários na baixa do analise, mas a NF esta ativa e lançada. Em anexo o erro e a NF ativa. Poderia me ajudar?</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F573" s="1" t="n">
-        <v>4944</v>
+        <v>6640</v>
       </c>
       <c r="G573" s="1" t="inlineStr">
         <is>
-          <t>THZ WORK TERCEIRIZADA LTDA</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H573" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I573" s="1" t="inlineStr">
@@ -43625,35 +43639,45 @@
         </is>
       </c>
       <c r="J573" s="2" t="n">
-        <v>46192.711678125</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K573" s="2" t="n">
-        <v>46195</v>
+        <v>46034</v>
       </c>
       <c r="L573" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M573" s="1" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="N573" s="1" t="n"/>
-      <c r="O573" s="1" t="n"/>
-      <c r="P573" s="1" t="inlineStr"/>
-      <c r="Q573" s="1" t="inlineStr"/>
+      <c r="O573" s="2" t="n">
+        <v>46030.63182743055</v>
+      </c>
+      <c r="P573" s="1" t="inlineStr">
+        <is>
+          <t>nicoleo</t>
+        </is>
+      </c>
+      <c r="Q573" s="1" t="inlineStr">
+        <is>
+          <t>Baixadas.</t>
+        </is>
+      </c>
       <c r="R573" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S573" s="1" t="n"/>
     </row>
     <row r="574">
       <c r="A574" s="1" t="n">
-        <v>80261</v>
+        <v>76515</v>
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
@@ -43662,30 +43686,30 @@
       </c>
       <c r="C574" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Verificar Validação Obrigação</t>
         </is>
       </c>
       <c r="D574" s="1" t="inlineStr">
         <is>
-          <t>RJ - CTB</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E574" s="1" t="inlineStr">
         <is>
-          <t>Esta com erro honorários na baixa do analise, mas a NF esta ativa e lançada. Em anexo o erro e a NF ativa. Poderia me ajudar?</t>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
         </is>
       </c>
       <c r="F574" s="1" t="n">
-        <v>4946</v>
+        <v>6641</v>
       </c>
       <c r="G574" s="1" t="inlineStr">
         <is>
-          <t>LEAL PRESTAÇÃO DE SERVIÇOS LTDA</t>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
         </is>
       </c>
       <c r="H574" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Nicole Oliveira</t>
         </is>
       </c>
       <c r="I574" s="1" t="inlineStr">
@@ -43694,35 +43718,45 @@
         </is>
       </c>
       <c r="J574" s="2" t="n">
-        <v>46192.71273252315</v>
+        <v>46030.73046079861</v>
       </c>
       <c r="K574" s="2" t="n">
-        <v>46195</v>
+        <v>46034</v>
       </c>
       <c r="L574" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M574" s="1" t="inlineStr">
         <is>
-          <t>Jessica Roque</t>
+          <t>Bianca Castro</t>
         </is>
       </c>
       <c r="N574" s="1" t="n"/>
-      <c r="O574" s="1" t="n"/>
-      <c r="P574" s="1" t="inlineStr"/>
-      <c r="Q574" s="1" t="inlineStr"/>
+      <c r="O574" s="2" t="n">
+        <v>46030.74734336806</v>
+      </c>
+      <c r="P574" s="1" t="inlineStr">
+        <is>
+          <t>nicoleo</t>
+        </is>
+      </c>
+      <c r="Q574" s="1" t="inlineStr">
+        <is>
+          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
+        </is>
+      </c>
       <c r="R574" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S574" s="1" t="n"/>
     </row>
     <row r="575">
       <c r="A575" s="1" t="n">
-        <v>76508</v>
+        <v>76501</v>
       </c>
       <c r="B575" s="1" t="inlineStr">
         <is>
@@ -43741,15 +43775,15 @@
       </c>
       <c r="E575" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
         </is>
       </c>
       <c r="F575" s="1" t="n">
-        <v>6605</v>
+        <v>6641</v>
       </c>
       <c r="G575" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
         </is>
       </c>
       <c r="H575" s="1" t="inlineStr">
@@ -43763,7 +43797,7 @@
         </is>
       </c>
       <c r="J575" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46030.51327708333</v>
       </c>
       <c r="K575" s="2" t="n">
         <v>46034</v>
@@ -43780,7 +43814,7 @@
       </c>
       <c r="N575" s="1" t="n"/>
       <c r="O575" s="2" t="n">
-        <v>46030.75027241898</v>
+        <v>46030.64333047454</v>
       </c>
       <c r="P575" s="1" t="inlineStr">
         <is>
@@ -43798,243 +43832,6 @@
         </is>
       </c>
       <c r="S575" s="1" t="n"/>
-    </row>
-    <row r="576">
-      <c r="A576" s="1" t="n">
-        <v>76505</v>
-      </c>
-      <c r="B576" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C576" s="1" t="inlineStr">
-        <is>
-          <t>Verificar Validação Obrigação</t>
-        </is>
-      </c>
-      <c r="D576" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E576" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
-        </is>
-      </c>
-      <c r="F576" s="1" t="n">
-        <v>6640</v>
-      </c>
-      <c r="G576" s="1" t="inlineStr">
-        <is>
-          <t>FORT FRUIT LTDA</t>
-        </is>
-      </c>
-      <c r="H576" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
-      <c r="I576" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J576" s="2" t="n">
-        <v>46030.60213634259</v>
-      </c>
-      <c r="K576" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="L576" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M576" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N576" s="1" t="n"/>
-      <c r="O576" s="2" t="n">
-        <v>46030.63182743055</v>
-      </c>
-      <c r="P576" s="1" t="inlineStr">
-        <is>
-          <t>nicoleo</t>
-        </is>
-      </c>
-      <c r="Q576" s="1" t="inlineStr">
-        <is>
-          <t>Baixadas.</t>
-        </is>
-      </c>
-      <c r="R576" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S576" s="1" t="n"/>
-    </row>
-    <row r="577">
-      <c r="A577" s="1" t="n">
-        <v>76515</v>
-      </c>
-      <c r="B577" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C577" s="1" t="inlineStr">
-        <is>
-          <t>Verificar Validação Obrigação</t>
-        </is>
-      </c>
-      <c r="D577" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E577" s="1" t="inlineStr">
-        <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
-        </is>
-      </c>
-      <c r="F577" s="1" t="n">
-        <v>6641</v>
-      </c>
-      <c r="G577" s="1" t="inlineStr">
-        <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
-        </is>
-      </c>
-      <c r="H577" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
-      <c r="I577" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J577" s="2" t="n">
-        <v>46030.73046079861</v>
-      </c>
-      <c r="K577" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="L577" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M577" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N577" s="1" t="n"/>
-      <c r="O577" s="2" t="n">
-        <v>46030.74734336806</v>
-      </c>
-      <c r="P577" s="1" t="inlineStr">
-        <is>
-          <t>nicoleo</t>
-        </is>
-      </c>
-      <c r="Q577" s="1" t="inlineStr">
-        <is>
-          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
-        </is>
-      </c>
-      <c r="R577" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S577" s="1" t="n"/>
-    </row>
-    <row r="578">
-      <c r="A578" s="1" t="n">
-        <v>76501</v>
-      </c>
-      <c r="B578" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C578" s="1" t="inlineStr">
-        <is>
-          <t>Verificar Validação Obrigação</t>
-        </is>
-      </c>
-      <c r="D578" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E578" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
-        </is>
-      </c>
-      <c r="F578" s="1" t="n">
-        <v>6641</v>
-      </c>
-      <c r="G578" s="1" t="inlineStr">
-        <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
-        </is>
-      </c>
-      <c r="H578" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
-      <c r="I578" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J578" s="2" t="n">
-        <v>46030.51327708333</v>
-      </c>
-      <c r="K578" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="L578" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M578" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N578" s="1" t="n"/>
-      <c r="O578" s="2" t="n">
-        <v>46030.64333047454</v>
-      </c>
-      <c r="P578" s="1" t="inlineStr">
-        <is>
-          <t>nicoleo</t>
-        </is>
-      </c>
-      <c r="Q578" s="1" t="inlineStr">
-        <is>
-          <t>Baixadas.</t>
-        </is>
-      </c>
-      <c r="R578" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S578" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -1342,7 +1342,11 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="n"/>
-      <c r="H12" s="1" t="n"/>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -1356,7 +1360,7 @@
       </c>
       <c r="L12" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M12" s="1" t="inlineStr">
@@ -1367,7 +1371,7 @@
       <c r="N12" s="1" t="n"/>
       <c r="O12" s="1" t="n"/>
       <c r="P12" s="1" t="inlineStr"/>
-      <c r="Q12" s="1" t="n"/>
+      <c r="Q12" s="1" t="inlineStr"/>
       <c r="R12" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -1962,7 +1966,11 @@
           <t>BANDEIRANTES REFRIGERAÇÃO COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="H20" s="1" t="n"/>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -1976,7 +1984,7 @@
       </c>
       <c r="L20" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M20" s="1" t="inlineStr">
@@ -1987,7 +1995,7 @@
       <c r="N20" s="1" t="n"/>
       <c r="O20" s="1" t="n"/>
       <c r="P20" s="1" t="inlineStr"/>
-      <c r="Q20" s="1" t="n"/>
+      <c r="Q20" s="1" t="inlineStr"/>
       <c r="R20" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -4221,7 +4229,11 @@
           <t>SUPERMERCADO MAGNATA LTDA</t>
         </is>
       </c>
-      <c r="H49" s="1" t="n"/>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>Ana Barbosa</t>
+        </is>
+      </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -4235,7 +4247,7 @@
       </c>
       <c r="L49" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M49" s="1" t="inlineStr">
@@ -4246,7 +4258,7 @@
       <c r="N49" s="1" t="n"/>
       <c r="O49" s="1" t="n"/>
       <c r="P49" s="1" t="inlineStr"/>
-      <c r="Q49" s="1" t="n"/>
+      <c r="Q49" s="1" t="inlineStr"/>
       <c r="R49" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -7290,26 +7302,26 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>80224</v>
+        <v>80235</v>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>PER/DCOMP - Intimação/Comunicado</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>PER/DCOMP - Intimação/Comunicado</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D89" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
         <is>
-          <t>3464 - SUPERMERCADO VICALI PARATY LTDA 				(28.466.073/0001-92)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Segue notificação em anexo.Qualquer duvida estou a disposição.</t>
+          <t xml:space="preserve">Por gentileza, avaliar debito em aberto na SF inerente a PIS/COFINS. </t>
         </is>
       </c>
       <c r="F89" s="1" t="n">
@@ -7322,63 +7334,74 @@
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="I89" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>46191.71619447917</v>
+        <v>46192.46505482639</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M89" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="N89" s="1" t="n"/>
-      <c r="O89" s="1" t="n"/>
-      <c r="P89" s="1" t="inlineStr"/>
-      <c r="Q89" s="1" t="inlineStr"/>
+      <c r="O89" s="2" t="n">
+        <v>46192.68080598379</v>
+      </c>
+      <c r="P89" s="1" t="inlineStr">
+        <is>
+          <t>fernandaa</t>
+        </is>
+      </c>
+      <c r="Q89" s="1" t="inlineStr">
+        <is>
+          <t>A divergencia é porque o valor pago de PIS e COFINS esta diferente do valor apurado.
+Não identificamos perdcomp para esses tributos.</t>
+        </is>
+      </c>
       <c r="R89" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S89" s="1" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>80235</v>
+        <v>80224</v>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>PER/DCOMP - Intimação/Comunicado</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>PER/DCOMP - Intimação/Comunicado</t>
         </is>
       </c>
       <c r="D90" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E90" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, avaliar debito em aberto na SF inerente a PIS/COFINS. </t>
+          <t>3464 - SUPERMERCADO VICALI PARATY LTDA 				(28.466.073/0001-92)Boa tarde, prezados!!Por gentileza, verificar e tomar as devidas providencias, referente a notificação recepcionada no ECAC, sobre: IRREGULARIDADES NA UTILIZAÇÃO DE CRÉDITOS DE PIS/COFINS.Segue notificação em anexo.Qualquer duvida estou a disposição.</t>
         </is>
       </c>
       <c r="F90" s="1" t="n">
@@ -7391,48 +7414,37 @@
       </c>
       <c r="H90" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I90" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>46192.46505482639</v>
+        <v>46191.71619447917</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="L90" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M90" s="1" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N90" s="1" t="n"/>
-      <c r="O90" s="2" t="n">
-        <v>46192.68080598379</v>
-      </c>
-      <c r="P90" s="1" t="inlineStr">
-        <is>
-          <t>fernandaa</t>
-        </is>
-      </c>
-      <c r="Q90" s="1" t="inlineStr">
-        <is>
-          <t>A divergencia é porque o valor pago de PIS e COFINS esta diferente do valor apurado.
-Não identificamos perdcomp para esses tributos.</t>
-        </is>
-      </c>
+      <c r="O90" s="1" t="n"/>
+      <c r="P90" s="1" t="inlineStr"/>
+      <c r="Q90" s="1" t="inlineStr"/>
       <c r="R90" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S90" s="1" t="n"/>
@@ -7787,7 +7799,11 @@
           <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
-      <c r="H95" s="1" t="n"/>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I95" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -7801,7 +7817,7 @@
       </c>
       <c r="L95" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M95" s="1" t="inlineStr">
@@ -7812,7 +7828,7 @@
       <c r="N95" s="1" t="n"/>
       <c r="O95" s="1" t="n"/>
       <c r="P95" s="1" t="inlineStr"/>
-      <c r="Q95" s="1" t="n"/>
+      <c r="Q95" s="1" t="inlineStr"/>
       <c r="R95" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -9551,16 +9567,16 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>80158</v>
+        <v>80168</v>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Termos de Intimação</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D118" s="1" t="inlineStr">
@@ -9570,29 +9586,29 @@
       </c>
       <c r="E118" s="1" t="inlineStr">
         <is>
-          <t>Verificar  a Pendência na conta fiscal  do IPI l 03.2026 saldo 47.157,32 -Darf e comprovante anexo para analise analisar o Mit. Após a análise, caso esteja tudo correto, por gentileza me informe. Solicitarei a correção por meio de processo junto à SEFAZ, com o apoio da Paralegal. Prazo 19.06.2026</t>
+          <t>A D&amp;T recebeu uma carta de cobrança referente aos débitos de IRPJ  e CSLL do 4º trimestre de 2021. A Inara informou que não deveria existir saldo devedor, pois houve compensação desses tributos à época.  Prazo 22.06.2026 (Dna Inara pede urgência na analise)</t>
         </is>
       </c>
       <c r="F118" s="1" t="n">
-        <v>4219</v>
+        <v>4220</v>
       </c>
       <c r="G118" s="1" t="inlineStr">
         <is>
-          <t>REPUME REPUXAÇÃO E METALÚRGICA LTDA</t>
+          <t>D&amp;T BRASIL INDUSTRIA DE ELETRÔNICOS LTDA</t>
         </is>
       </c>
       <c r="H118" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>46190.6549837963</v>
+        <v>46190.77325285879</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>46192</v>
@@ -9607,221 +9623,217 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N118" s="1" t="n"/>
+      <c r="N118" s="2" t="n">
+        <v>46192.44483642361</v>
+      </c>
       <c r="O118" s="2" t="n">
-        <v>46191.48537488426</v>
+        <v>46192.4474815625</v>
       </c>
       <c r="P118" s="1" t="inlineStr">
         <is>
-          <t>inascimento</t>
+          <t>pvolpe</t>
         </is>
       </c>
       <c r="Q118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MIT Retificado- era diferença no codigo </t>
-        </is>
-      </c>
-      <c r="R118" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S118" s="1" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>80168</v>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>Termos de Intimação</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>Receita Federal</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t>A D&amp;T recebeu uma carta de cobrança referente aos débitos de IRPJ  e CSLL do 4º trimestre de 2021. A Inara informou que não deveria existir saldo devedor, pois houve compensação desses tributos à época.  Prazo 22.06.2026 (Dna Inara pede urgência na analise)</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="n">
-        <v>4220</v>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t>D&amp;T BRASIL INDUSTRIA DE ELETRÔNICOS LTDA</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="I119" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="n">
-        <v>46190.77325285879</v>
-      </c>
-      <c r="K119" s="2" t="n">
-        <v>46192</v>
-      </c>
-      <c r="L119" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M119" s="1" t="inlineStr">
-        <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N119" s="2" t="n">
-        <v>46192.44483642361</v>
-      </c>
-      <c r="O119" s="2" t="n">
-        <v>46192.4474815625</v>
-      </c>
-      <c r="P119" s="1" t="inlineStr">
-        <is>
-          <t>pvolpe</t>
-        </is>
-      </c>
-      <c r="Q119" s="1" t="inlineStr">
         <is>
           <t>Bom Dia, prezados 
 A perdcomp foi indeferida no processo e a perdcomp na época fi realizada pela Marilia do CTB. 
 Por favor, abrir um chamado ao CTBI para a realização  da validação do indeferfimento.</t>
         </is>
       </c>
-      <c r="R119" s="1" t="inlineStr">
+      <c r="R118" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="S119" s="1" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="S118" s="1" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
         <v>80177</v>
       </c>
-      <c r="B120" s="1" t="inlineStr">
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t>Termos de Intimação</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t>Receita Federal</t>
         </is>
       </c>
-      <c r="D120" s="1" t="inlineStr">
+      <c r="D119" s="1" t="inlineStr">
         <is>
           <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E120" s="1" t="inlineStr">
+      <c r="E119" s="1" t="inlineStr">
         <is>
           <t>Bom dia! Segue intimação. CARTA - COBRANÇA - COB/ECOB/DEVAT02</t>
         </is>
       </c>
-      <c r="F120" s="1" t="n">
+      <c r="F119" s="1" t="n">
         <v>4220</v>
       </c>
-      <c r="G120" s="1" t="inlineStr">
+      <c r="G119" s="1" t="inlineStr">
         <is>
           <t>D&amp;T BRASIL INDUSTRIA DE ELETRÔNICOS LTDA</t>
         </is>
       </c>
-      <c r="H120" s="1" t="inlineStr">
+      <c r="H119" s="1" t="inlineStr">
         <is>
           <t>Priscila Volpe</t>
         </is>
       </c>
-      <c r="I120" s="1" t="inlineStr">
+      <c r="I119" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
-      <c r="J120" s="2" t="n">
+      <c r="J119" s="2" t="n">
         <v>46191.38164320602</v>
       </c>
-      <c r="K120" s="2" t="n">
+      <c r="K119" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="L120" s="1" t="inlineStr">
+      <c r="L119" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M120" s="1" t="inlineStr">
+      <c r="M119" s="1" t="inlineStr">
         <is>
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N120" s="1" t="n"/>
-      <c r="O120" s="2" t="n">
+      <c r="N119" s="1" t="n"/>
+      <c r="O119" s="2" t="n">
         <v>46192.44560752315</v>
       </c>
-      <c r="P120" s="1" t="inlineStr">
+      <c r="P119" s="1" t="inlineStr">
         <is>
           <t>pvolpe</t>
         </is>
       </c>
-      <c r="Q120" s="1" t="inlineStr">
+      <c r="Q119" s="1" t="inlineStr">
         <is>
           <t>Bom Dia, prezados 
 A perdcomp foi indeferida no processo e a perdcomp na época fi realizada pela Marilia do CTB. 
 Por favor, abrir um chamado ao CTBI para a realização  da validação do indeferfimento.</t>
         </is>
       </c>
+      <c r="R119" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S119" s="1" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>80112</v>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, verificar o transporte de saldo incorreto referente o mes 03/2026 conforme imagem anexa. Qualquer duvida sigo a disposição</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>4272</v>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>MERCADINHO J. SILVA - EIRELI</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>46189.68182241898</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>46190</v>
+      </c>
+      <c r="L120" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M120" s="1" t="inlineStr">
+        <is>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="n">
+        <v>46190.48067052083</v>
+      </c>
+      <c r="O120" s="1" t="n"/>
+      <c r="P120" s="1" t="inlineStr"/>
+      <c r="Q120" s="1" t="inlineStr">
+        <is>
+          <t>verificando.</t>
+        </is>
+      </c>
       <c r="R120" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S120" s="1" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>80112</v>
+        <v>79799</v>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, verificar o transporte de saldo incorreto referente o mes 03/2026 conforme imagem anexa. Qualquer duvida sigo a disposição</t>
+          <t>Segue em anexo mensagem DEC Estadual do cliente: 4319 - SUPERMERCADO SANTA MARIA LTDAComplemento do Assunto: EFD substitutiva pendente de pagamento de taxa</t>
         </is>
       </c>
       <c r="F121" s="1" t="n">
-        <v>4272</v>
+        <v>4319</v>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t>MERCADINHO J. SILVA - EIRELI</t>
+          <t>SUPERMERCADO SANTA MARIA LTDA</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
@@ -9831,33 +9843,31 @@
       </c>
       <c r="I121" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>46189.68182241898</v>
+        <v>46182.64187924768</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>46190</v>
+        <v>46189</v>
       </c>
       <c r="L121" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M121" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N121" s="2" t="n">
-        <v>46190.48067052083</v>
-      </c>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N121" s="1" t="n"/>
       <c r="O121" s="1" t="n"/>
       <c r="P121" s="1" t="inlineStr"/>
       <c r="Q121" s="1" t="inlineStr">
         <is>
-          <t>verificando.</t>
+          <t>Verificando.</t>
         </is>
       </c>
       <c r="R121" s="1" t="inlineStr">
@@ -9865,20 +9875,24 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="S121" s="1" t="n"/>
+      <c r="S121" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>79799</v>
+        <v>79464</v>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -9888,49 +9902,51 @@
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t>Segue em anexo mensagem DEC Estadual do cliente: 4319 - SUPERMERCADO SANTA MARIA LTDAComplemento do Assunto: EFD substitutiva pendente de pagamento de taxa</t>
+          <t>Boa tarde! Segue malha fiscal.  Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
         </is>
       </c>
       <c r="F122" s="1" t="n">
-        <v>4319</v>
+        <v>4327</v>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO SANTA MARIA LTDA</t>
+          <t>ACCESS EVENTOS E VIAGENS LTDA</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="I122" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>46182.64187924768</v>
+        <v>46168.51368692129</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>46189</v>
+        <v>46170</v>
       </c>
       <c r="L122" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M122" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N122" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="n">
+        <v>46180.42641712963</v>
+      </c>
       <c r="O122" s="1" t="n"/>
       <c r="P122" s="1" t="inlineStr"/>
       <c r="Q122" s="1" t="inlineStr">
         <is>
-          <t>Verificando.</t>
+          <t>RETORNO ATÉ 25/06/2026 - EM ANALISE</t>
         </is>
       </c>
       <c r="R122" s="1" t="inlineStr">
@@ -9938,34 +9954,30 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="S122" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
+      <c r="S122" s="1" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>79464</v>
+        <v>80141</v>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Segue malha fiscal.  Divergências entre os valores a pagar de IRPJ e CSLL apurados na Escrituração Contábil Fiscal (ECF) e os valores informados em Declarações de Débitos e Créditos Tributários Federais (DCTF).QUAL O PRAZO PARA REGULARIZAÇÃO?Até o dia 31/07/2026.</t>
+          <t xml:space="preserve">Por gentileza encaminhar Balanço e DRE dos últimos 3 anos da ECD. </t>
         </is>
       </c>
       <c r="F123" s="1" t="n">
@@ -9978,50 +9990,54 @@
       </c>
       <c r="H123" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I123" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>46168.51368692129</v>
+        <v>46190.48975185185</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>46170</v>
+        <v>46191</v>
       </c>
       <c r="L123" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M123" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N123" s="2" t="n">
-        <v>46180.42641712963</v>
-      </c>
-      <c r="O123" s="1" t="n"/>
-      <c r="P123" s="1" t="inlineStr"/>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N123" s="1" t="n"/>
+      <c r="O123" s="2" t="n">
+        <v>46195.71893035879</v>
+      </c>
+      <c r="P123" s="1" t="inlineStr">
+        <is>
+          <t>erikas</t>
+        </is>
+      </c>
       <c r="Q123" s="1" t="inlineStr">
         <is>
-          <t>RETORNO ATÉ 25/06/2026 - EM ANALISE</t>
+          <t>Segue</t>
         </is>
       </c>
       <c r="R123" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S123" s="1" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>80141</v>
+        <v>80471</v>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
@@ -10040,15 +10056,15 @@
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza encaminhar Balanço e DRE dos últimos 3 anos da ECD. </t>
+          <t>Por gentileza encaminhar balanço e DRE referente 2025</t>
         </is>
       </c>
       <c r="F124" s="1" t="n">
-        <v>4327</v>
+        <v>4359</v>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t>ACCESS EVENTOS E VIAGENS LTDA</t>
+          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr">
@@ -10062,14 +10078,14 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>46190.48975185185</v>
+        <v>46196.41235833333</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>46191</v>
+        <v>46197</v>
       </c>
       <c r="L124" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M124" s="1" t="inlineStr">
@@ -10078,29 +10094,19 @@
         </is>
       </c>
       <c r="N124" s="1" t="n"/>
-      <c r="O124" s="2" t="n">
-        <v>46195.71893035879</v>
-      </c>
-      <c r="P124" s="1" t="inlineStr">
-        <is>
-          <t>erikas</t>
-        </is>
-      </c>
-      <c r="Q124" s="1" t="inlineStr">
-        <is>
-          <t>Segue</t>
-        </is>
-      </c>
+      <c r="O124" s="1" t="n"/>
+      <c r="P124" s="1" t="inlineStr"/>
+      <c r="Q124" s="1" t="inlineStr"/>
       <c r="R124" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S124" s="1" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>80471</v>
+        <v>79608</v>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
@@ -10114,90 +10120,104 @@
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza encaminhar balanço e DRE referente 2025</t>
+          <t>Bom dia!!Por gentileza, gerar BALANÇO E DRE 2025 da empresa 4371.</t>
         </is>
       </c>
       <c r="F125" s="1" t="n">
-        <v>4359</v>
+        <v>4371</v>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS</t>
-        </is>
-      </c>
-      <c r="H125" s="1" t="n"/>
+          <t>SUPERMERCADO XODO LTDA</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>Danielle Silva</t>
+        </is>
+      </c>
       <c r="I125" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>46196.41235833333</v>
+        <v>46175.47560806713</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>46197</v>
+        <v>46176</v>
       </c>
       <c r="L125" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M125" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Yasmin Peixoto</t>
         </is>
       </c>
       <c r="N125" s="1" t="n"/>
-      <c r="O125" s="1" t="n"/>
-      <c r="P125" s="1" t="inlineStr"/>
-      <c r="Q125" s="1" t="n"/>
+      <c r="O125" s="2" t="n">
+        <v>46181.60018538195</v>
+      </c>
+      <c r="P125" s="1" t="inlineStr">
+        <is>
+          <t>danielles</t>
+        </is>
+      </c>
+      <c r="Q125" s="1" t="inlineStr">
+        <is>
+          <t>Enviado por e-mail dia 08/06/2026.</t>
+        </is>
+      </c>
       <c r="R125" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S125" s="1" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>79608</v>
+        <v>80213</v>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, gerar BALANÇO E DRE 2025 da empresa 4371.</t>
+          <t>Por gentileza enviar:Memoria de Calculo IRPJ/CSLL - 01/2025 a 05/2026Controle Patrimonial com Depreciação Mensal - 06/2021 a 05/2026</t>
         </is>
       </c>
       <c r="F126" s="1" t="n">
-        <v>4371</v>
+        <v>4396</v>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO XODO LTDA</t>
+          <t>SAMPA ATACADO DE GENEROS ALIMENTICIOS E BEBIDAS LTDA</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr">
         <is>
-          <t>Danielle Silva</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="I126" s="1" t="inlineStr">
@@ -10206,38 +10226,28 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>46175.47560806713</v>
+        <v>46191.64893958333</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>46176</v>
+        <v>46192</v>
       </c>
       <c r="L126" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M126" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N126" s="1" t="n"/>
-      <c r="O126" s="2" t="n">
-        <v>46181.60018538195</v>
-      </c>
-      <c r="P126" s="1" t="inlineStr">
-        <is>
-          <t>danielles</t>
-        </is>
-      </c>
-      <c r="Q126" s="1" t="inlineStr">
-        <is>
-          <t>Enviado por e-mail dia 08/06/2026.</t>
-        </is>
-      </c>
+      <c r="O126" s="1" t="n"/>
+      <c r="P126" s="1" t="inlineStr"/>
+      <c r="Q126" s="1" t="inlineStr"/>
       <c r="R126" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S126" s="1" t="n"/>
@@ -10281,7 +10291,7 @@
       </c>
       <c r="I127" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
@@ -10292,7 +10302,7 @@
       </c>
       <c r="L127" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M127" s="1" t="inlineStr">
@@ -10300,9 +10310,7 @@
           <t>Rogerio Egidio</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
-        <v>46195.56635929398</v>
-      </c>
+      <c r="N127" s="1" t="n"/>
       <c r="O127" s="1" t="n"/>
       <c r="P127" s="1" t="inlineStr"/>
       <c r="Q127" s="1" t="inlineStr">
@@ -10316,20 +10324,24 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="S127" s="1" t="n"/>
+      <c r="S127" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>80213</v>
+        <v>80228</v>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Solicitação de Documentação</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
@@ -10339,36 +10351,32 @@
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza enviar:Memoria de Calculo IRPJ/CSLL - 01/2025 a 05/2026Controle Patrimonial com Depreciação Mensal - 06/2021 a 05/2026</t>
+          <t>Bom dia!!Por gentileza, enviar MANAD ou resumo de Folha Mensal 06/2021 a 07/2024</t>
         </is>
       </c>
       <c r="F128" s="1" t="n">
-        <v>4396</v>
+        <v>4397</v>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t>SAMPA ATACADO DE GENEROS ALIMENTICIOS E BEBIDAS LTDA</t>
-        </is>
-      </c>
-      <c r="H128" s="1" t="inlineStr">
-        <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
+          <t>SAMPATACADO DE GENEROS ALIMENTÍCIOS E BEBIDAS LTDA (FILIAL 01)</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="n"/>
       <c r="I128" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>46191.64893958333</v>
+        <v>46192.39995659722</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>46192</v>
+        <v>46195</v>
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M128" s="1" t="inlineStr">
@@ -10379,7 +10387,7 @@
       <c r="N128" s="1" t="n"/>
       <c r="O128" s="1" t="n"/>
       <c r="P128" s="1" t="inlineStr"/>
-      <c r="Q128" s="1" t="inlineStr"/>
+      <c r="Q128" s="1" t="n"/>
       <c r="R128" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -10389,72 +10397,86 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>80228</v>
+        <v>76499</v>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentação</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, enviar MANAD ou resumo de Folha Mensal 06/2021 a 07/2024</t>
+          <t>ADTO CLIENTES/FORNECEDORES/EMPRÉTIMOS A RECEBER	Avaliar valores constantes nestas contas de : ADTO FORNECEDOR, CLIENTES e EPRÉSTIMOS A RECEBER, se alguns destes valores poderiam ser empréstimos à sócios e que podem distribuidos em 2025, exceto adto de clientes que precisa identificação de qual cliente se refere a baixa considerando que o cliente não recebe se não emitir nota fiscal.PENDÊNCIA FEDERAL: SALDOS	"Cliente precisa apresentar ao cliente CND megativa, ocorre que na última reunião de 2/10/2025 foi apontado: Avaliar Pendência - Débito (SIEF)CNPJ: 14.237.012/0001-49Receita PA/Exerc. Dt. Vcto Vl. Original Sdo. Devedor Multa Juros Sdo. Dev. Cons. Situação0561-07 - IRRF 06/2021 20/07/2021 2.766,99 8,07 1,61 3,77 13,45 DEVEDOR0561-07 - IRRF 07/2021 20/08/2021 341,07 1,12 0,22 0,51 1,85 DEVEDOR1082-21 - CP-SEGUR. 2024 20/12/2024 7.090,18 95,94 19,18 9,30 124,42 DEVEDOR1646-21 - CP-PATRONAL 2024 20/12/2024 1.267,43 19,19 3,83 1,86 24,88 DEVEDORTomar medidas imediatas para regularização."</t>
         </is>
       </c>
       <c r="F129" s="1" t="n">
-        <v>4397</v>
+        <v>4422</v>
       </c>
       <c r="G129" s="1" t="inlineStr">
         <is>
-          <t>SAMPATACADO DE GENEROS ALIMENTÍCIOS E BEBIDAS LTDA (FILIAL 01)</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="n"/>
+          <t>ALL SERVICE INSTALAÇÕES E SERVIÇOS LTDA</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="I129" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>46192.39995659722</v>
+        <v>46030.51013417824</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>46195</v>
+        <v>46037</v>
       </c>
       <c r="L129" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M129" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N129" s="1" t="n"/>
-      <c r="O129" s="1" t="n"/>
-      <c r="P129" s="1" t="inlineStr"/>
-      <c r="Q129" s="1" t="n"/>
+      <c r="O129" s="2" t="n">
+        <v>46113.60901288194</v>
+      </c>
+      <c r="P129" s="1" t="inlineStr">
+        <is>
+          <t>tatiana</t>
+        </is>
+      </c>
+      <c r="Q129" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
       <c r="R129" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S129" s="1" t="n"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>76499</v>
+        <v>76368</v>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
@@ -10473,7 +10495,7 @@
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t>ADTO CLIENTES/FORNECEDORES/EMPRÉTIMOS A RECEBER	Avaliar valores constantes nestas contas de : ADTO FORNECEDOR, CLIENTES e EPRÉSTIMOS A RECEBER, se alguns destes valores poderiam ser empréstimos à sócios e que podem distribuidos em 2025, exceto adto de clientes que precisa identificação de qual cliente se refere a baixa considerando que o cliente não recebe se não emitir nota fiscal.PENDÊNCIA FEDERAL: SALDOS	"Cliente precisa apresentar ao cliente CND megativa, ocorre que na última reunião de 2/10/2025 foi apontado: Avaliar Pendência - Débito (SIEF)CNPJ: 14.237.012/0001-49Receita PA/Exerc. Dt. Vcto Vl. Original Sdo. Devedor Multa Juros Sdo. Dev. Cons. Situação0561-07 - IRRF 06/2021 20/07/2021 2.766,99 8,07 1,61 3,77 13,45 DEVEDOR0561-07 - IRRF 07/2021 20/08/2021 341,07 1,12 0,22 0,51 1,85 DEVEDOR1082-21 - CP-SEGUR. 2024 20/12/2024 7.090,18 95,94 19,18 9,30 124,42 DEVEDOR1646-21 - CP-PATRONAL 2024 20/12/2024 1.267,43 19,19 3,83 1,86 24,88 DEVEDORTomar medidas imediatas para regularização."</t>
+          <t>PENDÊNCIA FEDERAL: SALDOS	"Cliente precisa apresentar ao cliente CND megativa, ocorre que na última reunião de 2/10/2025 foi apontado: Avaliar Pendência - Débito (SIEF)CNPJ: 14.237.012/0001-49Receita PA/Exerc. Dt. Vcto Vl. Original Sdo. Devedor Multa Juros Sdo. Dev. Cons. Situação0561-07 - IRRF 06/2021 20/07/2021 2.766,99 8,07 1,61 3,77 13,45 DEVEDOR0561-07 - IRRF 07/2021 20/08/2021 341,07 1,12 0,22 0,51 1,85 DEVEDOR1082-21 - CP-SEGUR. 2024 20/12/2024 7.090,18 95,94 19,18 9,30 124,42 DEVEDOR1646-21 - CP-PATRONAL 2024 20/12/2024 1.267,43 19,19 3,83 1,86 24,88 DEVEDORInfelizmente ainda pendente, Tomar medidas imediatas para regularização."</t>
         </is>
       </c>
       <c r="F130" s="1" t="n">
@@ -10495,10 +10517,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>46030.51013417824</v>
+        <v>46024.65297202546</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>46037</v>
+        <v>46031</v>
       </c>
       <c r="L130" s="1" t="inlineStr">
         <is>
@@ -10512,7 +10534,7 @@
       </c>
       <c r="N130" s="1" t="n"/>
       <c r="O130" s="2" t="n">
-        <v>46113.60901288194</v>
+        <v>46113.60221331019</v>
       </c>
       <c r="P130" s="1" t="inlineStr">
         <is>
@@ -10533,16 +10555,16 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>76368</v>
+        <v>79643</v>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
@@ -10552,176 +10574,176 @@
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>PENDÊNCIA FEDERAL: SALDOS	"Cliente precisa apresentar ao cliente CND megativa, ocorre que na última reunião de 2/10/2025 foi apontado: Avaliar Pendência - Débito (SIEF)CNPJ: 14.237.012/0001-49Receita PA/Exerc. Dt. Vcto Vl. Original Sdo. Devedor Multa Juros Sdo. Dev. Cons. Situação0561-07 - IRRF 06/2021 20/07/2021 2.766,99 8,07 1,61 3,77 13,45 DEVEDOR0561-07 - IRRF 07/2021 20/08/2021 341,07 1,12 0,22 0,51 1,85 DEVEDOR1082-21 - CP-SEGUR. 2024 20/12/2024 7.090,18 95,94 19,18 9,30 124,42 DEVEDOR1646-21 - CP-PATRONAL 2024 20/12/2024 1.267,43 19,19 3,83 1,86 24,88 DEVEDORInfelizmente ainda pendente, Tomar medidas imediatas para regularização."</t>
+          <t>segue autorregularização do cliente 4457 - yara design e decoração ltda</t>
         </is>
       </c>
       <c r="F131" s="1" t="n">
-        <v>4422</v>
+        <v>4457</v>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>ALL SERVICE INSTALAÇÕES E SERVIÇOS LTDA</t>
+          <t>YARA DESIGN E DECORAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46024.65297202546</v>
+        <v>46175.70834563657</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>46031</v>
+        <v>46182</v>
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N131" s="1" t="n"/>
-      <c r="O131" s="2" t="n">
-        <v>46113.60221331019</v>
-      </c>
-      <c r="P131" s="1" t="inlineStr">
-        <is>
-          <t>tatiana</t>
-        </is>
-      </c>
+      <c r="O131" s="1" t="n"/>
+      <c r="P131" s="1" t="inlineStr"/>
       <c r="Q131" s="1" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">Verificando. </t>
         </is>
       </c>
       <c r="R131" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S131" s="1" t="n"/>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="S131" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>79643</v>
+        <v>80147</v>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
         <is>
-          <t>segue autorregularização do cliente 4457 - yara design e decoração ltda</t>
+          <t>CAP  mês 04 - Necessário verificar esses 6 participantes que estão com divergência entre o arquivo do cliente e nosso Balancete.Necessário desse retorno HOJE para o cliente repassar aos investidores. Grato</t>
         </is>
       </c>
       <c r="F132" s="1" t="n">
-        <v>4457</v>
+        <v>4527</v>
       </c>
       <c r="G132" s="1" t="inlineStr">
         <is>
-          <t>YARA DESIGN E DECORAÇÃO LTDA</t>
+          <t>SMART BREAK COMERCIO LANCHES S.A.</t>
         </is>
       </c>
       <c r="H132" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Rachel Lima</t>
         </is>
       </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>46175.70834563657</v>
+        <v>46190.50748202546</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="L132" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M132" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N132" s="1" t="n"/>
-      <c r="O132" s="1" t="n"/>
-      <c r="P132" s="1" t="inlineStr"/>
+      <c r="O132" s="2" t="n">
+        <v>46190.62353538194</v>
+      </c>
+      <c r="P132" s="1" t="inlineStr">
+        <is>
+          <t>rachell</t>
+        </is>
+      </c>
       <c r="Q132" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verificando. </t>
+          <t>posicionado por e-mail, para o Gerente de Contas.</t>
         </is>
       </c>
       <c r="R132" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="S132" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S132" s="1" t="n"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>80147</v>
+        <v>77047</v>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>CAP  mês 04 - Necessário verificar esses 6 participantes que estão com divergência entre o arquivo do cliente e nosso Balancete.Necessário desse retorno HOJE para o cliente repassar aos investidores. Grato</t>
+          <t>Correção Estoques:Por gentileza, corrigir os estoques no mês 12/2025 para o valor de R$ 401.327,29.</t>
         </is>
       </c>
       <c r="F133" s="1" t="n">
-        <v>4527</v>
+        <v>4545</v>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t>SMART BREAK COMERCIO LANCHES S.A.</t>
+          <t>BF COMERCIO DE ARTIGOS PARA FESTAS, EMBALAGENS E ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H133" s="1" t="inlineStr">
         <is>
-          <t>Rachel Lima</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I133" s="1" t="inlineStr">
@@ -10730,10 +10752,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46190.50748202546</v>
+        <v>46059.65848981481</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>46190</v>
+        <v>46066</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
@@ -10742,21 +10764,21 @@
       </c>
       <c r="M133" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>mtoledo</t>
         </is>
       </c>
       <c r="N133" s="1" t="n"/>
       <c r="O133" s="2" t="n">
-        <v>46190.62353538194</v>
+        <v>46113.6337659375</v>
       </c>
       <c r="P133" s="1" t="inlineStr">
         <is>
-          <t>rachell</t>
+          <t>tatiana</t>
         </is>
       </c>
       <c r="Q133" s="1" t="inlineStr">
         <is>
-          <t>posicionado por e-mail, para o Gerente de Contas.</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="R133" s="1" t="inlineStr">
@@ -10768,7 +10790,7 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>77047</v>
+        <v>76375</v>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
@@ -10787,32 +10809,32 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>Correção Estoques:Por gentileza, corrigir os estoques no mês 12/2025 para o valor de R$ 401.327,29.</t>
+          <t>SIMPLES NACIONAL 09/2025	Cliente recebeu duas DARFs de valores diferentes e recolheu os valores d alí constantes, com a referência 09/2025. Levantar recolhimentos e confirmar autenticidade das remessas de duas guias para recolhimento e o que poderá ser feito com o saldo supostamente pago em duplicidade.</t>
         </is>
       </c>
       <c r="F134" s="1" t="n">
-        <v>4545</v>
+        <v>4593</v>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t>BF COMERCIO DE ARTIGOS PARA FESTAS, EMBALAGENS E ALIMENTOS LTDA</t>
+          <t>EKIIM RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46059.65848981481</v>
+        <v>46024.6679871875</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>46066</v>
+        <v>46031</v>
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
@@ -10821,21 +10843,23 @@
       </c>
       <c r="M134" s="1" t="inlineStr">
         <is>
-          <t>mtoledo</t>
-        </is>
-      </c>
-      <c r="N134" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="n">
+        <v>46122.57300196759</v>
+      </c>
       <c r="O134" s="2" t="n">
-        <v>46113.6337659375</v>
+        <v>46182.73449135417</v>
       </c>
       <c r="P134" s="1" t="inlineStr">
         <is>
-          <t>tatiana</t>
+          <t>pvolpe</t>
         </is>
       </c>
       <c r="Q134" s="1" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t>resolvido</t>
         </is>
       </c>
       <c r="R134" s="1" t="inlineStr">
@@ -10847,7 +10871,7 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>76375</v>
+        <v>76806</v>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
@@ -10866,32 +10890,32 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>SIMPLES NACIONAL 09/2025	Cliente recebeu duas DARFs de valores diferentes e recolheu os valores d alí constantes, com a referência 09/2025. Levantar recolhimentos e confirmar autenticidade das remessas de duas guias para recolhimento e o que poderá ser feito com o saldo supostamente pago em duplicidade.</t>
+          <t>Reclassificação AVCB	Reclassificar as despesas atualmente lançadas em "Seguro Incêndio" para a conta de despesas com AVCB (Documentação Predial), conforme solicitado pelo cliente.</t>
         </is>
       </c>
       <c r="F135" s="1" t="n">
-        <v>4593</v>
+        <v>4610</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>EKIIM RESTAURANTE LTDA</t>
+          <t>JARDIM ELÉTRICO PRODUÇÕES LTDA</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46024.6679871875</v>
+        <v>46048.46379232639</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>46031</v>
+        <v>46055</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -10903,20 +10927,18 @@
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N135" s="2" t="n">
-        <v>46122.57300196759</v>
-      </c>
+      <c r="N135" s="1" t="n"/>
       <c r="O135" s="2" t="n">
-        <v>46182.73449135417</v>
+        <v>46113.62079417824</v>
       </c>
       <c r="P135" s="1" t="inlineStr">
         <is>
-          <t>pvolpe</t>
+          <t>tatiana</t>
         </is>
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>resolvido</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr">
@@ -10928,7 +10950,7 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>76806</v>
+        <v>78342</v>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
@@ -10947,7 +10969,7 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>Reclassificação AVCB	Reclassificar as despesas atualmente lançadas em "Seguro Incêndio" para a conta de despesas com AVCB (Documentação Predial), conforme solicitado pelo cliente.</t>
+          <t>Pendências estaduais	"Em consulta fiscal atualizada, foram identificadas pendências estaduais em aberto, por gentileza verificar"</t>
         </is>
       </c>
       <c r="F136" s="1" t="n">
@@ -10960,19 +10982,19 @@
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I136" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46048.46379232639</v>
+        <v>46112.41193811342</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>46055</v>
+        <v>46119</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
@@ -10986,16 +11008,16 @@
       </c>
       <c r="N136" s="1" t="n"/>
       <c r="O136" s="2" t="n">
-        <v>46113.62079417824</v>
+        <v>46182.38611759259</v>
       </c>
       <c r="P136" s="1" t="inlineStr">
         <is>
-          <t>tatiana</t>
+          <t>pvolpe</t>
         </is>
       </c>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>ok</t>
+          <t xml:space="preserve">POR FAVOR, ANEXAR QUAIS AS PENDENCIAS </t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr">
@@ -11007,26 +11029,26 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>78342</v>
+        <v>79995</v>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>Pendências estaduais	"Em consulta fiscal atualizada, foram identificadas pendências estaduais em aberto, por gentileza verificar"</t>
+          <t>Bom dia, a Jardim Elétrico entrou em contato conosco e informou que o rendimento de alguel esta incorreto. Peço a gentileza de verificarem o quanto antes.                  Segue os valores que nos foram passados Valor total 12 meses: R$ 347.731,94Retido R$ 84.797,94</t>
         </is>
       </c>
       <c r="F137" s="1" t="n">
@@ -11039,63 +11061,53 @@
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46112.41193811342</v>
+        <v>46188.37072855324</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>46119</v>
+        <v>46190</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N137" s="1" t="n"/>
-      <c r="O137" s="2" t="n">
-        <v>46182.38611759259</v>
-      </c>
-      <c r="P137" s="1" t="inlineStr">
-        <is>
-          <t>pvolpe</t>
-        </is>
-      </c>
-      <c r="Q137" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">POR FAVOR, ANEXAR QUAIS AS PENDENCIAS </t>
-        </is>
-      </c>
+      <c r="O137" s="1" t="n"/>
+      <c r="P137" s="1" t="inlineStr"/>
+      <c r="Q137" s="1" t="inlineStr"/>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S137" s="1" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>79995</v>
+        <v>79894</v>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -11105,66 +11117,77 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, a Jardim Elétrico entrou em contato conosco e informou que o rendimento de alguel esta incorreto. Peço a gentileza de verificarem o quanto antes.                  Segue os valores que nos foram passados Valor total 12 meses: R$ 347.731,94Retido R$ 84.797,94</t>
+          <t>J:\Importação\AUTO REGULARIZAÇÃO -DIFIS - VINHO NCM 2204\Daniel Oliveira\Memoria Calculo mes 052026Planilha com calculo atualizado para MAIO. Favor incluir na apuração de MAIO</t>
         </is>
       </c>
       <c r="F138" s="1" t="n">
-        <v>4610</v>
+        <v>4685</v>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>JARDIM ELÉTRICO PRODUÇÕES LTDA</t>
+          <t xml:space="preserve">EMPÓRIO SOLERA LTDA </t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46188.37072855324</v>
+        <v>46184.47569001158</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>46190</v>
+        <v>46188</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="N138" s="1" t="n"/>
-      <c r="O138" s="1" t="n"/>
-      <c r="P138" s="1" t="inlineStr"/>
-      <c r="Q138" s="1" t="inlineStr"/>
+      <c r="O138" s="2" t="n">
+        <v>46189.53722265046</v>
+      </c>
+      <c r="P138" s="1" t="inlineStr">
+        <is>
+          <t>thaizao</t>
+        </is>
+      </c>
+      <c r="Q138" s="1" t="inlineStr">
+        <is>
+          <t>Valores lançados na apuração 05/2026 conforme planilha disponibilizada pelo GC.
+R$ 7.009.025,06</t>
+        </is>
+      </c>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S138" s="1" t="n"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>79894</v>
+        <v>80227</v>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Solicitação de Documentação</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -11174,64 +11197,62 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>J:\Importação\AUTO REGULARIZAÇÃO -DIFIS - VINHO NCM 2204\Daniel Oliveira\Memoria Calculo mes 052026Planilha com calculo atualizado para MAIO. Favor incluir na apuração de MAIO</t>
+          <t>Bom dia!!Por gentileza, enviar MANAD ou resumo de Folha Mensal 06/2021 a 05/2026.</t>
         </is>
       </c>
       <c r="F139" s="1" t="n">
-        <v>4685</v>
+        <v>4726</v>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EMPÓRIO SOLERA LTDA </t>
+          <t>SAMPATACADO DE GÊNEROS ALIMENTÍCIOS E BEBIDAS LTDA (FILIAL 02)</t>
         </is>
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Natalia Silva</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46184.47569001158</v>
+        <v>46192.39938819445</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M139" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N139" s="1" t="n"/>
-      <c r="O139" s="2" t="n">
-        <v>46189.53722265046</v>
-      </c>
-      <c r="P139" s="1" t="inlineStr">
-        <is>
-          <t>thaizao</t>
-        </is>
-      </c>
+      <c r="O139" s="1" t="n"/>
+      <c r="P139" s="1" t="inlineStr"/>
       <c r="Q139" s="1" t="inlineStr">
         <is>
-          <t>Valores lançados na apuração 05/2026 conforme planilha disponibilizada pelo GC.
-R$ 7.009.025,06</t>
+          <t xml:space="preserve">Boa tarde, Rogério !
+Pra quem devemos enviar ? </t>
         </is>
       </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S139" s="1" t="n"/>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="S139" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -11304,16 +11325,16 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>80227</v>
+        <v>80517</v>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentação</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -11323,54 +11344,43 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Por gentileza, enviar MANAD ou resumo de Folha Mensal 06/2021 a 05/2026.</t>
+          <t>Por gentileza, providenciar regularização ocorrência de transporte de saldo credor incorretos nos períodos de 01/2024, 12/2024, 01/2025, 04/2026 conforme situação fiscal anexa.</t>
         </is>
       </c>
       <c r="F141" s="1" t="n">
-        <v>4726</v>
+        <v>4808</v>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>SAMPATACADO DE GÊNEROS ALIMENTÍCIOS E BEBIDAS LTDA (FILIAL 02)</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t>Natalia Silva</t>
-        </is>
-      </c>
+          <t>DAN AGRO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="H141" s="1" t="n"/>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46192.39938819445</v>
+        <v>46196.74807453703</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>46195</v>
+        <v>46213</v>
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N141" s="2" t="n">
-        <v>46195.56649575231</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N141" s="1" t="n"/>
       <c r="O141" s="1" t="n"/>
       <c r="P141" s="1" t="inlineStr"/>
-      <c r="Q141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boa tarde, Rogério !
-Pra quem devemos enviar ? </t>
-        </is>
-      </c>
+      <c r="Q141" s="1" t="n"/>
       <c r="R141" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -11380,16 +11390,16 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>80517</v>
+        <v>79660</v>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -11399,7 +11409,7 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar regularização ocorrência de transporte de saldo credor incorretos nos períodos de 01/2024, 12/2024, 01/2025, 04/2026 conforme situação fiscal anexa.</t>
+          <t>Favor retificar declarações na Sefaz, consta transporte de saldo credor incorreto GIA 01/2024 - 12/2024 E 01/2025</t>
         </is>
       </c>
       <c r="F142" s="1" t="n">
@@ -11410,21 +11420,25 @@
           <t>DAN AGRO COMERCIAL LTDA</t>
         </is>
       </c>
-      <c r="H142" s="1" t="n"/>
+      <c r="H142" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="I142" s="1" t="inlineStr">
         <is>
           <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46196.74807453703</v>
+        <v>46176.45003255787</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>46213</v>
+        <v>46183</v>
       </c>
       <c r="L142" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M142" s="1" t="inlineStr">
@@ -11432,10 +11446,16 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N142" s="1" t="n"/>
+      <c r="N142" s="2" t="n">
+        <v>46182.62023232639</v>
+      </c>
       <c r="O142" s="1" t="n"/>
       <c r="P142" s="1" t="inlineStr"/>
-      <c r="Q142" s="1" t="n"/>
+      <c r="Q142" s="1" t="inlineStr">
+        <is>
+          <t>Fazendo levando das ocorrências. Deve ser analisado pois pode influenciar em meses anteriores e posteriores</t>
+        </is>
+      </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -11445,16 +11465,16 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>79660</v>
+        <v>80518</v>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -11464,36 +11484,32 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t>Favor retificar declarações na Sefaz, consta transporte de saldo credor incorreto GIA 01/2024 - 12/2024 E 01/2025</t>
+          <t>Por gentileza, regularizar transporte de saldo credor incorreto 07/2025, 08/2025, 01/2026 e 02/2026 conforme situação fiscal anexa.</t>
         </is>
       </c>
       <c r="F143" s="1" t="n">
-        <v>4808</v>
+        <v>4810</v>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>DAN AGRO COMERCIAL LTDA</t>
-        </is>
-      </c>
-      <c r="H143" s="1" t="inlineStr">
-        <is>
-          <t>Ricardo Fischer</t>
-        </is>
-      </c>
+          <t>ECOFRUT AGRO COMERCIAL LTDA</t>
+        </is>
+      </c>
+      <c r="H143" s="1" t="n"/>
       <c r="I143" s="1" t="inlineStr">
         <is>
           <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46176.45003255787</v>
+        <v>46196.76729903935</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M143" s="1" t="inlineStr">
@@ -11501,16 +11517,10 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N143" s="2" t="n">
-        <v>46182.62023232639</v>
-      </c>
+      <c r="N143" s="1" t="n"/>
       <c r="O143" s="1" t="n"/>
       <c r="P143" s="1" t="inlineStr"/>
-      <c r="Q143" s="1" t="inlineStr">
-        <is>
-          <t>Fazendo levando das ocorrências. Deve ser analisado pois pode influenciar em meses anteriores e posteriores</t>
-        </is>
-      </c>
+      <c r="Q143" s="1" t="n"/>
       <c r="R143" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -12821,16 +12831,16 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>79930</v>
+        <v>79948</v>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
@@ -12840,7 +12850,7 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderiam providenciar Última declaração do IRPJ entregue do cliente CEREALISTA</t>
+          <t>Por gentileza, poderiam providenciar o BALANÇO E DRE da empresa 5101 - CEREALISTA IDEAL1) Balancete atualizado2) DRE - comprovante de faturamento; Demonstrativo de resultado do exercício 2025informo que tentei gerar o balanço e a DRE porem esta incorreto os resultados apresentados</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
@@ -12862,10 +12872,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46184.70223510417</v>
+        <v>46185.47699907408</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="L161" s="1" t="inlineStr">
         <is>
@@ -12877,9 +12887,11 @@
           <t>Leticia Queiroz</t>
         </is>
       </c>
-      <c r="N161" s="1" t="n"/>
+      <c r="N161" s="2" t="n">
+        <v>46189.73606628472</v>
+      </c>
       <c r="O161" s="2" t="n">
-        <v>46192.46905616898</v>
+        <v>46191.60069417824</v>
       </c>
       <c r="P161" s="1" t="inlineStr">
         <is>
@@ -12888,7 +12900,7 @@
       </c>
       <c r="Q161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia, não entendi, favor ser mais e especifica, seria memoria de cálculo ou alguma obrigação acessória como Sped????? </t>
+          <t>segue balanço e dre 2025</t>
         </is>
       </c>
       <c r="R161" s="1" t="inlineStr">
@@ -12900,16 +12912,16 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>79948</v>
+        <v>79930</v>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -12919,7 +12931,7 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, poderiam providenciar o BALANÇO E DRE da empresa 5101 - CEREALISTA IDEAL1) Balancete atualizado2) DRE - comprovante de faturamento; Demonstrativo de resultado do exercício 2025informo que tentei gerar o balanço e a DRE porem esta incorreto os resultados apresentados</t>
+          <t>Por gentileza, poderiam providenciar Última declaração do IRPJ entregue do cliente CEREALISTA</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
@@ -12941,10 +12953,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46185.47699907408</v>
+        <v>46184.70223510417</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
@@ -12956,11 +12968,9 @@
           <t>Leticia Queiroz</t>
         </is>
       </c>
-      <c r="N162" s="2" t="n">
-        <v>46189.73606628472</v>
-      </c>
+      <c r="N162" s="1" t="n"/>
       <c r="O162" s="2" t="n">
-        <v>46191.60069417824</v>
+        <v>46192.46905616898</v>
       </c>
       <c r="P162" s="1" t="inlineStr">
         <is>
@@ -12969,7 +12979,7 @@
       </c>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>segue balanço e dre 2025</t>
+          <t xml:space="preserve">Bom dia, não entendi, favor ser mais e especifica, seria memoria de cálculo ou alguma obrigação acessória como Sped????? </t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr">
@@ -16630,7 +16640,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>80247</v>
+        <v>80249</v>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
@@ -16649,7 +16659,7 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>Prezadas, periodo ex-contador.cliente com CNPJ inapto URGENTE!com autorização da diretoria (anexo).providenciar a entrega em branco das obrigações abaixo.ECF anual 2023 - DCTF mensal 2023 março, abril, maio, junho, julho - DCTF mensal 2022 fevereiro - DCTF mensal 2021 novembro e dezembro - DCTF mensal 2022 janeiro - DCTF mensal 2021 outubro. .</t>
+          <t xml:space="preserve">Prezadas, periodo ex-contador.cliente com CNPJ inapto URGENTE!com autorização da diretoria (anexo).providenciar a entrega em branco das obrigações abaixo.PGDAS - mensal 2024 fevereiro - EFD Contribuições 2021 outubro, novembro e dezembro. </t>
         </is>
       </c>
       <c r="F210" s="1" t="n">
@@ -16660,21 +16670,25 @@
           <t>APOLO ARTES LTDA</t>
         </is>
       </c>
-      <c r="H210" s="1" t="n"/>
+      <c r="H210" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46192.65557515046</v>
+        <v>46192.65839660879</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>46195</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M210" s="1" t="inlineStr">
@@ -16683,93 +16697,89 @@
         </is>
       </c>
       <c r="N210" s="1" t="n"/>
-      <c r="O210" s="1" t="n"/>
-      <c r="P210" s="1" t="inlineStr"/>
-      <c r="Q210" s="1" t="n"/>
-      <c r="R210" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="S210" s="1" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="n">
-        <v>80249</v>
-      </c>
-      <c r="B211" s="1" t="inlineStr">
-        <is>
-          <t>Omissão de Obrigações Acessórias</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr">
-        <is>
-          <t>Omissão de Obrigações Acessórias</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezadas, periodo ex-contador.cliente com CNPJ inapto URGENTE!com autorização da diretoria (anexo).providenciar a entrega em branco das obrigações abaixo.PGDAS - mensal 2024 fevereiro - EFD Contribuições 2021 outubro, novembro e dezembro. </t>
-        </is>
-      </c>
-      <c r="F211" s="1" t="n">
-        <v>5729</v>
-      </c>
-      <c r="G211" s="1" t="inlineStr">
-        <is>
-          <t>APOLO ARTES LTDA</t>
-        </is>
-      </c>
-      <c r="H211" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="I211" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
-      <c r="J211" s="2" t="n">
-        <v>46192.65839660879</v>
-      </c>
-      <c r="K211" s="2" t="n">
-        <v>46195</v>
-      </c>
-      <c r="L211" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M211" s="1" t="inlineStr">
-        <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N211" s="1" t="n"/>
-      <c r="O211" s="2" t="n">
+      <c r="O210" s="2" t="n">
         <v>46195.7003940162</v>
       </c>
-      <c r="P211" s="1" t="inlineStr">
+      <c r="P210" s="1" t="inlineStr">
         <is>
           <t>pvolpe</t>
         </is>
       </c>
-      <c r="Q211" s="1" t="inlineStr">
+      <c r="Q210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">boa tarde, 
 Sped contribuição entregue em 25/05/2022 e DAS 02/2024 entregue dentro do prazo correto. 
 não há pedencias pro parte do fiscal </t>
         </is>
       </c>
+      <c r="R210" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S210" s="1" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>80247</v>
+      </c>
+      <c r="B211" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="inlineStr">
+        <is>
+          <t>Omissão de Obrigações Acessórias</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E211" s="1" t="inlineStr">
+        <is>
+          <t>Prezadas, periodo ex-contador.cliente com CNPJ inapto URGENTE!com autorização da diretoria (anexo).providenciar a entrega em branco das obrigações abaixo.ECF anual 2023 - DCTF mensal 2023 março, abril, maio, junho, julho - DCTF mensal 2022 fevereiro - DCTF mensal 2021 novembro e dezembro - DCTF mensal 2022 janeiro - DCTF mensal 2021 outubro. .</t>
+        </is>
+      </c>
+      <c r="F211" s="1" t="n">
+        <v>5729</v>
+      </c>
+      <c r="G211" s="1" t="inlineStr">
+        <is>
+          <t>APOLO ARTES LTDA</t>
+        </is>
+      </c>
+      <c r="H211" s="1" t="n"/>
+      <c r="I211" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J211" s="2" t="n">
+        <v>46192.65557515046</v>
+      </c>
+      <c r="K211" s="2" t="n">
+        <v>46195</v>
+      </c>
+      <c r="L211" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M211" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Ferreira</t>
+        </is>
+      </c>
+      <c r="N211" s="1" t="n"/>
+      <c r="O211" s="1" t="n"/>
+      <c r="P211" s="1" t="inlineStr"/>
+      <c r="Q211" s="1" t="n"/>
       <c r="R211" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S211" s="1" t="n"/>
@@ -18456,7 +18466,7 @@
       </c>
       <c r="L233" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M233" s="1" t="inlineStr">
@@ -18465,8 +18475,14 @@
         </is>
       </c>
       <c r="N233" s="1" t="n"/>
-      <c r="O233" s="1" t="n"/>
-      <c r="P233" s="1" t="inlineStr"/>
+      <c r="O233" s="2" t="n">
+        <v>46197.37187415509</v>
+      </c>
+      <c r="P233" s="1" t="inlineStr">
+        <is>
+          <t>inascimento</t>
+        </is>
+      </c>
       <c r="Q233" s="1" t="inlineStr">
         <is>
           <t>enviado por email 05/06</t>
@@ -18474,7 +18490,7 @@
       </c>
       <c r="R233" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S233" s="1" t="n"/>
@@ -19266,26 +19282,26 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>80136</v>
+        <v>77014</v>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D244" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E244" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza verificar saldo credor incorreto. </t>
+          <t>E-cac	Debito em aberto 10/2025 - IRRF e CSRF - enviar para o cliente!Despesas - Assistência Medica	Por favor, Conta 872 - verificar lançamentos (vale refeição lançado errado) e dois laçamento de assist. medica. Foi feito?Comissões	Por favor, Conta 3853 - verificar lançamentos, valor muito abaixo dos meses anteriores. Foi feito?Comissões	Por favor, Conta 948 - Conta igual a 3853 verificar. Foi feito?Pro-LaborePor favor, Conta 1001- sem lançamento na DRE (verificar). Foi feito?</t>
         </is>
       </c>
       <c r="F244" s="1" t="n">
@@ -19298,44 +19314,54 @@
       </c>
       <c r="H244" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I244" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J244" s="2" t="n">
-        <v>46190.46544413194</v>
+        <v>46057.5935528125</v>
       </c>
       <c r="K244" s="2" t="n">
-        <v>46192</v>
+        <v>46064</v>
       </c>
       <c r="L244" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M244" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N244" s="1" t="n"/>
-      <c r="O244" s="1" t="n"/>
-      <c r="P244" s="1" t="inlineStr"/>
-      <c r="Q244" s="1" t="inlineStr"/>
+      <c r="O244" s="2" t="n">
+        <v>46113.6484346875</v>
+      </c>
+      <c r="P244" s="1" t="inlineStr">
+        <is>
+          <t>erikas</t>
+        </is>
+      </c>
+      <c r="Q244" s="1" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
       <c r="R244" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S244" s="1" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>77014</v>
+        <v>77015</v>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
@@ -19354,7 +19380,7 @@
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t>E-cac	Debito em aberto 10/2025 - IRRF e CSRF - enviar para o cliente!Despesas - Assistência Medica	Por favor, Conta 872 - verificar lançamentos (vale refeição lançado errado) e dois laçamento de assist. medica. Foi feito?Comissões	Por favor, Conta 3853 - verificar lançamentos, valor muito abaixo dos meses anteriores. Foi feito?Comissões	Por favor, Conta 948 - Conta igual a 3853 verificar. Foi feito?Pro-LaborePor favor, Conta 1001- sem lançamento na DRE (verificar). Foi feito?</t>
+          <t>Fiscal	EFD 10, 11 e 12/2025 - Transporte de Saldo Credor Incorreto, corrigir por favor!</t>
         </is>
       </c>
       <c r="F245" s="1" t="n">
@@ -19367,23 +19393,23 @@
       </c>
       <c r="H245" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I245" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J245" s="2" t="n">
-        <v>46057.5935528125</v>
+        <v>46057.59395454861</v>
       </c>
       <c r="K245" s="2" t="n">
         <v>46064</v>
       </c>
       <c r="L245" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M245" s="1" t="inlineStr">
@@ -19391,49 +19417,45 @@
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N245" s="1" t="n"/>
-      <c r="O245" s="2" t="n">
-        <v>46113.6484346875</v>
-      </c>
-      <c r="P245" s="1" t="inlineStr">
-        <is>
-          <t>erikas</t>
-        </is>
-      </c>
+      <c r="N245" s="2" t="n">
+        <v>46182.65223278935</v>
+      </c>
+      <c r="O245" s="1" t="n"/>
+      <c r="P245" s="1" t="inlineStr"/>
       <c r="Q245" s="1" t="inlineStr">
         <is>
-          <t>Verificado</t>
+          <t>Operação em execução do processo de retificação - prazo 30/06/2026</t>
         </is>
       </c>
       <c r="R245" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S245" s="1" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>77015</v>
+        <v>80136</v>
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t>Fiscal	EFD 10, 11 e 12/2025 - Transporte de Saldo Credor Incorreto, corrigir por favor!</t>
+          <t xml:space="preserve">Por gentileza verificar saldo credor incorreto. </t>
         </is>
       </c>
       <c r="F246" s="1" t="n">
@@ -19446,7 +19468,7 @@
       </c>
       <c r="H246" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I246" s="1" t="inlineStr">
@@ -19455,31 +19477,25 @@
         </is>
       </c>
       <c r="J246" s="2" t="n">
-        <v>46057.59395454861</v>
+        <v>46190.46544413194</v>
       </c>
       <c r="K246" s="2" t="n">
-        <v>46064</v>
+        <v>46192</v>
       </c>
       <c r="L246" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N246" s="2" t="n">
-        <v>46182.65223278935</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N246" s="1" t="n"/>
       <c r="O246" s="1" t="n"/>
       <c r="P246" s="1" t="inlineStr"/>
-      <c r="Q246" s="1" t="inlineStr">
-        <is>
-          <t>Operação em execução do processo de retificação - prazo 30/06/2026</t>
-        </is>
-      </c>
+      <c r="Q246" s="1" t="inlineStr"/>
       <c r="R246" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21835,7 +21851,11 @@
           <t>RESOLVE MIDIA SOLUTIONS LTDA</t>
         </is>
       </c>
-      <c r="H277" s="1" t="n"/>
+      <c r="H277" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -21849,7 +21869,7 @@
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
@@ -21860,7 +21880,7 @@
       <c r="N277" s="1" t="n"/>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="inlineStr"/>
-      <c r="Q277" s="1" t="n"/>
+      <c r="Q277" s="1" t="inlineStr"/>
       <c r="R277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22498,7 +22518,11 @@
           <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H286" s="1" t="n"/>
+      <c r="H286" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I286" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -22512,7 +22536,7 @@
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M286" s="1" t="inlineStr">
@@ -22523,7 +22547,7 @@
       <c r="N286" s="1" t="n"/>
       <c r="O286" s="1" t="n"/>
       <c r="P286" s="1" t="inlineStr"/>
-      <c r="Q286" s="1" t="n"/>
+      <c r="Q286" s="1" t="inlineStr"/>
       <c r="R286" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -24461,154 +24485,140 @@
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
+        <v>80522</v>
+      </c>
+      <c r="B312" s="1" t="inlineStr">
+        <is>
+          <t>Retificação de Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="C312" s="1" t="inlineStr">
+        <is>
+          <t>Retificação de Obrigação Acessória</t>
+        </is>
+      </c>
+      <c r="D312" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E312" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia, por gentileza verificar mensagem recebida no DEC referente irregularidade na EFD 05/2026.</t>
+        </is>
+      </c>
+      <c r="F312" s="1" t="n">
+        <v>6880</v>
+      </c>
+      <c r="G312" s="1" t="inlineStr">
+        <is>
+          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS (FILIAL)</t>
+        </is>
+      </c>
+      <c r="H312" s="1" t="n"/>
+      <c r="I312" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="n">
+        <v>46197.36092913194</v>
+      </c>
+      <c r="K312" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="L312" s="1" t="inlineStr">
+        <is>
+          <t>Sem Responsavel Atribuido</t>
+        </is>
+      </c>
+      <c r="M312" s="1" t="inlineStr">
+        <is>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N312" s="1" t="n"/>
+      <c r="O312" s="1" t="n"/>
+      <c r="P312" s="1" t="inlineStr"/>
+      <c r="Q312" s="1" t="n"/>
+      <c r="R312" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="S312" s="1" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="1" t="n">
         <v>78847</v>
       </c>
-      <c r="B312" s="1" t="inlineStr">
+      <c r="B313" s="1" t="inlineStr">
         <is>
           <t>Reunião externa</t>
         </is>
       </c>
-      <c r="C312" s="1" t="inlineStr">
+      <c r="C313" s="1" t="inlineStr">
         <is>
           <t>Inclusão de Ata</t>
         </is>
       </c>
-      <c r="D312" s="1" t="inlineStr">
+      <c r="D313" s="1" t="inlineStr">
         <is>
           <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E312" s="1" t="inlineStr">
+      <c r="E313" s="1" t="inlineStr">
         <is>
           <t>Verificar o sindicato Patronal, lembrando que o cliente não abre mais aos domingosCliente tem dificuldade sobre os recebimentos dos atestados demissionaisApresentar ao cliente sobre as obrigações da empresa5350 - AKAFER</t>
         </is>
       </c>
-      <c r="F312" s="1" t="n">
+      <c r="F313" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G312" s="1" t="n"/>
-      <c r="H312" s="1" t="inlineStr">
+      <c r="G313" s="1" t="n"/>
+      <c r="H313" s="1" t="inlineStr">
         <is>
           <t>Mauricio Lermen</t>
         </is>
       </c>
-      <c r="I312" s="1" t="inlineStr">
+      <c r="I313" s="1" t="inlineStr">
         <is>
           <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
-      <c r="J312" s="2" t="n">
+      <c r="J313" s="2" t="n">
         <v>46134.66965193287</v>
       </c>
-      <c r="K312" s="2" t="n">
+      <c r="K313" s="2" t="n">
         <v>46142</v>
       </c>
-      <c r="L312" s="1" t="inlineStr">
+      <c r="L313" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M312" s="1" t="inlineStr">
+      <c r="M313" s="1" t="inlineStr">
         <is>
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N312" s="2" t="n">
+      <c r="N313" s="2" t="n">
         <v>46171.59439259259</v>
       </c>
-      <c r="O312" s="2" t="n">
+      <c r="O313" s="2" t="n">
         <v>46176.76352538195</v>
       </c>
-      <c r="P312" s="1" t="inlineStr">
+      <c r="P313" s="1" t="inlineStr">
         <is>
           <t>mauricio</t>
         </is>
       </c>
-      <c r="Q312" s="1" t="inlineStr">
+      <c r="Q313" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">EM ATENDIMENTO
 </t>
         </is>
       </c>
-      <c r="R312" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="S312" s="1" t="n"/>
-    </row>
-    <row r="313">
-      <c r="A313" s="1" t="n">
-        <v>78425</v>
-      </c>
-      <c r="B313" s="1" t="inlineStr">
-        <is>
-          <t>Ata de Reunião</t>
-        </is>
-      </c>
-      <c r="C313" s="1" t="inlineStr">
-        <is>
-          <t>Inclusão de Ata</t>
-        </is>
-      </c>
-      <c r="D313" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E313" s="1" t="inlineStr">
-        <is>
-          <t>Verificar valores ref. 11/2025 em aberto qual a origem dos débitos e enviar ao cliente para pagamentoverificar SITUAÇÃO FISCAL</t>
-        </is>
-      </c>
-      <c r="F313" s="1" t="n">
-        <v>1180</v>
-      </c>
-      <c r="G313" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO YAMATO LTDA</t>
-        </is>
-      </c>
-      <c r="H313" s="1" t="inlineStr">
-        <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
-      <c r="I313" s="1" t="inlineStr">
-        <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
-        </is>
-      </c>
-      <c r="J313" s="2" t="n">
-        <v>46113.68943684028</v>
-      </c>
-      <c r="K313" s="2" t="n">
-        <v>46120</v>
-      </c>
-      <c r="L313" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M313" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N313" s="1" t="n"/>
-      <c r="O313" s="2" t="n">
-        <v>46114.6203158912</v>
-      </c>
-      <c r="P313" s="1" t="inlineStr">
-        <is>
-          <t>renatac</t>
-        </is>
-      </c>
-      <c r="Q313" s="1" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
       <c r="R313" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -24618,137 +24628,220 @@
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>80353</v>
+        <v>78425</v>
       </c>
       <c r="B314" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C314" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D314" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E314" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicitou a atualização da DCTFWeb, pois não conseguiu pagar no vencimento (19/06/2026).</t>
+          <t>Verificar valores ref. 11/2025 em aberto qual a origem dos débitos e enviar ao cliente para pagamentoverificar SITUAÇÃO FISCAL</t>
         </is>
       </c>
       <c r="F314" s="1" t="n">
-        <v>1768</v>
+        <v>1180</v>
       </c>
       <c r="G314" s="1" t="inlineStr">
         <is>
-          <t>FIESTA LTDA</t>
-        </is>
-      </c>
-      <c r="H314" s="1" t="n"/>
+          <t>SUPERMERCADO YAMATO LTDA</t>
+        </is>
+      </c>
+      <c r="H314" s="1" t="inlineStr">
+        <is>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
       <c r="I314" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J314" s="2" t="n">
-        <v>46195.4976246875</v>
+        <v>46113.68943684028</v>
       </c>
       <c r="K314" s="2" t="n">
-        <v>46196</v>
+        <v>46120</v>
       </c>
       <c r="L314" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M314" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N314" s="1" t="n"/>
-      <c r="O314" s="1" t="n"/>
-      <c r="P314" s="1" t="inlineStr"/>
-      <c r="Q314" s="1" t="n"/>
+      <c r="O314" s="2" t="n">
+        <v>46114.6203158912</v>
+      </c>
+      <c r="P314" s="1" t="inlineStr">
+        <is>
+          <t>renatac</t>
+        </is>
+      </c>
+      <c r="Q314" s="1" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
       <c r="R314" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S314" s="1" t="n"/>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
+        <v>80353</v>
+      </c>
+      <c r="B315" s="1" t="inlineStr">
+        <is>
+          <t>DCTFWeb</t>
+        </is>
+      </c>
+      <c r="C315" s="1" t="inlineStr">
+        <is>
+          <t>DCTFWeb</t>
+        </is>
+      </c>
+      <c r="D315" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E315" s="1" t="inlineStr">
+        <is>
+          <t>Cliente solicitou a atualização da DCTFWeb, pois não conseguiu pagar no vencimento (19/06/2026).</t>
+        </is>
+      </c>
+      <c r="F315" s="1" t="n">
+        <v>1768</v>
+      </c>
+      <c r="G315" s="1" t="inlineStr">
+        <is>
+          <t>FIESTA LTDA</t>
+        </is>
+      </c>
+      <c r="H315" s="1" t="inlineStr">
+        <is>
+          <t>Ana Barbosa</t>
+        </is>
+      </c>
+      <c r="I315" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL VAREJO</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="n">
+        <v>46195.4976246875</v>
+      </c>
+      <c r="K315" s="2" t="n">
+        <v>46196</v>
+      </c>
+      <c r="L315" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M315" s="1" t="inlineStr">
+        <is>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
+      <c r="N315" s="1" t="n"/>
+      <c r="O315" s="1" t="n"/>
+      <c r="P315" s="1" t="inlineStr"/>
+      <c r="Q315" s="1" t="inlineStr"/>
+      <c r="R315" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="S315" s="1" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="1" t="n">
         <v>79943</v>
       </c>
-      <c r="B315" s="1" t="inlineStr">
+      <c r="B316" s="1" t="inlineStr">
         <is>
           <t>Ata de Reunião</t>
         </is>
       </c>
-      <c r="C315" s="1" t="inlineStr">
+      <c r="C316" s="1" t="inlineStr">
         <is>
           <t>Inclusão de Ata</t>
         </is>
       </c>
-      <c r="D315" s="1" t="inlineStr">
+      <c r="D316" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
-      <c r="E315" s="1" t="inlineStr">
+      <c r="E316" s="1" t="inlineStr">
         <is>
           <t>* Cliente está realizando a manutenção predial referente ao imóvel aonde localiza-se a Interfrios. Favor verificar e reclassificar tudo com DESPESA E NÃO BENFEITORIA EM IMÓVEIS DE TERCEIROS E ATÉ MESMO IMOBILIZADO - FOI RECLASSIFICADO?* Notas do Ifood, referentes a comissão de outubro, novembro e dezembro não foram enviadas. Em Janeiro eles enviaram NOTAS DE DÉBITO referentes ao ultimo trimestre.* Preciso trazer para o cliente no próximo mês DFC do ano de 2024 para auxiliar o cliente em suas tomadas de decisão - Teremos condições de apresentar?</t>
         </is>
       </c>
-      <c r="F315" s="1" t="n">
+      <c r="F316" s="1" t="n">
         <v>2502</v>
       </c>
-      <c r="G315" s="1" t="inlineStr">
+      <c r="G316" s="1" t="inlineStr">
         <is>
           <t>INTERFRIOS COMÉRCIO DE FRIOS E LATICÍNIOS EIRELI</t>
         </is>
       </c>
-      <c r="H315" s="1" t="inlineStr">
+      <c r="H316" s="1" t="inlineStr">
         <is>
           <t>Edileide Dias</t>
         </is>
       </c>
-      <c r="I315" s="1" t="inlineStr">
+      <c r="I316" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
-      <c r="J315" s="2" t="n">
+      <c r="J316" s="2" t="n">
         <v>46185.4118128125</v>
       </c>
-      <c r="K315" s="2" t="n">
+      <c r="K316" s="2" t="n">
         <v>46185</v>
       </c>
-      <c r="L315" s="1" t="inlineStr">
+      <c r="L316" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M315" s="1" t="inlineStr">
+      <c r="M316" s="1" t="inlineStr">
         <is>
           <t>Rodrigo Rego</t>
         </is>
       </c>
-      <c r="N315" s="1" t="n"/>
-      <c r="O315" s="2" t="n">
+      <c r="N316" s="1" t="n"/>
+      <c r="O316" s="2" t="n">
         <v>46185.57578209491</v>
       </c>
-      <c r="P315" s="1" t="inlineStr">
+      <c r="P316" s="1" t="inlineStr">
         <is>
           <t>edileide</t>
         </is>
       </c>
-      <c r="Q315" s="1" t="inlineStr">
+      <c r="Q316" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve"> Cliente está realizando a manutenção predial referente ao imóvel aonde localiza-se a Interfrios. Favor verificar e reclassificar tudo com DESPESA E NÃO BENFEITORIA EM IMÓVEIS DE TERCEIROS E ATÉ MESMO IMOBILIZADO - FOI RECLASSIFICADO?
 Não foi possivel entender o sua solicitação, pois não identificamos conta com saldo de Bens em Imoveis de terceiros, seria construções em andamento?
@@ -24759,81 +24852,16 @@
 ok,em anexo o dumento solicitado</t>
         </is>
       </c>
-      <c r="R315" s="1" t="inlineStr">
+      <c r="R316" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="S315" s="1" t="n"/>
-    </row>
-    <row r="316">
-      <c r="A316" s="1" t="n">
-        <v>80311</v>
-      </c>
-      <c r="B316" s="1" t="inlineStr">
-        <is>
-          <t>DCTFWeb</t>
-        </is>
-      </c>
-      <c r="C316" s="1" t="inlineStr">
-        <is>
-          <t>DCTFWeb</t>
-        </is>
-      </c>
-      <c r="D316" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E316" s="1" t="inlineStr">
-        <is>
-          <t>Há 3 pendencias de omissão de DCTWeb para o cliente. Dez/2022, Fev/2026 e Mar/2026, por favor verificar e retornar esse chamado, pois está na malha fiscal referente ao mês de dez/2022.</t>
-        </is>
-      </c>
-      <c r="F316" s="1" t="n">
-        <v>2744</v>
-      </c>
-      <c r="G316" s="1" t="inlineStr">
-        <is>
-          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H316" s="1" t="n"/>
-      <c r="I316" s="1" t="inlineStr">
-        <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
-        </is>
-      </c>
-      <c r="J316" s="2" t="n">
-        <v>46195.44287422454</v>
-      </c>
-      <c r="K316" s="2" t="n">
-        <v>46198</v>
-      </c>
-      <c r="L316" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M316" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
-      <c r="N316" s="1" t="n"/>
-      <c r="O316" s="1" t="n"/>
-      <c r="P316" s="1" t="inlineStr"/>
-      <c r="Q316" s="1" t="n"/>
-      <c r="R316" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="S316" s="1" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>80317</v>
+        <v>80311</v>
       </c>
       <c r="B317" s="1" t="inlineStr">
         <is>
@@ -24852,7 +24880,7 @@
       </c>
       <c r="E317" s="1" t="inlineStr">
         <is>
-          <t>Verificar os valores informados na DCTFWeb referente ao IRRF, CSRF, CP-SEGUR, CP-PATRONAL, CP-TERCEIROS dos períodos que constam na situação fiscal, pois como o saldo do valor original está diferente do saldo devedor creio que há divergência entre a guia emitida e o que foi informado na DCTFWeb.</t>
+          <t>Há 3 pendencias de omissão de DCTWeb para o cliente. Dez/2022, Fev/2026 e Mar/2026, por favor verificar e retornar esse chamado, pois está na malha fiscal referente ao mês de dez/2022.</t>
         </is>
       </c>
       <c r="F317" s="1" t="n">
@@ -24863,21 +24891,25 @@
           <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (MATRIZ)</t>
         </is>
       </c>
-      <c r="H317" s="1" t="n"/>
+      <c r="H317" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I317" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J317" s="2" t="n">
-        <v>46195.4506077199</v>
+        <v>46195.44287422454</v>
       </c>
       <c r="K317" s="2" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="L317" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M317" s="1" t="inlineStr">
@@ -24888,7 +24920,7 @@
       <c r="N317" s="1" t="n"/>
       <c r="O317" s="1" t="n"/>
       <c r="P317" s="1" t="inlineStr"/>
-      <c r="Q317" s="1" t="n"/>
+      <c r="Q317" s="1" t="inlineStr"/>
       <c r="R317" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -24898,62 +24930,66 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>80415</v>
+        <v>80317</v>
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Por gentileza, solicito o envio do Balanço e da DRE referentes ao exercício de 2025Caso não seja possível anexar os documentos neste chamado, peço a gentileza de encaminhá-los para o meu e-mail:apoio.gc11@mgcontecnica.com.brInformo que tentei gerar os documentos por aqui, porém os valores apresentados não estão conciliando com as informações esperadas.Como se trata de uma demanda com certa urgência, peço, se possível, que os documentos sejam encaminhados ainda hoje.Desde já, agradeço pela atenção e fico no aguardo.</t>
+          <t>Verificar os valores informados na DCTFWeb referente ao IRRF, CSRF, CP-SEGUR, CP-PATRONAL, CP-TERCEIROS dos períodos que constam na situação fiscal, pois como o saldo do valor original está diferente do saldo devedor creio que há divergência entre a guia emitida e o que foi informado na DCTFWeb.</t>
         </is>
       </c>
       <c r="F318" s="1" t="n">
-        <v>3638</v>
+        <v>2744</v>
       </c>
       <c r="G318" s="1" t="inlineStr">
         <is>
-          <t>MEE LOCAÇÃO DE EQUIPAMENTOS LTDA</t>
-        </is>
-      </c>
-      <c r="H318" s="1" t="n"/>
+          <t>CUCINARE PRO ALIMENTAÇÃO LTDA  (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H318" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I318" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J318" s="2" t="n">
-        <v>46195.68175674768</v>
+        <v>46195.4506077199</v>
       </c>
       <c r="K318" s="2" t="n">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="L318" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M318" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N318" s="1" t="n"/>
       <c r="O318" s="1" t="n"/>
       <c r="P318" s="1" t="inlineStr"/>
-      <c r="Q318" s="1" t="n"/>
+      <c r="Q318" s="1" t="inlineStr"/>
       <c r="R318" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -24963,16 +24999,16 @@
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>78854</v>
+        <v>80415</v>
       </c>
       <c r="B319" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C319" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D319" s="1" t="inlineStr">
@@ -24982,53 +25018,47 @@
       </c>
       <c r="E319" s="1" t="inlineStr">
         <is>
-          <t>IMPORTANTEPor gentileza, necessário realizar a captura de 100% dos arquivos XML referentes a compras realizadas pela empresa de janeiro a novembro/2025, para a contabilização correta de todas as compras realizadas pela empresa no período citado.</t>
+          <t>Prezados, boa tarde!Por gentileza, solicito o envio do Balanço e da DRE referentes ao exercício de 2025Caso não seja possível anexar os documentos neste chamado, peço a gentileza de encaminhá-los para o meu e-mail:apoio.gc11@mgcontecnica.com.brInformo que tentei gerar os documentos por aqui, porém os valores apresentados não estão conciliando com as informações esperadas.Como se trata de uma demanda com certa urgência, peço, se possível, que os documentos sejam encaminhados ainda hoje.Desde já, agradeço pela atenção e fico no aguardo.</t>
         </is>
       </c>
       <c r="F319" s="1" t="n">
-        <v>4811</v>
+        <v>3638</v>
       </c>
       <c r="G319" s="1" t="inlineStr">
         <is>
-          <t>ORIVALDO DAN</t>
+          <t>MEE LOCAÇÃO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="H319" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="I319" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J319" s="2" t="n">
-        <v>46134.74738626157</v>
+        <v>46195.68175674768</v>
       </c>
       <c r="K319" s="2" t="n">
-        <v>46142</v>
+        <v>46196</v>
       </c>
       <c r="L319" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M319" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N319" s="2" t="n">
-        <v>46183.48642873843</v>
-      </c>
+          <t>Victoria Virgens</t>
+        </is>
+      </c>
+      <c r="N319" s="1" t="n"/>
       <c r="O319" s="1" t="n"/>
       <c r="P319" s="1" t="inlineStr"/>
-      <c r="Q319" s="1" t="inlineStr">
-        <is>
-          <t>Fazendo levantamento das notas enviadas pelo cliente e o que consta no gax para confirmar com o GC se realmente devem ser lançadas.</t>
-        </is>
-      </c>
+      <c r="Q319" s="1" t="inlineStr"/>
       <c r="R319" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -25038,166 +25068,172 @@
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
+        <v>78854</v>
+      </c>
+      <c r="B320" s="1" t="inlineStr">
+        <is>
+          <t>Ata de Reunião</t>
+        </is>
+      </c>
+      <c r="C320" s="1" t="inlineStr">
+        <is>
+          <t>Inclusão de Ata</t>
+        </is>
+      </c>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E320" s="1" t="inlineStr">
+        <is>
+          <t>IMPORTANTEPor gentileza, necessário realizar a captura de 100% dos arquivos XML referentes a compras realizadas pela empresa de janeiro a novembro/2025, para a contabilização correta de todas as compras realizadas pela empresa no período citado.</t>
+        </is>
+      </c>
+      <c r="F320" s="1" t="n">
+        <v>4811</v>
+      </c>
+      <c r="G320" s="1" t="inlineStr">
+        <is>
+          <t>ORIVALDO DAN</t>
+        </is>
+      </c>
+      <c r="H320" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
+      <c r="I320" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="n">
+        <v>46134.74738626157</v>
+      </c>
+      <c r="K320" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="L320" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M320" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N320" s="2" t="n">
+        <v>46183.48642873843</v>
+      </c>
+      <c r="O320" s="1" t="n"/>
+      <c r="P320" s="1" t="inlineStr"/>
+      <c r="Q320" s="1" t="inlineStr">
+        <is>
+          <t>Fazendo levantamento das notas enviadas pelo cliente e o que consta no gax para confirmar com o GC se realmente devem ser lançadas.</t>
+        </is>
+      </c>
+      <c r="R320" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="S320" s="1" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="1" t="n">
         <v>79765</v>
       </c>
-      <c r="B320" s="1" t="inlineStr">
+      <c r="B321" s="1" t="inlineStr">
         <is>
           <t>Balanço e DRE</t>
         </is>
       </c>
-      <c r="C320" s="1" t="inlineStr">
+      <c r="C321" s="1" t="inlineStr">
         <is>
           <t>Balanço e DRE</t>
         </is>
       </c>
-      <c r="D320" s="1" t="inlineStr">
+      <c r="D321" s="1" t="inlineStr">
         <is>
           <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
-      <c r="E320" s="1" t="inlineStr">
+      <c r="E321" s="1" t="inlineStr">
         <is>
           <t>providenciar balanço de e dre da empresa 5044 ano: 2025</t>
         </is>
       </c>
-      <c r="F320" s="1" t="n">
+      <c r="F321" s="1" t="n">
         <v>5044</v>
       </c>
-      <c r="G320" s="1" t="inlineStr">
+      <c r="G321" s="1" t="inlineStr">
         <is>
           <t>BARATÃO SÃO LUCAS LTDA</t>
         </is>
       </c>
-      <c r="H320" s="1" t="inlineStr">
+      <c r="H321" s="1" t="inlineStr">
         <is>
           <t>Edileide Dias</t>
         </is>
       </c>
-      <c r="I320" s="1" t="inlineStr">
+      <c r="I321" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
-      <c r="J320" s="2" t="n">
+      <c r="J321" s="2" t="n">
         <v>46181.69699834491</v>
       </c>
-      <c r="K320" s="2" t="n">
+      <c r="K321" s="2" t="n">
         <v>46182</v>
       </c>
-      <c r="L320" s="1" t="inlineStr">
+      <c r="L321" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M320" s="1" t="inlineStr">
+      <c r="M321" s="1" t="inlineStr">
         <is>
           <t>Daniela Silva</t>
         </is>
       </c>
-      <c r="N320" s="1" t="n"/>
-      <c r="O320" s="2" t="n">
+      <c r="N321" s="1" t="n"/>
+      <c r="O321" s="2" t="n">
         <v>46181.73338240741</v>
       </c>
-      <c r="P320" s="1" t="inlineStr">
+      <c r="P321" s="1" t="inlineStr">
         <is>
           <t>edileide</t>
         </is>
       </c>
-      <c r="Q320" s="1" t="inlineStr">
+      <c r="Q321" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Boa tarde
 Segue conforme solicitado
 </t>
         </is>
       </c>
-      <c r="R320" s="1" t="inlineStr">
+      <c r="R321" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
-        </is>
-      </c>
-      <c r="S320" s="1" t="n"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="1" t="n">
-        <v>78445</v>
-      </c>
-      <c r="B321" s="1" t="inlineStr">
-        <is>
-          <t>Ata de Reunião</t>
-        </is>
-      </c>
-      <c r="C321" s="1" t="inlineStr">
-        <is>
-          <t>Inclusão de Ata</t>
-        </is>
-      </c>
-      <c r="D321" s="1" t="inlineStr">
-        <is>
-          <t>GC - ADMINISTRATIVO</t>
-        </is>
-      </c>
-      <c r="E321" s="1" t="inlineStr">
-        <is>
-          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025, 11/2025 e 12/2025Verificar se o cliente responde o e-mail com as críticas das NFs de entrada</t>
-        </is>
-      </c>
-      <c r="F321" s="1" t="n">
-        <v>5100</v>
-      </c>
-      <c r="G321" s="1" t="inlineStr">
-        <is>
-          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
-        </is>
-      </c>
-      <c r="H321" s="1" t="inlineStr">
-        <is>
-          <t>Thaiza Oliveira</t>
-        </is>
-      </c>
-      <c r="I321" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="J321" s="2" t="n">
-        <v>46114.57570729167</v>
-      </c>
-      <c r="K321" s="2" t="n">
-        <v>46121</v>
-      </c>
-      <c r="L321" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M321" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N321" s="1" t="n"/>
-      <c r="O321" s="1" t="n"/>
-      <c r="P321" s="1" t="inlineStr"/>
-      <c r="Q321" s="1" t="inlineStr"/>
-      <c r="R321" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
         </is>
       </c>
       <c r="S321" s="1" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>78446</v>
+        <v>78445</v>
       </c>
       <c r="B322" s="1" t="inlineStr">
         <is>
-          <t>Reunião externa</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C322" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D322" s="1" t="inlineStr">
@@ -25207,7 +25243,7 @@
       </c>
       <c r="E322" s="1" t="inlineStr">
         <is>
-          <t>Enviar guia para pagamentoEnviar guia para pagamento</t>
+          <t>Verificar EFD Transporte de Saldo Credor Incorreto ref. 08/2025, 11/2025 e 12/2025Verificar se o cliente responde o e-mail com as críticas das NFs de entrada</t>
         </is>
       </c>
       <c r="F322" s="1" t="n">
@@ -25220,23 +25256,23 @@
       </c>
       <c r="H322" s="1" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I322" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J322" s="2" t="n">
-        <v>46114.57664811343</v>
+        <v>46114.57570729167</v>
       </c>
       <c r="K322" s="2" t="n">
         <v>46121</v>
       </c>
       <c r="L322" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M322" s="1" t="inlineStr">
@@ -25245,38 +25281,28 @@
         </is>
       </c>
       <c r="N322" s="1" t="n"/>
-      <c r="O322" s="2" t="n">
-        <v>46114.61985003472</v>
-      </c>
-      <c r="P322" s="1" t="inlineStr">
-        <is>
-          <t>renatac</t>
-        </is>
-      </c>
-      <c r="Q322" s="1" t="inlineStr">
-        <is>
-          <t>De qual imposto se refere?</t>
-        </is>
-      </c>
+      <c r="O322" s="1" t="n"/>
+      <c r="P322" s="1" t="inlineStr"/>
+      <c r="Q322" s="1" t="inlineStr"/>
       <c r="R322" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S322" s="1" t="n"/>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>79641</v>
+        <v>78446</v>
       </c>
       <c r="B323" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Reunião externa</t>
         </is>
       </c>
       <c r="C323" s="1" t="inlineStr">
         <is>
-          <t>Alteração de Regime Tributário</t>
+          <t>Inclusão de Ata de reunião</t>
         </is>
       </c>
       <c r="D323" s="1" t="inlineStr">
@@ -25286,32 +25312,32 @@
       </c>
       <c r="E323" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração</t>
+          <t>Enviar guia para pagamentoEnviar guia para pagamento</t>
         </is>
       </c>
       <c r="F323" s="1" t="n">
-        <v>5726</v>
+        <v>5100</v>
       </c>
       <c r="G323" s="1" t="inlineStr">
         <is>
-          <t>VIANA &amp; CIA LTDA</t>
+          <t>A P SOARES DA SILVA MERCADO E PADARIA</t>
         </is>
       </c>
       <c r="H323" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Renata Cavalheiro</t>
         </is>
       </c>
       <c r="I323" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J323" s="2" t="n">
-        <v>46175.70509568287</v>
+        <v>46114.57664811343</v>
       </c>
       <c r="K323" s="2" t="n">
-        <v>46178</v>
+        <v>46121</v>
       </c>
       <c r="L323" s="1" t="inlineStr">
         <is>
@@ -25320,21 +25346,21 @@
       </c>
       <c r="M323" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N323" s="1" t="n"/>
       <c r="O323" s="2" t="n">
-        <v>46181.75103634259</v>
+        <v>46114.61985003472</v>
       </c>
       <c r="P323" s="1" t="inlineStr">
         <is>
-          <t>pvolpe</t>
+          <t>renatac</t>
         </is>
       </c>
       <c r="Q323" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">deverá ser aberto um chamado sinalizando o reprocesso dessa empresa </t>
+          <t>De qual imposto se refere?</t>
         </is>
       </c>
       <c r="R323" s="1" t="inlineStr">
@@ -25346,7 +25372,7 @@
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>80110</v>
+        <v>79641</v>
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
@@ -25365,7 +25391,7 @@
       </c>
       <c r="E324" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, boa tarde!Solicitamos o reprocesso das obrigações acessorias do periodo de 2026 devido a alteração de regime tributario do lucro presumido para o lucro real.obs:Chamado aberto anteriormente 79641O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026. </t>
+          <t>Prezados, boa tarde!O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026.Em conversa com o Ronaldo Dias do Paralegal, devemos retificar as obrigações acessórias e as guias de PIS e COFINS que foram recolhidas como lucro presumido, quando concluido devemos comunicá-lo para que faça o pedido da alteração</t>
         </is>
       </c>
       <c r="F324" s="1" t="n">
@@ -25378,7 +25404,7 @@
       </c>
       <c r="H324" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I324" s="1" t="inlineStr">
@@ -25387,14 +25413,14 @@
         </is>
       </c>
       <c r="J324" s="2" t="n">
-        <v>46189.67080621528</v>
+        <v>46175.70509568287</v>
       </c>
       <c r="K324" s="2" t="n">
-        <v>46192</v>
+        <v>46178</v>
       </c>
       <c r="L324" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M324" s="1" t="inlineStr">
@@ -25403,28 +25429,38 @@
         </is>
       </c>
       <c r="N324" s="1" t="n"/>
-      <c r="O324" s="1" t="n"/>
-      <c r="P324" s="1" t="inlineStr"/>
-      <c r="Q324" s="1" t="inlineStr"/>
+      <c r="O324" s="2" t="n">
+        <v>46181.75103634259</v>
+      </c>
+      <c r="P324" s="1" t="inlineStr">
+        <is>
+          <t>pvolpe</t>
+        </is>
+      </c>
+      <c r="Q324" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deverá ser aberto um chamado sinalizando o reprocesso dessa empresa </t>
+        </is>
+      </c>
       <c r="R324" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S324" s="1" t="n"/>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>78447</v>
+        <v>80110</v>
       </c>
       <c r="B325" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Alteração de Regime Tributário</t>
         </is>
       </c>
       <c r="C325" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Alteração de Regime Tributário</t>
         </is>
       </c>
       <c r="D325" s="1" t="inlineStr">
@@ -25434,111 +25470,101 @@
       </c>
       <c r="E325" s="1" t="inlineStr">
         <is>
-          <t>Ref. 01/2026 GIA/EFD Não apresentou GIA/EFD Cobrança RecorrenteVerificar MAED - PGDAS-D em aberto Cobrança Recorrente</t>
+          <t xml:space="preserve">Prezados, boa tarde!Solicitamos o reprocesso das obrigações acessorias do periodo de 2026 devido a alteração de regime tributario do lucro presumido para o lucro real.obs:Chamado aberto anteriormente 79641O cliente em assunto deveria ter migrado para o lucro real no iniciío de 2026. </t>
         </is>
       </c>
       <c r="F325" s="1" t="n">
-        <v>5740</v>
+        <v>5726</v>
       </c>
       <c r="G325" s="1" t="inlineStr">
         <is>
-          <t>MARIA VALDENE FERREIRA RIBEIRO</t>
+          <t>VIANA &amp; CIA LTDA</t>
         </is>
       </c>
       <c r="H325" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I325" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J325" s="2" t="n">
-        <v>46114.58255327546</v>
+        <v>46189.67080621528</v>
       </c>
       <c r="K325" s="2" t="n">
-        <v>46121</v>
+        <v>46192</v>
       </c>
       <c r="L325" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M325" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="N325" s="1" t="n"/>
-      <c r="O325" s="2" t="n">
-        <v>46182.53676319445</v>
-      </c>
-      <c r="P325" s="1" t="inlineStr">
-        <is>
-          <t>lorrane</t>
-        </is>
-      </c>
-      <c r="Q325" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde! Sobre qual empresa essa solicitação?</t>
-        </is>
-      </c>
+      <c r="O325" s="1" t="n"/>
+      <c r="P325" s="1" t="inlineStr"/>
+      <c r="Q325" s="1" t="inlineStr"/>
       <c r="R325" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S325" s="1" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>80095</v>
+        <v>78447</v>
       </c>
       <c r="B326" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C326" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D326" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E326" s="1" t="inlineStr">
         <is>
-          <t>Cliente solicitou a atualização da guia para pagamento da Dctfweb referente ao mês de março/2026 para regularização da pendencia.</t>
+          <t>Ref. 01/2026 GIA/EFD Não apresentou GIA/EFD Cobrança RecorrenteVerificar MAED - PGDAS-D em aberto Cobrança Recorrente</t>
         </is>
       </c>
       <c r="F326" s="1" t="n">
-        <v>5886</v>
+        <v>5740</v>
       </c>
       <c r="G326" s="1" t="inlineStr">
         <is>
-          <t>ITA - TECNOLOGIA ASSISTIVA LTDA</t>
+          <t>MARIA VALDENE FERREIRA RIBEIRO</t>
         </is>
       </c>
       <c r="H326" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I326" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J326" s="2" t="n">
-        <v>46189.54521195602</v>
+        <v>46114.58255327546</v>
       </c>
       <c r="K326" s="2" t="n">
-        <v>46190</v>
+        <v>46121</v>
       </c>
       <c r="L326" s="1" t="inlineStr">
         <is>
@@ -25547,21 +25573,21 @@
       </c>
       <c r="M326" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N326" s="1" t="n"/>
       <c r="O326" s="2" t="n">
-        <v>46191.47922549769</v>
+        <v>46182.53676319445</v>
       </c>
       <c r="P326" s="1" t="inlineStr">
         <is>
-          <t>inascimento</t>
+          <t>lorrane</t>
         </is>
       </c>
       <c r="Q326" s="1" t="inlineStr">
         <is>
-          <t>ENVIADO POR EMAIL</t>
+          <t>Boa tarde! Sobre qual empresa essa solicitação?</t>
         </is>
       </c>
       <c r="R326" s="1" t="inlineStr">
@@ -25573,39 +25599,39 @@
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>80043</v>
+        <v>80095</v>
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
         <is>
-          <t>DCTFWeb</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
         <is>
-          <t>Prezados boa tardePendência - Omissão de DCTFWeb* _________________________________________________________________________________(Período de Apuração)2025 - JAN FEV MAR ABR MAI JUN JUL AGO SET OUT NOV DEZ</t>
+          <t>Cliente solicitou a atualização da guia para pagamento da Dctfweb referente ao mês de março/2026 para regularização da pendencia.</t>
         </is>
       </c>
       <c r="F327" s="1" t="n">
-        <v>5995</v>
+        <v>5886</v>
       </c>
       <c r="G327" s="1" t="inlineStr">
         <is>
-          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
+          <t>ITA - TECNOLOGIA ASSISTIVA LTDA</t>
         </is>
       </c>
       <c r="H327" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I327" s="1" t="inlineStr">
@@ -25614,10 +25640,10 @@
         </is>
       </c>
       <c r="J327" s="2" t="n">
-        <v>46188.60840798611</v>
+        <v>46189.54521195602</v>
       </c>
       <c r="K327" s="2" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="L327" s="1" t="inlineStr">
         <is>
@@ -25626,21 +25652,21 @@
       </c>
       <c r="M327" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N327" s="1" t="n"/>
       <c r="O327" s="2" t="n">
-        <v>46189.6038</v>
+        <v>46191.47922549769</v>
       </c>
       <c r="P327" s="1" t="inlineStr">
         <is>
-          <t>erikas</t>
+          <t>inascimento</t>
         </is>
       </c>
       <c r="Q327" s="1" t="inlineStr">
         <is>
-          <t>Declaração retificadas</t>
+          <t>ENVIADO POR EMAIL</t>
         </is>
       </c>
       <c r="R327" s="1" t="inlineStr">
@@ -25652,51 +25678,51 @@
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>79919</v>
+        <v>80043</v>
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
         <is>
-          <t>Cliente está fazendo um empréstimo junto ao banco e para a liberação desse empréstimo o banco está solicitando o envio da ECF 2026 AB 2025.</t>
+          <t>Prezados boa tardePendência - Omissão de DCTFWeb* _________________________________________________________________________________(Período de Apuração)2025 - JAN FEV MAR ABR MAI JUN JUL AGO SET OUT NOV DEZ</t>
         </is>
       </c>
       <c r="F328" s="1" t="n">
-        <v>6440</v>
+        <v>5995</v>
       </c>
       <c r="G328" s="1" t="inlineStr">
         <is>
-          <t>INFINITY UTILIDADES LTDA</t>
+          <t>LITOCOMP INDUSTRIA GRAFICA E EDITORA LTDA</t>
         </is>
       </c>
       <c r="H328" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I328" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J328" s="2" t="n">
-        <v>46184.5967934375</v>
+        <v>46188.60840798611</v>
       </c>
       <c r="K328" s="2" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="L328" s="1" t="inlineStr">
         <is>
@@ -25705,21 +25731,21 @@
       </c>
       <c r="M328" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="N328" s="1" t="n"/>
       <c r="O328" s="2" t="n">
-        <v>46195.73638541667</v>
+        <v>46189.6038</v>
       </c>
       <c r="P328" s="1" t="inlineStr">
         <is>
-          <t>karinasantos</t>
+          <t>erikas</t>
         </is>
       </c>
       <c r="Q328" s="1" t="inlineStr">
         <is>
-          <t>Entrega realizada</t>
+          <t>Declaração retificadas</t>
         </is>
       </c>
       <c r="R328" s="1" t="inlineStr">
@@ -25838,7 +25864,11 @@
           <t>LSV GESTAO COMERCIO LOCACAO MANUTENCAO DE EQUIPAMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H330" s="1" t="n"/>
+      <c r="H330" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I330" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -25852,7 +25882,7 @@
       </c>
       <c r="L330" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M330" s="1" t="inlineStr">
@@ -25863,7 +25893,7 @@
       <c r="N330" s="1" t="n"/>
       <c r="O330" s="1" t="n"/>
       <c r="P330" s="1" t="inlineStr"/>
-      <c r="Q330" s="1" t="n"/>
+      <c r="Q330" s="1" t="inlineStr"/>
       <c r="R330" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -25903,7 +25933,11 @@
           <t>ARAO PEREIRA DE SA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H331" s="1" t="n"/>
+      <c r="H331" s="1" t="inlineStr">
+        <is>
+          <t>Jackson Silva</t>
+        </is>
+      </c>
       <c r="I331" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -25917,7 +25951,7 @@
       </c>
       <c r="L331" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M331" s="1" t="inlineStr">
@@ -25928,7 +25962,7 @@
       <c r="N331" s="1" t="n"/>
       <c r="O331" s="1" t="n"/>
       <c r="P331" s="1" t="inlineStr"/>
-      <c r="Q331" s="1" t="n"/>
+      <c r="Q331" s="1" t="inlineStr"/>
       <c r="R331" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -25970,7 +26004,7 @@
       </c>
       <c r="H332" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Jackson Silva</t>
         </is>
       </c>
       <c r="I332" s="1" t="inlineStr">

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S574" headerRowCount="1">
-  <autoFilter ref="A1:S574"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S575" headerRowCount="1">
+  <autoFilter ref="A1:S575"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S574"/>
+  <dimension ref="A1:S575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43354,7 +43354,7 @@
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
-        <v>76508</v>
+        <v>80610</v>
       </c>
       <c r="B571" s="1" t="inlineStr">
         <is>
@@ -43363,77 +43363,63 @@
       </c>
       <c r="C571" s="1" t="inlineStr">
         <is>
-          <t>Verificar Validação Obrigação</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D571" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>RJ - CTB</t>
         </is>
       </c>
       <c r="E571" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>Prezados, a tarefa de totalizador do mês 05 da 6547 continua constando como aberta, mesmo já tendo sido validada conforme documentação anexada.</t>
         </is>
       </c>
       <c r="F571" s="1" t="n">
-        <v>6605</v>
+        <v>6547</v>
       </c>
       <c r="G571" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
-        </is>
-      </c>
-      <c r="H571" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
+          <t>PERSONAL FORCE ASSISTANCE &amp; SERVICES LTDA</t>
+        </is>
+      </c>
+      <c r="H571" s="1" t="n"/>
       <c r="I571" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J571" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46203.36833799769</v>
       </c>
       <c r="K571" s="2" t="n">
-        <v>46034</v>
+        <v>46204</v>
       </c>
       <c r="L571" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M571" s="1" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Luis Junior</t>
         </is>
       </c>
       <c r="N571" s="1" t="n"/>
-      <c r="O571" s="2" t="n">
-        <v>46030.75027241898</v>
-      </c>
-      <c r="P571" s="1" t="inlineStr">
-        <is>
-          <t>nicoleo</t>
-        </is>
-      </c>
-      <c r="Q571" s="1" t="inlineStr">
-        <is>
-          <t>Baixadas.</t>
-        </is>
-      </c>
+      <c r="O571" s="1" t="n"/>
+      <c r="P571" s="1" t="inlineStr"/>
+      <c r="Q571" s="1" t="n"/>
       <c r="R571" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S571" s="1" t="n"/>
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
-        <v>76505</v>
+        <v>76508</v>
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
@@ -43452,15 +43438,15 @@
       </c>
       <c r="E572" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F572" s="1" t="n">
-        <v>6640</v>
+        <v>6605</v>
       </c>
       <c r="G572" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H572" s="1" t="inlineStr">
@@ -43474,7 +43460,7 @@
         </is>
       </c>
       <c r="J572" s="2" t="n">
-        <v>46030.60213634259</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K572" s="2" t="n">
         <v>46034</v>
@@ -43491,7 +43477,7 @@
       </c>
       <c r="N572" s="1" t="n"/>
       <c r="O572" s="2" t="n">
-        <v>46030.63182743055</v>
+        <v>46030.75027241898</v>
       </c>
       <c r="P572" s="1" t="inlineStr">
         <is>
@@ -43512,7 +43498,7 @@
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
-        <v>76501</v>
+        <v>76505</v>
       </c>
       <c r="B573" s="1" t="inlineStr">
         <is>
@@ -43531,15 +43517,15 @@
       </c>
       <c r="E573" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F573" s="1" t="n">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="G573" s="1" t="inlineStr">
         <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H573" s="1" t="inlineStr">
@@ -43553,7 +43539,7 @@
         </is>
       </c>
       <c r="J573" s="2" t="n">
-        <v>46030.51327708333</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K573" s="2" t="n">
         <v>46034</v>
@@ -43570,7 +43556,7 @@
       </c>
       <c r="N573" s="1" t="n"/>
       <c r="O573" s="2" t="n">
-        <v>46030.64333047454</v>
+        <v>46030.63182743055</v>
       </c>
       <c r="P573" s="1" t="inlineStr">
         <is>
@@ -43591,7 +43577,7 @@
     </row>
     <row r="574">
       <c r="A574" s="1" t="n">
-        <v>76515</v>
+        <v>76501</v>
       </c>
       <c r="B574" s="1" t="inlineStr">
         <is>
@@ -43610,7 +43596,7 @@
       </c>
       <c r="E574" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
         </is>
       </c>
       <c r="F574" s="1" t="n">
@@ -43632,7 +43618,7 @@
         </is>
       </c>
       <c r="J574" s="2" t="n">
-        <v>46030.73046079861</v>
+        <v>46030.51327708333</v>
       </c>
       <c r="K574" s="2" t="n">
         <v>46034</v>
@@ -43649,24 +43635,103 @@
       </c>
       <c r="N574" s="1" t="n"/>
       <c r="O574" s="2" t="n">
+        <v>46030.64333047454</v>
+      </c>
+      <c r="P574" s="1" t="inlineStr">
+        <is>
+          <t>nicoleo</t>
+        </is>
+      </c>
+      <c r="Q574" s="1" t="inlineStr">
+        <is>
+          <t>Baixadas.</t>
+        </is>
+      </c>
+      <c r="R574" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S574" s="1" t="n"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>76515</v>
+      </c>
+      <c r="B575" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C575" s="1" t="inlineStr">
+        <is>
+          <t>Verificar Validação Obrigação</t>
+        </is>
+      </c>
+      <c r="D575" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E575" s="1" t="inlineStr">
+        <is>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+        </is>
+      </c>
+      <c r="F575" s="1" t="n">
+        <v>6641</v>
+      </c>
+      <c r="G575" s="1" t="inlineStr">
+        <is>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+        </is>
+      </c>
+      <c r="H575" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="I575" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J575" s="2" t="n">
+        <v>46030.73046079861</v>
+      </c>
+      <c r="K575" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L575" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M575" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Castro</t>
+        </is>
+      </c>
+      <c r="N575" s="1" t="n"/>
+      <c r="O575" s="2" t="n">
         <v>46030.74734336806</v>
       </c>
-      <c r="P574" s="1" t="inlineStr">
+      <c r="P575" s="1" t="inlineStr">
         <is>
           <t>nicoleo</t>
         </is>
       </c>
-      <c r="Q574" s="1" t="inlineStr">
+      <c r="Q575" s="1" t="inlineStr">
         <is>
           <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
         </is>
       </c>
-      <c r="R574" s="1" t="inlineStr">
+      <c r="R575" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="S574" s="1" t="n"/>
+      <c r="S575" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L14" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M14" s="1" t="inlineStr">
@@ -1535,12 +1535,22 @@
         </is>
       </c>
       <c r="N14" s="1" t="n"/>
-      <c r="O14" s="1" t="n"/>
-      <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="O14" s="2" t="n">
+        <v>46205.57891142361</v>
+      </c>
+      <c r="P14" s="1" t="inlineStr">
+        <is>
+          <t>inascimento</t>
+        </is>
+      </c>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>ao verificarmos com o cliente ainda não tivemos resposta</t>
+        </is>
+      </c>
       <c r="R14" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S14" s="1" t="n"/>
@@ -12039,7 +12049,7 @@
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M148" s="1" t="inlineStr">
@@ -12048,12 +12058,22 @@
         </is>
       </c>
       <c r="N148" s="1" t="n"/>
-      <c r="O148" s="1" t="n"/>
-      <c r="P148" s="1" t="inlineStr"/>
-      <c r="Q148" s="1" t="inlineStr"/>
+      <c r="O148" s="2" t="n">
+        <v>46205.56024097222</v>
+      </c>
+      <c r="P148" s="1" t="inlineStr">
+        <is>
+          <t>ricardof</t>
+        </is>
+      </c>
+      <c r="Q148" s="1" t="inlineStr">
+        <is>
+          <t>Conforme anexos, as declarações não foram entregues pela MG. O responsável pelo preenchimento é: GILDASIO RIBEIRO MACHADO JUNIOR - CPF 216.647.538-85</t>
+        </is>
+      </c>
       <c r="R148" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S148" s="1" t="n"/>
@@ -13610,7 +13630,7 @@
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M168" s="1" t="inlineStr">
@@ -13621,8 +13641,14 @@
       <c r="N168" s="2" t="n">
         <v>46182.75536666666</v>
       </c>
-      <c r="O168" s="1" t="n"/>
-      <c r="P168" s="1" t="inlineStr"/>
+      <c r="O168" s="2" t="n">
+        <v>46205.55345760417</v>
+      </c>
+      <c r="P168" s="1" t="inlineStr">
+        <is>
+          <t>ricardof</t>
+        </is>
+      </c>
       <c r="Q168" s="1" t="inlineStr">
         <is>
           <t>Aguardando regularização do acesso ao Posto Fiscal com a senha da Alexandra. Sem ela não conseguimos efetuar consultas e retificar GIA.</t>
@@ -13630,7 +13656,7 @@
       </c>
       <c r="R168" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S168" s="1" t="n"/>
@@ -24249,7 +24275,7 @@
       </c>
       <c r="H305" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I305" s="1" t="inlineStr">
@@ -24265,7 +24291,7 @@
       </c>
       <c r="L305" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M305" s="1" t="inlineStr">
@@ -24274,12 +24300,23 @@
         </is>
       </c>
       <c r="N305" s="1" t="n"/>
-      <c r="O305" s="1" t="n"/>
-      <c r="P305" s="1" t="inlineStr"/>
-      <c r="Q305" s="1" t="inlineStr"/>
+      <c r="O305" s="2" t="n">
+        <v>46205.57428920139</v>
+      </c>
+      <c r="P305" s="1" t="inlineStr">
+        <is>
+          <t>pvolpe</t>
+        </is>
+      </c>
+      <c r="Q305" s="1" t="inlineStr">
+        <is>
+          <t>boa tarde
+retificação realizada na data de 02-07</t>
+        </is>
+      </c>
       <c r="R305" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S305" s="1" t="n"/>
@@ -26643,7 +26680,7 @@
       </c>
       <c r="L336" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M336" s="1" t="inlineStr">
@@ -26652,12 +26689,23 @@
         </is>
       </c>
       <c r="N336" s="1" t="n"/>
-      <c r="O336" s="1" t="n"/>
-      <c r="P336" s="1" t="inlineStr"/>
-      <c r="Q336" s="1" t="inlineStr"/>
+      <c r="O336" s="2" t="n">
+        <v>46205.55968140046</v>
+      </c>
+      <c r="P336" s="1" t="inlineStr">
+        <is>
+          <t>fernandaa</t>
+        </is>
+      </c>
+      <c r="Q336" s="1" t="inlineStr">
+        <is>
+          <t>Períodos fechados.
+E-mail enviado ao cliente para que valide junto ao seu Departamento pessoal as divergências dos valores das verbas de folha.</t>
+        </is>
+      </c>
       <c r="R336" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S336" s="1" t="n"/>
@@ -26712,7 +26760,7 @@
       </c>
       <c r="L337" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M337" s="1" t="inlineStr">
@@ -26721,12 +26769,23 @@
         </is>
       </c>
       <c r="N337" s="1" t="n"/>
-      <c r="O337" s="1" t="n"/>
-      <c r="P337" s="1" t="inlineStr"/>
-      <c r="Q337" s="1" t="inlineStr"/>
+      <c r="O337" s="2" t="n">
+        <v>46205.55982739583</v>
+      </c>
+      <c r="P337" s="1" t="inlineStr">
+        <is>
+          <t>fernandaa</t>
+        </is>
+      </c>
+      <c r="Q337" s="1" t="inlineStr">
+        <is>
+          <t>Períodos fechados.
+E-mail enviado ao cliente para que valide junto ao seu Departamento pessoal as divergências dos valores das verbas de folha.</t>
+        </is>
+      </c>
       <c r="R337" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S337" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S605" headerRowCount="1">
-  <autoFilter ref="A1:S605"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:S606" headerRowCount="1">
+  <autoFilter ref="A1:S606"/>
   <tableColumns count="19">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S605"/>
+  <dimension ref="A1:S606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -45855,7 +45855,7 @@
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
-        <v>80743</v>
+        <v>80776</v>
       </c>
       <c r="B601" s="1" t="inlineStr">
         <is>
@@ -45869,22 +45869,18 @@
       </c>
       <c r="D601" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E601" s="1" t="inlineStr">
         <is>
-          <t>5281 - E A P PINGO - NÃO FOI DISPONIBILZAR O PDF PARA BAIXAR TAREFA  DE DESONERAÇÃO DA FOLHA Preciso que baixem minha tarefa, não consigo fazer porque depende de relatório de DCFWEB que não está mais sendo disponibilizado pelo contábil.Att.Vander</t>
+          <t>Boa tarde, referente a tarefa de serviços prestados da empresa 2209, ela não esta aceitando o arquivo em branco (não possui movimento de serviços) poderiam realizar a baixa por favor</t>
         </is>
       </c>
       <c r="F601" s="1" t="n">
-        <v>5281</v>
-      </c>
-      <c r="G601" s="1" t="inlineStr">
-        <is>
-          <t>E A P PINGO REFRIGERAÇÃO</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G601" s="1" t="n"/>
       <c r="H601" s="1" t="inlineStr">
         <is>
           <t>Gabriel Amaral</t>
@@ -45896,45 +45892,35 @@
         </is>
       </c>
       <c r="J601" s="2" t="n">
-        <v>46209.43690501157</v>
+        <v>46209.74850755787</v>
       </c>
       <c r="K601" s="2" t="n">
         <v>46210</v>
       </c>
       <c r="L601" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M601" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Gustavo Tonan</t>
         </is>
       </c>
       <c r="N601" s="1" t="n"/>
-      <c r="O601" s="2" t="n">
-        <v>46209.45948171296</v>
-      </c>
-      <c r="P601" s="1" t="inlineStr">
-        <is>
-          <t>gamaral</t>
-        </is>
-      </c>
-      <c r="Q601" s="1" t="inlineStr">
-        <is>
-          <t>Tarefa baixada</t>
-        </is>
-      </c>
+      <c r="O601" s="1" t="n"/>
+      <c r="P601" s="1" t="inlineStr"/>
+      <c r="Q601" s="1" t="inlineStr"/>
       <c r="R601" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S601" s="1" t="n"/>
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
-        <v>76508</v>
+        <v>80743</v>
       </c>
       <c r="B602" s="1" t="inlineStr">
         <is>
@@ -45943,30 +45929,30 @@
       </c>
       <c r="C602" s="1" t="inlineStr">
         <is>
-          <t>Verificar Validação Obrigação</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D602" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E602" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>5281 - E A P PINGO - NÃO FOI DISPONIBILZAR O PDF PARA BAIXAR TAREFA  DE DESONERAÇÃO DA FOLHA Preciso que baixem minha tarefa, não consigo fazer porque depende de relatório de DCFWEB que não está mais sendo disponibilizado pelo contábil.Att.Vander</t>
         </is>
       </c>
       <c r="F602" s="1" t="n">
-        <v>6605</v>
+        <v>5281</v>
       </c>
       <c r="G602" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
+          <t>E A P PINGO REFRIGERAÇÃO</t>
         </is>
       </c>
       <c r="H602" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I602" s="1" t="inlineStr">
@@ -45975,10 +45961,10 @@
         </is>
       </c>
       <c r="J602" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46209.43690501157</v>
       </c>
       <c r="K602" s="2" t="n">
-        <v>46034</v>
+        <v>46210</v>
       </c>
       <c r="L602" s="1" t="inlineStr">
         <is>
@@ -45987,21 +45973,21 @@
       </c>
       <c r="M602" s="1" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N602" s="1" t="n"/>
       <c r="O602" s="2" t="n">
-        <v>46030.75027241898</v>
+        <v>46209.45948171296</v>
       </c>
       <c r="P602" s="1" t="inlineStr">
         <is>
-          <t>nicoleo</t>
+          <t>gamaral</t>
         </is>
       </c>
       <c r="Q602" s="1" t="inlineStr">
         <is>
-          <t>Baixadas.</t>
+          <t>Tarefa baixada</t>
         </is>
       </c>
       <c r="R602" s="1" t="inlineStr">
@@ -46013,7 +45999,7 @@
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
-        <v>76505</v>
+        <v>76508</v>
       </c>
       <c r="B603" s="1" t="inlineStr">
         <is>
@@ -46032,15 +46018,15 @@
       </c>
       <c r="E603" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F603" s="1" t="n">
-        <v>6640</v>
+        <v>6605</v>
       </c>
       <c r="G603" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H603" s="1" t="inlineStr">
@@ -46054,7 +46040,7 @@
         </is>
       </c>
       <c r="J603" s="2" t="n">
-        <v>46030.60213634259</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K603" s="2" t="n">
         <v>46034</v>
@@ -46071,7 +46057,7 @@
       </c>
       <c r="N603" s="1" t="n"/>
       <c r="O603" s="2" t="n">
-        <v>46030.63182743055</v>
+        <v>46030.75027241898</v>
       </c>
       <c r="P603" s="1" t="inlineStr">
         <is>
@@ -46092,7 +46078,7 @@
     </row>
     <row r="604">
       <c r="A604" s="1" t="n">
-        <v>76515</v>
+        <v>76505</v>
       </c>
       <c r="B604" s="1" t="inlineStr">
         <is>
@@ -46111,15 +46097,15 @@
       </c>
       <c r="E604" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F604" s="1" t="n">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="G604" s="1" t="inlineStr">
         <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H604" s="1" t="inlineStr">
@@ -46133,7 +46119,7 @@
         </is>
       </c>
       <c r="J604" s="2" t="n">
-        <v>46030.73046079861</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K604" s="2" t="n">
         <v>46034</v>
@@ -46150,7 +46136,7 @@
       </c>
       <c r="N604" s="1" t="n"/>
       <c r="O604" s="2" t="n">
-        <v>46030.74734336806</v>
+        <v>46030.63182743055</v>
       </c>
       <c r="P604" s="1" t="inlineStr">
         <is>
@@ -46159,7 +46145,7 @@
       </c>
       <c r="Q604" s="1" t="inlineStr">
         <is>
-          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
+          <t>Baixadas.</t>
         </is>
       </c>
       <c r="R604" s="1" t="inlineStr">
@@ -46171,7 +46157,7 @@
     </row>
     <row r="605">
       <c r="A605" s="1" t="n">
-        <v>76501</v>
+        <v>76515</v>
       </c>
       <c r="B605" s="1" t="inlineStr">
         <is>
@@ -46190,7 +46176,7 @@
       </c>
       <c r="E605" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
         </is>
       </c>
       <c r="F605" s="1" t="n">
@@ -46212,7 +46198,7 @@
         </is>
       </c>
       <c r="J605" s="2" t="n">
-        <v>46030.51327708333</v>
+        <v>46030.73046079861</v>
       </c>
       <c r="K605" s="2" t="n">
         <v>46034</v>
@@ -46229,24 +46215,103 @@
       </c>
       <c r="N605" s="1" t="n"/>
       <c r="O605" s="2" t="n">
+        <v>46030.74734336806</v>
+      </c>
+      <c r="P605" s="1" t="inlineStr">
+        <is>
+          <t>nicoleo</t>
+        </is>
+      </c>
+      <c r="Q605" s="1" t="inlineStr">
+        <is>
+          <t>Tarefas se encontram baixadas conforme solicitado no chamado: 76436.</t>
+        </is>
+      </c>
+      <c r="R605" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S605" s="1" t="n"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="n">
+        <v>76501</v>
+      </c>
+      <c r="B606" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C606" s="1" t="inlineStr">
+        <is>
+          <t>Verificar Validação Obrigação</t>
+        </is>
+      </c>
+      <c r="D606" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E606" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+        </is>
+      </c>
+      <c r="F606" s="1" t="n">
+        <v>6641</v>
+      </c>
+      <c r="G606" s="1" t="inlineStr">
+        <is>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+        </is>
+      </c>
+      <c r="H606" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="I606" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J606" s="2" t="n">
+        <v>46030.51327708333</v>
+      </c>
+      <c r="K606" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L606" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M606" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Castro</t>
+        </is>
+      </c>
+      <c r="N606" s="1" t="n"/>
+      <c r="O606" s="2" t="n">
         <v>46030.64333047454</v>
       </c>
-      <c r="P605" s="1" t="inlineStr">
+      <c r="P606" s="1" t="inlineStr">
         <is>
           <t>nicoleo</t>
         </is>
       </c>
-      <c r="Q605" s="1" t="inlineStr">
+      <c r="Q606" s="1" t="inlineStr">
         <is>
           <t>Baixadas.</t>
         </is>
       </c>
-      <c r="R605" s="1" t="inlineStr">
+      <c r="R606" s="1" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
       </c>
-      <c r="S605" s="1" t="n"/>
+      <c r="S606" s="1" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -14219,7 +14219,7 @@
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M169" s="1" t="inlineStr">
@@ -14227,9 +14227,17 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N169" s="1" t="n"/>
-      <c r="O169" s="1" t="n"/>
-      <c r="P169" s="1" t="inlineStr"/>
+      <c r="N169" s="2" t="n">
+        <v>46183.62114679398</v>
+      </c>
+      <c r="O169" s="2" t="n">
+        <v>46211.66080744213</v>
+      </c>
+      <c r="P169" s="1" t="inlineStr">
+        <is>
+          <t>thaizao</t>
+        </is>
+      </c>
       <c r="Q169" s="1" t="inlineStr">
         <is>
           <t>Aguardando definição gerencia departamento e gerencia operacional</t>
@@ -14237,7 +14245,7 @@
       </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S169" s="1" t="n"/>
@@ -18401,7 +18409,7 @@
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M220" s="1" t="inlineStr">
@@ -18409,9 +18417,17 @@
           <t>Yasmin Peixoto</t>
         </is>
       </c>
-      <c r="N220" s="1" t="n"/>
-      <c r="O220" s="1" t="n"/>
-      <c r="P220" s="1" t="inlineStr"/>
+      <c r="N220" s="2" t="n">
+        <v>46183.62145471065</v>
+      </c>
+      <c r="O220" s="2" t="n">
+        <v>46211.66036420139</v>
+      </c>
+      <c r="P220" s="1" t="inlineStr">
+        <is>
+          <t>thaizao</t>
+        </is>
+      </c>
       <c r="Q220" s="1" t="inlineStr">
         <is>
           <t>Aguardando definição gerencia departamento e gerencia operacional</t>
@@ -18419,7 +18435,7 @@
       </c>
       <c r="R220" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="S220" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:T586" headerRowCount="1">
-  <autoFilter ref="A1:T586"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:T587" headerRowCount="1">
+  <autoFilter ref="A1:T587"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T586"/>
+  <dimension ref="A1:T587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43749,7 +43749,7 @@
     </row>
     <row r="582">
       <c r="A582" s="1" t="n">
-        <v>80672</v>
+        <v>80930</v>
       </c>
       <c r="B582" s="1" t="inlineStr">
         <is>
@@ -43758,52 +43758,46 @@
       </c>
       <c r="C582" s="1" t="inlineStr">
         <is>
-          <t>Criação de Tarefas</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D582" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>RJ - DP</t>
         </is>
       </c>
       <c r="E582" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Solicito a criação da tarefa manual: Regularização eSocial - Intermitente. Esta tarefa deverá exigir o e-mail de retorno ao cliente para executar a baixa.</t>
+          <t>Por favor, baixar a tarefa eSocial - Fechamento mensal da empresa 6684 - Nova Moda Comercio de Roupas Calçados e Acessórios, porque a empresa não possui colaboradores ativos.</t>
         </is>
       </c>
       <c r="F582" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G582" s="1" t="n"/>
-      <c r="H582" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
+      <c r="H582" s="1" t="n"/>
       <c r="I582" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J582" s="2" t="n">
-        <v>46204.49980644676</v>
+        <v>46212.41216331018</v>
       </c>
       <c r="K582" s="2" t="n">
-        <v>46206</v>
+        <v>46213</v>
       </c>
       <c r="L582" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M582" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
-      <c r="N582" s="2" t="n">
-        <v>46209.45593140047</v>
-      </c>
+          <t>Rosilene Silva</t>
+        </is>
+      </c>
+      <c r="N582" s="1" t="n"/>
       <c r="O582" s="1" t="n"/>
       <c r="P582" s="1" t="n"/>
       <c r="Q582" s="1" t="inlineStr"/>
@@ -43817,7 +43811,7 @@
     </row>
     <row r="583">
       <c r="A583" s="1" t="n">
-        <v>76508</v>
+        <v>80672</v>
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
@@ -43826,30 +43820,26 @@
       </c>
       <c r="C583" s="1" t="inlineStr">
         <is>
-          <t>Verificar Validação Obrigação</t>
+          <t>Criação de Tarefas</t>
         </is>
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>Bom dia!!Solicito a criação da tarefa manual: Regularização eSocial - Intermitente. Esta tarefa deverá exigir o e-mail de retorno ao cliente para executar a baixa.</t>
         </is>
       </c>
       <c r="F583" s="1" t="n">
-        <v>6605</v>
-      </c>
-      <c r="G583" s="1" t="inlineStr">
-        <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G583" s="1" t="n"/>
       <c r="H583" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I583" s="1" t="inlineStr">
@@ -43858,34 +43848,30 @@
         </is>
       </c>
       <c r="J583" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46204.49980644676</v>
       </c>
       <c r="K583" s="2" t="n">
-        <v>46034</v>
+        <v>46206</v>
       </c>
       <c r="L583" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N583" s="1" t="n"/>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>46209.45593140047</v>
+      </c>
       <c r="O583" s="1" t="n"/>
-      <c r="P583" s="3" t="n">
-        <v>46030.75027241898</v>
-      </c>
-      <c r="Q583" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
+      <c r="P583" s="1" t="n"/>
+      <c r="Q583" s="1" t="inlineStr"/>
       <c r="R583" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S583" s="1" t="n"/>
@@ -43893,7 +43879,7 @@
     </row>
     <row r="584">
       <c r="A584" s="1" t="n">
-        <v>76505</v>
+        <v>76508</v>
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
@@ -43912,15 +43898,15 @@
       </c>
       <c r="E584" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F584" s="1" t="n">
-        <v>6640</v>
+        <v>6605</v>
       </c>
       <c r="G584" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H584" s="1" t="inlineStr">
@@ -43934,7 +43920,7 @@
         </is>
       </c>
       <c r="J584" s="2" t="n">
-        <v>46030.60213634259</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K584" s="2" t="n">
         <v>46034</v>
@@ -43952,7 +43938,7 @@
       <c r="N584" s="1" t="n"/>
       <c r="O584" s="1" t="n"/>
       <c r="P584" s="3" t="n">
-        <v>46030.63182743055</v>
+        <v>46030.75027241898</v>
       </c>
       <c r="Q584" s="1" t="inlineStr">
         <is>
@@ -43969,7 +43955,7 @@
     </row>
     <row r="585">
       <c r="A585" s="1" t="n">
-        <v>76515</v>
+        <v>76505</v>
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
@@ -43988,15 +43974,15 @@
       </c>
       <c r="E585" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F585" s="1" t="n">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="G585" s="1" t="inlineStr">
         <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H585" s="1" t="inlineStr">
@@ -44010,7 +43996,7 @@
         </is>
       </c>
       <c r="J585" s="2" t="n">
-        <v>46030.73046079861</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K585" s="2" t="n">
         <v>46034</v>
@@ -44028,7 +44014,7 @@
       <c r="N585" s="1" t="n"/>
       <c r="O585" s="1" t="n"/>
       <c r="P585" s="3" t="n">
-        <v>46030.74734336806</v>
+        <v>46030.63182743055</v>
       </c>
       <c r="Q585" s="1" t="inlineStr">
         <is>
@@ -44045,7 +44031,7 @@
     </row>
     <row r="586">
       <c r="A586" s="1" t="n">
-        <v>76501</v>
+        <v>76515</v>
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
@@ -44064,7 +44050,7 @@
       </c>
       <c r="E586" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
         </is>
       </c>
       <c r="F586" s="1" t="n">
@@ -44086,7 +44072,7 @@
         </is>
       </c>
       <c r="J586" s="2" t="n">
-        <v>46030.51327708333</v>
+        <v>46030.73046079861</v>
       </c>
       <c r="K586" s="2" t="n">
         <v>46034</v>
@@ -44104,7 +44090,7 @@
       <c r="N586" s="1" t="n"/>
       <c r="O586" s="1" t="n"/>
       <c r="P586" s="3" t="n">
-        <v>46030.64333047454</v>
+        <v>46030.74734336806</v>
       </c>
       <c r="Q586" s="1" t="inlineStr">
         <is>
@@ -44118,6 +44104,82 @@
       </c>
       <c r="S586" s="1" t="n"/>
       <c r="T586" s="1" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>76501</v>
+      </c>
+      <c r="B587" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C587" s="1" t="inlineStr">
+        <is>
+          <t>Verificar Validação Obrigação</t>
+        </is>
+      </c>
+      <c r="D587" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E587" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+        </is>
+      </c>
+      <c r="F587" s="1" t="n">
+        <v>6641</v>
+      </c>
+      <c r="G587" s="1" t="inlineStr">
+        <is>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+        </is>
+      </c>
+      <c r="H587" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="I587" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J587" s="2" t="n">
+        <v>46030.51327708333</v>
+      </c>
+      <c r="K587" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L587" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M587" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Castro</t>
+        </is>
+      </c>
+      <c r="N587" s="1" t="n"/>
+      <c r="O587" s="1" t="n"/>
+      <c r="P587" s="3" t="n">
+        <v>46030.64333047454</v>
+      </c>
+      <c r="Q587" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="R587" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S587" s="1" t="n"/>
+      <c r="T587" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:T587" headerRowCount="1">
-  <autoFilter ref="A1:T587"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:T588" headerRowCount="1">
+  <autoFilter ref="A1:T588"/>
   <tableColumns count="20">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T587"/>
+  <dimension ref="A1:T588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -43811,7 +43811,7 @@
     </row>
     <row r="583">
       <c r="A583" s="1" t="n">
-        <v>80672</v>
+        <v>80933</v>
       </c>
       <c r="B583" s="1" t="inlineStr">
         <is>
@@ -43820,52 +43820,46 @@
       </c>
       <c r="C583" s="1" t="inlineStr">
         <is>
-          <t>Criação de Tarefas</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D583" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>SANTOS - EF</t>
         </is>
       </c>
       <c r="E583" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!!Solicito a criação da tarefa manual: Regularização eSocial - Intermitente. Esta tarefa deverá exigir o e-mail de retorno ao cliente para executar a baixa.</t>
+          <t>Boa tarde, estou com problema para dar baixa na na empresa 2648 - JC Marketing, na tarefa de Reinf. Ao colocar o recibo fica dando erro, e também já tentei pela baixa automatica mas não funcionou.Se possível pode dar baixa pra mim na tarefa.</t>
         </is>
       </c>
       <c r="F583" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G583" s="1" t="n"/>
-      <c r="H583" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
+      <c r="H583" s="1" t="n"/>
       <c r="I583" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J583" s="2" t="n">
-        <v>46204.49980644676</v>
+        <v>46212.72987685185</v>
       </c>
       <c r="K583" s="2" t="n">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="L583" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M583" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
-        </is>
-      </c>
-      <c r="N583" s="2" t="n">
-        <v>46209.45593140047</v>
-      </c>
+          <t>Jasmina Melo</t>
+        </is>
+      </c>
+      <c r="N583" s="1" t="n"/>
       <c r="O583" s="1" t="n"/>
       <c r="P583" s="1" t="n"/>
       <c r="Q583" s="1" t="inlineStr"/>
@@ -43879,7 +43873,7 @@
     </row>
     <row r="584">
       <c r="A584" s="1" t="n">
-        <v>76508</v>
+        <v>80672</v>
       </c>
       <c r="B584" s="1" t="inlineStr">
         <is>
@@ -43888,30 +43882,26 @@
       </c>
       <c r="C584" s="1" t="inlineStr">
         <is>
-          <t>Verificar Validação Obrigação</t>
+          <t>Criação de Tarefas</t>
         </is>
       </c>
       <c r="D584" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E584" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
+          <t>Bom dia!!Solicito a criação da tarefa manual: Regularização eSocial - Intermitente. Esta tarefa deverá exigir o e-mail de retorno ao cliente para executar a baixa.</t>
         </is>
       </c>
       <c r="F584" s="1" t="n">
-        <v>6605</v>
-      </c>
-      <c r="G584" s="1" t="inlineStr">
-        <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G584" s="1" t="n"/>
       <c r="H584" s="1" t="inlineStr">
         <is>
-          <t>Nicole Oliveira</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I584" s="1" t="inlineStr">
@@ -43920,34 +43910,30 @@
         </is>
       </c>
       <c r="J584" s="2" t="n">
-        <v>46030.67108090278</v>
+        <v>46204.49980644676</v>
       </c>
       <c r="K584" s="2" t="n">
-        <v>46034</v>
+        <v>46206</v>
       </c>
       <c r="L584" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M584" s="1" t="inlineStr">
         <is>
-          <t>Bianca Castro</t>
-        </is>
-      </c>
-      <c r="N584" s="1" t="n"/>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>46209.45593140047</v>
+      </c>
       <c r="O584" s="1" t="n"/>
-      <c r="P584" s="3" t="n">
-        <v>46030.75027241898</v>
-      </c>
-      <c r="Q584" s="1" t="inlineStr">
-        <is>
-          <t>Nicole Oliveira</t>
-        </is>
-      </c>
+      <c r="P584" s="1" t="n"/>
+      <c r="Q584" s="1" t="inlineStr"/>
       <c r="R584" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="S584" s="1" t="n"/>
@@ -43955,7 +43941,7 @@
     </row>
     <row r="585">
       <c r="A585" s="1" t="n">
-        <v>76505</v>
+        <v>76508</v>
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
@@ -43974,15 +43960,15 @@
       </c>
       <c r="E585" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
+          <t>Por favor, fazer baixa das tarefas de cadastro de e-mail para as filiais abaixo, pois só fazemos cadastro para as matrizes6605 - RESTAURANTE FLV RAIZ LTDA (FILIAL 1) SP6606 - RESTAURANTE FLV RAIZ LTDA (FILIAL 2) SP6607 - RESTAURANTE FLV RAIZ LTDA (FILIAL 3) SP6608 - RESTAURANTE FLV RAIZ LTDA (FILIAL 4) SP</t>
         </is>
       </c>
       <c r="F585" s="1" t="n">
-        <v>6640</v>
+        <v>6605</v>
       </c>
       <c r="G585" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H585" s="1" t="inlineStr">
@@ -43996,7 +43982,7 @@
         </is>
       </c>
       <c r="J585" s="2" t="n">
-        <v>46030.60213634259</v>
+        <v>46030.67108090278</v>
       </c>
       <c r="K585" s="2" t="n">
         <v>46034</v>
@@ -44014,7 +44000,7 @@
       <c r="N585" s="1" t="n"/>
       <c r="O585" s="1" t="n"/>
       <c r="P585" s="3" t="n">
-        <v>46030.63182743055</v>
+        <v>46030.75027241898</v>
       </c>
       <c r="Q585" s="1" t="inlineStr">
         <is>
@@ -44031,7 +44017,7 @@
     </row>
     <row r="586">
       <c r="A586" s="1" t="n">
-        <v>76515</v>
+        <v>76505</v>
       </c>
       <c r="B586" s="1" t="inlineStr">
         <is>
@@ -44050,15 +44036,15 @@
       </c>
       <c r="E586" s="1" t="inlineStr">
         <is>
-          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
+          <t>Boa tarde.Por gentileza, excluir tarefas de Procurações ref a empresa 6640 - FORT FRUIT LTDA, pois a mesma não faz DP com a MG</t>
         </is>
       </c>
       <c r="F586" s="1" t="n">
-        <v>6641</v>
+        <v>6640</v>
       </c>
       <c r="G586" s="1" t="inlineStr">
         <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+          <t>FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H586" s="1" t="inlineStr">
@@ -44072,7 +44058,7 @@
         </is>
       </c>
       <c r="J586" s="2" t="n">
-        <v>46030.73046079861</v>
+        <v>46030.60213634259</v>
       </c>
       <c r="K586" s="2" t="n">
         <v>46034</v>
@@ -44090,7 +44076,7 @@
       <c r="N586" s="1" t="n"/>
       <c r="O586" s="1" t="n"/>
       <c r="P586" s="3" t="n">
-        <v>46030.74734336806</v>
+        <v>46030.63182743055</v>
       </c>
       <c r="Q586" s="1" t="inlineStr">
         <is>
@@ -44107,7 +44093,7 @@
     </row>
     <row r="587">
       <c r="A587" s="1" t="n">
-        <v>76501</v>
+        <v>76515</v>
       </c>
       <c r="B587" s="1" t="inlineStr">
         <is>
@@ -44126,7 +44112,7 @@
       </c>
       <c r="E587" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+          <t>Por favor, fazer baixa das tarefas de Procurações (DET, CONECTIVIDADE, FGTS, FAP) da empresa 6641 - FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA, pois não tem DP conosco.</t>
         </is>
       </c>
       <c r="F587" s="1" t="n">
@@ -44148,7 +44134,7 @@
         </is>
       </c>
       <c r="J587" s="2" t="n">
-        <v>46030.51327708333</v>
+        <v>46030.73046079861</v>
       </c>
       <c r="K587" s="2" t="n">
         <v>46034</v>
@@ -44166,7 +44152,7 @@
       <c r="N587" s="1" t="n"/>
       <c r="O587" s="1" t="n"/>
       <c r="P587" s="3" t="n">
-        <v>46030.64333047454</v>
+        <v>46030.74734336806</v>
       </c>
       <c r="Q587" s="1" t="inlineStr">
         <is>
@@ -44180,6 +44166,82 @@
       </c>
       <c r="S587" s="1" t="n"/>
       <c r="T587" s="1" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>76501</v>
+      </c>
+      <c r="B588" s="1" t="inlineStr">
+        <is>
+          <t>MG Controle</t>
+        </is>
+      </c>
+      <c r="C588" s="1" t="inlineStr">
+        <is>
+          <t>Verificar Validação Obrigação</t>
+        </is>
+      </c>
+      <c r="D588" s="1" t="inlineStr">
+        <is>
+          <t>GC - ADMINISTRATIVO</t>
+        </is>
+      </c>
+      <c r="E588" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde.Por favor, fazer baixa da tarefa de cadastro de e-mail Dec Municipal da loja 6640 - FORT FRUIT LTDA SP, pois a mesma não faz parte do município de SP</t>
+        </is>
+      </c>
+      <c r="F588" s="1" t="n">
+        <v>6641</v>
+      </c>
+      <c r="G588" s="1" t="inlineStr">
+        <is>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+        </is>
+      </c>
+      <c r="H588" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="I588" s="1" t="inlineStr">
+        <is>
+          <t>CONTROLADORIA</t>
+        </is>
+      </c>
+      <c r="J588" s="2" t="n">
+        <v>46030.51327708333</v>
+      </c>
+      <c r="K588" s="2" t="n">
+        <v>46034</v>
+      </c>
+      <c r="L588" s="1" t="inlineStr">
+        <is>
+          <t>Entregue Ao Solicitante</t>
+        </is>
+      </c>
+      <c r="M588" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Castro</t>
+        </is>
+      </c>
+      <c r="N588" s="1" t="n"/>
+      <c r="O588" s="1" t="n"/>
+      <c r="P588" s="3" t="n">
+        <v>46030.64333047454</v>
+      </c>
+      <c r="Q588" s="1" t="inlineStr">
+        <is>
+          <t>Nicole Oliveira</t>
+        </is>
+      </c>
+      <c r="R588" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="S588" s="1" t="n"/>
+      <c r="T588" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U301" headerRowCount="1">
-  <autoFilter ref="A1:U301"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U299" headerRowCount="1">
+  <autoFilter ref="A1:U299"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U301"/>
+  <dimension ref="A1:U299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5597,7 +5597,11 @@
           <t>PRISTELA PIZZARIA LTDA</t>
         </is>
       </c>
-      <c r="H62" s="1" t="n"/>
+      <c r="H62" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I62" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -5611,7 +5615,7 @@
       </c>
       <c r="L62" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M62" s="1" t="inlineStr">
@@ -5623,14 +5627,18 @@
       <c r="O62" s="1" t="n"/>
       <c r="P62" s="1" t="n"/>
       <c r="Q62" s="1" t="inlineStr"/>
-      <c r="R62" s="1" t="n"/>
+      <c r="R62" s="1" t="inlineStr"/>
       <c r="S62" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T62" s="1" t="n"/>
-      <c r="U62" s="1" t="inlineStr"/>
+      <c r="U62" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -7791,7 +7799,7 @@
       </c>
       <c r="H89" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I89" s="1" t="inlineStr">
@@ -7807,7 +7815,7 @@
       </c>
       <c r="L89" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M89" s="1" t="inlineStr">
@@ -7815,11 +7823,18 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N89" s="1" t="n"/>
+      <c r="N89" s="2" t="n">
+        <v>46216.36492291667</v>
+      </c>
       <c r="O89" s="1" t="n"/>
       <c r="P89" s="1" t="n"/>
       <c r="Q89" s="1" t="inlineStr"/>
-      <c r="R89" s="1" t="inlineStr"/>
+      <c r="R89" s="1" t="inlineStr">
+        <is>
+          <t>operação em validação 
+25-07</t>
+        </is>
+      </c>
       <c r="S89" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -8772,7 +8787,7 @@
       </c>
       <c r="L101" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M101" s="1" t="inlineStr">
@@ -8782,14 +8797,8 @@
       </c>
       <c r="N101" s="1" t="n"/>
       <c r="O101" s="1" t="n"/>
-      <c r="P101" s="2" t="n">
-        <v>46213.47285034722</v>
-      </c>
-      <c r="Q101" s="1" t="inlineStr">
-        <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
+      <c r="P101" s="1" t="n"/>
+      <c r="Q101" s="1" t="inlineStr"/>
       <c r="R101" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
@@ -8798,7 +8807,7 @@
       </c>
       <c r="S101" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T101" s="1" t="n"/>
@@ -9924,7 +9933,11 @@
           <t>PERFIL REFRIGERAÇÃO INDUSTRIA ,COMÉRCIO E SERVIÇO LTDA</t>
         </is>
       </c>
-      <c r="H115" s="1" t="n"/>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I115" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -9938,7 +9951,7 @@
       </c>
       <c r="L115" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M115" s="1" t="inlineStr">
@@ -9950,14 +9963,18 @@
       <c r="O115" s="1" t="n"/>
       <c r="P115" s="1" t="n"/>
       <c r="Q115" s="1" t="inlineStr"/>
-      <c r="R115" s="1" t="n"/>
+      <c r="R115" s="1" t="inlineStr"/>
       <c r="S115" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T115" s="1" t="n"/>
-      <c r="U115" s="1" t="inlineStr"/>
+      <c r="U115" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -11922,7 +11939,11 @@
           <t>MAC FRIO DISTRIBUIDORA LTDA</t>
         </is>
       </c>
-      <c r="H139" s="1" t="n"/>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -11936,7 +11957,7 @@
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M139" s="1" t="inlineStr">
@@ -11944,18 +11965,29 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N139" s="1" t="n"/>
+      <c r="N139" s="2" t="n">
+        <v>46216.373265625</v>
+      </c>
       <c r="O139" s="1" t="n"/>
       <c r="P139" s="1" t="n"/>
       <c r="Q139" s="1" t="inlineStr"/>
-      <c r="R139" s="1" t="n"/>
+      <c r="R139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERAÇÃO EM FASE DE EXECUÇÃO 
+</t>
+        </is>
+      </c>
       <c r="S139" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T139" s="1" t="n"/>
-      <c r="U139" s="1" t="inlineStr"/>
+      <c r="U139" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -11989,7 +12021,11 @@
           <t>M &amp; M INDUSTRIA E COMERCIO LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H140" s="1" t="n"/>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -12003,7 +12039,7 @@
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M140" s="1" t="inlineStr">
@@ -12011,18 +12047,28 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N140" s="1" t="n"/>
+      <c r="N140" s="2" t="n">
+        <v>46216.37073711806</v>
+      </c>
       <c r="O140" s="1" t="n"/>
       <c r="P140" s="1" t="n"/>
       <c r="Q140" s="1" t="inlineStr"/>
-      <c r="R140" s="1" t="n"/>
+      <c r="R140" s="1" t="inlineStr">
+        <is>
+          <t>OPERAÇÃO IRÁ REALIZAR A ENTREGA</t>
+        </is>
+      </c>
       <c r="S140" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T140" s="1" t="n"/>
-      <c r="U140" s="1" t="inlineStr"/>
+      <c r="U140" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -13276,7 +13322,11 @@
           <t>AMATRUDA LOCADORA DE GUINDASTES E ARTICULADOS LTDA</t>
         </is>
       </c>
-      <c r="H156" s="1" t="n"/>
+      <c r="H156" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -13290,7 +13340,7 @@
       </c>
       <c r="L156" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M156" s="1" t="inlineStr">
@@ -13302,14 +13352,18 @@
       <c r="O156" s="1" t="n"/>
       <c r="P156" s="1" t="n"/>
       <c r="Q156" s="1" t="inlineStr"/>
-      <c r="R156" s="1" t="n"/>
+      <c r="R156" s="1" t="inlineStr"/>
       <c r="S156" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T156" s="1" t="n"/>
-      <c r="U156" s="1" t="inlineStr"/>
+      <c r="U156" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -14235,7 +14289,11 @@
           <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
         </is>
       </c>
-      <c r="H168" s="1" t="n"/>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14249,7 +14307,7 @@
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M168" s="1" t="inlineStr">
@@ -14257,18 +14315,28 @@
           <t>Rogerio Egidio</t>
         </is>
       </c>
-      <c r="N168" s="1" t="n"/>
+      <c r="N168" s="2" t="n">
+        <v>46216.37496550926</v>
+      </c>
       <c r="O168" s="1" t="n"/>
       <c r="P168" s="1" t="n"/>
       <c r="Q168" s="1" t="inlineStr"/>
-      <c r="R168" s="1" t="n"/>
+      <c r="R168" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM EXECUÇÃO PELA OPERAÇÃO </t>
+        </is>
+      </c>
       <c r="S168" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T168" s="1" t="n"/>
-      <c r="U168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -14390,7 +14458,7 @@
       </c>
       <c r="H170" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I170" s="1" t="inlineStr">
@@ -14406,7 +14474,7 @@
       </c>
       <c r="L170" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M170" s="1" t="inlineStr">
@@ -14416,12 +14484,22 @@
       </c>
       <c r="N170" s="1" t="n"/>
       <c r="O170" s="1" t="n"/>
-      <c r="P170" s="1" t="n"/>
-      <c r="Q170" s="1" t="inlineStr"/>
-      <c r="R170" s="1" t="inlineStr"/>
+      <c r="P170" s="2" t="n">
+        <v>46216.37008005787</v>
+      </c>
+      <c r="Q170" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R170" s="1" t="inlineStr">
+        <is>
+          <t>PRCOESSO REALIZADO EM 10-07-2026</t>
+        </is>
+      </c>
       <c r="S170" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T170" s="1" t="n"/>
@@ -14463,7 +14541,11 @@
           <t xml:space="preserve">MAGAZINE DAS PANELAS LTDA </t>
         </is>
       </c>
-      <c r="H171" s="1" t="n"/>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14477,7 +14559,7 @@
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M171" s="1" t="inlineStr">
@@ -14489,14 +14571,18 @@
       <c r="O171" s="1" t="n"/>
       <c r="P171" s="1" t="n"/>
       <c r="Q171" s="1" t="inlineStr"/>
-      <c r="R171" s="1" t="n"/>
+      <c r="R171" s="1" t="inlineStr"/>
       <c r="S171" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T171" s="1" t="n"/>
-      <c r="U171" s="1" t="inlineStr"/>
+      <c r="U171" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -24025,132 +24111,6 @@
       <c r="T299" s="1" t="n"/>
       <c r="U299" s="1" t="inlineStr"/>
     </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>80949</v>
-      </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C300" s="1" t="inlineStr">
-        <is>
-          <t>Erro de Baixa</t>
-        </is>
-      </c>
-      <c r="D300" s="1" t="inlineStr">
-        <is>
-          <t>RJ - EF</t>
-        </is>
-      </c>
-      <c r="E300" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde, poderiam por gentileza baixar a tarefa "confirmação de faturamento"empresas;6957/6965motivo; empresas simples nacional.At.te</t>
-        </is>
-      </c>
-      <c r="F300" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G300" s="1" t="n"/>
-      <c r="H300" s="1" t="n"/>
-      <c r="I300" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J300" s="2" t="n">
-        <v>46213.65257700231</v>
-      </c>
-      <c r="K300" s="2" t="n">
-        <v>46216</v>
-      </c>
-      <c r="L300" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M300" s="1" t="inlineStr">
-        <is>
-          <t>Beatriz Oliveira</t>
-        </is>
-      </c>
-      <c r="N300" s="1" t="n"/>
-      <c r="O300" s="1" t="n"/>
-      <c r="P300" s="1" t="n"/>
-      <c r="Q300" s="1" t="inlineStr"/>
-      <c r="R300" s="1" t="n"/>
-      <c r="S300" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T300" s="1" t="n"/>
-      <c r="U300" s="1" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="1" t="n">
-        <v>80950</v>
-      </c>
-      <c r="B301" s="1" t="inlineStr">
-        <is>
-          <t>MG Controle</t>
-        </is>
-      </c>
-      <c r="C301" s="1" t="inlineStr">
-        <is>
-          <t>Erro de Baixa</t>
-        </is>
-      </c>
-      <c r="D301" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E301" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde!Por favor baixar  a tarefa eSocial - Fechamento Mensal da empresa 2791, erro no relatório de base s5012.</t>
-        </is>
-      </c>
-      <c r="F301" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G301" s="1" t="n"/>
-      <c r="H301" s="1" t="n"/>
-      <c r="I301" s="1" t="inlineStr">
-        <is>
-          <t>CONTROLADORIA</t>
-        </is>
-      </c>
-      <c r="J301" s="2" t="n">
-        <v>46213.66592195602</v>
-      </c>
-      <c r="K301" s="2" t="n">
-        <v>46216</v>
-      </c>
-      <c r="L301" s="1" t="inlineStr">
-        <is>
-          <t>Sem Responsavel Atribuido</t>
-        </is>
-      </c>
-      <c r="M301" s="1" t="inlineStr">
-        <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
-      <c r="N301" s="1" t="n"/>
-      <c r="O301" s="1" t="n"/>
-      <c r="P301" s="1" t="n"/>
-      <c r="Q301" s="1" t="inlineStr"/>
-      <c r="R301" s="1" t="n"/>
-      <c r="S301" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T301" s="1" t="n"/>
-      <c r="U301" s="1" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U303" headerRowCount="1">
-  <autoFilter ref="A1:U303"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U304" headerRowCount="1">
+  <autoFilter ref="A1:U304"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U303"/>
+  <dimension ref="A1:U304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17138,67 +17138,59 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>80792</v>
+        <v>81074</v>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D205" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
+          <t>Atualização do certificado da empresa 4218 - Arabaiana que esta vencido no meu dinamo</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
-        <v>861</v>
-      </c>
-      <c r="G205" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="inlineStr">
-        <is>
-          <t>Diego Lima</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G205" s="1" t="n"/>
+      <c r="H205" s="1" t="n"/>
       <c r="I205" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>46210.5704596412</v>
+        <v>46218.57761681713</v>
       </c>
       <c r="K205" s="2" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="L205" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="N205" s="1" t="n"/>
       <c r="O205" s="1" t="n"/>
       <c r="P205" s="1" t="n"/>
       <c r="Q205" s="1" t="inlineStr"/>
-      <c r="R205" s="1" t="inlineStr"/>
+      <c r="R205" s="1" t="n"/>
       <c r="S205" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17209,7 +17201,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>80732</v>
+        <v>80792</v>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
@@ -17228,7 +17220,7 @@
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
+          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
@@ -17250,10 +17242,10 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>46206.67579409722</v>
+        <v>46210.5704596412</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="L206" s="1" t="inlineStr">
         <is>
@@ -17280,7 +17272,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>80733</v>
+        <v>80732</v>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
@@ -17299,7 +17291,7 @@
       </c>
       <c r="E207" s="1" t="inlineStr">
         <is>
-          <t>1.01.001.0001.00001 - Caixa</t>
+          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
         </is>
       </c>
       <c r="F207" s="1" t="n">
@@ -17321,7 +17313,7 @@
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>46206.67633518518</v>
+        <v>46206.67579409722</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>46210</v>
@@ -17351,7 +17343,7 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>80734</v>
+        <v>80733</v>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
@@ -17370,7 +17362,7 @@
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
+          <t>1.01.001.0001.00001 - Caixa</t>
         </is>
       </c>
       <c r="F208" s="1" t="n">
@@ -17392,7 +17384,7 @@
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>46206.6769059375</v>
+        <v>46206.67633518518</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>46210</v>
@@ -17422,16 +17414,16 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>80008</v>
+        <v>80734</v>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D209" s="1" t="inlineStr">
@@ -17441,20 +17433,20 @@
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
+          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
         </is>
       </c>
       <c r="F209" s="1" t="n">
-        <v>1065</v>
+        <v>861</v>
       </c>
       <c r="G209" s="1" t="inlineStr">
         <is>
-          <t>MARTINICA COMERCIAL LTDA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H209" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="I209" s="1" t="inlineStr">
@@ -17463,10 +17455,10 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>46188.45542777778</v>
+        <v>46206.6769059375</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
@@ -17475,7 +17467,7 @@
       </c>
       <c r="M209" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="N209" s="1" t="n"/>
@@ -17493,16 +17485,16 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>79890</v>
+        <v>80008</v>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D210" s="1" t="inlineStr">
@@ -17512,20 +17504,20 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
+          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
         </is>
       </c>
       <c r="F210" s="1" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G210" s="1" t="inlineStr">
         <is>
-          <t>Supermercado Kanashiro Ltda</t>
+          <t>MARTINICA COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H210" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="I210" s="1" t="inlineStr">
@@ -17534,32 +17526,26 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46184.46686350695</v>
+        <v>46188.45542777778</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M210" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
-      <c r="N210" s="2" t="n">
-        <v>46185.43777230324</v>
-      </c>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
+      <c r="N210" s="1" t="n"/>
       <c r="O210" s="1" t="n"/>
       <c r="P210" s="1" t="n"/>
       <c r="Q210" s="1" t="inlineStr"/>
-      <c r="R210" s="1" t="inlineStr">
-        <is>
-          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
-        </is>
-      </c>
+      <c r="R210" s="1" t="inlineStr"/>
       <c r="S210" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17570,39 +17556,39 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>78306</v>
+        <v>79890</v>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
-        <v>1286</v>
+        <v>1066</v>
       </c>
       <c r="G211" s="1" t="inlineStr">
         <is>
-          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
+          <t>Supermercado Kanashiro Ltda</t>
         </is>
       </c>
       <c r="H211" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I211" s="1" t="inlineStr">
@@ -17611,26 +17597,32 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>46111.42803700231</v>
+        <v>46184.46686350695</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>46122</v>
+        <v>46188</v>
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
-        </is>
-      </c>
-      <c r="N211" s="1" t="n"/>
+          <t>Karina Santos</t>
+        </is>
+      </c>
+      <c r="N211" s="2" t="n">
+        <v>46185.43777230324</v>
+      </c>
       <c r="O211" s="1" t="n"/>
       <c r="P211" s="1" t="n"/>
       <c r="Q211" s="1" t="inlineStr"/>
-      <c r="R211" s="1" t="inlineStr"/>
+      <c r="R211" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
+        </is>
+      </c>
       <c r="S211" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17641,16 +17633,16 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>79733</v>
+        <v>78306</v>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
@@ -17660,20 +17652,20 @@
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
-        <v>1556</v>
+        <v>1286</v>
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
+          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H212" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I212" s="1" t="inlineStr">
@@ -17682,10 +17674,10 @@
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>46180.49354722222</v>
+        <v>46111.42803700231</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>46182</v>
+        <v>46122</v>
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
@@ -17694,7 +17686,7 @@
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N212" s="1" t="n"/>
@@ -17712,7 +17704,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>79731</v>
+        <v>79733</v>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
@@ -17731,20 +17723,20 @@
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
+          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
         </is>
       </c>
       <c r="F213" s="1" t="n">
-        <v>1931</v>
+        <v>1556</v>
       </c>
       <c r="G213" s="1" t="inlineStr">
         <is>
-          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
+          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
         </is>
       </c>
       <c r="H213" s="1" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I213" s="1" t="inlineStr">
@@ -17753,10 +17745,10 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>46180.44674649306</v>
+        <v>46180.49354722222</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
@@ -17779,24 +17771,20 @@
         </is>
       </c>
       <c r="T213" s="1" t="n"/>
-      <c r="U213" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="U213" s="1" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>78322</v>
+        <v>79731</v>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
@@ -17806,20 +17794,20 @@
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
         </is>
       </c>
       <c r="F214" s="1" t="n">
-        <v>2209</v>
+        <v>1931</v>
       </c>
       <c r="G214" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H214" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="I214" s="1" t="inlineStr">
@@ -17828,10 +17816,10 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>46111.44774475694</v>
+        <v>46180.44674649306</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>46122</v>
+        <v>46185</v>
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
@@ -17840,7 +17828,7 @@
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N214" s="1" t="n"/>
@@ -17854,43 +17842,47 @@
         </is>
       </c>
       <c r="T214" s="1" t="n"/>
-      <c r="U214" s="1" t="inlineStr"/>
+      <c r="U214" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>80013</v>
+        <v>78322</v>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F215" s="1" t="n">
-        <v>2480</v>
+        <v>2209</v>
       </c>
       <c r="G215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H215" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I215" s="1" t="inlineStr">
@@ -17899,10 +17891,10 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>46188.46272334491</v>
+        <v>46111.44774475694</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>46189</v>
+        <v>46122</v>
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
@@ -17911,7 +17903,7 @@
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N215" s="1" t="n"/>
@@ -17929,7 +17921,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>80039</v>
+        <v>80013</v>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
@@ -17948,15 +17940,15 @@
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
+          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
         </is>
       </c>
       <c r="F216" s="1" t="n">
-        <v>2491</v>
+        <v>2480</v>
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
+          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
         </is>
       </c>
       <c r="H216" s="1" t="inlineStr">
@@ -17970,7 +17962,7 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>46188.58172743056</v>
+        <v>46188.46272334491</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>46189</v>
@@ -17982,7 +17974,7 @@
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N216" s="1" t="n"/>
@@ -18000,7 +17992,7 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>80014</v>
+        <v>80039</v>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
@@ -18019,15 +18011,15 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
+          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
         </is>
       </c>
       <c r="F217" s="1" t="n">
-        <v>2500</v>
+        <v>2491</v>
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t>CAEFHOLD Participações S.A.</t>
+          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
@@ -18041,7 +18033,7 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>46188.46337480324</v>
+        <v>46188.58172743056</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>46189</v>
@@ -18053,7 +18045,7 @@
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="N217" s="1" t="n"/>
@@ -18071,39 +18063,39 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>78304</v>
+        <v>80014</v>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
         </is>
       </c>
       <c r="F218" s="1" t="n">
-        <v>2620</v>
+        <v>2500</v>
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t>ANTOCON GALVANOPLASTIA LTDA</t>
+          <t>CAEFHOLD Participações S.A.</t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I218" s="1" t="inlineStr">
@@ -18112,10 +18104,10 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>46111.42458850695</v>
+        <v>46188.46337480324</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>46122</v>
+        <v>46189</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
@@ -18124,7 +18116,7 @@
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N218" s="1" t="n"/>
@@ -18142,39 +18134,39 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>81061</v>
+        <v>78304</v>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza realizar a assinatura do ecf do cliente 2821-Espite</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F219" s="1" t="n">
-        <v>2821</v>
+        <v>2620</v>
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t>ESPITE PARTICIPAÇÕES S.A.</t>
+          <t>ANTOCON GALVANOPLASTIA LTDA</t>
         </is>
       </c>
       <c r="H219" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I219" s="1" t="inlineStr">
@@ -18183,10 +18175,10 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>46218.42798252315</v>
+        <v>46111.42458850695</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>46219</v>
+        <v>46122</v>
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
@@ -18195,7 +18187,7 @@
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N219" s="1" t="n"/>
@@ -18213,39 +18205,39 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>79738</v>
+        <v>81061</v>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DE ANALISE DE MALHA DESDE 25/05/2026 - ANALISE POR E-MAI - SERGIO SUGERIU NA ULTIMA SEMANA QUE PODIAMOS VERIFICAR OS VALORES DE 2022 PARA CREDITO, ANALISEI E VERIFIQUEI QUE A VALOR DE 227.186,29 DE RENDIMENTOS A MAIOR DO QUE ESTA NA DIRF VERIFICAR E LEVANTAR E-MAIL DA EPOCA, NÃO HA PERDCOMP PARA ESTES PERIODOS</t>
+          <t>Bom diaPor gentileza realizar a assinatura do ecf do cliente 2821-Espite</t>
         </is>
       </c>
       <c r="F220" s="1" t="n">
-        <v>2956</v>
+        <v>2821</v>
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
+          <t>ESPITE PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I220" s="1" t="inlineStr">
@@ -18254,10 +18246,10 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>46180.61864918981</v>
+        <v>46218.42798252315</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>46182</v>
+        <v>46219</v>
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
@@ -18266,7 +18258,7 @@
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N220" s="1" t="n"/>
@@ -18284,7 +18276,7 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>79735</v>
+        <v>79738</v>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
@@ -18303,15 +18295,15 @@
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUARDANDO RETORNO DA ANALISE DA MALHA DESDE 26/05/2026 - ENVIADO POR E-MAIL </t>
+          <t>AGUARDANDO RETORNO DE ANALISE DE MALHA DESDE 25/05/2026 - ANALISE POR E-MAI - SERGIO SUGERIU NA ULTIMA SEMANA QUE PODIAMOS VERIFICAR OS VALORES DE 2022 PARA CREDITO, ANALISEI E VERIFIQUEI QUE A VALOR DE 227.186,29 DE RENDIMENTOS A MAIOR DO QUE ESTA NA DIRF VERIFICAR E LEVANTAR E-MAIL DA EPOCA, NÃO HA PERDCOMP PARA ESTES PERIODOS</t>
         </is>
       </c>
       <c r="F221" s="1" t="n">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="G221" s="1" t="inlineStr">
         <is>
-          <t>SAVYS EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H221" s="1" t="inlineStr">
@@ -18325,7 +18317,7 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>46180.50447491898</v>
+        <v>46180.61864918981</v>
       </c>
       <c r="K221" s="2" t="n">
         <v>46182</v>
@@ -18355,39 +18347,39 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>79889</v>
+        <v>79735</v>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Carvalho, o cliente não possui controle, mas retira todo ano.</t>
+          <t xml:space="preserve">AGUARDANDO RETORNO DA ANALISE DA MALHA DESDE 26/05/2026 - ENVIADO POR E-MAIL </t>
         </is>
       </c>
       <c r="F222" s="1" t="n">
-        <v>3195</v>
+        <v>2959</v>
       </c>
       <c r="G222" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO RT CARVALHO LTDA</t>
+          <t>SAVYS EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
         </is>
       </c>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I222" s="1" t="inlineStr">
@@ -18396,10 +18388,10 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>46184.46640107639</v>
+        <v>46180.50447491898</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
@@ -18408,7 +18400,7 @@
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N222" s="1" t="n"/>
@@ -18426,39 +18418,39 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>78313</v>
+        <v>79889</v>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Carvalho, o cliente não possui controle, mas retira todo ano.</t>
         </is>
       </c>
       <c r="F223" s="1" t="n">
-        <v>3262</v>
+        <v>3195</v>
       </c>
       <c r="G223" s="1" t="inlineStr">
         <is>
-          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
+          <t>EMPORIO RT CARVALHO LTDA</t>
         </is>
       </c>
       <c r="H223" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I223" s="1" t="inlineStr">
@@ -18467,10 +18459,10 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>46111.43707260417</v>
+        <v>46184.46640107639</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>46122</v>
+        <v>46188</v>
       </c>
       <c r="L223" s="1" t="inlineStr">
         <is>
@@ -18479,7 +18471,7 @@
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="N223" s="1" t="n"/>
@@ -18497,7 +18489,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>80092</v>
+        <v>78313</v>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
@@ -18506,30 +18498,30 @@
       </c>
       <c r="C224" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D224" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t>Por favor, disponibilizar certificado para envio da ECD 2025 (e-CNPJ ou e-CPF)</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F224" s="1" t="n">
-        <v>3293</v>
+        <v>3262</v>
       </c>
       <c r="G224" s="1" t="inlineStr">
         <is>
-          <t>NELSINHO ASSESSORIA E SERVICOS ADMINISTRATIVOS LTDA</t>
+          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
         </is>
       </c>
       <c r="H224" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I224" s="1" t="inlineStr">
@@ -18538,10 +18530,10 @@
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>46189.5134965625</v>
+        <v>46111.43707260417</v>
       </c>
       <c r="K224" s="2" t="n">
-        <v>46191</v>
+        <v>46122</v>
       </c>
       <c r="L224" s="1" t="inlineStr">
         <is>
@@ -18550,7 +18542,7 @@
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N224" s="1" t="n"/>
@@ -18568,7 +18560,7 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>78309</v>
+        <v>80092</v>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
@@ -18577,30 +18569,30 @@
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por favor, disponibilizar certificado para envio da ECD 2025 (e-CNPJ ou e-CPF)</t>
         </is>
       </c>
       <c r="F225" s="1" t="n">
-        <v>3499</v>
+        <v>3293</v>
       </c>
       <c r="G225" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
+          <t>NELSINHO ASSESSORIA E SERVICOS ADMINISTRATIVOS LTDA</t>
         </is>
       </c>
       <c r="H225" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I225" s="1" t="inlineStr">
@@ -18609,10 +18601,10 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>46111.43159019676</v>
+        <v>46189.5134965625</v>
       </c>
       <c r="K225" s="2" t="n">
-        <v>46122</v>
+        <v>46191</v>
       </c>
       <c r="L225" s="1" t="inlineStr">
         <is>
@@ -18621,7 +18613,7 @@
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N225" s="1" t="n"/>
@@ -18639,7 +18631,7 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>78326</v>
+        <v>78309</v>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
@@ -18662,16 +18654,16 @@
         </is>
       </c>
       <c r="F226" s="1" t="n">
-        <v>3598</v>
+        <v>3499</v>
       </c>
       <c r="G226" s="1" t="inlineStr">
         <is>
-          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
+          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
         </is>
       </c>
       <c r="H226" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I226" s="1" t="inlineStr">
@@ -18680,7 +18672,7 @@
         </is>
       </c>
       <c r="J226" s="2" t="n">
-        <v>46111.45085925926</v>
+        <v>46111.43159019676</v>
       </c>
       <c r="K226" s="2" t="n">
         <v>46122</v>
@@ -18710,7 +18702,7 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>80038</v>
+        <v>78326</v>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
@@ -18719,30 +18711,30 @@
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t>APURAÇÃO IRPJ E CSLL 2025</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F227" s="1" t="n">
-        <v>3661</v>
+        <v>3598</v>
       </c>
       <c r="G227" s="1" t="inlineStr">
         <is>
-          <t>BROGOTÁ INDÚSTRIA GRÁFICA LTDA</t>
+          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H227" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I227" s="1" t="inlineStr">
@@ -18751,10 +18743,10 @@
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>46188.55930297454</v>
+        <v>46111.45085925926</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>46190</v>
+        <v>46122</v>
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
@@ -18763,7 +18755,7 @@
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N227" s="1" t="n"/>
@@ -18781,7 +18773,7 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>78319</v>
+        <v>80038</v>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
@@ -18790,30 +18782,30 @@
       </c>
       <c r="C228" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="D228" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E228" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>APURAÇÃO IRPJ E CSLL 2025</t>
         </is>
       </c>
       <c r="F228" s="1" t="n">
-        <v>3723</v>
+        <v>3661</v>
       </c>
       <c r="G228" s="1" t="inlineStr">
         <is>
-          <t>PLASTIJAPA INDUSTRIA E COMÉRCIO LTDA</t>
+          <t>BROGOTÁ INDÚSTRIA GRÁFICA LTDA</t>
         </is>
       </c>
       <c r="H228" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I228" s="1" t="inlineStr">
@@ -18822,10 +18814,10 @@
         </is>
       </c>
       <c r="J228" s="2" t="n">
-        <v>46111.44368935185</v>
+        <v>46188.55930297454</v>
       </c>
       <c r="K228" s="2" t="n">
-        <v>46122</v>
+        <v>46190</v>
       </c>
       <c r="L228" s="1" t="inlineStr">
         <is>
@@ -18834,7 +18826,7 @@
       </c>
       <c r="M228" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="N228" s="1" t="n"/>
@@ -18852,39 +18844,39 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>80040</v>
+        <v>78319</v>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D229" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E229" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde por gentileza, poderia por gentileza verificar a procuração da loja 3854 pois não conta na SDD e consultecnica.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F229" s="1" t="n">
-        <v>3854</v>
+        <v>3723</v>
       </c>
       <c r="G229" s="1" t="inlineStr">
         <is>
-          <t>Benevento Participações S.A.</t>
+          <t>PLASTIJAPA INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H229" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I229" s="1" t="inlineStr">
@@ -18893,10 +18885,10 @@
         </is>
       </c>
       <c r="J229" s="2" t="n">
-        <v>46188.58404074074</v>
+        <v>46111.44368935185</v>
       </c>
       <c r="K229" s="2" t="n">
-        <v>46189</v>
+        <v>46122</v>
       </c>
       <c r="L229" s="1" t="inlineStr">
         <is>
@@ -18905,7 +18897,7 @@
       </c>
       <c r="M229" s="1" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N229" s="1" t="n"/>
@@ -18923,16 +18915,16 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>80689</v>
+        <v>80040</v>
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
@@ -18942,7 +18934,7 @@
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde Por gentileza verificar o apontamento realizado pelo colaborador do EFI Jonatan para tratar a questão das apurações de IRPJ/CSLL referente a Holding 3854- Benevento , no qual não foi realizado as apurações referente ao 1º e 4º trimestre_2025.Não havíamos recepcionado na contabilidade para contabilização e envio ao EFI•	Em relação ao 1º e ao 4º trimestre, considerando que as guias não foram encaminhadas, quem será o responsável pelo pagamento dos juros e da multa decorrentes do atraso? (não foi encontrado via E-mail a aplicação financeira para nós do fiscal) •	enquanto ao 2º trimestre, considerando que o cliente não efetuou o pagamento da guia, até qual data devo considerar para a emissão do recálculo com os devidos acréscimos legais?</t>
+          <t>Boa tarde por gentileza, poderia por gentileza verificar a procuração da loja 3854 pois não conta na SDD e consultecnica.</t>
         </is>
       </c>
       <c r="F230" s="1" t="n">
@@ -18955,7 +18947,7 @@
       </c>
       <c r="H230" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I230" s="1" t="inlineStr">
@@ -18964,10 +18956,10 @@
         </is>
       </c>
       <c r="J230" s="2" t="n">
-        <v>46204.73023341435</v>
+        <v>46188.58404074074</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>46206</v>
+        <v>46189</v>
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
@@ -18976,7 +18968,7 @@
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="N230" s="1" t="n"/>
@@ -18994,7 +18986,7 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>78308</v>
+        <v>80689</v>
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
@@ -19003,30 +18995,30 @@
       </c>
       <c r="C231" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="D231" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E231" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Boa tarde Por gentileza verificar o apontamento realizado pelo colaborador do EFI Jonatan para tratar a questão das apurações de IRPJ/CSLL referente a Holding 3854- Benevento , no qual não foi realizado as apurações referente ao 1º e 4º trimestre_2025.Não havíamos recepcionado na contabilidade para contabilização e envio ao EFI•	Em relação ao 1º e ao 4º trimestre, considerando que as guias não foram encaminhadas, quem será o responsável pelo pagamento dos juros e da multa decorrentes do atraso? (não foi encontrado via E-mail a aplicação financeira para nós do fiscal) •	enquanto ao 2º trimestre, considerando que o cliente não efetuou o pagamento da guia, até qual data devo considerar para a emissão do recálculo com os devidos acréscimos legais?</t>
         </is>
       </c>
       <c r="F231" s="1" t="n">
-        <v>3954</v>
+        <v>3854</v>
       </c>
       <c r="G231" s="1" t="inlineStr">
         <is>
-          <t>Cristaleria Bruxelas Indústria e Comércio Eireli</t>
+          <t>Benevento Participações S.A.</t>
         </is>
       </c>
       <c r="H231" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I231" s="1" t="inlineStr">
@@ -19035,10 +19027,10 @@
         </is>
       </c>
       <c r="J231" s="2" t="n">
-        <v>46111.43023637732</v>
+        <v>46204.73023341435</v>
       </c>
       <c r="K231" s="2" t="n">
-        <v>46122</v>
+        <v>46206</v>
       </c>
       <c r="L231" s="1" t="inlineStr">
         <is>
@@ -19047,7 +19039,7 @@
       </c>
       <c r="M231" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N231" s="1" t="n"/>
@@ -19065,16 +19057,16 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>79732</v>
+        <v>78308</v>
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D232" s="1" t="inlineStr">
@@ -19084,20 +19076,20 @@
       </c>
       <c r="E232" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DESDE 26/05/2026 - ANALISE SUBIU NO E-MAIL</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F232" s="1" t="n">
-        <v>4034</v>
+        <v>3954</v>
       </c>
       <c r="G232" s="1" t="inlineStr">
         <is>
-          <t>CLV3 EMPREENDIMENTOS E PARTICIPAÇÕES S.A.</t>
+          <t>Cristaleria Bruxelas Indústria e Comércio Eireli</t>
         </is>
       </c>
       <c r="H232" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I232" s="1" t="inlineStr">
@@ -19106,10 +19098,10 @@
         </is>
       </c>
       <c r="J232" s="2" t="n">
-        <v>46180.49062167824</v>
+        <v>46111.43023637732</v>
       </c>
       <c r="K232" s="2" t="n">
-        <v>46182</v>
+        <v>46122</v>
       </c>
       <c r="L232" s="1" t="inlineStr">
         <is>
@@ -19118,7 +19110,7 @@
       </c>
       <c r="M232" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N232" s="1" t="n"/>
@@ -19136,39 +19128,39 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>80007</v>
+        <v>79732</v>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D233" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E233" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza verificar pois o certificado digital venceu4036	Associação Portuguesa de Desportos	61.957.981/0001-54</t>
+          <t>AGUARDANDO RETORNO DESDE 26/05/2026 - ANALISE SUBIU NO E-MAIL</t>
         </is>
       </c>
       <c r="F233" s="1" t="n">
-        <v>4036</v>
+        <v>4034</v>
       </c>
       <c r="G233" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASSOCIAÇÃO PORTUGUESA DE DESPORTOS </t>
+          <t>CLV3 EMPREENDIMENTOS E PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H233" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I233" s="1" t="inlineStr">
@@ -19177,10 +19169,10 @@
         </is>
       </c>
       <c r="J233" s="2" t="n">
-        <v>46188.45496971065</v>
+        <v>46180.49062167824</v>
       </c>
       <c r="K233" s="2" t="n">
-        <v>46189</v>
+        <v>46182</v>
       </c>
       <c r="L233" s="1" t="inlineStr">
         <is>
@@ -19189,7 +19181,7 @@
       </c>
       <c r="M233" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N233" s="1" t="n"/>
@@ -19207,7 +19199,7 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>80018</v>
+        <v>80007</v>
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
@@ -19226,20 +19218,20 @@
       </c>
       <c r="E234" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza disponibilizar o ecpf do socio4115	AR4 TAVARES PARTICIPAÇÕES LTDA	23.114.368/0001-86	REGINALDO TAVARES DE SOUZA</t>
+          <t>Bom diaPor gentileza verificar pois o certificado digital venceu4036	Associação Portuguesa de Desportos	61.957.981/0001-54</t>
         </is>
       </c>
       <c r="F234" s="1" t="n">
-        <v>4115</v>
+        <v>4036</v>
       </c>
       <c r="G234" s="1" t="inlineStr">
         <is>
-          <t>AR4 TAVARES PARTICIPAÇÕES LTDA</t>
+          <t xml:space="preserve">ASSOCIAÇÃO PORTUGUESA DE DESPORTOS </t>
         </is>
       </c>
       <c r="H234" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I234" s="1" t="inlineStr">
@@ -19248,7 +19240,7 @@
         </is>
       </c>
       <c r="J234" s="2" t="n">
-        <v>46188.46483194445</v>
+        <v>46188.45496971065</v>
       </c>
       <c r="K234" s="2" t="n">
         <v>46189</v>
@@ -19278,7 +19270,7 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>80019</v>
+        <v>80018</v>
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
@@ -19297,20 +19289,20 @@
       </c>
       <c r="E235" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu4426	ASSOCIAÇÃO COMERCIAL INDUSTRIAL E SERVIÇOS DE EMBU	49.672.462/0001-44</t>
+          <t>Por gentileza disponibilizar o ecpf do socio4115	AR4 TAVARES PARTICIPAÇÕES LTDA	23.114.368/0001-86	REGINALDO TAVARES DE SOUZA</t>
         </is>
       </c>
       <c r="F235" s="1" t="n">
-        <v>4426</v>
+        <v>4115</v>
       </c>
       <c r="G235" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ASSOCIAÇÃO COMERCIAL INDUSTRIAL E SERVIÇOS DE EMBU </t>
+          <t>AR4 TAVARES PARTICIPAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H235" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="I235" s="1" t="inlineStr">
@@ -19319,7 +19311,7 @@
         </is>
       </c>
       <c r="J235" s="2" t="n">
-        <v>46188.46509869213</v>
+        <v>46188.46483194445</v>
       </c>
       <c r="K235" s="2" t="n">
         <v>46189</v>
@@ -19349,7 +19341,7 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>80020</v>
+        <v>80019</v>
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
@@ -19368,20 +19360,20 @@
       </c>
       <c r="E236" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu4703	MERCADINHO REILAR DE ITAQUA LTDA	10.861.370/0001-77</t>
+          <t>Por gentileza verificar pois o certificado venceu4426	ASSOCIAÇÃO COMERCIAL INDUSTRIAL E SERVIÇOS DE EMBU	49.672.462/0001-44</t>
         </is>
       </c>
       <c r="F236" s="1" t="n">
-        <v>4703</v>
+        <v>4426</v>
       </c>
       <c r="G236" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO REILAR DE ITAQUA LTDA</t>
+          <t xml:space="preserve">ASSOCIAÇÃO COMERCIAL INDUSTRIAL E SERVIÇOS DE EMBU </t>
         </is>
       </c>
       <c r="H236" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="I236" s="1" t="inlineStr">
@@ -19390,7 +19382,7 @@
         </is>
       </c>
       <c r="J236" s="2" t="n">
-        <v>46188.46537982639</v>
+        <v>46188.46509869213</v>
       </c>
       <c r="K236" s="2" t="n">
         <v>46189</v>
@@ -19420,7 +19412,7 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>80021</v>
+        <v>80020</v>
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
@@ -19439,15 +19431,15 @@
       </c>
       <c r="E237" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu4705	MERCADINHO SITIO NOVO DE GUARULHOS LTDA	04.514.934/0001-00</t>
+          <t>Por gentileza verificar pois o certificado venceu4703	MERCADINHO REILAR DE ITAQUA LTDA	10.861.370/0001-77</t>
         </is>
       </c>
       <c r="F237" s="1" t="n">
-        <v>4705</v>
+        <v>4703</v>
       </c>
       <c r="G237" s="1" t="inlineStr">
         <is>
-          <t>MERCADINHO SITIO NOVO DE GUARULHOS LTDA</t>
+          <t>SUPERMERCADO REILAR DE ITAQUA LTDA</t>
         </is>
       </c>
       <c r="H237" s="1" t="inlineStr">
@@ -19461,7 +19453,7 @@
         </is>
       </c>
       <c r="J237" s="2" t="n">
-        <v>46188.46571021991</v>
+        <v>46188.46537982639</v>
       </c>
       <c r="K237" s="2" t="n">
         <v>46189</v>
@@ -19491,7 +19483,7 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>80022</v>
+        <v>80021</v>
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
@@ -19510,15 +19502,15 @@
       </c>
       <c r="E238" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu4706	IRMÃOS J. WILL LTDA	02.187.619/0001-82</t>
+          <t>Por gentileza verificar pois o certificado venceu4705	MERCADINHO SITIO NOVO DE GUARULHOS LTDA	04.514.934/0001-00</t>
         </is>
       </c>
       <c r="F238" s="1" t="n">
-        <v>4706</v>
+        <v>4705</v>
       </c>
       <c r="G238" s="1" t="inlineStr">
         <is>
-          <t>IRMÃOS J. WILL LTDA</t>
+          <t>MERCADINHO SITIO NOVO DE GUARULHOS LTDA</t>
         </is>
       </c>
       <c r="H238" s="1" t="inlineStr">
@@ -19532,7 +19524,7 @@
         </is>
       </c>
       <c r="J238" s="2" t="n">
-        <v>46188.4660287037</v>
+        <v>46188.46571021991</v>
       </c>
       <c r="K238" s="2" t="n">
         <v>46189</v>
@@ -19562,39 +19554,39 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>78320</v>
+        <v>80022</v>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por gentileza verificar pois o certificado venceu4706	IRMÃOS J. WILL LTDA	02.187.619/0001-82</t>
         </is>
       </c>
       <c r="F239" s="1" t="n">
-        <v>5053</v>
+        <v>4706</v>
       </c>
       <c r="G239" s="1" t="inlineStr">
         <is>
-          <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
+          <t>IRMÃOS J. WILL LTDA</t>
         </is>
       </c>
       <c r="H239" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I239" s="1" t="inlineStr">
@@ -19603,10 +19595,10 @@
         </is>
       </c>
       <c r="J239" s="2" t="n">
-        <v>46111.4448534375</v>
+        <v>46188.4660287037</v>
       </c>
       <c r="K239" s="2" t="n">
-        <v>46122</v>
+        <v>46189</v>
       </c>
       <c r="L239" s="1" t="inlineStr">
         <is>
@@ -19615,7 +19607,7 @@
       </c>
       <c r="M239" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N239" s="1" t="n"/>
@@ -19633,16 +19625,16 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>79725</v>
+        <v>78320</v>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D240" s="1" t="inlineStr">
@@ -19652,20 +19644,20 @@
       </c>
       <c r="E240" s="1" t="inlineStr">
         <is>
-          <t>Em anexo, analise de Malha prazo de atendimento a RFB dia 10/06/2026</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F240" s="1" t="n">
-        <v>5178</v>
+        <v>5053</v>
       </c>
       <c r="G240" s="1" t="inlineStr">
         <is>
-          <t>COXA PARTICIPACOES S A</t>
+          <t>RJR INDUSTRIA DE ALIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H240" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I240" s="1" t="inlineStr">
@@ -19674,10 +19666,10 @@
         </is>
       </c>
       <c r="J240" s="2" t="n">
-        <v>46178.66981053241</v>
+        <v>46111.4448534375</v>
       </c>
       <c r="K240" s="2" t="n">
-        <v>46182</v>
+        <v>46122</v>
       </c>
       <c r="L240" s="1" t="inlineStr">
         <is>
@@ -19686,7 +19678,7 @@
       </c>
       <c r="M240" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N240" s="1" t="n"/>
@@ -19704,7 +19696,7 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>79847</v>
+        <v>79725</v>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
@@ -19723,7 +19715,7 @@
       </c>
       <c r="E241" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar e-mail enviado hoje 10/06/2026.Valores devidos de IRPJ e CSLL de 2023., É para fazer a PERDCOMP do Saldo Negativo? É para Gerar os DARFS para Gerencia encaminhar ao cliente? Da parte da Operação aguardamos autorização para envio da ECF e entrega perdcomp</t>
+          <t>Em anexo, analise de Malha prazo de atendimento a RFB dia 10/06/2026</t>
         </is>
       </c>
       <c r="F241" s="1" t="n">
@@ -19745,10 +19737,10 @@
         </is>
       </c>
       <c r="J241" s="2" t="n">
-        <v>46183.54804001158</v>
+        <v>46178.66981053241</v>
       </c>
       <c r="K241" s="2" t="n">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="L241" s="1" t="inlineStr">
         <is>
@@ -19775,16 +19767,16 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>78294</v>
+        <v>79847</v>
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D242" s="1" t="inlineStr">
@@ -19794,20 +19786,20 @@
       </c>
       <c r="E242" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por gentileza verificar e-mail enviado hoje 10/06/2026.Valores devidos de IRPJ e CSLL de 2023., É para fazer a PERDCOMP do Saldo Negativo? É para Gerar os DARFS para Gerencia encaminhar ao cliente? Da parte da Operação aguardamos autorização para envio da ECF e entrega perdcomp</t>
         </is>
       </c>
       <c r="F242" s="1" t="n">
-        <v>5370</v>
+        <v>5178</v>
       </c>
       <c r="G242" s="1" t="inlineStr">
         <is>
-          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
+          <t>COXA PARTICIPACOES S A</t>
         </is>
       </c>
       <c r="H242" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I242" s="1" t="inlineStr">
@@ -19816,10 +19808,10 @@
         </is>
       </c>
       <c r="J242" s="2" t="n">
-        <v>46111.41717407407</v>
+        <v>46183.54804001158</v>
       </c>
       <c r="K242" s="2" t="n">
-        <v>46122</v>
+        <v>46185</v>
       </c>
       <c r="L242" s="1" t="inlineStr">
         <is>
@@ -19828,7 +19820,7 @@
       </c>
       <c r="M242" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N242" s="1" t="n"/>
@@ -19846,7 +19838,7 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>78316</v>
+        <v>78294</v>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
@@ -19869,11 +19861,11 @@
         </is>
       </c>
       <c r="F243" s="1" t="n">
-        <v>5371</v>
+        <v>5370</v>
       </c>
       <c r="G243" s="1" t="inlineStr">
         <is>
-          <t>METALBRAS INDUSTRIA E COMERCIO DE METAIS LTDA</t>
+          <t>ALUFENIX INDUSTRIA E COMERCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="H243" s="1" t="inlineStr">
@@ -19887,7 +19879,7 @@
         </is>
       </c>
       <c r="J243" s="2" t="n">
-        <v>46111.44022480324</v>
+        <v>46111.41717407407</v>
       </c>
       <c r="K243" s="2" t="n">
         <v>46122</v>
@@ -19917,7 +19909,7 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>78314</v>
+        <v>78316</v>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
@@ -19940,16 +19932,16 @@
         </is>
       </c>
       <c r="F244" s="1" t="n">
-        <v>5427</v>
+        <v>5371</v>
       </c>
       <c r="G244" s="1" t="inlineStr">
         <is>
-          <t>LEANDRO SEBASTIAO SIQUEIRA LTDA</t>
+          <t>METALBRAS INDUSTRIA E COMERCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="H244" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I244" s="1" t="inlineStr">
@@ -19958,7 +19950,7 @@
         </is>
       </c>
       <c r="J244" s="2" t="n">
-        <v>46111.43827118055</v>
+        <v>46111.44022480324</v>
       </c>
       <c r="K244" s="2" t="n">
         <v>46122</v>
@@ -19988,7 +19980,7 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>79832</v>
+        <v>78314</v>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
@@ -20002,25 +19994,25 @@
       </c>
       <c r="D245" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E245" s="1" t="inlineStr">
         <is>
-          <t>Favor entrar em contato com o cliente e verificar como vamos fazer com as despesas de IOF que o cliente diz que tem porém não está em nenhum extrato.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F245" s="1" t="n">
-        <v>5528</v>
+        <v>5427</v>
       </c>
       <c r="G245" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA FERRAZ GUERRA LTDA</t>
+          <t>LEANDRO SEBASTIAO SIQUEIRA LTDA</t>
         </is>
       </c>
       <c r="H245" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I245" s="1" t="inlineStr">
@@ -20029,32 +20021,26 @@
         </is>
       </c>
       <c r="J245" s="2" t="n">
-        <v>46183.45493344907</v>
+        <v>46111.43827118055</v>
       </c>
       <c r="K245" s="2" t="n">
-        <v>46183</v>
+        <v>46122</v>
       </c>
       <c r="L245" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M245" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="N245" s="2" t="n">
-        <v>46190.69785497685</v>
-      </c>
+          <t>Taina Silva</t>
+        </is>
+      </c>
+      <c r="N245" s="1" t="n"/>
       <c r="O245" s="1" t="n"/>
       <c r="P245" s="1" t="n"/>
       <c r="Q245" s="1" t="inlineStr"/>
-      <c r="R245" s="1" t="inlineStr">
-        <is>
-          <t>caso enviado ao GM para demais providencias.</t>
-        </is>
-      </c>
+      <c r="R245" s="1" t="inlineStr"/>
       <c r="S245" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -20065,7 +20051,7 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>78305</v>
+        <v>79832</v>
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
@@ -20079,25 +20065,25 @@
       </c>
       <c r="D246" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E246" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Favor entrar em contato com o cliente e verificar como vamos fazer com as despesas de IOF que o cliente diz que tem porém não está em nenhum extrato.</t>
         </is>
       </c>
       <c r="F246" s="1" t="n">
-        <v>5744</v>
+        <v>5528</v>
       </c>
       <c r="G246" s="1" t="inlineStr">
         <is>
-          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
+          <t>DISTRIBUIDORA FERRAZ GUERRA LTDA</t>
         </is>
       </c>
       <c r="H246" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="I246" s="1" t="inlineStr">
@@ -20106,26 +20092,32 @@
         </is>
       </c>
       <c r="J246" s="2" t="n">
-        <v>46111.42608159722</v>
+        <v>46183.45493344907</v>
       </c>
       <c r="K246" s="2" t="n">
-        <v>46122</v>
+        <v>46183</v>
       </c>
       <c r="L246" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M246" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
-        </is>
-      </c>
-      <c r="N246" s="1" t="n"/>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
+      <c r="N246" s="2" t="n">
+        <v>46190.69785497685</v>
+      </c>
       <c r="O246" s="1" t="n"/>
       <c r="P246" s="1" t="n"/>
       <c r="Q246" s="1" t="inlineStr"/>
-      <c r="R246" s="1" t="inlineStr"/>
+      <c r="R246" s="1" t="inlineStr">
+        <is>
+          <t>caso enviado ao GM para demais providencias.</t>
+        </is>
+      </c>
       <c r="S246" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -20136,7 +20128,7 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>78318</v>
+        <v>78305</v>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
@@ -20159,11 +20151,11 @@
         </is>
       </c>
       <c r="F247" s="1" t="n">
-        <v>5801</v>
+        <v>5744</v>
       </c>
       <c r="G247" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
+          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H247" s="1" t="inlineStr">
@@ -20177,7 +20169,7 @@
         </is>
       </c>
       <c r="J247" s="2" t="n">
-        <v>46111.44276319444</v>
+        <v>46111.42608159722</v>
       </c>
       <c r="K247" s="2" t="n">
         <v>46122</v>
@@ -20207,7 +20199,7 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>78311</v>
+        <v>78318</v>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
@@ -20230,11 +20222,11 @@
         </is>
       </c>
       <c r="F248" s="1" t="n">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="G248" s="1" t="inlineStr">
         <is>
-          <t>Ink Flex Industria Grafica LTDA</t>
+          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
         </is>
       </c>
       <c r="H248" s="1" t="inlineStr">
@@ -20248,7 +20240,7 @@
         </is>
       </c>
       <c r="J248" s="2" t="n">
-        <v>46111.43436825232</v>
+        <v>46111.44276319444</v>
       </c>
       <c r="K248" s="2" t="n">
         <v>46122</v>
@@ -20278,7 +20270,7 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>78301</v>
+        <v>78311</v>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
@@ -20301,16 +20293,16 @@
         </is>
       </c>
       <c r="F249" s="1" t="n">
-        <v>6016</v>
+        <v>5803</v>
       </c>
       <c r="G249" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
+          <t>Ink Flex Industria Grafica LTDA</t>
         </is>
       </c>
       <c r="H249" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I249" s="1" t="inlineStr">
@@ -20319,7 +20311,7 @@
         </is>
       </c>
       <c r="J249" s="2" t="n">
-        <v>46111.42218321759</v>
+        <v>46111.43436825232</v>
       </c>
       <c r="K249" s="2" t="n">
         <v>46122</v>
@@ -20349,7 +20341,7 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>79830</v>
+        <v>78301</v>
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
@@ -20363,25 +20355,25 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
         <is>
-          <t>O cliente 6068-R.T. CARVALHO Aluguel de Imóveis enviou os recibos anexos correspondentes a receita com aluguéis durante o exercício 2025.No sistema de análise consta movimentação somente nos meses de outubro e novembro 2025, precisamos de um retorno de como tratar.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F250" s="1" t="n">
-        <v>6068</v>
+        <v>6016</v>
       </c>
       <c r="G250" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.T CARVALHO ALUGUEL DE IMOVEIS PROPRIOS LTDA </t>
+          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
         </is>
       </c>
       <c r="H250" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I250" s="1" t="inlineStr">
@@ -20390,10 +20382,10 @@
         </is>
       </c>
       <c r="J250" s="2" t="n">
-        <v>46183.45075188657</v>
+        <v>46111.42218321759</v>
       </c>
       <c r="K250" s="2" t="n">
-        <v>46184</v>
+        <v>46122</v>
       </c>
       <c r="L250" s="1" t="inlineStr">
         <is>
@@ -20402,7 +20394,7 @@
       </c>
       <c r="M250" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N250" s="1" t="n"/>
@@ -20420,7 +20412,7 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>78321</v>
+        <v>79830</v>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
@@ -20434,25 +20426,25 @@
       </c>
       <c r="D251" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E251" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>O cliente 6068-R.T. CARVALHO Aluguel de Imóveis enviou os recibos anexos correspondentes a receita com aluguéis durante o exercício 2025.No sistema de análise consta movimentação somente nos meses de outubro e novembro 2025, precisamos de um retorno de como tratar.</t>
         </is>
       </c>
       <c r="F251" s="1" t="n">
-        <v>6088</v>
+        <v>6068</v>
       </c>
       <c r="G251" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
+          <t xml:space="preserve">R.T CARVALHO ALUGUEL DE IMOVEIS PROPRIOS LTDA </t>
         </is>
       </c>
       <c r="H251" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I251" s="1" t="inlineStr">
@@ -20461,17 +20453,21 @@
         </is>
       </c>
       <c r="J251" s="2" t="n">
-        <v>46111.44696084491</v>
+        <v>46183.45075188657</v>
       </c>
       <c r="K251" s="2" t="n">
-        <v>46122</v>
+        <v>46184</v>
       </c>
       <c r="L251" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M251" s="1" t="n"/>
+      <c r="M251" s="1" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="N251" s="1" t="n"/>
       <c r="O251" s="1" t="n"/>
       <c r="P251" s="1" t="n"/>
@@ -20487,7 +20483,7 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>78798</v>
+        <v>78321</v>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
@@ -20506,15 +20502,15 @@
       </c>
       <c r="E252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F252" s="1" t="n">
-        <v>6106</v>
+        <v>6088</v>
       </c>
       <c r="G252" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
+          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
         </is>
       </c>
       <c r="H252" s="1" t="inlineStr">
@@ -20528,21 +20524,17 @@
         </is>
       </c>
       <c r="J252" s="2" t="n">
-        <v>46128.70572581018</v>
+        <v>46111.44696084491</v>
       </c>
       <c r="K252" s="2" t="n">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="L252" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M252" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+      <c r="M252" s="1" t="n"/>
       <c r="N252" s="1" t="n"/>
       <c r="O252" s="1" t="n"/>
       <c r="P252" s="1" t="n"/>
@@ -20558,7 +20550,7 @@
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>79837</v>
+        <v>78798</v>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
@@ -20572,25 +20564,25 @@
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
         <is>
-          <t>Segue empresas que não possuem estoque suficiente para bater a lucratividade.6125	Piquini Comercio de Materiais Para Construção LTDA - Matriz 	Casa Glória	02.494.541/0001-49	Bruno	Estoque insuficiente desde 03/2025</t>
+          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
         </is>
       </c>
       <c r="F253" s="1" t="n">
-        <v>6125</v>
+        <v>6106</v>
       </c>
       <c r="G253" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
       <c r="H253" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I253" s="1" t="inlineStr">
@@ -20599,10 +20591,10 @@
         </is>
       </c>
       <c r="J253" s="2" t="n">
-        <v>46183.47519135417</v>
+        <v>46128.70572581018</v>
       </c>
       <c r="K253" s="2" t="n">
-        <v>46184</v>
+        <v>46132</v>
       </c>
       <c r="L253" s="1" t="inlineStr">
         <is>
@@ -20611,7 +20603,7 @@
       </c>
       <c r="M253" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N253" s="1" t="n"/>
@@ -20629,7 +20621,7 @@
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
-        <v>78325</v>
+        <v>79837</v>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
@@ -20643,25 +20635,25 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Segue empresas que não possuem estoque suficiente para bater a lucratividade.6125	Piquini Comercio de Materiais Para Construção LTDA - Matriz 	Casa Glória	02.494.541/0001-49	Bruno	Estoque insuficiente desde 03/2025</t>
         </is>
       </c>
       <c r="F254" s="1" t="n">
-        <v>6148</v>
+        <v>6125</v>
       </c>
       <c r="G254" s="1" t="inlineStr">
         <is>
-          <t>VALE CONCRETO LTDA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H254" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I254" s="1" t="inlineStr">
@@ -20670,10 +20662,10 @@
         </is>
       </c>
       <c r="J254" s="2" t="n">
-        <v>46111.45013549768</v>
+        <v>46183.47519135417</v>
       </c>
       <c r="K254" s="2" t="n">
-        <v>46122</v>
+        <v>46184</v>
       </c>
       <c r="L254" s="1" t="inlineStr">
         <is>
@@ -20682,7 +20674,7 @@
       </c>
       <c r="M254" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N254" s="1" t="n"/>
@@ -20700,7 +20692,7 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>78324</v>
+        <v>78325</v>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
@@ -20723,16 +20715,16 @@
         </is>
       </c>
       <c r="F255" s="1" t="n">
-        <v>6261</v>
+        <v>6148</v>
       </c>
       <c r="G255" s="1" t="inlineStr">
         <is>
-          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
+          <t>VALE CONCRETO LTDA</t>
         </is>
       </c>
       <c r="H255" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I255" s="1" t="inlineStr">
@@ -20741,7 +20733,7 @@
         </is>
       </c>
       <c r="J255" s="2" t="n">
-        <v>46111.44946597222</v>
+        <v>46111.45013549768</v>
       </c>
       <c r="K255" s="2" t="n">
         <v>46122</v>
@@ -20771,7 +20763,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>78317</v>
+        <v>78324</v>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
@@ -20794,16 +20786,16 @@
         </is>
       </c>
       <c r="F256" s="1" t="n">
-        <v>6288</v>
+        <v>6261</v>
       </c>
       <c r="G256" s="1" t="inlineStr">
         <is>
-          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
+          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
         </is>
       </c>
       <c r="H256" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I256" s="1" t="inlineStr">
@@ -20812,7 +20804,7 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>46111.44151450232</v>
+        <v>46111.44946597222</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>46122</v>
@@ -20842,7 +20834,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>78289</v>
+        <v>78317</v>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
@@ -20865,11 +20857,11 @@
         </is>
       </c>
       <c r="F257" s="1" t="n">
-        <v>6289</v>
+        <v>6288</v>
       </c>
       <c r="G257" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
+          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H257" s="1" t="inlineStr">
@@ -20883,7 +20875,7 @@
         </is>
       </c>
       <c r="J257" s="2" t="n">
-        <v>46111.41423260417</v>
+        <v>46111.44151450232</v>
       </c>
       <c r="K257" s="2" t="n">
         <v>46122</v>
@@ -20913,39 +20905,39 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>81011</v>
+        <v>78289</v>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
         <is>
-          <t>NCM - consultar a tributação do NCM 87116000 - enviar para o cliente!</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F258" s="1" t="n">
-        <v>6399</v>
+        <v>6289</v>
       </c>
       <c r="G258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
+          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
         </is>
       </c>
       <c r="H258" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I258" s="1" t="inlineStr">
@@ -20954,10 +20946,10 @@
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>46217.3885827199</v>
+        <v>46111.41423260417</v>
       </c>
       <c r="K258" s="2" t="n">
-        <v>46223</v>
+        <v>46122</v>
       </c>
       <c r="L258" s="1" t="inlineStr">
         <is>
@@ -20966,7 +20958,7 @@
       </c>
       <c r="M258" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N258" s="1" t="n"/>
@@ -20984,39 +20976,39 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>77557</v>
+        <v>81011</v>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
         <is>
-          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
+          <t>NCM - consultar a tributação do NCM 87116000 - enviar para o cliente!</t>
         </is>
       </c>
       <c r="F259" s="1" t="n">
-        <v>6640</v>
+        <v>6399</v>
       </c>
       <c r="G259" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
         </is>
       </c>
       <c r="H259" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="I259" s="1" t="inlineStr">
@@ -21025,10 +21017,10 @@
         </is>
       </c>
       <c r="J259" s="2" t="n">
-        <v>46079.72002283565</v>
+        <v>46217.3885827199</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>46079</v>
+        <v>46223</v>
       </c>
       <c r="L259" s="1" t="inlineStr">
         <is>
@@ -21037,7 +21029,7 @@
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="N259" s="1" t="n"/>
@@ -21055,76 +21047,70 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>80165</v>
+        <v>77557</v>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
         </is>
       </c>
       <c r="F260" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G260" s="1" t="n"/>
+        <v>6640</v>
+      </c>
+      <c r="G260" s="1" t="inlineStr">
+        <is>
+          <t>FORT FRUIT LTDA</t>
+        </is>
+      </c>
       <c r="H260" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I260" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J260" s="2" t="n">
-        <v>46190.71175925926</v>
+        <v>46079.72002283565</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>46191</v>
+        <v>46079</v>
       </c>
       <c r="L260" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M260" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="N260" s="1" t="n"/>
       <c r="O260" s="1" t="n"/>
-      <c r="P260" s="2" t="n">
-        <v>46190.7346272338</v>
-      </c>
-      <c r="Q260" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R260" s="1" t="inlineStr">
-        <is>
-          <t>Tarefas baixadas</t>
-        </is>
-      </c>
+      <c r="P260" s="1" t="n"/>
+      <c r="Q260" s="1" t="inlineStr"/>
+      <c r="R260" s="1" t="inlineStr"/>
       <c r="S260" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T260" s="1" t="n"/>
@@ -21132,7 +21118,7 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>80174</v>
+        <v>80165</v>
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
@@ -21141,7 +21127,7 @@
       </c>
       <c r="C261" s="1" t="inlineStr">
         <is>
-          <t>Vencimento de Tarefas</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D261" s="1" t="inlineStr">
@@ -21151,7 +21137,7 @@
       </c>
       <c r="E261" s="1" t="inlineStr">
         <is>
-          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F261" s="1" t="n">
@@ -21169,10 +21155,10 @@
         </is>
       </c>
       <c r="J261" s="2" t="n">
-        <v>46191.36721832176</v>
+        <v>46190.71175925926</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="L261" s="1" t="inlineStr">
         <is>
@@ -21181,13 +21167,13 @@
       </c>
       <c r="M261" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N261" s="1" t="n"/>
       <c r="O261" s="1" t="n"/>
       <c r="P261" s="2" t="n">
-        <v>46191.49335512731</v>
+        <v>46190.7346272338</v>
       </c>
       <c r="Q261" s="1" t="inlineStr">
         <is>
@@ -21209,7 +21195,7 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>80250</v>
+        <v>80174</v>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
@@ -21218,7 +21204,7 @@
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Vencimento de Tarefas</t>
         </is>
       </c>
       <c r="D262" s="1" t="inlineStr">
@@ -21228,7 +21214,7 @@
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza, baixar as consultas Dec das seguintes empresas;635765986911</t>
+          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
         </is>
       </c>
       <c r="F262" s="1" t="n">
@@ -21246,21 +21232,25 @@
         </is>
       </c>
       <c r="J262" s="2" t="n">
-        <v>46192.6584477662</v>
+        <v>46191.36721832176</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M262" s="1" t="n"/>
+      <c r="M262" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
       <c r="N262" s="1" t="n"/>
       <c r="O262" s="1" t="n"/>
       <c r="P262" s="2" t="n">
-        <v>46192.70597966435</v>
+        <v>46191.49335512731</v>
       </c>
       <c r="Q262" s="1" t="inlineStr">
         <is>
@@ -21282,7 +21272,7 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>80709</v>
+        <v>80250</v>
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
@@ -21301,7 +21291,7 @@
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 1º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>Boa tarde!Por gentileza, baixar as consultas Dec das seguintes empresas;635765986911</t>
         </is>
       </c>
       <c r="F263" s="1" t="n">
@@ -21319,25 +21309,21 @@
         </is>
       </c>
       <c r="J263" s="2" t="n">
-        <v>46205.72485570602</v>
+        <v>46192.6584477662</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M263" s="1" t="inlineStr">
-        <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
+      <c r="M263" s="1" t="n"/>
       <c r="N263" s="1" t="n"/>
       <c r="O263" s="1" t="n"/>
       <c r="P263" s="2" t="n">
-        <v>46205.73248877314</v>
+        <v>46192.70597966435</v>
       </c>
       <c r="Q263" s="1" t="inlineStr">
         <is>
@@ -21359,7 +21345,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>81034</v>
+        <v>80709</v>
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
@@ -21373,12 +21359,12 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tardecolaborador suede informa colocar comentarios nas tarefas, incluindo previsões e o MGC "apaga" ou "some" parecendo que ela não colocou informação.Por gentileza verificar</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 1º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F264" s="1" t="n">
@@ -21396,29 +21382,39 @@
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>46217.58055833333</v>
+        <v>46205.72485570602</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>46218</v>
+        <v>46206</v>
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N264" s="1" t="n"/>
       <c r="O264" s="1" t="n"/>
-      <c r="P264" s="1" t="n"/>
-      <c r="Q264" s="1" t="inlineStr"/>
-      <c r="R264" s="1" t="inlineStr"/>
+      <c r="P264" s="2" t="n">
+        <v>46205.73248877314</v>
+      </c>
+      <c r="Q264" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="R264" s="1" t="inlineStr">
+        <is>
+          <t>Tarefas baixadas</t>
+        </is>
+      </c>
       <c r="S264" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T264" s="1" t="n"/>
@@ -21426,7 +21422,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>81063</v>
+        <v>81034</v>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
@@ -21435,17 +21431,17 @@
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Abertura de protocolo</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t>Precisamos da baixa da tarefa "Fed - DAS" competência 06/2026 das empresas com arquivos disponíveis no diretório abaixo:\\finlandia\PUBLICA\RomeroBorges\DAS - Documentos chamado</t>
+          <t>Prezados, boa tardecolaborador suede informa colocar comentarios nas tarefas, incluindo previsões e o MGC "apaga" ou "some" parecendo que ela não colocou informação.Por gentileza verificar</t>
         </is>
       </c>
       <c r="F265" s="1" t="n">
@@ -21463,10 +21459,10 @@
         </is>
       </c>
       <c r="J265" s="2" t="n">
-        <v>46218.44771315972</v>
+        <v>46217.58055833333</v>
       </c>
       <c r="K265" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="L265" s="1" t="inlineStr">
         <is>
@@ -21475,7 +21471,7 @@
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="N265" s="1" t="n"/>
@@ -21493,26 +21489,26 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>76498</v>
+        <v>81063</v>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Abertura de protocolo</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
+          <t>Precisamos da baixa da tarefa "Fed - DAS" competência 06/2026 das empresas com arquivos disponíveis no diretório abaixo:\\finlandia\PUBLICA\RomeroBorges\DAS - Documentos chamado</t>
         </is>
       </c>
       <c r="F266" s="1" t="n">
@@ -21521,19 +21517,19 @@
       <c r="G266" s="1" t="n"/>
       <c r="H266" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I266" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>46030.50436203703</v>
+        <v>46218.44771315972</v>
       </c>
       <c r="K266" s="2" t="n">
-        <v>46031</v>
+        <v>46219</v>
       </c>
       <c r="L266" s="1" t="inlineStr">
         <is>
@@ -21542,7 +21538,7 @@
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N266" s="1" t="n"/>
@@ -21560,26 +21556,26 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>76514</v>
+        <v>76498</v>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
+          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
         </is>
       </c>
       <c r="F267" s="1" t="n">
@@ -21597,7 +21593,7 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46030.72255292824</v>
+        <v>46030.50436203703</v>
       </c>
       <c r="K267" s="2" t="n">
         <v>46031</v>
@@ -21609,7 +21605,7 @@
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N267" s="1" t="n"/>
@@ -21627,7 +21623,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>76892</v>
+        <v>76514</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
@@ -21641,12 +21637,12 @@
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
+          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
@@ -21664,10 +21660,10 @@
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46051.62030378472</v>
+        <v>46030.72255292824</v>
       </c>
       <c r="K268" s="2" t="n">
-        <v>46052</v>
+        <v>46031</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
@@ -21676,7 +21672,7 @@
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="N268" s="1" t="n"/>
@@ -21694,16 +21690,16 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>77913</v>
+        <v>76892</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
@@ -21713,7 +21709,7 @@
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
@@ -21731,10 +21727,10 @@
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46051.62030378472</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>46097</v>
+        <v>46052</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -21743,7 +21739,7 @@
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
@@ -21761,59 +21757,63 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>79609</v>
+        <v>77913</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G270" s="1" t="n"/>
-      <c r="H270" s="1" t="n"/>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46205</v>
+        <v>46097</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="n"/>
+      <c r="R270" s="1" t="inlineStr"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21824,7 +21824,7 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>80515</v>
+        <v>79609</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
@@ -21843,44 +21843,40 @@
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G271" s="1" t="n"/>
-      <c r="H271" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H271" s="1" t="n"/>
       <c r="I271" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46226</v>
+        <v>46205</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
       <c r="O271" s="1" t="n"/>
       <c r="P271" s="1" t="n"/>
       <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="inlineStr"/>
+      <c r="R271" s="1" t="n"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21891,7 +21887,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>80697</v>
+        <v>80515</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
@@ -21900,7 +21896,7 @@
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
@@ -21910,28 +21906,32 @@
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G272" s="1" t="n"/>
-      <c r="H272" s="1" t="n"/>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I272" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M272" s="1" t="inlineStr">
@@ -21943,7 +21943,7 @@
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="1" t="n"/>
       <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="n"/>
+      <c r="R272" s="1" t="inlineStr"/>
       <c r="S272" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21954,7 +21954,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>80714</v>
+        <v>80697</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -21973,7 +21973,7 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -21987,10 +21987,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -22017,16 +22017,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80919</v>
+        <v>80714</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -22036,7 +22036,7 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22050,10 +22050,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -22080,16 +22080,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>80935</v>
+        <v>80919</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
@@ -22113,10 +22113,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>80936</v>
+        <v>80935</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -22162,7 +22162,7 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
@@ -22176,7 +22176,7 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K276" s="2" t="n">
         <v>46241</v>
@@ -22206,7 +22206,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80951</v>
+        <v>80936</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
@@ -22239,7 +22239,7 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K277" s="2" t="n">
         <v>46241</v>
@@ -22269,63 +22269,59 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80989</v>
+        <v>80951</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G278" s="1" t="n"/>
-      <c r="H278" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="H278" s="1" t="n"/>
       <c r="I278" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46217</v>
+        <v>46241</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N278" s="1" t="n"/>
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="inlineStr"/>
+      <c r="R278" s="1" t="n"/>
       <c r="S278" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22336,11 +22332,11 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>80995</v>
+        <v>80989</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
@@ -22350,45 +22346,49 @@
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G279" s="1" t="n"/>
-      <c r="H279" s="1" t="n"/>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I279" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46217.33131420139</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N279" s="1" t="n"/>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="n"/>
+      <c r="R279" s="1" t="inlineStr"/>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22399,67 +22399,59 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>79793</v>
+        <v>80995</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G280" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
-      <c r="H280" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G280" s="1" t="n"/>
+      <c r="H280" s="1" t="n"/>
       <c r="I280" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46217.33131420139</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46185</v>
+        <v>46219</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N280" s="1" t="n"/>
       <c r="O280" s="1" t="n"/>
       <c r="P280" s="1" t="n"/>
       <c r="Q280" s="1" t="inlineStr"/>
-      <c r="R280" s="1" t="inlineStr"/>
+      <c r="R280" s="1" t="n"/>
       <c r="S280" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22470,59 +22462,67 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>81068</v>
+        <v>79793</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G281" s="1" t="n"/>
-      <c r="H281" s="1" t="n"/>
+        <v>5655</v>
+      </c>
+      <c r="G281" s="1" t="inlineStr">
+        <is>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="H281" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I281" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46218.47815153936</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46220</v>
+        <v>46185</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
       <c r="O281" s="1" t="n"/>
       <c r="P281" s="1" t="n"/>
       <c r="Q281" s="1" t="inlineStr"/>
-      <c r="R281" s="1" t="n"/>
+      <c r="R281" s="1" t="inlineStr"/>
       <c r="S281" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22533,7 +22533,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>81070</v>
+        <v>81068</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
@@ -22552,7 +22552,7 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
@@ -22566,7 +22566,7 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46218.51467572917</v>
+        <v>46218.47815153936</v>
       </c>
       <c r="K282" s="2" t="n">
         <v>46220</v>
@@ -22596,7 +22596,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>81071</v>
+        <v>81070</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
@@ -22615,7 +22615,7 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
@@ -22629,7 +22629,7 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46218.51533788195</v>
+        <v>46218.51467572917</v>
       </c>
       <c r="K283" s="2" t="n">
         <v>46220</v>
@@ -22659,7 +22659,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>81072</v>
+        <v>81071</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
@@ -22678,7 +22678,7 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46218.51577677084</v>
+        <v>46218.51533788195</v>
       </c>
       <c r="K284" s="2" t="n">
         <v>46220</v>
@@ -22722,16 +22722,16 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>81004</v>
+        <v>81072</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
@@ -22741,17 +22741,13 @@
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>6869</v>
-      </c>
-      <c r="G285" s="1" t="inlineStr">
-        <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G285" s="1" t="n"/>
       <c r="H285" s="1" t="n"/>
       <c r="I285" s="1" t="inlineStr">
         <is>
@@ -22759,10 +22755,10 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46218.51577677084</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
@@ -22771,7 +22767,7 @@
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N285" s="1" t="n"/>
@@ -22789,7 +22785,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>81005</v>
+        <v>81004</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
@@ -22812,11 +22808,11 @@
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6870</v>
+        <v>6869</v>
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
       <c r="H286" s="1" t="n"/>
@@ -22826,7 +22822,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K286" s="2" t="n">
         <v>46218</v>
@@ -22856,16 +22852,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>80961</v>
+        <v>81005</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
@@ -22875,15 +22871,15 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6950</v>
+        <v>6870</v>
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>MERCH LTDA (FILIAL 1)</t>
+          <t>AC HOME PET RAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H287" s="1" t="n"/>
@@ -22893,7 +22889,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46216.41692731481</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K287" s="2" t="n">
         <v>46218</v>
@@ -22923,67 +22919,63 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>79856</v>
+        <v>80961</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>4225</v>
+        <v>6950</v>
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
-        </is>
-      </c>
-      <c r="H288" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>MERCH LTDA (FILIAL 1)</t>
+        </is>
+      </c>
+      <c r="H288" s="1" t="n"/>
       <c r="I288" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46216.41692731481</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N288" s="1" t="n"/>
       <c r="O288" s="1" t="n"/>
       <c r="P288" s="1" t="n"/>
       <c r="Q288" s="1" t="inlineStr"/>
-      <c r="R288" s="1" t="inlineStr"/>
+      <c r="R288" s="1" t="n"/>
       <c r="S288" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22994,7 +22986,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79855</v>
+        <v>79856</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
@@ -23013,15 +23005,15 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>4765</v>
+        <v>4225</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
         </is>
       </c>
       <c r="H289" s="1" t="inlineStr">
@@ -23035,10 +23027,10 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
@@ -23065,16 +23057,16 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79833</v>
+        <v>79855</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
@@ -23084,15 +23076,15 @@
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>6125</v>
+        <v>4765</v>
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
         </is>
       </c>
       <c r="H290" s="1" t="inlineStr">
@@ -23106,10 +23098,10 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -23136,7 +23128,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>79834</v>
+        <v>79833</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
@@ -23159,11 +23151,11 @@
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6162</v>
+        <v>6125</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H291" s="1" t="inlineStr">
@@ -23177,7 +23169,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K291" s="2" t="n">
         <v>46184</v>
@@ -23207,16 +23199,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>79865</v>
+        <v>79834</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -23226,15 +23218,15 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6278</v>
+        <v>6162</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H292" s="1" t="inlineStr">
@@ -23248,10 +23240,10 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
@@ -23260,7 +23252,7 @@
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N292" s="1" t="n"/>
@@ -23278,7 +23270,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>79854</v>
+        <v>79865</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
@@ -23297,15 +23289,15 @@
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>6302</v>
+        <v>6278</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H293" s="1" t="inlineStr">
@@ -23319,10 +23311,10 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
@@ -23331,7 +23323,7 @@
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N293" s="1" t="n"/>
@@ -23349,7 +23341,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79863</v>
+        <v>79854</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
@@ -23368,15 +23360,15 @@
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>6404</v>
+        <v>6302</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H294" s="1" t="inlineStr">
@@ -23390,10 +23382,10 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -23402,7 +23394,7 @@
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N294" s="1" t="n"/>
@@ -23420,16 +23412,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79835</v>
+        <v>79863</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
@@ -23439,15 +23431,15 @@
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>6485</v>
+        <v>6404</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H295" s="1" t="inlineStr">
@@ -23461,10 +23453,10 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -23473,7 +23465,7 @@
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N295" s="1" t="n"/>
@@ -23491,16 +23483,16 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79866</v>
+        <v>79835</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D296" s="1" t="inlineStr">
@@ -23510,15 +23502,15 @@
       </c>
       <c r="E296" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23532,10 +23524,10 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
@@ -23544,7 +23536,7 @@
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N296" s="1" t="n"/>
@@ -23562,7 +23554,7 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79859</v>
+        <v>79866</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
@@ -23581,15 +23573,15 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>6570</v>
+        <v>6539</v>
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H297" s="1" t="inlineStr">
@@ -23603,7 +23595,7 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K297" s="2" t="n">
         <v>46185</v>
@@ -23633,7 +23625,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>79860</v>
+        <v>79859</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
@@ -23652,15 +23644,15 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
-        <v>6581</v>
+        <v>6570</v>
       </c>
       <c r="G298" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H298" s="1" t="inlineStr">
@@ -23674,7 +23666,7 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K298" s="2" t="n">
         <v>46185</v>
@@ -23704,7 +23696,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>79861</v>
+        <v>79860</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
@@ -23723,15 +23715,15 @@
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
-        <v>6583</v>
+        <v>6581</v>
       </c>
       <c r="G299" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H299" s="1" t="inlineStr">
@@ -23745,7 +23737,7 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K299" s="2" t="n">
         <v>46185</v>
@@ -23775,16 +23767,16 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>79867</v>
+        <v>79861</v>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
@@ -23794,15 +23786,15 @@
       </c>
       <c r="E300" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F300" s="1" t="n">
-        <v>6704</v>
+        <v>6583</v>
       </c>
       <c r="G300" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H300" s="1" t="inlineStr">
@@ -23816,7 +23808,7 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K300" s="2" t="n">
         <v>46185</v>
@@ -23846,7 +23838,7 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>81019</v>
+        <v>79867</v>
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
@@ -23855,23 +23847,27 @@
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E301" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F301" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G301" s="1" t="n"/>
+        <v>6704</v>
+      </c>
+      <c r="G301" s="1" t="inlineStr">
+        <is>
+          <t>TECNO COM INFORMATICA LTDA</t>
+        </is>
+      </c>
       <c r="H301" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23883,10 +23879,10 @@
         </is>
       </c>
       <c r="J301" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
@@ -23895,7 +23891,7 @@
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N301" s="1" t="n"/>
@@ -23913,7 +23909,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>81052</v>
+        <v>81019</v>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
@@ -23932,7 +23928,7 @@
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F302" s="1" t="n">
@@ -23950,10 +23946,10 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="L302" s="1" t="inlineStr">
         <is>
@@ -23962,7 +23958,7 @@
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N302" s="1" t="n"/>
@@ -23980,7 +23976,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>81055</v>
+        <v>81052</v>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
@@ -23999,7 +23995,7 @@
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
         </is>
       </c>
       <c r="F303" s="1" t="n">
@@ -24017,7 +24013,7 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46218.38736744213</v>
       </c>
       <c r="K303" s="2" t="n">
         <v>46219</v>
@@ -24044,6 +24040,73 @@
       </c>
       <c r="T303" s="1" t="n"/>
       <c r="U303" s="1" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="1" t="n">
+        <v>81055</v>
+      </c>
+      <c r="B304" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C304" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E304" s="1" t="inlineStr">
+        <is>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+        </is>
+      </c>
+      <c r="F304" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G304" s="1" t="n"/>
+      <c r="H304" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I304" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J304" s="2" t="n">
+        <v>46218.40379614583</v>
+      </c>
+      <c r="K304" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L304" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M304" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N304" s="1" t="n"/>
+      <c r="O304" s="1" t="n"/>
+      <c r="P304" s="1" t="n"/>
+      <c r="Q304" s="1" t="inlineStr"/>
+      <c r="R304" s="1" t="inlineStr"/>
+      <c r="S304" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T304" s="1" t="n"/>
+      <c r="U304" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U304" headerRowCount="1">
-  <autoFilter ref="A1:U304"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U308" headerRowCount="1">
+  <autoFilter ref="A1:U308"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U304"/>
+  <dimension ref="A1:U308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21556,63 +21556,59 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>76498</v>
+        <v>81075</v>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Reabertura de tarefa</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
+          <t>Favor reabrir a tarefa E-SOCIAL e FGTS, EMPRESA KAÇULA, AMBOS tiveram alterações devido correção na folha.</t>
         </is>
       </c>
       <c r="F267" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G267" s="1" t="n"/>
-      <c r="H267" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H267" s="1" t="n"/>
       <c r="I267" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46030.50436203703</v>
+        <v>46218.60342256945</v>
       </c>
       <c r="K267" s="2" t="n">
-        <v>46031</v>
+        <v>46219</v>
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Camila Oliveira</t>
         </is>
       </c>
       <c r="N267" s="1" t="n"/>
       <c r="O267" s="1" t="n"/>
       <c r="P267" s="1" t="n"/>
       <c r="Q267" s="1" t="inlineStr"/>
-      <c r="R267" s="1" t="inlineStr"/>
+      <c r="R267" s="1" t="n"/>
       <c r="S267" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21623,63 +21619,59 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>76514</v>
+        <v>81076</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
+          <t>Pessoal, boa tardepor favor baixar a tarefa de REINF da empresa 5835 - CAETE 06/2026esta dando erro de layout pq tivemos que tirar o recibo do ECAC, sci estava com erro.</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G268" s="1" t="n"/>
-      <c r="H268" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H268" s="1" t="n"/>
       <c r="I268" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46030.72255292824</v>
+        <v>46218.61204498843</v>
       </c>
       <c r="K268" s="2" t="n">
-        <v>46031</v>
+        <v>46219</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="N268" s="1" t="n"/>
       <c r="O268" s="1" t="n"/>
       <c r="P268" s="1" t="n"/>
       <c r="Q268" s="1" t="inlineStr"/>
-      <c r="R268" s="1" t="inlineStr"/>
+      <c r="R268" s="1" t="n"/>
       <c r="S268" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21690,63 +21682,59 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>76892</v>
+        <v>81077</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>SANTOS - DP</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
+          <t xml:space="preserve">Boa tarde, pode por favor baixar a tarefa FGTS das empresas 6535 e 6865, uma não possui funcionário e a outra é filial. </t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G269" s="1" t="n"/>
-      <c r="H269" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H269" s="1" t="n"/>
       <c r="I269" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46051.62030378472</v>
+        <v>46218.61339695602</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>46052</v>
+        <v>46219</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Bruna Silva</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
       <c r="O269" s="1" t="n"/>
       <c r="P269" s="1" t="n"/>
       <c r="Q269" s="1" t="inlineStr"/>
-      <c r="R269" s="1" t="inlineStr"/>
+      <c r="R269" s="1" t="n"/>
       <c r="S269" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21757,63 +21745,59 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>77913</v>
+        <v>81078</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>Boa tarde!Favor baixar a tarefa Envio de Impostos DCTF Web com os documentos em anexo das lojas 4833, 5020, 5023 e 5197 enviadas por e-mail ao cliente. Em tentativa de baixar, aparece o erro "Não foi possivel efetuar a leitura do arquivo. O mesmo pode estar criptografado ou corrompido."</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G270" s="1" t="n"/>
-      <c r="H270" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H270" s="1" t="n"/>
       <c r="I270" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46218.62635208333</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46097</v>
+        <v>46219</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Aline Petrini</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="inlineStr"/>
+      <c r="R270" s="1" t="n"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21824,59 +21808,63 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>79609</v>
+        <v>76498</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G271" s="1" t="n"/>
-      <c r="H271" s="1" t="n"/>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I271" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46030.50436203703</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46205</v>
+        <v>46031</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
       <c r="O271" s="1" t="n"/>
       <c r="P271" s="1" t="n"/>
       <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="n"/>
+      <c r="R271" s="1" t="inlineStr"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21887,26 +21875,26 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>80515</v>
+        <v>76514</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
@@ -21924,10 +21912,10 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46030.72255292824</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46226</v>
+        <v>46031</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -21936,7 +21924,7 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
@@ -21954,59 +21942,63 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>80697</v>
+        <v>76892</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G273" s="1" t="n"/>
-      <c r="H273" s="1" t="n"/>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I273" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46051.62030378472</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46237</v>
+        <v>46052</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="1" t="n"/>
       <c r="Q273" s="1" t="inlineStr"/>
-      <c r="R273" s="1" t="n"/>
+      <c r="R273" s="1" t="inlineStr"/>
       <c r="S273" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22017,59 +22009,63 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80714</v>
+        <v>77913</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G274" s="1" t="n"/>
-      <c r="H274" s="1" t="n"/>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I274" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46241</v>
+        <v>46097</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
       <c r="O274" s="1" t="n"/>
       <c r="P274" s="1" t="n"/>
       <c r="Q274" s="1" t="inlineStr"/>
-      <c r="R274" s="1" t="n"/>
+      <c r="R274" s="1" t="inlineStr"/>
       <c r="S274" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22080,16 +22076,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>80919</v>
+        <v>79609</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -22099,7 +22095,7 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
@@ -22113,10 +22109,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46239</v>
+        <v>46205</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22125,7 +22121,7 @@
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N275" s="1" t="n"/>
@@ -22143,7 +22139,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>80935</v>
+        <v>80515</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22152,7 +22148,7 @@
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -22162,28 +22158,32 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G276" s="1" t="n"/>
-      <c r="H276" s="1" t="n"/>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I276" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46241</v>
+        <v>46226</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
@@ -22195,7 +22195,7 @@
       <c r="O276" s="1" t="n"/>
       <c r="P276" s="1" t="n"/>
       <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="n"/>
+      <c r="R276" s="1" t="inlineStr"/>
       <c r="S276" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22206,7 +22206,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80936</v>
+        <v>80697</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22215,7 +22215,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
@@ -22239,10 +22239,10 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80951</v>
+        <v>80714</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
@@ -22278,7 +22278,7 @@
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
@@ -22288,7 +22288,7 @@
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
@@ -22302,7 +22302,7 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K278" s="2" t="n">
         <v>46241</v>
@@ -22332,63 +22332,59 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>80989</v>
+        <v>80919</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G279" s="1" t="n"/>
-      <c r="H279" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="H279" s="1" t="n"/>
       <c r="I279" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46217</v>
+        <v>46239</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N279" s="1" t="n"/>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="inlineStr"/>
+      <c r="R279" s="1" t="n"/>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22399,26 +22395,26 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>80995</v>
+        <v>80935</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
@@ -22432,10 +22428,10 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46217.33131420139</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46219</v>
+        <v>46241</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -22444,7 +22440,7 @@
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N280" s="1" t="n"/>
@@ -22462,67 +22458,59 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>79793</v>
+        <v>80936</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G281" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
-      <c r="H281" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G281" s="1" t="n"/>
+      <c r="H281" s="1" t="n"/>
       <c r="I281" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46185</v>
+        <v>46241</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
       <c r="O281" s="1" t="n"/>
       <c r="P281" s="1" t="n"/>
       <c r="Q281" s="1" t="inlineStr"/>
-      <c r="R281" s="1" t="inlineStr"/>
+      <c r="R281" s="1" t="n"/>
       <c r="S281" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22533,26 +22521,26 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>81068</v>
+        <v>80951</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
@@ -22566,10 +22554,10 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46218.47815153936</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>46220</v>
+        <v>46241</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -22578,7 +22566,7 @@
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N282" s="1" t="n"/>
@@ -22596,11 +22584,11 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>81070</v>
+        <v>80989</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -22615,40 +22603,44 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G283" s="1" t="n"/>
-      <c r="H283" s="1" t="n"/>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46218.51467572917</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="n"/>
+      <c r="R283" s="1" t="inlineStr"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22659,7 +22651,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>81071</v>
+        <v>80995</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
@@ -22673,12 +22665,12 @@
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
+          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
@@ -22692,10 +22684,10 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46218.51533788195</v>
+        <v>46217.33131420139</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
@@ -22704,7 +22696,7 @@
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N284" s="1" t="n"/>
@@ -22722,59 +22714,67 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>81072</v>
+        <v>79793</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" s="1" t="n"/>
-      <c r="H285" s="1" t="n"/>
+        <v>5655</v>
+      </c>
+      <c r="G285" s="1" t="inlineStr">
+        <is>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="H285" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I285" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46218.51577677084</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46220</v>
+        <v>46185</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N285" s="1" t="n"/>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="n"/>
+      <c r="R285" s="1" t="inlineStr"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22785,16 +22785,16 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>81004</v>
+        <v>81068</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
@@ -22804,17 +22804,13 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6869</v>
-      </c>
-      <c r="G286" s="1" t="inlineStr">
-        <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G286" s="1" t="n"/>
       <c r="H286" s="1" t="n"/>
       <c r="I286" s="1" t="inlineStr">
         <is>
@@ -22822,10 +22818,10 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46218.47815153936</v>
       </c>
       <c r="K286" s="2" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
@@ -22834,7 +22830,7 @@
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N286" s="1" t="n"/>
@@ -22852,16 +22848,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>81005</v>
+        <v>81070</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
@@ -22871,17 +22867,13 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6870</v>
-      </c>
-      <c r="G287" s="1" t="inlineStr">
-        <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G287" s="1" t="n"/>
       <c r="H287" s="1" t="n"/>
       <c r="I287" s="1" t="inlineStr">
         <is>
@@ -22889,10 +22881,10 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46218.51467572917</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
@@ -22901,7 +22893,7 @@
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N287" s="1" t="n"/>
@@ -22919,7 +22911,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>80961</v>
+        <v>81071</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
@@ -22938,17 +22930,13 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>6950</v>
-      </c>
-      <c r="G288" s="1" t="inlineStr">
-        <is>
-          <t>MERCH LTDA (FILIAL 1)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G288" s="1" t="n"/>
       <c r="H288" s="1" t="n"/>
       <c r="I288" s="1" t="inlineStr">
         <is>
@@ -22956,10 +22944,10 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46216.41692731481</v>
+        <v>46218.51533788195</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -22968,7 +22956,7 @@
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N288" s="1" t="n"/>
@@ -22986,67 +22974,59 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79856</v>
+        <v>81072</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>4225</v>
-      </c>
-      <c r="G289" s="1" t="inlineStr">
-        <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
-        </is>
-      </c>
-      <c r="H289" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G289" s="1" t="n"/>
+      <c r="H289" s="1" t="n"/>
       <c r="I289" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46218.51577677084</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46184</v>
+        <v>46220</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N289" s="1" t="n"/>
       <c r="O289" s="1" t="n"/>
       <c r="P289" s="1" t="n"/>
       <c r="Q289" s="1" t="inlineStr"/>
-      <c r="R289" s="1" t="inlineStr"/>
+      <c r="R289" s="1" t="n"/>
       <c r="S289" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23057,67 +23037,63 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79855</v>
+        <v>81004</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>4765</v>
+        <v>6869</v>
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
-        </is>
-      </c>
-      <c r="H290" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+        </is>
+      </c>
+      <c r="H290" s="1" t="n"/>
       <c r="I290" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
       <c r="O290" s="1" t="n"/>
       <c r="P290" s="1" t="n"/>
       <c r="Q290" s="1" t="inlineStr"/>
-      <c r="R290" s="1" t="inlineStr"/>
+      <c r="R290" s="1" t="n"/>
       <c r="S290" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23128,67 +23104,63 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>79833</v>
+        <v>81005</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6125</v>
+        <v>6870</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H291" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>AC HOME PET RAÇÕES LTDA</t>
+        </is>
+      </c>
+      <c r="H291" s="1" t="n"/>
       <c r="I291" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N291" s="1" t="n"/>
       <c r="O291" s="1" t="n"/>
       <c r="P291" s="1" t="n"/>
       <c r="Q291" s="1" t="inlineStr"/>
-      <c r="R291" s="1" t="inlineStr"/>
+      <c r="R291" s="1" t="n"/>
       <c r="S291" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23199,67 +23171,63 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>79834</v>
+        <v>80961</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6162</v>
+        <v>6950</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
-        </is>
-      </c>
-      <c r="H292" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>MERCH LTDA (FILIAL 1)</t>
+        </is>
+      </c>
+      <c r="H292" s="1" t="n"/>
       <c r="I292" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46216.41692731481</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N292" s="1" t="n"/>
       <c r="O292" s="1" t="n"/>
       <c r="P292" s="1" t="n"/>
       <c r="Q292" s="1" t="inlineStr"/>
-      <c r="R292" s="1" t="inlineStr"/>
+      <c r="R292" s="1" t="n"/>
       <c r="S292" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23270,7 +23238,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>79865</v>
+        <v>79856</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
@@ -23289,15 +23257,15 @@
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>6278</v>
+        <v>4225</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
         </is>
       </c>
       <c r="H293" s="1" t="inlineStr">
@@ -23311,10 +23279,10 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
@@ -23323,7 +23291,7 @@
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N293" s="1" t="n"/>
@@ -23341,7 +23309,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79854</v>
+        <v>79855</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
@@ -23360,15 +23328,15 @@
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>6302</v>
+        <v>4765</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
         </is>
       </c>
       <c r="H294" s="1" t="inlineStr">
@@ -23382,10 +23350,10 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -23412,16 +23380,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79863</v>
+        <v>79833</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
@@ -23431,15 +23399,15 @@
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>6404</v>
+        <v>6125</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H295" s="1" t="inlineStr">
@@ -23453,10 +23421,10 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -23465,7 +23433,7 @@
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N295" s="1" t="n"/>
@@ -23483,7 +23451,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79835</v>
+        <v>79834</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
@@ -23506,11 +23474,11 @@
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>6485</v>
+        <v>6162</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23524,7 +23492,7 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K296" s="2" t="n">
         <v>46184</v>
@@ -23554,7 +23522,7 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79866</v>
+        <v>79865</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
@@ -23573,15 +23541,15 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>6539</v>
+        <v>6278</v>
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H297" s="1" t="inlineStr">
@@ -23595,7 +23563,7 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K297" s="2" t="n">
         <v>46185</v>
@@ -23625,7 +23593,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>79859</v>
+        <v>79854</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
@@ -23644,15 +23612,15 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
-        <v>6570</v>
+        <v>6302</v>
       </c>
       <c r="G298" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H298" s="1" t="inlineStr">
@@ -23666,10 +23634,10 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -23678,7 +23646,7 @@
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N298" s="1" t="n"/>
@@ -23696,7 +23664,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>79860</v>
+        <v>79863</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
@@ -23715,15 +23683,15 @@
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
-        <v>6581</v>
+        <v>6404</v>
       </c>
       <c r="G299" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H299" s="1" t="inlineStr">
@@ -23737,7 +23705,7 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K299" s="2" t="n">
         <v>46185</v>
@@ -23767,16 +23735,16 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>79861</v>
+        <v>79835</v>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
@@ -23786,15 +23754,15 @@
       </c>
       <c r="E300" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F300" s="1" t="n">
-        <v>6583</v>
+        <v>6485</v>
       </c>
       <c r="G300" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H300" s="1" t="inlineStr">
@@ -23808,10 +23776,10 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
@@ -23820,7 +23788,7 @@
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N300" s="1" t="n"/>
@@ -23838,16 +23806,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>79867</v>
+        <v>79866</v>
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
@@ -23857,15 +23825,15 @@
       </c>
       <c r="E301" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F301" s="1" t="n">
-        <v>6704</v>
+        <v>6539</v>
       </c>
       <c r="G301" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H301" s="1" t="inlineStr">
@@ -23879,7 +23847,7 @@
         </is>
       </c>
       <c r="J301" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K301" s="2" t="n">
         <v>46185</v>
@@ -23909,32 +23877,36 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>81019</v>
+        <v>79859</v>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F302" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" s="1" t="n"/>
+        <v>6570</v>
+      </c>
+      <c r="G302" s="1" t="inlineStr">
+        <is>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+        </is>
+      </c>
       <c r="H302" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23946,10 +23918,10 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K302" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L302" s="1" t="inlineStr">
         <is>
@@ -23958,7 +23930,7 @@
       </c>
       <c r="M302" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N302" s="1" t="n"/>
@@ -23976,32 +23948,36 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>81052</v>
+        <v>79860</v>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F303" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G303" s="1" t="n"/>
+        <v>6581</v>
+      </c>
+      <c r="G303" s="1" t="inlineStr">
+        <is>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+        </is>
+      </c>
       <c r="H303" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24013,10 +23989,10 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K303" s="2" t="n">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="L303" s="1" t="inlineStr">
         <is>
@@ -24025,7 +24001,7 @@
       </c>
       <c r="M303" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N303" s="1" t="n"/>
@@ -24043,32 +24019,36 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>81055</v>
+        <v>79861</v>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C304" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D304" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E304" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F304" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G304" s="1" t="n"/>
+        <v>6583</v>
+      </c>
+      <c r="G304" s="1" t="inlineStr">
+        <is>
+          <t>DROGA MX LTDA (MATRIZ)</t>
+        </is>
+      </c>
       <c r="H304" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24080,10 +24060,10 @@
         </is>
       </c>
       <c r="J304" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K304" s="2" t="n">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="L304" s="1" t="inlineStr">
         <is>
@@ -24092,7 +24072,7 @@
       </c>
       <c r="M304" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N304" s="1" t="n"/>
@@ -24107,6 +24087,278 @@
       </c>
       <c r="T304" s="1" t="n"/>
       <c r="U304" s="1" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="1" t="n">
+        <v>79867</v>
+      </c>
+      <c r="B305" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C305" s="1" t="inlineStr">
+        <is>
+          <t>Implantação Contábil</t>
+        </is>
+      </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL VAREJO</t>
+        </is>
+      </c>
+      <c r="E305" s="1" t="inlineStr">
+        <is>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+        </is>
+      </c>
+      <c r="F305" s="1" t="n">
+        <v>6704</v>
+      </c>
+      <c r="G305" s="1" t="inlineStr">
+        <is>
+          <t>TECNO COM INFORMATICA LTDA</t>
+        </is>
+      </c>
+      <c r="H305" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I305" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J305" s="2" t="n">
+        <v>46183.62582114583</v>
+      </c>
+      <c r="K305" s="2" t="n">
+        <v>46185</v>
+      </c>
+      <c r="L305" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M305" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
+      <c r="N305" s="1" t="n"/>
+      <c r="O305" s="1" t="n"/>
+      <c r="P305" s="1" t="n"/>
+      <c r="Q305" s="1" t="inlineStr"/>
+      <c r="R305" s="1" t="inlineStr"/>
+      <c r="S305" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T305" s="1" t="n"/>
+      <c r="U305" s="1" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="1" t="n">
+        <v>81019</v>
+      </c>
+      <c r="B306" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C306" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E306" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+        </is>
+      </c>
+      <c r="F306" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G306" s="1" t="n"/>
+      <c r="H306" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I306" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J306" s="2" t="n">
+        <v>46217.43210269676</v>
+      </c>
+      <c r="K306" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="L306" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M306" s="1" t="inlineStr">
+        <is>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N306" s="1" t="n"/>
+      <c r="O306" s="1" t="n"/>
+      <c r="P306" s="1" t="n"/>
+      <c r="Q306" s="1" t="inlineStr"/>
+      <c r="R306" s="1" t="inlineStr"/>
+      <c r="S306" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T306" s="1" t="n"/>
+      <c r="U306" s="1" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="1" t="n">
+        <v>81052</v>
+      </c>
+      <c r="B307" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C307" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E307" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+        </is>
+      </c>
+      <c r="F307" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G307" s="1" t="n"/>
+      <c r="H307" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I307" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J307" s="2" t="n">
+        <v>46218.38736744213</v>
+      </c>
+      <c r="K307" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L307" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M307" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N307" s="1" t="n"/>
+      <c r="O307" s="1" t="n"/>
+      <c r="P307" s="1" t="n"/>
+      <c r="Q307" s="1" t="inlineStr"/>
+      <c r="R307" s="1" t="inlineStr"/>
+      <c r="S307" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T307" s="1" t="n"/>
+      <c r="U307" s="1" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="1" t="n">
+        <v>81055</v>
+      </c>
+      <c r="B308" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C308" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E308" s="1" t="inlineStr">
+        <is>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+        </is>
+      </c>
+      <c r="F308" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G308" s="1" t="n"/>
+      <c r="H308" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I308" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J308" s="2" t="n">
+        <v>46218.40379614583</v>
+      </c>
+      <c r="K308" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L308" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M308" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N308" s="1" t="n"/>
+      <c r="O308" s="1" t="n"/>
+      <c r="P308" s="1" t="n"/>
+      <c r="Q308" s="1" t="inlineStr"/>
+      <c r="R308" s="1" t="inlineStr"/>
+      <c r="S308" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T308" s="1" t="n"/>
+      <c r="U308" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U309" headerRowCount="1">
-  <autoFilter ref="A1:U309"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U308" headerRowCount="1">
+  <autoFilter ref="A1:U308"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U309"/>
+  <dimension ref="A1:U308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21629,7 +21629,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>81082</v>
+        <v>81083</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
@@ -21638,53 +21638,67 @@
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>Tarefas baixadas - Ausência de Arquivos</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>Baixar tarefa GFD 3458 funcionarios afastados não tem guia.</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G268" s="1" t="n"/>
-      <c r="H268" s="1" t="n"/>
+      <c r="H268" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I268" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46218.68031246528</v>
+        <v>46218.68119872685</v>
       </c>
       <c r="K268" s="2" t="n">
-        <v>46223</v>
+        <v>46219</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
-          <t>Erica Oliveira</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N268" s="1" t="n"/>
       <c r="O268" s="1" t="n"/>
-      <c r="P268" s="1" t="n"/>
-      <c r="Q268" s="1" t="inlineStr"/>
-      <c r="R268" s="1" t="n"/>
+      <c r="P268" s="2" t="n">
+        <v>46218.7466727662</v>
+      </c>
+      <c r="Q268" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="R268" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarefas já se encontram baixadas </t>
+        </is>
+      </c>
       <c r="S268" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T268" s="1" t="n"/>
@@ -21692,7 +21706,7 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>81083</v>
+        <v>81087</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
@@ -21701,50 +21715,54 @@
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Forçar baixa de tarefas via banco de dados</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>Boa tarde,Por favor baixar a tarefa "retificação FOPAG FOPAG 062026 das empresa 1330 e 2607, está pedindo para anexar arquivo, mas, não tem modelo fixado como exemplo.Obrigado</t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G269" s="1" t="n"/>
-      <c r="H269" s="1" t="n"/>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I269" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46218.68119872685</v>
+        <v>46218.71363287037</v>
       </c>
       <c r="K269" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>David Bragança</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
       <c r="O269" s="1" t="n"/>
       <c r="P269" s="1" t="n"/>
       <c r="Q269" s="1" t="inlineStr"/>
-      <c r="R269" s="1" t="n"/>
+      <c r="R269" s="1" t="inlineStr"/>
       <c r="S269" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21755,7 +21773,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>81085</v>
+        <v>81088</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
@@ -21764,7 +21782,7 @@
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Criação de Relatórios</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
@@ -21774,40 +21792,44 @@
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, baixar a tarefa Envio de ATA de Implantação - DP - SP da empresa 6983, já é cliente da MG não vai ter ata de reunião.</t>
+          <t>Boa tarde!Criar os "problemas", no setor GC - ADMINISTRATIVO - Procurações DPValidar se elas estão orientadas para o uso.</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G270" s="1" t="n"/>
-      <c r="H270" s="1" t="n"/>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46218.69246809028</v>
+        <v>46218.72544799768</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="n"/>
+      <c r="R270" s="1" t="inlineStr"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21818,59 +21840,63 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>81086</v>
+        <v>76498</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Forçar baixa de tarefas via banco de dados</t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza, realizar a baixa da tarefa "GFD - FGTS MENSAL" da empresa 1325. Os colaboradores "ativos" na empresa estão afastados por invalidez ou com reclamatória trabalhista em andamento, sendo assim, não há guia de FGTS para emitir.</t>
+          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G271" s="1" t="n"/>
-      <c r="H271" s="1" t="n"/>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I271" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46218.69883325232</v>
+        <v>46030.50436203703</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46219</v>
+        <v>46031</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Grasiele Santos</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
       <c r="O271" s="1" t="n"/>
       <c r="P271" s="1" t="n"/>
       <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="n"/>
+      <c r="R271" s="1" t="inlineStr"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21881,26 +21907,26 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>76498</v>
+        <v>76514</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
+          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
@@ -21918,7 +21944,7 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46030.50436203703</v>
+        <v>46030.72255292824</v>
       </c>
       <c r="K272" s="2" t="n">
         <v>46031</v>
@@ -21930,7 +21956,7 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
@@ -21948,7 +21974,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>76514</v>
+        <v>76892</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -21962,12 +21988,12 @@
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
+          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -21985,10 +22011,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46030.72255292824</v>
+        <v>46051.62030378472</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46031</v>
+        <v>46052</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -21997,7 +22023,7 @@
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
@@ -22015,16 +22041,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>76892</v>
+        <v>77913</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -22034,7 +22060,7 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22052,10 +22078,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46051.62030378472</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46052</v>
+        <v>46097</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -22064,7 +22090,7 @@
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
@@ -22082,63 +22108,59 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>77913</v>
+        <v>79609</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G275" s="1" t="n"/>
-      <c r="H275" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H275" s="1" t="n"/>
       <c r="I275" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46097</v>
+        <v>46205</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N275" s="1" t="n"/>
       <c r="O275" s="1" t="n"/>
       <c r="P275" s="1" t="n"/>
       <c r="Q275" s="1" t="inlineStr"/>
-      <c r="R275" s="1" t="inlineStr"/>
+      <c r="R275" s="1" t="n"/>
       <c r="S275" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22149,7 +22171,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>79609</v>
+        <v>80515</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22158,7 +22180,7 @@
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -22168,40 +22190,44 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G276" s="1" t="n"/>
-      <c r="H276" s="1" t="n"/>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I276" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46205</v>
+        <v>46226</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N276" s="1" t="n"/>
       <c r="O276" s="1" t="n"/>
       <c r="P276" s="1" t="n"/>
       <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="n"/>
+      <c r="R276" s="1" t="inlineStr"/>
       <c r="S276" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22212,7 +22238,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80515</v>
+        <v>80697</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22221,7 +22247,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -22231,32 +22257,28 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G277" s="1" t="n"/>
-      <c r="H277" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H277" s="1" t="n"/>
       <c r="I277" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
@@ -22268,7 +22290,7 @@
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="inlineStr"/>
+      <c r="R277" s="1" t="n"/>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22279,7 +22301,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80697</v>
+        <v>80714</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
@@ -22288,7 +22310,7 @@
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
@@ -22298,7 +22320,7 @@
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
@@ -22312,10 +22334,10 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
@@ -22342,16 +22364,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>80714</v>
+        <v>80919</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
@@ -22361,7 +22383,7 @@
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
@@ -22375,10 +22397,10 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
@@ -22405,16 +22427,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>80919</v>
+        <v>80935</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -22424,7 +22446,7 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
@@ -22438,10 +22460,10 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -22468,7 +22490,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>80935</v>
+        <v>80936</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
@@ -22477,7 +22499,7 @@
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -22487,7 +22509,7 @@
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
@@ -22501,7 +22523,7 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K281" s="2" t="n">
         <v>46241</v>
@@ -22531,7 +22553,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>80936</v>
+        <v>80951</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
@@ -22540,7 +22562,7 @@
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
@@ -22550,7 +22572,7 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
@@ -22564,7 +22586,7 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K282" s="2" t="n">
         <v>46241</v>
@@ -22594,59 +22616,63 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>80951</v>
+        <v>80989</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G283" s="1" t="n"/>
-      <c r="H283" s="1" t="n"/>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46241</v>
+        <v>46217</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="n"/>
+      <c r="R283" s="1" t="inlineStr"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22657,11 +22683,11 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>80989</v>
+        <v>80995</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -22671,49 +22697,45 @@
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G284" s="1" t="n"/>
-      <c r="H284" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="H284" s="1" t="n"/>
       <c r="I284" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46217.33131420139</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N284" s="1" t="n"/>
       <c r="O284" s="1" t="n"/>
       <c r="P284" s="1" t="n"/>
       <c r="Q284" s="1" t="inlineStr"/>
-      <c r="R284" s="1" t="inlineStr"/>
+      <c r="R284" s="1" t="n"/>
       <c r="S284" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22724,59 +22746,67 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>80995</v>
+        <v>79793</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G285" s="1" t="n"/>
-      <c r="H285" s="1" t="n"/>
+        <v>5655</v>
+      </c>
+      <c r="G285" s="1" t="inlineStr">
+        <is>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="H285" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I285" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46217.33131420139</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N285" s="1" t="n"/>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="n"/>
+      <c r="R285" s="1" t="inlineStr"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22787,67 +22817,59 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>79793</v>
+        <v>81068</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G286" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
-      <c r="H286" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G286" s="1" t="n"/>
+      <c r="H286" s="1" t="n"/>
       <c r="I286" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46218.47815153936</v>
       </c>
       <c r="K286" s="2" t="n">
-        <v>46185</v>
+        <v>46220</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N286" s="1" t="n"/>
       <c r="O286" s="1" t="n"/>
       <c r="P286" s="1" t="n"/>
       <c r="Q286" s="1" t="inlineStr"/>
-      <c r="R286" s="1" t="inlineStr"/>
+      <c r="R286" s="1" t="n"/>
       <c r="S286" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22858,7 +22880,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>81068</v>
+        <v>81070</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
@@ -22877,7 +22899,7 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
@@ -22891,7 +22913,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46218.47815153936</v>
+        <v>46218.51467572917</v>
       </c>
       <c r="K287" s="2" t="n">
         <v>46220</v>
@@ -22921,7 +22943,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>81070</v>
+        <v>81071</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
@@ -22940,7 +22962,7 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
@@ -22954,7 +22976,7 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46218.51467572917</v>
+        <v>46218.51533788195</v>
       </c>
       <c r="K288" s="2" t="n">
         <v>46220</v>
@@ -22984,7 +23006,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>81071</v>
+        <v>81072</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
@@ -23003,7 +23025,7 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
@@ -23017,7 +23039,7 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46218.51533788195</v>
+        <v>46218.51577677084</v>
       </c>
       <c r="K289" s="2" t="n">
         <v>46220</v>
@@ -23047,16 +23069,16 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>81072</v>
+        <v>81004</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
@@ -23066,13 +23088,17 @@
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G290" s="1" t="n"/>
+        <v>6869</v>
+      </c>
+      <c r="G290" s="1" t="inlineStr">
+        <is>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+        </is>
+      </c>
       <c r="H290" s="1" t="n"/>
       <c r="I290" s="1" t="inlineStr">
         <is>
@@ -23080,10 +23106,10 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46218.51577677084</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -23092,7 +23118,7 @@
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
@@ -23110,7 +23136,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>81004</v>
+        <v>81005</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
@@ -23133,11 +23159,11 @@
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6869</v>
+        <v>6870</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+          <t>AC HOME PET RAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H291" s="1" t="n"/>
@@ -23147,7 +23173,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K291" s="2" t="n">
         <v>46218</v>
@@ -23177,16 +23203,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>81005</v>
+        <v>80961</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -23196,15 +23222,15 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6870</v>
+        <v>6950</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
+          <t>MERCH LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H292" s="1" t="n"/>
@@ -23214,7 +23240,7 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46216.41692731481</v>
       </c>
       <c r="K292" s="2" t="n">
         <v>46218</v>
@@ -23244,63 +23270,67 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>80961</v>
+        <v>79856</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>6950</v>
+        <v>4225</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>MERCH LTDA (FILIAL 1)</t>
-        </is>
-      </c>
-      <c r="H293" s="1" t="n"/>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+        </is>
+      </c>
+      <c r="H293" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I293" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46216.41692731481</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>46218</v>
+        <v>46184</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N293" s="1" t="n"/>
       <c r="O293" s="1" t="n"/>
       <c r="P293" s="1" t="n"/>
       <c r="Q293" s="1" t="inlineStr"/>
-      <c r="R293" s="1" t="n"/>
+      <c r="R293" s="1" t="inlineStr"/>
       <c r="S293" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23311,7 +23341,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79856</v>
+        <v>79855</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
@@ -23330,15 +23360,15 @@
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>4225</v>
+        <v>4765</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
         </is>
       </c>
       <c r="H294" s="1" t="inlineStr">
@@ -23352,10 +23382,10 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -23382,16 +23412,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79855</v>
+        <v>79833</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
@@ -23401,15 +23431,15 @@
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>4765</v>
+        <v>6125</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H295" s="1" t="inlineStr">
@@ -23423,10 +23453,10 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -23453,7 +23483,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79833</v>
+        <v>79834</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
@@ -23476,11 +23506,11 @@
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>6125</v>
+        <v>6162</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23494,7 +23524,7 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K296" s="2" t="n">
         <v>46184</v>
@@ -23524,16 +23554,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79834</v>
+        <v>79865</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
@@ -23543,15 +23573,15 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>6162</v>
+        <v>6278</v>
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H297" s="1" t="inlineStr">
@@ -23565,10 +23595,10 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
@@ -23577,7 +23607,7 @@
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N297" s="1" t="n"/>
@@ -23595,7 +23625,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>79865</v>
+        <v>79854</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
@@ -23614,15 +23644,15 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
-        <v>6278</v>
+        <v>6302</v>
       </c>
       <c r="G298" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H298" s="1" t="inlineStr">
@@ -23636,10 +23666,10 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -23648,7 +23678,7 @@
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N298" s="1" t="n"/>
@@ -23666,7 +23696,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>79854</v>
+        <v>79863</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
@@ -23685,15 +23715,15 @@
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
-        <v>6302</v>
+        <v>6404</v>
       </c>
       <c r="G299" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H299" s="1" t="inlineStr">
@@ -23707,10 +23737,10 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K299" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
@@ -23719,7 +23749,7 @@
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N299" s="1" t="n"/>
@@ -23737,16 +23767,16 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>79863</v>
+        <v>79835</v>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
@@ -23756,15 +23786,15 @@
       </c>
       <c r="E300" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F300" s="1" t="n">
-        <v>6404</v>
+        <v>6485</v>
       </c>
       <c r="G300" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H300" s="1" t="inlineStr">
@@ -23778,10 +23808,10 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
@@ -23790,7 +23820,7 @@
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N300" s="1" t="n"/>
@@ -23808,16 +23838,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>79835</v>
+        <v>79866</v>
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
@@ -23827,15 +23857,15 @@
       </c>
       <c r="E301" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F301" s="1" t="n">
-        <v>6485</v>
+        <v>6539</v>
       </c>
       <c r="G301" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H301" s="1" t="inlineStr">
@@ -23849,10 +23879,10 @@
         </is>
       </c>
       <c r="J301" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
@@ -23861,7 +23891,7 @@
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N301" s="1" t="n"/>
@@ -23879,7 +23909,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>79866</v>
+        <v>79859</v>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
@@ -23898,15 +23928,15 @@
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F302" s="1" t="n">
-        <v>6539</v>
+        <v>6570</v>
       </c>
       <c r="G302" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H302" s="1" t="inlineStr">
@@ -23920,7 +23950,7 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K302" s="2" t="n">
         <v>46185</v>
@@ -23950,7 +23980,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>79859</v>
+        <v>79860</v>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
@@ -23969,15 +23999,15 @@
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F303" s="1" t="n">
-        <v>6570</v>
+        <v>6581</v>
       </c>
       <c r="G303" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H303" s="1" t="inlineStr">
@@ -23991,7 +24021,7 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K303" s="2" t="n">
         <v>46185</v>
@@ -24021,7 +24051,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>79860</v>
+        <v>79861</v>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
@@ -24040,15 +24070,15 @@
       </c>
       <c r="E304" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F304" s="1" t="n">
-        <v>6581</v>
+        <v>6583</v>
       </c>
       <c r="G304" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H304" s="1" t="inlineStr">
@@ -24062,7 +24092,7 @@
         </is>
       </c>
       <c r="J304" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K304" s="2" t="n">
         <v>46185</v>
@@ -24092,16 +24122,16 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>79861</v>
+        <v>79867</v>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
@@ -24111,15 +24141,15 @@
       </c>
       <c r="E305" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F305" s="1" t="n">
-        <v>6583</v>
+        <v>6704</v>
       </c>
       <c r="G305" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H305" s="1" t="inlineStr">
@@ -24133,7 +24163,7 @@
         </is>
       </c>
       <c r="J305" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K305" s="2" t="n">
         <v>46185</v>
@@ -24163,7 +24193,7 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>79867</v>
+        <v>81019</v>
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
@@ -24172,27 +24202,23 @@
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F306" s="1" t="n">
-        <v>6704</v>
-      </c>
-      <c r="G306" s="1" t="inlineStr">
-        <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G306" s="1" t="n"/>
       <c r="H306" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24204,10 +24230,10 @@
         </is>
       </c>
       <c r="J306" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
@@ -24216,7 +24242,7 @@
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N306" s="1" t="n"/>
@@ -24234,7 +24260,7 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>81019</v>
+        <v>81052</v>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
@@ -24253,7 +24279,7 @@
       </c>
       <c r="E307" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
         </is>
       </c>
       <c r="F307" s="1" t="n">
@@ -24271,10 +24297,10 @@
         </is>
       </c>
       <c r="J307" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46218.38736744213</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="L307" s="1" t="inlineStr">
         <is>
@@ -24283,7 +24309,7 @@
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="N307" s="1" t="n"/>
@@ -24301,7 +24327,7 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>81052</v>
+        <v>81055</v>
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
@@ -24320,7 +24346,7 @@
       </c>
       <c r="E308" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
         </is>
       </c>
       <c r="F308" s="1" t="n">
@@ -24338,7 +24364,7 @@
         </is>
       </c>
       <c r="J308" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46218.40379614583</v>
       </c>
       <c r="K308" s="2" t="n">
         <v>46219</v>
@@ -24365,73 +24391,6 @@
       </c>
       <c r="T308" s="1" t="n"/>
       <c r="U308" s="1" t="inlineStr"/>
-    </row>
-    <row r="309">
-      <c r="A309" s="1" t="n">
-        <v>81055</v>
-      </c>
-      <c r="B309" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C309" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D309" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E309" s="1" t="inlineStr">
-        <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
-        </is>
-      </c>
-      <c r="F309" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G309" s="1" t="n"/>
-      <c r="H309" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I309" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J309" s="2" t="n">
-        <v>46218.40379614583</v>
-      </c>
-      <c r="K309" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L309" s="1" t="inlineStr">
-        <is>
-          <t>Esperando Atendimento</t>
-        </is>
-      </c>
-      <c r="M309" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N309" s="1" t="n"/>
-      <c r="O309" s="1" t="n"/>
-      <c r="P309" s="1" t="n"/>
-      <c r="Q309" s="1" t="inlineStr"/>
-      <c r="R309" s="1" t="inlineStr"/>
-      <c r="S309" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T309" s="1" t="n"/>
-      <c r="U309" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U308" headerRowCount="1">
-  <autoFilter ref="A1:U308"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U311" headerRowCount="1">
+  <autoFilter ref="A1:U311"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U308"/>
+  <dimension ref="A1:U311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1178,7 +1178,11 @@
         <v>0</v>
       </c>
       <c r="G9" s="1" t="n"/>
-      <c r="H9" s="1" t="n"/>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>Ana Flavia Silva</t>
+        </is>
+      </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL HOLDING</t>
@@ -1192,7 +1196,7 @@
       </c>
       <c r="L9" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M9" s="1" t="inlineStr">
@@ -1201,17 +1205,23 @@
         </is>
       </c>
       <c r="N9" s="1" t="n"/>
-      <c r="O9" s="1" t="n"/>
+      <c r="O9" s="2" t="n">
+        <v>46219</v>
+      </c>
       <c r="P9" s="1" t="n"/>
       <c r="Q9" s="1" t="inlineStr"/>
-      <c r="R9" s="1" t="n"/>
+      <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T9" s="1" t="n"/>
-      <c r="U9" s="1" t="inlineStr"/>
+      <c r="U9" s="1" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -21495,7 +21505,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>81034</v>
+        <v>81001</v>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
@@ -21509,12 +21519,12 @@
       </c>
       <c r="D266" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tardecolaborador suede informa colocar comentarios nas tarefas, incluindo previsões e o MGC "apaga" ou "some" parecendo que ela não colocou informação.Por gentileza verificar</t>
+          <t>POR GENTILEZA PODEM BAIXAR A TAREFA "Recebimento de NF ICMS Centr. e Lançamento - 6/2026" DA LOJA 6001 DO MÊS DE JUNHO.</t>
         </is>
       </c>
       <c r="F266" s="1" t="n">
@@ -21532,26 +21542,30 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>46217.58055833333</v>
+        <v>46217.36753545139</v>
       </c>
       <c r="K266" s="2" t="n">
         <v>46218</v>
       </c>
       <c r="L266" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M266" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="N266" s="1" t="n"/>
       <c r="O266" s="1" t="n"/>
       <c r="P266" s="1" t="n"/>
       <c r="Q266" s="1" t="inlineStr"/>
-      <c r="R266" s="1" t="inlineStr"/>
+      <c r="R266" s="1" t="inlineStr">
+        <is>
+          <t>Tarefa baixada</t>
+        </is>
+      </c>
       <c r="S266" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21562,7 +21576,7 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>81063</v>
+        <v>81034</v>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
@@ -21571,17 +21585,17 @@
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>Abertura de protocolo</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t>Precisamos da baixa da tarefa "Fed - DAS" competência 06/2026 das empresas com arquivos disponíveis no diretório abaixo:\\finlandia\PUBLICA\RomeroBorges\DAS - Documentos chamado</t>
+          <t>Prezados, boa tardecolaborador suede informa colocar comentarios nas tarefas, incluindo previsões e o MGC "apaga" ou "some" parecendo que ela não colocou informação.Por gentileza verificar</t>
         </is>
       </c>
       <c r="F267" s="1" t="n">
@@ -21599,10 +21613,10 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46218.44771315972</v>
+        <v>46217.58055833333</v>
       </c>
       <c r="K267" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
@@ -21611,7 +21625,7 @@
       </c>
       <c r="M267" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="N267" s="1" t="n"/>
@@ -21629,7 +21643,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>81083</v>
+        <v>81063</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
@@ -21638,17 +21652,17 @@
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Abertura de protocolo</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>Precisamos da baixa da tarefa "Fed - DAS" competência 06/2026 das empresas com arquivos disponíveis no diretório abaixo:\\finlandia\PUBLICA\RomeroBorges\DAS - Documentos chamado</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
@@ -21666,39 +21680,29 @@
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46218.68119872685</v>
+        <v>46218.44771315972</v>
       </c>
       <c r="K268" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N268" s="1" t="n"/>
       <c r="O268" s="1" t="n"/>
-      <c r="P268" s="2" t="n">
-        <v>46218.7466727662</v>
-      </c>
-      <c r="Q268" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tarefas já se encontram baixadas </t>
-        </is>
-      </c>
+      <c r="P268" s="1" t="n"/>
+      <c r="Q268" s="1" t="inlineStr"/>
+      <c r="R268" s="1" t="inlineStr"/>
       <c r="S268" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T268" s="1" t="n"/>
@@ -21706,7 +21710,7 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>81087</v>
+        <v>81083</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
@@ -21715,17 +21719,17 @@
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Forçar baixa de tarefas via banco de dados</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Por favor baixar a tarefa "retificação FOPAG FOPAG 062026 das empresa 1330 e 2607, está pedindo para anexar arquivo, mas, não tem modelo fixado como exemplo.Obrigado</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
@@ -21743,29 +21747,39 @@
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46218.71363287037</v>
+        <v>46218.68119872685</v>
       </c>
       <c r="K269" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>David Bragança</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
       <c r="O269" s="1" t="n"/>
-      <c r="P269" s="1" t="n"/>
-      <c r="Q269" s="1" t="inlineStr"/>
-      <c r="R269" s="1" t="inlineStr"/>
+      <c r="P269" s="2" t="n">
+        <v>46218.7466727662</v>
+      </c>
+      <c r="Q269" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="R269" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarefas já se encontram baixadas </t>
+        </is>
+      </c>
       <c r="S269" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T269" s="1" t="n"/>
@@ -21840,26 +21854,26 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>76498</v>
+        <v>81090</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Endereço</t>
+          <t>Chamados</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>B.P.O. - GUARANI CTB</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
+          <t>por gentileza poderia baixar a reeinf da empresas 4059 e a tarefas da caixa postal das empresas 4059, 4064, 4065 ,4066, 4067, 4068, 4602, 4815, 4917 em Anexo</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
@@ -21868,19 +21882,19 @@
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46030.50436203703</v>
+        <v>46218.76292554398</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46031</v>
+        <v>46220</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -21889,7 +21903,7 @@
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Alaine Neres</t>
+          <t>Flavia Dariolli</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
@@ -21907,63 +21921,59 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>76514</v>
+        <v>81092</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
+          <t>POR GENTILEZA BAIXAR A TAREFA "CONTA DE ENERGIA" DO MÊS 06/2026 DA EMPRESA 4922 - SUPERMERCADOS CAPPI DUARTE LTDA</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G272" s="1" t="n"/>
-      <c r="H272" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H272" s="1" t="n"/>
       <c r="I272" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46030.72255292824</v>
+        <v>46219.37092832176</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46031</v>
+        <v>46220</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Glaucia Santos</t>
+          <t>Diego Pereira</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="1" t="n"/>
       <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="inlineStr"/>
+      <c r="R272" s="1" t="n"/>
       <c r="S272" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21974,16 +21984,16 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>76892</v>
+        <v>76498</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Endereço</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -21993,7 +22003,7 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
+          <t>2279 - FRUTILAR: de São Paulo para Taboão da Serra, ela mudou de endereço, de São Paulo para Taboão da Serra.E tem notas de serviços prestados para a prefeitura de São Paulo, quando vou converter a nota no site, não deixar por conta do cadastro, consta que não precisar emitir a nota, por ser do mesmo município.</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -22011,10 +22021,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46051.62030378472</v>
+        <v>46030.50436203703</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46052</v>
+        <v>46031</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -22023,7 +22033,7 @@
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Alaine Neres</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
@@ -22041,26 +22051,26 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>77913</v>
+        <v>76514</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>Boa tarde !A empresa 6603 esta cadastrada no SCI (BASE VAREJO) com um CNPJ divergente do cadastrado no MG controle.Segue em anexo os cartões CNPJ, para conferencia.</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22078,10 +22088,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46030.72255292824</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46097</v>
+        <v>46031</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -22090,7 +22100,7 @@
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
@@ -22108,59 +22118,63 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>79609</v>
+        <v>76892</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Boa tarde,Identificamos que a loja 5225 – CUCINARE PRO (Filial 71) está com o CNPJ incorreto cadastrado no MG Controle, na aba Clientes.Solicitamos, por gentileza, a correção do CNPJ no sistema.Ficamos no aguardo da confirmação após o ajuste. OBS: ramal para contato: 1341 - Igor bastos</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G275" s="1" t="n"/>
-      <c r="H275" s="1" t="n"/>
+      <c r="H275" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I275" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46051.62030378472</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46205</v>
+        <v>46052</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N275" s="1" t="n"/>
       <c r="O275" s="1" t="n"/>
       <c r="P275" s="1" t="n"/>
       <c r="Q275" s="1" t="inlineStr"/>
-      <c r="R275" s="1" t="n"/>
+      <c r="R275" s="1" t="inlineStr"/>
       <c r="S275" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22171,26 +22185,26 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>80515</v>
+        <v>77913</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
@@ -22208,10 +22222,10 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46226</v>
+        <v>46097</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
@@ -22220,7 +22234,7 @@
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="N276" s="1" t="n"/>
@@ -22238,7 +22252,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80697</v>
+        <v>79609</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22247,7 +22261,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -22257,7 +22271,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
@@ -22271,10 +22285,10 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46237</v>
+        <v>46205</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
@@ -22283,7 +22297,7 @@
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N277" s="1" t="n"/>
@@ -22301,7 +22315,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80714</v>
+        <v>80515</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
@@ -22310,7 +22324,7 @@
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
@@ -22320,28 +22334,32 @@
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G278" s="1" t="n"/>
-      <c r="H278" s="1" t="n"/>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I278" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46241</v>
+        <v>46226</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M278" s="1" t="inlineStr">
@@ -22353,7 +22371,7 @@
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="n"/>
+      <c r="R278" s="1" t="inlineStr"/>
       <c r="S278" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22364,16 +22382,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>80919</v>
+        <v>80697</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
@@ -22383,7 +22401,7 @@
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
@@ -22397,10 +22415,10 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
@@ -22427,7 +22445,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>80935</v>
+        <v>80714</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
@@ -22436,7 +22454,7 @@
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -22446,7 +22464,7 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
@@ -22460,7 +22478,7 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K280" s="2" t="n">
         <v>46241</v>
@@ -22490,16 +22508,16 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>80936</v>
+        <v>80919</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -22509,7 +22527,7 @@
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
@@ -22523,10 +22541,10 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -22553,7 +22571,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>80951</v>
+        <v>80935</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
@@ -22572,7 +22590,7 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
@@ -22586,7 +22604,7 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K282" s="2" t="n">
         <v>46241</v>
@@ -22616,63 +22634,59 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>80989</v>
+        <v>80936</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G283" s="1" t="n"/>
-      <c r="H283" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+      <c r="H283" s="1" t="n"/>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46217</v>
+        <v>46241</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="inlineStr"/>
+      <c r="R283" s="1" t="n"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22683,26 +22697,26 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>80995</v>
+        <v>80951</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
@@ -22716,10 +22730,10 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46217.33131420139</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46219</v>
+        <v>46241</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
@@ -22728,7 +22742,7 @@
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
-          <t>Jonatan Hayashibara</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N284" s="1" t="n"/>
@@ -22746,67 +22760,59 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>79793</v>
+        <v>81068</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G285" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
-      <c r="H285" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G285" s="1" t="n"/>
+      <c r="H285" s="1" t="n"/>
       <c r="I285" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46218.47815153936</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46185</v>
+        <v>46220</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Regiane Santos</t>
         </is>
       </c>
       <c r="N285" s="1" t="n"/>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="inlineStr"/>
+      <c r="R285" s="1" t="n"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22817,7 +22823,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>81068</v>
+        <v>81070</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
@@ -22836,7 +22842,7 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ3252 Comercio de Alimentos Alves e Farias FILIAL 013257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
@@ -22850,7 +22856,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46218.47815153936</v>
+        <v>46218.51467572917</v>
       </c>
       <c r="K286" s="2" t="n">
         <v>46220</v>
@@ -22880,7 +22886,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>81070</v>
+        <v>81071</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
@@ -22899,7 +22905,7 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
@@ -22913,7 +22919,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46218.51467572917</v>
+        <v>46218.51533788195</v>
       </c>
       <c r="K287" s="2" t="n">
         <v>46220</v>
@@ -22943,7 +22949,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>81071</v>
+        <v>81072</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
@@ -22962,7 +22968,7 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
+          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
@@ -22976,7 +22982,7 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46218.51533788195</v>
+        <v>46218.51577677084</v>
       </c>
       <c r="K288" s="2" t="n">
         <v>46220</v>
@@ -23006,11 +23012,11 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>81072</v>
+        <v>80989</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -23025,40 +23031,44 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G289" s="1" t="n"/>
-      <c r="H289" s="1" t="n"/>
+      <c r="H289" s="1" t="inlineStr">
+        <is>
+          <t>Ellen Leite</t>
+        </is>
+      </c>
       <c r="I289" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46218.51577677084</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N289" s="1" t="n"/>
       <c r="O289" s="1" t="n"/>
       <c r="P289" s="1" t="n"/>
       <c r="Q289" s="1" t="inlineStr"/>
-      <c r="R289" s="1" t="n"/>
+      <c r="R289" s="1" t="inlineStr"/>
       <c r="S289" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23069,36 +23079,32 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>81004</v>
+        <v>80995</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Bom dia!Solicito acesso a prefeitura de Holambra na qual efetuou uma atualização.Já foi testado o Login e senha com o que está no Intranet quanto também apenas com a inscrição municipalNovo Emissor: https://holambra.citynex.com.br/ords/holambra/f?p=778:70:Antigo: http://179.175.14.22:8080/issweb/paginas/admin/declaracoes/tomador/declaracoesempresas em questão em anexo:com prioridade a B3R</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>6869</v>
-      </c>
-      <c r="G290" s="1" t="inlineStr">
-        <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G290" s="1" t="n"/>
       <c r="H290" s="1" t="n"/>
       <c r="I290" s="1" t="inlineStr">
         <is>
@@ -23106,10 +23112,10 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46217.33131420139</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -23118,7 +23124,7 @@
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Jonatan Hayashibara</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
@@ -23136,63 +23142,67 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>81005</v>
+        <v>79793</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6870</v>
+        <v>5655</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
-        </is>
-      </c>
-      <c r="H291" s="1" t="n"/>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="H291" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I291" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N291" s="1" t="n"/>
       <c r="O291" s="1" t="n"/>
       <c r="P291" s="1" t="n"/>
       <c r="Q291" s="1" t="inlineStr"/>
-      <c r="R291" s="1" t="n"/>
+      <c r="R291" s="1" t="inlineStr"/>
       <c r="S291" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23203,16 +23213,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>80961</v>
+        <v>81004</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -23222,15 +23232,15 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6950</v>
+        <v>6869</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>MERCH LTDA (FILIAL 1)</t>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
       <c r="H292" s="1" t="n"/>
@@ -23240,7 +23250,7 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46216.41692731481</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K292" s="2" t="n">
         <v>46218</v>
@@ -23270,67 +23280,63 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>79856</v>
+        <v>81005</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>4225</v>
+        <v>6870</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
-        </is>
-      </c>
-      <c r="H293" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>AC HOME PET RAÇÕES LTDA</t>
+        </is>
+      </c>
+      <c r="H293" s="1" t="n"/>
       <c r="I293" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N293" s="1" t="n"/>
       <c r="O293" s="1" t="n"/>
       <c r="P293" s="1" t="n"/>
       <c r="Q293" s="1" t="inlineStr"/>
-      <c r="R293" s="1" t="inlineStr"/>
+      <c r="R293" s="1" t="n"/>
       <c r="S293" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23341,67 +23347,63 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79855</v>
+        <v>81091</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>4765</v>
+        <v>6907</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
-        </is>
-      </c>
-      <c r="H294" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+        </is>
+      </c>
+      <c r="H294" s="1" t="n"/>
       <c r="I294" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46219.3374690162</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>46185</v>
+        <v>46223</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N294" s="1" t="n"/>
       <c r="O294" s="1" t="n"/>
       <c r="P294" s="1" t="n"/>
       <c r="Q294" s="1" t="inlineStr"/>
-      <c r="R294" s="1" t="inlineStr"/>
+      <c r="R294" s="1" t="n"/>
       <c r="S294" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23412,67 +23414,63 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79833</v>
+        <v>80961</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Bom dia! Por gentileza, solicitado o login e senha da prefeitura da empresa 6950.</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>6125</v>
+        <v>6950</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H295" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t>MERCH LTDA (FILIAL 1)</t>
+        </is>
+      </c>
+      <c r="H295" s="1" t="n"/>
       <c r="I295" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46216.41692731481</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N295" s="1" t="n"/>
       <c r="O295" s="1" t="n"/>
       <c r="P295" s="1" t="n"/>
       <c r="Q295" s="1" t="inlineStr"/>
-      <c r="R295" s="1" t="inlineStr"/>
+      <c r="R295" s="1" t="n"/>
       <c r="S295" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23483,7 +23481,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79834</v>
+        <v>79833</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
@@ -23506,11 +23504,11 @@
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>6162</v>
+        <v>6125</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23524,7 +23522,7 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K296" s="2" t="n">
         <v>46184</v>
@@ -23554,16 +23552,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79865</v>
+        <v>79834</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
@@ -23573,15 +23571,15 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>6278</v>
+        <v>6162</v>
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H297" s="1" t="inlineStr">
@@ -23595,10 +23593,10 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
@@ -23607,7 +23605,7 @@
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N297" s="1" t="n"/>
@@ -23625,7 +23623,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>79854</v>
+        <v>79865</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
@@ -23644,15 +23642,15 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
-        <v>6302</v>
+        <v>6278</v>
       </c>
       <c r="G298" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H298" s="1" t="inlineStr">
@@ -23666,10 +23664,10 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -23678,7 +23676,7 @@
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N298" s="1" t="n"/>
@@ -23696,7 +23694,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>79863</v>
+        <v>79854</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
@@ -23715,15 +23713,15 @@
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
-        <v>6404</v>
+        <v>6302</v>
       </c>
       <c r="G299" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H299" s="1" t="inlineStr">
@@ -23737,10 +23735,10 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K299" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
@@ -23749,7 +23747,7 @@
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N299" s="1" t="n"/>
@@ -23767,16 +23765,16 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>79835</v>
+        <v>79863</v>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C300" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D300" s="1" t="inlineStr">
@@ -23786,15 +23784,15 @@
       </c>
       <c r="E300" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F300" s="1" t="n">
-        <v>6485</v>
+        <v>6404</v>
       </c>
       <c r="G300" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H300" s="1" t="inlineStr">
@@ -23808,10 +23806,10 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
@@ -23820,7 +23818,7 @@
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N300" s="1" t="n"/>
@@ -23838,16 +23836,16 @@
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>79866</v>
+        <v>79835</v>
       </c>
       <c r="B301" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C301" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D301" s="1" t="inlineStr">
@@ -23857,15 +23855,15 @@
       </c>
       <c r="E301" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F301" s="1" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="G301" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H301" s="1" t="inlineStr">
@@ -23879,10 +23877,10 @@
         </is>
       </c>
       <c r="J301" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K301" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L301" s="1" t="inlineStr">
         <is>
@@ -23891,7 +23889,7 @@
       </c>
       <c r="M301" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N301" s="1" t="n"/>
@@ -23909,7 +23907,7 @@
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
-        <v>79859</v>
+        <v>79866</v>
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
@@ -23928,15 +23926,15 @@
       </c>
       <c r="E302" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F302" s="1" t="n">
-        <v>6570</v>
+        <v>6539</v>
       </c>
       <c r="G302" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H302" s="1" t="inlineStr">
@@ -23950,7 +23948,7 @@
         </is>
       </c>
       <c r="J302" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K302" s="2" t="n">
         <v>46185</v>
@@ -23980,7 +23978,7 @@
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>79860</v>
+        <v>79859</v>
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
@@ -23999,15 +23997,15 @@
       </c>
       <c r="E303" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F303" s="1" t="n">
-        <v>6581</v>
+        <v>6570</v>
       </c>
       <c r="G303" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H303" s="1" t="inlineStr">
@@ -24021,7 +24019,7 @@
         </is>
       </c>
       <c r="J303" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K303" s="2" t="n">
         <v>46185</v>
@@ -24051,7 +24049,7 @@
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>79861</v>
+        <v>79860</v>
       </c>
       <c r="B304" s="1" t="inlineStr">
         <is>
@@ -24070,15 +24068,15 @@
       </c>
       <c r="E304" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F304" s="1" t="n">
-        <v>6583</v>
+        <v>6581</v>
       </c>
       <c r="G304" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H304" s="1" t="inlineStr">
@@ -24092,7 +24090,7 @@
         </is>
       </c>
       <c r="J304" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K304" s="2" t="n">
         <v>46185</v>
@@ -24122,16 +24120,16 @@
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>79867</v>
+        <v>79861</v>
       </c>
       <c r="B305" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C305" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D305" s="1" t="inlineStr">
@@ -24141,15 +24139,15 @@
       </c>
       <c r="E305" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F305" s="1" t="n">
-        <v>6704</v>
+        <v>6583</v>
       </c>
       <c r="G305" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H305" s="1" t="inlineStr">
@@ -24163,7 +24161,7 @@
         </is>
       </c>
       <c r="J305" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K305" s="2" t="n">
         <v>46185</v>
@@ -24193,7 +24191,7 @@
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>81019</v>
+        <v>79867</v>
       </c>
       <c r="B306" s="1" t="inlineStr">
         <is>
@@ -24202,23 +24200,27 @@
       </c>
       <c r="C306" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D306" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E306" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F306" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G306" s="1" t="n"/>
+        <v>6704</v>
+      </c>
+      <c r="G306" s="1" t="inlineStr">
+        <is>
+          <t>TECNO COM INFORMATICA LTDA</t>
+        </is>
+      </c>
       <c r="H306" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24230,10 +24232,10 @@
         </is>
       </c>
       <c r="J306" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K306" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L306" s="1" t="inlineStr">
         <is>
@@ -24242,7 +24244,7 @@
       </c>
       <c r="M306" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N306" s="1" t="n"/>
@@ -24260,32 +24262,36 @@
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>81052</v>
+        <v>79856</v>
       </c>
       <c r="B307" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C307" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D307" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E307" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F307" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G307" s="1" t="n"/>
+        <v>4225</v>
+      </c>
+      <c r="G307" s="1" t="inlineStr">
+        <is>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+        </is>
+      </c>
       <c r="H307" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24297,10 +24303,10 @@
         </is>
       </c>
       <c r="J307" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K307" s="2" t="n">
-        <v>46219</v>
+        <v>46184</v>
       </c>
       <c r="L307" s="1" t="inlineStr">
         <is>
@@ -24309,7 +24315,7 @@
       </c>
       <c r="M307" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N307" s="1" t="n"/>
@@ -24327,32 +24333,36 @@
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>81055</v>
+        <v>79855</v>
       </c>
       <c r="B308" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C308" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D308" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E308" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F308" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G308" s="1" t="n"/>
+        <v>4765</v>
+      </c>
+      <c r="G308" s="1" t="inlineStr">
+        <is>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+        </is>
+      </c>
       <c r="H308" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24364,10 +24374,10 @@
         </is>
       </c>
       <c r="J308" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K308" s="2" t="n">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="L308" s="1" t="inlineStr">
         <is>
@@ -24376,7 +24386,7 @@
       </c>
       <c r="M308" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N308" s="1" t="n"/>
@@ -24391,6 +24401,207 @@
       </c>
       <c r="T308" s="1" t="n"/>
       <c r="U308" s="1" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="1" t="n">
+        <v>81019</v>
+      </c>
+      <c r="B309" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C309" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E309" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+        </is>
+      </c>
+      <c r="F309" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G309" s="1" t="n"/>
+      <c r="H309" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I309" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J309" s="2" t="n">
+        <v>46217.43210269676</v>
+      </c>
+      <c r="K309" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="L309" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M309" s="1" t="inlineStr">
+        <is>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N309" s="1" t="n"/>
+      <c r="O309" s="1" t="n"/>
+      <c r="P309" s="1" t="n"/>
+      <c r="Q309" s="1" t="inlineStr"/>
+      <c r="R309" s="1" t="inlineStr"/>
+      <c r="S309" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T309" s="1" t="n"/>
+      <c r="U309" s="1" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="1" t="n">
+        <v>81052</v>
+      </c>
+      <c r="B310" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C310" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E310" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+        </is>
+      </c>
+      <c r="F310" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G310" s="1" t="n"/>
+      <c r="H310" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I310" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="n">
+        <v>46218.38736744213</v>
+      </c>
+      <c r="K310" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L310" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M310" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N310" s="1" t="n"/>
+      <c r="O310" s="1" t="n"/>
+      <c r="P310" s="1" t="n"/>
+      <c r="Q310" s="1" t="inlineStr"/>
+      <c r="R310" s="1" t="inlineStr"/>
+      <c r="S310" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T310" s="1" t="n"/>
+      <c r="U310" s="1" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="1" t="n">
+        <v>81055</v>
+      </c>
+      <c r="B311" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C311" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D311" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E311" s="1" t="inlineStr">
+        <is>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+        </is>
+      </c>
+      <c r="F311" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G311" s="1" t="n"/>
+      <c r="H311" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I311" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="n">
+        <v>46218.40379614583</v>
+      </c>
+      <c r="K311" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L311" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M311" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N311" s="1" t="n"/>
+      <c r="O311" s="1" t="n"/>
+      <c r="P311" s="1" t="n"/>
+      <c r="Q311" s="1" t="inlineStr"/>
+      <c r="R311" s="1" t="inlineStr"/>
+      <c r="S311" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T311" s="1" t="n"/>
+      <c r="U311" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -9173,7 +9173,7 @@
       </c>
       <c r="L106" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M106" s="1" t="inlineStr">
@@ -9185,12 +9185,22 @@
       <c r="O106" s="2" t="n">
         <v>46218</v>
       </c>
-      <c r="P106" s="1" t="n"/>
-      <c r="Q106" s="1" t="inlineStr"/>
-      <c r="R106" s="1" t="inlineStr"/>
+      <c r="P106" s="2" t="n">
+        <v>46219.58110721065</v>
+      </c>
+      <c r="Q106" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R106" s="1" t="inlineStr">
+        <is>
+          <t>Segue demonstrativos solicitados</t>
+        </is>
+      </c>
       <c r="S106" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T106" s="1" t="n"/>
@@ -9250,7 +9260,7 @@
       </c>
       <c r="L107" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M107" s="1" t="inlineStr">
@@ -9262,12 +9272,22 @@
       <c r="O107" s="2" t="n">
         <v>46217</v>
       </c>
-      <c r="P107" s="1" t="n"/>
-      <c r="Q107" s="1" t="inlineStr"/>
-      <c r="R107" s="1" t="inlineStr"/>
+      <c r="P107" s="2" t="n">
+        <v>46219.56934945602</v>
+      </c>
+      <c r="Q107" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R107" s="1" t="inlineStr">
+        <is>
+          <t>Vander, como já foi informado algumas vezes, houve uma mudança na baixa da tarefa, e já tinha sido acordado que o TI liberaria um acesso no SCIWEB para a conferencia de vocês.</t>
+        </is>
+      </c>
       <c r="S107" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T107" s="1" t="n"/>
@@ -10998,7 +11018,7 @@
       </c>
       <c r="L128" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M128" s="1" t="inlineStr">
@@ -11010,12 +11030,22 @@
       <c r="O128" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="P128" s="1" t="n"/>
-      <c r="Q128" s="1" t="inlineStr"/>
-      <c r="R128" s="1" t="inlineStr"/>
+      <c r="P128" s="2" t="n">
+        <v>46219.57306721065</v>
+      </c>
+      <c r="Q128" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R128" s="1" t="inlineStr">
+        <is>
+          <t>Conforme conversado no e-mail os valores do balancete estavam desatualizados, se for necessário fazer outros ajuste por favor orientar via chamado com autorização previa do GM e Diretoria.</t>
+        </is>
+      </c>
       <c r="S128" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T128" s="1" t="n"/>
@@ -11729,7 +11759,7 @@
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M137" s="1" t="inlineStr">
@@ -11741,12 +11771,22 @@
       <c r="O137" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="P137" s="1" t="n"/>
-      <c r="Q137" s="1" t="inlineStr"/>
-      <c r="R137" s="1" t="inlineStr"/>
+      <c r="P137" s="2" t="n">
+        <v>46219.5832929051</v>
+      </c>
+      <c r="Q137" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R137" s="1" t="inlineStr">
+        <is>
+          <t>Em anexo</t>
+        </is>
+      </c>
       <c r="S137" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T137" s="1" t="n"/>
@@ -13004,7 +13044,7 @@
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M153" s="1" t="inlineStr">
@@ -13016,12 +13056,22 @@
       <c r="O153" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="P153" s="1" t="n"/>
-      <c r="Q153" s="1" t="inlineStr"/>
-      <c r="R153" s="1" t="inlineStr"/>
+      <c r="P153" s="2" t="n">
+        <v>46219.59946519676</v>
+      </c>
+      <c r="Q153" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R153" s="1" t="inlineStr">
+        <is>
+          <t>Anexo</t>
+        </is>
+      </c>
       <c r="S153" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T153" s="1" t="n"/>
@@ -13822,7 +13872,7 @@
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M163" s="1" t="inlineStr">
@@ -13834,12 +13884,22 @@
       <c r="O163" s="2" t="n">
         <v>46217</v>
       </c>
-      <c r="P163" s="1" t="n"/>
-      <c r="Q163" s="1" t="inlineStr"/>
-      <c r="R163" s="1" t="inlineStr"/>
+      <c r="P163" s="2" t="n">
+        <v>46219.57626284722</v>
+      </c>
+      <c r="Q163" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
+      <c r="R163" s="1" t="inlineStr">
+        <is>
+          <t>Já foi ajustado conforme solicitado anteriormente na Analise Balanço</t>
+        </is>
+      </c>
       <c r="S163" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T163" s="1" t="n"/>
@@ -16751,7 +16811,11 @@
         <v>0</v>
       </c>
       <c r="G201" s="1" t="n"/>
-      <c r="H201" s="1" t="n"/>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>Ana Santana</t>
+        </is>
+      </c>
       <c r="I201" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
@@ -16765,7 +16829,7 @@
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M201" s="1" t="inlineStr">
@@ -16777,7 +16841,7 @@
       <c r="O201" s="1" t="n"/>
       <c r="P201" s="1" t="n"/>
       <c r="Q201" s="1" t="inlineStr"/>
-      <c r="R201" s="1" t="n"/>
+      <c r="R201" s="1" t="inlineStr"/>
       <c r="S201" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -20167,7 +20231,11 @@
           <t xml:space="preserve">MONTE CARLO LAB SERVICOS ADMINISTRATIVOS E COMERCIO LTDA </t>
         </is>
       </c>
-      <c r="H249" s="1" t="n"/>
+      <c r="H249" s="1" t="inlineStr">
+        <is>
+          <t>Rodrigo Rego</t>
+        </is>
+      </c>
       <c r="I249" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
@@ -20181,7 +20249,7 @@
       </c>
       <c r="L249" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M249" s="1" t="inlineStr">
@@ -20193,7 +20261,7 @@
       <c r="O249" s="1" t="n"/>
       <c r="P249" s="1" t="n"/>
       <c r="Q249" s="1" t="inlineStr"/>
-      <c r="R249" s="1" t="n"/>
+      <c r="R249" s="1" t="inlineStr"/>
       <c r="S249" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -20660,7 +20728,11 @@
           <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
         </is>
       </c>
-      <c r="H256" s="1" t="n"/>
+      <c r="H256" s="1" t="inlineStr">
+        <is>
+          <t>Vander Silva</t>
+        </is>
+      </c>
       <c r="I256" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
@@ -20674,7 +20746,7 @@
       </c>
       <c r="L256" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M256" s="1" t="inlineStr">
@@ -20686,7 +20758,7 @@
       <c r="O256" s="1" t="n"/>
       <c r="P256" s="1" t="n"/>
       <c r="Q256" s="1" t="inlineStr"/>
-      <c r="R256" s="1" t="n"/>
+      <c r="R256" s="1" t="inlineStr"/>
       <c r="S256" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21193,7 +21265,7 @@
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M263" s="1" t="inlineStr">
@@ -21201,11 +21273,17 @@
           <t>Alaine Neres</t>
         </is>
       </c>
-      <c r="N263" s="1" t="n"/>
+      <c r="N263" s="2" t="n">
+        <v>46219.62708564815</v>
+      </c>
       <c r="O263" s="1" t="n"/>
       <c r="P263" s="1" t="n"/>
       <c r="Q263" s="1" t="inlineStr"/>
-      <c r="R263" s="1" t="inlineStr"/>
+      <c r="R263" s="1" t="inlineStr">
+        <is>
+          <t>Empresa possui débitos que impedem a baixa em São Paulo, enviado ao cliente para pagamento e protocolado nomente o processo. Aguardando a baixa definitiva do CCM SP.</t>
+        </is>
+      </c>
       <c r="S263" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21443,7 +21521,11 @@
         <v>0</v>
       </c>
       <c r="G267" s="1" t="n"/>
-      <c r="H267" s="1" t="n"/>
+      <c r="H267" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I267" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21457,7 +21539,7 @@
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M267" s="1" t="inlineStr">
@@ -21469,7 +21551,7 @@
       <c r="O267" s="1" t="n"/>
       <c r="P267" s="1" t="n"/>
       <c r="Q267" s="1" t="inlineStr"/>
-      <c r="R267" s="1" t="n"/>
+      <c r="R267" s="1" t="inlineStr"/>
       <c r="S267" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21573,7 +21655,11 @@
         <v>0</v>
       </c>
       <c r="G269" s="1" t="n"/>
-      <c r="H269" s="1" t="n"/>
+      <c r="H269" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I269" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21587,7 +21673,7 @@
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M269" s="1" t="inlineStr">
@@ -21599,7 +21685,7 @@
       <c r="O269" s="1" t="n"/>
       <c r="P269" s="1" t="n"/>
       <c r="Q269" s="1" t="inlineStr"/>
-      <c r="R269" s="1" t="n"/>
+      <c r="R269" s="1" t="inlineStr"/>
       <c r="S269" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21636,7 +21722,11 @@
         <v>0</v>
       </c>
       <c r="G270" s="1" t="n"/>
-      <c r="H270" s="1" t="n"/>
+      <c r="H270" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21650,7 +21740,7 @@
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
@@ -21662,7 +21752,7 @@
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="n"/>
+      <c r="R270" s="1" t="inlineStr"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21699,7 +21789,11 @@
         <v>0</v>
       </c>
       <c r="G271" s="1" t="n"/>
-      <c r="H271" s="1" t="n"/>
+      <c r="H271" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I271" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21713,7 +21807,7 @@
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
@@ -21725,7 +21819,7 @@
       <c r="O271" s="1" t="n"/>
       <c r="P271" s="1" t="n"/>
       <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="n"/>
+      <c r="R271" s="1" t="inlineStr"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21762,7 +21856,11 @@
         <v>0</v>
       </c>
       <c r="G272" s="1" t="n"/>
-      <c r="H272" s="1" t="n"/>
+      <c r="H272" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I272" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21776,7 +21874,7 @@
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M272" s="1" t="inlineStr">
@@ -21788,7 +21886,7 @@
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="1" t="n"/>
       <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="n"/>
+      <c r="R272" s="1" t="inlineStr"/>
       <c r="S272" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21825,7 +21923,11 @@
         <v>0</v>
       </c>
       <c r="G273" s="1" t="n"/>
-      <c r="H273" s="1" t="n"/>
+      <c r="H273" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I273" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21839,7 +21941,7 @@
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M273" s="1" t="inlineStr">
@@ -21851,7 +21953,7 @@
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="1" t="n"/>
       <c r="Q273" s="1" t="inlineStr"/>
-      <c r="R273" s="1" t="n"/>
+      <c r="R273" s="1" t="inlineStr"/>
       <c r="S273" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21888,7 +21990,11 @@
         <v>0</v>
       </c>
       <c r="G274" s="1" t="n"/>
-      <c r="H274" s="1" t="n"/>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I274" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21902,7 +22008,7 @@
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M274" s="1" t="inlineStr">
@@ -21914,7 +22020,7 @@
       <c r="O274" s="1" t="n"/>
       <c r="P274" s="1" t="n"/>
       <c r="Q274" s="1" t="inlineStr"/>
-      <c r="R274" s="1" t="n"/>
+      <c r="R274" s="1" t="inlineStr"/>
       <c r="S274" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21951,7 +22057,11 @@
         <v>0</v>
       </c>
       <c r="G275" s="1" t="n"/>
-      <c r="H275" s="1" t="n"/>
+      <c r="H275" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I275" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -21965,7 +22075,7 @@
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M275" s="1" t="inlineStr">
@@ -21977,7 +22087,7 @@
       <c r="O275" s="1" t="n"/>
       <c r="P275" s="1" t="n"/>
       <c r="Q275" s="1" t="inlineStr"/>
-      <c r="R275" s="1" t="n"/>
+      <c r="R275" s="1" t="inlineStr"/>
       <c r="S275" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22014,7 +22124,11 @@
         <v>0</v>
       </c>
       <c r="G276" s="1" t="n"/>
-      <c r="H276" s="1" t="n"/>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I276" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22028,7 +22142,7 @@
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
@@ -22040,7 +22154,7 @@
       <c r="O276" s="1" t="n"/>
       <c r="P276" s="1" t="n"/>
       <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="n"/>
+      <c r="R276" s="1" t="inlineStr"/>
       <c r="S276" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22077,7 +22191,11 @@
         <v>0</v>
       </c>
       <c r="G277" s="1" t="n"/>
-      <c r="H277" s="1" t="n"/>
+      <c r="H277" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22091,7 +22209,7 @@
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
@@ -22103,7 +22221,7 @@
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="n"/>
+      <c r="R277" s="1" t="inlineStr"/>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22140,7 +22258,11 @@
         <v>0</v>
       </c>
       <c r="G278" s="1" t="n"/>
-      <c r="H278" s="1" t="n"/>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I278" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22154,7 +22276,7 @@
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M278" s="1" t="inlineStr">
@@ -22166,7 +22288,7 @@
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="n"/>
+      <c r="R278" s="1" t="inlineStr"/>
       <c r="S278" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22270,7 +22392,11 @@
         <v>0</v>
       </c>
       <c r="G280" s="1" t="n"/>
-      <c r="H280" s="1" t="n"/>
+      <c r="H280" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I280" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22284,7 +22410,7 @@
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M280" s="1" t="inlineStr">
@@ -22296,7 +22422,7 @@
       <c r="O280" s="1" t="n"/>
       <c r="P280" s="1" t="n"/>
       <c r="Q280" s="1" t="inlineStr"/>
-      <c r="R280" s="1" t="n"/>
+      <c r="R280" s="1" t="inlineStr"/>
       <c r="S280" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22408,7 +22534,11 @@
           <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
-      <c r="H282" s="1" t="n"/>
+      <c r="H282" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I282" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22422,7 +22552,7 @@
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M282" s="1" t="inlineStr">
@@ -22434,7 +22564,7 @@
       <c r="O282" s="1" t="n"/>
       <c r="P282" s="1" t="n"/>
       <c r="Q282" s="1" t="inlineStr"/>
-      <c r="R282" s="1" t="n"/>
+      <c r="R282" s="1" t="inlineStr"/>
       <c r="S282" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22475,7 +22605,11 @@
           <t>AC HOME PET RAÇÕES LTDA</t>
         </is>
       </c>
-      <c r="H283" s="1" t="n"/>
+      <c r="H283" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22489,7 +22623,7 @@
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
@@ -22501,7 +22635,7 @@
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="n"/>
+      <c r="R283" s="1" t="inlineStr"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22542,7 +22676,11 @@
           <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
         </is>
       </c>
-      <c r="H284" s="1" t="n"/>
+      <c r="H284" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I284" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22556,7 +22694,7 @@
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M284" s="1" t="inlineStr">
@@ -22568,7 +22706,7 @@
       <c r="O284" s="1" t="n"/>
       <c r="P284" s="1" t="n"/>
       <c r="Q284" s="1" t="inlineStr"/>
-      <c r="R284" s="1" t="n"/>
+      <c r="R284" s="1" t="inlineStr"/>
       <c r="S284" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22609,7 +22747,11 @@
           <t>MERCH LTDA (FILIAL 1)</t>
         </is>
       </c>
-      <c r="H285" s="1" t="n"/>
+      <c r="H285" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
       <c r="I285" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
@@ -22623,7 +22765,7 @@
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
@@ -22635,7 +22777,7 @@
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="n"/>
+      <c r="R285" s="1" t="inlineStr"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U295" headerRowCount="1">
-  <autoFilter ref="A1:U295"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U292" headerRowCount="1">
+  <autoFilter ref="A1:U292"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U295"/>
+  <dimension ref="A1:U292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M264" s="1" t="inlineStr">
@@ -21296,11 +21296,17 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N264" s="1" t="n"/>
+      <c r="N264" s="2" t="n">
+        <v>46219.75157017361</v>
+      </c>
       <c r="O264" s="1" t="n"/>
       <c r="P264" s="1" t="n"/>
       <c r="Q264" s="1" t="inlineStr"/>
-      <c r="R264" s="1" t="inlineStr"/>
+      <c r="R264" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enviado para registro </t>
+        </is>
+      </c>
       <c r="S264" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21690,7 +21696,7 @@
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
@@ -21698,11 +21704,17 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N270" s="1" t="n"/>
+      <c r="N270" s="2" t="n">
+        <v>46219.74920023148</v>
+      </c>
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="inlineStr"/>
+      <c r="R270" s="1" t="inlineStr">
+        <is>
+          <t>Minuta enviada ao cliente</t>
+        </is>
+      </c>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21713,11 +21725,11 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>81070</v>
+        <v>80989</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -21732,7 +21744,7 @@
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.2681 Comercio de Alimentos Alves e Farias MATRIZ</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
@@ -21741,7 +21753,7 @@
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
@@ -21750,10 +21762,10 @@
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46218.51467572917</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46220</v>
+        <v>46217</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -21762,7 +21774,7 @@
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
@@ -21780,35 +21792,39 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>81071</v>
+        <v>79793</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3252 Comercio de Alimentos Alves e Farias FILIAL 01</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G272" s="1" t="n"/>
+        <v>5655</v>
+      </c>
+      <c r="G272" s="1" t="inlineStr">
+        <is>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
       <c r="H272" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I272" s="1" t="inlineStr">
@@ -21817,10 +21833,10 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46218.51533788195</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46220</v>
+        <v>46185</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -21829,7 +21845,7 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
@@ -21847,16 +21863,16 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>81072</v>
+        <v>81004</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -21866,16 +21882,20 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Bom Dia, Por favorPreciso da nova senha para acesso ao novo portal GissOnline das lojas abaixo.3257 Comercio de Alimentos Alves e Farias FILIAL 06</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G273" s="1" t="n"/>
+        <v>6869</v>
+      </c>
+      <c r="G273" s="1" t="inlineStr">
+        <is>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+        </is>
+      </c>
       <c r="H273" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I273" s="1" t="inlineStr">
@@ -21884,10 +21904,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46218.51577677084</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -21896,7 +21916,7 @@
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Regiane Santos</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
@@ -21914,16 +21934,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80989</v>
+        <v>81005</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -21933,16 +21953,20 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="1" t="n"/>
+        <v>6870</v>
+      </c>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>AC HOME PET RAÇÕES LTDA</t>
+        </is>
+      </c>
       <c r="H274" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I274" s="1" t="inlineStr">
@@ -21951,10 +21975,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -21963,7 +21987,7 @@
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
@@ -21981,34 +22005,34 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>79793</v>
+        <v>81091</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
-        <v>5655</v>
+        <v>6907</v>
       </c>
       <c r="G275" s="1" t="inlineStr">
         <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
         </is>
       </c>
       <c r="H275" s="1" t="inlineStr">
@@ -22022,10 +22046,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46219.3374690162</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46185</v>
+        <v>46223</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22034,7 +22058,7 @@
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N275" s="1" t="n"/>
@@ -22052,7 +22076,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>81004</v>
+        <v>81161</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22066,25 +22090,25 @@
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Sarah, boa tarde!Por gentileza incluir no MGC o número da Inscrição Municipal - Prefeitura de Embu das Artes.</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
-        <v>6869</v>
+        <v>6916</v>
       </c>
       <c r="G276" s="1" t="inlineStr">
         <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+          <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H276" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Sarah Amaro</t>
         </is>
       </c>
       <c r="I276" s="1" t="inlineStr">
@@ -22093,10 +22117,10 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46219.69548784722</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
@@ -22105,7 +22129,7 @@
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="N276" s="1" t="n"/>
@@ -22123,67 +22147,73 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>81005</v>
+        <v>79833</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
-        <v>6870</v>
+        <v>6125</v>
       </c>
       <c r="G277" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H277" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46218</v>
+        <v>46184</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
-      <c r="N277" s="1" t="n"/>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>46219.71277496528</v>
+      </c>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="inlineStr"/>
+      <c r="R277" s="1" t="inlineStr">
+        <is>
+          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
+        </is>
+      </c>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22194,34 +22224,34 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>81091</v>
+        <v>79834</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
-        <v>6907</v>
+        <v>6162</v>
       </c>
       <c r="G278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H278" s="1" t="inlineStr">
@@ -22231,14 +22261,14 @@
       </c>
       <c r="I278" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46219.3374690162</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46223</v>
+        <v>46184</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
@@ -22247,7 +22277,7 @@
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N278" s="1" t="n"/>
@@ -22265,63 +22295,67 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>81161</v>
+        <v>79865</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Sarah, boa tarde!Por gentileza incluir no MGC o número da Inscrição Municipal - Prefeitura de Embu das Artes.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
-        <v>6916</v>
+        <v>6278</v>
       </c>
       <c r="G279" s="1" t="inlineStr">
         <is>
-          <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA (FILIAL 1)</t>
-        </is>
-      </c>
-      <c r="H279" s="1" t="n"/>
+          <t>EMPORIO DOS FRIOS LTDA</t>
+        </is>
+      </c>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I279" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46219.69548784722</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46220</v>
+        <v>46185</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N279" s="1" t="n"/>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="n"/>
+      <c r="R279" s="1" t="inlineStr"/>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22332,16 +22366,16 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>79833</v>
+        <v>79854</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -22351,15 +22385,15 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
-        <v>6125</v>
+        <v>6302</v>
       </c>
       <c r="G280" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H280" s="1" t="inlineStr">
@@ -22373,7 +22407,7 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K280" s="2" t="n">
         <v>46184</v>
@@ -22403,16 +22437,16 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>79834</v>
+        <v>79863</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -22422,15 +22456,15 @@
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>6162</v>
+        <v>6404</v>
       </c>
       <c r="G281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H281" s="1" t="inlineStr">
@@ -22444,10 +22478,10 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -22456,7 +22490,7 @@
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
@@ -22474,16 +22508,16 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>79865</v>
+        <v>79835</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
@@ -22493,15 +22527,15 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
-        <v>6278</v>
+        <v>6485</v>
       </c>
       <c r="G282" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H282" s="1" t="inlineStr">
@@ -22515,10 +22549,10 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -22527,7 +22561,7 @@
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N282" s="1" t="n"/>
@@ -22545,7 +22579,7 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>79854</v>
+        <v>79866</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
@@ -22564,15 +22598,15 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
-        <v>6302</v>
+        <v>6539</v>
       </c>
       <c r="G283" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H283" s="1" t="inlineStr">
@@ -22586,10 +22620,10 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
@@ -22598,7 +22632,7 @@
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
@@ -22616,7 +22650,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>79863</v>
+        <v>79859</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
@@ -22635,15 +22669,15 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
-        <v>6404</v>
+        <v>6570</v>
       </c>
       <c r="G284" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H284" s="1" t="inlineStr">
@@ -22657,7 +22691,7 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K284" s="2" t="n">
         <v>46185</v>
@@ -22687,16 +22721,16 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>79835</v>
+        <v>79860</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
@@ -22706,15 +22740,15 @@
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>6485</v>
+        <v>6581</v>
       </c>
       <c r="G285" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H285" s="1" t="inlineStr">
@@ -22728,10 +22762,10 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
@@ -22740,7 +22774,7 @@
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N285" s="1" t="n"/>
@@ -22758,7 +22792,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>79866</v>
+        <v>79861</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
@@ -22777,15 +22811,15 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6539</v>
+        <v>6583</v>
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H286" s="1" t="inlineStr">
@@ -22799,7 +22833,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K286" s="2" t="n">
         <v>46185</v>
@@ -22829,16 +22863,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>79859</v>
+        <v>79867</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
@@ -22848,15 +22882,15 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6570</v>
+        <v>6704</v>
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H287" s="1" t="inlineStr">
@@ -22870,7 +22904,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K287" s="2" t="n">
         <v>46185</v>
@@ -22900,7 +22934,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>79860</v>
+        <v>79856</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
@@ -22919,15 +22953,15 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>6581</v>
+        <v>4225</v>
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
         </is>
       </c>
       <c r="H288" s="1" t="inlineStr">
@@ -22941,10 +22975,10 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -22953,7 +22987,7 @@
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N288" s="1" t="n"/>
@@ -22971,7 +23005,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79861</v>
+        <v>79855</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
@@ -22990,15 +23024,15 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>6583</v>
+        <v>4765</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
         </is>
       </c>
       <c r="H289" s="1" t="inlineStr">
@@ -23012,7 +23046,7 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K289" s="2" t="n">
         <v>46185</v>
@@ -23024,7 +23058,7 @@
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N289" s="1" t="n"/>
@@ -23042,7 +23076,7 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79867</v>
+        <v>81019</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
@@ -23051,27 +23085,23 @@
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>6704</v>
-      </c>
-      <c r="G290" s="1" t="inlineStr">
-        <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G290" s="1" t="n"/>
       <c r="H290" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23079,70 +23109,75 @@
       </c>
       <c r="I290" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
       <c r="O290" s="1" t="n"/>
       <c r="P290" s="1" t="n"/>
       <c r="Q290" s="1" t="inlineStr"/>
-      <c r="R290" s="1" t="inlineStr"/>
+      <c r="R290" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia 
+Segue recibos conforme solictiado </t>
+        </is>
+      </c>
       <c r="S290" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T290" s="1" t="n"/>
+      <c r="T290" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U290" s="1" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>79856</v>
+        <v>81052</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>4225</v>
-      </c>
-      <c r="G291" s="1" t="inlineStr">
-        <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G291" s="1" t="n"/>
       <c r="H291" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23154,26 +23189,30 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46218.38736744213</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>46184</v>
+        <v>46219</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="N291" s="1" t="n"/>
       <c r="O291" s="1" t="n"/>
       <c r="P291" s="1" t="n"/>
       <c r="Q291" s="1" t="inlineStr"/>
-      <c r="R291" s="1" t="inlineStr"/>
+      <c r="R291" s="1" t="inlineStr">
+        <is>
+          <t>cobramos os documentos do antigo contador.</t>
+        </is>
+      </c>
       <c r="S291" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23184,36 +23223,32 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>79855</v>
+        <v>81055</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>4765</v>
-      </c>
-      <c r="G292" s="1" t="inlineStr">
-        <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G292" s="1" t="n"/>
       <c r="H292" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23225,26 +23260,32 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46218.40379614583</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>46185</v>
+        <v>46219</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="N292" s="1" t="n"/>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N292" s="2" t="n">
+        <v>46219.50607847222</v>
+      </c>
       <c r="O292" s="1" t="n"/>
       <c r="P292" s="1" t="n"/>
       <c r="Q292" s="1" t="inlineStr"/>
-      <c r="R292" s="1" t="inlineStr"/>
+      <c r="R292" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando retorno dos dados do contador</t>
+        </is>
+      </c>
       <c r="S292" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23252,226 +23293,6 @@
       </c>
       <c r="T292" s="1" t="n"/>
       <c r="U292" s="1" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="1" t="n">
-        <v>81019</v>
-      </c>
-      <c r="B293" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C293" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D293" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
-        </is>
-      </c>
-      <c r="F293" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G293" s="1" t="n"/>
-      <c r="H293" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I293" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="J293" s="2" t="n">
-        <v>46217.43210269676</v>
-      </c>
-      <c r="K293" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="L293" s="1" t="inlineStr">
-        <is>
-          <t>Devolvido para Solicitante</t>
-        </is>
-      </c>
-      <c r="M293" s="1" t="inlineStr">
-        <is>
-          <t>Santos Karina</t>
-        </is>
-      </c>
-      <c r="N293" s="1" t="n"/>
-      <c r="O293" s="1" t="n"/>
-      <c r="P293" s="1" t="n"/>
-      <c r="Q293" s="1" t="inlineStr"/>
-      <c r="R293" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia 
-Segue recibos conforme solictiado </t>
-        </is>
-      </c>
-      <c r="S293" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T293" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="U293" s="1" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="1" t="n">
-        <v>81052</v>
-      </c>
-      <c r="B294" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C294" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D294" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E294" s="1" t="inlineStr">
-        <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
-        </is>
-      </c>
-      <c r="F294" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G294" s="1" t="n"/>
-      <c r="H294" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I294" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J294" s="2" t="n">
-        <v>46218.38736744213</v>
-      </c>
-      <c r="K294" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L294" s="1" t="inlineStr">
-        <is>
-          <t>Devolvido para Responsável</t>
-        </is>
-      </c>
-      <c r="M294" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N294" s="1" t="n"/>
-      <c r="O294" s="1" t="n"/>
-      <c r="P294" s="1" t="n"/>
-      <c r="Q294" s="1" t="inlineStr"/>
-      <c r="R294" s="1" t="inlineStr">
-        <is>
-          <t>cobramos os documentos do antigo contador.</t>
-        </is>
-      </c>
-      <c r="S294" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T294" s="1" t="n"/>
-      <c r="U294" s="1" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="1" t="n">
-        <v>81055</v>
-      </c>
-      <c r="B295" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C295" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D295" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E295" s="1" t="inlineStr">
-        <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
-        </is>
-      </c>
-      <c r="F295" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G295" s="1" t="n"/>
-      <c r="H295" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I295" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J295" s="2" t="n">
-        <v>46218.40379614583</v>
-      </c>
-      <c r="K295" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L295" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M295" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N295" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
-      <c r="O295" s="1" t="n"/>
-      <c r="P295" s="1" t="n"/>
-      <c r="Q295" s="1" t="inlineStr"/>
-      <c r="R295" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando retorno dos dados do contador</t>
-        </is>
-      </c>
-      <c r="S295" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T295" s="1" t="n"/>
-      <c r="U295" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U292" headerRowCount="1">
-  <autoFilter ref="A1:U292"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U293" headerRowCount="1">
+  <autoFilter ref="A1:U293"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U292"/>
+  <dimension ref="A1:U293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -11189,150 +11189,73 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>80944</v>
+        <v>79820</v>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, adiantar a entrega da ECF pois o cliente está participando do Pronampe.</t>
+          <t>Consta pendência parcial de INSS referente mês 03/2026. Favor verificar se a pendência é indevida para retificação da DCTF.</t>
         </is>
       </c>
       <c r="F131" s="1" t="n">
-        <v>5901</v>
+        <v>5908</v>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t>Local Serviços Especializados LTDA</t>
+          <t>MERCH LINK LTDA</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Mauricio Lermen</t>
         </is>
       </c>
       <c r="I131" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>46213.59176006944</v>
+        <v>46182.79089837963</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>46216</v>
+        <v>46189</v>
       </c>
       <c r="L131" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M131" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N131" s="1" t="n"/>
-      <c r="O131" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="P131" s="1" t="n"/>
-      <c r="Q131" s="1" t="inlineStr"/>
-      <c r="R131" s="1" t="inlineStr"/>
-      <c r="S131" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T131" s="1" t="n"/>
-      <c r="U131" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>79820</v>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>Pendência de Débito</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>Pendência de Débito</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>Consta pendência parcial de INSS referente mês 03/2026. Favor verificar se a pendência é indevida para retificação da DCTF.</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="n">
-        <v>5908</v>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t>MERCH LINK LTDA</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
+      <c r="O131" s="1" t="n"/>
+      <c r="P131" s="2" t="n">
+        <v>46189.41413730324</v>
+      </c>
+      <c r="Q131" s="1" t="inlineStr">
         <is>
           <t>Mauricio Lermen</t>
         </is>
       </c>
-      <c r="I132" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="J132" s="2" t="n">
-        <v>46182.79089837963</v>
-      </c>
-      <c r="K132" s="2" t="n">
-        <v>46189</v>
-      </c>
-      <c r="L132" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M132" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N132" s="1" t="n"/>
-      <c r="O132" s="1" t="n"/>
-      <c r="P132" s="2" t="n">
-        <v>46189.41413730324</v>
-      </c>
-      <c r="Q132" s="1" t="inlineStr">
-        <is>
-          <t>Mauricio Lermen</t>
-        </is>
-      </c>
-      <c r="R132" s="1" t="inlineStr">
+      <c r="R131" s="1" t="inlineStr">
         <is>
           <t>Bom dia!
 Os valores são devidos conforme resumo, estou levantando se houve alteração após liberação.
@@ -11340,26 +11263,109 @@
 devolve este chamado para continuidade.</t>
         </is>
       </c>
+      <c r="S131" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T131" s="1" t="n"/>
+      <c r="U131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>80203</v>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>Autorregularização</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>Autorregularização</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>Prezados, Boa tarde!Clienrte notificado ref autoregularização ref divergências na comparação por referência entre os valores do PGDAS e da Declaração de Informações de Meios de Pagamentos (DIMP).Prazo para regularização até 12/07/26Documentos disponiveis na pasta abaixo:J:\Importação\AUTO REGULARIZAÇÃO - PGDAS\5908</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>5908</v>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>MERCH LINK LTDA</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>46191.57591585648</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>46203</v>
+      </c>
+      <c r="L132" s="1" t="inlineStr">
+        <is>
+          <t>Devolvido para Solicitante</t>
+        </is>
+      </c>
+      <c r="M132" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N132" s="1" t="n"/>
+      <c r="O132" s="1" t="n"/>
+      <c r="P132" s="1" t="n"/>
+      <c r="Q132" s="1" t="inlineStr"/>
+      <c r="R132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">verificando </t>
+        </is>
+      </c>
       <c r="S132" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T132" s="1" t="n"/>
-      <c r="U132" s="1" t="inlineStr"/>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T132" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="U132" s="1" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>80203</v>
+        <v>79868</v>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -11369,7 +11375,7 @@
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t>Prezados, Boa tarde!Clienrte notificado ref autoregularização ref divergências na comparação por referência entre os valores do PGDAS e da Declaração de Informações de Meios de Pagamentos (DIMP).Prazo para regularização até 12/07/26Documentos disponiveis na pasta abaixo:J:\Importação\AUTO REGULARIZAÇÃO - PGDAS\5908</t>
+          <t>Prezados, boa tarde!Cliente comunicou que o valor apurado no período de março 2026 está incompleto. Segundo cliente os valores de NFCe não foram considerados.Por gentileza, avaliar se os arquivos disponibilizados na época, via FTP foram escriturados.</t>
         </is>
       </c>
       <c r="F133" s="1" t="n">
@@ -11391,10 +11397,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>46191.57591585648</v>
+        <v>46183.63777893518</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>46203</v>
+        <v>46184</v>
       </c>
       <c r="L133" s="1" t="inlineStr">
         <is>
@@ -11412,7 +11418,8 @@
       <c r="Q133" s="1" t="inlineStr"/>
       <c r="R133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">verificando </t>
+          <t xml:space="preserve">Irei verificar. 
+foi enviado ao cliente a confirmação de faturamento, porém não tivemos retorno na época. </t>
         </is>
       </c>
       <c r="S133" s="1" t="inlineStr">
@@ -11433,16 +11440,16 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>79868</v>
+        <v>80527</v>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Ajuste de Documentação</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -11452,7 +11459,7 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Cliente comunicou que o valor apurado no período de março 2026 está incompleto. Segundo cliente os valores de NFCe não foram considerados.Por gentileza, avaliar se os arquivos disponibilizados na época, via FTP foram escriturados.</t>
+          <t>Prezados,Conforme solicitação do cliente favor providenciar o prólabore abaixo a partir do mês de julho 2026Merch Link LTDA: 49.797.761/0001-05- Ana Ligia Ribeiro Terensi Silva (proprietária)- ?Pró-labore: R$3.000,00</t>
         </is>
       </c>
       <c r="F134" s="1" t="n">
@@ -11465,23 +11472,23 @@
       </c>
       <c r="H134" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>46183.63777893518</v>
+        <v>46197.47626122685</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>46184</v>
+        <v>46203</v>
       </c>
       <c r="L134" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M134" s="1" t="inlineStr">
@@ -11489,44 +11496,43 @@
           <t>Bruno Contieri</t>
         </is>
       </c>
-      <c r="N134" s="1" t="n"/>
+      <c r="N134" s="2" t="n">
+        <v>46197.57248116898</v>
+      </c>
       <c r="O134" s="1" t="n"/>
-      <c r="P134" s="1" t="n"/>
-      <c r="Q134" s="1" t="inlineStr"/>
+      <c r="P134" s="2" t="n">
+        <v>46203.72243090278</v>
+      </c>
+      <c r="Q134" s="1" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="R134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Irei verificar. 
-foi enviado ao cliente a confirmação de faturamento, porém não tivemos retorno na época. </t>
+          <t>Realizando cadastro para a folha de pro-labore.</t>
         </is>
       </c>
       <c r="S134" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T134" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
-      <c r="U134" s="1" t="inlineStr">
-        <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T134" s="1" t="n"/>
+      <c r="U134" s="1" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>80527</v>
+        <v>80631</v>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Termos de Intimação</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t>Ajuste de Documentação</t>
+          <t>Receita Federal</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
@@ -11536,32 +11542,32 @@
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Conforme solicitação do cliente favor providenciar o prólabore abaixo a partir do mês de julho 2026Merch Link LTDA: 49.797.761/0001-05- Ana Ligia Ribeiro Terensi Silva (proprietária)- ?Pró-labore: R$3.000,00</t>
+          <t>Bom dia, por gentileza verificar termo de intimação recebido na caixa postal referente a omissão das declarações: DCTF MENSAL 2024 DEZECF ANUAL 2024EFD CONTR MENSAL 2024 DEZConforme o e-mail em anexo foi autorizada a entrega das obrigações em branco pelo Nélio, por gentileza verificar com a Tatiana se houve tratativa junto ao Natan, pois não localizei retorno do mesmo. Precisamos encaminhar as obrigações o quanto antes, pois a empresa passou a ficar Inapta.</t>
         </is>
       </c>
       <c r="F135" s="1" t="n">
-        <v>5908</v>
+        <v>5979</v>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t>MERCH LINK LTDA</t>
+          <t>AMATRUDA LOCADORA DE GUINDASTES E ARTICULADOS LTDA</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I135" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>46197.47626122685</v>
+        <v>46203.51057075232</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -11570,24 +11576,22 @@
       </c>
       <c r="M135" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N135" s="2" t="n">
-        <v>46197.57248116898</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N135" s="1" t="n"/>
       <c r="O135" s="1" t="n"/>
       <c r="P135" s="2" t="n">
-        <v>46203.72243090278</v>
+        <v>46206.71474591435</v>
       </c>
       <c r="Q135" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R135" s="1" t="inlineStr">
         <is>
-          <t>Realizando cadastro para a folha de pro-labore.</t>
+          <t>Empresa simples nacional, porem inicio de responsabilidade mg 01/01/2025 , pendencia ref 12/2024</t>
         </is>
       </c>
       <c r="S135" s="1" t="inlineStr">
@@ -11596,43 +11600,47 @@
         </is>
       </c>
       <c r="T135" s="1" t="n"/>
-      <c r="U135" s="1" t="inlineStr"/>
+      <c r="U135" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>80631</v>
+        <v>80797</v>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>Termos de Intimação</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>Receita Federal</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza verificar termo de intimação recebido na caixa postal referente a omissão das declarações: DCTF MENSAL 2024 DEZECF ANUAL 2024EFD CONTR MENSAL 2024 DEZConforme o e-mail em anexo foi autorizada a entrega das obrigações em branco pelo Nélio, por gentileza verificar com a Tatiana se houve tratativa junto ao Natan, pois não localizei retorno do mesmo. Precisamos encaminhar as obrigações o quanto antes, pois a empresa passou a ficar Inapta.</t>
+          <t>Boa tarde! Por gentileza, poderia me encaminhar o balanço e DRE 2025.</t>
         </is>
       </c>
       <c r="F136" s="1" t="n">
-        <v>5979</v>
+        <v>5983</v>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t>AMATRUDA LOCADORA DE GUINDASTES E ARTICULADOS LTDA</t>
+          <t xml:space="preserve">ENBRAGEO ENGENHARIA LTDA </t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I136" s="1" t="inlineStr">
@@ -11641,10 +11649,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>46203.51057075232</v>
+        <v>46210.62739077547</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>46204</v>
+        <v>46211</v>
       </c>
       <c r="L136" s="1" t="inlineStr">
         <is>
@@ -11653,22 +11661,24 @@
       </c>
       <c r="M136" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N136" s="1" t="n"/>
-      <c r="O136" s="1" t="n"/>
+      <c r="O136" s="2" t="n">
+        <v>46219</v>
+      </c>
       <c r="P136" s="2" t="n">
-        <v>46206.71474591435</v>
+        <v>46219.5832929051</v>
       </c>
       <c r="Q136" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="R136" s="1" t="inlineStr">
         <is>
-          <t>Empresa simples nacional, porem inicio de responsabilidade mg 01/01/2025 , pendencia ref 12/2024</t>
+          <t>Em anexo</t>
         </is>
       </c>
       <c r="S136" s="1" t="inlineStr">
@@ -11679,109 +11689,99 @@
       <c r="T136" s="1" t="n"/>
       <c r="U136" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>80797</v>
+        <v>81043</v>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, poderia me encaminhar o balanço e DRE 2025.</t>
+          <t>O cliente está solicitando a antecipação da ECF para o envio ao banco.</t>
         </is>
       </c>
       <c r="F137" s="1" t="n">
-        <v>5983</v>
+        <v>5985</v>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENBRAGEO ENGENHARIA LTDA </t>
+          <t>COMERCIAL TOP DOCES LTDA</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="I137" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>46210.62739077547</v>
+        <v>46217.71009487269</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="L137" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M137" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="N137" s="1" t="n"/>
       <c r="O137" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="P137" s="2" t="n">
-        <v>46219.5832929051</v>
-      </c>
-      <c r="Q137" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="P137" s="1" t="n"/>
+      <c r="Q137" s="1" t="inlineStr"/>
       <c r="R137" s="1" t="inlineStr">
         <is>
-          <t>Em anexo</t>
+          <t>ECF transmitida.</t>
         </is>
       </c>
       <c r="S137" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T137" s="1" t="n"/>
-      <c r="U137" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="U137" s="1" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>81043</v>
+        <v>80003</v>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -11791,80 +11791,81 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t>O cliente está solicitando a antecipação da ECF para o envio ao banco.</t>
+          <t>Favor regularizar transporte de saldo credor incorreto GIA/EFD 06/2025, 07/2025, 03/2026 e 04/2026.GIA/EFD não apresentada período 12/2024</t>
         </is>
       </c>
       <c r="F138" s="1" t="n">
-        <v>5985</v>
+        <v>6010</v>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t>COMERCIAL TOP DOCES LTDA</t>
+          <t>OBA OBA MIX LTDA</t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t>Lucas Fischer</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I138" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>46217.71009487269</v>
+        <v>46188.44638746528</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>46218</v>
+        <v>46203</v>
       </c>
       <c r="L138" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M138" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N138" s="1" t="n"/>
-      <c r="O138" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="P138" s="2" t="n">
-        <v>46218.42829212963</v>
-      </c>
-      <c r="Q138" s="1" t="inlineStr">
-        <is>
-          <t>Lucas Fischer</t>
-        </is>
-      </c>
+      <c r="O138" s="1" t="n"/>
+      <c r="P138" s="1" t="n"/>
+      <c r="Q138" s="1" t="inlineStr"/>
       <c r="R138" s="1" t="inlineStr">
         <is>
-          <t>ECF transmitida.</t>
+          <t>operação em fase de execução, 
+prazo 23/06</t>
         </is>
       </c>
       <c r="S138" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T138" s="1" t="n"/>
-      <c r="U138" s="1" t="inlineStr"/>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T138" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
+      <c r="U138" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>80003</v>
+        <v>80004</v>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -11874,7 +11875,7 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t>Favor regularizar transporte de saldo credor incorreto GIA/EFD 06/2025, 07/2025, 03/2026 e 04/2026.GIA/EFD não apresentada período 12/2024</t>
+          <t>Favor verificar omissão de DCTFweb 12/2025 (Ausência de entrega de DCTFWeb original ou de retificadora em andamento)</t>
         </is>
       </c>
       <c r="F139" s="1" t="n">
@@ -11887,23 +11888,23 @@
       </c>
       <c r="H139" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I139" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>46188.44638746528</v>
+        <v>46188.4483466088</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>46203</v>
+        <v>46199</v>
       </c>
       <c r="L139" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M139" s="1" t="inlineStr">
@@ -11913,42 +11914,43 @@
       </c>
       <c r="N139" s="1" t="n"/>
       <c r="O139" s="1" t="n"/>
-      <c r="P139" s="1" t="n"/>
-      <c r="Q139" s="1" t="inlineStr"/>
+      <c r="P139" s="2" t="n">
+        <v>46189.61642210648</v>
+      </c>
+      <c r="Q139" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="R139" s="1" t="inlineStr">
         <is>
-          <t>operação em fase de execução, 
-prazo 23/06</t>
+          <t>Declaração retificadas</t>
         </is>
       </c>
       <c r="S139" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T139" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T139" s="1" t="n"/>
       <c r="U139" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>80004</v>
+        <v>80138</v>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D140" s="1" t="inlineStr">
@@ -11958,7 +11960,7 @@
       </c>
       <c r="E140" s="1" t="inlineStr">
         <is>
-          <t>Favor verificar omissão de DCTFweb 12/2025 (Ausência de entrega de DCTFWeb original ou de retificadora em andamento)</t>
+          <t>Conforme autoregularização anexo, foram encontradas diferenças entre os valores de ICMS destacados nos documentos fiscais e o valores declarados na GIA/EFD no período de 03/2025 a 12/2025.</t>
         </is>
       </c>
       <c r="F140" s="1" t="n">
@@ -11971,23 +11973,23 @@
       </c>
       <c r="H140" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I140" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>46188.4483466088</v>
+        <v>46190.48124814815</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="L140" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M140" s="1" t="inlineStr">
@@ -11997,43 +11999,37 @@
       </c>
       <c r="N140" s="1" t="n"/>
       <c r="O140" s="1" t="n"/>
-      <c r="P140" s="2" t="n">
-        <v>46189.61642210648</v>
-      </c>
-      <c r="Q140" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="P140" s="1" t="n"/>
+      <c r="Q140" s="1" t="inlineStr"/>
       <c r="R140" s="1" t="inlineStr">
         <is>
-          <t>Declaração retificadas</t>
+          <t>Em atendimento, estou verificando o que aconteceu na GIA x EFD, prazo de retorno até dia 24/06/2026</t>
         </is>
       </c>
       <c r="S140" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T140" s="1" t="n"/>
       <c r="U140" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>80138</v>
+        <v>79620</v>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -12043,67 +12039,73 @@
       </c>
       <c r="E141" s="1" t="inlineStr">
         <is>
-          <t>Conforme autoregularização anexo, foram encontradas diferenças entre os valores de ICMS destacados nos documentos fiscais e o valores declarados na GIA/EFD no período de 03/2025 a 12/2025.</t>
+          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
         </is>
       </c>
       <c r="F141" s="1" t="n">
-        <v>6010</v>
+        <v>6018</v>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t>OBA OBA MIX LTDA</t>
+          <t xml:space="preserve">MENOR PRECO BRASIL DIGITAL LTDA </t>
         </is>
       </c>
       <c r="H141" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I141" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>46190.48124814815</v>
+        <v>46175.58723063657</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>46203</v>
+        <v>46176</v>
       </c>
       <c r="L141" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M141" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N141" s="1" t="n"/>
       <c r="O141" s="1" t="n"/>
-      <c r="P141" s="1" t="n"/>
-      <c r="Q141" s="1" t="inlineStr"/>
+      <c r="P141" s="2" t="n">
+        <v>46197.37187415509</v>
+      </c>
+      <c r="Q141" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="R141" s="1" t="inlineStr">
         <is>
-          <t>Em atendimento, estou verificando o que aconteceu na GIA x EFD, prazo de retorno até dia 24/06/2026</t>
+          <t>enviado por email 05/06</t>
         </is>
       </c>
       <c r="S141" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T141" s="1" t="n"/>
       <c r="U141" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>79620</v>
+        <v>79621</v>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
@@ -12126,11 +12128,11 @@
         </is>
       </c>
       <c r="F142" s="1" t="n">
-        <v>6018</v>
+        <v>6019</v>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MENOR PRECO BRASIL DIGITAL LTDA </t>
+          <t>FELIPE CIUFFA LIMA LTDA</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
@@ -12144,7 +12146,7 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>46175.58723063657</v>
+        <v>46175.58796859954</v>
       </c>
       <c r="K142" s="2" t="n">
         <v>46176</v>
@@ -12162,16 +12164,16 @@
       <c r="N142" s="1" t="n"/>
       <c r="O142" s="1" t="n"/>
       <c r="P142" s="2" t="n">
-        <v>46197.37187415509</v>
+        <v>46205.58014232639</v>
       </c>
       <c r="Q142" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Renata Cavalheiro</t>
         </is>
       </c>
       <c r="R142" s="1" t="inlineStr">
         <is>
-          <t>enviado por email 05/06</t>
+          <t>Chamado duplicado.</t>
         </is>
       </c>
       <c r="S142" s="1" t="inlineStr">
@@ -12188,39 +12190,39 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>79621</v>
+        <v>80218</v>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Balanço, Balancete e DRE com posição em 31/12/2025, após a implantação dos saldos encaminhados pelo master José Carlos. Solicitamos também o Balanço, Balancete e DRE com posição de 01/01/2026 a 28/02/2026, para que possamos encaminhar a documentação ao atual contador. (solicitação foi realizada em 06/05/2026, às 11h23)</t>
+          <t>Boa tarde! Por gentileza, poderia encaminhar os informes de rendimento de todos os sócios do grupo Fomtoura e Linhares?</t>
         </is>
       </c>
       <c r="F143" s="1" t="n">
-        <v>6019</v>
+        <v>6066</v>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t>FELIPE CIUFFA LIMA LTDA</t>
+          <t xml:space="preserve">LINHARES E FONTOURA CONSTRUCAO CIVIL LTDA </t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I143" s="1" t="inlineStr">
@@ -12229,10 +12231,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>46175.58796859954</v>
+        <v>46191.67221045139</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>46176</v>
+        <v>46192</v>
       </c>
       <c r="L143" s="1" t="inlineStr">
         <is>
@@ -12241,22 +12243,22 @@
       </c>
       <c r="M143" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N143" s="1" t="n"/>
       <c r="O143" s="1" t="n"/>
       <c r="P143" s="2" t="n">
-        <v>46205.58014232639</v>
+        <v>46192.57801774306</v>
       </c>
       <c r="Q143" s="1" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="R143" s="1" t="inlineStr">
         <is>
-          <t>Chamado duplicado.</t>
+          <t>Informe solicitado é do período anterior a nossa responsabilidade, Tatiana já conversou com André que pediu para aguardar aprovação para enviar.</t>
         </is>
       </c>
       <c r="S143" s="1" t="inlineStr">
@@ -12267,32 +12269,32 @@
       <c r="T143" s="1" t="n"/>
       <c r="U143" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>80218</v>
+        <v>80954</v>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pesquisa IBGE</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pesquisa IBGE</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, poderia encaminhar os informes de rendimento de todos os sócios do grupo Fomtoura e Linhares?</t>
+          <t>Bom dia, por gentileza responder Pesquisa Anual da Indústria da Construção - PAIC 2025</t>
         </is>
       </c>
       <c r="F144" s="1" t="n">
@@ -12314,39 +12316,31 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>46191.67221045139</v>
+        <v>46215.3711772338</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>46192</v>
+        <v>46217</v>
       </c>
       <c r="L144" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M144" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N144" s="1" t="n"/>
-      <c r="O144" s="1" t="n"/>
-      <c r="P144" s="2" t="n">
-        <v>46192.57801774306</v>
-      </c>
-      <c r="Q144" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
-      <c r="R144" s="1" t="inlineStr">
-        <is>
-          <t>Informe solicitado é do período anterior a nossa responsabilidade, Tatiana já conversou com André que pediu para aguardar aprovação para enviar.</t>
-        </is>
-      </c>
+      <c r="O144" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="P144" s="1" t="n"/>
+      <c r="Q144" s="1" t="inlineStr"/>
+      <c r="R144" s="1" t="inlineStr"/>
       <c r="S144" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T144" s="1" t="n"/>
@@ -12358,16 +12352,16 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>80954</v>
+        <v>80929</v>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>Pesquisa IBGE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t>Pesquisa IBGE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -12377,50 +12371,54 @@
       </c>
       <c r="E145" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza responder Pesquisa Anual da Indústria da Construção - PAIC 2025</t>
+          <t>Por gentileza, disponibilizar recibo de entrega e declaração completa da ultima DMED.</t>
         </is>
       </c>
       <c r="F145" s="1" t="n">
-        <v>6066</v>
+        <v>6094</v>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINHARES E FONTOURA CONSTRUCAO CIVIL LTDA </t>
+          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
         </is>
       </c>
       <c r="H145" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I145" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>46215.3711772338</v>
+        <v>46211.75253086806</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>46217</v>
+        <v>46213</v>
       </c>
       <c r="L145" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M145" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N145" s="1" t="n"/>
-      <c r="O145" s="2" t="n">
-        <v>46220</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="n">
+        <v>46216.37496550926</v>
+      </c>
+      <c r="O145" s="1" t="n"/>
       <c r="P145" s="1" t="n"/>
       <c r="Q145" s="1" t="inlineStr"/>
-      <c r="R145" s="1" t="inlineStr"/>
+      <c r="R145" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM EXECUÇÃO PELA OPERAÇÃO </t>
+        </is>
+      </c>
       <c r="S145" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -12429,22 +12427,22 @@
       <c r="T145" s="1" t="n"/>
       <c r="U145" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>80929</v>
+        <v>80136</v>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -12454,15 +12452,15 @@
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, disponibilizar recibo de entrega e declaração completa da ultima DMED.</t>
+          <t xml:space="preserve">Por gentileza verificar saldo credor incorreto. </t>
         </is>
       </c>
       <c r="F146" s="1" t="n">
-        <v>6094</v>
+        <v>6106</v>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
+          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
       <c r="H146" s="1" t="inlineStr">
@@ -12476,35 +12474,40 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>46211.75253086806</v>
+        <v>46190.46544413194</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>46213</v>
+        <v>46192</v>
       </c>
       <c r="L146" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M146" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N146" s="2" t="n">
-        <v>46216.37496550926</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N146" s="1" t="n"/>
       <c r="O146" s="1" t="n"/>
-      <c r="P146" s="1" t="n"/>
-      <c r="Q146" s="1" t="inlineStr"/>
+      <c r="P146" s="2" t="n">
+        <v>46203.39613290509</v>
+      </c>
+      <c r="Q146" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM EXECUÇÃO PELA OPERAÇÃO </t>
+          <t>BOM DIA, 
+PENDENCIA JA SENDO TRATADA NO CHAMDO 77015</t>
         </is>
       </c>
       <c r="S146" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T146" s="1" t="n"/>
@@ -12516,26 +12519,26 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>80136</v>
+        <v>80738</v>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza verificar saldo credor incorreto. </t>
+          <t>Bom dia! Por gentileza, verificar EFD substitutiva recusada ref. 02/2026 e 11/2025</t>
         </is>
       </c>
       <c r="F147" s="1" t="n">
@@ -12557,40 +12560,33 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>46190.46544413194</v>
+        <v>46209.37140378472</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>46192</v>
+        <v>46211</v>
       </c>
       <c r="L147" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M147" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N147" s="1" t="n"/>
       <c r="O147" s="1" t="n"/>
-      <c r="P147" s="2" t="n">
-        <v>46203.39613290509</v>
-      </c>
-      <c r="Q147" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+      <c r="P147" s="1" t="n"/>
+      <c r="Q147" s="1" t="inlineStr"/>
       <c r="R147" s="1" t="inlineStr">
         <is>
-          <t>BOM DIA, 
-PENDENCIA JA SENDO TRATADA NO CHAMDO 77015</t>
+          <t>PRCOESSO REALIZADO EM 10-07-2026</t>
         </is>
       </c>
       <c r="S147" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T147" s="1" t="n"/>
@@ -12602,7 +12598,7 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>80738</v>
+        <v>81036</v>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
@@ -12621,7 +12617,7 @@
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, verificar EFD substitutiva recusada ref. 02/2026 e 11/2025</t>
+          <t>Boa tarde! Por gentileza verificar o  EFD substitutiva recusada.</t>
         </is>
       </c>
       <c r="F148" s="1" t="n">
@@ -12632,65 +12628,53 @@
           <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
-      <c r="H148" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+      <c r="H148" s="1" t="n"/>
       <c r="I148" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>46209.37140378472</v>
+        <v>46217.62481033565</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>46211</v>
+        <v>46219</v>
       </c>
       <c r="L148" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M148" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N148" s="1" t="n"/>
       <c r="O148" s="1" t="n"/>
       <c r="P148" s="1" t="n"/>
       <c r="Q148" s="1" t="inlineStr"/>
-      <c r="R148" s="1" t="inlineStr">
-        <is>
-          <t>PRCOESSO REALIZADO EM 10-07-2026</t>
-        </is>
-      </c>
+      <c r="R148" s="1" t="n"/>
       <c r="S148" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T148" s="1" t="n"/>
-      <c r="U148" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U148" s="1" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>81036</v>
+        <v>80952</v>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>SPED</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>SPED</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
@@ -12700,64 +12684,72 @@
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza verificar o  EFD substitutiva recusada.</t>
+          <t>Boa tarde! Por gentileza, verificar o SPED contribuições referente a 12/2025</t>
         </is>
       </c>
       <c r="F149" s="1" t="n">
-        <v>6106</v>
+        <v>6117</v>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
-        </is>
-      </c>
-      <c r="H149" s="1" t="n"/>
+          <t xml:space="preserve">MAGAZINE DAS PANELAS LTDA </t>
+        </is>
+      </c>
+      <c r="H149" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I149" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>46217.62481033565</v>
+        <v>46213.67173417824</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>46219</v>
+        <v>46217</v>
       </c>
       <c r="L149" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M149" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N149" s="1" t="n"/>
       <c r="O149" s="1" t="n"/>
       <c r="P149" s="1" t="n"/>
       <c r="Q149" s="1" t="inlineStr"/>
-      <c r="R149" s="1" t="n"/>
+      <c r="R149" s="1" t="inlineStr"/>
       <c r="S149" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T149" s="1" t="n"/>
-      <c r="U149" s="1" t="inlineStr"/>
+      <c r="U149" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>80952</v>
+        <v>81037</v>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>SPED</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t>SPED</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
@@ -12767,219 +12759,231 @@
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, verificar o SPED contribuições referente a 12/2025</t>
+          <t>Boa tarde! Por gentileza verificar o EFD substitutiva recusada.</t>
         </is>
       </c>
       <c r="F150" s="1" t="n">
-        <v>6117</v>
+        <v>6120</v>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MAGAZINE DAS PANELAS LTDA </t>
-        </is>
-      </c>
-      <c r="H150" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+          <t>POWER FINANCIAL DO BRASIL S.A.</t>
+        </is>
+      </c>
+      <c r="H150" s="1" t="n"/>
       <c r="I150" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>46213.67173417824</v>
+        <v>46217.62920228009</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="L150" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M150" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Sofia Souza</t>
         </is>
       </c>
       <c r="N150" s="1" t="n"/>
       <c r="O150" s="1" t="n"/>
       <c r="P150" s="1" t="n"/>
       <c r="Q150" s="1" t="inlineStr"/>
-      <c r="R150" s="1" t="inlineStr"/>
+      <c r="R150" s="1" t="n"/>
       <c r="S150" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T150" s="1" t="n"/>
-      <c r="U150" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U150" s="1" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>81037</v>
+        <v>80616</v>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza verificar o EFD substitutiva recusada.</t>
+          <t>Segue questionamento realizado em Ata: Por favor, precisamos com urgência gerar e enviar para o cliente as guias de ISS retido de outros municípios. Cliente cobrando em aberto desde 04/2025. cliente pedindo reembolso de multa e juros. Foi feito de todos os meses?</t>
         </is>
       </c>
       <c r="F151" s="1" t="n">
-        <v>6120</v>
+        <v>6148</v>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t>POWER FINANCIAL DO BRASIL S.A.</t>
-        </is>
-      </c>
-      <c r="H151" s="1" t="n"/>
+          <t>VALE CONCRETO LTDA</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I151" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>46217.62920228009</v>
+        <v>46203.43626111111</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>46219</v>
+        <v>46205</v>
       </c>
       <c r="L151" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M151" s="1" t="inlineStr">
         <is>
-          <t>Sofia Souza</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N151" s="1" t="n"/>
       <c r="O151" s="1" t="n"/>
       <c r="P151" s="1" t="n"/>
       <c r="Q151" s="1" t="inlineStr"/>
-      <c r="R151" s="1" t="n"/>
+      <c r="R151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bom dia, 
+Em relação ao questionamento, não esta sendo enviado nada em atraso ao cliente. As guias estão sendo enviadas no prazo. </t>
+        </is>
+      </c>
       <c r="S151" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T151" s="1" t="n"/>
-      <c r="U151" s="1" t="inlineStr"/>
+      <c r="U151" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>80616</v>
+        <v>80787</v>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Documentação Contábil</t>
         </is>
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
         <is>
-          <t>Segue questionamento realizado em Ata: Por favor, precisamos com urgência gerar e enviar para o cliente as guias de ISS retido de outros municípios. Cliente cobrando em aberto desde 04/2025. cliente pedindo reembolso de multa e juros. Foi feito de todos os meses?</t>
+          <t xml:space="preserve">Bom dia! Por gentileza, encaminhar balanço e DRE 2026 das empresas RN e Muros Perimetral . </t>
         </is>
       </c>
       <c r="F152" s="1" t="n">
-        <v>6148</v>
+        <v>6152</v>
       </c>
       <c r="G152" s="1" t="inlineStr">
         <is>
-          <t>VALE CONCRETO LTDA</t>
+          <t>RN MUROS LTDA</t>
         </is>
       </c>
       <c r="H152" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I152" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>46203.43626111111</v>
+        <v>46210.49657619213</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>46205</v>
+        <v>46211</v>
       </c>
       <c r="L152" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M152" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N152" s="1" t="n"/>
-      <c r="O152" s="1" t="n"/>
-      <c r="P152" s="1" t="n"/>
-      <c r="Q152" s="1" t="inlineStr"/>
+      <c r="O152" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="P152" s="2" t="n">
+        <v>46219.59946519676</v>
+      </c>
+      <c r="Q152" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="R152" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">bom dia, 
-Em relação ao questionamento, não esta sendo enviado nada em atraso ao cliente. As guias estão sendo enviadas no prazo. </t>
+          <t>Anexo</t>
         </is>
       </c>
       <c r="S152" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T152" s="1" t="n"/>
       <c r="U152" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>80787</v>
+        <v>80070</v>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>Documentação Contábil</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D153" s="1" t="inlineStr">
@@ -12989,32 +12993,32 @@
       </c>
       <c r="E153" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia! Por gentileza, encaminhar balanço e DRE 2026 das empresas RN e Muros Perimetral . </t>
+          <t>Por gentileza, verificar a pendencia de débito.</t>
         </is>
       </c>
       <c r="F153" s="1" t="n">
-        <v>6152</v>
+        <v>6153</v>
       </c>
       <c r="G153" s="1" t="inlineStr">
         <is>
-          <t>RN MUROS LTDA</t>
+          <t>PERIMETRAL SERVICOS LTDA</t>
         </is>
       </c>
       <c r="H153" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>46210.49657619213</v>
+        <v>46188.73918179398</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>46211</v>
+        <v>46190</v>
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
@@ -13023,24 +13027,25 @@
       </c>
       <c r="M153" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N153" s="1" t="n"/>
-      <c r="O153" s="2" t="n">
-        <v>46220</v>
-      </c>
+          <t>Beatriz Rangel</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="n">
+        <v>46197.44562376157</v>
+      </c>
+      <c r="O153" s="1" t="n"/>
       <c r="P153" s="2" t="n">
-        <v>46219.59946519676</v>
+        <v>46204.729928125</v>
       </c>
       <c r="Q153" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R153" s="1" t="inlineStr">
         <is>
-          <t>Anexo</t>
+          <t xml:space="preserve">EM VALIDAÇÃO - PRAZO - 25--06
+</t>
         </is>
       </c>
       <c r="S153" s="1" t="inlineStr">
@@ -13051,101 +13056,88 @@
       <c r="T153" s="1" t="n"/>
       <c r="U153" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>80070</v>
+        <v>80764</v>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, verificar a pendencia de débito.</t>
+          <t>Bom dia, Departamento Fiscal.Segue notificação recebida referente ao cliente 6179 - Italo.Notificação de refere a Diferença de Valores entre GIA x SPED no período de 09/2024 a 12/2025. Total questionado de R$ 408.019,75Por favor verifiquem as divergências para que sejam feitas as devidas correções. Me mantenho a disposição.Chamado aberto para controle #80750Prazo máximo para atendimento de 01/09/2026.</t>
         </is>
       </c>
       <c r="F154" s="1" t="n">
-        <v>6153</v>
+        <v>6179</v>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t>PERIMETRAL SERVICOS LTDA</t>
+          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I154" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>46188.73918179398</v>
+        <v>46209.60344498842</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>46190</v>
+        <v>46237</v>
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M154" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N154" s="2" t="n">
-        <v>46197.44562376157</v>
-      </c>
+          <t>Daniel Oliveira</t>
+        </is>
+      </c>
+      <c r="N154" s="1" t="n"/>
       <c r="O154" s="1" t="n"/>
-      <c r="P154" s="2" t="n">
-        <v>46204.729928125</v>
-      </c>
-      <c r="Q154" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
-      <c r="R154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">EM VALIDAÇÃO - PRAZO - 25--06
-</t>
-        </is>
-      </c>
+      <c r="P154" s="1" t="n"/>
+      <c r="Q154" s="1" t="inlineStr"/>
+      <c r="R154" s="1" t="inlineStr"/>
       <c r="S154" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T154" s="1" t="n"/>
       <c r="U154" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>80764</v>
+        <v>80765</v>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
@@ -13164,15 +13156,15 @@
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, Departamento Fiscal.Segue notificação recebida referente ao cliente 6179 - Italo.Notificação de refere a Diferença de Valores entre GIA x SPED no período de 09/2024 a 12/2025. Total questionado de R$ 408.019,75Por favor verifiquem as divergências para que sejam feitas as devidas correções. Me mantenho a disposição.Chamado aberto para controle #80750Prazo máximo para atendimento de 01/09/2026.</t>
+          <t>Bom dia, Departamento Fiscal.Segue notificação recebida referente ao cliente 6180 - Balbinot.Notificação de refere a Diferença de Valores entre GIA x SPED no período de 05/2025 a 12/2025. Total questionado de R$ 166.730,10Por favor verifiquem as divergências para que sejam feitas as devidas correções. Me mantenho a disposição.Prazo máximo para atendimento de 01/09/2026.</t>
         </is>
       </c>
       <c r="F155" s="1" t="n">
-        <v>6179</v>
+        <v>6180</v>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t>ITALO BRASILEIRA AGRO COMERCIAL LTDA</t>
+          <t>DISTRIBUIDORA  AGRICOLA BALBINOT LTDA</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
@@ -13186,7 +13178,7 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>46209.60344498842</v>
+        <v>46209.60424221065</v>
       </c>
       <c r="K155" s="2" t="n">
         <v>46237</v>
@@ -13220,101 +13212,111 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>80765</v>
+        <v>79673</v>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, Departamento Fiscal.Segue notificação recebida referente ao cliente 6180 - Balbinot.Notificação de refere a Diferença de Valores entre GIA x SPED no período de 05/2025 a 12/2025. Total questionado de R$ 166.730,10Por favor verifiquem as divergências para que sejam feitas as devidas correções. Me mantenho a disposição.Prazo máximo para atendimento de 01/09/2026.</t>
+          <t>Por gentileza, verificar omissão de DCTFWeb 12/2025 e 03/2026.</t>
         </is>
       </c>
       <c r="F156" s="1" t="n">
-        <v>6180</v>
+        <v>6217</v>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA  AGRICOLA BALBINOT LTDA</t>
+          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I156" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>46209.60424221065</v>
+        <v>46176.61147271991</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>46237</v>
+        <v>46181</v>
       </c>
       <c r="L156" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M156" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N156" s="1" t="n"/>
       <c r="O156" s="1" t="n"/>
-      <c r="P156" s="1" t="n"/>
-      <c r="Q156" s="1" t="inlineStr"/>
-      <c r="R156" s="1" t="inlineStr"/>
+      <c r="P156" s="2" t="n">
+        <v>46178.65404637731</v>
+      </c>
+      <c r="Q156" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R156" s="1" t="inlineStr">
+        <is>
+          <t>Transmitido. Não houve alteração de valores</t>
+        </is>
+      </c>
       <c r="S156" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T156" s="1" t="n"/>
       <c r="U156" s="1" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>79673</v>
+        <v>79680</v>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, verificar omissão de DCTFWeb 12/2025 e 03/2026.</t>
+          <t xml:space="preserve">Cliente possui débitos em aberto com saldo devedor menor do que o valor original.  O saldo devedor remanescente é devido a retificações? Por gentileza realizar o levantamento, cliente esta precisando de uma CND e recebeu Painel de Conformidade. </t>
         </is>
       </c>
       <c r="F157" s="1" t="n">
@@ -13327,69 +13329,64 @@
       </c>
       <c r="H157" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I157" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>46176.61147271991</v>
+        <v>46176.65661782408</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>46181</v>
       </c>
       <c r="L157" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Devolvido</t>
         </is>
       </c>
       <c r="M157" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N157" s="1" t="n"/>
       <c r="O157" s="1" t="n"/>
-      <c r="P157" s="2" t="n">
-        <v>46178.65404637731</v>
-      </c>
-      <c r="Q157" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="P157" s="1" t="n"/>
+      <c r="Q157" s="1" t="inlineStr"/>
       <c r="R157" s="1" t="inlineStr">
         <is>
-          <t>Transmitido. Não houve alteração de valores</t>
+          <t>Em processo de analise
+Prazo de entrega até dia: 23/06</t>
         </is>
       </c>
       <c r="S157" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T157" s="1" t="n"/>
       <c r="U157" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>79680</v>
+        <v>80188</v>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Antecipação de ECF</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
@@ -13399,32 +13396,32 @@
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cliente possui débitos em aberto com saldo devedor menor do que o valor original.  O saldo devedor remanescente é devido a retificações? Por gentileza realizar o levantamento, cliente esta precisando de uma CND e recebeu Painel de Conformidade. </t>
+          <t>cliente solicita antecipação da ECF 2025.</t>
         </is>
       </c>
       <c r="F158" s="1" t="n">
-        <v>6217</v>
+        <v>6224</v>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>AQUAPROOF IMPERMEABILIZACAO E CONSTRUCAO LTDA</t>
+          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
         </is>
       </c>
       <c r="H158" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="I158" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>46176.65661782408</v>
+        <v>46191.46223873842</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="L158" s="1" t="inlineStr">
         <is>
@@ -13433,17 +13430,19 @@
       </c>
       <c r="M158" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N158" s="1" t="n"/>
-      <c r="O158" s="1" t="n"/>
+      <c r="O158" s="2" t="n">
+        <v>46217</v>
+      </c>
       <c r="P158" s="1" t="n"/>
       <c r="Q158" s="1" t="inlineStr"/>
       <c r="R158" s="1" t="inlineStr">
         <is>
-          <t>Em processo de analise
-Prazo de entrega até dia: 23/06</t>
+          <t>Bom dia, 
+por qual motivo o cliente precisa que antecipe a ECF, favor explicar que temos um prazo até 31/07/2026.</t>
         </is>
       </c>
       <c r="S158" s="1" t="inlineStr">
@@ -13452,24 +13451,20 @@
         </is>
       </c>
       <c r="T158" s="1" t="n"/>
-      <c r="U158" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U158" s="1" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>80188</v>
+        <v>80123</v>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
         <is>
-          <t>Antecipação de ECF</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D159" s="1" t="inlineStr">
@@ -13479,75 +13474,83 @@
       </c>
       <c r="E159" s="1" t="inlineStr">
         <is>
-          <t>cliente solicita antecipação da ECF 2025.</t>
+          <t>Por gentileza verificar se o valor de R$ 20,07 é realmente devido, se sim por gentileza recalcular a guia para que possamos encaminhar ao cliente</t>
         </is>
       </c>
       <c r="F159" s="1" t="n">
-        <v>6224</v>
+        <v>6287</v>
       </c>
       <c r="G159" s="1" t="inlineStr">
         <is>
-          <t>VIEIRA E REZENDE TEND TUDO LTDA</t>
+          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H159" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I159" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>46191.46223873842</v>
+        <v>46190.38330320602</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="L159" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M159" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N159" s="1" t="n"/>
-      <c r="O159" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="P159" s="1" t="n"/>
-      <c r="Q159" s="1" t="inlineStr"/>
+      <c r="O159" s="1" t="n"/>
+      <c r="P159" s="2" t="n">
+        <v>46204.72650277778</v>
+      </c>
+      <c r="Q159" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R159" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, 
-por qual motivo o cliente precisa que antecipe a ECF, favor explicar que temos um prazo até 31/07/2026.</t>
+          <t xml:space="preserve">O cliente não esta recolhendo o difal no Estado de SP na emissão da NFe. enviamos os debitos que consta no sefaz de SP .
+aguardando cliente autorizar a emissão da guia. </t>
         </is>
       </c>
       <c r="S159" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T159" s="1" t="n"/>
-      <c r="U159" s="1" t="inlineStr"/>
+      <c r="U159" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>80123</v>
+        <v>79917</v>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
@@ -13557,29 +13560,29 @@
       </c>
       <c r="E160" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar se o valor de R$ 20,07 é realmente devido, se sim por gentileza recalcular a guia para que possamos encaminhar ao cliente</t>
+          <t xml:space="preserve">Verificar Não apresentou GIA/EFD ref. 02/2025, 03/2025, 04/2025 e 05/2025 </t>
         </is>
       </c>
       <c r="F160" s="1" t="n">
-        <v>6287</v>
+        <v>6337</v>
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (MATRIZ)</t>
+          <t>SUPERMERCADO QUEIROZ LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H160" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="I160" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>46190.38330320602</v>
+        <v>46184.59184070602</v>
       </c>
       <c r="K160" s="2" t="n">
         <v>46192</v>
@@ -13591,23 +13594,24 @@
       </c>
       <c r="M160" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N160" s="1" t="n"/>
       <c r="O160" s="1" t="n"/>
       <c r="P160" s="2" t="n">
-        <v>46204.72650277778</v>
+        <v>46210.538125</v>
       </c>
       <c r="Q160" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="R160" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">O cliente não esta recolhendo o difal no Estado de SP na emissão da NFe. enviamos os debitos que consta no sefaz de SP .
-aguardando cliente autorizar a emissão da guia. </t>
+          <t>Boa tarde!
+Até o momento, não tivemos retorno do gerente sobre a tratativa referente a esse cliente.
+Segue, em anexo, o e-mail com os questionamentos levantados à época.</t>
         </is>
       </c>
       <c r="S160" s="1" t="inlineStr">
@@ -13618,13 +13622,13 @@
       <c r="T160" s="1" t="n"/>
       <c r="U160" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>79917</v>
+        <v>79918</v>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
@@ -13643,15 +13647,15 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verificar Não apresentou GIA/EFD ref. 02/2025, 03/2025, 04/2025 e 05/2025 </t>
+          <t>Verificar Não apresentou GIA/EFD ref. 04/2025 e 05/2025</t>
         </is>
       </c>
       <c r="F161" s="1" t="n">
-        <v>6337</v>
+        <v>6338</v>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO QUEIROZ LTDA (FILIAL 1)</t>
+          <t>SUPERMERCADO QUEIROZ LTDA (FILIAL2)</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
@@ -13665,7 +13669,7 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>46184.59184070602</v>
+        <v>46184.59223240741</v>
       </c>
       <c r="K161" s="2" t="n">
         <v>46192</v>
@@ -13683,7 +13687,7 @@
       <c r="N161" s="1" t="n"/>
       <c r="O161" s="1" t="n"/>
       <c r="P161" s="2" t="n">
-        <v>46210.538125</v>
+        <v>46210.53817569445</v>
       </c>
       <c r="Q161" s="1" t="inlineStr">
         <is>
@@ -13711,16 +13715,16 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>79918</v>
+        <v>80771</v>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -13730,32 +13734,32 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t>Verificar Não apresentou GIA/EFD ref. 04/2025 e 05/2025</t>
+          <t>6352 - NOVAIS ITCorrigir capital social da empresa, última alteração em anexo, valor 300 mil totalmente integralizados.Att. Vander</t>
         </is>
       </c>
       <c r="F162" s="1" t="n">
-        <v>6338</v>
+        <v>6352</v>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO QUEIROZ LTDA (FILIAL2)</t>
+          <t>NOVAIS IT SOLUCOES TECNOLOGICAS LTDA</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="I162" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>46184.59223240741</v>
+        <v>46209.70276883102</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>46192</v>
+        <v>46210</v>
       </c>
       <c r="L162" s="1" t="inlineStr">
         <is>
@@ -13764,24 +13768,24 @@
       </c>
       <c r="M162" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N162" s="1" t="n"/>
-      <c r="O162" s="1" t="n"/>
+      <c r="O162" s="2" t="n">
+        <v>46217</v>
+      </c>
       <c r="P162" s="2" t="n">
-        <v>46210.53817569445</v>
+        <v>46219.57626284722</v>
       </c>
       <c r="Q162" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="R162" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-Até o momento, não tivemos retorno do gerente sobre a tratativa referente a esse cliente.
-Segue, em anexo, o e-mail com os questionamentos levantados à época.</t>
+          <t>Já foi ajustado conforme solicitado anteriormente na Analise Balanço</t>
         </is>
       </c>
       <c r="S162" s="1" t="inlineStr">
@@ -13792,160 +13796,156 @@
       <c r="T162" s="1" t="n"/>
       <c r="U162" s="1" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Erika Santana</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>80771</v>
+        <v>81009</v>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D163" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E163" s="1" t="inlineStr">
         <is>
-          <t>6352 - NOVAIS ITCorrigir capital social da empresa, última alteração em anexo, valor 300 mil totalmente integralizados.Att. Vander</t>
+          <t>Estoque - Cobrar do cliente envio mensal do estoque, via cobrança automática!</t>
         </is>
       </c>
       <c r="F163" s="1" t="n">
-        <v>6352</v>
+        <v>6399</v>
       </c>
       <c r="G163" s="1" t="inlineStr">
         <is>
-          <t>NOVAIS IT SOLUCOES TECNOLOGICAS LTDA</t>
+          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
         </is>
       </c>
       <c r="H163" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I163" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>46209.70276883102</v>
+        <v>46217.38787060185</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="L163" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M163" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="N163" s="1" t="n"/>
-      <c r="O163" s="2" t="n">
-        <v>46217</v>
-      </c>
-      <c r="P163" s="2" t="n">
-        <v>46219.57626284722</v>
-      </c>
-      <c r="Q163" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
-      <c r="R163" s="1" t="inlineStr">
-        <is>
-          <t>Já foi ajustado conforme solicitado anteriormente na Analise Balanço</t>
-        </is>
-      </c>
+      <c r="O163" s="1" t="n"/>
+      <c r="P163" s="1" t="n"/>
+      <c r="Q163" s="1" t="inlineStr"/>
+      <c r="R163" s="1" t="inlineStr"/>
       <c r="S163" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T163" s="1" t="n"/>
       <c r="U163" s="1" t="inlineStr">
         <is>
-          <t>Erika Santana</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>81009</v>
+        <v>80635</v>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t>Estoque - Cobrar do cliente envio mensal do estoque, via cobrança automática!</t>
+          <t>CONCEITO - CONCILIAÇÃO EMPRESTIMO ENTRE O GRUPO Preciso que concilie os valores lançados na ESTRUTURA 6439, na CONCEITO 6427 E CZLOC 6438Att.Vander</t>
         </is>
       </c>
       <c r="F164" s="1" t="n">
-        <v>6399</v>
+        <v>6427</v>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
+          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H164" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I164" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>46217.38787060185</v>
+        <v>46203.57973564815</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>46223</v>
+        <v>46204</v>
       </c>
       <c r="L164" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M164" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
-        </is>
-      </c>
-      <c r="N164" s="1" t="n"/>
-      <c r="O164" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="n">
+        <v>46205.39969475695</v>
+      </c>
+      <c r="O164" s="2" t="n">
+        <v>46220</v>
+      </c>
       <c r="P164" s="1" t="n"/>
       <c r="Q164" s="1" t="inlineStr"/>
-      <c r="R164" s="1" t="inlineStr"/>
+      <c r="R164" s="1" t="inlineStr">
+        <is>
+          <t>Vai ser conciliado junto ao fechamento 06/2026</t>
+        </is>
+      </c>
       <c r="S164" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -13954,22 +13954,22 @@
       <c r="T164" s="1" t="n"/>
       <c r="U164" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>80635</v>
+        <v>81029</v>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
@@ -13979,7 +13979,7 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO - CONCILIAÇÃO EMPRESTIMO ENTRE O GRUPO Preciso que concilie os valores lançados na ESTRUTURA 6439, na CONCEITO 6427 E CZLOC 6438Att.Vander</t>
+          <t>CONCEITO 6427 - COMPENSAÇÃO DE DEBITO DE ICMS COM O CRÉDITO ACUMULADO DA MATRIZPreciso que zero o saldo devedor de ICMS da filial com o saldo credor da MATRIZAtt.Vander</t>
         </is>
       </c>
       <c r="F165" s="1" t="n">
@@ -13990,25 +13990,21 @@
           <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H165" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="H165" s="1" t="n"/>
       <c r="I165" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>46203.57973564815</v>
+        <v>46217.49787554398</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="L165" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M165" s="1" t="inlineStr">
@@ -14016,43 +14012,31 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
-        <v>46205.39969475695</v>
-      </c>
-      <c r="O165" s="2" t="n">
-        <v>46220</v>
-      </c>
+      <c r="N165" s="1" t="n"/>
+      <c r="O165" s="1" t="n"/>
       <c r="P165" s="1" t="n"/>
       <c r="Q165" s="1" t="inlineStr"/>
-      <c r="R165" s="1" t="inlineStr">
-        <is>
-          <t>Vai ser conciliado junto ao fechamento 06/2026</t>
-        </is>
-      </c>
+      <c r="R165" s="1" t="n"/>
       <c r="S165" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T165" s="1" t="n"/>
-      <c r="U165" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="U165" s="1" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>81029</v>
+        <v>81157</v>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D166" s="1" t="inlineStr">
@@ -14062,7 +14046,7 @@
       </c>
       <c r="E166" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO 6427 - COMPENSAÇÃO DE DEBITO DE ICMS COM O CRÉDITO ACUMULADO DA MATRIZPreciso que zero o saldo devedor de ICMS da filial com o saldo credor da MATRIZAtt.Vander</t>
+          <t>CONCEITO - BALANCETES DE IMPLANTAÇÃO - 01 A 08 DE 2025Solicitação do Master, para inclusão de balanço de implantação com urgência. Depois disponibilizar balanço e DRE 2025.Solicitação de conclusão até amanhã 17/07/2026.Att.Vander</t>
         </is>
       </c>
       <c r="F166" s="1" t="n">
@@ -14076,14 +14060,14 @@
       <c r="H166" s="1" t="n"/>
       <c r="I166" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>46217.49787554398</v>
+        <v>46219.63261427083</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="L166" s="1" t="inlineStr">
         <is>
@@ -14110,16 +14094,16 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>81157</v>
+        <v>81030</v>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D167" s="1" t="inlineStr">
@@ -14129,28 +14113,28 @@
       </c>
       <c r="E167" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO - BALANCETES DE IMPLANTAÇÃO - 01 A 08 DE 2025Solicitação do Master, para inclusão de balanço de implantação com urgência. Depois disponibilizar balanço e DRE 2025.Solicitação de conclusão até amanhã 17/07/2026.Att.Vander</t>
+          <t>6438 - CZLOC - PIS E COFINS 02/2026Corrigir divergência de valores entre o SPED CONTRIBUIÇÃO e valor devido na RFB hoje. Atualizar e enviar boletos com vencimento para 31/07/2026Att.Vander</t>
         </is>
       </c>
       <c r="F167" s="1" t="n">
-        <v>6427</v>
+        <v>6438</v>
       </c>
       <c r="G167" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
+          <t>CZLOC LOCACAO DE EQUIPAMENTOS PARA CONSTRUCAO CIVIL LTDA</t>
         </is>
       </c>
       <c r="H167" s="1" t="n"/>
       <c r="I167" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>46219.63261427083</v>
+        <v>46217.51475706018</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="L167" s="1" t="inlineStr">
         <is>
@@ -14177,16 +14161,16 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>81030</v>
+        <v>80641</v>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
@@ -14196,32 +14180,36 @@
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t>6438 - CZLOC - PIS E COFINS 02/2026Corrigir divergência de valores entre o SPED CONTRIBUIÇÃO e valor devido na RFB hoje. Atualizar e enviar boletos com vencimento para 31/07/2026Att.Vander</t>
+          <t>6439 - CONCEITO ESTRUTURA - CONTA EMPRESTIMO ENTRE EMPRESAS NO ATIVOPreciso que avalie novamente se os terceiros lançados nesta conta estão corretos, os terceiros que permanecer quero saber o motivo. Conta: 921181 01.2.1.10.001  Empréstimo entre EmpresasAtt.Vander</t>
         </is>
       </c>
       <c r="F168" s="1" t="n">
-        <v>6438</v>
+        <v>6439</v>
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t>CZLOC LOCACAO DE EQUIPAMENTOS PARA CONSTRUCAO CIVIL LTDA</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="n"/>
+          <t>CONCEITO ESTRUTURA LOCADORA LTDA</t>
+        </is>
+      </c>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>46217.51475706018</v>
+        <v>46203.60078723379</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M168" s="1" t="inlineStr">
@@ -14229,105 +14217,115 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N168" s="1" t="n"/>
-      <c r="O168" s="1" t="n"/>
+      <c r="N168" s="2" t="n">
+        <v>46216.75252230324</v>
+      </c>
+      <c r="O168" s="2" t="n">
+        <v>46218</v>
+      </c>
       <c r="P168" s="1" t="n"/>
       <c r="Q168" s="1" t="inlineStr"/>
-      <c r="R168" s="1" t="n"/>
+      <c r="R168" s="1" t="inlineStr">
+        <is>
+          <t>Vai ser feito no fechamento</t>
+        </is>
+      </c>
       <c r="S168" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T168" s="1" t="n"/>
-      <c r="U168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>80641</v>
+        <v>79681</v>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t>6439 - CONCEITO ESTRUTURA - CONTA EMPRESTIMO ENTRE EMPRESAS NO ATIVOPreciso que avalie novamente se os terceiros lançados nesta conta estão corretos, os terceiros que permanecer quero saber o motivo. Conta: 921181 01.2.1.10.001  Empréstimo entre EmpresasAtt.Vander</t>
+          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2025/2026 até abril</t>
         </is>
       </c>
       <c r="F169" s="1" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO ESTRUTURA LOCADORA LTDA</t>
+          <t>INFINITY UTILIDADES LTDA</t>
         </is>
       </c>
       <c r="H169" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Renata Cavalheiro</t>
         </is>
       </c>
       <c r="I169" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>46203.60078723379</v>
+        <v>46176.66350790509</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>46204</v>
+        <v>46178</v>
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M169" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="n">
-        <v>46216.75252230324</v>
-      </c>
-      <c r="O169" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="P169" s="1" t="n"/>
-      <c r="Q169" s="1" t="inlineStr"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N169" s="1" t="n"/>
+      <c r="O169" s="1" t="n"/>
+      <c r="P169" s="2" t="n">
+        <v>46182.75284528935</v>
+      </c>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
-          <t>Vai ser feito no fechamento</t>
+          <t>Enviado por e-mail em 08/06.</t>
         </is>
       </c>
       <c r="S169" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T169" s="1" t="n"/>
-      <c r="U169" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="U169" s="1" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>79681</v>
+        <v>79744</v>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
@@ -14346,7 +14344,7 @@
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2025/2026 até abril</t>
+          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2023/2024</t>
         </is>
       </c>
       <c r="F170" s="1" t="n">
@@ -14359,7 +14357,7 @@
       </c>
       <c r="H170" s="1" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
+          <t>ryang</t>
         </is>
       </c>
       <c r="I170" s="1" t="inlineStr">
@@ -14368,10 +14366,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>46176.66350790509</v>
+        <v>46181.41362399305</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="L170" s="1" t="inlineStr">
         <is>
@@ -14386,16 +14384,13 @@
       <c r="N170" s="1" t="n"/>
       <c r="O170" s="1" t="n"/>
       <c r="P170" s="2" t="n">
-        <v>46182.75284528935</v>
-      </c>
-      <c r="Q170" s="1" t="inlineStr">
-        <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
+        <v>46181.47254537037</v>
+      </c>
+      <c r="Q170" s="1" t="n"/>
       <c r="R170" s="1" t="inlineStr">
         <is>
-          <t>Enviado por e-mail em 08/06.</t>
+          <t>Boa tarde!
+A loja 6440 Infinity não estava na MG nessa época.</t>
         </is>
       </c>
       <c r="S170" s="1" t="inlineStr">
@@ -14408,16 +14403,16 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>79744</v>
+        <v>81168</v>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
@@ -14427,58 +14422,47 @@
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2023/2024</t>
+          <t>Boa tarde! Por gentileza, verificar saldo credor incorreto. Cliente precisa de uma CND.</t>
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>6440</v>
+        <v>6443</v>
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t>INFINITY UTILIDADES LTDA</t>
-        </is>
-      </c>
-      <c r="H171" s="1" t="inlineStr">
-        <is>
-          <t>ryang</t>
-        </is>
-      </c>
+          <t>INDUSTRIA E COMERCIO RAIZES DO NORDESTE LTDA</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="n"/>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46181.41362399305</v>
+        <v>46219.77042769676</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>46182</v>
+        <v>46223</v>
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N171" s="1" t="n"/>
       <c r="O171" s="1" t="n"/>
-      <c r="P171" s="2" t="n">
-        <v>46181.47254537037</v>
-      </c>
-      <c r="Q171" s="1" t="n"/>
-      <c r="R171" s="1" t="inlineStr">
-        <is>
-          <t>Boa tarde!
-A loja 6440 Infinity não estava na MG nessa época.</t>
-        </is>
-      </c>
+      <c r="P171" s="1" t="n"/>
+      <c r="Q171" s="1" t="inlineStr"/>
+      <c r="R171" s="1" t="n"/>
       <c r="S171" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T171" s="1" t="n"/>
@@ -21110,63 +21094,59 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>77913</v>
+        <v>81171</v>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>Bom dia!Por favor, baixar tarefa FGTS parcelamento - VERIFICAÇÃO PARCELAMENTO FGTS, tarefa criada errada.</t>
         </is>
       </c>
       <c r="F262" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G262" s="1" t="n"/>
-      <c r="H262" s="1" t="inlineStr">
-        <is>
-          <t>Bianca Ribeiro</t>
-        </is>
-      </c>
+      <c r="H262" s="1" t="n"/>
       <c r="I262" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J262" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46220.38125339121</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>46097</v>
+        <v>46223</v>
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="N262" s="1" t="n"/>
       <c r="O262" s="1" t="n"/>
       <c r="P262" s="1" t="n"/>
       <c r="Q262" s="1" t="inlineStr"/>
-      <c r="R262" s="1" t="inlineStr"/>
+      <c r="R262" s="1" t="n"/>
       <c r="S262" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21177,63 +21157,59 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>79609</v>
+        <v>81172</v>
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Bom dia! Por gentileza, poderia realizar a baixa da terafa DEC 2 quinzena dos clientes abaixo?ISENTO3498	EMPLACA SERVIÇOS LTDA4327	ACCESS EVENTOS E VIAGENS LTDA5780	A Estancia Morro Grande Centro de R5873	FRRD ADMINISTRADORA DE IMOVEIS LTDA5906	A Estancia Morro Grande - Centro de5978	HLL LOCADORA DE GUINDASTES LTDA5979	AMATRUDA LOCADORA DE GUINDASTES E A6172	MEDICAL DISCOVERY TREINAMENTOS &amp; DE6173	CLINICA TONON DE DERMATOLOGISTA LTD6416	SINZATO ENTERTAINMENT LTDA6450	RDF VEICULOS LTDA6501	MD TREINAMENTOS E DESENVOLVIMENTO L6652	RAZEC EMPRESA DE APOIO ADMINISTRATI6766	MASTER IN THREADS CURSOS E EVENTOS6794	C.M.A EDUCACIONAL LTDA6796	COLÉGIO JOAQUIM MARIA MACHADO DE AS6798	LFJ TRANSPORTE LTDA6930	DOMENICO BIEMMI FRANCISCO LEITE6415	FABIO PEREIRA DA COSTAERRO DE BAIXA5084	REPUME REPUXAÇÃO E METALURGICA LTDA5292	EZEKY LTDA</t>
         </is>
       </c>
       <c r="F263" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G263" s="1" t="n"/>
-      <c r="H263" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+      <c r="H263" s="1" t="n"/>
       <c r="I263" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J263" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46220.38165829861</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>46205</v>
+        <v>46223</v>
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N263" s="1" t="n"/>
       <c r="O263" s="1" t="n"/>
       <c r="P263" s="1" t="n"/>
       <c r="Q263" s="1" t="inlineStr"/>
-      <c r="R263" s="1" t="inlineStr"/>
+      <c r="R263" s="1" t="n"/>
       <c r="S263" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21244,26 +21220,26 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>80515</v>
+        <v>77913</v>
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F264" s="1" t="n">
@@ -21272,7 +21248,7 @@
       <c r="G264" s="1" t="n"/>
       <c r="H264" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I264" s="1" t="inlineStr">
@@ -21281,32 +21257,26 @@
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>46226</v>
+        <v>46097</v>
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N264" s="2" t="n">
-        <v>46219.75157017361</v>
-      </c>
+          <t>Larissa Félix</t>
+        </is>
+      </c>
+      <c r="N264" s="1" t="n"/>
       <c r="O264" s="1" t="n"/>
       <c r="P264" s="1" t="n"/>
       <c r="Q264" s="1" t="inlineStr"/>
-      <c r="R264" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enviado para registro </t>
-        </is>
-      </c>
+      <c r="R264" s="1" t="inlineStr"/>
       <c r="S264" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21317,7 +21287,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>80697</v>
+        <v>79609</v>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
@@ -21326,7 +21296,7 @@
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D265" s="1" t="inlineStr">
@@ -21336,7 +21306,7 @@
       </c>
       <c r="E265" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F265" s="1" t="n">
@@ -21354,10 +21324,10 @@
         </is>
       </c>
       <c r="J265" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K265" s="2" t="n">
-        <v>46237</v>
+        <v>46205</v>
       </c>
       <c r="L265" s="1" t="inlineStr">
         <is>
@@ -21366,7 +21336,7 @@
       </c>
       <c r="M265" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N265" s="1" t="n"/>
@@ -21384,7 +21354,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>80714</v>
+        <v>80515</v>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
@@ -21393,7 +21363,7 @@
       </c>
       <c r="C266" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D266" s="1" t="inlineStr">
@@ -21403,7 +21373,7 @@
       </c>
       <c r="E266" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F266" s="1" t="n">
@@ -21412,7 +21382,7 @@
       <c r="G266" s="1" t="n"/>
       <c r="H266" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I266" s="1" t="inlineStr">
@@ -21421,14 +21391,14 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K266" s="2" t="n">
-        <v>46241</v>
+        <v>46226</v>
       </c>
       <c r="L266" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M266" s="1" t="inlineStr">
@@ -21436,11 +21406,17 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N266" s="1" t="n"/>
+      <c r="N266" s="2" t="n">
+        <v>46219.75157017361</v>
+      </c>
       <c r="O266" s="1" t="n"/>
       <c r="P266" s="1" t="n"/>
       <c r="Q266" s="1" t="inlineStr"/>
-      <c r="R266" s="1" t="inlineStr"/>
+      <c r="R266" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enviado para registro </t>
+        </is>
+      </c>
       <c r="S266" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21451,16 +21427,16 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>80919</v>
+        <v>80697</v>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D267" s="1" t="inlineStr">
@@ -21470,7 +21446,7 @@
       </c>
       <c r="E267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F267" s="1" t="n">
@@ -21488,10 +21464,10 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K267" s="2" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="L267" s="1" t="inlineStr">
         <is>
@@ -21518,7 +21494,7 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>80935</v>
+        <v>80714</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
@@ -21527,7 +21503,7 @@
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
@@ -21537,7 +21513,7 @@
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
@@ -21555,7 +21531,7 @@
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K268" s="2" t="n">
         <v>46241</v>
@@ -21585,16 +21561,16 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>80936</v>
+        <v>80919</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
@@ -21604,7 +21580,7 @@
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
@@ -21613,7 +21589,7 @@
       <c r="G269" s="1" t="n"/>
       <c r="H269" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I269" s="1" t="inlineStr">
@@ -21622,10 +21598,10 @@
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -21652,7 +21628,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>80951</v>
+        <v>80935</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
@@ -21671,7 +21647,7 @@
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
@@ -21680,7 +21656,7 @@
       <c r="G270" s="1" t="n"/>
       <c r="H270" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I270" s="1" t="inlineStr">
@@ -21689,14 +21665,14 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K270" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
@@ -21704,17 +21680,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N270" s="2" t="n">
-        <v>46219.74920023148</v>
-      </c>
+      <c r="N270" s="1" t="n"/>
       <c r="O270" s="1" t="n"/>
       <c r="P270" s="1" t="n"/>
       <c r="Q270" s="1" t="inlineStr"/>
-      <c r="R270" s="1" t="inlineStr">
-        <is>
-          <t>Minuta enviada ao cliente</t>
-        </is>
-      </c>
+      <c r="R270" s="1" t="inlineStr"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21725,26 +21695,26 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>80989</v>
+        <v>80936</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
@@ -21753,7 +21723,7 @@
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
@@ -21762,10 +21732,10 @@
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46217</v>
+        <v>46241</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -21774,7 +21744,7 @@
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
@@ -21792,39 +21762,35 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>79793</v>
+        <v>80951</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G272" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G272" s="1" t="n"/>
       <c r="H272" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I272" s="1" t="inlineStr">
@@ -21833,26 +21799,32 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46185</v>
+        <v>46241</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N272" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>46219.74920023148</v>
+      </c>
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="1" t="n"/>
       <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="inlineStr"/>
+      <c r="R272" s="1" t="inlineStr">
+        <is>
+          <t>Minuta enviada ao cliente</t>
+        </is>
+      </c>
       <c r="S272" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21863,16 +21835,16 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>81004</v>
+        <v>80989</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -21882,20 +21854,16 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
-        <v>6869</v>
-      </c>
-      <c r="G273" s="1" t="inlineStr">
-        <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G273" s="1" t="n"/>
       <c r="H273" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I273" s="1" t="inlineStr">
@@ -21904,10 +21872,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -21916,7 +21884,7 @@
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
@@ -21934,39 +21902,39 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>81005</v>
+        <v>79793</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
-        <v>6870</v>
+        <v>5655</v>
       </c>
       <c r="G274" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
+          <t>VANESSA DUARTE RODRIGUES</t>
         </is>
       </c>
       <c r="H274" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I274" s="1" t="inlineStr">
@@ -21975,10 +21943,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -21987,7 +21955,7 @@
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
@@ -22005,34 +21973,34 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>81091</v>
+        <v>81004</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
-        <v>6907</v>
+        <v>6869</v>
       </c>
       <c r="G275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
       <c r="H275" s="1" t="inlineStr">
@@ -22046,10 +22014,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46219.3374690162</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22058,7 +22026,7 @@
       </c>
       <c r="M275" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N275" s="1" t="n"/>
@@ -22076,7 +22044,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>81161</v>
+        <v>81005</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22090,37 +22058,37 @@
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="E276" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+        </is>
+      </c>
+      <c r="F276" s="1" t="n">
+        <v>6870</v>
+      </c>
+      <c r="G276" s="1" t="inlineStr">
+        <is>
+          <t>AC HOME PET RAÇÕES LTDA</t>
+        </is>
+      </c>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>Ronaldo Dias</t>
+        </is>
+      </c>
+      <c r="I276" s="1" t="inlineStr">
+        <is>
           <t>PARALEGAL</t>
         </is>
       </c>
-      <c r="E276" s="1" t="inlineStr">
-        <is>
-          <t>Sarah, boa tarde!Por gentileza incluir no MGC o número da Inscrição Municipal - Prefeitura de Embu das Artes.</t>
-        </is>
-      </c>
-      <c r="F276" s="1" t="n">
-        <v>6916</v>
-      </c>
-      <c r="G276" s="1" t="inlineStr">
-        <is>
-          <t>TAITI COMERCIO DE MATERIAIS PARA CONSTRUCAO LTDA (FILIAL 1)</t>
-        </is>
-      </c>
-      <c r="H276" s="1" t="inlineStr">
-        <is>
-          <t>Sarah Amaro</t>
-        </is>
-      </c>
-      <c r="I276" s="1" t="inlineStr">
-        <is>
-          <t>PARALEGAL</t>
-        </is>
-      </c>
       <c r="J276" s="2" t="n">
-        <v>46219.69548784722</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
@@ -22129,7 +22097,7 @@
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N276" s="1" t="n"/>
@@ -22147,34 +22115,34 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>79833</v>
+        <v>81091</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
-        <v>6125</v>
+        <v>6907</v>
       </c>
       <c r="G277" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
         </is>
       </c>
       <c r="H277" s="1" t="inlineStr">
@@ -22184,36 +22152,30 @@
       </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46219.3374690162</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46184</v>
+        <v>46223</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="N277" s="2" t="n">
-        <v>46219.71277496528</v>
-      </c>
+          <t>Denis Reis</t>
+        </is>
+      </c>
+      <c r="N277" s="1" t="n"/>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="inlineStr">
-        <is>
-          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
-        </is>
-      </c>
+      <c r="R277" s="1" t="inlineStr"/>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22224,7 +22186,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>79834</v>
+        <v>79833</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
@@ -22247,11 +22209,11 @@
         </is>
       </c>
       <c r="F278" s="1" t="n">
-        <v>6162</v>
+        <v>6125</v>
       </c>
       <c r="G278" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H278" s="1" t="inlineStr">
@@ -22265,14 +22227,14 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K278" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M278" s="1" t="inlineStr">
@@ -22280,11 +22242,17 @@
           <t>Tatiana Linardi</t>
         </is>
       </c>
-      <c r="N278" s="1" t="n"/>
+      <c r="N278" s="2" t="n">
+        <v>46219.71277496528</v>
+      </c>
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="inlineStr"/>
+      <c r="R278" s="1" t="inlineStr">
+        <is>
+          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
+        </is>
+      </c>
       <c r="S278" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22295,16 +22263,16 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>79865</v>
+        <v>79834</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
@@ -22314,15 +22282,15 @@
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
-        <v>6278</v>
+        <v>6162</v>
       </c>
       <c r="G279" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H279" s="1" t="inlineStr">
@@ -22336,10 +22304,10 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
@@ -22348,7 +22316,7 @@
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N279" s="1" t="n"/>
@@ -22366,7 +22334,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>79854</v>
+        <v>79865</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
@@ -22385,15 +22353,15 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
-        <v>6302</v>
+        <v>6278</v>
       </c>
       <c r="G280" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H280" s="1" t="inlineStr">
@@ -22407,10 +22375,10 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -22419,7 +22387,7 @@
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N280" s="1" t="n"/>
@@ -22437,7 +22405,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>79863</v>
+        <v>79854</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
@@ -22456,15 +22424,15 @@
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>6404</v>
+        <v>6302</v>
       </c>
       <c r="G281" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H281" s="1" t="inlineStr">
@@ -22478,10 +22446,10 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -22490,7 +22458,7 @@
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
@@ -22508,16 +22476,16 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>79835</v>
+        <v>79863</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
@@ -22527,15 +22495,15 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
-        <v>6485</v>
+        <v>6404</v>
       </c>
       <c r="G282" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H282" s="1" t="inlineStr">
@@ -22549,10 +22517,10 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -22561,7 +22529,7 @@
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N282" s="1" t="n"/>
@@ -22579,16 +22547,16 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>79866</v>
+        <v>79835</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
@@ -22598,15 +22566,15 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
-        <v>6539</v>
+        <v>6485</v>
       </c>
       <c r="G283" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H283" s="1" t="inlineStr">
@@ -22620,10 +22588,10 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
@@ -22632,7 +22600,7 @@
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
@@ -22650,7 +22618,7 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>79859</v>
+        <v>79866</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
@@ -22669,15 +22637,15 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
-        <v>6570</v>
+        <v>6539</v>
       </c>
       <c r="G284" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H284" s="1" t="inlineStr">
@@ -22691,7 +22659,7 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K284" s="2" t="n">
         <v>46185</v>
@@ -22721,7 +22689,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>79860</v>
+        <v>79859</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
@@ -22740,15 +22708,15 @@
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>6581</v>
+        <v>6570</v>
       </c>
       <c r="G285" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H285" s="1" t="inlineStr">
@@ -22762,7 +22730,7 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K285" s="2" t="n">
         <v>46185</v>
@@ -22792,7 +22760,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>79861</v>
+        <v>79860</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
@@ -22811,15 +22779,15 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6583</v>
+        <v>6581</v>
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H286" s="1" t="inlineStr">
@@ -22833,7 +22801,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K286" s="2" t="n">
         <v>46185</v>
@@ -22863,16 +22831,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>79867</v>
+        <v>79861</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
@@ -22882,15 +22850,15 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6704</v>
+        <v>6583</v>
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H287" s="1" t="inlineStr">
@@ -22904,7 +22872,7 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K287" s="2" t="n">
         <v>46185</v>
@@ -22934,16 +22902,16 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>79856</v>
+        <v>79867</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
@@ -22953,15 +22921,15 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>4225</v>
+        <v>6704</v>
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H288" s="1" t="inlineStr">
@@ -22975,10 +22943,10 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -22987,7 +22955,7 @@
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N288" s="1" t="n"/>
@@ -23005,7 +22973,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79855</v>
+        <v>79856</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
@@ -23024,15 +22992,15 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>4765</v>
+        <v>4225</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
         </is>
       </c>
       <c r="H289" s="1" t="inlineStr">
@@ -23046,10 +23014,10 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
@@ -23076,32 +23044,36 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>81019</v>
+        <v>79855</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G290" s="1" t="n"/>
+        <v>4765</v>
+      </c>
+      <c r="G290" s="1" t="inlineStr">
+        <is>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+        </is>
+      </c>
       <c r="H290" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23109,50 +23081,41 @@
       </c>
       <c r="I290" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
       <c r="O290" s="1" t="n"/>
       <c r="P290" s="1" t="n"/>
       <c r="Q290" s="1" t="inlineStr"/>
-      <c r="R290" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia 
-Segue recibos conforme solictiado </t>
-        </is>
-      </c>
+      <c r="R290" s="1" t="inlineStr"/>
       <c r="S290" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T290" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
+      <c r="T290" s="1" t="n"/>
       <c r="U290" s="1" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>81052</v>
+        <v>81019</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
@@ -23171,7 +23134,7 @@
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
@@ -23185,23 +23148,23 @@
       </c>
       <c r="I291" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N291" s="1" t="n"/>
@@ -23210,7 +23173,8 @@
       <c r="Q291" s="1" t="inlineStr"/>
       <c r="R291" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t xml:space="preserve">Bom dia 
+Segue recibos conforme solictiado </t>
         </is>
       </c>
       <c r="S291" s="1" t="inlineStr">
@@ -23218,12 +23182,16 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T291" s="1" t="n"/>
+      <c r="T291" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
       <c r="U291" s="1" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>81055</v>
+        <v>81052</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
@@ -23242,7 +23210,7 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
@@ -23260,14 +23228,14 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46218.38736744213</v>
       </c>
       <c r="K292" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M292" s="1" t="inlineStr">
@@ -23275,15 +23243,13 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N292" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
+      <c r="N292" s="1" t="n"/>
       <c r="O292" s="1" t="n"/>
       <c r="P292" s="1" t="n"/>
       <c r="Q292" s="1" t="inlineStr"/>
       <c r="R292" s="1" t="inlineStr">
         <is>
-          <t>Aguardando retorno dos dados do contador</t>
+          <t>cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S292" s="1" t="inlineStr">
@@ -23293,6 +23259,79 @@
       </c>
       <c r="T292" s="1" t="n"/>
       <c r="U292" s="1" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="1" t="n">
+        <v>81055</v>
+      </c>
+      <c r="B293" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C293" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E293" s="1" t="inlineStr">
+        <is>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+        </is>
+      </c>
+      <c r="F293" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G293" s="1" t="n"/>
+      <c r="H293" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I293" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J293" s="2" t="n">
+        <v>46218.40379614583</v>
+      </c>
+      <c r="K293" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L293" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M293" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N293" s="2" t="n">
+        <v>46219.50607847222</v>
+      </c>
+      <c r="O293" s="1" t="n"/>
+      <c r="P293" s="1" t="n"/>
+      <c r="Q293" s="1" t="inlineStr"/>
+      <c r="R293" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando retorno dos dados do contador</t>
+        </is>
+      </c>
+      <c r="S293" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T293" s="1" t="n"/>
+      <c r="U293" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -3179,7 +3179,7 @@
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M34" s="1" t="inlineStr">
@@ -3198,11 +3198,9 @@
           <t>Simone Marques</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
-        <v>46190.46143564815</v>
-      </c>
+      <c r="N34" s="1" t="n"/>
       <c r="O34" s="2" t="n">
-        <v>46227</v>
+        <v>46234</v>
       </c>
       <c r="P34" s="1" t="n"/>
       <c r="Q34" s="1" t="inlineStr"/>
@@ -3216,7 +3214,11 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T34" s="1" t="n"/>
+      <c r="T34" s="1" t="inlineStr">
+        <is>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
+        </is>
+      </c>
       <c r="U34" s="1" t="inlineStr">
         <is>
           <t>Isabella Nascimento</t>
@@ -6703,7 +6705,7 @@
       </c>
       <c r="L77" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M77" s="1" t="inlineStr">
@@ -6715,12 +6717,22 @@
       <c r="O77" s="2" t="n">
         <v>46217</v>
       </c>
-      <c r="P77" s="1" t="n"/>
-      <c r="Q77" s="1" t="inlineStr"/>
-      <c r="R77" s="1" t="inlineStr"/>
+      <c r="P77" s="2" t="n">
+        <v>46220.66134609954</v>
+      </c>
+      <c r="Q77" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R77" s="1" t="inlineStr">
+        <is>
+          <t>Paralegal em atendimento</t>
+        </is>
+      </c>
       <c r="S77" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T77" s="1" t="n"/>
@@ -14220,7 +14232,7 @@
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M169" s="1" t="inlineStr">
@@ -14234,8 +14246,14 @@
       <c r="O169" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="P169" s="1" t="n"/>
-      <c r="Q169" s="1" t="inlineStr"/>
+      <c r="P169" s="2" t="n">
+        <v>46220.66189042824</v>
+      </c>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="R169" s="1" t="inlineStr">
         <is>
           <t>Vai ser conciliado junto ao fechamento 06/2026</t>
@@ -14243,7 +14261,7 @@
       </c>
       <c r="S169" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T169" s="1" t="n"/>
@@ -14504,7 +14522,7 @@
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M173" s="1" t="inlineStr">
@@ -14518,8 +14536,14 @@
       <c r="O173" s="2" t="n">
         <v>46218</v>
       </c>
-      <c r="P173" s="1" t="n"/>
-      <c r="Q173" s="1" t="inlineStr"/>
+      <c r="P173" s="2" t="n">
+        <v>46220.66202916667</v>
+      </c>
+      <c r="Q173" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="R173" s="1" t="inlineStr">
         <is>
           <t>Vai ser feito no fechamento</t>
@@ -14527,7 +14551,7 @@
       </c>
       <c r="S173" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T173" s="1" t="n"/>
@@ -15069,7 +15093,7 @@
       </c>
       <c r="L180" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M180" s="1" t="inlineStr">
@@ -15081,12 +15105,22 @@
       <c r="O180" s="2" t="n">
         <v>46218</v>
       </c>
-      <c r="P180" s="1" t="n"/>
-      <c r="Q180" s="1" t="inlineStr"/>
-      <c r="R180" s="1" t="inlineStr"/>
+      <c r="P180" s="2" t="n">
+        <v>46220.66110667824</v>
+      </c>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R180" s="1" t="inlineStr">
+        <is>
+          <t>Enviado no email 14/07</t>
+        </is>
+      </c>
       <c r="S180" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T180" s="1" t="n"/>
@@ -15158,7 +15192,7 @@
         <v>46216.74338672453</v>
       </c>
       <c r="O181" s="2" t="n">
-        <v>46217</v>
+        <v>46234</v>
       </c>
       <c r="P181" s="1" t="n"/>
       <c r="Q181" s="1" t="inlineStr"/>
@@ -15314,7 +15348,7 @@
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M183" s="1" t="inlineStr">
@@ -15326,12 +15360,22 @@
       <c r="O183" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="P183" s="1" t="n"/>
-      <c r="Q183" s="1" t="inlineStr"/>
-      <c r="R183" s="1" t="inlineStr"/>
+      <c r="P183" s="2" t="n">
+        <v>46220.65923896991</v>
+      </c>
+      <c r="Q183" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R183" s="1" t="inlineStr">
+        <is>
+          <t>Vai ser lançado no fechamento</t>
+        </is>
+      </c>
       <c r="S183" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T183" s="1" t="n"/>
@@ -16043,7 +16087,7 @@
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M192" s="1" t="inlineStr">
@@ -16055,12 +16099,22 @@
       <c r="O192" s="2" t="n">
         <v>46218</v>
       </c>
-      <c r="P192" s="1" t="n"/>
-      <c r="Q192" s="1" t="inlineStr"/>
-      <c r="R192" s="1" t="inlineStr"/>
+      <c r="P192" s="2" t="n">
+        <v>46220.65987260417</v>
+      </c>
+      <c r="Q192" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="R192" s="1" t="inlineStr">
+        <is>
+          <t>Estoque ja foi ajustado (solicitação duplicada , recebido via email)</t>
+        </is>
+      </c>
       <c r="S192" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T192" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -5376,7 +5376,11 @@
           <t>LUSINDE INVEST EMPREENDIMENTOS S.A.</t>
         </is>
       </c>
-      <c r="H61" s="1" t="n"/>
+      <c r="H61" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I61" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -5390,7 +5394,7 @@
       </c>
       <c r="L61" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M61" s="1" t="inlineStr">
@@ -5402,14 +5406,18 @@
       <c r="O61" s="1" t="n"/>
       <c r="P61" s="1" t="n"/>
       <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="n"/>
+      <c r="R61" s="1" t="inlineStr"/>
       <c r="S61" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T61" s="1" t="n"/>
-      <c r="U61" s="1" t="inlineStr"/>
+      <c r="U61" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -12945,7 +12953,11 @@
           <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
-      <c r="H153" s="1" t="n"/>
+      <c r="H153" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I153" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -12959,7 +12971,7 @@
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M153" s="1" t="inlineStr">
@@ -12971,14 +12983,18 @@
       <c r="O153" s="1" t="n"/>
       <c r="P153" s="1" t="n"/>
       <c r="Q153" s="1" t="inlineStr"/>
-      <c r="R153" s="1" t="n"/>
+      <c r="R153" s="1" t="inlineStr"/>
       <c r="S153" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T153" s="1" t="n"/>
-      <c r="U153" s="1" t="inlineStr"/>
+      <c r="U153" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -13087,7 +13103,11 @@
           <t>POWER FINANCIAL DO BRASIL S.A.</t>
         </is>
       </c>
-      <c r="H155" s="1" t="n"/>
+      <c r="H155" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I155" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -13101,7 +13121,7 @@
       </c>
       <c r="L155" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M155" s="1" t="inlineStr">
@@ -13113,14 +13133,18 @@
       <c r="O155" s="1" t="n"/>
       <c r="P155" s="1" t="n"/>
       <c r="Q155" s="1" t="inlineStr"/>
-      <c r="R155" s="1" t="n"/>
+      <c r="R155" s="1" t="inlineStr"/>
       <c r="S155" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T155" s="1" t="n"/>
-      <c r="U155" s="1" t="inlineStr"/>
+      <c r="U155" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -14149,7 +14173,11 @@
           <t>NOVAIS IT SOLUCOES TECNOLOGICAS LTDA</t>
         </is>
       </c>
-      <c r="H168" s="1" t="n"/>
+      <c r="H168" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I168" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14163,7 +14191,7 @@
       </c>
       <c r="L168" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M168" s="1" t="inlineStr">
@@ -14175,14 +14203,18 @@
       <c r="O168" s="1" t="n"/>
       <c r="P168" s="1" t="n"/>
       <c r="Q168" s="1" t="inlineStr"/>
-      <c r="R168" s="1" t="n"/>
+      <c r="R168" s="1" t="inlineStr"/>
       <c r="S168" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T168" s="1" t="n"/>
-      <c r="U168" s="1" t="inlineStr"/>
+      <c r="U168" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -14380,7 +14412,11 @@
           <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H171" s="1" t="n"/>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14394,7 +14430,7 @@
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M171" s="1" t="inlineStr">
@@ -14406,14 +14442,18 @@
       <c r="O171" s="1" t="n"/>
       <c r="P171" s="1" t="n"/>
       <c r="Q171" s="1" t="inlineStr"/>
-      <c r="R171" s="1" t="n"/>
+      <c r="R171" s="1" t="inlineStr"/>
       <c r="S171" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T171" s="1" t="n"/>
-      <c r="U171" s="1" t="inlineStr"/>
+      <c r="U171" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -14514,7 +14554,11 @@
           <t>CZLOC LOCACAO DE EQUIPAMENTOS PARA CONSTRUCAO CIVIL LTDA</t>
         </is>
       </c>
-      <c r="H173" s="1" t="n"/>
+      <c r="H173" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14528,7 +14572,7 @@
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M173" s="1" t="inlineStr">
@@ -14540,14 +14584,18 @@
       <c r="O173" s="1" t="n"/>
       <c r="P173" s="1" t="n"/>
       <c r="Q173" s="1" t="inlineStr"/>
-      <c r="R173" s="1" t="n"/>
+      <c r="R173" s="1" t="inlineStr"/>
       <c r="S173" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T173" s="1" t="n"/>
-      <c r="U173" s="1" t="inlineStr"/>
+      <c r="U173" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -14829,7 +14877,11 @@
           <t>INDUSTRIA E COMERCIO RAIZES DO NORDESTE LTDA</t>
         </is>
       </c>
-      <c r="H177" s="1" t="n"/>
+      <c r="H177" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I177" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -14843,7 +14895,7 @@
       </c>
       <c r="L177" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M177" s="1" t="inlineStr">
@@ -14855,14 +14907,18 @@
       <c r="O177" s="1" t="n"/>
       <c r="P177" s="1" t="n"/>
       <c r="Q177" s="1" t="inlineStr"/>
-      <c r="R177" s="1" t="n"/>
+      <c r="R177" s="1" t="inlineStr"/>
       <c r="S177" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T177" s="1" t="n"/>
-      <c r="U177" s="1" t="inlineStr"/>
+      <c r="U177" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -16233,7 +16289,11 @@
           <t>GRIFFY FERRAMENTARIA DE PRECISAO LTDA</t>
         </is>
       </c>
-      <c r="H194" s="1" t="n"/>
+      <c r="H194" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
           <t>EF - INDUSTRIA</t>
@@ -16247,7 +16307,7 @@
       </c>
       <c r="L194" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M194" s="1" t="inlineStr">
@@ -16259,14 +16319,18 @@
       <c r="O194" s="1" t="n"/>
       <c r="P194" s="1" t="n"/>
       <c r="Q194" s="1" t="inlineStr"/>
-      <c r="R194" s="1" t="n"/>
+      <c r="R194" s="1" t="inlineStr"/>
       <c r="S194" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T194" s="1" t="n"/>
-      <c r="U194" s="1" t="inlineStr"/>
+      <c r="U194" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -17218,67 +17282,59 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>80792</v>
+        <v>81202</v>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
+          <t>Bom dia, preciso do certificado da empresa 5603 -Carlos Antunes e que seja renovado o certificado da empresa 4793- Costa lima</t>
         </is>
       </c>
       <c r="F208" s="1" t="n">
-        <v>861</v>
-      </c>
-      <c r="G208" s="1" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H208" s="1" t="inlineStr">
-        <is>
-          <t>Diego Lima</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G208" s="1" t="n"/>
+      <c r="H208" s="1" t="n"/>
       <c r="I208" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>46210.5704596412</v>
+        <v>46223.39712596065</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>46213</v>
+        <v>46224</v>
       </c>
       <c r="L208" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="N208" s="1" t="n"/>
       <c r="O208" s="1" t="n"/>
       <c r="P208" s="1" t="n"/>
       <c r="Q208" s="1" t="inlineStr"/>
-      <c r="R208" s="1" t="inlineStr"/>
+      <c r="R208" s="1" t="n"/>
       <c r="S208" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17289,7 +17345,7 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>80732</v>
+        <v>80792</v>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
@@ -17308,7 +17364,7 @@
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
+          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
         </is>
       </c>
       <c r="F209" s="1" t="n">
@@ -17330,10 +17386,10 @@
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>46206.67579409722</v>
+        <v>46210.5704596412</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
@@ -17360,7 +17416,7 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>80733</v>
+        <v>80732</v>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
@@ -17379,7 +17435,7 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>1.01.001.0001.00001 - Caixa</t>
+          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
         </is>
       </c>
       <c r="F210" s="1" t="n">
@@ -17401,7 +17457,7 @@
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46206.67633518518</v>
+        <v>46206.67579409722</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>46210</v>
@@ -17431,7 +17487,7 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>80734</v>
+        <v>80733</v>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
@@ -17450,7 +17506,7 @@
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
+          <t>1.01.001.0001.00001 - Caixa</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
@@ -17472,7 +17528,7 @@
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>46206.6769059375</v>
+        <v>46206.67633518518</v>
       </c>
       <c r="K211" s="2" t="n">
         <v>46210</v>
@@ -17502,16 +17558,16 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>80008</v>
+        <v>80734</v>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
@@ -17521,20 +17577,20 @@
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
+          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
-        <v>1065</v>
+        <v>861</v>
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t>MARTINICA COMERCIAL LTDA</t>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H212" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Diego Lima</t>
         </is>
       </c>
       <c r="I212" s="1" t="inlineStr">
@@ -17543,10 +17599,10 @@
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>46188.45542777778</v>
+        <v>46206.6769059375</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>46189</v>
+        <v>46210</v>
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
@@ -17555,7 +17611,7 @@
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="N212" s="1" t="n"/>
@@ -17573,16 +17629,16 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>79890</v>
+        <v>80008</v>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
@@ -17592,20 +17648,20 @@
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
+          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
         </is>
       </c>
       <c r="F213" s="1" t="n">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G213" s="1" t="inlineStr">
         <is>
-          <t>Supermercado Kanashiro Ltda</t>
+          <t>MARTINICA COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H213" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="I213" s="1" t="inlineStr">
@@ -17614,32 +17670,26 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>46184.46686350695</v>
+        <v>46188.45542777778</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M213" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
-      <c r="N213" s="2" t="n">
-        <v>46185.43777230324</v>
-      </c>
+          <t>Edileide Dias</t>
+        </is>
+      </c>
+      <c r="N213" s="1" t="n"/>
       <c r="O213" s="1" t="n"/>
       <c r="P213" s="1" t="n"/>
       <c r="Q213" s="1" t="inlineStr"/>
-      <c r="R213" s="1" t="inlineStr">
-        <is>
-          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
-        </is>
-      </c>
+      <c r="R213" s="1" t="inlineStr"/>
       <c r="S213" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17650,39 +17700,39 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>78306</v>
+        <v>79890</v>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D214" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
         </is>
       </c>
       <c r="F214" s="1" t="n">
-        <v>1286</v>
+        <v>1066</v>
       </c>
       <c r="G214" s="1" t="inlineStr">
         <is>
-          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
+          <t>Supermercado Kanashiro Ltda</t>
         </is>
       </c>
       <c r="H214" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I214" s="1" t="inlineStr">
@@ -17691,26 +17741,32 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>46111.42803700231</v>
+        <v>46184.46686350695</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>46122</v>
+        <v>46188</v>
       </c>
       <c r="L214" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M214" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
-        </is>
-      </c>
-      <c r="N214" s="1" t="n"/>
+          <t>Karina Santos</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="n">
+        <v>46185.43777230324</v>
+      </c>
       <c r="O214" s="1" t="n"/>
       <c r="P214" s="1" t="n"/>
       <c r="Q214" s="1" t="inlineStr"/>
-      <c r="R214" s="1" t="inlineStr"/>
+      <c r="R214" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
+        </is>
+      </c>
       <c r="S214" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17721,16 +17777,16 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>79733</v>
+        <v>78306</v>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
@@ -17740,20 +17796,20 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F215" s="1" t="n">
-        <v>1556</v>
+        <v>1286</v>
       </c>
       <c r="G215" s="1" t="inlineStr">
         <is>
-          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
+          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H215" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I215" s="1" t="inlineStr">
@@ -17762,10 +17818,10 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>46180.49354722222</v>
+        <v>46111.42803700231</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>46182</v>
+        <v>46122</v>
       </c>
       <c r="L215" s="1" t="inlineStr">
         <is>
@@ -17774,7 +17830,7 @@
       </c>
       <c r="M215" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N215" s="1" t="n"/>
@@ -17792,7 +17848,7 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>79731</v>
+        <v>79733</v>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
@@ -17811,20 +17867,20 @@
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
+          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
         </is>
       </c>
       <c r="F216" s="1" t="n">
-        <v>1931</v>
+        <v>1556</v>
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
+          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
         </is>
       </c>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I216" s="1" t="inlineStr">
@@ -17833,10 +17889,10 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>46180.44674649306</v>
+        <v>46180.49354722222</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
@@ -17859,24 +17915,20 @@
         </is>
       </c>
       <c r="T216" s="1" t="n"/>
-      <c r="U216" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="U216" s="1" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>78322</v>
+        <v>79731</v>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
@@ -17886,20 +17938,20 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
         </is>
       </c>
       <c r="F217" s="1" t="n">
-        <v>2209</v>
+        <v>1931</v>
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="I217" s="1" t="inlineStr">
@@ -17908,10 +17960,10 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>46111.44774475694</v>
+        <v>46180.44674649306</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>46122</v>
+        <v>46185</v>
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
@@ -17920,7 +17972,7 @@
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N217" s="1" t="n"/>
@@ -17934,43 +17986,47 @@
         </is>
       </c>
       <c r="T217" s="1" t="n"/>
-      <c r="U217" s="1" t="inlineStr"/>
+      <c r="U217" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>80013</v>
+        <v>78322</v>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F218" s="1" t="n">
-        <v>2480</v>
+        <v>2209</v>
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I218" s="1" t="inlineStr">
@@ -17979,10 +18035,10 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>46188.46272334491</v>
+        <v>46111.44774475694</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>46189</v>
+        <v>46122</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
@@ -17991,7 +18047,7 @@
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N218" s="1" t="n"/>
@@ -18009,7 +18065,7 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>80039</v>
+        <v>80013</v>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
@@ -18028,15 +18084,15 @@
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
+          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
         </is>
       </c>
       <c r="F219" s="1" t="n">
-        <v>2491</v>
+        <v>2480</v>
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
+          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
         </is>
       </c>
       <c r="H219" s="1" t="inlineStr">
@@ -18050,7 +18106,7 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>46188.58172743056</v>
+        <v>46188.46272334491</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>46189</v>
@@ -18062,7 +18118,7 @@
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N219" s="1" t="n"/>
@@ -18080,7 +18136,7 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>80014</v>
+        <v>80039</v>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
@@ -18099,15 +18155,15 @@
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
+          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
         </is>
       </c>
       <c r="F220" s="1" t="n">
-        <v>2500</v>
+        <v>2491</v>
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t>CAEFHOLD Participações S.A.</t>
+          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
@@ -18121,7 +18177,7 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>46188.46337480324</v>
+        <v>46188.58172743056</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>46189</v>
@@ -18133,7 +18189,7 @@
       </c>
       <c r="M220" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="N220" s="1" t="n"/>
@@ -18151,39 +18207,39 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>78304</v>
+        <v>80014</v>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
         </is>
       </c>
       <c r="F221" s="1" t="n">
-        <v>2620</v>
+        <v>2500</v>
       </c>
       <c r="G221" s="1" t="inlineStr">
         <is>
-          <t>ANTOCON GALVANOPLASTIA LTDA</t>
+          <t>CAEFHOLD Participações S.A.</t>
         </is>
       </c>
       <c r="H221" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I221" s="1" t="inlineStr">
@@ -18192,10 +18248,10 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>46111.42458850695</v>
+        <v>46188.46337480324</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>46122</v>
+        <v>46189</v>
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
@@ -18204,7 +18260,7 @@
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N221" s="1" t="n"/>
@@ -18222,39 +18278,39 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>81061</v>
+        <v>78304</v>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza realizar a assinatura do ecf do cliente 2821-Espite</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F222" s="1" t="n">
-        <v>2821</v>
+        <v>2620</v>
       </c>
       <c r="G222" s="1" t="inlineStr">
         <is>
-          <t>ESPITE PARTICIPAÇÕES S.A.</t>
+          <t>ANTOCON GALVANOPLASTIA LTDA</t>
         </is>
       </c>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I222" s="1" t="inlineStr">
@@ -18263,10 +18319,10 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>46218.42798252315</v>
+        <v>46111.42458850695</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>46219</v>
+        <v>46122</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
@@ -18275,7 +18331,7 @@
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N222" s="1" t="n"/>
@@ -18293,39 +18349,39 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>79738</v>
+        <v>81061</v>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DE ANALISE DE MALHA DESDE 25/05/2026 - ANALISE POR E-MAI - SERGIO SUGERIU NA ULTIMA SEMANA QUE PODIAMOS VERIFICAR OS VALORES DE 2022 PARA CREDITO, ANALISEI E VERIFIQUEI QUE A VALOR DE 227.186,29 DE RENDIMENTOS A MAIOR DO QUE ESTA NA DIRF VERIFICAR E LEVANTAR E-MAIL DA EPOCA, NÃO HA PERDCOMP PARA ESTES PERIODOS</t>
+          <t>Bom diaPor gentileza realizar a assinatura do ecf do cliente 2821-Espite</t>
         </is>
       </c>
       <c r="F223" s="1" t="n">
-        <v>2956</v>
+        <v>2821</v>
       </c>
       <c r="G223" s="1" t="inlineStr">
         <is>
-          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
+          <t>ESPITE PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H223" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I223" s="1" t="inlineStr">
@@ -18334,10 +18390,10 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>46180.61864918981</v>
+        <v>46218.42798252315</v>
       </c>
       <c r="K223" s="2" t="n">
-        <v>46182</v>
+        <v>46219</v>
       </c>
       <c r="L223" s="1" t="inlineStr">
         <is>
@@ -18346,7 +18402,7 @@
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N223" s="1" t="n"/>
@@ -18364,7 +18420,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>79735</v>
+        <v>79738</v>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
@@ -18383,15 +18439,15 @@
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGUARDANDO RETORNO DA ANALISE DA MALHA DESDE 26/05/2026 - ENVIADO POR E-MAIL </t>
+          <t>AGUARDANDO RETORNO DE ANALISE DE MALHA DESDE 25/05/2026 - ANALISE POR E-MAI - SERGIO SUGERIU NA ULTIMA SEMANA QUE PODIAMOS VERIFICAR OS VALORES DE 2022 PARA CREDITO, ANALISEI E VERIFIQUEI QUE A VALOR DE 227.186,29 DE RENDIMENTOS A MAIOR DO QUE ESTA NA DIRF VERIFICAR E LEVANTAR E-MAIL DA EPOCA, NÃO HA PERDCOMP PARA ESTES PERIODOS</t>
         </is>
       </c>
       <c r="F224" s="1" t="n">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="G224" s="1" t="inlineStr">
         <is>
-          <t>SAVYS EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
+          <t>AGGYO ADMINISTRAÇÃO DE BENS E PARTICIPAÇÕES S.A.</t>
         </is>
       </c>
       <c r="H224" s="1" t="inlineStr">
@@ -18405,7 +18461,7 @@
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>46180.50447491898</v>
+        <v>46180.61864918981</v>
       </c>
       <c r="K224" s="2" t="n">
         <v>46182</v>
@@ -18435,39 +18491,39 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>79889</v>
+        <v>79735</v>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Carvalho, o cliente não possui controle, mas retira todo ano.</t>
+          <t xml:space="preserve">AGUARDANDO RETORNO DA ANALISE DA MALHA DESDE 26/05/2026 - ENVIADO POR E-MAIL </t>
         </is>
       </c>
       <c r="F225" s="1" t="n">
-        <v>3195</v>
+        <v>2959</v>
       </c>
       <c r="G225" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO RT CARVALHO LTDA</t>
+          <t>SAVYS EMPREENDIMENTOS E PARTICIPAÇÕES S.A</t>
         </is>
       </c>
       <c r="H225" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I225" s="1" t="inlineStr">
@@ -18476,10 +18532,10 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>46184.46640107639</v>
+        <v>46180.50447491898</v>
       </c>
       <c r="K225" s="2" t="n">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="L225" s="1" t="inlineStr">
         <is>
@@ -18488,7 +18544,7 @@
       </c>
       <c r="M225" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N225" s="1" t="n"/>
@@ -18506,26 +18562,26 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>81194</v>
+        <v>79889</v>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D226" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E226" s="1" t="inlineStr">
         <is>
-          <t>solicitar que disponibilize o certificado em minha arvore.</t>
+          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Carvalho, o cliente não possui controle, mas retira todo ano.</t>
         </is>
       </c>
       <c r="F226" s="1" t="n">
@@ -18536,33 +18592,37 @@
           <t>EMPORIO RT CARVALHO LTDA</t>
         </is>
       </c>
-      <c r="H226" s="1" t="n"/>
+      <c r="H226" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
       <c r="I226" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J226" s="2" t="n">
-        <v>46220.61613811342</v>
+        <v>46184.46640107639</v>
       </c>
       <c r="K226" s="2" t="n">
-        <v>46223</v>
+        <v>46188</v>
       </c>
       <c r="L226" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M226" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Karina Santos</t>
         </is>
       </c>
       <c r="N226" s="1" t="n"/>
       <c r="O226" s="1" t="n"/>
       <c r="P226" s="1" t="n"/>
       <c r="Q226" s="1" t="inlineStr"/>
-      <c r="R226" s="1" t="n"/>
+      <c r="R226" s="1" t="inlineStr"/>
       <c r="S226" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -18573,67 +18633,63 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>78313</v>
+        <v>81194</v>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D227" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E227" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>solicitar que disponibilize o certificado em minha arvore.</t>
         </is>
       </c>
       <c r="F227" s="1" t="n">
-        <v>3262</v>
+        <v>3195</v>
       </c>
       <c r="G227" s="1" t="inlineStr">
         <is>
-          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
-        </is>
-      </c>
-      <c r="H227" s="1" t="inlineStr">
-        <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
+          <t>EMPORIO RT CARVALHO LTDA</t>
+        </is>
+      </c>
+      <c r="H227" s="1" t="n"/>
       <c r="I227" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J227" s="2" t="n">
-        <v>46111.43707260417</v>
+        <v>46220.61613811342</v>
       </c>
       <c r="K227" s="2" t="n">
-        <v>46122</v>
+        <v>46223</v>
       </c>
       <c r="L227" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M227" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N227" s="1" t="n"/>
       <c r="O227" s="1" t="n"/>
       <c r="P227" s="1" t="n"/>
       <c r="Q227" s="1" t="inlineStr"/>
-      <c r="R227" s="1" t="inlineStr"/>
+      <c r="R227" s="1" t="n"/>
       <c r="S227" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -18644,7 +18700,7 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>78309</v>
+        <v>78313</v>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
@@ -18667,11 +18723,11 @@
         </is>
       </c>
       <c r="F228" s="1" t="n">
-        <v>3499</v>
+        <v>3262</v>
       </c>
       <c r="G228" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
+          <t>JCV INDÚSTRIA E COMÉRCIO DE PLÁSTICOS LTDA</t>
         </is>
       </c>
       <c r="H228" s="1" t="inlineStr">
@@ -18685,7 +18741,7 @@
         </is>
       </c>
       <c r="J228" s="2" t="n">
-        <v>46111.43159019676</v>
+        <v>46111.43707260417</v>
       </c>
       <c r="K228" s="2" t="n">
         <v>46122</v>
@@ -18715,7 +18771,7 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>78326</v>
+        <v>78309</v>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
@@ -18738,16 +18794,16 @@
         </is>
       </c>
       <c r="F229" s="1" t="n">
-        <v>3598</v>
+        <v>3499</v>
       </c>
       <c r="G229" s="1" t="inlineStr">
         <is>
-          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
+          <t xml:space="preserve">Emplaca Automação e Tecnologia Ltda. </t>
         </is>
       </c>
       <c r="H229" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I229" s="1" t="inlineStr">
@@ -18756,7 +18812,7 @@
         </is>
       </c>
       <c r="J229" s="2" t="n">
-        <v>46111.45085925926</v>
+        <v>46111.43159019676</v>
       </c>
       <c r="K229" s="2" t="n">
         <v>46122</v>
@@ -18786,7 +18842,7 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>80038</v>
+        <v>78326</v>
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
@@ -18795,30 +18851,30 @@
       </c>
       <c r="C230" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D230" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E230" s="1" t="inlineStr">
         <is>
-          <t>APURAÇÃO IRPJ E CSLL 2025</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F230" s="1" t="n">
-        <v>3661</v>
+        <v>3598</v>
       </c>
       <c r="G230" s="1" t="inlineStr">
         <is>
-          <t>BROGOTÁ INDÚSTRIA GRÁFICA LTDA</t>
+          <t>VTZZ INDUSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H230" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I230" s="1" t="inlineStr">
@@ -18827,10 +18883,10 @@
         </is>
       </c>
       <c r="J230" s="2" t="n">
-        <v>46188.55930297454</v>
+        <v>46111.45085925926</v>
       </c>
       <c r="K230" s="2" t="n">
-        <v>46190</v>
+        <v>46122</v>
       </c>
       <c r="L230" s="1" t="inlineStr">
         <is>
@@ -18839,7 +18895,7 @@
       </c>
       <c r="M230" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N230" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U300" headerRowCount="1">
-  <autoFilter ref="A1:U300"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U299" headerRowCount="1">
+  <autoFilter ref="A1:U299"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U300"/>
+  <dimension ref="A1:U299"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1993,7 +1993,11 @@
           <t>MQ PRODUSERV COMÉRCIO E EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H19" s="1" t="n"/>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -2007,7 +2011,7 @@
       </c>
       <c r="L19" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M19" s="1" t="inlineStr">
@@ -2016,17 +2020,23 @@
         </is>
       </c>
       <c r="N19" s="1" t="n"/>
-      <c r="O19" s="1" t="n"/>
+      <c r="O19" s="2" t="n">
+        <v>46226</v>
+      </c>
       <c r="P19" s="1" t="n"/>
       <c r="Q19" s="1" t="inlineStr"/>
-      <c r="R19" s="1" t="n"/>
+      <c r="R19" s="1" t="inlineStr"/>
       <c r="S19" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T19" s="1" t="n"/>
-      <c r="U19" s="1" t="inlineStr"/>
+      <c r="U19" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -2461,7 +2471,11 @@
           <t xml:space="preserve">A.H.M.H. PARTICIPACOES S.A. </t>
         </is>
       </c>
-      <c r="H25" s="1" t="n"/>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I25" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL HOLDING</t>
@@ -2475,7 +2489,7 @@
       </c>
       <c r="L25" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M25" s="1" t="inlineStr">
@@ -2484,10 +2498,12 @@
         </is>
       </c>
       <c r="N25" s="1" t="n"/>
-      <c r="O25" s="1" t="n"/>
+      <c r="O25" s="2" t="n">
+        <v>46225</v>
+      </c>
       <c r="P25" s="1" t="n"/>
       <c r="Q25" s="1" t="inlineStr"/>
-      <c r="R25" s="1" t="n"/>
+      <c r="R25" s="1" t="inlineStr"/>
       <c r="S25" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -2528,7 +2544,11 @@
           <t>Adlpar Investimentos S.A.</t>
         </is>
       </c>
-      <c r="H26" s="1" t="n"/>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>Fernanda Araujo</t>
+        </is>
+      </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL HOLDING</t>
@@ -2542,7 +2562,7 @@
       </c>
       <c r="L26" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M26" s="1" t="inlineStr">
@@ -2551,10 +2571,12 @@
         </is>
       </c>
       <c r="N26" s="1" t="n"/>
-      <c r="O26" s="1" t="n"/>
+      <c r="O26" s="2" t="n">
+        <v>46225</v>
+      </c>
       <c r="P26" s="1" t="n"/>
       <c r="Q26" s="1" t="inlineStr"/>
-      <c r="R26" s="1" t="n"/>
+      <c r="R26" s="1" t="inlineStr"/>
       <c r="S26" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -3507,7 +3529,11 @@
           <t>ESQUADRIAS SIDNEY LTDA</t>
         </is>
       </c>
-      <c r="H38" s="1" t="n"/>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I38" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -3521,7 +3547,7 @@
       </c>
       <c r="L38" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M38" s="1" t="inlineStr">
@@ -3530,17 +3556,23 @@
         </is>
       </c>
       <c r="N38" s="1" t="n"/>
-      <c r="O38" s="1" t="n"/>
+      <c r="O38" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="P38" s="1" t="n"/>
       <c r="Q38" s="1" t="inlineStr"/>
-      <c r="R38" s="1" t="n"/>
+      <c r="R38" s="1" t="inlineStr"/>
       <c r="S38" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T38" s="1" t="n"/>
-      <c r="U38" s="1" t="inlineStr"/>
+      <c r="U38" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -4169,7 +4201,11 @@
           <t>DISTRIBUIDORA DE HORTIFRUTIGRANJEIROS 3 BBB LTDA  (MATRIZ)</t>
         </is>
       </c>
-      <c r="H46" s="1" t="n"/>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>Lucas Fischer</t>
+        </is>
+      </c>
       <c r="I46" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -4183,7 +4219,7 @@
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M46" s="1" t="inlineStr">
@@ -4192,10 +4228,12 @@
         </is>
       </c>
       <c r="N46" s="1" t="n"/>
-      <c r="O46" s="1" t="n"/>
+      <c r="O46" s="2" t="n">
+        <v>46227</v>
+      </c>
       <c r="P46" s="1" t="n"/>
       <c r="Q46" s="1" t="inlineStr"/>
-      <c r="R46" s="1" t="n"/>
+      <c r="R46" s="1" t="inlineStr"/>
       <c r="S46" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -5309,7 +5347,11 @@
           <t>AF DATALINK CABOS, CONEXOES E SISTEMAS LTDA</t>
         </is>
       </c>
-      <c r="H60" s="1" t="n"/>
+      <c r="H60" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
       <c r="I60" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -5323,7 +5365,7 @@
       </c>
       <c r="L60" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M60" s="1" t="inlineStr">
@@ -5332,17 +5374,23 @@
         </is>
       </c>
       <c r="N60" s="1" t="n"/>
-      <c r="O60" s="1" t="n"/>
+      <c r="O60" s="2" t="n">
+        <v>46225</v>
+      </c>
       <c r="P60" s="1" t="n"/>
       <c r="Q60" s="1" t="inlineStr"/>
-      <c r="R60" s="1" t="n"/>
+      <c r="R60" s="1" t="inlineStr"/>
       <c r="S60" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T60" s="1" t="n"/>
-      <c r="U60" s="1" t="inlineStr"/>
+      <c r="U60" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -7501,7 +7549,11 @@
           <t>SAMPA ATACADO DE GENEROS ALIMENTICIOS E BEBIDAS LTDA</t>
         </is>
       </c>
-      <c r="H87" s="1" t="n"/>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
       <c r="I87" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL VAREJO</t>
@@ -7515,7 +7567,7 @@
       </c>
       <c r="L87" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M87" s="1" t="inlineStr">
@@ -7525,12 +7577,22 @@
       </c>
       <c r="N87" s="1" t="n"/>
       <c r="O87" s="1" t="n"/>
-      <c r="P87" s="1" t="n"/>
-      <c r="Q87" s="1" t="inlineStr"/>
-      <c r="R87" s="1" t="n"/>
+      <c r="P87" s="2" t="n">
+        <v>46223.41618116898</v>
+      </c>
+      <c r="Q87" s="1" t="inlineStr">
+        <is>
+          <t>Renata Cavalheiro</t>
+        </is>
+      </c>
+      <c r="R87" s="1" t="inlineStr">
+        <is>
+          <t>Já foi enviado em 17/07/26.</t>
+        </is>
+      </c>
       <c r="S87" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T87" s="1" t="n"/>
@@ -10069,7 +10131,11 @@
           <t>T C DE CASTRO EMPREENDIMENTOS LTDA</t>
         </is>
       </c>
-      <c r="H118" s="1" t="n"/>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I118" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -10083,7 +10149,7 @@
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M118" s="1" t="inlineStr">
@@ -10092,17 +10158,23 @@
         </is>
       </c>
       <c r="N118" s="1" t="n"/>
-      <c r="O118" s="1" t="n"/>
+      <c r="O118" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="P118" s="1" t="n"/>
       <c r="Q118" s="1" t="inlineStr"/>
-      <c r="R118" s="1" t="n"/>
+      <c r="R118" s="1" t="inlineStr"/>
       <c r="S118" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T118" s="1" t="n"/>
-      <c r="U118" s="1" t="inlineStr"/>
+      <c r="U118" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -11232,7 +11304,11 @@
           <t xml:space="preserve">Parafutrecos Comercial LTDA </t>
         </is>
       </c>
-      <c r="H132" s="1" t="n"/>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I132" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -11246,7 +11322,7 @@
       </c>
       <c r="L132" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M132" s="1" t="inlineStr">
@@ -11255,17 +11331,23 @@
         </is>
       </c>
       <c r="N132" s="1" t="n"/>
-      <c r="O132" s="1" t="n"/>
+      <c r="O132" s="2" t="n">
+        <v>46224</v>
+      </c>
       <c r="P132" s="1" t="n"/>
       <c r="Q132" s="1" t="inlineStr"/>
-      <c r="R132" s="1" t="n"/>
+      <c r="R132" s="1" t="inlineStr"/>
       <c r="S132" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T132" s="1" t="n"/>
-      <c r="U132" s="1" t="inlineStr"/>
+      <c r="U132" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -14487,7 +14569,11 @@
           <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
-      <c r="H172" s="1" t="n"/>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
           <t>CTB - CONTÁBIL INDUSTRIA</t>
@@ -14501,7 +14587,7 @@
       </c>
       <c r="L172" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M172" s="1" t="inlineStr">
@@ -14510,17 +14596,23 @@
         </is>
       </c>
       <c r="N172" s="1" t="n"/>
-      <c r="O172" s="1" t="n"/>
+      <c r="O172" s="2" t="n">
+        <v>46225</v>
+      </c>
       <c r="P172" s="1" t="n"/>
       <c r="Q172" s="1" t="inlineStr"/>
-      <c r="R172" s="1" t="n"/>
+      <c r="R172" s="1" t="inlineStr"/>
       <c r="S172" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T172" s="1" t="n"/>
-      <c r="U172" s="1" t="inlineStr"/>
+      <c r="U172" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -21710,26 +21802,26 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>81172</v>
+        <v>77913</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Por gentileza, poderia realizar a baixa da terafa DEC 2 quinzena dos clientes abaixo?ISENTO3498	EMPLACA SERVIÇOS LTDA4327	ACCESS EVENTOS E VIAGENS LTDA5780	A Estancia Morro Grande Centro de R5873	FRRD ADMINISTRADORA DE IMOVEIS LTDA5906	A Estancia Morro Grande - Centro de5978	HLL LOCADORA DE GUINDASTES LTDA5979	AMATRUDA LOCADORA DE GUINDASTES E A6172	MEDICAL DISCOVERY TREINAMENTOS &amp; DE6173	CLINICA TONON DE DERMATOLOGISTA LTD6416	SINZATO ENTERTAINMENT LTDA6450	RDF VEICULOS LTDA6501	MD TREINAMENTOS E DESENVOLVIMENTO L6652	RAZEC EMPRESA DE APOIO ADMINISTRATI6766	MASTER IN THREADS CURSOS E EVENTOS6794	C.M.A EDUCACIONAL LTDA6796	COLÉGIO JOAQUIM MARIA MACHADO DE AS6798	LFJ TRANSPORTE LTDA6930	DOMENICO BIEMMI FRANCISCO LEITE6415	FABIO PEREIRA DA COSTAERRO DE BAIXA5084	REPUME REPUXAÇÃO E METALURGICA LTDA5292	EZEKY LTDA</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
@@ -21738,48 +21830,38 @@
       <c r="G270" s="1" t="n"/>
       <c r="H270" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46220.38165829861</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46223</v>
+        <v>46097</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Larissa Félix</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
       <c r="O270" s="1" t="n"/>
-      <c r="P270" s="2" t="n">
-        <v>46220.46443684028</v>
-      </c>
-      <c r="Q270" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R270" s="1" t="inlineStr">
-        <is>
-          <t>Tarefas baixadas</t>
-        </is>
-      </c>
+      <c r="P270" s="1" t="n"/>
+      <c r="Q270" s="1" t="inlineStr"/>
+      <c r="R270" s="1" t="inlineStr"/>
       <c r="S270" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T270" s="1" t="n"/>
@@ -21787,26 +21869,26 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>77913</v>
+        <v>79609</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
@@ -21815,7 +21897,7 @@
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
@@ -21824,10 +21906,10 @@
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46097</v>
+        <v>46205</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
@@ -21836,7 +21918,7 @@
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
@@ -21854,7 +21936,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>79609</v>
+        <v>80515</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
@@ -21863,7 +21945,7 @@
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
@@ -21873,7 +21955,7 @@
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
@@ -21882,7 +21964,7 @@
       <c r="G272" s="1" t="n"/>
       <c r="H272" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I272" s="1" t="inlineStr">
@@ -21891,26 +21973,32 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46205</v>
+        <v>46226</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
-        </is>
-      </c>
-      <c r="N272" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>46219.75157017361</v>
+      </c>
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="1" t="n"/>
       <c r="Q272" s="1" t="inlineStr"/>
-      <c r="R272" s="1" t="inlineStr"/>
+      <c r="R272" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enviado para registro </t>
+        </is>
+      </c>
       <c r="S272" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21921,7 +22009,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>80515</v>
+        <v>80697</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -21930,7 +22018,7 @@
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -21940,7 +22028,7 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -21949,7 +22037,7 @@
       <c r="G273" s="1" t="n"/>
       <c r="H273" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I273" s="1" t="inlineStr">
@@ -21958,14 +22046,14 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M273" s="1" t="inlineStr">
@@ -21973,17 +22061,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N273" s="2" t="n">
-        <v>46219.75157017361</v>
-      </c>
+      <c r="N273" s="1" t="n"/>
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="1" t="n"/>
       <c r="Q273" s="1" t="inlineStr"/>
-      <c r="R273" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enviado para registro </t>
-        </is>
-      </c>
+      <c r="R273" s="1" t="inlineStr"/>
       <c r="S273" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -21994,7 +22076,7 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80697</v>
+        <v>80714</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
@@ -22003,7 +22085,7 @@
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -22013,7 +22095,7 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22022,7 +22104,7 @@
       <c r="G274" s="1" t="n"/>
       <c r="H274" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I274" s="1" t="inlineStr">
@@ -22031,14 +22113,14 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M274" s="1" t="inlineStr">
@@ -22046,11 +22128,18 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N274" s="1" t="n"/>
+      <c r="N274" s="2" t="n">
+        <v>46223.41822326389</v>
+      </c>
       <c r="O274" s="1" t="n"/>
       <c r="P274" s="1" t="n"/>
       <c r="Q274" s="1" t="inlineStr"/>
-      <c r="R274" s="1" t="inlineStr"/>
+      <c r="R274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROCESSO ENCONTRA-SE EM ANDAMENTO. 
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL. </t>
+        </is>
+      </c>
       <c r="S274" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22061,16 +22150,16 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>80714</v>
+        <v>80919</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -22080,7 +22169,7 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
@@ -22089,7 +22178,7 @@
       <c r="G275" s="1" t="n"/>
       <c r="H275" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I275" s="1" t="inlineStr">
@@ -22098,10 +22187,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22128,16 +22217,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>80919</v>
+        <v>80935</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -22147,7 +22236,7 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
@@ -22156,7 +22245,7 @@
       <c r="G276" s="1" t="n"/>
       <c r="H276" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I276" s="1" t="inlineStr">
@@ -22165,14 +22254,14 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
@@ -22180,11 +22269,18 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N276" s="1" t="n"/>
+      <c r="N276" s="2" t="n">
+        <v>46223.41869637732</v>
+      </c>
       <c r="O276" s="1" t="n"/>
       <c r="P276" s="1" t="n"/>
       <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="inlineStr"/>
+      <c r="R276" s="1" t="inlineStr">
+        <is>
+          <t>PROCESSO ENCONTRA-SE EM ANDAMENTO.
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL.</t>
+        </is>
+      </c>
       <c r="S276" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22195,7 +22291,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80935</v>
+        <v>80936</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22204,7 +22300,7 @@
       </c>
       <c r="C277" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D277" s="1" t="inlineStr">
@@ -22214,7 +22310,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
@@ -22223,7 +22319,7 @@
       <c r="G277" s="1" t="n"/>
       <c r="H277" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I277" s="1" t="inlineStr">
@@ -22232,14 +22328,14 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K277" s="2" t="n">
         <v>46241</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
@@ -22247,11 +22343,17 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N277" s="1" t="n"/>
+      <c r="N277" s="2" t="n">
+        <v>46220.45547311343</v>
+      </c>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="inlineStr"/>
+      <c r="R277" s="1" t="inlineStr">
+        <is>
+          <t>Minuta enviado ao cliente</t>
+        </is>
+      </c>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22262,7 +22364,7 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80936</v>
+        <v>80951</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
@@ -22271,7 +22373,7 @@
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
@@ -22281,7 +22383,7 @@
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
@@ -22299,7 +22401,7 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K278" s="2" t="n">
         <v>46241</v>
@@ -22315,14 +22417,14 @@
         </is>
       </c>
       <c r="N278" s="2" t="n">
-        <v>46220.45547311343</v>
+        <v>46219.74920023148</v>
       </c>
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>Minuta enviado ao cliente</t>
+          <t>Minuta enviada ao cliente</t>
         </is>
       </c>
       <c r="S278" s="1" t="inlineStr">
@@ -22335,26 +22437,26 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>80951</v>
+        <v>80989</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
@@ -22363,7 +22465,7 @@
       <c r="G279" s="1" t="n"/>
       <c r="H279" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I279" s="1" t="inlineStr">
@@ -22372,32 +22474,26 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46241</v>
+        <v>46217</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="n">
-        <v>46219.74920023148</v>
-      </c>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="N279" s="1" t="n"/>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="inlineStr">
-        <is>
-          <t>Minuta enviada ao cliente</t>
-        </is>
-      </c>
+      <c r="R279" s="1" t="inlineStr"/>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22408,35 +22504,39 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>80989</v>
+        <v>79793</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G280" s="1" t="n"/>
+        <v>5655</v>
+      </c>
+      <c r="G280" s="1" t="inlineStr">
+        <is>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
       <c r="H280" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I280" s="1" t="inlineStr">
@@ -22445,10 +22545,10 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46217</v>
+        <v>46185</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
@@ -22457,7 +22557,7 @@
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N280" s="1" t="n"/>
@@ -22475,34 +22575,34 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>79793</v>
+        <v>81004</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>5655</v>
+        <v>6869</v>
       </c>
       <c r="G281" s="1" t="inlineStr">
         <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
       <c r="H281" s="1" t="inlineStr">
@@ -22516,10 +22616,10 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -22528,7 +22628,7 @@
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
@@ -22546,7 +22646,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>81004</v>
+        <v>81005</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
@@ -22569,16 +22669,16 @@
         </is>
       </c>
       <c r="F282" s="1" t="n">
-        <v>6869</v>
+        <v>6870</v>
       </c>
       <c r="G282" s="1" t="inlineStr">
         <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+          <t>AC HOME PET RAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H282" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I282" s="1" t="inlineStr">
@@ -22587,7 +22687,7 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K282" s="2" t="n">
         <v>46218</v>
@@ -22617,39 +22717,39 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>81005</v>
+        <v>81091</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
-        <v>6870</v>
+        <v>6907</v>
       </c>
       <c r="G283" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
         </is>
       </c>
       <c r="H283" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Edney Xavier</t>
         </is>
       </c>
       <c r="I283" s="1" t="inlineStr">
@@ -22658,10 +22758,10 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46219.3374690162</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
@@ -22670,7 +22770,7 @@
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
@@ -22688,34 +22788,34 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>81091</v>
+        <v>79833</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
-        <v>6907</v>
+        <v>6125</v>
       </c>
       <c r="G284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H284" s="1" t="inlineStr">
@@ -22725,30 +22825,36 @@
       </c>
       <c r="I284" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>PL - AUDITORIA</t>
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46219.3374690162</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46223</v>
+        <v>46184</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
-        </is>
-      </c>
-      <c r="N284" s="1" t="n"/>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
+      <c r="N284" s="2" t="n">
+        <v>46219.71277496528</v>
+      </c>
       <c r="O284" s="1" t="n"/>
       <c r="P284" s="1" t="n"/>
       <c r="Q284" s="1" t="inlineStr"/>
-      <c r="R284" s="1" t="inlineStr"/>
+      <c r="R284" s="1" t="inlineStr">
+        <is>
+          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
+        </is>
+      </c>
       <c r="S284" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22759,7 +22865,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>79833</v>
+        <v>79834</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
@@ -22782,11 +22888,11 @@
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>6125</v>
+        <v>6162</v>
       </c>
       <c r="G285" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H285" s="1" t="inlineStr">
@@ -22800,14 +22906,14 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K285" s="2" t="n">
         <v>46184</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
@@ -22815,17 +22921,11 @@
           <t>Tatiana Linardi</t>
         </is>
       </c>
-      <c r="N285" s="2" t="n">
-        <v>46219.71277496528</v>
-      </c>
+      <c r="N285" s="1" t="n"/>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="inlineStr">
-        <is>
-          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
-        </is>
-      </c>
+      <c r="R285" s="1" t="inlineStr"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22836,16 +22936,16 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>79834</v>
+        <v>79865</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
@@ -22855,15 +22955,15 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6162</v>
+        <v>6278</v>
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H286" s="1" t="inlineStr">
@@ -22877,10 +22977,10 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K286" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
@@ -22889,7 +22989,7 @@
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N286" s="1" t="n"/>
@@ -22907,7 +23007,7 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>79865</v>
+        <v>79854</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
@@ -22926,15 +23026,15 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6278</v>
+        <v>6302</v>
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H287" s="1" t="inlineStr">
@@ -22948,10 +23048,10 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
@@ -22960,7 +23060,7 @@
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N287" s="1" t="n"/>
@@ -22978,7 +23078,7 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>79854</v>
+        <v>79863</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
@@ -22997,15 +23097,15 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>6302</v>
+        <v>6404</v>
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H288" s="1" t="inlineStr">
@@ -23019,10 +23119,10 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
@@ -23031,7 +23131,7 @@
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N288" s="1" t="n"/>
@@ -23049,16 +23149,16 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79863</v>
+        <v>79835</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr">
@@ -23068,15 +23168,15 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>6404</v>
+        <v>6485</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H289" s="1" t="inlineStr">
@@ -23090,10 +23190,10 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
@@ -23102,7 +23202,7 @@
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N289" s="1" t="n"/>
@@ -23120,16 +23220,16 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79835</v>
+        <v>79866</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
@@ -23139,15 +23239,15 @@
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>6485</v>
+        <v>6539</v>
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H290" s="1" t="inlineStr">
@@ -23161,10 +23261,10 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
@@ -23173,7 +23273,7 @@
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
@@ -23191,7 +23291,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>79866</v>
+        <v>79859</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
@@ -23210,15 +23310,15 @@
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6539</v>
+        <v>6570</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H291" s="1" t="inlineStr">
@@ -23232,7 +23332,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K291" s="2" t="n">
         <v>46185</v>
@@ -23262,7 +23362,7 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>79859</v>
+        <v>79860</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
@@ -23281,15 +23381,15 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6570</v>
+        <v>6581</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H292" s="1" t="inlineStr">
@@ -23303,7 +23403,7 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K292" s="2" t="n">
         <v>46185</v>
@@ -23333,7 +23433,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>79860</v>
+        <v>79861</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
@@ -23352,15 +23452,15 @@
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>6581</v>
+        <v>6583</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H293" s="1" t="inlineStr">
@@ -23374,7 +23474,7 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K293" s="2" t="n">
         <v>46185</v>
@@ -23404,16 +23504,16 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79861</v>
+        <v>79867</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr">
@@ -23423,15 +23523,15 @@
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>6583</v>
+        <v>6704</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H294" s="1" t="inlineStr">
@@ -23445,7 +23545,7 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K294" s="2" t="n">
         <v>46185</v>
@@ -23475,16 +23575,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79867</v>
+        <v>79856</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
@@ -23494,15 +23594,15 @@
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>6704</v>
+        <v>4225</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
         </is>
       </c>
       <c r="H295" s="1" t="inlineStr">
@@ -23516,10 +23616,10 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K295" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L295" s="1" t="inlineStr">
         <is>
@@ -23528,7 +23628,7 @@
       </c>
       <c r="M295" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N295" s="1" t="n"/>
@@ -23546,7 +23646,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79856</v>
+        <v>79855</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
@@ -23565,15 +23665,15 @@
       </c>
       <c r="E296" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>4225</v>
+        <v>4765</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23587,10 +23687,10 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
@@ -23617,36 +23717,32 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79855</v>
+        <v>81019</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação DP</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>4765</v>
-      </c>
-      <c r="G297" s="1" t="inlineStr">
-        <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G297" s="1" t="n"/>
       <c r="H297" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23658,26 +23754,31 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K297" s="2" t="n">
-        <v>46185</v>
+        <v>46218</v>
       </c>
       <c r="L297" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Santos Karina</t>
         </is>
       </c>
       <c r="N297" s="1" t="n"/>
       <c r="O297" s="1" t="n"/>
       <c r="P297" s="1" t="n"/>
       <c r="Q297" s="1" t="inlineStr"/>
-      <c r="R297" s="1" t="inlineStr"/>
+      <c r="R297" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bom dia 
+Segue recibos conforme solictiado </t>
+        </is>
+      </c>
       <c r="S297" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23688,7 +23789,7 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>81019</v>
+        <v>81052</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
@@ -23707,7 +23808,7 @@
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
@@ -23725,10 +23826,10 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46218.38736744213</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
@@ -23737,7 +23838,7 @@
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Gabriela Peres</t>
         </is>
       </c>
       <c r="N298" s="1" t="n"/>
@@ -23746,8 +23847,7 @@
       <c r="Q298" s="1" t="inlineStr"/>
       <c r="R298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia 
-Segue recibos conforme solictiado </t>
+          <t>cobramos os documentos do antigo contador.</t>
         </is>
       </c>
       <c r="S298" s="1" t="inlineStr">
@@ -23760,7 +23860,7 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>81052</v>
+        <v>81055</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
@@ -23779,7 +23879,7 @@
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
@@ -23797,14 +23897,14 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46218.40379614583</v>
       </c>
       <c r="K299" s="2" t="n">
         <v>46219</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M299" s="1" t="inlineStr">
@@ -23812,13 +23912,15 @@
           <t>Gabriela Peres</t>
         </is>
       </c>
-      <c r="N299" s="1" t="n"/>
+      <c r="N299" s="2" t="n">
+        <v>46219.50607847222</v>
+      </c>
       <c r="O299" s="1" t="n"/>
       <c r="P299" s="1" t="n"/>
       <c r="Q299" s="1" t="inlineStr"/>
       <c r="R299" s="1" t="inlineStr">
         <is>
-          <t>cobramos os documentos do antigo contador.</t>
+          <t>Aguardando retorno dos dados do contador</t>
         </is>
       </c>
       <c r="S299" s="1" t="inlineStr">
@@ -23828,79 +23930,6 @@
       </c>
       <c r="T299" s="1" t="n"/>
       <c r="U299" s="1" t="inlineStr"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="1" t="n">
-        <v>81055</v>
-      </c>
-      <c r="B300" s="1" t="inlineStr">
-        <is>
-          <t>Auditoria</t>
-        </is>
-      </c>
-      <c r="C300" s="1" t="inlineStr">
-        <is>
-          <t>Implantação DP</t>
-        </is>
-      </c>
-      <c r="D300" s="1" t="inlineStr">
-        <is>
-          <t>DP - DEPTO. PESSOAL</t>
-        </is>
-      </c>
-      <c r="E300" s="1" t="inlineStr">
-        <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
-        </is>
-      </c>
-      <c r="F300" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G300" s="1" t="n"/>
-      <c r="H300" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
-      <c r="I300" s="1" t="inlineStr">
-        <is>
-          <t>PL - AUDITORIA</t>
-        </is>
-      </c>
-      <c r="J300" s="2" t="n">
-        <v>46218.40379614583</v>
-      </c>
-      <c r="K300" s="2" t="n">
-        <v>46219</v>
-      </c>
-      <c r="L300" s="1" t="inlineStr">
-        <is>
-          <t>Em Atendimento</t>
-        </is>
-      </c>
-      <c r="M300" s="1" t="inlineStr">
-        <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
-      <c r="O300" s="1" t="n"/>
-      <c r="P300" s="1" t="n"/>
-      <c r="Q300" s="1" t="inlineStr"/>
-      <c r="R300" s="1" t="inlineStr">
-        <is>
-          <t>Aguardando retorno dos dados do contador</t>
-        </is>
-      </c>
-      <c r="S300" s="1" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T300" s="1" t="n"/>
-      <c r="U300" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -2317,7 +2317,7 @@
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I23" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="L23" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M23" s="1" t="inlineStr">
@@ -2343,12 +2343,23 @@
       </c>
       <c r="N23" s="1" t="n"/>
       <c r="O23" s="1" t="n"/>
-      <c r="P23" s="1" t="n"/>
-      <c r="Q23" s="1" t="inlineStr"/>
-      <c r="R23" s="1" t="inlineStr"/>
+      <c r="P23" s="2" t="n">
+        <v>46223.45704140046</v>
+      </c>
+      <c r="Q23" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EMPRESA NÃO É OPTANTE PELO SIMPLES NACIONAL, O CODIGO DA EMPRESA ESTÁ CORRETO ?
+</t>
+        </is>
+      </c>
       <c r="S23" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T23" s="1" t="n"/>
@@ -5108,7 +5119,11 @@
           <t>DONA LELLA INDÚSTRIA E COMÉRCIO DE PRODUTOS PARA CONFEITARIA LTDA</t>
         </is>
       </c>
-      <c r="H57" s="1" t="n"/>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
           <t>EF - VAREJO</t>
@@ -5122,7 +5137,7 @@
       </c>
       <c r="L57" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M57" s="1" t="inlineStr">
@@ -5134,14 +5149,18 @@
       <c r="O57" s="1" t="n"/>
       <c r="P57" s="1" t="n"/>
       <c r="Q57" s="1" t="inlineStr"/>
-      <c r="R57" s="1" t="n"/>
+      <c r="R57" s="1" t="inlineStr"/>
       <c r="S57" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T57" s="1" t="n"/>
-      <c r="U57" s="1" t="inlineStr"/>
+      <c r="U57" s="1" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -5426,7 +5445,7 @@
       </c>
       <c r="H61" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I61" s="1" t="inlineStr">
@@ -5442,7 +5461,7 @@
       </c>
       <c r="L61" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M61" s="1" t="inlineStr">
@@ -5450,11 +5469,17 @@
           <t>Cristiane Simões</t>
         </is>
       </c>
-      <c r="N61" s="1" t="n"/>
+      <c r="N61" s="2" t="n">
+        <v>46223.47151377315</v>
+      </c>
       <c r="O61" s="1" t="n"/>
       <c r="P61" s="1" t="n"/>
       <c r="Q61" s="1" t="inlineStr"/>
-      <c r="R61" s="1" t="inlineStr"/>
+      <c r="R61" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPERAÇÃO RECALCULANDO </t>
+        </is>
+      </c>
       <c r="S61" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -6163,7 +6188,11 @@
           <t>MIL ACESSORIOS E PRODUTOS PARA CONFEITARIA LTDA</t>
         </is>
       </c>
-      <c r="H70" s="1" t="n"/>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
       <c r="I70" s="1" t="inlineStr">
         <is>
           <t>EF - VAREJO</t>
@@ -6177,7 +6206,7 @@
       </c>
       <c r="L70" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M70" s="1" t="inlineStr">
@@ -6189,14 +6218,18 @@
       <c r="O70" s="1" t="n"/>
       <c r="P70" s="1" t="n"/>
       <c r="Q70" s="1" t="inlineStr"/>
-      <c r="R70" s="1" t="n"/>
+      <c r="R70" s="1" t="inlineStr"/>
       <c r="S70" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
       <c r="T70" s="1" t="n"/>
-      <c r="U70" s="1" t="inlineStr"/>
+      <c r="U70" s="1" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -13037,7 +13070,7 @@
       </c>
       <c r="H153" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I153" s="1" t="inlineStr">
@@ -13053,7 +13086,7 @@
       </c>
       <c r="L153" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M153" s="1" t="inlineStr">
@@ -13063,12 +13096,23 @@
       </c>
       <c r="N153" s="1" t="n"/>
       <c r="O153" s="1" t="n"/>
-      <c r="P153" s="1" t="n"/>
-      <c r="Q153" s="1" t="inlineStr"/>
-      <c r="R153" s="1" t="inlineStr"/>
+      <c r="P153" s="2" t="n">
+        <v>46223.46573961806</v>
+      </c>
+      <c r="Q153" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R153" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">poderiam averiguar com o cliente para que ele pague a taxa ?
+No aguardo </t>
+        </is>
+      </c>
       <c r="S153" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T153" s="1" t="n"/>
@@ -13112,7 +13156,7 @@
       </c>
       <c r="H154" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I154" s="1" t="inlineStr">
@@ -13128,7 +13172,7 @@
       </c>
       <c r="L154" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M154" s="1" t="inlineStr">
@@ -13136,11 +13180,17 @@
           <t>Ana Santana</t>
         </is>
       </c>
-      <c r="N154" s="1" t="n"/>
+      <c r="N154" s="2" t="n">
+        <v>46223.45527280093</v>
+      </c>
       <c r="O154" s="1" t="n"/>
       <c r="P154" s="1" t="n"/>
       <c r="Q154" s="1" t="inlineStr"/>
-      <c r="R154" s="1" t="inlineStr"/>
+      <c r="R154" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM ANALISE PELA OPERAÇÃO </t>
+        </is>
+      </c>
       <c r="S154" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -13187,7 +13237,7 @@
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I155" s="1" t="inlineStr">
@@ -13203,7 +13253,7 @@
       </c>
       <c r="L155" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M155" s="1" t="inlineStr">
@@ -13213,12 +13263,22 @@
       </c>
       <c r="N155" s="1" t="n"/>
       <c r="O155" s="1" t="n"/>
-      <c r="P155" s="1" t="n"/>
-      <c r="Q155" s="1" t="inlineStr"/>
-      <c r="R155" s="1" t="inlineStr"/>
+      <c r="P155" s="2" t="n">
+        <v>46223.46976207176</v>
+      </c>
+      <c r="Q155" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R155" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAOR, AVERIGUAR JUNTO AO CLIENTE O PAGAMENTO DA TAXA ANUAL </t>
+        </is>
+      </c>
       <c r="S155" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T155" s="1" t="n"/>
@@ -14332,7 +14392,7 @@
       </c>
       <c r="H169" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I169" s="1" t="inlineStr">
@@ -14348,7 +14408,7 @@
       </c>
       <c r="L169" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M169" s="1" t="inlineStr">
@@ -14358,12 +14418,22 @@
       </c>
       <c r="N169" s="1" t="n"/>
       <c r="O169" s="1" t="n"/>
-      <c r="P169" s="1" t="n"/>
-      <c r="Q169" s="1" t="inlineStr"/>
-      <c r="R169" s="1" t="inlineStr"/>
+      <c r="P169" s="2" t="n">
+        <v>46223.47283167824</v>
+      </c>
+      <c r="Q169" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R169" s="1" t="inlineStr">
+        <is>
+          <t>NÃO ENTENDI O CHAMADO</t>
+        </is>
+      </c>
       <c r="S169" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T169" s="1" t="n"/>
@@ -14496,7 +14566,7 @@
       </c>
       <c r="H171" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I171" s="1" t="inlineStr">
@@ -14512,7 +14582,7 @@
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M171" s="1" t="inlineStr">
@@ -14522,12 +14592,23 @@
       </c>
       <c r="N171" s="1" t="n"/>
       <c r="O171" s="1" t="n"/>
-      <c r="P171" s="1" t="n"/>
-      <c r="Q171" s="1" t="inlineStr"/>
-      <c r="R171" s="1" t="inlineStr"/>
+      <c r="P171" s="2" t="n">
+        <v>46223.46101160879</v>
+      </c>
+      <c r="Q171" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R171" s="1" t="inlineStr">
+        <is>
+          <t>BOM DIA, 
+JÁ SOLICITADO</t>
+        </is>
+      </c>
       <c r="S171" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T171" s="1" t="n"/>
@@ -14648,7 +14729,7 @@
       </c>
       <c r="H173" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I173" s="1" t="inlineStr">
@@ -14664,7 +14745,7 @@
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M173" s="1" t="inlineStr">
@@ -14672,11 +14753,17 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N173" s="1" t="n"/>
+      <c r="N173" s="2" t="n">
+        <v>46223.46244545139</v>
+      </c>
       <c r="O173" s="1" t="n"/>
       <c r="P173" s="1" t="n"/>
       <c r="Q173" s="1" t="inlineStr"/>
-      <c r="R173" s="1" t="inlineStr"/>
+      <c r="R173" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM ATENDIMENTO PELA OPERAÇÃO </t>
+        </is>
+      </c>
       <c r="S173" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -138,8 +138,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U300" headerRowCount="1">
-  <autoFilter ref="A1:U300"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:U302" headerRowCount="1">
+  <autoFilter ref="A1:U302"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Id"/>
     <tableColumn id="2" name="Categoria"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U300"/>
+  <dimension ref="A1:U302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1113,7 +1113,7 @@
       </c>
       <c r="L8" s="1" t="inlineStr">
         <is>
-          <t>Devolvido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M8" s="1" t="inlineStr">
@@ -1123,8 +1123,14 @@
       </c>
       <c r="N8" s="1" t="n"/>
       <c r="O8" s="1" t="n"/>
-      <c r="P8" s="1" t="n"/>
-      <c r="Q8" s="1" t="inlineStr"/>
+      <c r="P8" s="2" t="n">
+        <v>46223.53752623843</v>
+      </c>
+      <c r="Q8" s="1" t="inlineStr">
+        <is>
+          <t>Andrea Medeiros</t>
+        </is>
+      </c>
       <c r="R8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">AGUARDANDO RETORNO DESDE 26/05/2026 - ANALISE ENVIADA VIA E-MAIL </t>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T8" s="1" t="n"/>
@@ -21875,26 +21881,26 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>77913</v>
+        <v>81210</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Forçar baixa de tarefas via banco de dados</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t xml:space="preserve">Boa tarde!Peço a gentileza de realizar a baixa na tarefa "GFD - FGTS Mensal" da empresa 2992 M CAVICHIOLLI, ref. a competencia 06/2026. A empresa em questão não tem guia emitida, apenas a da filial - Empresa 3204.Obrigado. </t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
@@ -21903,19 +21909,19 @@
       <c r="G269" s="1" t="n"/>
       <c r="H269" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I269" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46223.55477642361</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>46097</v>
+        <v>46223</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -21924,7 +21930,7 @@
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
+          <t>Vitor Guedes</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
@@ -21942,26 +21948,26 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>79609</v>
+        <v>81211</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Abertura de protocolo</t>
         </is>
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>MG EXPRESS - GC</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Por favor, precisamos da baixa das tarefas pendentes referente tarefa "Fed - DAS" da competência 06/2026 com os arquivos disponíveis na pasta "\\finlandia\PUBLICA\RomeroBorges\Fed - DAS"</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
@@ -21970,19 +21976,19 @@
       <c r="G270" s="1" t="n"/>
       <c r="H270" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Gabriel Amaral</t>
         </is>
       </c>
       <c r="I270" s="1" t="inlineStr">
         <is>
-          <t>PARALEGAL</t>
+          <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46223.56040540509</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46205</v>
+        <v>46224</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
@@ -21991,7 +21997,7 @@
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
+          <t>Romero Borges</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
@@ -22009,26 +22015,26 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>80515</v>
+        <v>77913</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
@@ -22037,7 +22043,7 @@
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
@@ -22046,32 +22052,26 @@
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46226</v>
+        <v>46097</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
-        </is>
-      </c>
-      <c r="N271" s="2" t="n">
-        <v>46219.75157017361</v>
-      </c>
+          <t>Larissa Félix</t>
+        </is>
+      </c>
+      <c r="N271" s="1" t="n"/>
       <c r="O271" s="1" t="n"/>
       <c r="P271" s="1" t="n"/>
       <c r="Q271" s="1" t="inlineStr"/>
-      <c r="R271" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enviado para registro </t>
-        </is>
-      </c>
+      <c r="R271" s="1" t="inlineStr"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22082,7 +22082,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>80697</v>
+        <v>79609</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
@@ -22119,10 +22119,10 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46237</v>
+        <v>46205</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>Claudio Correa</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
@@ -22149,7 +22149,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>80714</v>
+        <v>80515</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -22177,7 +22177,7 @@
       <c r="G273" s="1" t="n"/>
       <c r="H273" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I273" s="1" t="inlineStr">
@@ -22186,10 +22186,10 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46241</v>
+        <v>46226</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
@@ -22202,15 +22202,14 @@
         </is>
       </c>
       <c r="N273" s="2" t="n">
-        <v>46223.41822326389</v>
+        <v>46219.75157017361</v>
       </c>
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="1" t="n"/>
       <c r="Q273" s="1" t="inlineStr"/>
       <c r="R273" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PROCESSO ENCONTRA-SE EM ANDAMENTO. 
-TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL. </t>
+          <t xml:space="preserve">Enviado para registro </t>
         </is>
       </c>
       <c r="S273" s="1" t="inlineStr">
@@ -22223,16 +22222,16 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80919</v>
+        <v>80697</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D274" s="1" t="inlineStr">
@@ -22242,7 +22241,7 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22260,10 +22259,10 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46239</v>
+        <v>46237</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
@@ -22290,7 +22289,7 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>80935</v>
+        <v>80714</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
@@ -22299,7 +22298,7 @@
       </c>
       <c r="C275" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D275" s="1" t="inlineStr">
@@ -22309,7 +22308,7 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
@@ -22327,7 +22326,7 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K275" s="2" t="n">
         <v>46241</v>
@@ -22343,15 +22342,15 @@
         </is>
       </c>
       <c r="N275" s="2" t="n">
-        <v>46223.41869637732</v>
+        <v>46223.41822326389</v>
       </c>
       <c r="O275" s="1" t="n"/>
       <c r="P275" s="1" t="n"/>
       <c r="Q275" s="1" t="inlineStr"/>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t>PROCESSO ENCONTRA-SE EM ANDAMENTO.
-TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL.</t>
+          <t xml:space="preserve">PROCESSO ENCONTRA-SE EM ANDAMENTO. 
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL. </t>
         </is>
       </c>
       <c r="S275" s="1" t="inlineStr">
@@ -22364,16 +22363,16 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>80936</v>
+        <v>80919</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
@@ -22383,7 +22382,7 @@
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
@@ -22392,7 +22391,7 @@
       <c r="G276" s="1" t="n"/>
       <c r="H276" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I276" s="1" t="inlineStr">
@@ -22401,14 +22400,14 @@
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
@@ -22416,17 +22415,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N276" s="2" t="n">
-        <v>46220.45547311343</v>
-      </c>
+      <c r="N276" s="1" t="n"/>
       <c r="O276" s="1" t="n"/>
       <c r="P276" s="1" t="n"/>
       <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="inlineStr">
-        <is>
-          <t>Minuta enviado ao cliente</t>
-        </is>
-      </c>
+      <c r="R276" s="1" t="inlineStr"/>
       <c r="S276" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22437,7 +22430,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>80951</v>
+        <v>80935</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22456,7 +22449,7 @@
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
@@ -22465,7 +22458,7 @@
       <c r="G277" s="1" t="n"/>
       <c r="H277" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I277" s="1" t="inlineStr">
@@ -22474,7 +22467,7 @@
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K277" s="2" t="n">
         <v>46241</v>
@@ -22490,14 +22483,15 @@
         </is>
       </c>
       <c r="N277" s="2" t="n">
-        <v>46219.74920023148</v>
+        <v>46223.41869637732</v>
       </c>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
       <c r="R277" s="1" t="inlineStr">
         <is>
-          <t>Minuta enviada ao cliente</t>
+          <t>PROCESSO ENCONTRA-SE EM ANDAMENTO.
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL.</t>
         </is>
       </c>
       <c r="S277" s="1" t="inlineStr">
@@ -22510,26 +22504,26 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>80989</v>
+        <v>80936</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
@@ -22538,7 +22532,7 @@
       <c r="G278" s="1" t="n"/>
       <c r="H278" s="1" t="inlineStr">
         <is>
-          <t>Ellen Leite</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I278" s="1" t="inlineStr">
@@ -22547,10 +22541,10 @@
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46217</v>
+        <v>46241</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
@@ -22559,18 +22553,18 @@
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
+          <t>Raisa Sousa</t>
         </is>
       </c>
       <c r="N278" s="2" t="n">
-        <v>46223.4927846875</v>
+        <v>46220.45547311343</v>
       </c>
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
       <c r="R278" s="1" t="inlineStr">
         <is>
-          <t>Solicitação enviada à Prefeitura, aguardando retorno.</t>
+          <t>Minuta enviado ao cliente</t>
         </is>
       </c>
       <c r="S278" s="1" t="inlineStr">
@@ -22583,63 +22577,69 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>81208</v>
+        <v>80951</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião de Sócios</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Reeleição de Diretoria</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, encaminhar a Ata registrada para o cliente.</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
-        <v>5449</v>
-      </c>
-      <c r="G279" s="1" t="inlineStr">
-        <is>
-          <t>RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA</t>
-        </is>
-      </c>
-      <c r="H279" s="1" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="G279" s="1" t="n"/>
+      <c r="H279" s="1" t="inlineStr">
+        <is>
+          <t>Thifany Leite</t>
+        </is>
+      </c>
       <c r="I279" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46223.51713209491</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46225</v>
+        <v>46241</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
-        </is>
-      </c>
-      <c r="N279" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>46219.74920023148</v>
+      </c>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="n"/>
+      <c r="R279" s="1" t="inlineStr">
+        <is>
+          <t>Minuta enviada ao cliente</t>
+        </is>
+      </c>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22650,39 +22650,35 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>79793</v>
+        <v>80989</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
-        <v>5655</v>
-      </c>
-      <c r="G280" s="1" t="inlineStr">
-        <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G280" s="1" t="n"/>
       <c r="H280" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I280" s="1" t="inlineStr">
@@ -22691,26 +22687,32 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46185</v>
+        <v>46217</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
-        </is>
-      </c>
-      <c r="N280" s="1" t="n"/>
+          <t>João Oliveira</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>46223.4927846875</v>
+      </c>
       <c r="O280" s="1" t="n"/>
       <c r="P280" s="1" t="n"/>
       <c r="Q280" s="1" t="inlineStr"/>
-      <c r="R280" s="1" t="inlineStr"/>
+      <c r="R280" s="1" t="inlineStr">
+        <is>
+          <t>Solicitação enviada à Prefeitura, aguardando retorno.</t>
+        </is>
+      </c>
       <c r="S280" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22721,34 +22723,34 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>81209</v>
+        <v>81208</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Ata de Reunião de Sócios</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Reeleição de Diretoria</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
+          <t>Por gentileza, encaminhar a Ata registrada para o cliente.</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
-        <v>6094</v>
+        <v>5449</v>
       </c>
       <c r="G281" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
+          <t>RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA</t>
         </is>
       </c>
       <c r="H281" s="1" t="n"/>
@@ -22758,10 +22760,10 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46223.52088677084</v>
+        <v>46223.51713209491</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
@@ -22770,7 +22772,7 @@
       </c>
       <c r="M281" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="N281" s="1" t="n"/>
@@ -22788,34 +22790,34 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>81004</v>
+        <v>79793</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
-        <v>6869</v>
+        <v>5655</v>
       </c>
       <c r="G282" s="1" t="inlineStr">
         <is>
-          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
+          <t>VANESSA DUARTE RODRIGUES</t>
         </is>
       </c>
       <c r="H282" s="1" t="inlineStr">
@@ -22829,10 +22831,10 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46217.37983028935</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>46218</v>
+        <v>46185</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
@@ -22841,7 +22843,7 @@
       </c>
       <c r="M282" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N282" s="1" t="n"/>
@@ -22859,67 +22861,63 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>81005</v>
+        <v>81209</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Cadastro de Cliente</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alteração </t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
+          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
-        <v>6870</v>
+        <v>6094</v>
       </c>
       <c r="G283" s="1" t="inlineStr">
         <is>
-          <t>AC HOME PET RAÇÕES LTDA</t>
-        </is>
-      </c>
-      <c r="H283" s="1" t="inlineStr">
-        <is>
-          <t>Ronaldo Dias</t>
-        </is>
-      </c>
+          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
+        </is>
+      </c>
+      <c r="H283" s="1" t="n"/>
       <c r="I283" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46217.38025162037</v>
+        <v>46223.52088677084</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N283" s="1" t="n"/>
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="inlineStr"/>
+      <c r="R283" s="1" t="n"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22930,34 +22928,34 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>81091</v>
+        <v>81004</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>Outra</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
-        <v>6907</v>
+        <v>6869</v>
       </c>
       <c r="G284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
+          <t>PET HOME EXPRESS COMERCIO DE RACOES LTDA</t>
         </is>
       </c>
       <c r="H284" s="1" t="inlineStr">
@@ -22971,10 +22969,10 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46219.3374690162</v>
+        <v>46217.37983028935</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46223</v>
+        <v>46218</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
@@ -22983,7 +22981,7 @@
       </c>
       <c r="M284" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N284" s="1" t="n"/>
@@ -23001,73 +22999,67 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>79833</v>
+        <v>81005</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Bom dia! Referente AS LOJAS 6869 e 6870 do grupo PET HOME – ao fazer a entrega da SEDIF mostra que o CPF do responsável esta invalido, porem esta conforme o MG CONTROLE, pode nos ajudar com esse caso?</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
-        <v>6125</v>
+        <v>6870</v>
       </c>
       <c r="G285" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t>AC HOME PET RAÇÕES LTDA</t>
         </is>
       </c>
       <c r="H285" s="1" t="inlineStr">
         <is>
-          <t>Edney Xavier</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I285" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46183.45917465278</v>
+        <v>46217.38025162037</v>
       </c>
       <c r="K285" s="2" t="n">
-        <v>46184</v>
+        <v>46218</v>
       </c>
       <c r="L285" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M285" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
-        </is>
-      </c>
-      <c r="N285" s="2" t="n">
-        <v>46219.71277496528</v>
-      </c>
+          <t>Lorrane Santos</t>
+        </is>
+      </c>
+      <c r="N285" s="1" t="n"/>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
-      <c r="R285" s="1" t="inlineStr">
-        <is>
-          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
-        </is>
-      </c>
+      <c r="R285" s="1" t="inlineStr"/>
       <c r="S285" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23078,34 +23070,34 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>79834</v>
+        <v>81091</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Outra</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>Favor providenciar login e senha ou regularizar pois CPF não bate com o cadastrado no SEDIF.</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
-        <v>6162</v>
+        <v>6907</v>
       </c>
       <c r="G286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
+          <t xml:space="preserve">JDM DISTRIBUIDORA DE PRODUTOS ALIMENTÍCIOS LTDA </t>
         </is>
       </c>
       <c r="H286" s="1" t="inlineStr">
@@ -23115,14 +23107,14 @@
       </c>
       <c r="I286" s="1" t="inlineStr">
         <is>
-          <t>PL - AUDITORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46183.45954846065</v>
+        <v>46219.3374690162</v>
       </c>
       <c r="K286" s="2" t="n">
-        <v>46184</v>
+        <v>46223</v>
       </c>
       <c r="L286" s="1" t="inlineStr">
         <is>
@@ -23131,7 +23123,7 @@
       </c>
       <c r="M286" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N286" s="1" t="n"/>
@@ -23149,16 +23141,16 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>79865</v>
+        <v>79833</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
@@ -23168,15 +23160,15 @@
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
-        <v>6278</v>
+        <v>6125</v>
       </c>
       <c r="G287" s="1" t="inlineStr">
         <is>
-          <t>EMPORIO DOS FRIOS LTDA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H287" s="1" t="inlineStr">
@@ -23190,26 +23182,32 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46183.62243564815</v>
+        <v>46183.45917465278</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
-        </is>
-      </c>
-      <c r="N287" s="1" t="n"/>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
+      <c r="N287" s="2" t="n">
+        <v>46219.71277496528</v>
+      </c>
       <c r="O287" s="1" t="n"/>
       <c r="P287" s="1" t="n"/>
       <c r="Q287" s="1" t="inlineStr"/>
-      <c r="R287" s="1" t="inlineStr"/>
+      <c r="R287" s="1" t="inlineStr">
+        <is>
+          <t>Cobramos o antigo contador, porem nao tivemos retorno</t>
+        </is>
+      </c>
       <c r="S287" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23220,16 +23218,16 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>79854</v>
+        <v>79834</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
@@ -23239,15 +23237,15 @@
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>6302</v>
+        <v>6162</v>
       </c>
       <c r="G288" s="1" t="inlineStr">
         <is>
-          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
+          <t xml:space="preserve">RENOVACAO EMPREENDIMENTOS HOTELEIROS LTDA </t>
         </is>
       </c>
       <c r="H288" s="1" t="inlineStr">
@@ -23261,7 +23259,7 @@
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46183.60582329861</v>
+        <v>46183.45954846065</v>
       </c>
       <c r="K288" s="2" t="n">
         <v>46184</v>
@@ -23291,7 +23289,7 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>79863</v>
+        <v>79865</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
@@ -23310,15 +23308,15 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/06/2025, da empresa 6278.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>6404</v>
+        <v>6278</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>SOLAR INVESTIMENTOS LTDA</t>
+          <t>EMPORIO DOS FRIOS LTDA</t>
         </is>
       </c>
       <c r="H289" s="1" t="inlineStr">
@@ -23332,7 +23330,7 @@
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46183.6188202199</v>
+        <v>46183.62243564815</v>
       </c>
       <c r="K289" s="2" t="n">
         <v>46185</v>
@@ -23362,16 +23360,16 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79835</v>
+        <v>79854</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
@@ -23381,15 +23379,15 @@
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
+          <t>6302 - Coocerqui - Para enviar o Sped 2025 precisamos do Sped do periodo do ex contador ( Adriano ).</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>6485</v>
+        <v>6302</v>
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>SMA AGRONEGOCIOS LTDA</t>
+          <t>COOPERATIVA DE CONSUMO POPULAR DE CERQUILHO (MATRIZ)</t>
         </is>
       </c>
       <c r="H290" s="1" t="inlineStr">
@@ -23403,7 +23401,7 @@
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46183.45993642361</v>
+        <v>46183.60582329861</v>
       </c>
       <c r="K290" s="2" t="n">
         <v>46184</v>
@@ -23433,7 +23431,7 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>79866</v>
+        <v>79863</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
@@ -23452,15 +23450,15 @@
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/08/2025, da empresa 6404.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6539</v>
+        <v>6404</v>
       </c>
       <c r="G291" s="1" t="inlineStr">
         <is>
-          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
+          <t>SOLAR INVESTIMENTOS LTDA</t>
         </is>
       </c>
       <c r="H291" s="1" t="inlineStr">
@@ -23474,7 +23472,7 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46183.62343017361</v>
+        <v>46183.6188202199</v>
       </c>
       <c r="K291" s="2" t="n">
         <v>46185</v>
@@ -23504,16 +23502,16 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>79859</v>
+        <v>79835</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
@@ -23523,15 +23521,15 @@
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Favor solicitar o balancete de implantação para a entrega do Sped 2025</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
-        <v>6570</v>
+        <v>6485</v>
       </c>
       <c r="G292" s="1" t="inlineStr">
         <is>
-          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
+          <t>SMA AGRONEGOCIOS LTDA</t>
         </is>
       </c>
       <c r="H292" s="1" t="inlineStr">
@@ -23545,10 +23543,10 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46183.61569366898</v>
+        <v>46183.45993642361</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
@@ -23557,7 +23555,7 @@
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
-          <t>Fernanda Araujo</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N292" s="1" t="n"/>
@@ -23575,7 +23573,7 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>79860</v>
+        <v>79866</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
@@ -23594,15 +23592,15 @@
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 31/10/2025, da empresa 6539.A primeira solicitação foi feita por e-mail em 05/06.</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
-        <v>6581</v>
+        <v>6539</v>
       </c>
       <c r="G293" s="1" t="inlineStr">
         <is>
-          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
+          <t>TECHFEED ADITIVOS PARA NUTRICAO ANIMAL LTDA</t>
         </is>
       </c>
       <c r="H293" s="1" t="inlineStr">
@@ -23616,7 +23614,7 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46183.61707056713</v>
+        <v>46183.62343017361</v>
       </c>
       <c r="K293" s="2" t="n">
         <v>46185</v>
@@ -23646,7 +23644,7 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>79861</v>
+        <v>79859</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
@@ -23665,15 +23663,15 @@
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6570.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
-        <v>6583</v>
+        <v>6570</v>
       </c>
       <c r="G294" s="1" t="inlineStr">
         <is>
-          <t>DROGA MX LTDA (MATRIZ)</t>
+          <t>DROGARIA MIX I LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H294" s="1" t="inlineStr">
@@ -23687,7 +23685,7 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46183.61758677083</v>
+        <v>46183.61569366898</v>
       </c>
       <c r="K294" s="2" t="n">
         <v>46185</v>
@@ -23717,16 +23715,16 @@
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>79867</v>
+        <v>79860</v>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
         <is>
-          <t>Implantação Contábil</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D295" s="1" t="inlineStr">
@@ -23736,15 +23734,15 @@
       </c>
       <c r="E295" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6581.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F295" s="1" t="n">
-        <v>6704</v>
+        <v>6581</v>
       </c>
       <c r="G295" s="1" t="inlineStr">
         <is>
-          <t>TECNO COM INFORMATICA LTDA</t>
+          <t>PARIS STORE PERFUMARIA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H295" s="1" t="inlineStr">
@@ -23758,7 +23756,7 @@
         </is>
       </c>
       <c r="J295" s="2" t="n">
-        <v>46183.62582114583</v>
+        <v>46183.61707056713</v>
       </c>
       <c r="K295" s="2" t="n">
         <v>46185</v>
@@ -23788,7 +23786,7 @@
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>79856</v>
+        <v>79861</v>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
@@ -23807,15 +23805,15 @@
       </c>
       <c r="E296" s="1" t="inlineStr">
         <is>
-          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Boa tarde! Por favor, preciso que seja solicitado ao antigo contador a ECD , de 01/01/2025 a 30/09/2025, da empresa 6583.A primeira solicitação foi feita por e-mail em 18/05.</t>
         </is>
       </c>
       <c r="F296" s="1" t="n">
-        <v>4225</v>
+        <v>6583</v>
       </c>
       <c r="G296" s="1" t="inlineStr">
         <is>
-          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+          <t>DROGA MX LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H296" s="1" t="inlineStr">
@@ -23829,10 +23827,10 @@
         </is>
       </c>
       <c r="J296" s="2" t="n">
-        <v>46183.60759024305</v>
+        <v>46183.61758677083</v>
       </c>
       <c r="K296" s="2" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="L296" s="1" t="inlineStr">
         <is>
@@ -23841,7 +23839,7 @@
       </c>
       <c r="M296" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N296" s="1" t="n"/>
@@ -23859,16 +23857,16 @@
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>79855</v>
+        <v>79867</v>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>Arquivo</t>
+          <t>Auditoria</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
         <is>
-          <t>Solicitação de Documentos</t>
+          <t>Implantação Contábil</t>
         </is>
       </c>
       <c r="D297" s="1" t="inlineStr">
@@ -23878,15 +23876,15 @@
       </c>
       <c r="E297" s="1" t="inlineStr">
         <is>
-          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
+          <t>Boa tarde!Por favor, solicitar ao antigo contador balanço abertura.</t>
         </is>
       </c>
       <c r="F297" s="1" t="n">
-        <v>4765</v>
+        <v>6704</v>
       </c>
       <c r="G297" s="1" t="inlineStr">
         <is>
-          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+          <t>TECNO COM INFORMATICA LTDA</t>
         </is>
       </c>
       <c r="H297" s="1" t="inlineStr">
@@ -23900,7 +23898,7 @@
         </is>
       </c>
       <c r="J297" s="2" t="n">
-        <v>46183.60712457176</v>
+        <v>46183.62582114583</v>
       </c>
       <c r="K297" s="2" t="n">
         <v>46185</v>
@@ -23912,7 +23910,7 @@
       </c>
       <c r="M297" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Fernanda Araujo</t>
         </is>
       </c>
       <c r="N297" s="1" t="n"/>
@@ -23930,32 +23928,36 @@
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
-        <v>81019</v>
+        <v>79856</v>
       </c>
       <c r="B298" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C298" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D298" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E298" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
+          <t>verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F298" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G298" s="1" t="n"/>
+        <v>4225</v>
+      </c>
+      <c r="G298" s="1" t="inlineStr">
+        <is>
+          <t>ORGANIZAÇÕES FARINHA PURA LTDA</t>
+        </is>
+      </c>
       <c r="H298" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -23967,31 +23969,26 @@
         </is>
       </c>
       <c r="J298" s="2" t="n">
-        <v>46217.43210269676</v>
+        <v>46183.60759024305</v>
       </c>
       <c r="K298" s="2" t="n">
-        <v>46218</v>
+        <v>46184</v>
       </c>
       <c r="L298" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M298" s="1" t="inlineStr">
         <is>
-          <t>Santos Karina</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N298" s="1" t="n"/>
       <c r="O298" s="1" t="n"/>
       <c r="P298" s="1" t="n"/>
       <c r="Q298" s="1" t="inlineStr"/>
-      <c r="R298" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bom dia 
-Segue recibos conforme solictiado </t>
-        </is>
-      </c>
+      <c r="R298" s="1" t="inlineStr"/>
       <c r="S298" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -24002,32 +23999,36 @@
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>81052</v>
+        <v>79855</v>
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>Auditoria</t>
+          <t>Arquivo</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
         <is>
-          <t>Implantação DP</t>
+          <t>Solicitação de Documentos</t>
         </is>
       </c>
       <c r="D299" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E299" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+          <t>Brasileirão - verificar se o atual contador vai enviar o periodo inteiro de 2025, pois só temos 2 meses com a Mg.</t>
         </is>
       </c>
       <c r="F299" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G299" s="1" t="n"/>
+        <v>4765</v>
+      </c>
+      <c r="G299" s="1" t="inlineStr">
+        <is>
+          <t>BRASILEIRÃO ATACADO COMÉRCIO DE PRODUTOS ALIMENTICIOS SOCIEDADE ANÔNIMA</t>
+        </is>
+      </c>
       <c r="H299" s="1" t="inlineStr">
         <is>
           <t>Edney Xavier</t>
@@ -24039,30 +24040,26 @@
         </is>
       </c>
       <c r="J299" s="2" t="n">
-        <v>46218.38736744213</v>
+        <v>46183.60712457176</v>
       </c>
       <c r="K299" s="2" t="n">
-        <v>46219</v>
+        <v>46185</v>
       </c>
       <c r="L299" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M299" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N299" s="1" t="n"/>
       <c r="O299" s="1" t="n"/>
       <c r="P299" s="1" t="n"/>
       <c r="Q299" s="1" t="inlineStr"/>
-      <c r="R299" s="1" t="inlineStr">
-        <is>
-          <t>cobramos os documentos do antigo contador.</t>
-        </is>
-      </c>
+      <c r="R299" s="1" t="inlineStr"/>
       <c r="S299" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -24073,7 +24070,7 @@
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>81055</v>
+        <v>81019</v>
       </c>
       <c r="B300" s="1" t="inlineStr">
         <is>
@@ -24092,7 +24089,7 @@
       </c>
       <c r="E300" s="1" t="inlineStr">
         <is>
-          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+          <t xml:space="preserve">Por gentileza, solicitar que enviem as folhas de pagamento SEM RATEIO. </t>
         </is>
       </c>
       <c r="F300" s="1" t="n">
@@ -24110,30 +24107,29 @@
         </is>
       </c>
       <c r="J300" s="2" t="n">
-        <v>46218.40379614583</v>
+        <v>46217.43210269676</v>
       </c>
       <c r="K300" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="L300" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M300" s="1" t="inlineStr">
         <is>
-          <t>Gabriela Peres</t>
-        </is>
-      </c>
-      <c r="N300" s="2" t="n">
-        <v>46219.50607847222</v>
-      </c>
+          <t>Santos Karina</t>
+        </is>
+      </c>
+      <c r="N300" s="1" t="n"/>
       <c r="O300" s="1" t="n"/>
       <c r="P300" s="1" t="n"/>
       <c r="Q300" s="1" t="inlineStr"/>
       <c r="R300" s="1" t="inlineStr">
         <is>
-          <t>Aguardando retorno dos dados do contador</t>
+          <t xml:space="preserve">Bom dia 
+Segue recibos conforme solictiado </t>
         </is>
       </c>
       <c r="S300" s="1" t="inlineStr">
@@ -24143,6 +24139,150 @@
       </c>
       <c r="T300" s="1" t="n"/>
       <c r="U300" s="1" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="1" t="n">
+        <v>81052</v>
+      </c>
+      <c r="B301" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C301" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E301" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, providenciar os documentos pendentes no checklist anexo com urgência, já estamos no dia 15/07 e não recebemos nenhuma documentação, o atendimento ao cliente está prejudicado.</t>
+        </is>
+      </c>
+      <c r="F301" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G301" s="1" t="n"/>
+      <c r="H301" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I301" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J301" s="2" t="n">
+        <v>46218.38736744213</v>
+      </c>
+      <c r="K301" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L301" s="1" t="inlineStr">
+        <is>
+          <t>Devolvido para Responsável</t>
+        </is>
+      </c>
+      <c r="M301" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N301" s="1" t="n"/>
+      <c r="O301" s="1" t="n"/>
+      <c r="P301" s="1" t="n"/>
+      <c r="Q301" s="1" t="inlineStr"/>
+      <c r="R301" s="1" t="inlineStr">
+        <is>
+          <t>cobramos os documentos do antigo contador.</t>
+        </is>
+      </c>
+      <c r="S301" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T301" s="1" t="n"/>
+      <c r="U301" s="1" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="1" t="n">
+        <v>81055</v>
+      </c>
+      <c r="B302" s="1" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="C302" s="1" t="inlineStr">
+        <is>
+          <t>Implantação DP</t>
+        </is>
+      </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>DP - DEPTO. PESSOAL</t>
+        </is>
+      </c>
+      <c r="E302" s="1" t="inlineStr">
+        <is>
+          <t>6984 - SUPERMERCADOS BANDEIRA LTDA6985 - T F MIRANDA MERCADO LTDAPor gentileza, providenciar as documentações de implantação com urgência, cliente com grande quantidade de funcionários.</t>
+        </is>
+      </c>
+      <c r="F302" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" s="1" t="n"/>
+      <c r="H302" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
+      <c r="I302" s="1" t="inlineStr">
+        <is>
+          <t>PL - AUDITORIA</t>
+        </is>
+      </c>
+      <c r="J302" s="2" t="n">
+        <v>46218.40379614583</v>
+      </c>
+      <c r="K302" s="2" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L302" s="1" t="inlineStr">
+        <is>
+          <t>Em Atendimento</t>
+        </is>
+      </c>
+      <c r="M302" s="1" t="inlineStr">
+        <is>
+          <t>Gabriela Peres</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="n">
+        <v>46219.50607847222</v>
+      </c>
+      <c r="O302" s="1" t="n"/>
+      <c r="P302" s="1" t="n"/>
+      <c r="Q302" s="1" t="inlineStr"/>
+      <c r="R302" s="1" t="inlineStr">
+        <is>
+          <t>Aguardando retorno dos dados do contador</t>
+        </is>
+      </c>
+      <c r="S302" s="1" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="T302" s="1" t="n"/>
+      <c r="U302" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -22138,7 +22138,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>81211</v>
+        <v>81224</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -22147,54 +22147,50 @@
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Abertura de protocolo</t>
+          <t>Baixa automática - Arquivos</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
         <is>
-          <t>MG EXPRESS - GC</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Por favor, precisamos da baixa das tarefas pendentes referente tarefa "Fed - DAS" da competência 06/2026 com os arquivos disponíveis na pasta "\\finlandia\PUBLICA\RomeroBorges\Fed - DAS"</t>
+          <t xml:space="preserve">boa tarde por gentileza, poderia esta baixando os sped icms sem movimento, pois não estou conseguindo da baixa devido a estagio 06 , pois a loja não vem sped icms </t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G273" s="1" t="n"/>
-      <c r="H273" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
+      <c r="H273" s="1" t="n"/>
       <c r="I273" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46223.56040540509</v>
+        <v>46223.67153248843</v>
       </c>
       <c r="K273" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M273" s="1" t="inlineStr">
         <is>
-          <t>Romero Borges</t>
+          <t>Vanessa Tavares</t>
         </is>
       </c>
       <c r="N273" s="1" t="n"/>
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="1" t="n"/>
       <c r="Q273" s="1" t="inlineStr"/>
-      <c r="R273" s="1" t="inlineStr"/>
+      <c r="R273" s="1" t="n"/>
       <c r="S273" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22205,7 +22201,7 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>81221</v>
+        <v>81223</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
@@ -22219,45 +22215,53 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>RJ - GC ADMINISTRATIVO</t>
+          <t>DALBEN - CTB</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prezados, boa tarde!Solicito que seja realizada baixa das empresas referente a tarefa de DEC 2 quinzena de julho - 4120 - 4124 - 4183 - 4503 - 4504 - 4505 - 5700 (sem certificado no dinamo e não temos acesso ao fisco.)6958 - 6982 (empresas isentas ) </t>
+          <t>Boa tarde!Na baixa da tarefa do REINF, todo o grupo Dalben está dando erro de layout.Arquivos para baixa estão salvos na pasta publica/Dalben</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G274" s="1" t="n"/>
-      <c r="H274" s="1" t="n"/>
+        <v>3212</v>
+      </c>
+      <c r="G274" s="1" t="inlineStr">
+        <is>
+          <t>SUPERMERCADOS DALBEN LTDA. (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H274" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I274" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46223.65060582176</v>
+        <v>46223.65859783565</v>
       </c>
       <c r="K274" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M274" s="1" t="inlineStr">
         <is>
-          <t>Amanda Mesquita</t>
+          <t>Karen Corazza</t>
         </is>
       </c>
       <c r="N274" s="1" t="n"/>
       <c r="O274" s="1" t="n"/>
       <c r="P274" s="1" t="n"/>
       <c r="Q274" s="1" t="inlineStr"/>
-      <c r="R274" s="1" t="n"/>
+      <c r="R274" s="1" t="inlineStr"/>
       <c r="S274" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -20826,67 +20826,63 @@
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>78305</v>
+        <v>81235</v>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D255" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E255" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Não localizei o certificado do empresa 5725 no meu Dinamo por favor disponibilizar.</t>
         </is>
       </c>
       <c r="F255" s="1" t="n">
-        <v>5744</v>
+        <v>5725</v>
       </c>
       <c r="G255" s="1" t="inlineStr">
         <is>
-          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
-        </is>
-      </c>
-      <c r="H255" s="1" t="inlineStr">
-        <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
+          <t>ELFUTEC - ESCOLA PARA FORMACAO DE USUARIOS DE TECNOLOGIA E CONHECIMENTO LTDA</t>
+        </is>
+      </c>
+      <c r="H255" s="1" t="n"/>
       <c r="I255" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J255" s="2" t="n">
-        <v>46111.42608159722</v>
+        <v>46223.83941327546</v>
       </c>
       <c r="K255" s="2" t="n">
-        <v>46122</v>
+        <v>46225</v>
       </c>
       <c r="L255" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M255" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Erika Santana</t>
         </is>
       </c>
       <c r="N255" s="1" t="n"/>
       <c r="O255" s="1" t="n"/>
       <c r="P255" s="1" t="n"/>
       <c r="Q255" s="1" t="inlineStr"/>
-      <c r="R255" s="1" t="inlineStr"/>
+      <c r="R255" s="1" t="n"/>
       <c r="S255" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -20897,7 +20893,7 @@
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>78318</v>
+        <v>78305</v>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
@@ -20920,11 +20916,11 @@
         </is>
       </c>
       <c r="F256" s="1" t="n">
-        <v>5801</v>
+        <v>5744</v>
       </c>
       <c r="G256" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
+          <t>ATC LOCAÇÃO E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="H256" s="1" t="inlineStr">
@@ -20938,7 +20934,7 @@
         </is>
       </c>
       <c r="J256" s="2" t="n">
-        <v>46111.44276319444</v>
+        <v>46111.42608159722</v>
       </c>
       <c r="K256" s="2" t="n">
         <v>46122</v>
@@ -20968,7 +20964,7 @@
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>78311</v>
+        <v>78318</v>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
@@ -20991,11 +20987,11 @@
         </is>
       </c>
       <c r="F257" s="1" t="n">
-        <v>5803</v>
+        <v>5801</v>
       </c>
       <c r="G257" s="1" t="inlineStr">
         <is>
-          <t>Ink Flex Industria Grafica LTDA</t>
+          <t xml:space="preserve">Nilcap Renovadora de Pneus LTDA </t>
         </is>
       </c>
       <c r="H257" s="1" t="inlineStr">
@@ -21009,7 +21005,7 @@
         </is>
       </c>
       <c r="J257" s="2" t="n">
-        <v>46111.43436825232</v>
+        <v>46111.44276319444</v>
       </c>
       <c r="K257" s="2" t="n">
         <v>46122</v>
@@ -21039,7 +21035,7 @@
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>78301</v>
+        <v>78311</v>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
@@ -21062,16 +21058,16 @@
         </is>
       </c>
       <c r="F258" s="1" t="n">
-        <v>6016</v>
+        <v>5803</v>
       </c>
       <c r="G258" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
+          <t>Ink Flex Industria Grafica LTDA</t>
         </is>
       </c>
       <c r="H258" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I258" s="1" t="inlineStr">
@@ -21080,7 +21076,7 @@
         </is>
       </c>
       <c r="J258" s="2" t="n">
-        <v>46111.42218321759</v>
+        <v>46111.43436825232</v>
       </c>
       <c r="K258" s="2" t="n">
         <v>46122</v>
@@ -21110,7 +21106,7 @@
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>79830</v>
+        <v>78301</v>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
@@ -21124,25 +21120,25 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
         <is>
-          <t>O cliente 6068-R.T. CARVALHO Aluguel de Imóveis enviou os recibos anexos correspondentes a receita com aluguéis durante o exercício 2025.No sistema de análise consta movimentação somente nos meses de outubro e novembro 2025, precisamos de um retorno de como tratar.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F259" s="1" t="n">
-        <v>6068</v>
+        <v>6016</v>
       </c>
       <c r="G259" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">R.T CARVALHO ALUGUEL DE IMOVEIS PROPRIOS LTDA </t>
+          <t xml:space="preserve">ALUMINIO IMPERIAL LTDA </t>
         </is>
       </c>
       <c r="H259" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I259" s="1" t="inlineStr">
@@ -21151,10 +21147,10 @@
         </is>
       </c>
       <c r="J259" s="2" t="n">
-        <v>46183.45075188657</v>
+        <v>46111.42218321759</v>
       </c>
       <c r="K259" s="2" t="n">
-        <v>46184</v>
+        <v>46122</v>
       </c>
       <c r="L259" s="1" t="inlineStr">
         <is>
@@ -21163,7 +21159,7 @@
       </c>
       <c r="M259" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N259" s="1" t="n"/>
@@ -21181,7 +21177,7 @@
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>78321</v>
+        <v>79830</v>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
@@ -21195,25 +21191,25 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>O cliente 6068-R.T. CARVALHO Aluguel de Imóveis enviou os recibos anexos correspondentes a receita com aluguéis durante o exercício 2025.No sistema de análise consta movimentação somente nos meses de outubro e novembro 2025, precisamos de um retorno de como tratar.</t>
         </is>
       </c>
       <c r="F260" s="1" t="n">
-        <v>6088</v>
+        <v>6068</v>
       </c>
       <c r="G260" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
+          <t xml:space="preserve">R.T CARVALHO ALUGUEL DE IMOVEIS PROPRIOS LTDA </t>
         </is>
       </c>
       <c r="H260" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I260" s="1" t="inlineStr">
@@ -21222,17 +21218,21 @@
         </is>
       </c>
       <c r="J260" s="2" t="n">
-        <v>46111.44696084491</v>
+        <v>46183.45075188657</v>
       </c>
       <c r="K260" s="2" t="n">
-        <v>46122</v>
+        <v>46184</v>
       </c>
       <c r="L260" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M260" s="1" t="n"/>
+      <c r="M260" s="1" t="inlineStr">
+        <is>
+          <t>Tatiana Linardi</t>
+        </is>
+      </c>
       <c r="N260" s="1" t="n"/>
       <c r="O260" s="1" t="n"/>
       <c r="P260" s="1" t="n"/>
@@ -21248,7 +21248,7 @@
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
-        <v>78798</v>
+        <v>78321</v>
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
@@ -21267,15 +21267,15 @@
       </c>
       <c r="E261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F261" s="1" t="n">
-        <v>6106</v>
+        <v>6088</v>
       </c>
       <c r="G261" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
+          <t xml:space="preserve">SINZATO INDUSTRIA E COMERCIO DE CONFECCOES LTDA </t>
         </is>
       </c>
       <c r="H261" s="1" t="inlineStr">
@@ -21289,21 +21289,17 @@
         </is>
       </c>
       <c r="J261" s="2" t="n">
-        <v>46128.70572581018</v>
+        <v>46111.44696084491</v>
       </c>
       <c r="K261" s="2" t="n">
-        <v>46132</v>
+        <v>46122</v>
       </c>
       <c r="L261" s="1" t="inlineStr">
         <is>
           <t>Esperando Atendimento</t>
         </is>
       </c>
-      <c r="M261" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+      <c r="M261" s="1" t="n"/>
       <c r="N261" s="1" t="n"/>
       <c r="O261" s="1" t="n"/>
       <c r="P261" s="1" t="n"/>
@@ -21319,39 +21315,39 @@
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>81124</v>
+        <v>78798</v>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bom dia! Por gentileza, atualizar certificado no DINAMO e GAX - colocar na minha árvore. </t>
+          <t xml:space="preserve">por favor, orientar o cliente sobre a classificação das notas de entrada, por diversas vezes já falamos junto ao cliente sobre essa classificação. exemplo: coroa de flores - classificou como insumo / saco de lixo e copo descartavel - classificou como insumo. No aguardo </t>
         </is>
       </c>
       <c r="F262" s="1" t="n">
-        <v>6112</v>
+        <v>6106</v>
       </c>
       <c r="G262" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTE CARLO LAB SERVICOS ADMINISTRATIVOS E COMERCIO LTDA </t>
+          <t xml:space="preserve">PLANET GRAPHICS LTDA </t>
         </is>
       </c>
       <c r="H262" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I262" s="1" t="inlineStr">
@@ -21360,10 +21356,10 @@
         </is>
       </c>
       <c r="J262" s="2" t="n">
-        <v>46219.49444649305</v>
+        <v>46128.70572581018</v>
       </c>
       <c r="K262" s="2" t="n">
-        <v>46220</v>
+        <v>46132</v>
       </c>
       <c r="L262" s="1" t="inlineStr">
         <is>
@@ -21372,7 +21368,7 @@
       </c>
       <c r="M262" s="1" t="inlineStr">
         <is>
-          <t>Lorrane Santos</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="N262" s="1" t="n"/>
@@ -21390,39 +21386,39 @@
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>79837</v>
+        <v>81124</v>
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E263" s="1" t="inlineStr">
         <is>
-          <t>Segue empresas que não possuem estoque suficiente para bater a lucratividade.6125	Piquini Comercio de Materiais Para Construção LTDA - Matriz 	Casa Glória	02.494.541/0001-49	Bruno	Estoque insuficiente desde 03/2025</t>
+          <t xml:space="preserve">Bom dia! Por gentileza, atualizar certificado no DINAMO e GAX - colocar na minha árvore. </t>
         </is>
       </c>
       <c r="F263" s="1" t="n">
-        <v>6125</v>
+        <v>6112</v>
       </c>
       <c r="G263" s="1" t="inlineStr">
         <is>
-          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
+          <t xml:space="preserve">MONTE CARLO LAB SERVICOS ADMINISTRATIVOS E COMERCIO LTDA </t>
         </is>
       </c>
       <c r="H263" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="I263" s="1" t="inlineStr">
@@ -21431,10 +21427,10 @@
         </is>
       </c>
       <c r="J263" s="2" t="n">
-        <v>46183.47519135417</v>
+        <v>46219.49444649305</v>
       </c>
       <c r="K263" s="2" t="n">
-        <v>46184</v>
+        <v>46220</v>
       </c>
       <c r="L263" s="1" t="inlineStr">
         <is>
@@ -21443,7 +21439,7 @@
       </c>
       <c r="M263" s="1" t="inlineStr">
         <is>
-          <t>Tatiana Linardi</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="N263" s="1" t="n"/>
@@ -21461,7 +21457,7 @@
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>78325</v>
+        <v>79837</v>
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
@@ -21475,25 +21471,25 @@
       </c>
       <c r="D264" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E264" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Segue empresas que não possuem estoque suficiente para bater a lucratividade.6125	Piquini Comercio de Materiais Para Construção LTDA - Matriz 	Casa Glória	02.494.541/0001-49	Bruno	Estoque insuficiente desde 03/2025</t>
         </is>
       </c>
       <c r="F264" s="1" t="n">
-        <v>6148</v>
+        <v>6125</v>
       </c>
       <c r="G264" s="1" t="inlineStr">
         <is>
-          <t>VALE CONCRETO LTDA</t>
+          <t>CORA SERVIÇOS EMPRESARIAIS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H264" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I264" s="1" t="inlineStr">
@@ -21502,10 +21498,10 @@
         </is>
       </c>
       <c r="J264" s="2" t="n">
-        <v>46111.45013549768</v>
+        <v>46183.47519135417</v>
       </c>
       <c r="K264" s="2" t="n">
-        <v>46122</v>
+        <v>46184</v>
       </c>
       <c r="L264" s="1" t="inlineStr">
         <is>
@@ -21514,7 +21510,7 @@
       </c>
       <c r="M264" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Tatiana Linardi</t>
         </is>
       </c>
       <c r="N264" s="1" t="n"/>
@@ -21532,7 +21528,7 @@
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>78324</v>
+        <v>78325</v>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
@@ -21555,16 +21551,16 @@
         </is>
       </c>
       <c r="F265" s="1" t="n">
-        <v>6261</v>
+        <v>6148</v>
       </c>
       <c r="G265" s="1" t="inlineStr">
         <is>
-          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
+          <t>VALE CONCRETO LTDA</t>
         </is>
       </c>
       <c r="H265" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I265" s="1" t="inlineStr">
@@ -21573,7 +21569,7 @@
         </is>
       </c>
       <c r="J265" s="2" t="n">
-        <v>46111.44946597222</v>
+        <v>46111.45013549768</v>
       </c>
       <c r="K265" s="2" t="n">
         <v>46122</v>
@@ -21603,7 +21599,7 @@
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
-        <v>78317</v>
+        <v>78324</v>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
@@ -21626,16 +21622,16 @@
         </is>
       </c>
       <c r="F266" s="1" t="n">
-        <v>6288</v>
+        <v>6261</v>
       </c>
       <c r="G266" s="1" t="inlineStr">
         <is>
-          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
+          <t>V8 INDUSTRIA E COMERCIO DE PRODUTOS ABRASIVOS LTDA</t>
         </is>
       </c>
       <c r="H266" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="I266" s="1" t="inlineStr">
@@ -21644,7 +21640,7 @@
         </is>
       </c>
       <c r="J266" s="2" t="n">
-        <v>46111.44151450232</v>
+        <v>46111.44946597222</v>
       </c>
       <c r="K266" s="2" t="n">
         <v>46122</v>
@@ -21674,7 +21670,7 @@
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>78289</v>
+        <v>78317</v>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
@@ -21697,11 +21693,11 @@
         </is>
       </c>
       <c r="F267" s="1" t="n">
-        <v>6289</v>
+        <v>6288</v>
       </c>
       <c r="G267" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
+          <t>NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 2)</t>
         </is>
       </c>
       <c r="H267" s="1" t="inlineStr">
@@ -21715,7 +21711,7 @@
         </is>
       </c>
       <c r="J267" s="2" t="n">
-        <v>46111.41423260417</v>
+        <v>46111.44151450232</v>
       </c>
       <c r="K267" s="2" t="n">
         <v>46122</v>
@@ -21745,39 +21741,39 @@
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>81011</v>
+        <v>78289</v>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de ata de reunião</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
         <is>
-          <t>NCM - consultar a tributação do NCM 87116000 - enviar para o cliente!</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F268" s="1" t="n">
-        <v>6399</v>
+        <v>6289</v>
       </c>
       <c r="G268" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
+          <t xml:space="preserve"> NATURAL NUTS INDUSTRIA E COMERCIO DE ALIMENTOS LTDA (FILIAL 3)</t>
         </is>
       </c>
       <c r="H268" s="1" t="inlineStr">
         <is>
-          <t>Daniel Oliveira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I268" s="1" t="inlineStr">
@@ -21786,10 +21782,10 @@
         </is>
       </c>
       <c r="J268" s="2" t="n">
-        <v>46217.3885827199</v>
+        <v>46111.41423260417</v>
       </c>
       <c r="K268" s="2" t="n">
-        <v>46223</v>
+        <v>46122</v>
       </c>
       <c r="L268" s="1" t="inlineStr">
         <is>
@@ -21798,7 +21794,7 @@
       </c>
       <c r="M268" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N268" s="1" t="n"/>
@@ -21816,39 +21812,39 @@
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>81112</v>
+        <v>81011</v>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Inclusão de ata de reunião</t>
         </is>
       </c>
       <c r="D269" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
         <is>
-          <t>Bom dia!6499 - DFGAssunto: Cobrança do Sindicato ( SECABC) - Assistencial 2025Segue o e-mail encaminhado ao cliente.O sindicato voltou a cobrar as contribuições do período de 2025, eles me ligaram ontem e estou te encaminhando em anexo o e-mail que eles nos enviaram, e estão cobrando uma resposta, segue em anexo também a relação da cobrança.Por telefone eles estão ameaçando entrar com medidas legais e denúncia no MTE.O cliente informou que não vai realizar o pagamento, pois a contabilidade anterior informou que não era necessário realizar o recolhimento da contribuição Assistencial dos colaboradores. Por favor, abordar esse assunto na reunião, aguardo retorno.</t>
+          <t>NCM - consultar a tributação do NCM 87116000 - enviar para o cliente!</t>
         </is>
       </c>
       <c r="F269" s="1" t="n">
-        <v>6499</v>
+        <v>6399</v>
       </c>
       <c r="G269" s="1" t="inlineStr">
         <is>
-          <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
+          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
         </is>
       </c>
       <c r="H269" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Daniel Oliveira</t>
         </is>
       </c>
       <c r="I269" s="1" t="inlineStr">
@@ -21857,10 +21853,10 @@
         </is>
       </c>
       <c r="J269" s="2" t="n">
-        <v>46219.48029166667</v>
+        <v>46217.3885827199</v>
       </c>
       <c r="K269" s="2" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="L269" s="1" t="inlineStr">
         <is>
@@ -21869,7 +21865,7 @@
       </c>
       <c r="M269" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
+          <t>Clara Maria</t>
         </is>
       </c>
       <c r="N269" s="1" t="n"/>
@@ -21887,7 +21883,7 @@
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>77557</v>
+        <v>81112</v>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
@@ -21901,25 +21897,25 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
         <is>
-          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
+          <t>Bom dia!6499 - DFGAssunto: Cobrança do Sindicato ( SECABC) - Assistencial 2025Segue o e-mail encaminhado ao cliente.O sindicato voltou a cobrar as contribuições do período de 2025, eles me ligaram ontem e estou te encaminhando em anexo o e-mail que eles nos enviaram, e estão cobrando uma resposta, segue em anexo também a relação da cobrança.Por telefone eles estão ameaçando entrar com medidas legais e denúncia no MTE.O cliente informou que não vai realizar o pagamento, pois a contabilidade anterior informou que não era necessário realizar o recolhimento da contribuição Assistencial dos colaboradores. Por favor, abordar esse assunto na reunião, aguardo retorno.</t>
         </is>
       </c>
       <c r="F270" s="1" t="n">
-        <v>6640</v>
+        <v>6499</v>
       </c>
       <c r="G270" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
         </is>
       </c>
       <c r="H270" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I270" s="1" t="inlineStr">
@@ -21928,10 +21924,10 @@
         </is>
       </c>
       <c r="J270" s="2" t="n">
-        <v>46079.72002283565</v>
+        <v>46219.48029166667</v>
       </c>
       <c r="K270" s="2" t="n">
-        <v>46079</v>
+        <v>46220</v>
       </c>
       <c r="L270" s="1" t="inlineStr">
         <is>
@@ -21940,7 +21936,7 @@
       </c>
       <c r="M270" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Edivaldo Veiga</t>
         </is>
       </c>
       <c r="N270" s="1" t="n"/>
@@ -21958,76 +21954,70 @@
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>80165</v>
+        <v>77557</v>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D271" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E271" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>A loja 6640 é de São Paulo, porém, a Matriz é de Belém, precisa alinhar quais documentos ele precisam que a gente mande, esse mes solicitaram o SPED, calculo do DIFAL e Calculo do laudo de combustivel (não recebi nenhuma informação). Questionaram também se será considerada a nossa apuação ou a do sistema, porq a nossa deu diferença em "Outras " do ICMS e querem tudo batido igual o deles.Sobre a 6639 é uma transportadora, não recebemos SPED e não encontrei onde extrair no sistema que deram acesso, será sempre montagem aqui? Lançamos tbm o credito outorgado (20%), vimos que foi feito assim no mes anterior com o antigo contador.</t>
         </is>
       </c>
       <c r="F271" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G271" s="1" t="n"/>
+        <v>6640</v>
+      </c>
+      <c r="G271" s="1" t="inlineStr">
+        <is>
+          <t>FORT FRUIT LTDA</t>
+        </is>
+      </c>
       <c r="H271" s="1" t="inlineStr">
         <is>
-          <t>Gabriel Amaral</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I271" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J271" s="2" t="n">
-        <v>46190.71175925926</v>
+        <v>46079.72002283565</v>
       </c>
       <c r="K271" s="2" t="n">
-        <v>46191</v>
+        <v>46079</v>
       </c>
       <c r="L271" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M271" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Thaiza Oliveira</t>
         </is>
       </c>
       <c r="N271" s="1" t="n"/>
       <c r="O271" s="1" t="n"/>
-      <c r="P271" s="2" t="n">
-        <v>46190.7346272338</v>
-      </c>
-      <c r="Q271" s="1" t="inlineStr">
-        <is>
-          <t>Gabriel Amaral</t>
-        </is>
-      </c>
-      <c r="R271" s="1" t="inlineStr">
-        <is>
-          <t>Tarefas baixadas</t>
-        </is>
-      </c>
+      <c r="P271" s="1" t="n"/>
+      <c r="Q271" s="1" t="inlineStr"/>
+      <c r="R271" s="1" t="inlineStr"/>
       <c r="S271" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T271" s="1" t="n"/>
@@ -22035,7 +22025,7 @@
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>80174</v>
+        <v>80165</v>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
@@ -22044,7 +22034,7 @@
       </c>
       <c r="C272" s="1" t="inlineStr">
         <is>
-          <t>Vencimento de Tarefas</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D272" s="1" t="inlineStr">
@@ -22054,7 +22044,7 @@
       </c>
       <c r="E272" s="1" t="inlineStr">
         <is>
-          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F272" s="1" t="n">
@@ -22072,10 +22062,10 @@
         </is>
       </c>
       <c r="J272" s="2" t="n">
-        <v>46191.36721832176</v>
+        <v>46190.71175925926</v>
       </c>
       <c r="K272" s="2" t="n">
-        <v>46192</v>
+        <v>46191</v>
       </c>
       <c r="L272" s="1" t="inlineStr">
         <is>
@@ -22084,13 +22074,13 @@
       </c>
       <c r="M272" s="1" t="inlineStr">
         <is>
-          <t>Yasmin Peixoto</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N272" s="1" t="n"/>
       <c r="O272" s="1" t="n"/>
       <c r="P272" s="2" t="n">
-        <v>46191.49335512731</v>
+        <v>46190.7346272338</v>
       </c>
       <c r="Q272" s="1" t="inlineStr">
         <is>
@@ -22112,7 +22102,7 @@
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>80250</v>
+        <v>80174</v>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
@@ -22121,7 +22111,7 @@
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Vencimento de Tarefas</t>
         </is>
       </c>
       <c r="D273" s="1" t="inlineStr">
@@ -22131,7 +22121,7 @@
       </c>
       <c r="E273" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por gentileza, baixar as consultas Dec das seguintes empresas;635765986911</t>
+          <t>Bom dia prezados!Por gentileza dar baixa na tarefa DEC 1 Consulta, pois não possui inscrição estadual.6091 - CARTAO DE TODOS ITAPETININGA LTDA6093 - CARTAO DE TODOS ADMINISTRADORA E VENDAS LTDA6094 - CLINICA SAUDE &amp; VIDA LTDA6095 - N S ACADEMIA SOROCABA VILA CARVALHO LTDA6096 - CLINICA SAUDE &amp; VIDA LTDA (FILIAL)6330 - ADM SERVICE ITAPETININGA E BOTUCATU LTDA6391 - ADMINISTRADORA ACADEMIA ALLPFIT LTDA6556 - CLINICA MEDICA E ODONTOLOGICA AMOR SAUDE BOTUCATU LTDA6371 - CLUBE ATLETICO INDIANO6383 - THSAVEG ASSESSORIA EMPRESARIAL LTDA6482 - RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA (FILIAL 1)6419 - QUALITY INDUSTRIA E COMERCIO DE PRODUTOS PARA LIMPEZA LTDA (FILIAL 1)6359 - MACHADO PRESTACAO DE SERVICOS LTDA1861 - S &amp; B MARKETING E COMUNICAÇÃO VISUAL LTDA6579 - DROGARIA MIX I LTDA (FILIAL 9)3293 - SUPERMERCADO NELSINHO3465 - Vicali Administração, Participações e Investimentos Ltda.</t>
         </is>
       </c>
       <c r="F273" s="1" t="n">
@@ -22149,21 +22139,25 @@
         </is>
       </c>
       <c r="J273" s="2" t="n">
-        <v>46192.6584477662</v>
+        <v>46191.36721832176</v>
       </c>
       <c r="K273" s="2" t="n">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="L273" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M273" s="1" t="n"/>
+      <c r="M273" s="1" t="inlineStr">
+        <is>
+          <t>Yasmin Peixoto</t>
+        </is>
+      </c>
       <c r="N273" s="1" t="n"/>
       <c r="O273" s="1" t="n"/>
       <c r="P273" s="2" t="n">
-        <v>46192.70597966435</v>
+        <v>46191.49335512731</v>
       </c>
       <c r="Q273" s="1" t="inlineStr">
         <is>
@@ -22185,7 +22179,7 @@
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>80709</v>
+        <v>80250</v>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
@@ -22204,7 +22198,7 @@
       </c>
       <c r="E274" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 1º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>Boa tarde!Por gentileza, baixar as consultas Dec das seguintes empresas;635765986911</t>
         </is>
       </c>
       <c r="F274" s="1" t="n">
@@ -22222,25 +22216,21 @@
         </is>
       </c>
       <c r="J274" s="2" t="n">
-        <v>46205.72485570602</v>
+        <v>46192.6584477662</v>
       </c>
       <c r="K274" s="2" t="n">
-        <v>46206</v>
+        <v>46195</v>
       </c>
       <c r="L274" s="1" t="inlineStr">
         <is>
           <t>Entregue Ao Solicitante</t>
         </is>
       </c>
-      <c r="M274" s="1" t="inlineStr">
-        <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
+      <c r="M274" s="1" t="n"/>
       <c r="N274" s="1" t="n"/>
       <c r="O274" s="1" t="n"/>
       <c r="P274" s="2" t="n">
-        <v>46205.73248877314</v>
+        <v>46192.70597966435</v>
       </c>
       <c r="Q274" s="1" t="inlineStr">
         <is>
@@ -22262,7 +22252,7 @@
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>81083</v>
+        <v>80709</v>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
@@ -22281,7 +22271,7 @@
       </c>
       <c r="E275" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 1º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F275" s="1" t="n">
@@ -22299,10 +22289,10 @@
         </is>
       </c>
       <c r="J275" s="2" t="n">
-        <v>46218.68119872685</v>
+        <v>46205.72485570602</v>
       </c>
       <c r="K275" s="2" t="n">
-        <v>46219</v>
+        <v>46206</v>
       </c>
       <c r="L275" s="1" t="inlineStr">
         <is>
@@ -22317,7 +22307,7 @@
       <c r="N275" s="1" t="n"/>
       <c r="O275" s="1" t="n"/>
       <c r="P275" s="2" t="n">
-        <v>46218.7466727662</v>
+        <v>46205.73248877314</v>
       </c>
       <c r="Q275" s="1" t="inlineStr">
         <is>
@@ -22326,7 +22316,7 @@
       </c>
       <c r="R275" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarefas já se encontram baixadas </t>
+          <t>Tarefas baixadas</t>
         </is>
       </c>
       <c r="S275" s="1" t="inlineStr">
@@ -22339,7 +22329,7 @@
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
-        <v>81230</v>
+        <v>81083</v>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
@@ -22348,53 +22338,67 @@
       </c>
       <c r="C276" s="1" t="inlineStr">
         <is>
-          <t>Reabertura de tarefa</t>
+          <t>Erro de Baixa</t>
         </is>
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>RJ - EF</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde,solicito a reabertura da tarefa 3659 - Fed - DAS da empresa 4951 - SUPER SERVIÇOS TERCEIRIZADOS DE APOIO LTDA do mês 06.2026, porque houve retificadora com valor.</t>
+          <t>Boa tarde, por gentileza baixar a tarefa de DEC 2º quinzena das seguintes empresas:DEC ACESSO NEGADO - RODRIGO5043 17.081.544/0001-28 ACESSO NEGADO6548 23.707.689/0001-94 ACESSO NEGADO6486 28.604.255/0001-82 ACESSO NEGADO3545 29.621.654/0001-14 ACESSO NEGADO6707 41.963.494/0002-78 ACESSO NEGADO6118 43.462.720/0010-72 ACESSO NEGADO6619 04.596.502/0116-27 ACESSO NEGADO6082 59.041.787/0001-82 ACESSO NEGADO</t>
         </is>
       </c>
       <c r="F276" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G276" s="1" t="n"/>
-      <c r="H276" s="1" t="n"/>
+      <c r="H276" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I276" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J276" s="2" t="n">
-        <v>46223.71789861111</v>
+        <v>46218.68119872685</v>
       </c>
       <c r="K276" s="2" t="n">
-        <v>46224</v>
+        <v>46219</v>
       </c>
       <c r="L276" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M276" s="1" t="inlineStr">
         <is>
-          <t>Isabela Barbosa</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="N276" s="1" t="n"/>
       <c r="O276" s="1" t="n"/>
-      <c r="P276" s="1" t="n"/>
-      <c r="Q276" s="1" t="inlineStr"/>
-      <c r="R276" s="1" t="n"/>
+      <c r="P276" s="2" t="n">
+        <v>46218.7466727662</v>
+      </c>
+      <c r="Q276" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
+      <c r="R276" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarefas já se encontram baixadas </t>
+        </is>
+      </c>
       <c r="S276" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T276" s="1" t="n"/>
@@ -22402,7 +22406,7 @@
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>81231</v>
+        <v>81236</v>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
@@ -22416,45 +22420,49 @@
       </c>
       <c r="D277" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>RJ - EF</t>
         </is>
       </c>
       <c r="E277" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tardeSolicito a baixa na tarefa "´Prévia rescisões individuais" da empresa 2109 ICERI E ICERI SUPERMERCADO. Ao tentar realizar a baixa, retornou com uma notificação de erro, informando que o arquivo anexado não é compatível para baixar a tarefa.Segue a mesma em anexo para análise. Obrigado. </t>
+          <t>Bom dia !É enviado ao grupo SERVI um e-mail único de confirmação de faturamento referente a todas as empresas do GRUPO, por favor realizar a baixa da tarefa via banco de dados com o e-mail em anexo.</t>
         </is>
       </c>
       <c r="F277" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G277" s="1" t="n"/>
-      <c r="H277" s="1" t="n"/>
+      <c r="H277" s="1" t="inlineStr">
+        <is>
+          <t>Gabriel Amaral</t>
+        </is>
+      </c>
       <c r="I277" s="1" t="inlineStr">
         <is>
           <t>CONTROLADORIA</t>
         </is>
       </c>
       <c r="J277" s="2" t="n">
-        <v>46223.72315987269</v>
+        <v>46224.35354027778</v>
       </c>
       <c r="K277" s="2" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="L277" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M277" s="1" t="inlineStr">
         <is>
-          <t>Vitor Guedes</t>
+          <t>Glaucia Santos</t>
         </is>
       </c>
       <c r="N277" s="1" t="n"/>
       <c r="O277" s="1" t="n"/>
       <c r="P277" s="1" t="n"/>
       <c r="Q277" s="1" t="inlineStr"/>
-      <c r="R277" s="1" t="n"/>
+      <c r="R277" s="1" t="inlineStr"/>
       <c r="S277" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22465,59 +22473,70 @@
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>81233</v>
+        <v>77913</v>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
         <is>
-          <t>Erro de Baixa</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D278" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E278" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!Por favor, baixar as tarefas (Prévias rescisões individuais - PREVIA  e Prévias rescisões individuais - 662 -NICOLLY) da empresa 6559. MOTIVO: Cliente solicitou o cancelamento da solicitação.</t>
+          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
         </is>
       </c>
       <c r="F278" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G278" s="1" t="n"/>
-      <c r="H278" s="1" t="n"/>
+      <c r="H278" s="1" t="inlineStr">
+        <is>
+          <t>Bianca Ribeiro</t>
+        </is>
+      </c>
       <c r="I278" s="1" t="inlineStr">
         <is>
-          <t>CONTROLADORIA</t>
+          <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J278" s="2" t="n">
-        <v>46223.74468653935</v>
+        <v>46092.7773144676</v>
       </c>
       <c r="K278" s="2" t="n">
-        <v>46224</v>
+        <v>46097</v>
       </c>
       <c r="L278" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M278" s="1" t="inlineStr">
         <is>
-          <t>Edivaldo Veiga</t>
-        </is>
-      </c>
-      <c r="N278" s="1" t="n"/>
+          <t>Larissa Félix</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>46223.70421145833</v>
+      </c>
       <c r="O278" s="1" t="n"/>
       <c r="P278" s="1" t="n"/>
       <c r="Q278" s="1" t="inlineStr"/>
-      <c r="R278" s="1" t="n"/>
+      <c r="R278" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prezados(as), boa tarde!
+Estamos verificando com a Prefeitura, tendo em vista que não recebemos os documentos por parte do cliente. </t>
+        </is>
+      </c>
       <c r="S278" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22528,26 +22547,26 @@
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>77913</v>
+        <v>79609</v>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Eireli - Comércio</t>
         </is>
       </c>
       <c r="D279" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA MASTER</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Por gentileza, preciso que inclua login e senha para o acesso a prefeitura da loja 6353 - ARMANDO E MARGARIDA RESTAURANTE E LANCHONETE LTDA (FILIAL 1).Aguardo um retorno,Obrigada!</t>
+          <t>TESTE TESTE</t>
         </is>
       </c>
       <c r="F279" s="1" t="n">
@@ -22556,7 +22575,7 @@
       <c r="G279" s="1" t="n"/>
       <c r="H279" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I279" s="1" t="inlineStr">
@@ -22565,33 +22584,26 @@
         </is>
       </c>
       <c r="J279" s="2" t="n">
-        <v>46092.7773144676</v>
+        <v>46175.48423082176</v>
       </c>
       <c r="K279" s="2" t="n">
-        <v>46097</v>
+        <v>46205</v>
       </c>
       <c r="L279" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M279" s="1" t="inlineStr">
         <is>
-          <t>Larissa Félix</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="n">
-        <v>46223.70421145833</v>
-      </c>
+          <t>Claudio Correa</t>
+        </is>
+      </c>
+      <c r="N279" s="1" t="n"/>
       <c r="O279" s="1" t="n"/>
       <c r="P279" s="1" t="n"/>
       <c r="Q279" s="1" t="inlineStr"/>
-      <c r="R279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Prezados(as), boa tarde!
-Estamos verificando com a Prefeitura, tendo em vista que não recebemos os documentos por parte do cliente. </t>
-        </is>
-      </c>
+      <c r="R279" s="1" t="inlineStr"/>
       <c r="S279" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22602,7 +22614,7 @@
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>79609</v>
+        <v>80515</v>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
@@ -22611,7 +22623,7 @@
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D280" s="1" t="inlineStr">
@@ -22621,7 +22633,7 @@
       </c>
       <c r="E280" s="1" t="inlineStr">
         <is>
-          <t>TESTE TESTE</t>
+          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
         </is>
       </c>
       <c r="F280" s="1" t="n">
@@ -22630,7 +22642,7 @@
       <c r="G280" s="1" t="n"/>
       <c r="H280" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I280" s="1" t="inlineStr">
@@ -22639,26 +22651,32 @@
         </is>
       </c>
       <c r="J280" s="2" t="n">
-        <v>46175.48423082176</v>
+        <v>46196.7259258449</v>
       </c>
       <c r="K280" s="2" t="n">
-        <v>46205</v>
+        <v>46226</v>
       </c>
       <c r="L280" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M280" s="1" t="inlineStr">
         <is>
-          <t>Claudio Correa</t>
-        </is>
-      </c>
-      <c r="N280" s="1" t="n"/>
+          <t>Raisa Sousa</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>46219.75157017361</v>
+      </c>
       <c r="O280" s="1" t="n"/>
       <c r="P280" s="1" t="n"/>
       <c r="Q280" s="1" t="inlineStr"/>
-      <c r="R280" s="1" t="inlineStr"/>
+      <c r="R280" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Enviado para registro </t>
+        </is>
+      </c>
       <c r="S280" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22669,7 +22687,7 @@
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>80515</v>
+        <v>80697</v>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
@@ -22678,7 +22696,7 @@
       </c>
       <c r="C281" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Eireli - Serviços</t>
         </is>
       </c>
       <c r="D281" s="1" t="inlineStr">
@@ -22688,7 +22706,7 @@
       </c>
       <c r="E281" s="1" t="inlineStr">
         <is>
-          <t>Pedido de abertura de empresa prestadora de serviços que será um novo cliente, sem vínculo com qualquer um outro cliente MG Contécnica.No pedido de abertura contém:_ 3 sujestões de nome;_ CNAE´s já pré definidos;_ Objeto social (Considerar empresa já cliente DUO Cenografia como exemplo)_ Capital social já definido;_ e-mail da sócia para envio da minuta para conferência;_ Telefone e e-mail do Sr. Felipe Silveira, responsável pelas documentações;</t>
+          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
         </is>
       </c>
       <c r="F281" s="1" t="n">
@@ -22697,7 +22715,7 @@
       <c r="G281" s="1" t="n"/>
       <c r="H281" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I281" s="1" t="inlineStr">
@@ -22706,14 +22724,14 @@
         </is>
       </c>
       <c r="J281" s="2" t="n">
-        <v>46196.7259258449</v>
+        <v>46205.39919077546</v>
       </c>
       <c r="K281" s="2" t="n">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="L281" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M281" s="1" t="inlineStr">
@@ -22721,17 +22739,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N281" s="2" t="n">
-        <v>46219.75157017361</v>
-      </c>
+      <c r="N281" s="1" t="n"/>
       <c r="O281" s="1" t="n"/>
       <c r="P281" s="1" t="n"/>
       <c r="Q281" s="1" t="inlineStr"/>
-      <c r="R281" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enviado para registro </t>
-        </is>
-      </c>
+      <c r="R281" s="1" t="inlineStr"/>
       <c r="S281" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22742,7 +22754,7 @@
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>80697</v>
+        <v>80714</v>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
@@ -22751,7 +22763,7 @@
       </c>
       <c r="C282" s="1" t="inlineStr">
         <is>
-          <t>Eireli - Serviços</t>
+          <t>Sociedade - Serviços</t>
         </is>
       </c>
       <c r="D282" s="1" t="inlineStr">
@@ -22761,7 +22773,7 @@
       </c>
       <c r="E282" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE NOVA EMPRESA DO GRUPO 1803 - SERVISUL, EMPRESA COM  TRIBUTAÇÃO SIMPLES NACIONAL, TIPO DE ATIVIDADE: SERVIÇOS, FINALIDADE: OPERACIONAL E FORMA JURIDICA: LTDA. PROPOSTA NEGOCIADA COM O VALOR DE R$1.800,00. RAZÃO SOCIAL: MCESCON ASSESSORIA EMPRESARIAL LTDA. OBJETO SOCIAL: APOIO ADMINISTRATIVO/COBRANÇA. CAPITAL SOCIAL:10.000,00. DOCUMENTAÇÃO DISPONIBILIZADA: RG / CPF / CNH, IPTU E COMPROVANTE DE ENDEREÇO.</t>
+          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
         </is>
       </c>
       <c r="F282" s="1" t="n">
@@ -22770,7 +22782,7 @@
       <c r="G282" s="1" t="n"/>
       <c r="H282" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I282" s="1" t="inlineStr">
@@ -22779,14 +22791,14 @@
         </is>
       </c>
       <c r="J282" s="2" t="n">
-        <v>46205.39919077546</v>
+        <v>46206.37795378472</v>
       </c>
       <c r="K282" s="2" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="L282" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M282" s="1" t="inlineStr">
@@ -22794,11 +22806,18 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N282" s="1" t="n"/>
+      <c r="N282" s="2" t="n">
+        <v>46223.41822326389</v>
+      </c>
       <c r="O282" s="1" t="n"/>
       <c r="P282" s="1" t="n"/>
       <c r="Q282" s="1" t="inlineStr"/>
-      <c r="R282" s="1" t="inlineStr"/>
+      <c r="R282" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PROCESSO ENCONTRA-SE EM ANDAMENTO. 
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL. </t>
+        </is>
+      </c>
       <c r="S282" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22809,16 +22828,16 @@
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>80714</v>
+        <v>80919</v>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Alteração Contratual</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
         <is>
-          <t>Sociedade - Serviços</t>
+          <t>Razão Social</t>
         </is>
       </c>
       <c r="D283" s="1" t="inlineStr">
@@ -22828,7 +22847,7 @@
       </c>
       <c r="E283" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE FILIAL - RIO DE JANEIRO</t>
+          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
         </is>
       </c>
       <c r="F283" s="1" t="n">
@@ -22837,7 +22856,7 @@
       <c r="G283" s="1" t="n"/>
       <c r="H283" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Ronaldo Dias</t>
         </is>
       </c>
       <c r="I283" s="1" t="inlineStr">
@@ -22846,14 +22865,14 @@
         </is>
       </c>
       <c r="J283" s="2" t="n">
-        <v>46206.37795378472</v>
+        <v>46211.63019085648</v>
       </c>
       <c r="K283" s="2" t="n">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="L283" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M283" s="1" t="inlineStr">
@@ -22861,18 +22880,11 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N283" s="2" t="n">
-        <v>46223.41822326389</v>
-      </c>
+      <c r="N283" s="1" t="n"/>
       <c r="O283" s="1" t="n"/>
       <c r="P283" s="1" t="n"/>
       <c r="Q283" s="1" t="inlineStr"/>
-      <c r="R283" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PROCESSO ENCONTRA-SE EM ANDAMENTO. 
-TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL. </t>
-        </is>
-      </c>
+      <c r="R283" s="1" t="inlineStr"/>
       <c r="S283" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22883,16 +22895,16 @@
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>80919</v>
+        <v>80935</v>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>Alteração Contratual</t>
+          <t>Abertura de Empresa</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
         <is>
-          <t>Razão Social</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D284" s="1" t="inlineStr">
@@ -22902,7 +22914,7 @@
       </c>
       <c r="E284" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALTERAÇÃO CONTRATUAL DA RAZÃO SOCIAL, ATIVIDADE E ENDEREÇO DO CLIENTE 6651 - POLEN COMERCIO DE EMBALAGENS. PROPOSTA JÁ NEGOCIADA. </t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
         </is>
       </c>
       <c r="F284" s="1" t="n">
@@ -22911,7 +22923,7 @@
       <c r="G284" s="1" t="n"/>
       <c r="H284" s="1" t="inlineStr">
         <is>
-          <t>Ronaldo Dias</t>
+          <t>Bianca Ribeiro</t>
         </is>
       </c>
       <c r="I284" s="1" t="inlineStr">
@@ -22920,14 +22932,14 @@
         </is>
       </c>
       <c r="J284" s="2" t="n">
-        <v>46211.63019085648</v>
+        <v>46213.35976299769</v>
       </c>
       <c r="K284" s="2" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="L284" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M284" s="1" t="inlineStr">
@@ -22935,11 +22947,18 @@
           <t>Raisa Sousa</t>
         </is>
       </c>
-      <c r="N284" s="1" t="n"/>
+      <c r="N284" s="2" t="n">
+        <v>46223.41869637732</v>
+      </c>
       <c r="O284" s="1" t="n"/>
       <c r="P284" s="1" t="n"/>
       <c r="Q284" s="1" t="inlineStr"/>
-      <c r="R284" s="1" t="inlineStr"/>
+      <c r="R284" s="1" t="inlineStr">
+        <is>
+          <t>PROCESSO ENCONTRA-SE EM ANDAMENTO.
+TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL.</t>
+        </is>
+      </c>
       <c r="S284" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -22950,7 +22969,7 @@
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>80935</v>
+        <v>80936</v>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
@@ -22959,7 +22978,7 @@
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Individual - Serviços</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
@@ -22969,7 +22988,7 @@
       </c>
       <c r="E285" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 2681 - PARANÁ GUARULHOSTRIBUTAÇÃO: LUCRO PRESUMIDOTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: HOLDING/ESTRATÉGIAFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: H FARIAS NEGÓCIOS LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
         </is>
       </c>
       <c r="F285" s="1" t="n">
@@ -22978,7 +22997,7 @@
       <c r="G285" s="1" t="n"/>
       <c r="H285" s="1" t="inlineStr">
         <is>
-          <t>Bianca Ribeiro</t>
+          <t>Thifany Leite</t>
         </is>
       </c>
       <c r="I285" s="1" t="inlineStr">
@@ -22987,7 +23006,7 @@
         </is>
       </c>
       <c r="J285" s="2" t="n">
-        <v>46213.35976299769</v>
+        <v>46213.36620841435</v>
       </c>
       <c r="K285" s="2" t="n">
         <v>46241</v>
@@ -23003,15 +23022,14 @@
         </is>
       </c>
       <c r="N285" s="2" t="n">
-        <v>46223.41869637732</v>
+        <v>46220.45547311343</v>
       </c>
       <c r="O285" s="1" t="n"/>
       <c r="P285" s="1" t="n"/>
       <c r="Q285" s="1" t="inlineStr"/>
       <c r="R285" s="1" t="inlineStr">
         <is>
-          <t>PROCESSO ENCONTRA-SE EM ANDAMENTO.
-TRATATIVA REALIZADA COM O CLIENTE VIA E-MAIL.</t>
+          <t>Minuta enviado ao cliente</t>
         </is>
       </c>
       <c r="S285" s="1" t="inlineStr">
@@ -23024,7 +23042,7 @@
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
-        <v>80936</v>
+        <v>80951</v>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
@@ -23033,7 +23051,7 @@
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>Individual - Serviços</t>
+          <t>Individual - Comércio</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
@@ -23043,7 +23061,7 @@
       </c>
       <c r="E286" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 5442 - EQUIPOOLSTRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: SERVIÇOSFINALIDADE: OPERACIONALFORMA JURIDICA: LTDAPROPOSTA JÁ NEGOCIADA NO VALOR DE R$2.100,00RAZÃO SOCIAL: VANLOG SERVICOS DE EMBALAGEM E GALPAO LOGISTICO LTDA</t>
+          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
         </is>
       </c>
       <c r="F286" s="1" t="n">
@@ -23061,7 +23079,7 @@
         </is>
       </c>
       <c r="J286" s="2" t="n">
-        <v>46213.36620841435</v>
+        <v>46213.66707554398</v>
       </c>
       <c r="K286" s="2" t="n">
         <v>46241</v>
@@ -23077,14 +23095,14 @@
         </is>
       </c>
       <c r="N286" s="2" t="n">
-        <v>46220.45547311343</v>
+        <v>46219.74920023148</v>
       </c>
       <c r="O286" s="1" t="n"/>
       <c r="P286" s="1" t="n"/>
       <c r="Q286" s="1" t="inlineStr"/>
       <c r="R286" s="1" t="inlineStr">
         <is>
-          <t>Minuta enviado ao cliente</t>
+          <t>Minuta enviada ao cliente</t>
         </is>
       </c>
       <c r="S286" s="1" t="inlineStr">
@@ -23097,26 +23115,26 @@
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>80951</v>
+        <v>80989</v>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>Abertura de Empresa</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
         <is>
-          <t>Individual - Comércio</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D287" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA MASTER</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E287" s="1" t="inlineStr">
         <is>
-          <t>ABERTURA DE EMPRESA DO GRUPO: 3697 - BOSTON.TRIBUTAÇÃO: SIMPLES NACIONALTIPO DE ATIVIDADE: COMÉRCIOFINALIDADE: OPERACIONALFORMA JURIDICA: LTDARAZÃO SOCIAL: NOVA BOSTON GRILL RESTAURANTE LTDA</t>
+          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
         </is>
       </c>
       <c r="F287" s="1" t="n">
@@ -23125,7 +23143,7 @@
       <c r="G287" s="1" t="n"/>
       <c r="H287" s="1" t="inlineStr">
         <is>
-          <t>Thifany Leite</t>
+          <t>Ellen Leite</t>
         </is>
       </c>
       <c r="I287" s="1" t="inlineStr">
@@ -23134,10 +23152,10 @@
         </is>
       </c>
       <c r="J287" s="2" t="n">
-        <v>46213.66707554398</v>
+        <v>46216.72016431713</v>
       </c>
       <c r="K287" s="2" t="n">
-        <v>46241</v>
+        <v>46217</v>
       </c>
       <c r="L287" s="1" t="inlineStr">
         <is>
@@ -23146,18 +23164,18 @@
       </c>
       <c r="M287" s="1" t="inlineStr">
         <is>
-          <t>Raisa Sousa</t>
+          <t>João Oliveira</t>
         </is>
       </c>
       <c r="N287" s="2" t="n">
-        <v>46219.74920023148</v>
+        <v>46223.4927846875</v>
       </c>
       <c r="O287" s="1" t="n"/>
       <c r="P287" s="1" t="n"/>
       <c r="Q287" s="1" t="inlineStr"/>
       <c r="R287" s="1" t="inlineStr">
         <is>
-          <t>Minuta enviada ao cliente</t>
+          <t>Solicitação enviada à Prefeitura, aguardando retorno.</t>
         </is>
       </c>
       <c r="S287" s="1" t="inlineStr">
@@ -23170,69 +23188,63 @@
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>80989</v>
+        <v>81208</v>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Ata de Reunião de Sócios</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>Reeleição de Diretoria</t>
         </is>
       </c>
       <c r="D288" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E288" s="1" t="inlineStr">
         <is>
-          <t>Por favor, regularizar a Guia ISS gerada em duplicidade da loja 3917 de Itapecerica da Serra. Seguem anexos, guia paga, guia duplicada (para retirar) e comprovante de pagamento.</t>
+          <t>Por gentileza, encaminhar a Ata registrada para o cliente.</t>
         </is>
       </c>
       <c r="F288" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G288" s="1" t="n"/>
-      <c r="H288" s="1" t="inlineStr">
-        <is>
-          <t>Ellen Leite</t>
-        </is>
-      </c>
+        <v>5449</v>
+      </c>
+      <c r="G288" s="1" t="inlineStr">
+        <is>
+          <t>RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA</t>
+        </is>
+      </c>
+      <c r="H288" s="1" t="n"/>
       <c r="I288" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J288" s="2" t="n">
-        <v>46216.72016431713</v>
+        <v>46223.51713209491</v>
       </c>
       <c r="K288" s="2" t="n">
-        <v>46217</v>
+        <v>46225</v>
       </c>
       <c r="L288" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M288" s="1" t="inlineStr">
         <is>
-          <t>João Oliveira</t>
-        </is>
-      </c>
-      <c r="N288" s="2" t="n">
-        <v>46223.4927846875</v>
-      </c>
+          <t>Rogerio Egidio</t>
+        </is>
+      </c>
+      <c r="N288" s="1" t="n"/>
       <c r="O288" s="1" t="n"/>
       <c r="P288" s="1" t="n"/>
       <c r="Q288" s="1" t="inlineStr"/>
-      <c r="R288" s="1" t="inlineStr">
-        <is>
-          <t>Solicitação enviada à Prefeitura, aguardando retorno.</t>
-        </is>
-      </c>
+      <c r="R288" s="1" t="n"/>
       <c r="S288" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23243,16 +23255,16 @@
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>81208</v>
+        <v>79793</v>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião de Sócios</t>
+          <t>Certidão</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
         <is>
-          <t>Reeleição de Diretoria</t>
+          <t>Outras</t>
         </is>
       </c>
       <c r="D289" s="1" t="inlineStr">
@@ -23262,44 +23274,48 @@
       </c>
       <c r="E289" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, encaminhar a Ata registrada para o cliente.</t>
+          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
         </is>
       </c>
       <c r="F289" s="1" t="n">
-        <v>5449</v>
+        <v>5655</v>
       </c>
       <c r="G289" s="1" t="inlineStr">
         <is>
-          <t>RRW DISTRIBUIDORA E IMPORTADORA DE PECAS LTDA</t>
-        </is>
-      </c>
-      <c r="H289" s="1" t="n"/>
+          <t>VANESSA DUARTE RODRIGUES</t>
+        </is>
+      </c>
+      <c r="H289" s="1" t="inlineStr">
+        <is>
+          <t>Edney Xavier</t>
+        </is>
+      </c>
       <c r="I289" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J289" s="2" t="n">
-        <v>46223.51713209491</v>
+        <v>46182.60128996528</v>
       </c>
       <c r="K289" s="2" t="n">
-        <v>46225</v>
+        <v>46185</v>
       </c>
       <c r="L289" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M289" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Ricardo Ferreira</t>
         </is>
       </c>
       <c r="N289" s="1" t="n"/>
       <c r="O289" s="1" t="n"/>
       <c r="P289" s="1" t="n"/>
       <c r="Q289" s="1" t="inlineStr"/>
-      <c r="R289" s="1" t="n"/>
+      <c r="R289" s="1" t="inlineStr"/>
       <c r="S289" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23310,67 +23326,63 @@
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
-        <v>79793</v>
+        <v>81209</v>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>Certidão</t>
+          <t>Processo de Prefeitura</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
         <is>
-          <t>Outras</t>
+          <t>Geral</t>
         </is>
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
         <is>
-          <t>caros, boa tarde.cliente solicita:Certidão de inteiro TEOR junta comercial BA, e a CND Federal.apenas da empresa 5655 - Vanessa Duarte.</t>
+          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
         </is>
       </c>
       <c r="F290" s="1" t="n">
-        <v>5655</v>
+        <v>6094</v>
       </c>
       <c r="G290" s="1" t="inlineStr">
         <is>
-          <t>VANESSA DUARTE RODRIGUES</t>
-        </is>
-      </c>
-      <c r="H290" s="1" t="inlineStr">
-        <is>
-          <t>Edney Xavier</t>
-        </is>
-      </c>
+          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
+        </is>
+      </c>
+      <c r="H290" s="1" t="n"/>
       <c r="I290" s="1" t="inlineStr">
         <is>
           <t>PARALEGAL</t>
         </is>
       </c>
       <c r="J290" s="2" t="n">
-        <v>46182.60128996528</v>
+        <v>46223.52088677084</v>
       </c>
       <c r="K290" s="2" t="n">
-        <v>46185</v>
+        <v>46224</v>
       </c>
       <c r="L290" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M290" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Ferreira</t>
+          <t>Denis Reis</t>
         </is>
       </c>
       <c r="N290" s="1" t="n"/>
       <c r="O290" s="1" t="n"/>
       <c r="P290" s="1" t="n"/>
       <c r="Q290" s="1" t="inlineStr"/>
-      <c r="R290" s="1" t="inlineStr"/>
+      <c r="R290" s="1" t="n"/>
       <c r="S290" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -23381,36 +23393,32 @@
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>81209</v>
+        <v>81225</v>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>Processo de Prefeitura</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
         <is>
-          <t>Geral</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D291" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E291" s="1" t="inlineStr">
         <is>
-          <t>Cliente cancelou NFS-e posterior a emissão da guia de ISS no mês de junho e emitiu notas fiscais em junho com competência em maio, informado ao GC do ocorrido, o qual solicitou que o cliente cancelasse as notas emitidas na competência errada e que já esta encerrada e emitisse corretamente na competência de junho, contudo esta prefeitura (Itapetininga) não é possível cancelar as guias geradas de forma remota sendo necessário protocolar pessoalmente no balcão do setor de protocolos.</t>
+          <t>Boa tarde, Poderiam disponibilizar o login e senha da loja 4545 - FRIOS BRASIL. Municipio de hortolandia e o acesso e link no MGC não entra. Continuo no aguardo.</t>
         </is>
       </c>
       <c r="F291" s="1" t="n">
-        <v>6094</v>
-      </c>
-      <c r="G291" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CLINICA SAUDE &amp; VIDA LTDA </t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G291" s="1" t="n"/>
       <c r="H291" s="1" t="n"/>
       <c r="I291" s="1" t="inlineStr">
         <is>
@@ -23418,10 +23426,10 @@
         </is>
       </c>
       <c r="J291" s="2" t="n">
-        <v>46223.52088677084</v>
+        <v>46223.67691084491</v>
       </c>
       <c r="K291" s="2" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="L291" s="1" t="inlineStr">
         <is>
@@ -23430,7 +23438,7 @@
       </c>
       <c r="M291" s="1" t="inlineStr">
         <is>
-          <t>Denis Reis</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="N291" s="1" t="n"/>
@@ -23448,26 +23456,26 @@
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>81225</v>
+        <v>81227</v>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Regularização de Débitos</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t>RFB</t>
         </is>
       </c>
       <c r="D292" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>SANTOS - ADM</t>
         </is>
       </c>
       <c r="E292" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Poderiam disponibilizar o login e senha da loja 4545 - FRIOS BRASIL. Municipio de hortolandia e o acesso e link no MGC não entra. Continuo no aguardo.</t>
+          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
         </is>
       </c>
       <c r="F292" s="1" t="n">
@@ -23481,10 +23489,10 @@
         </is>
       </c>
       <c r="J292" s="2" t="n">
-        <v>46223.67691084491</v>
+        <v>46223.69836307871</v>
       </c>
       <c r="K292" s="2" t="n">
-        <v>46226</v>
+        <v>46224</v>
       </c>
       <c r="L292" s="1" t="inlineStr">
         <is>
@@ -23493,7 +23501,7 @@
       </c>
       <c r="M292" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Lidia Tavares</t>
         </is>
       </c>
       <c r="N292" s="1" t="n"/>
@@ -23511,26 +23519,26 @@
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>81227</v>
+        <v>81228</v>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>Regularização de Débitos</t>
+          <t>Senha</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
         <is>
-          <t>RFB</t>
+          <t>Prefeitura</t>
         </is>
       </c>
       <c r="D293" s="1" t="inlineStr">
         <is>
-          <t>SANTOS - ADM</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E293" s="1" t="inlineStr">
         <is>
-          <t>Empresa 5988 - Maurício Toniati - Cliente que haviamos feito a apuração incorreta de pis e cofins - Foi feito parcelamento , mais depois da retificação dos impostos não teria imposto a apagar. Gerei um relatório da situação fiscal e não consta nenhuma informação referente à Malha Fiscal, apenas a indicação de Parcelamento Suspenso.Poderia verificar, por gentileza, se há algum procedimento adicional que precise ser realizado ou alguma outra consulta que devemos efetuar?</t>
+          <t>Boa tarde, Poderiam por gentileza disponibilizar o login e senha da loja 6353.Obrigada!</t>
         </is>
       </c>
       <c r="F293" s="1" t="n">
@@ -23544,10 +23552,10 @@
         </is>
       </c>
       <c r="J293" s="2" t="n">
-        <v>46223.69836307871</v>
+        <v>46223.70694884259</v>
       </c>
       <c r="K293" s="2" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="L293" s="1" t="inlineStr">
         <is>
@@ -23556,7 +23564,7 @@
       </c>
       <c r="M293" s="1" t="inlineStr">
         <is>
-          <t>Lidia Tavares</t>
+          <t>Beatriz Ferreira</t>
         </is>
       </c>
       <c r="N293" s="1" t="n"/>
@@ -23574,26 +23582,26 @@
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>81228</v>
+        <v>81234</v>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>Senha</t>
+          <t>Cadastro de Cliente</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>Prefeitura</t>
+          <t xml:space="preserve">Alteração </t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, Poderiam por gentileza disponibilizar o login e senha da loja 6353.Obrigada!</t>
+          <t>Atualizar cadastro dos sócios da loja 2681 - COMERCIO ALVES E FARIAS.Tem 99% para a LINDELE no cadastro e a IBUACU que tbm está no quadro societário nem consta no cadastro.</t>
         </is>
       </c>
       <c r="F294" s="1" t="n">
@@ -23607,10 +23615,10 @@
         </is>
       </c>
       <c r="J294" s="2" t="n">
-        <v>46223.70694884259</v>
+        <v>46223.81885586806</v>
       </c>
       <c r="K294" s="2" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="L294" s="1" t="inlineStr">
         <is>
@@ -23619,7 +23627,7 @@
       </c>
       <c r="M294" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Ferreira</t>
+          <t>Lucas Fischer</t>
         </is>
       </c>
       <c r="N294" s="1" t="n"/>

--- a/data/base.xlsx
+++ b/data/base.xlsx
@@ -14461,51 +14461,51 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>81009</v>
+        <v>80635</v>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t>Estoque - Cobrar do cliente envio mensal do estoque, via cobrança automática!</t>
+          <t>CONCEITO - CONCILIAÇÃO EMPRESTIMO ENTRE O GRUPO Preciso que concilie os valores lançados na ESTRUTURA 6439, na CONCEITO 6427 E CZLOC 6438Att.Vander</t>
         </is>
       </c>
       <c r="F171" s="1" t="n">
-        <v>6399</v>
+        <v>6427</v>
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">LIQUIM E-BIKE LTDA </t>
+          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H171" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I171" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>46217.38787060185</v>
+        <v>46203.57973564815</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>46223</v>
+        <v>46204</v>
       </c>
       <c r="L171" s="1" t="inlineStr">
         <is>
@@ -14514,22 +14514,26 @@
       </c>
       <c r="M171" s="1" t="inlineStr">
         <is>
-          <t>Clara Maria</t>
-        </is>
-      </c>
-      <c r="N171" s="1" t="n"/>
-      <c r="O171" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="n">
+        <v>46205.39969475695</v>
+      </c>
+      <c r="O171" s="2" t="n">
+        <v>46220</v>
+      </c>
       <c r="P171" s="2" t="n">
-        <v>46223.47283167824</v>
+        <v>46220.66189042824</v>
       </c>
       <c r="Q171" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R171" s="1" t="inlineStr">
         <is>
-          <t>NÃO ENTENDI O CHAMADO</t>
+          <t>Vai ser conciliado junto ao fechamento 06/2026</t>
         </is>
       </c>
       <c r="S171" s="1" t="inlineStr">
@@ -14540,22 +14544,22 @@
       <c r="T171" s="1" t="n"/>
       <c r="U171" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>80635</v>
+        <v>81029</v>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D172" s="1" t="inlineStr">
@@ -14565,7 +14569,7 @@
       </c>
       <c r="E172" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO - CONCILIAÇÃO EMPRESTIMO ENTRE O GRUPO Preciso que concilie os valores lançados na ESTRUTURA 6439, na CONCEITO 6427 E CZLOC 6438Att.Vander</t>
+          <t>CONCEITO 6427 - COMPENSAÇÃO DE DEBITO DE ICMS COM O CRÉDITO ACUMULADO DA MATRIZPreciso que zero o saldo devedor de ICMS da filial com o saldo credor da MATRIZAtt.Vander</t>
         </is>
       </c>
       <c r="F172" s="1" t="n">
@@ -14578,19 +14582,19 @@
       </c>
       <c r="H172" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I172" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>46203.57973564815</v>
+        <v>46217.49787554398</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="L172" s="1" t="inlineStr">
         <is>
@@ -14602,23 +14606,20 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N172" s="2" t="n">
-        <v>46205.39969475695</v>
-      </c>
-      <c r="O172" s="2" t="n">
-        <v>46220</v>
-      </c>
+      <c r="N172" s="1" t="n"/>
+      <c r="O172" s="1" t="n"/>
       <c r="P172" s="2" t="n">
-        <v>46220.66189042824</v>
+        <v>46223.46101160879</v>
       </c>
       <c r="Q172" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="R172" s="1" t="inlineStr">
         <is>
-          <t>Vai ser conciliado junto ao fechamento 06/2026</t>
+          <t>BOM DIA, 
+JÁ SOLICITADO</t>
         </is>
       </c>
       <c r="S172" s="1" t="inlineStr">
@@ -14629,22 +14630,22 @@
       <c r="T172" s="1" t="n"/>
       <c r="U172" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>81029</v>
+        <v>81157</v>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D173" s="1" t="inlineStr">
@@ -14654,7 +14655,7 @@
       </c>
       <c r="E173" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO 6427 - COMPENSAÇÃO DE DEBITO DE ICMS COM O CRÉDITO ACUMULADO DA MATRIZPreciso que zero o saldo devedor de ICMS da filial com o saldo credor da MATRIZAtt.Vander</t>
+          <t>CONCEITO - BALANCETES DE IMPLANTAÇÃO - 01 A 08 DE 2025Solicitação do Master, para inclusão de balanço de implantação com urgência. Depois disponibilizar balanço e DRE 2025.Solicitação de conclusão até amanhã 17/07/2026.Att.Vander</t>
         </is>
       </c>
       <c r="F173" s="1" t="n">
@@ -14667,23 +14668,23 @@
       </c>
       <c r="H173" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I173" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>46217.49787554398</v>
+        <v>46219.63261427083</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="L173" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M173" s="1" t="inlineStr">
@@ -14692,45 +14693,36 @@
         </is>
       </c>
       <c r="N173" s="1" t="n"/>
-      <c r="O173" s="1" t="n"/>
-      <c r="P173" s="2" t="n">
-        <v>46223.46101160879</v>
-      </c>
-      <c r="Q173" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="R173" s="1" t="inlineStr">
-        <is>
-          <t>BOM DIA, 
-JÁ SOLICITADO</t>
-        </is>
-      </c>
+      <c r="O173" s="2" t="n">
+        <v>46225</v>
+      </c>
+      <c r="P173" s="1" t="n"/>
+      <c r="Q173" s="1" t="inlineStr"/>
+      <c r="R173" s="1" t="inlineStr"/>
       <c r="S173" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T173" s="1" t="n"/>
       <c r="U173" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>81157</v>
+        <v>81030</v>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
@@ -14740,36 +14732,36 @@
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO - BALANCETES DE IMPLANTAÇÃO - 01 A 08 DE 2025Solicitação do Master, para inclusão de balanço de implantação com urgência. Depois disponibilizar balanço e DRE 2025.Solicitação de conclusão até amanhã 17/07/2026.Att.Vander</t>
+          <t>6438 - CZLOC - PIS E COFINS 02/2026Corrigir divergência de valores entre o SPED CONTRIBUIÇÃO e valor devido na RFB hoje. Atualizar e enviar boletos com vencimento para 31/07/2026Att.Vander</t>
         </is>
       </c>
       <c r="F174" s="1" t="n">
-        <v>6427</v>
+        <v>6438</v>
       </c>
       <c r="G174" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO LOCADORA LTDA (MATRIZ)</t>
+          <t>CZLOC LOCACAO DE EQUIPAMENTOS PARA CONSTRUCAO CIVIL LTDA</t>
         </is>
       </c>
       <c r="H174" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I174" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>46219.63261427083</v>
+        <v>46217.51475706018</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>46220</v>
+        <v>46219</v>
       </c>
       <c r="L174" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M174" s="1" t="inlineStr">
@@ -14777,13 +14769,17 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N174" s="1" t="n"/>
-      <c r="O174" s="2" t="n">
-        <v>46225</v>
-      </c>
+      <c r="N174" s="2" t="n">
+        <v>46223.46244545139</v>
+      </c>
+      <c r="O174" s="1" t="n"/>
       <c r="P174" s="1" t="n"/>
       <c r="Q174" s="1" t="inlineStr"/>
-      <c r="R174" s="1" t="inlineStr"/>
+      <c r="R174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EM ATENDIMENTO PELA OPERAÇÃO </t>
+        </is>
+      </c>
       <c r="S174" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -14792,22 +14788,22 @@
       <c r="T174" s="1" t="n"/>
       <c r="U174" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>81030</v>
+        <v>80641</v>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -14817,36 +14813,36 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t>6438 - CZLOC - PIS E COFINS 02/2026Corrigir divergência de valores entre o SPED CONTRIBUIÇÃO e valor devido na RFB hoje. Atualizar e enviar boletos com vencimento para 31/07/2026Att.Vander</t>
+          <t>6439 - CONCEITO ESTRUTURA - CONTA EMPRESTIMO ENTRE EMPRESAS NO ATIVOPreciso que avalie novamente se os terceiros lançados nesta conta estão corretos, os terceiros que permanecer quero saber o motivo. Conta: 921181 01.2.1.10.001  Empréstimo entre EmpresasAtt.Vander</t>
         </is>
       </c>
       <c r="F175" s="1" t="n">
-        <v>6438</v>
+        <v>6439</v>
       </c>
       <c r="G175" s="1" t="inlineStr">
         <is>
-          <t>CZLOC LOCACAO DE EQUIPAMENTOS PARA CONSTRUCAO CIVIL LTDA</t>
+          <t>CONCEITO ESTRUTURA LOCADORA LTDA</t>
         </is>
       </c>
       <c r="H175" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I175" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>46217.51475706018</v>
+        <v>46203.60078723379</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>46219</v>
+        <v>46204</v>
       </c>
       <c r="L175" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M175" s="1" t="inlineStr">
@@ -14855,75 +14851,83 @@
         </is>
       </c>
       <c r="N175" s="2" t="n">
-        <v>46223.46244545139</v>
-      </c>
-      <c r="O175" s="1" t="n"/>
-      <c r="P175" s="1" t="n"/>
-      <c r="Q175" s="1" t="inlineStr"/>
+        <v>46216.75252230324</v>
+      </c>
+      <c r="O175" s="2" t="n">
+        <v>46218</v>
+      </c>
+      <c r="P175" s="2" t="n">
+        <v>46220.66202916667</v>
+      </c>
+      <c r="Q175" s="1" t="inlineStr">
+        <is>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
       <c r="R175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">EM ATENDIMENTO PELA OPERAÇÃO </t>
+          <t>Vai ser feito no fechamento</t>
         </is>
       </c>
       <c r="S175" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T175" s="1" t="n"/>
       <c r="U175" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>80641</v>
+        <v>79681</v>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t>6439 - CONCEITO ESTRUTURA - CONTA EMPRESTIMO ENTRE EMPRESAS NO ATIVOPreciso que avalie novamente se os terceiros lançados nesta conta estão corretos, os terceiros que permanecer quero saber o motivo. Conta: 921181 01.2.1.10.001  Empréstimo entre EmpresasAtt.Vander</t>
+          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2025/2026 até abril</t>
         </is>
       </c>
       <c r="F176" s="1" t="n">
-        <v>6439</v>
+        <v>6440</v>
       </c>
       <c r="G176" s="1" t="inlineStr">
         <is>
-          <t>CONCEITO ESTRUTURA LOCADORA LTDA</t>
+          <t>INFINITY UTILIDADES LTDA</t>
         </is>
       </c>
       <c r="H176" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Renata Cavalheiro</t>
         </is>
       </c>
       <c r="I176" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>46203.60078723379</v>
+        <v>46176.66350790509</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>46204</v>
+        <v>46178</v>
       </c>
       <c r="L176" s="1" t="inlineStr">
         <is>
@@ -14932,26 +14936,22 @@
       </c>
       <c r="M176" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N176" s="2" t="n">
-        <v>46216.75252230324</v>
-      </c>
-      <c r="O176" s="2" t="n">
-        <v>46218</v>
-      </c>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N176" s="1" t="n"/>
+      <c r="O176" s="1" t="n"/>
       <c r="P176" s="2" t="n">
-        <v>46220.66202916667</v>
+        <v>46182.75284528935</v>
       </c>
       <c r="Q176" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Renata Cavalheiro</t>
         </is>
       </c>
       <c r="R176" s="1" t="inlineStr">
         <is>
-          <t>Vai ser feito no fechamento</t>
+          <t>Enviado por e-mail em 08/06.</t>
         </is>
       </c>
       <c r="S176" s="1" t="inlineStr">
@@ -14960,15 +14960,11 @@
         </is>
       </c>
       <c r="T176" s="1" t="n"/>
-      <c r="U176" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="U176" s="1" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>79681</v>
+        <v>79744</v>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
@@ -14987,7 +14983,7 @@
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2025/2026 até abril</t>
+          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2023/2024</t>
         </is>
       </c>
       <c r="F177" s="1" t="n">
@@ -15000,7 +14996,7 @@
       </c>
       <c r="H177" s="1" t="inlineStr">
         <is>
-          <t>Renata Cavalheiro</t>
+          <t>ryang</t>
         </is>
       </c>
       <c r="I177" s="1" t="inlineStr">
@@ -15009,10 +15005,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>46176.66350790509</v>
+        <v>46181.41362399305</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="L177" s="1" t="inlineStr">
         <is>
@@ -15027,16 +15023,13 @@
       <c r="N177" s="1" t="n"/>
       <c r="O177" s="1" t="n"/>
       <c r="P177" s="2" t="n">
-        <v>46182.75284528935</v>
-      </c>
-      <c r="Q177" s="1" t="inlineStr">
-        <is>
-          <t>Renata Cavalheiro</t>
-        </is>
-      </c>
+        <v>46181.47254537037</v>
+      </c>
+      <c r="Q177" s="1" t="n"/>
       <c r="R177" s="1" t="inlineStr">
         <is>
-          <t>Enviado por e-mail em 08/06.</t>
+          <t>Boa tarde!
+A loja 6440 Infinity não estava na MG nessa época.</t>
         </is>
       </c>
       <c r="S177" s="1" t="inlineStr">
@@ -15049,16 +15042,16 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>79744</v>
+        <v>81168</v>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
@@ -15068,93 +15061,97 @@
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, providenciar balanço e DRE do grupo INFINITY do seguinte periodo: 2023/2024</t>
+          <t>Boa tarde! Por gentileza, verificar saldo credor incorreto. Cliente precisa de uma CND.</t>
         </is>
       </c>
       <c r="F178" s="1" t="n">
-        <v>6440</v>
+        <v>6443</v>
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t>INFINITY UTILIDADES LTDA</t>
+          <t>INDUSTRIA E COMERCIO RAIZES DO NORDESTE LTDA</t>
         </is>
       </c>
       <c r="H178" s="1" t="inlineStr">
         <is>
-          <t>ryang</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I178" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>46181.41362399305</v>
+        <v>46219.77042769676</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>46182</v>
+        <v>46223</v>
       </c>
       <c r="L178" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M178" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
-        </is>
-      </c>
-      <c r="N178" s="1" t="n"/>
+          <t>Ana Santana</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="n">
+        <v>46223.48236674769</v>
+      </c>
       <c r="O178" s="1" t="n"/>
-      <c r="P178" s="2" t="n">
-        <v>46181.47254537037</v>
-      </c>
-      <c r="Q178" s="1" t="n"/>
+      <c r="P178" s="1" t="n"/>
+      <c r="Q178" s="1" t="inlineStr"/>
       <c r="R178" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde!
-A loja 6440 Infinity não estava na MG nessa época.</t>
+          <t xml:space="preserve">OPERAÇÃO EM EXECUÇÃO 
+</t>
         </is>
       </c>
       <c r="S178" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T178" s="1" t="n"/>
-      <c r="U178" s="1" t="inlineStr"/>
+      <c r="U178" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>81168</v>
+        <v>79588</v>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, verificar saldo credor incorreto. Cliente precisa de uma CND.</t>
+          <t xml:space="preserve">Regularizar pendência de Omissão de EFD 02.2026 Saldo de transporte incorreto </t>
         </is>
       </c>
       <c r="F179" s="1" t="n">
-        <v>6443</v>
+        <v>6460</v>
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t>INDUSTRIA E COMERCIO RAIZES DO NORDESTE LTDA</t>
+          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H179" s="1" t="inlineStr">
@@ -15164,34 +15161,32 @@
       </c>
       <c r="I179" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>46219.77042769676</v>
+        <v>46174.63777623843</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>46223</v>
+        <v>46176</v>
       </c>
       <c r="L179" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M179" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
-        </is>
-      </c>
-      <c r="N179" s="2" t="n">
-        <v>46223.48236674769</v>
-      </c>
+          <t>Simone Marques</t>
+        </is>
+      </c>
+      <c r="N179" s="1" t="n"/>
       <c r="O179" s="1" t="n"/>
       <c r="P179" s="1" t="n"/>
       <c r="Q179" s="1" t="inlineStr"/>
       <c r="R179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPERAÇÃO EM EXECUÇÃO 
+          <t xml:space="preserve">OPERAÇÃO EM FASE DE RETIFICAÇÃO - PRAZO 12/06/2026
 </t>
         </is>
       </c>
@@ -15200,7 +15195,11 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T179" s="1" t="n"/>
+      <c r="T179" s="1" t="inlineStr">
+        <is>
+          <t>EF - INDUSTRIA</t>
+        </is>
+      </c>
       <c r="U179" s="1" t="inlineStr">
         <is>
           <t>Nayara Oliveira</t>
@@ -15209,26 +15208,26 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>79588</v>
+        <v>80645</v>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Pendência de Débito</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Regularizar pendência de Omissão de EFD 02.2026 Saldo de transporte incorreto </t>
+          <t>Boa tarde! Por gentileza, verificar a pendencia de débito. Valor divergente da guia encaminhada ao cliente.</t>
         </is>
       </c>
       <c r="F180" s="1" t="n">
@@ -15246,45 +15245,47 @@
       </c>
       <c r="I180" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>46174.63777623843</v>
+        <v>46203.62030621528</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="L180" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M180" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N180" s="1" t="n"/>
       <c r="O180" s="1" t="n"/>
-      <c r="P180" s="1" t="n"/>
-      <c r="Q180" s="1" t="inlineStr"/>
+      <c r="P180" s="2" t="n">
+        <v>46205.57428920139</v>
+      </c>
+      <c r="Q180" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPERAÇÃO EM FASE DE RETIFICAÇÃO - PRAZO 12/06/2026
-</t>
+          <t>boa tarde
+retificação realizada na data de 02-07</t>
         </is>
       </c>
       <c r="S180" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="T180" s="1" t="inlineStr">
-        <is>
-          <t>EF - INDUSTRIA</t>
-        </is>
-      </c>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T180" s="1" t="n"/>
       <c r="U180" s="1" t="inlineStr">
         <is>
           <t>Nayara Oliveira</t>
@@ -15293,93 +15294,74 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>80645</v>
+        <v>81216</v>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
         <is>
-          <t>Pendência de Débito</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, verificar a pendencia de débito. Valor divergente da guia encaminhada ao cliente.</t>
+          <t>6499 - DFG COMERCIO - DEPRECIAÇÃO 2026Preciso que façam as depreciações da empresa, com urgência, por favor.Att.Vander</t>
         </is>
       </c>
       <c r="F181" s="1" t="n">
-        <v>6460</v>
+        <v>6499</v>
       </c>
       <c r="G181" s="1" t="inlineStr">
         <is>
-          <t>NOR - IMPORT COMERCIAL DE ALIMENTOS LTDA (MATRIZ)</t>
-        </is>
-      </c>
-      <c r="H181" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
+          <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="n"/>
       <c r="I181" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>46203.62030621528</v>
+        <v>46223.60524675926</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>46206</v>
+        <v>46224</v>
       </c>
       <c r="L181" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M181" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N181" s="1" t="n"/>
       <c r="O181" s="1" t="n"/>
-      <c r="P181" s="2" t="n">
-        <v>46205.57428920139</v>
-      </c>
-      <c r="Q181" s="1" t="inlineStr">
-        <is>
-          <t>Priscila Volpe</t>
-        </is>
-      </c>
-      <c r="R181" s="1" t="inlineStr">
-        <is>
-          <t>boa tarde
-retificação realizada na data de 02-07</t>
-        </is>
-      </c>
+      <c r="P181" s="1" t="n"/>
+      <c r="Q181" s="1" t="inlineStr"/>
+      <c r="R181" s="1" t="n"/>
       <c r="S181" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T181" s="1" t="n"/>
-      <c r="U181" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U181" s="1" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>81216</v>
+        <v>81226</v>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
@@ -15398,7 +15380,7 @@
       </c>
       <c r="E182" s="1" t="inlineStr">
         <is>
-          <t>6499 - DFG COMERCIO - DEPRECIAÇÃO 2026Preciso que façam as depreciações da empresa, com urgência, por favor.Att.Vander</t>
+          <t>DFG - INFORMATIÇÃO DE ESTOQUEPreciso que seja ajustados os saldos de estoque conforme informações do bloco k, 06/2026 enviado no DRIVER. OBS: 03/2026 vocês conseguem as informações de estoque pelo Receita Net BX. Contábil e fiscal precisam trabalhar juntos.Att.Vander</t>
         </is>
       </c>
       <c r="F182" s="1" t="n">
@@ -15416,7 +15398,7 @@
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>46223.60524675926</v>
+        <v>46223.68591797454</v>
       </c>
       <c r="K182" s="2" t="n">
         <v>46224</v>
@@ -15446,16 +15428,16 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>81226</v>
+        <v>80116</v>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
@@ -15465,99 +15447,118 @@
       </c>
       <c r="E183" s="1" t="inlineStr">
         <is>
-          <t>DFG - INFORMATIÇÃO DE ESTOQUEPreciso que seja ajustados os saldos de estoque conforme informações do bloco k, 06/2026 enviado no DRIVER. OBS: 03/2026 vocês conseguem as informações de estoque pelo Receita Net BX. Contábil e fiscal precisam trabalhar juntos.Att.Vander</t>
+          <t>O Master Eduardo nos informou que os faturamentos referentes aos períodos 10/2025, 11/2025 e 02/2026 apresentam divergências.Por gentileza, verifiquem a planilha encaminhada pela Elaine, contendo os valores de receita informados, e nos informem o motivo dessas diferenças.</t>
         </is>
       </c>
       <c r="F183" s="1" t="n">
-        <v>6499</v>
+        <v>6520</v>
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t>DFG COMERCIO IMPORTACAO, EXPORTACAO E REPRESENTACAO LTDA</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="n"/>
+          <t>BONNARO COMERCIO E REPRESENTAÇÃO LTDA</t>
+        </is>
+      </c>
+      <c r="H183" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="I183" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>46223.68591797454</v>
+        <v>46189.71619001158</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>46224</v>
+        <v>46191</v>
       </c>
       <c r="L183" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M183" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N183" s="1" t="n"/>
       <c r="O183" s="1" t="n"/>
-      <c r="P183" s="1" t="n"/>
-      <c r="Q183" s="1" t="inlineStr"/>
-      <c r="R183" s="1" t="n"/>
+      <c r="P183" s="2" t="n">
+        <v>46199.69882708333</v>
+      </c>
+      <c r="Q183" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
+      <c r="R183" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boa tarde, 
+Foi passado um e-mail sobre esse assunto, referente as notas fiscais não recebidas pela cliente na época. Aguardando resposta da gerencia para a resolcução do caso. </t>
+        </is>
+      </c>
       <c r="S183" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T183" s="1" t="n"/>
-      <c r="U183" s="1" t="inlineStr"/>
+      <c r="U183" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>80116</v>
+        <v>80707</v>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Balanço e DRE</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t>O Master Eduardo nos informou que os faturamentos referentes aos períodos 10/2025, 11/2025 e 02/2026 apresentam divergências.Por gentileza, verifiquem a planilha encaminhada pela Elaine, contendo os valores de receita informados, e nos informem o motivo dessas diferenças.</t>
+          <t>Prezados, boa tarde!Por gentileza, solicito o envio do Balanço Patrimonial e da DRE mais recentes da empresa NAKABOX - COMÉRCIO DE PEÇAS E ACESSÓRIOS PARA VEÍCULOS E MOTOCICLETAS LTDA.Tentei gerar os demonstrativos por aqui, porém identifiquei divergência entre o Ativo e o PassivoDesde já, agradeço pela atenção e fico no aguardo do retorno.</t>
         </is>
       </c>
       <c r="F184" s="1" t="n">
-        <v>6520</v>
+        <v>6537</v>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t>BONNARO COMERCIO E REPRESENTAÇÃO LTDA</t>
+          <t xml:space="preserve">NAKABOX - COMERCIO DE PECAS E ACESSORIOS PARA VEICULOS E MOTOCICLETAS LTDA  </t>
         </is>
       </c>
       <c r="H184" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I184" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>46189.71619001158</v>
+        <v>46205.65223012731</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>46191</v>
+        <v>46206</v>
       </c>
       <c r="L184" s="1" t="inlineStr">
         <is>
@@ -15566,23 +15567,24 @@
       </c>
       <c r="M184" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Victoria Virgens</t>
         </is>
       </c>
       <c r="N184" s="1" t="n"/>
-      <c r="O184" s="1" t="n"/>
+      <c r="O184" s="2" t="n">
+        <v>46218</v>
+      </c>
       <c r="P184" s="2" t="n">
-        <v>46199.69882708333</v>
+        <v>46220.66110667824</v>
       </c>
       <c r="Q184" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boa tarde, 
-Foi passado um e-mail sobre esse assunto, referente as notas fiscais não recebidas pela cliente na época. Aguardando resposta da gerencia para a resolcução do caso. </t>
+          <t>Enviado no email 14/07</t>
         </is>
       </c>
       <c r="S184" s="1" t="inlineStr">
@@ -15593,13 +15595,13 @@
       <c r="T184" s="1" t="n"/>
       <c r="U184" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>80707</v>
+        <v>80943</v>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
@@ -15613,20 +15615,20 @@
       </c>
       <c r="D185" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t>Prezados, boa tarde!Por gentileza, solicito o envio do Balanço Patrimonial e da DRE mais recentes da empresa NAKABOX - COMÉRCIO DE PEÇAS E ACESSÓRIOS PARA VEÍCULOS E MOTOCICLETAS LTDA.Tentei gerar os demonstrativos por aqui, porém identifiquei divergência entre o Ativo e o PassivoDesde já, agradeço pela atenção e fico no aguardo do retorno.</t>
+          <t>6559 - ACERTONLINE - BALANÇO DE IMPLANTAÇÃOPrezados,Segue balanço de implantação.Fonte: Receita NetBXAtt.Vander</t>
         </is>
       </c>
       <c r="F185" s="1" t="n">
-        <v>6537</v>
+        <v>6559</v>
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">NAKABOX - COMERCIO DE PECAS E ACESSORIOS PARA VEICULOS E MOTOCICLETAS LTDA  </t>
+          <t>ACERTONLINE ASSESSORIA EMPRESARIAL LTDA</t>
         </is>
       </c>
       <c r="H185" s="1" t="inlineStr">
@@ -15640,41 +15642,37 @@
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>46205.65223012731</v>
+        <v>46213.52011203704</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="L185" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M185" s="1" t="inlineStr">
         <is>
-          <t>Victoria Virgens</t>
-        </is>
-      </c>
-      <c r="N185" s="1" t="n"/>
+          <t>Vander Silva</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="n">
+        <v>46216.74338672453</v>
+      </c>
       <c r="O185" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="P185" s="2" t="n">
-        <v>46220.66110667824</v>
-      </c>
-      <c r="Q185" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+        <v>46234</v>
+      </c>
+      <c r="P185" s="1" t="n"/>
+      <c r="Q185" s="1" t="inlineStr"/>
       <c r="R185" s="1" t="inlineStr">
         <is>
-          <t>Enviado no email 14/07</t>
+          <t>Vai ser implantado junto ao fechamento do trimestre</t>
         </is>
       </c>
       <c r="S185" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T185" s="1" t="n"/>
@@ -15686,134 +15684,136 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>80943</v>
+        <v>79800</v>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t>Balanço e DRE</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t>6559 - ACERTONLINE - BALANÇO DE IMPLANTAÇÃOPrezados,Segue balanço de implantação.Fonte: Receita NetBXAtt.Vander</t>
+          <t>Segue em anexo mensagem DEC Estadual do cliente: 6608 - Restaurante FLV raizComplemento do Assunto: 1o. processo de suspensão de 2026Omissão da entrega de GIAs/EFDs referencia Abril, Maio e Junho de 2025.</t>
         </is>
       </c>
       <c r="F186" s="1" t="n">
-        <v>6559</v>
+        <v>6608</v>
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t>ACERTONLINE ASSESSORIA EMPRESARIAL LTDA</t>
+          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
         </is>
       </c>
       <c r="H186" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I186" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J186" s="2" t="n">
-        <v>46213.52011203704</v>
+        <v>46182.64716554398</v>
       </c>
       <c r="K186" s="2" t="n">
-        <v>46216</v>
+        <v>46189</v>
       </c>
       <c r="L186" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M186" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
-        </is>
-      </c>
-      <c r="N186" s="2" t="n">
-        <v>46216.74338672453</v>
-      </c>
-      <c r="O186" s="2" t="n">
-        <v>46234</v>
-      </c>
-      <c r="P186" s="1" t="n"/>
-      <c r="Q186" s="1" t="inlineStr"/>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N186" s="1" t="n"/>
+      <c r="O186" s="1" t="n"/>
+      <c r="P186" s="2" t="n">
+        <v>46182.78246716435</v>
+      </c>
+      <c r="Q186" s="1" t="inlineStr">
+        <is>
+          <t>Ricardo Fischer</t>
+        </is>
+      </c>
       <c r="R186" s="1" t="inlineStr">
         <is>
-          <t>Vai ser implantado junto ao fechamento do trimestre</t>
+          <t>Situação já resolvida com a entrega das obrigações</t>
         </is>
       </c>
       <c r="S186" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T186" s="1" t="n"/>
       <c r="U186" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>79800</v>
+        <v>80535</v>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Material de Reunião - Solicitação Interna</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Material de Reunião - Solicitação Interna</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t>Segue em anexo mensagem DEC Estadual do cliente: 6608 - Restaurante FLV raizComplemento do Assunto: 1o. processo de suspensão de 2026Omissão da entrega de GIAs/EFDs referencia Abril, Maio e Junho de 2025.</t>
+          <t>GTG - BALANÇO E DRE DE IMPLANTAÇÃO@Isabella Nascimento - CTI, bom dia!Preciso que lance o saldo anterior, antes da próxima reunião 02/07.Documentação está na MG desde 25 de março.Att. Vander</t>
         </is>
       </c>
       <c r="F187" s="1" t="n">
-        <v>6608</v>
+        <v>6627</v>
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t>RESTAURANTE FLV RAIZ LTDA (FILIAL 4)</t>
+          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="H187" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I187" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J187" s="2" t="n">
-        <v>46182.64716554398</v>
+        <v>46197.52568237269</v>
       </c>
       <c r="K187" s="2" t="n">
-        <v>46189</v>
+        <v>46197</v>
       </c>
       <c r="L187" s="1" t="inlineStr">
         <is>
@@ -15822,22 +15822,24 @@
       </c>
       <c r="M187" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N187" s="1" t="n"/>
-      <c r="O187" s="1" t="n"/>
+      <c r="O187" s="2" t="n">
+        <v>46219</v>
+      </c>
       <c r="P187" s="2" t="n">
-        <v>46182.78246716435</v>
+        <v>46220.65923896991</v>
       </c>
       <c r="Q187" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R187" s="1" t="inlineStr">
         <is>
-          <t>Situação já resolvida com a entrega das obrigações</t>
+          <t>Vai ser lançado no fechamento</t>
         </is>
       </c>
       <c r="S187" s="1" t="inlineStr">
@@ -15848,22 +15850,22 @@
       <c r="T187" s="1" t="n"/>
       <c r="U187" s="1" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>80535</v>
+        <v>80569</v>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>Material de Reunião - Solicitação Interna</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
         <is>
-          <t>Material de Reunião - Solicitação Interna</t>
+          <t>DCTFWeb</t>
         </is>
       </c>
       <c r="D188" s="1" t="inlineStr">
@@ -15873,32 +15875,32 @@
       </c>
       <c r="E188" s="1" t="inlineStr">
         <is>
-          <t>GTG - BALANÇO E DRE DE IMPLANTAÇÃO@Isabella Nascimento - CTI, bom dia!Preciso que lance o saldo anterior, antes da próxima reunião 02/07.Documentação está na MG desde 25 de março.Att. Vander</t>
+          <t>Constam pendências de PIS-COFINS com códigos que não correspondem com as guias publicas e pagas pelo cliente.Por gentileza, verificar e regularizar.</t>
         </is>
       </c>
       <c r="F188" s="1" t="n">
-        <v>6627</v>
+        <v>6639</v>
       </c>
       <c r="G188" s="1" t="inlineStr">
         <is>
-          <t>GTG EMPREENDIMENTOS SERVIÇOS E COMERCIO LTDA</t>
+          <t>TRANSPORTE FORT FRUIT LTDA</t>
         </is>
       </c>
       <c r="H188" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="I188" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="J188" s="2" t="n">
-        <v>46197.52568237269</v>
+        <v>46198.76468001158</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>46197</v>
+        <v>46203</v>
       </c>
       <c r="L188" s="1" t="inlineStr">
         <is>
@@ -15907,133 +15909,121 @@
       </c>
       <c r="M188" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="N188" s="1" t="n"/>
-      <c r="O188" s="2" t="n">
-        <v>46219</v>
-      </c>
+      <c r="O188" s="1" t="n"/>
       <c r="P188" s="2" t="n">
-        <v>46220.65923896991</v>
+        <v>46206.68733584491</v>
       </c>
       <c r="Q188" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="R188" s="1" t="inlineStr">
-        <is>
-          <t>Vai ser lançado no fechamento</t>
-        </is>
-      </c>
-      <c r="S188" s="1" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-      <c r="T188" s="1" t="n"/>
-      <c r="U188" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="1" t="n">
-        <v>80569</v>
-      </c>
-      <c r="B189" s="1" t="inlineStr">
-        <is>
-          <t>DCTFWeb</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr">
-        <is>
-          <t>DCTFWeb</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
-      <c r="E189" s="1" t="inlineStr">
-        <is>
-          <t>Constam pendências de PIS-COFINS com códigos que não correspondem com as guias publicas e pagas pelo cliente.Por gentileza, verificar e regularizar.</t>
-        </is>
-      </c>
-      <c r="F189" s="1" t="n">
-        <v>6639</v>
-      </c>
-      <c r="G189" s="1" t="inlineStr">
-        <is>
-          <t>TRANSPORTE FORT FRUIT LTDA</t>
-        </is>
-      </c>
-      <c r="H189" s="1" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
-      <c r="I189" s="1" t="inlineStr">
-        <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>46198.76468001158</v>
-      </c>
-      <c r="K189" s="2" t="n">
-        <v>46203</v>
-      </c>
-      <c r="L189" s="1" t="inlineStr">
-        <is>
-          <t>Entregue Ao Solicitante</t>
-        </is>
-      </c>
-      <c r="M189" s="1" t="inlineStr">
-        <is>
-          <t>Bruno Contieri</t>
-        </is>
-      </c>
-      <c r="N189" s="1" t="n"/>
-      <c r="O189" s="1" t="n"/>
-      <c r="P189" s="2" t="n">
-        <v>46206.68733584491</v>
-      </c>
-      <c r="Q189" s="1" t="inlineStr">
-        <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
-      <c r="R189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Boa tarde
 Mit e dctfweb já realizada a retificação
 </t>
         </is>
       </c>
+      <c r="S188" s="1" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="T188" s="1" t="n"/>
+      <c r="U188" s="1" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>80570</v>
+      </c>
+      <c r="B189" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="inlineStr">
+        <is>
+          <t>Saldo Credor Incorreto</t>
+        </is>
+      </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
+      <c r="E189" s="1" t="inlineStr">
+        <is>
+          <t>Favor providenciar regularização de transporte de saldo credor incorreto 01, 02, 03, 04 e 05/2026.</t>
+        </is>
+      </c>
+      <c r="F189" s="1" t="n">
+        <v>6640</v>
+      </c>
+      <c r="G189" s="1" t="inlineStr">
+        <is>
+          <t>FORT FRUIT LTDA</t>
+        </is>
+      </c>
+      <c r="H189" s="1" t="inlineStr">
+        <is>
+          <t>Thaiza Oliveira</t>
+        </is>
+      </c>
+      <c r="I189" s="1" t="inlineStr">
+        <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="J189" s="2" t="n">
+        <v>46198.77076709491</v>
+      </c>
+      <c r="K189" s="2" t="n">
+        <v>46206</v>
+      </c>
+      <c r="L189" s="1" t="inlineStr">
+        <is>
+          <t>Esperando Atendimento</t>
+        </is>
+      </c>
+      <c r="M189" s="1" t="inlineStr">
+        <is>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N189" s="1" t="n"/>
+      <c r="O189" s="1" t="n"/>
+      <c r="P189" s="1" t="n"/>
+      <c r="Q189" s="1" t="inlineStr"/>
+      <c r="R189" s="1" t="inlineStr"/>
       <c r="S189" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T189" s="1" t="n"/>
-      <c r="U189" s="1" t="inlineStr"/>
+      <c r="U189" s="1" t="inlineStr">
+        <is>
+          <t>Claudineia Rodrigues</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Omissão de Obrigações Acessórias</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
@@ -16043,15 +16033,15 @@
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t>Favor providenciar regularização de transporte de saldo credor incorreto 01, 02, 03, 04 e 05/2026.</t>
+          <t>Por gentileza, verificar ocorrências nas declarações 04, 05, 06, 07, 08, 09/2025 GIA/EFD.</t>
         </is>
       </c>
       <c r="F190" s="1" t="n">
-        <v>6640</v>
+        <v>6641</v>
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t>FORT FRUIT LTDA</t>
+          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
         </is>
       </c>
       <c r="H190" s="1" t="inlineStr">
@@ -16065,7 +16055,7 @@
         </is>
       </c>
       <c r="J190" s="2" t="n">
-        <v>46198.77076709491</v>
+        <v>46198.7760443287</v>
       </c>
       <c r="K190" s="2" t="n">
         <v>46206</v>
@@ -16099,16 +16089,16 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>80571</v>
+        <v>80509</v>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Ata de Reunião</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
         <is>
-          <t>Omissão de Obrigações Acessórias</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D191" s="1" t="inlineStr">
@@ -16118,48 +16108,52 @@
       </c>
       <c r="E191" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza, verificar ocorrências nas declarações 04, 05, 06, 07, 08, 09/2025 GIA/EFD.</t>
+          <t>Boa tarde, segue apontamento feito em ATA referente o fechamento 04/2026: Não foi considerado o crédito sobre a despesa de 219mil, solicito que seja retificada a apuração. Cliente salvou as NFs no DRIVE MG</t>
         </is>
       </c>
       <c r="F191" s="1" t="n">
-        <v>6641</v>
+        <v>6697</v>
       </c>
       <c r="G191" s="1" t="inlineStr">
         <is>
-          <t>FORT-FRUIT COMERCIO E DISTRIBUICAO LTDA</t>
+          <t>HEAD INFORMATICA MULTIMARCAS LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H191" s="1" t="inlineStr">
         <is>
-          <t>Thaiza Oliveira</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I191" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J191" s="2" t="n">
-        <v>46198.7760443287</v>
+        <v>46196.61037410879</v>
       </c>
       <c r="K191" s="2" t="n">
-        <v>46206</v>
+        <v>46198</v>
       </c>
       <c r="L191" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Responsável</t>
         </is>
       </c>
       <c r="M191" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N191" s="1" t="n"/>
       <c r="O191" s="1" t="n"/>
       <c r="P191" s="1" t="n"/>
       <c r="Q191" s="1" t="inlineStr"/>
-      <c r="R191" s="1" t="inlineStr"/>
+      <c r="R191" s="1" t="inlineStr">
+        <is>
+          <t>operação analisando os  questionamentos em relação ao serviços tomados de market place</t>
+        </is>
+      </c>
       <c r="S191" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -16168,22 +16162,22 @@
       <c r="T191" s="1" t="n"/>
       <c r="U191" s="1" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>80509</v>
+        <v>80528</v>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>Ata de Reunião</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Ajuste de Documentação</t>
         </is>
       </c>
       <c r="D192" s="1" t="inlineStr">
@@ -16193,76 +16187,80 @@
       </c>
       <c r="E192" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde, segue apontamento feito em ATA referente o fechamento 04/2026: Não foi considerado o crédito sobre a despesa de 219mil, solicito que seja retificada a apuração. Cliente salvou as NFs no DRIVE MG</t>
+          <t>Prezados,Favor atender solicitação do cliente a partir do mês de Julho 2026.MERCH LTDA: 65.021.126/0001-98- Rodrigo Marquezini (proprietário)- ?- ?Pró-labore: R$5.000,00</t>
         </is>
       </c>
       <c r="F192" s="1" t="n">
-        <v>6697</v>
+        <v>6740</v>
       </c>
       <c r="G192" s="1" t="inlineStr">
         <is>
-          <t>HEAD INFORMATICA MULTIMARCAS LTDA (MATRIZ)</t>
+          <t>MERCH LTDA</t>
         </is>
       </c>
       <c r="H192" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Sara Cavalheiro</t>
         </is>
       </c>
       <c r="I192" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>DP - DEPTO. PESSOAL</t>
         </is>
       </c>
       <c r="J192" s="2" t="n">
-        <v>46196.61037410879</v>
+        <v>46197.47721107639</v>
       </c>
       <c r="K192" s="2" t="n">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="L192" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Responsável</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M192" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N192" s="1" t="n"/>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="n">
+        <v>46197.56968244213</v>
+      </c>
       <c r="O192" s="1" t="n"/>
-      <c r="P192" s="1" t="n"/>
-      <c r="Q192" s="1" t="inlineStr"/>
+      <c r="P192" s="2" t="n">
+        <v>46203.72275605324</v>
+      </c>
+      <c r="Q192" s="1" t="inlineStr">
+        <is>
+          <t>Sara Cavalheiro</t>
+        </is>
+      </c>
       <c r="R192" s="1" t="inlineStr">
         <is>
-          <t>operação analisando os  questionamentos em relação ao serviços tomados de market place</t>
+          <t>Realizando cadastro para a folha de pro-labore.</t>
         </is>
       </c>
       <c r="S192" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T192" s="1" t="n"/>
-      <c r="U192" s="1" t="inlineStr">
-        <is>
-          <t>Nayara Oliveira</t>
-        </is>
-      </c>
+      <c r="U192" s="1" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>80528</v>
+        <v>80124</v>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t>Ajuste de Documentação</t>
+          <t>Recálculo de Guia</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -16272,32 +16270,32 @@
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t>Prezados,Favor atender solicitação do cliente a partir do mês de Julho 2026.MERCH LTDA: 65.021.126/0001-98- Rodrigo Marquezini (proprietário)- ?- ?Pró-labore: R$5.000,00</t>
+          <t>Recalcular todos os débitos de responsabilidade do departamento fiscal e enviar para  andrew@localservicos.com.br; m.rocha@localservicos.com.br; 'Reinaldo Souza - Local Serviços' &lt;reinaldo@localservicos.com.br&gt; Copiando master Cesar Prazo 18/06.2026</t>
         </is>
       </c>
       <c r="F193" s="1" t="n">
-        <v>6740</v>
+        <v>6742</v>
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t>MERCH LTDA</t>
+          <t>ARMS TERCERIZACAO DE SERVICOS</t>
         </is>
       </c>
       <c r="H193" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="I193" s="1" t="inlineStr">
         <is>
-          <t>DP - DEPTO. PESSOAL</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J193" s="2" t="n">
-        <v>46197.47721107639</v>
+        <v>46190.38983144676</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>46203</v>
+        <v>46191</v>
       </c>
       <c r="L193" s="1" t="inlineStr">
         <is>
@@ -16306,24 +16304,24 @@
       </c>
       <c r="M193" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Simone Marques</t>
         </is>
       </c>
       <c r="N193" s="2" t="n">
-        <v>46197.56968244213</v>
+        <v>46204.38703950231</v>
       </c>
       <c r="O193" s="1" t="n"/>
       <c r="P193" s="2" t="n">
-        <v>46203.72275605324</v>
+        <v>46204.68701346065</v>
       </c>
       <c r="Q193" s="1" t="inlineStr">
         <is>
-          <t>Sara Cavalheiro</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
       <c r="R193" s="1" t="inlineStr">
         <is>
-          <t>Realizando cadastro para a folha de pro-labore.</t>
+          <t xml:space="preserve">OPERAÇÃO VALIDANDO O FECHAMENTO. </t>
         </is>
       </c>
       <c r="S193" s="1" t="inlineStr">
@@ -16332,52 +16330,56 @@
         </is>
       </c>
       <c r="T193" s="1" t="n"/>
-      <c r="U193" s="1" t="inlineStr"/>
+      <c r="U193" s="1" t="inlineStr">
+        <is>
+          <t>Nayara Oliveira</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>80124</v>
+        <v>79931</v>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t>Recálculo de Guia</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t>Recalcular todos os débitos de responsabilidade do departamento fiscal e enviar para  andrew@localservicos.com.br; m.rocha@localservicos.com.br; 'Reinaldo Souza - Local Serviços' &lt;reinaldo@localservicos.com.br&gt; Copiando master Cesar Prazo 18/06.2026</t>
+          <t>Segue em anexo mensagem DEC Estadual do cliente: 6752 - NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDAComplemento do Assunto: EFD substitutiva recusada</t>
         </is>
       </c>
       <c r="F194" s="1" t="n">
-        <v>6742</v>
+        <v>6752</v>
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t>ARMS TERCERIZACAO DE SERVICOS</t>
+          <t>NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDA</t>
         </is>
       </c>
       <c r="H194" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="I194" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J194" s="2" t="n">
-        <v>46190.38983144676</v>
+        <v>46184.70804741898</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>46191</v>
@@ -16389,24 +16391,22 @@
       </c>
       <c r="M194" s="1" t="inlineStr">
         <is>
-          <t>Simone Marques</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="n">
-        <v>46204.38703950231</v>
-      </c>
+          <t>Leticia Queiroz</t>
+        </is>
+      </c>
+      <c r="N194" s="1" t="n"/>
       <c r="O194" s="1" t="n"/>
       <c r="P194" s="2" t="n">
-        <v>46204.68701346065</v>
+        <v>46188.7774003125</v>
       </c>
       <c r="Q194" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Ricardo Fischer</t>
         </is>
       </c>
       <c r="R194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPERAÇÃO VALIDANDO O FECHAMENTO. </t>
+          <t>Períodos das pendencias não são de responsabilidade técnica da MG</t>
         </is>
       </c>
       <c r="S194" s="1" t="inlineStr">
@@ -16417,13 +16417,13 @@
       <c r="T194" s="1" t="n"/>
       <c r="U194" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>79931</v>
+        <v>79797</v>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t>Segue em anexo mensagem DEC Estadual do cliente: 6752 - NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDAComplemento do Assunto: EFD substitutiva recusada</t>
+          <t>Segue em anexo mensagem DEC Estadual do cliente: 6752 - NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDAComplemento do Assunto: EFD substitutiva pendente de pagamento de taxa</t>
         </is>
       </c>
       <c r="F195" s="1" t="n">
@@ -16464,10 +16464,10 @@
         </is>
       </c>
       <c r="J195" s="2" t="n">
-        <v>46184.70804741898</v>
+        <v>46182.63507638889</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>46191</v>
+        <v>46189</v>
       </c>
       <c r="L195" s="1" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
       <c r="N195" s="1" t="n"/>
       <c r="O195" s="1" t="n"/>
       <c r="P195" s="2" t="n">
-        <v>46188.7774003125</v>
+        <v>46183.48591420139</v>
       </c>
       <c r="Q195" s="1" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
       </c>
       <c r="R195" s="1" t="inlineStr">
         <is>
-          <t>Períodos das pendencias não são de responsabilidade técnica da MG</t>
+          <t>Cliente iniciou na MG em 04/2026 e o período da pendencia é anterior a isso. De qualquer maneira, é importante verificar se o cliente não pretende pagar a taxa anual para dar condição de regularizar este tipo de problema.</t>
         </is>
       </c>
       <c r="S195" s="1" t="inlineStr">
@@ -16508,51 +16508,51 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>79797</v>
+        <v>80545</v>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Conciliação de Contas</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t>Segue em anexo mensagem DEC Estadual do cliente: 6752 - NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDAComplemento do Assunto: EFD substitutiva pendente de pagamento de taxa</t>
+          <t>DM COMERCIO - AJUSTES CONTÁBEIS - PRÉ REUNIÃO@Isabella Nascimento - CTI, boa tarde!Preciso que faça os seguintes ajuste•	Estoque final 04/2026 – R$ 2.814.945,19  (conforme relatório em anexo recebido pelo cliente).•	Estoque final 05/2026 – R$ 2.750.973,85 (conforme relatório em anexo recebido pelo cliente).•	Baixar saldo da conta SIMPLES NACIONAL A PAGAR, cliente não tem dívida do imposto.•	Cliente não reconhece os R$ 49,81 de rendimento de aplicação financeira, PRECISO DE UMA COMPROVAÇÃO, pode ser por print do extrato.•	Implantar saldo inicial, enviamos em 13/05 e até o momento não foi feitoAtt.Vander</t>
         </is>
       </c>
       <c r="F196" s="1" t="n">
-        <v>6752</v>
+        <v>6816</v>
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t>NOHKER COMERCIO E REPRESENTACAO DE PRODUTOS PARA HIGIENE, LIMPEZA E COSMETICOS LTDA</t>
+          <t>DM COMERCIO ALIMENTICIO LTDA</t>
         </is>
       </c>
       <c r="H196" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="I196" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="J196" s="2" t="n">
-        <v>46182.63507638889</v>
+        <v>46197.68548206019</v>
       </c>
       <c r="K196" s="2" t="n">
-        <v>46189</v>
+        <v>46198</v>
       </c>
       <c r="L196" s="1" t="inlineStr">
         <is>
@@ -16561,22 +16561,24 @@
       </c>
       <c r="M196" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="N196" s="1" t="n"/>
-      <c r="O196" s="1" t="n"/>
+      <c r="O196" s="2" t="n">
+        <v>46218</v>
+      </c>
       <c r="P196" s="2" t="n">
-        <v>46183.48591420139</v>
+        <v>46220.65987260417</v>
       </c>
       <c r="Q196" s="1" t="inlineStr">
         <is>
-          <t>Ricardo Fischer</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
       <c r="R196" s="1" t="inlineStr">
         <is>
-          <t>Cliente iniciou na MG em 04/2026 e o período da pendencia é anterior a isso. De qualquer maneira, é importante verificar se o cliente não pretende pagar a taxa anual para dar condição de regularizar este tipo de problema.</t>
+          <t>Estoque ja foi ajustado (solicitação duplicada , recebido via email)</t>
         </is>
       </c>
       <c r="S196" s="1" t="inlineStr">
@@ -16587,22 +16589,22 @@
       <c r="T196" s="1" t="n"/>
       <c r="U196" s="1" t="inlineStr">
         <is>
-          <t>Claudineia Rodrigues</t>
+          <t>Isabella Nascimento</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>80545</v>
+        <v>81183</v>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>MG Controle</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
         <is>
-          <t>Conciliação de Contas</t>
+          <t>Fiscalização Municipal</t>
         </is>
       </c>
       <c r="D197" s="1" t="inlineStr">
@@ -16612,36 +16614,36 @@
       </c>
       <c r="E197" s="1" t="inlineStr">
         <is>
-          <t>DM COMERCIO - AJUSTES CONTÁBEIS - PRÉ REUNIÃO@Isabella Nascimento - CTI, boa tarde!Preciso que faça os seguintes ajuste•	Estoque final 04/2026 – R$ 2.814.945,19  (conforme relatório em anexo recebido pelo cliente).•	Estoque final 05/2026 – R$ 2.750.973,85 (conforme relatório em anexo recebido pelo cliente).•	Baixar saldo da conta SIMPLES NACIONAL A PAGAR, cliente não tem dívida do imposto.•	Cliente não reconhece os R$ 49,81 de rendimento de aplicação financeira, PRECISO DE UMA COMPROVAÇÃO, pode ser por print do extrato.•	Implantar saldo inicial, enviamos em 13/05 e até o momento não foi feitoAtt.Vander</t>
+          <t>EFI,  6826 GRIFFY, não estão conseguindo emitir nota de serviços, prefeitura pede o encerramento fiscal no sistema antes de liberar novas emissões, cliente precisa emitir a nota hoje 17/07 até a tarde, consegue atender por favor ?Att.Vander</t>
         </is>
       </c>
       <c r="F197" s="1" t="n">
-        <v>6816</v>
+        <v>6826</v>
       </c>
       <c r="G197" s="1" t="inlineStr">
         <is>
-          <t>DM COMERCIO ALIMENTICIO LTDA</t>
+          <t>GRIFFY FERRAMENTARIA DE PRECISAO LTDA</t>
         </is>
       </c>
       <c r="H197" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Priscila Volpe</t>
         </is>
       </c>
       <c r="I197" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="J197" s="2" t="n">
-        <v>46197.68548206019</v>
+        <v>46220.47079363426</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>46198</v>
+        <v>46225</v>
       </c>
       <c r="L197" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M197" s="1" t="inlineStr">
@@ -16649,65 +16651,59 @@
           <t>Vander Silva</t>
         </is>
       </c>
-      <c r="N197" s="1" t="n"/>
-      <c r="O197" s="2" t="n">
-        <v>46218</v>
-      </c>
-      <c r="P197" s="2" t="n">
-        <v>46220.65987260417</v>
-      </c>
-      <c r="Q197" s="1" t="inlineStr">
-        <is>
-          <t>Isabella Nascimento</t>
-        </is>
-      </c>
+      <c r="N197" s="2" t="n">
+        <v>46223.48601396991</v>
+      </c>
+      <c r="O197" s="1" t="n"/>
+      <c r="P197" s="1" t="n"/>
+      <c r="Q197" s="1" t="inlineStr"/>
       <c r="R197" s="1" t="inlineStr">
         <is>
-          <t>Estoque ja foi ajustado (solicitação duplicada , recebido via email)</t>
+          <t>OPERAÇÃO EXECUTANDO</t>
         </is>
       </c>
       <c r="S197" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T197" s="1" t="n"/>
       <c r="U197" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Nayara Oliveira</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>81183</v>
+        <v>80705</v>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>MG Controle</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
         <is>
-          <t>Fiscalização Municipal</t>
+          <t>Saldo Credor Incorreto</t>
         </is>
       </c>
       <c r="D198" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>GC - ADMINISTRATIVO</t>
         </is>
       </c>
       <c r="E198" s="1" t="inlineStr">
         <is>
-          <t>EFI,  6826 GRIFFY, não estão conseguindo emitir nota de serviços, prefeitura pede o encerramento fiscal no sistema antes de liberar novas emissões, cliente precisa emitir a nota hoje 17/07 até a tarde, consegue atender por favor ?Att.Vander</t>
+          <t>Boa tarde! Por gentileza, verificar se a taxa foi paga. Caso não, por gentileza, encaminhar a guia atualizada para o cliente.</t>
         </is>
       </c>
       <c r="F198" s="1" t="n">
-        <v>6826</v>
+        <v>6838</v>
       </c>
       <c r="G198" s="1" t="inlineStr">
         <is>
-          <t>GRIFFY FERRAMENTARIA DE PRECISAO LTDA</t>
+          <t>GR MIX CONCRETOS LTDA</t>
         </is>
       </c>
       <c r="H198" s="1" t="inlineStr">
@@ -16721,10 +16717,10 @@
         </is>
       </c>
       <c r="J198" s="2" t="n">
-        <v>46220.47079363426</v>
+        <v>46205.59532480324</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>46225</v>
+        <v>46209</v>
       </c>
       <c r="L198" s="1" t="inlineStr">
         <is>
@@ -16733,18 +16729,19 @@
       </c>
       <c r="M198" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Ana Santana</t>
         </is>
       </c>
       <c r="N198" s="2" t="n">
-        <v>46223.48601396991</v>
+        <v>46206.46338136574</v>
       </c>
       <c r="O198" s="1" t="n"/>
       <c r="P198" s="1" t="n"/>
       <c r="Q198" s="1" t="inlineStr"/>
       <c r="R198" s="1" t="inlineStr">
         <is>
-          <t>OPERAÇÃO EXECUTANDO</t>
+          <t>operação em validação dos fatos,
+prazo 06-07</t>
         </is>
       </c>
       <c r="S198" s="1" t="inlineStr">
@@ -16761,34 +16758,34 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>80705</v>
+        <v>80522</v>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t>Saldo Credor Incorreto</t>
+          <t>Retificação de Obrigação Acessória</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>GC - ADMINISTRATIVO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde! Por gentileza, verificar se a taxa foi paga. Caso não, por gentileza, encaminhar a guia atualizada para o cliente.</t>
+          <t>Bom dia, por gentileza verificar mensagem recebida no DEC referente irregularidade na EFD 05/2026.</t>
         </is>
       </c>
       <c r="F199" s="1" t="n">
-        <v>6838</v>
+        <v>6880</v>
       </c>
       <c r="G199" s="1" t="inlineStr">
         <is>
-          <t>GR MIX CONCRETOS LTDA</t>
+          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS (FILIAL)</t>
         </is>
       </c>
       <c r="H199" s="1" t="inlineStr">
@@ -16802,36 +16799,42 @@
         </is>
       </c>
       <c r="J199" s="2" t="n">
-        <v>46205.59532480324</v>
+        <v>46197.36092913194</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>46209</v>
+        <v>46199</v>
       </c>
       <c r="L199" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Entregue Ao Solicitante</t>
         </is>
       </c>
       <c r="M199" s="1" t="inlineStr">
         <is>
-          <t>Ana Santana</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="N199" s="2" t="n">
-        <v>46206.46338136574</v>
+        <v>46197.50481565972</v>
       </c>
       <c r="O199" s="1" t="n"/>
-      <c r="P199" s="1" t="n"/>
-      <c r="Q199" s="1" t="inlineStr"/>
+      <c r="P199" s="2" t="n">
+        <v>46210.67503584491</v>
+      </c>
+      <c r="Q199" s="1" t="inlineStr">
+        <is>
+          <t>Priscila Volpe</t>
+        </is>
+      </c>
       <c r="R199" s="1" t="inlineStr">
         <is>
-          <t>operação em validação dos fatos,
-prazo 06-07</t>
+          <t xml:space="preserve">em atendimento pelqa operação 
+</t>
         </is>
       </c>
       <c r="S199" s="1" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="T199" s="1" t="n"/>
@@ -16843,7 +16846,7 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>80522</v>
+        <v>80660</v>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
@@ -16862,32 +16865,32 @@
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, por gentileza verificar mensagem recebida no DEC referente irregularidade na EFD 05/2026.</t>
+          <t xml:space="preserve">DeSTDA transmitida referente período 05/2026 rejeitada, pois é incompatível com a situação cadastral do contribuinte.Favor verificar. </t>
         </is>
       </c>
       <c r="F200" s="1" t="n">
-        <v>6880</v>
+        <v>6950</v>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t>ROBSON DE SOUSA LIMA COMERCIO DE ABRASIVOS (FILIAL)</t>
+          <t>MERCH LTDA (FILIAL 1)</t>
         </is>
       </c>
       <c r="H200" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="I200" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J200" s="2" t="n">
-        <v>46197.36092913194</v>
+        <v>46203.77092060186</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>46199</v>
+        <v>46213</v>
       </c>
       <c r="L200" s="1" t="inlineStr">
         <is>
@@ -16896,24 +16899,22 @@
       </c>
       <c r="M200" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="n">
-        <v>46197.50481565972</v>
-      </c>
+          <t>Bruno Contieri</t>
+        </is>
+      </c>
+      <c r="N200" s="1" t="n"/>
       <c r="O200" s="1" t="n"/>
       <c r="P200" s="2" t="n">
-        <v>46210.67503584491</v>
+        <v>46205.48101550926</v>
       </c>
       <c r="Q200" s="1" t="inlineStr">
         <is>
-          <t>Priscila Volpe</t>
+          <t>Lorrane Santos</t>
         </is>
       </c>
       <c r="R200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">em atendimento pelqa operação 
+          <t xml:space="preserve">boa tarde! DeSTDA não aceita pois ref. ao mês 05/2026 pois sua Inscrição Estadual saiu no dia 16/06/2026. 
 </t>
         </is>
       </c>
@@ -16925,118 +16926,99 @@
       <c r="T200" s="1" t="n"/>
       <c r="U200" s="1" t="inlineStr">
         <is>
-          <t>Nayara Oliveira</t>
+          <t>Claudineia Rodrigues</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>80660</v>
+        <v>80230</v>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t>Retificação de Obrigação Acessória</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
         <is>
+          <t>EF - VAREJO</t>
+        </is>
+      </c>
+      <c r="E201" s="1" t="inlineStr">
+        <is>
+          <t>Bom dia,por gentileza disponibilizar o certificado da loja 5795 no dinamo da coordenadora Lorrane do EFV, precisamos desse certificado para fazer consulta na prefeitura.</t>
+        </is>
+      </c>
+      <c r="F201" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G201" s="1" t="n"/>
+      <c r="H201" s="1" t="inlineStr">
+        <is>
+          <t>Bruna Costa</t>
+        </is>
+      </c>
+      <c r="I201" s="1" t="inlineStr">
+        <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
-      <c r="E201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DeSTDA transmitida referente período 05/2026 rejeitada, pois é incompatível com a situação cadastral do contribuinte.Favor verificar. </t>
-        </is>
-      </c>
-      <c r="F201" s="1" t="n">
-        <v>6950</v>
-      </c>
-      <c r="G201" s="1" t="inlineStr">
-        <is>
-          <t>MERCH LTDA (FILIAL 1)</t>
-        </is>
-      </c>
-      <c r="H201" s="1" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
-      <c r="I201" s="1" t="inlineStr">
-        <is>
-          <t>EF - VAREJO</t>
-        </is>
-      </c>
       <c r="J201" s="2" t="n">
-        <v>46203.77092060186</v>
+        <v>46192.40449980324</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>46213</v>
+        <v>46195</v>
       </c>
       <c r="L201" s="1" t="inlineStr">
         <is>
-          <t>Entregue Ao Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M201" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Idna Sousa</t>
         </is>
       </c>
       <c r="N201" s="1" t="n"/>
       <c r="O201" s="1" t="n"/>
-      <c r="P201" s="2" t="n">
-        <v>46205.48101550926</v>
-      </c>
-      <c r="Q201" s="1" t="inlineStr">
-        <is>
-          <t>Lorrane Santos</t>
-        </is>
-      </c>
-      <c r="R201" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">boa tarde! DeSTDA não aceita pois ref. ao mês 05/2026 pois sua Inscrição Estadual saiu no dia 16/06/2026. 
-</t>
-        </is>
-      </c>
+      <c r="P201" s="1" t="n"/>
+      <c r="Q201" s="1" t="inlineStr"/>
+      <c r="R201" s="1" t="inlineStr"/>
       <c r="S201" s="1" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="T201" s="1" t="n"/>
-      <c r="U201" s="1" t="inlineStr">
-        <is>
-          <t>Claudineia Rodrigues</t>
-        </is>
-      </c>
+      <c r="U201" s="1" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>80230</v>
+        <v>80233</v>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,por gentileza disponibilizar o certificado da loja 5795 no dinamo da coordenadora Lorrane do EFV, precisamos desse certificado para fazer consulta na prefeitura.</t>
+          <t>Bom dia Beatriz,A empresa 5598 - Distribuidora de Morangos, realizou uma venda de 2 veículos no mês 04/2026, mas não emitiu nota fiscal e o recebimento foi pela conta física do Sócio Fábio Pereira da Costa, preciso saber como vou tratar a depreciação de veículos sendo que não tem como fazer a baixa sem a nota fiscal ?</t>
         </is>
       </c>
       <c r="F202" s="1" t="n">
@@ -17054,7 +17036,7 @@
         </is>
       </c>
       <c r="J202" s="2" t="n">
-        <v>46192.40449980324</v>
+        <v>46192.42203209491</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>46195</v>
@@ -17066,7 +17048,7 @@
       </c>
       <c r="M202" s="1" t="inlineStr">
         <is>
-          <t>Idna Sousa</t>
+          <t>Fatima Rocha</t>
         </is>
       </c>
       <c r="N202" s="1" t="n"/>
@@ -17084,7 +17066,7 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>80233</v>
+        <v>80234</v>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
@@ -17103,7 +17085,7 @@
       </c>
       <c r="E203" s="1" t="inlineStr">
         <is>
-          <t>Bom dia Beatriz,A empresa 5598 - Distribuidora de Morangos, realizou uma venda de 2 veículos no mês 04/2026, mas não emitiu nota fiscal e o recebimento foi pela conta física do Sócio Fábio Pereira da Costa, preciso saber como vou tratar a depreciação de veículos sendo que não tem como fazer a baixa sem a nota fiscal ?</t>
+          <t>Bom dia Beatriz,  A empresa 5598 - Distribuidor de Morangos o pró-labore está no nome da Thais kazi de Menezes, mas sócio é Fabio Pereira da costa e 5599 - Sweet Berry o pró-labore está no nome Fabio Pereira da costa, mas a sócia é Thais kazi de Menezes. Precisa ser corregido.</t>
         </is>
       </c>
       <c r="F203" s="1" t="n">
@@ -17121,7 +17103,7 @@
         </is>
       </c>
       <c r="J203" s="2" t="n">
-        <v>46192.42203209491</v>
+        <v>46192.43073827546</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>46195</v>
@@ -17151,26 +17133,26 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>80234</v>
+        <v>80754</v>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Solicitação do cliente</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Solicitação do cliente</t>
         </is>
       </c>
       <c r="D204" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="E204" s="1" t="inlineStr">
         <is>
-          <t>Bom dia Beatriz,  A empresa 5598 - Distribuidor de Morangos o pró-labore está no nome da Thais kazi de Menezes, mas sócio é Fabio Pereira da costa e 5599 - Sweet Berry o pró-labore está no nome Fabio Pereira da costa, mas a sócia é Thais kazi de Menezes. Precisa ser corregido.</t>
+          <t>Olá boa tarde, a loja 3355 - DISTRIBUIDORA DE HORTIFRUTIGRANJEIRO GATÃO LTDA-ME (F1) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
         </is>
       </c>
       <c r="F204" s="1" t="n">
@@ -17179,7 +17161,7 @@
       <c r="G204" s="1" t="n"/>
       <c r="H204" s="1" t="inlineStr">
         <is>
-          <t>Bruna Costa</t>
+          <t>Bruno Contieri</t>
         </is>
       </c>
       <c r="I204" s="1" t="inlineStr">
@@ -17188,10 +17170,10 @@
         </is>
       </c>
       <c r="J204" s="2" t="n">
-        <v>46192.43073827546</v>
+        <v>46209.51393387732</v>
       </c>
       <c r="K204" s="2" t="n">
-        <v>46195</v>
+        <v>46211</v>
       </c>
       <c r="L204" s="1" t="inlineStr">
         <is>
@@ -17200,7 +17182,7 @@
       </c>
       <c r="M204" s="1" t="inlineStr">
         <is>
-          <t>Fatima Rocha</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="N204" s="1" t="n"/>
@@ -17218,7 +17200,7 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>80754</v>
+        <v>80755</v>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
@@ -17237,7 +17219,7 @@
       </c>
       <c r="E205" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 3355 - DISTRIBUIDORA DE HORTIFRUTIGRANJEIRO GATÃO LTDA-ME (F1) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
+          <t>Olá boa tarde, a loja 1337 - DEOLA RESTAURANTE BUFFET LTDA possuí XMLs  de entrada localizados  no GAX WEB. Poderiam verificar e se devemos considerar no FECHAMENTO.</t>
         </is>
       </c>
       <c r="F205" s="1" t="n">
@@ -17255,7 +17237,7 @@
         </is>
       </c>
       <c r="J205" s="2" t="n">
-        <v>46209.51393387732</v>
+        <v>46209.51404274305</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>46211</v>
@@ -17267,7 +17249,7 @@
       </c>
       <c r="M205" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N205" s="1" t="n"/>
@@ -17285,7 +17267,7 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>80755</v>
+        <v>80758</v>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
@@ -17304,7 +17286,7 @@
       </c>
       <c r="E206" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 1337 - DEOLA RESTAURANTE BUFFET LTDA possuí XMLs  de entrada localizados  no GAX WEB. Poderiam verificar e se devemos considerar no FECHAMENTO.</t>
+          <t>Olá boa tarde, a loja 5954 - IKIGAI SERVICE LTDA, possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
         </is>
       </c>
       <c r="F206" s="1" t="n">
@@ -17322,7 +17304,7 @@
         </is>
       </c>
       <c r="J206" s="2" t="n">
-        <v>46209.51404274305</v>
+        <v>46209.51704957176</v>
       </c>
       <c r="K206" s="2" t="n">
         <v>46211</v>
@@ -17334,7 +17316,7 @@
       </c>
       <c r="M206" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="N206" s="1" t="n"/>
@@ -17352,7 +17334,7 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>80758</v>
+        <v>80759</v>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
@@ -17371,7 +17353,7 @@
       </c>
       <c r="E207" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 5954 - IKIGAI SERVICE LTDA, possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
+          <t>Olá boa tarde, a loja 5746 - PADARIA VILA NOVA CONCEICAO LTDA possuí XMLs  de entrada localizados  no GAX WEB. Poderiam verificar e se devemos considerar no FECHAMENTO.</t>
         </is>
       </c>
       <c r="F207" s="1" t="n">
@@ -17380,46 +17362,54 @@
       <c r="G207" s="1" t="n"/>
       <c r="H207" s="1" t="inlineStr">
         <is>
-          <t>Bruno Contieri</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="I207" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J207" s="2" t="n">
-        <v>46209.51704957176</v>
+        <v>46209.5173503125</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="L207" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M207" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
+          <t>Izabely Araujo</t>
         </is>
       </c>
       <c r="N207" s="1" t="n"/>
       <c r="O207" s="1" t="n"/>
       <c r="P207" s="1" t="n"/>
       <c r="Q207" s="1" t="inlineStr"/>
-      <c r="R207" s="1" t="inlineStr"/>
+      <c r="R207" s="1" t="inlineStr">
+        <is>
+          <t>Enviado para o cliente, aguardando o retorno do mesmo.</t>
+        </is>
+      </c>
       <c r="S207" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T207" s="1" t="n"/>
+      <c r="T207" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
       <c r="U207" s="1" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>80759</v>
+        <v>80751</v>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
@@ -17438,7 +17428,7 @@
       </c>
       <c r="E208" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 5746 - PADARIA VILA NOVA CONCEICAO LTDA possuí XMLs  de entrada localizados  no GAX WEB. Poderiam verificar e se devemos considerar no FECHAMENTO.</t>
+          <t>Olá boa tarde, a loja 2226 - SUPERMERCADO BEIRA ALTA LTDA (FILIAL 03) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento</t>
         </is>
       </c>
       <c r="F208" s="1" t="n">
@@ -17447,54 +17437,46 @@
       <c r="G208" s="1" t="n"/>
       <c r="H208" s="1" t="inlineStr">
         <is>
-          <t>Rodrigo Rego</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I208" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J208" s="2" t="n">
-        <v>46209.5173503125</v>
+        <v>46209.50389690972</v>
       </c>
       <c r="K208" s="2" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="L208" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M208" s="1" t="inlineStr">
         <is>
-          <t>Izabely Araujo</t>
+          <t>Eduardo Lopes</t>
         </is>
       </c>
       <c r="N208" s="1" t="n"/>
       <c r="O208" s="1" t="n"/>
       <c r="P208" s="1" t="n"/>
       <c r="Q208" s="1" t="inlineStr"/>
-      <c r="R208" s="1" t="inlineStr">
-        <is>
-          <t>Enviado para o cliente, aguardando o retorno do mesmo.</t>
-        </is>
-      </c>
+      <c r="R208" s="1" t="inlineStr"/>
       <c r="S208" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T208" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
+      <c r="T208" s="1" t="n"/>
       <c r="U208" s="1" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>80751</v>
+        <v>80753</v>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
@@ -17513,7 +17495,7 @@
       </c>
       <c r="E209" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 2226 - SUPERMERCADO BEIRA ALTA LTDA (FILIAL 03) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento</t>
+          <t>Olá boa tarde, a loja 2382 - NOVA CANADÁ PÃES E DOCES EIRELI) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento</t>
         </is>
       </c>
       <c r="F209" s="1" t="n">
@@ -17522,23 +17504,23 @@
       <c r="G209" s="1" t="n"/>
       <c r="H209" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Rodrigo Rego</t>
         </is>
       </c>
       <c r="I209" s="1" t="inlineStr">
         <is>
-          <t>GERENCIA DE CONTAS</t>
+          <t>EF - VAREJO</t>
         </is>
       </c>
       <c r="J209" s="2" t="n">
-        <v>46209.50389690972</v>
+        <v>46209.51103012732</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="L209" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Devolvido para Solicitante</t>
         </is>
       </c>
       <c r="M209" s="1" t="inlineStr">
@@ -17550,18 +17532,26 @@
       <c r="O209" s="1" t="n"/>
       <c r="P209" s="1" t="n"/>
       <c r="Q209" s="1" t="inlineStr"/>
-      <c r="R209" s="1" t="inlineStr"/>
+      <c r="R209" s="1" t="inlineStr">
+        <is>
+          <t>Enviado para o cliente, aguardando o retorno do mesmo.</t>
+        </is>
+      </c>
       <c r="S209" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T209" s="1" t="n"/>
+      <c r="T209" s="1" t="inlineStr">
+        <is>
+          <t>GERENCIA DE CONTAS</t>
+        </is>
+      </c>
       <c r="U209" s="1" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>80753</v>
+        <v>80760</v>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
@@ -17580,7 +17570,7 @@
       </c>
       <c r="E210" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 2382 - NOVA CANADÁ PÃES E DOCES EIRELI) possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento</t>
+          <t>Olá boa tarde, a loja 6205 - CUCINARE PRO ALIMENTACAO LTDA (FILIAL 93), possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
         </is>
       </c>
       <c r="F210" s="1" t="n">
@@ -17594,18 +17584,18 @@
       </c>
       <c r="I210" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J210" s="2" t="n">
-        <v>46209.51103012732</v>
+        <v>46209.51804047454</v>
       </c>
       <c r="K210" s="2" t="n">
         <v>46211</v>
       </c>
       <c r="L210" s="1" t="inlineStr">
         <is>
-          <t>Devolvido para Solicitante</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M210" s="1" t="inlineStr">
@@ -17613,7 +17603,9 @@
           <t>Eduardo Lopes</t>
         </is>
       </c>
-      <c r="N210" s="1" t="n"/>
+      <c r="N210" s="2" t="n">
+        <v>46216.38251855324</v>
+      </c>
       <c r="O210" s="1" t="n"/>
       <c r="P210" s="1" t="n"/>
       <c r="Q210" s="1" t="inlineStr"/>
@@ -17627,78 +17619,64 @@
           <t>NÃO</t>
         </is>
       </c>
-      <c r="T210" s="1" t="inlineStr">
-        <is>
-          <t>GERENCIA DE CONTAS</t>
-        </is>
-      </c>
+      <c r="T210" s="1" t="n"/>
       <c r="U210" s="1" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>80760</v>
+        <v>81202</v>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>Solicitação do cliente</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t>Solicitação do cliente</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>EF - VAREJO</t>
+          <t>CTB - CONTÁBIL INDUSTRIA</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
         <is>
-          <t>Olá boa tarde, a loja 6205 - CUCINARE PRO ALIMENTACAO LTDA (FILIAL 93), possuí XMLs de entrada localizados no GAX web... poderiam verificar se devemos considerar no fechamento?</t>
+          <t>Bom dia, preciso do certificado da empresa 5603 -Carlos Antunes e que seja renovado o certificado da empresa 4793- Costa lima</t>
         </is>
       </c>
       <c r="F211" s="1" t="n">
         <v>0</v>
       </c>
       <c r="G211" s="1" t="n"/>
-      <c r="H211" s="1" t="inlineStr">
-        <is>
-          <t>Rodrigo Rego</t>
-        </is>
-      </c>
+      <c r="H211" s="1" t="n"/>
       <c r="I211" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J211" s="2" t="n">
-        <v>46209.51804047454</v>
+        <v>46223.39712596065</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>46211</v>
+        <v>46224</v>
       </c>
       <c r="L211" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Sem Responsavel Atribuido</t>
         </is>
       </c>
       <c r="M211" s="1" t="inlineStr">
         <is>
-          <t>Eduardo Lopes</t>
-        </is>
-      </c>
-      <c r="N211" s="2" t="n">
-        <v>46216.38251855324</v>
-      </c>
+          <t>Isabella Nascimento</t>
+        </is>
+      </c>
+      <c r="N211" s="1" t="n"/>
       <c r="O211" s="1" t="n"/>
       <c r="P211" s="1" t="n"/>
       <c r="Q211" s="1" t="inlineStr"/>
-      <c r="R211" s="1" t="inlineStr">
-        <is>
-          <t>Enviado para o cliente, aguardando o retorno do mesmo.</t>
-        </is>
-      </c>
+      <c r="R211" s="1" t="n"/>
       <c r="S211" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17709,59 +17687,67 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>81202</v>
+        <v>80792</v>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
         <is>
-          <t>Bom dia, preciso do certificado da empresa 5603 -Carlos Antunes e que seja renovado o certificado da empresa 4793- Costa lima</t>
+          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
         </is>
       </c>
       <c r="F212" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G212" s="1" t="n"/>
-      <c r="H212" s="1" t="n"/>
+        <v>861</v>
+      </c>
+      <c r="G212" s="1" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
+        </is>
+      </c>
+      <c r="H212" s="1" t="inlineStr">
+        <is>
+          <t>Diego Lima</t>
+        </is>
+      </c>
       <c r="I212" s="1" t="inlineStr">
         <is>
           <t>GERENCIA DE CONTAS</t>
         </is>
       </c>
       <c r="J212" s="2" t="n">
-        <v>46223.39712596065</v>
+        <v>46210.5704596412</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>46224</v>
+        <v>46213</v>
       </c>
       <c r="L212" s="1" t="inlineStr">
         <is>
-          <t>Sem Responsavel Atribuido</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M212" s="1" t="inlineStr">
         <is>
-          <t>Isabella Nascimento</t>
+          <t>Rejane Coelho</t>
         </is>
       </c>
       <c r="N212" s="1" t="n"/>
       <c r="O212" s="1" t="n"/>
       <c r="P212" s="1" t="n"/>
       <c r="Q212" s="1" t="inlineStr"/>
-      <c r="R212" s="1" t="n"/>
+      <c r="R212" s="1" t="inlineStr"/>
       <c r="S212" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -17772,7 +17758,7 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>80792</v>
+        <v>80732</v>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
@@ -17791,7 +17777,7 @@
       </c>
       <c r="E213" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0007.00013 - Devoluções de Compra a Receber1.01.002.0007.00014 - Devoluções de Troca a Receber</t>
+          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
         </is>
       </c>
       <c r="F213" s="1" t="n">
@@ -17813,10 +17799,10 @@
         </is>
       </c>
       <c r="J213" s="2" t="n">
-        <v>46210.5704596412</v>
+        <v>46206.67579409722</v>
       </c>
       <c r="K213" s="2" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="L213" s="1" t="inlineStr">
         <is>
@@ -17843,7 +17829,7 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>80732</v>
+        <v>80733</v>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
@@ -17862,7 +17848,7 @@
       </c>
       <c r="E214" s="1" t="inlineStr">
         <is>
-          <t>1.01.002.0001.00005 - Acordos Comerciais e Bonificações a Receber</t>
+          <t>1.01.001.0001.00001 - Caixa</t>
         </is>
       </c>
       <c r="F214" s="1" t="n">
@@ -17884,7 +17870,7 @@
         </is>
       </c>
       <c r="J214" s="2" t="n">
-        <v>46206.67579409722</v>
+        <v>46206.67633518518</v>
       </c>
       <c r="K214" s="2" t="n">
         <v>46210</v>
@@ -17914,7 +17900,7 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>80733</v>
+        <v>80734</v>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
@@ -17933,7 +17919,7 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t>1.01.001.0001.00001 - Caixa</t>
+          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
         </is>
       </c>
       <c r="F215" s="1" t="n">
@@ -17955,7 +17941,7 @@
         </is>
       </c>
       <c r="J215" s="2" t="n">
-        <v>46206.67633518518</v>
+        <v>46206.6769059375</v>
       </c>
       <c r="K215" s="2" t="n">
         <v>46210</v>
@@ -17985,16 +17971,16 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>80734</v>
+        <v>80008</v>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
@@ -18004,20 +17990,20 @@
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t>2.01.005.0002.00024 - Faturas Pendentes de Repasse</t>
+          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
         </is>
       </c>
       <c r="F216" s="1" t="n">
-        <v>861</v>
+        <v>1065</v>
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t>SUPERMERCADO CASTELO DA SERRA LTDA (MATRIZ)</t>
+          <t>MARTINICA COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="H216" s="1" t="inlineStr">
         <is>
-          <t>Diego Lima</t>
+          <t>Leticia Queiroz</t>
         </is>
       </c>
       <c r="I216" s="1" t="inlineStr">
@@ -18026,10 +18012,10 @@
         </is>
       </c>
       <c r="J216" s="2" t="n">
-        <v>46206.6769059375</v>
+        <v>46188.45542777778</v>
       </c>
       <c r="K216" s="2" t="n">
-        <v>46210</v>
+        <v>46189</v>
       </c>
       <c r="L216" s="1" t="inlineStr">
         <is>
@@ -18038,7 +18024,7 @@
       </c>
       <c r="M216" s="1" t="inlineStr">
         <is>
-          <t>Rejane Coelho</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N216" s="1" t="n"/>
@@ -18056,16 +18042,16 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>80008</v>
+        <v>79890</v>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Solicitação sem retorno</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
@@ -18075,20 +18061,20 @@
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t>Bom diaPor gentileza verificar pois o certificado venceu1065	Martinica Com.	65.486.375/0001-59</t>
+          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
         </is>
       </c>
       <c r="F217" s="1" t="n">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t>MARTINICA COMERCIAL LTDA</t>
+          <t>Supermercado Kanashiro Ltda</t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
         <is>
-          <t>Leticia Queiroz</t>
+          <t>Rogerio Egidio</t>
         </is>
       </c>
       <c r="I217" s="1" t="inlineStr">
@@ -18097,26 +18083,32 @@
         </is>
       </c>
       <c r="J217" s="2" t="n">
-        <v>46188.45542777778</v>
+        <v>46184.46686350695</v>
       </c>
       <c r="K217" s="2" t="n">
-        <v>46189</v>
+        <v>46188</v>
       </c>
       <c r="L217" s="1" t="inlineStr">
         <is>
-          <t>Esperando Atendimento</t>
+          <t>Em Atendimento</t>
         </is>
       </c>
       <c r="M217" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
-        </is>
-      </c>
-      <c r="N217" s="1" t="n"/>
+          <t>Karina Santos</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="n">
+        <v>46185.43777230324</v>
+      </c>
       <c r="O217" s="1" t="n"/>
       <c r="P217" s="1" t="n"/>
       <c r="Q217" s="1" t="inlineStr"/>
-      <c r="R217" s="1" t="inlineStr"/>
+      <c r="R217" s="1" t="inlineStr">
+        <is>
+          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
+        </is>
+      </c>
       <c r="S217" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -18127,39 +18119,39 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>79890</v>
+        <v>78306</v>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>Solicitação sem retorno</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
         <is>
-          <t>Bom dia,Por gentileza, verificar distribuição de lucros referente 2026, não recebemos nenhum e-mail do grupo Kanashiro.</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F218" s="1" t="n">
-        <v>1066</v>
+        <v>1286</v>
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t>Supermercado Kanashiro Ltda</t>
+          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
         <is>
-          <t>Rogerio Egidio</t>
+          <t>Vander Silva</t>
         </is>
       </c>
       <c r="I218" s="1" t="inlineStr">
@@ -18168,32 +18160,26 @@
         </is>
       </c>
       <c r="J218" s="2" t="n">
-        <v>46184.46686350695</v>
+        <v>46111.42803700231</v>
       </c>
       <c r="K218" s="2" t="n">
-        <v>46188</v>
+        <v>46122</v>
       </c>
       <c r="L218" s="1" t="inlineStr">
         <is>
-          <t>Em Atendimento</t>
+          <t>Esperando Atendimento</t>
         </is>
       </c>
       <c r="M218" s="1" t="inlineStr">
         <is>
-          <t>Karina Santos</t>
-        </is>
-      </c>
-      <c r="N218" s="2" t="n">
-        <v>46185.43777230324</v>
-      </c>
+          <t>Taina Silva</t>
+        </is>
+      </c>
+      <c r="N218" s="1" t="n"/>
       <c r="O218" s="1" t="n"/>
       <c r="P218" s="1" t="n"/>
       <c r="Q218" s="1" t="inlineStr"/>
-      <c r="R218" s="1" t="inlineStr">
-        <is>
-          <t>Por gentileza, ser mais clara na solicitação, o que deseja ser verificado ?</t>
-        </is>
-      </c>
+      <c r="R218" s="1" t="inlineStr"/>
       <c r="S218" s="1" t="inlineStr">
         <is>
           <t>NÃO</t>
@@ -18204,16 +18190,16 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>78306</v>
+        <v>79733</v>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Malha Fiscal</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Autorregularização</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
@@ -18223,20 +18209,20 @@
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
         </is>
       </c>
       <c r="F219" s="1" t="n">
-        <v>1286</v>
+        <v>1556</v>
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t>BY ENGENHARIA IMPORTAÇÃO E EXPORTAÇÃO LTDA (MATRIZ)</t>
+          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
         </is>
       </c>
       <c r="H219" s="1" t="inlineStr">
         <is>
-          <t>Vander Silva</t>
+          <t>Karine Gusmão</t>
         </is>
       </c>
       <c r="I219" s="1" t="inlineStr">
@@ -18245,10 +18231,10 @@
         </is>
       </c>
       <c r="J219" s="2" t="n">
-        <v>46111.42803700231</v>
+        <v>46180.49354722222</v>
       </c>
       <c r="K219" s="2" t="n">
-        <v>46122</v>
+        <v>46182</v>
       </c>
       <c r="L219" s="1" t="inlineStr">
         <is>
@@ -18257,7 +18243,7 @@
       </c>
       <c r="M219" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Andrea Medeiros</t>
         </is>
       </c>
       <c r="N219" s="1" t="n"/>
@@ -18275,7 +18261,7 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>79733</v>
+        <v>79731</v>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
@@ -18294,20 +18280,20 @@
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t>AGUARDANDO RETORNO DESDE 26/06/2026 - ANALISE ENVIADA E-MAIL</t>
+          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
         </is>
       </c>
       <c r="F220" s="1" t="n">
-        <v>1556</v>
+        <v>1931</v>
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t>GENGIBRE ADMINISTRACAO E PARTICIPACOES S.A.</t>
+          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
         <is>
-          <t>Karine Gusmão</t>
+          <t>Luiz Ferreira</t>
         </is>
       </c>
       <c r="I220" s="1" t="inlineStr">
@@ -18316,10 +18302,10 @@
         </is>
       </c>
       <c r="J220" s="2" t="n">
-        <v>46180.49354722222</v>
+        <v>46180.44674649306</v>
       </c>
       <c r="K220" s="2" t="n">
-        <v>46182</v>
+        <v>46185</v>
       </c>
       <c r="L220" s="1" t="inlineStr">
         <is>
@@ -18342,20 +18328,24 @@
         </is>
       </c>
       <c r="T220" s="1" t="n"/>
-      <c r="U220" s="1" t="inlineStr"/>
+      <c r="U220" s="1" t="inlineStr">
+        <is>
+          <t>Erika Santana</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>79731</v>
+        <v>78322</v>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>Malha Fiscal</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t>Autorregularização</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
@@ -18365,20 +18355,20 @@
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t>RETIFICAR DCTF ANO BASE 2023 - CONFORME EMAIL ENVIADO AO CLIENTE EM 27/05/2026</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F221" s="1" t="n">
-        <v>1931</v>
+        <v>2209</v>
       </c>
       <c r="G221" s="1" t="inlineStr">
         <is>
-          <t>GRILD - PLASTIC INDÚSTRIA, COMÉRCIO E IMPORTAÇÃO LTDA</t>
+          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
         </is>
       </c>
       <c r="H221" s="1" t="inlineStr">
         <is>
-          <t>Luiz Ferreira</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I221" s="1" t="inlineStr">
@@ -18387,10 +18377,10 @@
         </is>
       </c>
       <c r="J221" s="2" t="n">
-        <v>46180.44674649306</v>
+        <v>46111.44774475694</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>46185</v>
+        <v>46122</v>
       </c>
       <c r="L221" s="1" t="inlineStr">
         <is>
@@ -18399,7 +18389,7 @@
       </c>
       <c r="M221" s="1" t="inlineStr">
         <is>
-          <t>Andrea Medeiros</t>
+          <t>Taina Silva</t>
         </is>
       </c>
       <c r="N221" s="1" t="n"/>
@@ -18413,47 +18403,43 @@
         </is>
       </c>
       <c r="T221" s="1" t="n"/>
-      <c r="U221" s="1" t="inlineStr">
-        <is>
-          <t>Erika Santana</t>
-        </is>
-      </c>
+      <c r="U221" s="1" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>78322</v>
+        <v>80013</v>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>Apontamentos</t>
+          <t>Certificado</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
         <is>
-          <t>Inclusão de Ata</t>
+          <t>Certificado digital</t>
         </is>
       </c>
       <c r="D222" s="1" t="inlineStr">
         <is>
-          <t>EF - INDUSTRIA</t>
+          <t>CTB - CONTÁBIL VAREJO</t>
         </is>
       </c>
       <c r="E222" s="1" t="inlineStr">
         <is>
-          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
+          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
         </is>
       </c>
       <c r="F222" s="1" t="n">
-        <v>2209</v>
+        <v>2480</v>
       </c>
       <c r="G222" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">TENDAS PROMOCIONAIS INDUSTRIA E COMÉRCIO LTDA </t>
+          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
         </is>
       </c>
       <c r="H222" s="1" t="inlineStr">
         <is>
-          <t>Beatriz Rangel</t>
+          <t>Daniela Silva</t>
         </is>
       </c>
       <c r="I222" s="1" t="inlineStr">
@@ -18462,10 +18448,10 @@
         </is>
       </c>
       <c r="J222" s="2" t="n">
-        <v>46111.44774475694</v>
+        <v>46188.46272334491</v>
       </c>
       <c r="K222" s="2" t="n">
-        <v>46122</v>
+        <v>46189</v>
       </c>
       <c r="L222" s="1" t="inlineStr">
         <is>
@@ -18474,7 +18460,7 @@
       </c>
       <c r="M222" s="1" t="inlineStr">
         <is>
-          <t>Taina Silva</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N222" s="1" t="n"/>
@@ -18492,7 +18478,7 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>80013</v>
+        <v>80039</v>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
@@ -18511,15 +18497,15 @@
       </c>
       <c r="E223" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza verificar pois o certificado venceu2480	Marques Distribuidora de Horti Frutti Transportes Ltda	17.515.145/0001-28</t>
+          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
         </is>
       </c>
       <c r="F223" s="1" t="n">
-        <v>2480</v>
+        <v>2491</v>
       </c>
       <c r="G223" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARQUES DISTRIBUIDORA DE HORTI FRUTTI TRANSPORTES LTDA </t>
+          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
         </is>
       </c>
       <c r="H223" s="1" t="inlineStr">
@@ -18533,7 +18519,7 @@
         </is>
       </c>
       <c r="J223" s="2" t="n">
-        <v>46188.46272334491</v>
+        <v>46188.58172743056</v>
       </c>
       <c r="K223" s="2" t="n">
         <v>46189</v>
@@ -18545,7 +18531,7 @@
       </c>
       <c r="M223" s="1" t="inlineStr">
         <is>
-          <t>Edileide Dias</t>
+          <t>Ana Barbosa</t>
         </is>
       </c>
       <c r="N223" s="1" t="n"/>
@@ -18563,7 +18549,7 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>80039</v>
+        <v>80014</v>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
@@ -18582,15 +18568,15 @@
       </c>
       <c r="E224" s="1" t="inlineStr">
         <is>
-          <t>Boa tarde por gentileza verificar, pois não temos procuração eletronica para sdd</t>
+          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
         </is>
       </c>
       <c r="F224" s="1" t="n">
-        <v>2491</v>
+        <v>2500</v>
       </c>
       <c r="G224" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HARVEST HORTIFRUTTI LTDA </t>
+          <t>CAEFHOLD Participações S.A.</t>
         </is>
       </c>
       <c r="H224" s="1" t="inlineStr">
@@ -18604,7 +18590,7 @@
         </is>
       </c>
       <c r="J224" s="2" t="n">
-        <v>46188.58172743056</v>
+        <v>46188.46337480324</v>
       </c>
       <c r="K224" s="2" t="n">
         <v>46189</v>
@@ -18616,7 +18602,7 @@
       </c>
       <c r="M224" s="1" t="inlineStr">
         <is>
-          <t>Ana Barbosa</t>
+          <t>Edileide Dias</t>
         </is>
       </c>
       <c r="N224" s="1" t="n"/>
@@ -18634,39 +18620,39 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>80014</v>
+        <v>78304</v>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>Certificado</t>
+          <t>Apontamentos</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
         <is>
-          <t>Certificado digital</t>
+          <t>Inclusão de Ata</t>
         </is>
       </c>
       <c r="D225" s="1" t="inlineStr">
         <is>
-          <t>CTB - CONTÁBIL VAREJO</t>
+          <t>EF - INDUSTRIA</t>
         </is>
       </c>
       <c r="E225" s="1" t="inlineStr">
         <is>
-          <t>Por gentileza disponibilizar o ecpf do socio2500	CAEFHOLD Participações S.A.	17.655.772/0001-64	ANTONIO VAZ SILVA</t>
+          <t>O cliente em questão precisa nos enviar o controle de estoque - bloco K - Sendo assim, precisamos trabalhar juntos nesse quesito para nos respaldarmos em possíveis fiscalização e/ou intimação. Obrigatoriedade de entrega do Bloco K (Livro Registro de Controle da Produção e do Estoque):Obrigados:Empresas industriais ou equiparadas a industrial, enquadradas como:Estabelecimentos industriais dos seguintes CNAEs (de acordo com a Tabela de CNAEs da Receita Federal):Especialmente empresas do Lucro Real ou Lucro Presumido;Principalmente as dos setores de bebidas, alimentos, automotivo, metalurgia, químico, entre outros.Estabelecimentos atacadistas de determinados setores (obrigatoriedade progressiva, dependendo do CNAE e faturamento);Empresas com faturamento anual superior a R$ 300 milhões, conforme escalonamento determinado pelo Ajuste SINIEF 02/2009 e suas alterações.Empresas do Simples Nacional geralmente estão dispensadas, mas é sempre bom verificar legislações estaduais.? Observações importantes: A obrigatoriedade varia conforme o Estado, pois alguns exigem mais informações ou já anteciparam prazos.O Bloco K exige detalhamento mensal de:Insumos consumidos, Produção realizada, Estoque inicial e final,Terceirizações (envio e recebimento de industrialização). Em anexo a planilha modelo que deverá ser preenchida.</t>
         </is>
       </c>
       <c r="F225" s="1" t="n">
-        <v>2500</v>
+        <v>2620</v>
       </c>
       <c r="G225" s="1" t="inlineStr">
         <is>
-          <t>CAEFHOLD Participações S.A.</t>
+          <t>ANTOCON GALVANOPLASTIA LTDA</t>
         </is>
       </c>
       <c r="H225" s="1" t="inlineStr">
         <is>
-          <t>Daniela Silva</t>
+          <t>Beatriz Rangel</t>
         </is>
       </c>
       <c r="I225" s="1" t="inlineStr">
@@ -18675,10 +18661,10 @@
         </is>
       </c>
       <c r="J225" s="2" t="n">
-        <v>46188.46337480324</v>
+        <v>46111.42458850695</v>
       </c>
       <c r="K225" s="2" t="n">
-        <v>46189</v>
+        <v>46122</v>
       </c>
       <c r="L225" s="1" t="inlineStr">
 